--- a/data/IMS.MI.xlsx
+++ b/data/IMS.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>96960</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>0.523000001907349</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>0.510999977588654</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>0.513000011444092</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>0.514999985694885</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IMS.MI.xlsx
+++ b/data/IMS.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>314957</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>0.518999993801117</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>0.513999998569489</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>0.517000019550323</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>0.51800000667572</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IMS.MI.xlsx
+++ b/data/IMS.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>276267</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>0.521000027656555</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>0.507000029087067</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>0.510999977588654</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>0.508000016212463</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IMS.MI.xlsx
+++ b/data/IMS.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>156660</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>0.519999980926514</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>0.513000011444092</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>0.517000019550323</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>0.521000027656555</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IMS.MI.xlsx
+++ b/data/IMS.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>67154</v>
+        <v>134640</v>
       </c>
       <c r="C2715" t="n">
-        <v>0.512000024318695</v>
+        <v>0.517000019550323</v>
       </c>
       <c r="D2715" t="n">
-        <v>0.504000008106232</v>
+        <v>0.500999987125397</v>
       </c>
       <c r="E2715" t="n">
-        <v>0.504000008106232</v>
+        <v>0.517000019550323</v>
       </c>
       <c r="F2715" t="n">
-        <v>0.509999990463257</v>
+        <v>0.504999995231628</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>97519</v>
+        <v>67154</v>
       </c>
       <c r="C2716" t="n">
-        <v>0.510999977588654</v>
+        <v>0.512000024318695</v>
       </c>
       <c r="D2716" t="n">
         <v>0.504000008106232</v>
       </c>
       <c r="E2716" t="n">
+        <v>0.504000008106232</v>
+      </c>
+      <c r="F2716" t="n">
         <v>0.509999990463257</v>
-      </c>
-      <c r="F2716" t="n">
-        <v>0.505999982357025</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>1485430</v>
+        <v>97519</v>
       </c>
       <c r="C2717" t="n">
-        <v>0.540000021457672</v>
+        <v>0.510999977588654</v>
       </c>
       <c r="D2717" t="n">
+        <v>0.504000008106232</v>
+      </c>
+      <c r="E2717" t="n">
+        <v>0.509999990463257</v>
+      </c>
+      <c r="F2717" t="n">
         <v>0.505999982357025</v>
-      </c>
-      <c r="E2717" t="n">
-        <v>0.505999982357025</v>
-      </c>
-      <c r="F2717" t="n">
-        <v>0.524999976158142</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>499146</v>
+        <v>1485430</v>
       </c>
       <c r="C2718" t="n">
-        <v>0.523999989032745</v>
+        <v>0.540000021457672</v>
       </c>
       <c r="D2718" t="n">
-        <v>0.514999985694885</v>
+        <v>0.505999982357025</v>
       </c>
       <c r="E2718" t="n">
-        <v>0.518999993801117</v>
+        <v>0.505999982357025</v>
       </c>
       <c r="F2718" t="n">
-        <v>0.518999993801117</v>
+        <v>0.524999976158142</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>96960</v>
+        <v>499146</v>
       </c>
       <c r="C2719" t="n">
-        <v>0.523000001907349</v>
+        <v>0.523999989032745</v>
       </c>
       <c r="D2719" t="n">
-        <v>0.510999977588654</v>
+        <v>0.514999985694885</v>
       </c>
       <c r="E2719" t="n">
-        <v>0.513000011444092</v>
+        <v>0.518999993801117</v>
       </c>
       <c r="F2719" t="n">
-        <v>0.514999985694885</v>
+        <v>0.518999993801117</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>314957</v>
+        <v>96960</v>
       </c>
       <c r="C2720" t="n">
-        <v>0.518999993801117</v>
+        <v>0.523000001907349</v>
       </c>
       <c r="D2720" t="n">
-        <v>0.513999998569489</v>
+        <v>0.510999977588654</v>
       </c>
       <c r="E2720" t="n">
-        <v>0.517000019550323</v>
+        <v>0.513000011444092</v>
       </c>
       <c r="F2720" t="n">
-        <v>0.51800000667572</v>
+        <v>0.514999985694885</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>276267</v>
+        <v>314957</v>
       </c>
       <c r="C2721" t="n">
-        <v>0.521000027656555</v>
+        <v>0.518999993801117</v>
       </c>
       <c r="D2721" t="n">
-        <v>0.507000029087067</v>
+        <v>0.513999998569489</v>
       </c>
       <c r="E2721" t="n">
-        <v>0.510999977588654</v>
+        <v>0.517000019550323</v>
       </c>
       <c r="F2721" t="n">
-        <v>0.508000016212463</v>
+        <v>0.51800000667572</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>156660</v>
+        <v>276267</v>
       </c>
       <c r="C2722" t="n">
-        <v>0.519999980926514</v>
+        <v>0.521000027656555</v>
       </c>
       <c r="D2722" t="n">
-        <v>0.513000011444092</v>
+        <v>0.507000029087067</v>
       </c>
       <c r="E2722" t="n">
+        <v>0.510999977588654</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>0.508000016212463</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>380146</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>0.515999972820282</v>
+      </c>
+      <c r="E2723" t="n">
         <v>0.517000019550323</v>
       </c>
-      <c r="F2722" t="n">
-        <v>0.521000027656555</v>
-      </c>
-      <c r="G2722" t="s">
+      <c r="F2723" t="n">
+        <v>0.550999999046326</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/IMS.MI.xlsx
+++ b/data/IMS.MI.xlsx
@@ -525,7 +525,7 @@
         <v>0.415300011634827</v>
       </c>
       <c r="G6" t="n">
-        <v>0.307318478822708</v>
+        <v>0.307318508625031</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>0.386000007390976</v>
       </c>
       <c r="G10" t="n">
-        <v>0.285636723041534</v>
+        <v>0.285636752843857</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>0.370000004768372</v>
       </c>
       <c r="G11" t="n">
-        <v>0.273796826601028</v>
+        <v>0.273796856403351</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>0.349999994039536</v>
       </c>
       <c r="G12" t="n">
-        <v>0.258997023105621</v>
+        <v>0.258997052907944</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>0.329199999570847</v>
       </c>
       <c r="G14" t="n">
-        <v>0.243605226278305</v>
+        <v>0.243605211377144</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>0.333000004291534</v>
       </c>
       <c r="G15" t="n">
-        <v>0.246417209506035</v>
+        <v>0.246417179703712</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>0.354999989271164</v>
       </c>
       <c r="G16" t="n">
-        <v>0.262696981430054</v>
+        <v>0.262697011232376</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>0.346500009298325</v>
       </c>
       <c r="G17" t="n">
-        <v>0.256407052278519</v>
+        <v>0.256407082080841</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>0.351099997758865</v>
       </c>
       <c r="G18" t="n">
-        <v>0.259811013936996</v>
+        <v>0.259811043739319</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>0.387699991464615</v>
       </c>
       <c r="G22" t="n">
-        <v>0.286894738674164</v>
+        <v>0.286894708871841</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>0.384600013494492</v>
       </c>
       <c r="G23" t="n">
-        <v>0.284600734710693</v>
+        <v>0.284600764513016</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>0.388000011444092</v>
       </c>
       <c r="G25" t="n">
-        <v>0.287116706371307</v>
+        <v>0.28711673617363</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>0.392899990081787</v>
       </c>
       <c r="G26" t="n">
-        <v>0.290742635726929</v>
+        <v>0.290742665529251</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>0.354999989271164</v>
       </c>
       <c r="G29" t="n">
-        <v>0.262696981430054</v>
+        <v>0.262697011232376</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>0.337999999523163</v>
       </c>
       <c r="G30" t="n">
-        <v>0.250117152929306</v>
+        <v>0.250117123126984</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>0.349999994039536</v>
       </c>
       <c r="G31" t="n">
-        <v>0.258997023105621</v>
+        <v>0.258997052907944</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>0.375099986791611</v>
       </c>
       <c r="G33" t="n">
-        <v>0.277570843696594</v>
+        <v>0.277570784091949</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>0.402700006961823</v>
       </c>
       <c r="G34" t="n">
-        <v>0.297994613647461</v>
+        <v>0.297994583845139</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G35" t="n">
-        <v>0.310796439647675</v>
+        <v>0.310796469449997</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>0.411300003528595</v>
       </c>
       <c r="G37" t="n">
-        <v>0.304358541965485</v>
+        <v>0.304358512163162</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>0.437000006437302</v>
       </c>
       <c r="G42" t="n">
-        <v>0.323376297950745</v>
+        <v>0.323376357555389</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>0.449000000953674</v>
       </c>
       <c r="G48" t="n">
-        <v>0.332256227731705</v>
+        <v>0.332256197929382</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>0.42059999704361</v>
       </c>
       <c r="G51" t="n">
-        <v>0.311240404844284</v>
+        <v>0.311240434646606</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>0.405000001192093</v>
       </c>
       <c r="G53" t="n">
-        <v>0.299696534872055</v>
+        <v>0.299696564674377</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>0.401199996471405</v>
       </c>
       <c r="G54" t="n">
-        <v>0.296884566545486</v>
+        <v>0.296884596347809</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>0.404599994421005</v>
       </c>
       <c r="G55" t="n">
-        <v>0.299400568008423</v>
+        <v>0.2994005382061</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>0.40200001001358</v>
       </c>
       <c r="G56" t="n">
-        <v>0.297476589679718</v>
+        <v>0.29747661948204</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G57" t="n">
-        <v>0.295996606349945</v>
+        <v>0.295996636152267</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>0.396899998188019</v>
       </c>
       <c r="G58" t="n">
-        <v>0.293702661991119</v>
+        <v>0.293702632188797</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>0.402700006961823</v>
       </c>
       <c r="G60" t="n">
-        <v>0.297994613647461</v>
+        <v>0.297994583845139</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>0.387699991464615</v>
       </c>
       <c r="G61" t="n">
-        <v>0.286894738674164</v>
+        <v>0.286894708871841</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>0.386999994516373</v>
       </c>
       <c r="G62" t="n">
-        <v>0.286376744508743</v>
+        <v>0.286376714706421</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>0.374000012874603</v>
       </c>
       <c r="G63" t="n">
-        <v>0.276756882667542</v>
+        <v>0.276756823062897</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>0.362899988889694</v>
       </c>
       <c r="G66" t="n">
-        <v>0.268542945384979</v>
+        <v>0.268542915582657</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>0.365500003099442</v>
       </c>
       <c r="G67" t="n">
-        <v>0.270466893911362</v>
+        <v>0.270466864109039</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>0.362399995326996</v>
       </c>
       <c r="G69" t="n">
-        <v>0.268172979354858</v>
+        <v>0.268172919750214</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>0.363000005483627</v>
       </c>
       <c r="G70" t="n">
-        <v>0.268616944551468</v>
+        <v>0.268616914749146</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>0.36379998922348</v>
       </c>
       <c r="G71" t="n">
-        <v>0.269208908081055</v>
+        <v>0.269208878278732</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>0.372000008821487</v>
       </c>
       <c r="G72" t="n">
-        <v>0.275276839733124</v>
+        <v>0.275276869535446</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>0.39190000295639</v>
       </c>
       <c r="G76" t="n">
-        <v>0.290002703666687</v>
+        <v>0.290002673864365</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>0.405000001192093</v>
       </c>
       <c r="G77" t="n">
-        <v>0.299696534872055</v>
+        <v>0.299696564674377</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>0.417800009250641</v>
       </c>
       <c r="G79" t="n">
-        <v>0.309168517589569</v>
+        <v>0.309168457984924</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G80" t="n">
-        <v>0.318196356296539</v>
+        <v>0.318196386098862</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>0.428299993276596</v>
       </c>
       <c r="G81" t="n">
-        <v>0.31693834066391</v>
+        <v>0.316938370466232</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>0.424600005149841</v>
       </c>
       <c r="G83" t="n">
-        <v>0.31420037150383</v>
+        <v>0.314200431108475</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>0.431600004434586</v>
       </c>
       <c r="G85" t="n">
-        <v>0.31938037276268</v>
+        <v>0.319380342960358</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>0.419900000095367</v>
       </c>
       <c r="G86" t="n">
-        <v>0.310722440481186</v>
+        <v>0.310722470283508</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>0.423900008201599</v>
       </c>
       <c r="G87" t="n">
-        <v>0.313682407140732</v>
+        <v>0.313682436943054</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>0.423400014638901</v>
       </c>
       <c r="G88" t="n">
-        <v>0.313312381505966</v>
+        <v>0.313312411308289</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>0.41499999165535</v>
       </c>
       <c r="G89" t="n">
-        <v>0.307096481323242</v>
+        <v>0.30709645152092</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>0.401199996471405</v>
       </c>
       <c r="G90" t="n">
-        <v>0.296884566545486</v>
+        <v>0.296884596347809</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>0.405000001192093</v>
       </c>
       <c r="G91" t="n">
-        <v>0.299696534872055</v>
+        <v>0.299696564674377</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G92" t="n">
-        <v>0.295996606349945</v>
+        <v>0.295996636152267</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>0.412099987268448</v>
       </c>
       <c r="G94" t="n">
-        <v>0.304950535297394</v>
+        <v>0.304950475692749</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>0.404799997806549</v>
       </c>
       <c r="G96" t="n">
-        <v>0.299548536539078</v>
+        <v>0.2995485663414</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>0.399500012397766</v>
       </c>
       <c r="G98" t="n">
-        <v>0.295626610517502</v>
+        <v>0.295626640319824</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>0.414900004863739</v>
       </c>
       <c r="G101" t="n">
-        <v>0.318779796361923</v>
+        <v>0.318779826164246</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>0.416399985551834</v>
       </c>
       <c r="G104" t="n">
-        <v>0.319932281970978</v>
+        <v>0.319932252168655</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G109" t="n">
-        <v>0.307331681251526</v>
+        <v>0.307331711053848</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>0.416999995708466</v>
       </c>
       <c r="G112" t="n">
-        <v>0.320393294095993</v>
+        <v>0.320393264293671</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>0.405499994754791</v>
       </c>
       <c r="G113" t="n">
-        <v>0.311557501554489</v>
+        <v>0.311557471752167</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>0.398000001907349</v>
       </c>
       <c r="G114" t="n">
-        <v>0.305795013904572</v>
+        <v>0.305795043706894</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>0.392500013113022</v>
       </c>
       <c r="G115" t="n">
-        <v>0.301569253206253</v>
+        <v>0.301569223403931</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G120" t="n">
-        <v>0.314246654510498</v>
+        <v>0.31424668431282</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>0.414799988269806</v>
       </c>
       <c r="G122" t="n">
-        <v>0.318702936172485</v>
+        <v>0.318702965974808</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G123" t="n">
-        <v>0.32116162776947</v>
+        <v>0.321161597967148</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>0.403499990701675</v>
       </c>
       <c r="G124" t="n">
-        <v>0.310020834207535</v>
+        <v>0.310020804405212</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G128" t="n">
-        <v>0.307331681251526</v>
+        <v>0.307331711053848</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G129" t="n">
-        <v>0.307331681251526</v>
+        <v>0.307331711053848</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G130" t="n">
-        <v>0.307331681251526</v>
+        <v>0.307331711053848</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>0.399899989366531</v>
       </c>
       <c r="G131" t="n">
-        <v>0.307254821062088</v>
+        <v>0.30725485086441</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G133" t="n">
-        <v>0.307331681251526</v>
+        <v>0.307331711053848</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>0.397700011730194</v>
       </c>
       <c r="G134" t="n">
-        <v>0.305564492940903</v>
+        <v>0.30556458234787</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G135" t="n">
-        <v>0.307331681251526</v>
+        <v>0.307331711053848</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G136" t="n">
-        <v>0.307331681251526</v>
+        <v>0.307331711053848</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>0.398000001907349</v>
       </c>
       <c r="G137" t="n">
-        <v>0.305795013904572</v>
+        <v>0.305795043706894</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G138" t="n">
-        <v>0.307331681251526</v>
+        <v>0.307331711053848</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>0.396899998188019</v>
       </c>
       <c r="G139" t="n">
-        <v>0.304949849843979</v>
+        <v>0.304949879646301</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>0.399399995803833</v>
       </c>
       <c r="G141" t="n">
-        <v>0.306870669126511</v>
+        <v>0.306870639324188</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>0.387499988079071</v>
       </c>
       <c r="G142" t="n">
-        <v>0.297727584838867</v>
+        <v>0.297727555036545</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>0.389299988746643</v>
       </c>
       <c r="G152" t="n">
-        <v>0.299110531806946</v>
+        <v>0.299110561609268</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>0.397300004959106</v>
       </c>
       <c r="G153" t="n">
-        <v>0.305257171392441</v>
+        <v>0.305257230997086</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>0.397300004959106</v>
       </c>
       <c r="G154" t="n">
-        <v>0.305257171392441</v>
+        <v>0.305257230997086</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>0.385199993848801</v>
       </c>
       <c r="G156" t="n">
-        <v>0.295960426330566</v>
+        <v>0.295960396528244</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>0.387699991464615</v>
       </c>
       <c r="G158" t="n">
-        <v>0.297881215810776</v>
+        <v>0.297881275415421</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>0.387699991464615</v>
       </c>
       <c r="G159" t="n">
-        <v>0.297881215810776</v>
+        <v>0.297881275415421</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>0.382299989461899</v>
       </c>
       <c r="G160" t="n">
-        <v>0.293732196092606</v>
+        <v>0.29373225569725</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>0.391000002622604</v>
       </c>
       <c r="G163" t="n">
-        <v>0.300416737794876</v>
+        <v>0.300416707992554</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>0.402900010347366</v>
       </c>
       <c r="G170" t="n">
-        <v>0.30955982208252</v>
+        <v>0.309559881687164</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>0.394499987363815</v>
       </c>
       <c r="G171" t="n">
-        <v>0.30310583114624</v>
+        <v>0.303105890750885</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>0.395099997520447</v>
       </c>
       <c r="G172" t="n">
-        <v>0.303566873073578</v>
+        <v>0.303566843271255</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>0.401199996471405</v>
       </c>
       <c r="G173" t="n">
-        <v>0.308253675699234</v>
+        <v>0.308253645896912</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G174" t="n">
-        <v>0.307331681251526</v>
+        <v>0.307331711053848</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>0.396800011396408</v>
       </c>
       <c r="G175" t="n">
-        <v>0.304873079061508</v>
+        <v>0.304873019456863</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G176" t="n">
-        <v>0.307331681251526</v>
+        <v>0.307331711053848</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>0.39070001244545</v>
       </c>
       <c r="G178" t="n">
-        <v>0.30018624663353</v>
+        <v>0.300186216831207</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>0.388700008392334</v>
       </c>
       <c r="G179" t="n">
-        <v>0.298649579286575</v>
+        <v>0.298649609088898</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>0.385800004005432</v>
       </c>
       <c r="G180" t="n">
-        <v>0.296421378850937</v>
+        <v>0.296421408653259</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>0.392300009727478</v>
       </c>
       <c r="G181" t="n">
-        <v>0.301415592432022</v>
+        <v>0.3014155626297</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>0.391299992799759</v>
       </c>
       <c r="G182" t="n">
-        <v>0.300647228956223</v>
+        <v>0.300647258758545</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>0.36829999089241</v>
       </c>
       <c r="G183" t="n">
-        <v>0.282975614070892</v>
+        <v>0.282975643873215</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>0.379999995231628</v>
       </c>
       <c r="G184" t="n">
-        <v>0.291965067386627</v>
+        <v>0.291965126991272</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>0.377099990844727</v>
       </c>
       <c r="G185" t="n">
-        <v>0.289736926555634</v>
+        <v>0.289736956357956</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>0.379999995231628</v>
       </c>
       <c r="G186" t="n">
-        <v>0.291965067386627</v>
+        <v>0.291965126991272</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>0.380899995565414</v>
       </c>
       <c r="G188" t="n">
-        <v>0.292656630277634</v>
+        <v>0.292656600475311</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>0.381500005722046</v>
       </c>
       <c r="G196" t="n">
-        <v>0.293117582798004</v>
+        <v>0.293117612600327</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>0.37720000743866</v>
       </c>
       <c r="G198" t="n">
-        <v>0.289813786745071</v>
+        <v>0.289813756942749</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>0.372999995946884</v>
       </c>
       <c r="G199" t="n">
-        <v>0.286586791276932</v>
+        <v>0.286586821079254</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>0.381500005722046</v>
       </c>
       <c r="G200" t="n">
-        <v>0.293117582798004</v>
+        <v>0.293117612600327</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>0.379999995231628</v>
       </c>
       <c r="G202" t="n">
-        <v>0.291965067386627</v>
+        <v>0.291965126991272</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>0.380800008773804</v>
       </c>
       <c r="G204" t="n">
-        <v>0.292579799890518</v>
+        <v>0.292579770088196</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>0.384900003671646</v>
       </c>
       <c r="G205" t="n">
-        <v>0.29572993516922</v>
+        <v>0.295729905366898</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>0.388399988412857</v>
       </c>
       <c r="G206" t="n">
-        <v>0.298419028520584</v>
+        <v>0.298419088125229</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>0.388399988412857</v>
       </c>
       <c r="G207" t="n">
-        <v>0.298419028520584</v>
+        <v>0.298419088125229</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>0.388399988412857</v>
       </c>
       <c r="G208" t="n">
-        <v>0.298419028520584</v>
+        <v>0.298419088125229</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>0.383599996566772</v>
       </c>
       <c r="G209" t="n">
-        <v>0.294731080532074</v>
+        <v>0.294731110334396</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>0.379999995231628</v>
       </c>
       <c r="G211" t="n">
-        <v>0.291965067386627</v>
+        <v>0.291965126991272</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>0.374000012874603</v>
       </c>
       <c r="G212" t="n">
-        <v>0.287355154752731</v>
+        <v>0.287355124950409</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>0.379999995231628</v>
       </c>
       <c r="G213" t="n">
-        <v>0.291965067386627</v>
+        <v>0.291965126991272</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>0.382400006055832</v>
       </c>
       <c r="G214" t="n">
-        <v>0.293809115886688</v>
+        <v>0.293809086084366</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>0.373199999332428</v>
       </c>
       <c r="G216" t="n">
-        <v>0.286740481853485</v>
+        <v>0.286740452051163</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>0.351700007915497</v>
       </c>
       <c r="G221" t="n">
-        <v>0.270221382379532</v>
+        <v>0.270221412181854</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>0.354600012302399</v>
       </c>
       <c r="G222" t="n">
-        <v>0.272449553012848</v>
+        <v>0.27244958281517</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>0.360100001096725</v>
       </c>
       <c r="G223" t="n">
-        <v>0.276675343513489</v>
+        <v>0.276675373315811</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>0.356599986553192</v>
       </c>
       <c r="G224" t="n">
-        <v>0.273986130952835</v>
+        <v>0.27398619055748</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>0.360000014305115</v>
       </c>
       <c r="G228" t="n">
-        <v>0.276598542928696</v>
+        <v>0.276598513126373</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>0.360000014305115</v>
       </c>
       <c r="G230" t="n">
-        <v>0.276598542928696</v>
+        <v>0.276598513126373</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>0.352899998426437</v>
       </c>
       <c r="G231" t="n">
-        <v>0.27114337682724</v>
+        <v>0.271143347024918</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>0.35699999332428</v>
       </c>
       <c r="G232" t="n">
-        <v>0.274293541908264</v>
+        <v>0.274293512105942</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>0.351999998092651</v>
       </c>
       <c r="G233" t="n">
-        <v>0.270451903343201</v>
+        <v>0.270451873540878</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>0.349000006914139</v>
       </c>
       <c r="G234" t="n">
-        <v>0.268146902322769</v>
+        <v>0.268146932125092</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>0.345899999141693</v>
       </c>
       <c r="G237" t="n">
-        <v>0.265765100717545</v>
+        <v>0.265765070915222</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>0.341500014066696</v>
       </c>
       <c r="G238" t="n">
-        <v>0.262384414672852</v>
+        <v>0.262384444475174</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>0.348199993371964</v>
       </c>
       <c r="G239" t="n">
-        <v>0.267532229423523</v>
+        <v>0.267532199621201</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>0.345299988985062</v>
       </c>
       <c r="G240" t="n">
-        <v>0.265304088592529</v>
+        <v>0.265304058790207</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>0.354699999094009</v>
       </c>
       <c r="G243" t="n">
-        <v>0.272526383399963</v>
+        <v>0.272526353597641</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>0.368699997663498</v>
       </c>
       <c r="G244" t="n">
-        <v>0.283283025026321</v>
+        <v>0.283282965421677</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>0.364300012588501</v>
       </c>
       <c r="G245" t="n">
-        <v>0.279902338981628</v>
+        <v>0.279902309179306</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>0.360000014305115</v>
       </c>
       <c r="G250" t="n">
-        <v>0.276598542928696</v>
+        <v>0.276598513126373</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>0.362100005149841</v>
       </c>
       <c r="G255" t="n">
-        <v>0.278212010860443</v>
+        <v>0.278212040662766</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>0.360000014305115</v>
       </c>
       <c r="G256" t="n">
-        <v>0.276598542928696</v>
+        <v>0.276598513126373</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>0.378500014543533</v>
       </c>
       <c r="G258" t="n">
-        <v>0.290812611579895</v>
+        <v>0.290812641382217</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>0.383700013160706</v>
       </c>
       <c r="G261" t="n">
-        <v>0.294807940721512</v>
+        <v>0.294807970523834</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>0.384499996900558</v>
       </c>
       <c r="G263" t="n">
-        <v>0.295422554016113</v>
+        <v>0.295422583818436</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>0.375499993562698</v>
       </c>
       <c r="G265" t="n">
-        <v>0.288507610559464</v>
+        <v>0.288507580757141</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>0.378800004720688</v>
       </c>
       <c r="G268" t="n">
-        <v>0.291043132543564</v>
+        <v>0.291043102741241</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>0.388700008392334</v>
       </c>
       <c r="G270" t="n">
-        <v>0.298649579286575</v>
+        <v>0.298649609088898</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>0.384499996900558</v>
       </c>
       <c r="G274" t="n">
-        <v>0.295422554016113</v>
+        <v>0.295422583818436</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>0.384900003671646</v>
       </c>
       <c r="G276" t="n">
-        <v>0.29572993516922</v>
+        <v>0.295729905366898</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>0.372399985790253</v>
       </c>
       <c r="G278" t="n">
-        <v>0.286125779151917</v>
+        <v>0.286125808954239</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>0.370099991559982</v>
       </c>
       <c r="G279" t="n">
-        <v>0.284358620643616</v>
+        <v>0.284358650445938</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>0.368000000715256</v>
       </c>
       <c r="G280" t="n">
-        <v>0.282745122909546</v>
+        <v>0.282745152711868</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>0.360900014638901</v>
       </c>
       <c r="G281" t="n">
-        <v>0.277290016412735</v>
+        <v>0.277289986610413</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>0.359499990940094</v>
       </c>
       <c r="G283" t="n">
-        <v>0.276214331388474</v>
+        <v>0.276214301586151</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>0.351099997758865</v>
       </c>
       <c r="G285" t="n">
-        <v>0.269760400056839</v>
+        <v>0.269760370254517</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>0.353799998760223</v>
       </c>
       <c r="G287" t="n">
-        <v>0.271834880113602</v>
+        <v>0.271834909915924</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>0.358200013637543</v>
       </c>
       <c r="G289" t="n">
-        <v>0.27521550655365</v>
+        <v>0.275215536355972</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>0.36039999127388</v>
       </c>
       <c r="G290" t="n">
-        <v>0.276905804872513</v>
+        <v>0.276905834674835</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>0.35699999332428</v>
       </c>
       <c r="G291" t="n">
-        <v>0.274293541908264</v>
+        <v>0.274293512105942</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>0.364300012588501</v>
       </c>
       <c r="G292" t="n">
-        <v>0.279902338981628</v>
+        <v>0.279902309179306</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>0.367900013923645</v>
       </c>
       <c r="G294" t="n">
-        <v>0.282668352127075</v>
+        <v>0.282668322324753</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>0.365000009536743</v>
       </c>
       <c r="G295" t="n">
-        <v>0.280440151691437</v>
+        <v>0.280440181493759</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>0.361000001430511</v>
       </c>
       <c r="G297" t="n">
-        <v>0.27736684679985</v>
+        <v>0.277366876602173</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>0.361999988555908</v>
       </c>
       <c r="G298" t="n">
-        <v>0.278135120868683</v>
+        <v>0.278135150671005</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>0.36599999666214</v>
       </c>
       <c r="G299" t="n">
-        <v>0.281208544969559</v>
+        <v>0.281208485364914</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>0.36269998550415</v>
       </c>
       <c r="G301" t="n">
-        <v>0.278672993183136</v>
+        <v>0.278672963380814</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>0.363599985837936</v>
       </c>
       <c r="G303" t="n">
-        <v>0.279364496469498</v>
+        <v>0.279364466667175</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>0.37169998884201</v>
       </c>
       <c r="G304" t="n">
-        <v>0.285587966442108</v>
+        <v>0.285587996244431</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>0.368000000715256</v>
       </c>
       <c r="G310" t="n">
-        <v>0.282745122909546</v>
+        <v>0.282745152711868</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>0.369500011205673</v>
       </c>
       <c r="G311" t="n">
-        <v>0.283897697925568</v>
+        <v>0.283897638320923</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>0.36829999089241</v>
       </c>
       <c r="G312" t="n">
-        <v>0.282975614070892</v>
+        <v>0.282975643873215</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>0.371300011873245</v>
       </c>
       <c r="G313" t="n">
-        <v>0.285280615091324</v>
+        <v>0.285280674695969</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>0.371499985456467</v>
       </c>
       <c r="G314" t="n">
-        <v>0.285434305667877</v>
+        <v>0.285434246063232</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>0.38400000333786</v>
       </c>
       <c r="G315" t="n">
-        <v>0.295038402080536</v>
+        <v>0.295038431882858</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>0.418999999761581</v>
       </c>
       <c r="G319" t="n">
-        <v>0.321929961442947</v>
+        <v>0.321929901838303</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>0.423500001430511</v>
       </c>
       <c r="G322" t="n">
-        <v>0.325387448072433</v>
+        <v>0.325387418270111</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>0.412499994039536</v>
       </c>
       <c r="G323" t="n">
-        <v>0.316935837268829</v>
+        <v>0.316935807466507</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>0.403200000524521</v>
       </c>
       <c r="G325" t="n">
-        <v>0.309790313243866</v>
+        <v>0.309790343046188</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>0.402500003576279</v>
       </c>
       <c r="G326" t="n">
-        <v>0.309252500534058</v>
+        <v>0.30925253033638</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>0.404900014400482</v>
       </c>
       <c r="G327" t="n">
-        <v>0.311096519231796</v>
+        <v>0.311096549034119</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>0.407499998807907</v>
       </c>
       <c r="G328" t="n">
-        <v>0.313094168901443</v>
+        <v>0.313094139099121</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G331" t="n">
-        <v>0.307331681251526</v>
+        <v>0.307331711053848</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>0.375999987125397</v>
       </c>
       <c r="G332" t="n">
-        <v>0.288891762495041</v>
+        <v>0.288891792297363</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>0.381399989128113</v>
       </c>
       <c r="G334" t="n">
-        <v>0.293040782213211</v>
+        <v>0.293040752410889</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>0.384200006723404</v>
       </c>
       <c r="G335" t="n">
-        <v>0.295192092657089</v>
+        <v>0.295192062854767</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>0.387499988079071</v>
       </c>
       <c r="G337" t="n">
-        <v>0.297727584838867</v>
+        <v>0.297727555036545</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>0.386900007724762</v>
       </c>
       <c r="G339" t="n">
-        <v>0.297266602516174</v>
+        <v>0.297266572713852</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>0.403800010681152</v>
       </c>
       <c r="G341" t="n">
-        <v>0.310251325368881</v>
+        <v>0.310251355171204</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>0.408100008964539</v>
       </c>
       <c r="G342" t="n">
-        <v>0.313555181026459</v>
+        <v>0.313555151224136</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>0.396800011396408</v>
       </c>
       <c r="G343" t="n">
-        <v>0.304873079061508</v>
+        <v>0.304873019456863</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>0.390100002288818</v>
       </c>
       <c r="G348" t="n">
-        <v>0.299725204706192</v>
+        <v>0.299725234508514</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>0.418900012969971</v>
       </c>
       <c r="G349" t="n">
-        <v>0.32185310125351</v>
+        <v>0.321853131055832</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G350" t="n">
-        <v>0.327308267354965</v>
+        <v>0.327308237552643</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>0.414499998092651</v>
       </c>
       <c r="G351" t="n">
-        <v>0.318472445011139</v>
+        <v>0.318472474813461</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G352" t="n">
-        <v>0.307331681251526</v>
+        <v>0.307331711053848</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>0.402500003576279</v>
       </c>
       <c r="G353" t="n">
-        <v>0.309252500534058</v>
+        <v>0.30925253033638</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>0.407499998807907</v>
       </c>
       <c r="G355" t="n">
-        <v>0.313094168901443</v>
+        <v>0.313094139099121</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G357" t="n">
-        <v>0.315015017986298</v>
+        <v>0.315014988183975</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>0.406399995088577</v>
       </c>
       <c r="G358" t="n">
-        <v>0.312249004840851</v>
+        <v>0.312248975038528</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>0.408600002527237</v>
       </c>
       <c r="G359" t="n">
-        <v>0.313939303159714</v>
+        <v>0.313939332962036</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>0.400099992752075</v>
       </c>
       <c r="G361" t="n">
-        <v>0.307408541440964</v>
+        <v>0.307408481836319</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G363" t="n">
-        <v>0.307331681251526</v>
+        <v>0.307331711053848</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>0.402099996805191</v>
       </c>
       <c r="G364" t="n">
-        <v>0.308945149183273</v>
+        <v>0.308945178985596</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>0.403400003910065</v>
       </c>
       <c r="G370" t="n">
-        <v>0.309943974018097</v>
+        <v>0.309944003820419</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>0.413599997758865</v>
       </c>
       <c r="G371" t="n">
-        <v>0.317781001329422</v>
+        <v>0.3177809715271</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>0.412000000476837</v>
       </c>
       <c r="G372" t="n">
-        <v>0.316551625728607</v>
+        <v>0.31655165553093</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>0.411900013685226</v>
       </c>
       <c r="G373" t="n">
-        <v>0.316474825143814</v>
+        <v>0.316474795341492</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>0.422199994325638</v>
       </c>
       <c r="G374" t="n">
-        <v>0.32438862323761</v>
+        <v>0.324388563632965</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>0.413500010967255</v>
       </c>
       <c r="G377" t="n">
-        <v>0.317704141139984</v>
+        <v>0.317704111337662</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>0.418500006198883</v>
       </c>
       <c r="G378" t="n">
-        <v>0.321545779705048</v>
+        <v>0.32154580950737</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>0.417100012302399</v>
       </c>
       <c r="G379" t="n">
-        <v>0.320470124483109</v>
+        <v>0.320470094680786</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>0.421299993991852</v>
       </c>
       <c r="G381" t="n">
-        <v>0.323697090148926</v>
+        <v>0.323697119951248</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>0.426099985837936</v>
       </c>
       <c r="G383" t="n">
-        <v>0.327385038137436</v>
+        <v>0.327385097742081</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>0.441900014877319</v>
       </c>
       <c r="G385" t="n">
-        <v>0.339524686336517</v>
+        <v>0.33952471613884</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>0.44990000128746</v>
       </c>
       <c r="G386" t="n">
-        <v>0.345671325922012</v>
+        <v>0.34567129611969</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>0.4375</v>
       </c>
       <c r="G390" t="n">
-        <v>0.336144030094147</v>
+        <v>0.336144000291824</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>0.441100001335144</v>
       </c>
       <c r="G392" t="n">
-        <v>0.338910043239594</v>
+        <v>0.338910013437271</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>0.440100014209747</v>
       </c>
       <c r="G393" t="n">
-        <v>0.338141679763794</v>
+        <v>0.338141739368439</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>0.456000000238419</v>
       </c>
       <c r="G395" t="n">
-        <v>0.350358128547668</v>
+        <v>0.350358098745346</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>0.451099991798401</v>
       </c>
       <c r="G396" t="n">
-        <v>0.34659332036972</v>
+        <v>0.346593290567398</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G397" t="n">
-        <v>0.344211488962173</v>
+        <v>0.344211518764496</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>0.443399995565414</v>
       </c>
       <c r="G398" t="n">
-        <v>0.340677171945572</v>
+        <v>0.34067714214325</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>0.440200001001358</v>
       </c>
       <c r="G400" t="n">
-        <v>0.338218539953232</v>
+        <v>0.338218510150909</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>0.450500011444092</v>
       </c>
       <c r="G402" t="n">
-        <v>0.346132308244705</v>
+        <v>0.346132338047028</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>0.458999991416931</v>
       </c>
       <c r="G405" t="n">
-        <v>0.352663069963455</v>
+        <v>0.352663099765778</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>0.481499999761581</v>
       </c>
       <c r="G406" t="n">
-        <v>0.369950532913208</v>
+        <v>0.369950503110886</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>0.472499996423721</v>
       </c>
       <c r="G408" t="n">
-        <v>0.363035529851913</v>
+        <v>0.363035559654236</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>0.486900001764297</v>
       </c>
       <c r="G409" t="n">
-        <v>0.374099493026733</v>
+        <v>0.374099463224411</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>0.472600013017654</v>
       </c>
       <c r="G414" t="n">
-        <v>0.363112419843674</v>
+        <v>0.363112390041351</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>0.469999998807907</v>
       </c>
       <c r="G418" t="n">
-        <v>0.361114710569382</v>
+        <v>0.361114740371704</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>0.468400001525879</v>
       </c>
       <c r="G419" t="n">
-        <v>0.359885394573212</v>
+        <v>0.359885424375534</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>0.468400001525879</v>
       </c>
       <c r="G420" t="n">
-        <v>0.359885394573212</v>
+        <v>0.359885424375534</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>0.467500001192093</v>
       </c>
       <c r="G421" t="n">
-        <v>0.35919389128685</v>
+        <v>0.359193950891495</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>0.479699999094009</v>
       </c>
       <c r="G422" t="n">
-        <v>0.368567496538162</v>
+        <v>0.368567526340485</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>0.484200000762939</v>
       </c>
       <c r="G423" t="n">
-        <v>0.372025042772293</v>
+        <v>0.372024983167648</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>0.48879998922348</v>
       </c>
       <c r="G424" t="n">
-        <v>0.37555930018425</v>
+        <v>0.375559329986572</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>0.510999977588654</v>
       </c>
       <c r="G426" t="n">
-        <v>0.392616182565689</v>
+        <v>0.392616242170334</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>0.546000003814697</v>
       </c>
       <c r="G429" t="n">
-        <v>0.419507771730423</v>
+        <v>0.419507801532745</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>0.537999987602234</v>
       </c>
       <c r="G431" t="n">
-        <v>0.413361132144928</v>
+        <v>0.413361102342606</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G432" t="n">
-        <v>0.422581076622009</v>
+        <v>0.422581046819687</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>0.543500006198883</v>
       </c>
       <c r="G433" t="n">
-        <v>0.417586892843246</v>
+        <v>0.417586922645569</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>0.550999999046326</v>
       </c>
       <c r="G435" t="n">
-        <v>0.423349410295486</v>
+        <v>0.423349380493164</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G436" t="n">
-        <v>0.422581076622009</v>
+        <v>0.422581046819687</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>0.543500006198883</v>
       </c>
       <c r="G438" t="n">
-        <v>0.417586892843246</v>
+        <v>0.417586922645569</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G439" t="n">
-        <v>0.422581076622009</v>
+        <v>0.422581046819687</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>0.556999981403351</v>
       </c>
       <c r="G440" t="n">
-        <v>0.427959352731705</v>
+        <v>0.427959322929382</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>0.563499987125397</v>
       </c>
       <c r="G442" t="n">
-        <v>0.432953476905823</v>
+        <v>0.43295356631279</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>0.58950001001358</v>
       </c>
       <c r="G443" t="n">
-        <v>0.452930063009262</v>
+        <v>0.452930122613907</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G444" t="n">
-        <v>0.459460854530334</v>
+        <v>0.459460824728012</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>0.605499982833862</v>
       </c>
       <c r="G445" t="n">
-        <v>0.465223371982574</v>
+        <v>0.465223342180252</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>0.626500010490417</v>
       </c>
       <c r="G447" t="n">
-        <v>0.481358289718628</v>
+        <v>0.48135831952095</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G448" t="n">
-        <v>0.522463917732239</v>
+        <v>0.522463798522949</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>0.670499980449677</v>
       </c>
       <c r="G449" t="n">
-        <v>0.5151646733284</v>
+        <v>0.515164732933044</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G450" t="n">
-        <v>0.505560576915741</v>
+        <v>0.505560636520386</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G451" t="n">
-        <v>0.50709730386734</v>
+        <v>0.507097244262695</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>0.671000003814697</v>
       </c>
       <c r="G452" t="n">
-        <v>0.515548884868622</v>
+        <v>0.515548825263977</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>0.654999971389771</v>
       </c>
       <c r="G453" t="n">
-        <v>0.503255665302277</v>
+        <v>0.503255605697632</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>0.637499988079071</v>
       </c>
       <c r="G454" t="n">
-        <v>0.48980987071991</v>
+        <v>0.489809900522232</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>0.625</v>
       </c>
       <c r="G455" t="n">
-        <v>0.480205684900284</v>
+        <v>0.480205774307251</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>0.675499975681305</v>
       </c>
       <c r="G456" t="n">
-        <v>0.519006371498108</v>
+        <v>0.519006311893463</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>0.665499985218048</v>
       </c>
       <c r="G457" t="n">
-        <v>0.511323034763336</v>
+        <v>0.511323094367981</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G458" t="n">
-        <v>0.499413996934891</v>
+        <v>0.499413937330246</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G459" t="n">
-        <v>0.491730690002441</v>
+        <v>0.491730630397797</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>0.630500018596649</v>
       </c>
       <c r="G460" t="n">
-        <v>0.484431594610214</v>
+        <v>0.484431624412537</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>0.629499971866608</v>
       </c>
       <c r="G461" t="n">
-        <v>0.48366317152977</v>
+        <v>0.483663231134415</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>0.625</v>
       </c>
       <c r="G462" t="n">
-        <v>0.480205684900284</v>
+        <v>0.480205774307251</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>0.630500018596649</v>
       </c>
       <c r="G463" t="n">
-        <v>0.484431594610214</v>
+        <v>0.484431624412537</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>0.637499988079071</v>
       </c>
       <c r="G465" t="n">
-        <v>0.48980987071991</v>
+        <v>0.489809900522232</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>0.625</v>
       </c>
       <c r="G466" t="n">
-        <v>0.480205684900284</v>
+        <v>0.480205774307251</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>0.644500017166138</v>
       </c>
       <c r="G467" t="n">
-        <v>0.495188146829605</v>
+        <v>0.49518820643425</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G468" t="n">
-        <v>0.490194022655487</v>
+        <v>0.490194082260132</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G469" t="n">
-        <v>0.491730690002441</v>
+        <v>0.491730630397797</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G470" t="n">
-        <v>0.491730690002441</v>
+        <v>0.491730630397797</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G471" t="n">
-        <v>0.553197085857391</v>
+        <v>0.553197026252747</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>0.70550000667572</v>
       </c>
       <c r="G472" t="n">
-        <v>0.542056202888489</v>
+        <v>0.542056322097778</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>0.763000011444092</v>
       </c>
       <c r="G474" t="n">
-        <v>0.586235165596008</v>
+        <v>0.586235225200653</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G476" t="n">
-        <v>0.58239358663559</v>
+        <v>0.582393527030945</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>0.744499981403351</v>
       </c>
       <c r="G477" t="n">
-        <v>0.572021067142487</v>
+        <v>0.572021126747131</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>0.745500028133392</v>
       </c>
       <c r="G478" t="n">
-        <v>0.572789490222931</v>
+        <v>0.572789549827576</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>0.718999981880188</v>
       </c>
       <c r="G479" t="n">
-        <v>0.552428662776947</v>
+        <v>0.552428603172302</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>0.709500014781952</v>
       </c>
       <c r="G481" t="n">
-        <v>0.545129597187042</v>
+        <v>0.545129537582397</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G482" t="n">
-        <v>0.553197085857391</v>
+        <v>0.553197026252747</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>0.736500024795532</v>
       </c>
       <c r="G483" t="n">
-        <v>0.565874457359314</v>
+        <v>0.565874516963959</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>0.750999987125397</v>
       </c>
       <c r="G484" t="n">
-        <v>0.577015221118927</v>
+        <v>0.577015161514282</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>0.760999977588654</v>
       </c>
       <c r="G486" t="n">
-        <v>0.584698557853699</v>
+        <v>0.584698498249054</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>0.791499972343445</v>
       </c>
       <c r="G487" t="n">
-        <v>0.608132541179657</v>
+        <v>0.608132481575012</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>0.809499979019165</v>
       </c>
       <c r="G488" t="n">
-        <v>0.621962428092957</v>
+        <v>0.621962487697601</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>0.799499988555908</v>
       </c>
       <c r="G491" t="n">
-        <v>0.614279210567474</v>
+        <v>0.61427915096283</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>0.757000029087067</v>
       </c>
       <c r="G493" t="n">
-        <v>0.58162522315979</v>
+        <v>0.581625282764435</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G494" t="n">
-        <v>0.560880303382874</v>
+        <v>0.560880362987518</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>0.750999987125397</v>
       </c>
       <c r="G496" t="n">
-        <v>0.577015221118927</v>
+        <v>0.577015161514282</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>0.778500020503998</v>
       </c>
       <c r="G497" t="n">
-        <v>0.598144352436066</v>
+        <v>0.598144292831421</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>0.806500017642975</v>
       </c>
       <c r="G498" t="n">
-        <v>0.619657576084137</v>
+        <v>0.619657516479492</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>0.763499975204468</v>
       </c>
       <c r="G503" t="n">
-        <v>0.58661937713623</v>
+        <v>0.586619317531586</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>0.774999976158142</v>
       </c>
       <c r="G504" t="n">
-        <v>0.595455169677734</v>
+        <v>0.59545511007309</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>0.760500013828278</v>
       </c>
       <c r="G506" t="n">
-        <v>0.584314346313477</v>
+        <v>0.584314405918121</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>0.750999987125397</v>
       </c>
       <c r="G507" t="n">
-        <v>0.577015221118927</v>
+        <v>0.577015161514282</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>0.735000014305115</v>
       </c>
       <c r="G512" t="n">
-        <v>0.564721941947937</v>
+        <v>0.564722001552582</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G515" t="n">
-        <v>0.58239358663559</v>
+        <v>0.582393527030945</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G517" t="n">
-        <v>0.583930134773254</v>
+        <v>0.583930253982544</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>0.787000000476837</v>
       </c>
       <c r="G520" t="n">
-        <v>0.604675054550171</v>
+        <v>0.604675114154816</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>0.819000005722046</v>
       </c>
       <c r="G521" t="n">
-        <v>0.629261553287506</v>
+        <v>0.629261612892151</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>0.805000007152557</v>
       </c>
       <c r="G522" t="n">
-        <v>0.618505001068115</v>
+        <v>0.61850506067276</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>0.785000026226044</v>
       </c>
       <c r="G525" t="n">
-        <v>0.603138506412506</v>
+        <v>0.603138446807861</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G527" t="n">
-        <v>0.611590027809143</v>
+        <v>0.611590087413788</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>0.773000001907349</v>
       </c>
       <c r="G528" t="n">
-        <v>0.59391850233078</v>
+        <v>0.593918442726135</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>0.767000019550323</v>
       </c>
       <c r="G532" t="n">
-        <v>0.589308559894562</v>
+        <v>0.589308440685272</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>0.750999987125397</v>
       </c>
       <c r="G533" t="n">
-        <v>0.577015221118927</v>
+        <v>0.577015161514282</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>0.735000014305115</v>
       </c>
       <c r="G535" t="n">
-        <v>0.564721941947937</v>
+        <v>0.564722001552582</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>0.721000015735626</v>
       </c>
       <c r="G536" t="n">
-        <v>0.553965449333191</v>
+        <v>0.553965330123901</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>0.700999975204468</v>
       </c>
       <c r="G537" t="n">
-        <v>0.538598656654358</v>
+        <v>0.538598835468292</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G539" t="n">
-        <v>0.536293804645538</v>
+        <v>0.536293864250183</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G541" t="n">
-        <v>0.537830471992493</v>
+        <v>0.537830412387848</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>0.699000000953674</v>
       </c>
       <c r="G545" t="n">
-        <v>0.537062168121338</v>
+        <v>0.537062108516693</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G546" t="n">
-        <v>0.527073860168457</v>
+        <v>0.527073800563812</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G547" t="n">
-        <v>0.522463917732239</v>
+        <v>0.522463798522949</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G548" t="n">
-        <v>0.522463917732239</v>
+        <v>0.522463798522949</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G550" t="n">
-        <v>0.537830471992493</v>
+        <v>0.537830412387848</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G551" t="n">
-        <v>0.537830471992493</v>
+        <v>0.537830412387848</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G553" t="n">
-        <v>0.536293804645538</v>
+        <v>0.536293864250183</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>0.654999971389771</v>
       </c>
       <c r="G555" t="n">
-        <v>0.503255665302277</v>
+        <v>0.503255605697632</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G556" t="n">
-        <v>0.505560576915741</v>
+        <v>0.505560636520386</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G557" t="n">
-        <v>0.517853856086731</v>
+        <v>0.517853915691376</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G558" t="n">
-        <v>0.517853856086731</v>
+        <v>0.517853915691376</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G560" t="n">
-        <v>0.530147075653076</v>
+        <v>0.530147135257721</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>0.680999994277954</v>
       </c>
       <c r="G561" t="n">
-        <v>0.523232161998749</v>
+        <v>0.523232221603394</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G562" t="n">
-        <v>0.51939058303833</v>
+        <v>0.519390523433685</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>0.683000028133392</v>
       </c>
       <c r="G563" t="n">
-        <v>0.524768829345703</v>
+        <v>0.524768888950348</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G564" t="n">
-        <v>0.527073860168457</v>
+        <v>0.527073800563812</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>0.757000029087067</v>
       </c>
       <c r="G567" t="n">
-        <v>0.58162522315979</v>
+        <v>0.581625282764435</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>0.714999973773956</v>
       </c>
       <c r="G568" t="n">
-        <v>0.549355387687683</v>
+        <v>0.549355328083038</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>0.640999972820282</v>
       </c>
       <c r="G570" t="n">
-        <v>0.492498993873596</v>
+        <v>0.492499023675919</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>0.625</v>
       </c>
       <c r="G572" t="n">
-        <v>0.480205684900284</v>
+        <v>0.480205774307251</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G574" t="n">
-        <v>0.48865732550621</v>
+        <v>0.488657355308533</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G577" t="n">
-        <v>0.491730690002441</v>
+        <v>0.491730630397797</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>0.615000009536743</v>
       </c>
       <c r="G578" t="n">
-        <v>0.472522497177124</v>
+        <v>0.472522467374802</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G579" t="n">
-        <v>0.468680858612061</v>
+        <v>0.468680828809738</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>0.626999974250793</v>
       </c>
       <c r="G582" t="n">
-        <v>0.481742411851883</v>
+        <v>0.481742382049561</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G583" t="n">
-        <v>0.480974137783051</v>
+        <v>0.480974048376083</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>0.629000008106232</v>
       </c>
       <c r="G584" t="n">
-        <v>0.483279019594193</v>
+        <v>0.48327910900116</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>0.623000025749207</v>
       </c>
       <c r="G585" t="n">
-        <v>0.478669136762619</v>
+        <v>0.478669077157974</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G586" t="n">
-        <v>0.47021746635437</v>
+        <v>0.470217436552048</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G587" t="n">
-        <v>0.468680858612061</v>
+        <v>0.468680828809738</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>0.609000027179718</v>
       </c>
       <c r="G588" t="n">
-        <v>0.467912524938583</v>
+        <v>0.467912554740906</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>0.60699999332428</v>
       </c>
       <c r="G589" t="n">
-        <v>0.466375797986984</v>
+        <v>0.466375827789307</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G590" t="n">
-        <v>0.47021746635437</v>
+        <v>0.470217436552048</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G592" t="n">
-        <v>0.47021746635437</v>
+        <v>0.470217436552048</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>0.601000010967255</v>
       </c>
       <c r="G593" t="n">
-        <v>0.461765915155411</v>
+        <v>0.461765885353088</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>0.601000010967255</v>
       </c>
       <c r="G594" t="n">
-        <v>0.461765915155411</v>
+        <v>0.461765885353088</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>0.625</v>
       </c>
       <c r="G597" t="n">
-        <v>0.480205684900284</v>
+        <v>0.480205774307251</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G598" t="n">
-        <v>0.491730690002441</v>
+        <v>0.491730630397797</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>0.569000005722046</v>
       </c>
       <c r="G602" t="n">
-        <v>0.437179356813431</v>
+        <v>0.437179327011108</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>0.578999996185303</v>
       </c>
       <c r="G603" t="n">
-        <v>0.444862633943558</v>
+        <v>0.444862574338913</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>0.561999976634979</v>
       </c>
       <c r="G604" t="n">
-        <v>0.431800991296768</v>
+        <v>0.431801050901413</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>0.578000009059906</v>
       </c>
       <c r="G606" t="n">
-        <v>0.444094300270081</v>
+        <v>0.444094270467758</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G607" t="n">
-        <v>0.422581076622009</v>
+        <v>0.422581046819687</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G608" t="n">
-        <v>0.424117684364319</v>
+        <v>0.424117714166641</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G609" t="n">
-        <v>0.422581076622009</v>
+        <v>0.422581046819687</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G610" t="n">
-        <v>0.422581076622009</v>
+        <v>0.422581046819687</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>0.541000008583069</v>
       </c>
       <c r="G611" t="n">
-        <v>0.415666103363037</v>
+        <v>0.415666043758392</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>0.493499994277954</v>
       </c>
       <c r="G614" t="n">
-        <v>0.379170477390289</v>
+        <v>0.379170447587967</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>0.497500002384186</v>
       </c>
       <c r="G615" t="n">
-        <v>0.382243752479553</v>
+        <v>0.382243782281876</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>0.501999974250793</v>
       </c>
       <c r="G616" t="n">
-        <v>0.385701239109039</v>
+        <v>0.385701268911362</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>0.501999974250793</v>
       </c>
       <c r="G618" t="n">
-        <v>0.385701239109039</v>
+        <v>0.385701268911362</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>0.505999982357025</v>
       </c>
       <c r="G619" t="n">
-        <v>0.388774544000626</v>
+        <v>0.388774573802948</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>0.501999974250793</v>
       </c>
       <c r="G623" t="n">
-        <v>0.385701239109039</v>
+        <v>0.385701268911362</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G624" t="n">
-        <v>0.37648132443428</v>
+        <v>0.376481354236603</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>0.477999985218048</v>
       </c>
       <c r="G625" t="n">
-        <v>0.367261320352554</v>
+        <v>0.367261350154877</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>0.469999998807907</v>
       </c>
       <c r="G627" t="n">
-        <v>0.361114710569382</v>
+        <v>0.361114740371704</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>0.469999998807907</v>
       </c>
       <c r="G628" t="n">
-        <v>0.361114710569382</v>
+        <v>0.361114740371704</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>0.469999998807907</v>
       </c>
       <c r="G629" t="n">
-        <v>0.361114710569382</v>
+        <v>0.361114740371704</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>0.46900001168251</v>
       </c>
       <c r="G630" t="n">
-        <v>0.360346406698227</v>
+        <v>0.360346376895905</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>0.46399998664856</v>
       </c>
       <c r="G632" t="n">
-        <v>0.356504738330841</v>
+        <v>0.356504708528519</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>0.483500003814697</v>
       </c>
       <c r="G633" t="n">
-        <v>0.37148717045784</v>
+        <v>0.371487140655518</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>0.479000002145767</v>
       </c>
       <c r="G634" t="n">
-        <v>0.368029713630676</v>
+        <v>0.368029683828354</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>0.484499990940094</v>
       </c>
       <c r="G635" t="n">
-        <v>0.372255504131317</v>
+        <v>0.372255474328995</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>0.469999998807907</v>
       </c>
       <c r="G636" t="n">
-        <v>0.361114710569382</v>
+        <v>0.361114740371704</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>0.479000002145767</v>
       </c>
       <c r="G638" t="n">
-        <v>0.368029713630676</v>
+        <v>0.368029683828354</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>0.476999998092651</v>
       </c>
       <c r="G640" t="n">
-        <v>0.366492986679077</v>
+        <v>0.3664930164814</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>0.487500011920929</v>
       </c>
       <c r="G641" t="n">
-        <v>0.374560505151749</v>
+        <v>0.374560475349426</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>0.479000002145767</v>
       </c>
       <c r="G642" t="n">
-        <v>0.368029713630676</v>
+        <v>0.368029683828354</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>0.486999988555908</v>
       </c>
       <c r="G643" t="n">
-        <v>0.374176353216171</v>
+        <v>0.374176323413849</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>0.479000002145767</v>
       </c>
       <c r="G645" t="n">
-        <v>0.368029713630676</v>
+        <v>0.368029683828354</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>0.460500001907349</v>
       </c>
       <c r="G647" t="n">
-        <v>0.353815615177155</v>
+        <v>0.353815644979477</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>0.482499986886978</v>
       </c>
       <c r="G651" t="n">
-        <v>0.370718866586685</v>
+        <v>0.37071880698204</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>0.476999998092651</v>
       </c>
       <c r="G652" t="n">
-        <v>0.366492986679077</v>
+        <v>0.3664930164814</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>0.460999995470047</v>
       </c>
       <c r="G653" t="n">
-        <v>0.354199767112732</v>
+        <v>0.35419973731041</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>0.458999991416931</v>
       </c>
       <c r="G654" t="n">
-        <v>0.352663069963455</v>
+        <v>0.352663099765778</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>0.514999985694885</v>
       </c>
       <c r="G656" t="n">
-        <v>0.39568954706192</v>
+        <v>0.395689517259598</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G657" t="n">
-        <v>0.422581076622009</v>
+        <v>0.422581046819687</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>0.537999987602234</v>
       </c>
       <c r="G659" t="n">
-        <v>0.413361132144928</v>
+        <v>0.413361102342606</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>0.531000018119812</v>
       </c>
       <c r="G660" t="n">
-        <v>0.407982856035233</v>
+        <v>0.40798282623291</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>0.500999987125397</v>
       </c>
       <c r="G661" t="n">
-        <v>0.384932935237885</v>
+        <v>0.384932905435562</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>0.508000016212463</v>
       </c>
       <c r="G662" t="n">
-        <v>0.39031121134758</v>
+        <v>0.390311270952225</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>0.492000013589859</v>
       </c>
       <c r="G664" t="n">
-        <v>0.378018021583557</v>
+        <v>0.378017991781235</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>0.49549999833107</v>
       </c>
       <c r="G665" t="n">
-        <v>0.380707144737244</v>
+        <v>0.380707085132599</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>0.486999988555908</v>
       </c>
       <c r="G666" t="n">
-        <v>0.374176353216171</v>
+        <v>0.374176323413849</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>0.467999994754791</v>
       </c>
       <c r="G668" t="n">
-        <v>0.359578043222427</v>
+        <v>0.35957807302475</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>0.449000000953674</v>
       </c>
       <c r="G671" t="n">
-        <v>0.344979852437973</v>
+        <v>0.344979822635651</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>0.460999995470047</v>
       </c>
       <c r="G674" t="n">
-        <v>0.354199767112732</v>
+        <v>0.35419973731041</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>0.477999985218048</v>
       </c>
       <c r="G675" t="n">
-        <v>0.367261320352554</v>
+        <v>0.367261350154877</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>0.474000006914139</v>
       </c>
       <c r="G676" t="n">
-        <v>0.36418804526329</v>
+        <v>0.364188075065613</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>0.465000003576279</v>
       </c>
       <c r="G678" t="n">
-        <v>0.357273131608963</v>
+        <v>0.357273072004318</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>0.45550000667572</v>
       </c>
       <c r="G679" t="n">
-        <v>0.349973946809769</v>
+        <v>0.349973976612091</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>0.441500008106232</v>
       </c>
       <c r="G680" t="n">
-        <v>0.339217334985733</v>
+        <v>0.339217364788055</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>0.421499997377396</v>
       </c>
       <c r="G681" t="n">
-        <v>0.323850780725479</v>
+        <v>0.323850750923157</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>0.515999972820282</v>
       </c>
       <c r="G686" t="n">
-        <v>0.396457850933075</v>
+        <v>0.396457880735397</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>0.537000000476837</v>
       </c>
       <c r="G687" t="n">
-        <v>0.412592798471451</v>
+        <v>0.412592768669128</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>0.52700001001358</v>
       </c>
       <c r="G688" t="n">
-        <v>0.404909491539001</v>
+        <v>0.404909521341324</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G691" t="n">
-        <v>0.399531155824661</v>
+        <v>0.399531185626984</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>0.523999989032745</v>
       </c>
       <c r="G692" t="n">
-        <v>0.402604460716248</v>
+        <v>0.402604520320892</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>0.514999985694885</v>
       </c>
       <c r="G693" t="n">
-        <v>0.39568954706192</v>
+        <v>0.395689517259598</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>0.522000014781952</v>
       </c>
       <c r="G694" t="n">
-        <v>0.401067852973938</v>
+        <v>0.40106788277626</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>0.515999972820282</v>
       </c>
       <c r="G695" t="n">
-        <v>0.396457850933075</v>
+        <v>0.396457880735397</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G696" t="n">
-        <v>0.399531155824661</v>
+        <v>0.399531185626984</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>0.501999974250793</v>
       </c>
       <c r="G699" t="n">
-        <v>0.385701239109039</v>
+        <v>0.385701268911362</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>0.488999992609024</v>
       </c>
       <c r="G700" t="n">
-        <v>0.375712990760803</v>
+        <v>0.375712960958481</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>0.460999995470047</v>
       </c>
       <c r="G702" t="n">
-        <v>0.354199767112732</v>
+        <v>0.35419973731041</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G703" t="n">
-        <v>0.345748096704483</v>
+        <v>0.345748156309128</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>0.456000000238419</v>
       </c>
       <c r="G704" t="n">
-        <v>0.350358128547668</v>
+        <v>0.350358098745346</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G709" t="n">
-        <v>0.337296515703201</v>
+        <v>0.337296485900879</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G710" t="n">
-        <v>0.329613268375397</v>
+        <v>0.329613208770752</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G711" t="n">
-        <v>0.328076541423798</v>
+        <v>0.328076511621475</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G712" t="n">
-        <v>0.328076541423798</v>
+        <v>0.328076511621475</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>0.431499987840652</v>
       </c>
       <c r="G713" t="n">
-        <v>0.331534028053284</v>
+        <v>0.331534057855606</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G714" t="n">
-        <v>0.32116162776947</v>
+        <v>0.321161597967148</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G715" t="n">
-        <v>0.314246654510498</v>
+        <v>0.31424668431282</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>0.415499985218048</v>
       </c>
       <c r="G716" t="n">
-        <v>0.319240808486938</v>
+        <v>0.319240778684616</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>0.425500005483627</v>
       </c>
       <c r="G717" t="n">
-        <v>0.326924085617065</v>
+        <v>0.326924055814743</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>0.407499998807907</v>
       </c>
       <c r="G718" t="n">
-        <v>0.313094168901443</v>
+        <v>0.313094139099121</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>0.444000005722046</v>
       </c>
       <c r="G720" t="n">
-        <v>0.341138184070587</v>
+        <v>0.341138154268265</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>0.425500005483627</v>
       </c>
       <c r="G722" t="n">
-        <v>0.326924085617065</v>
+        <v>0.326924055814743</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G726" t="n">
-        <v>0.330381572246552</v>
+        <v>0.330381542444229</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>0.429500013589859</v>
       </c>
       <c r="G727" t="n">
-        <v>0.329997390508652</v>
+        <v>0.329997420310974</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G729" t="n">
-        <v>0.327308267354965</v>
+        <v>0.327308237552643</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G730" t="n">
-        <v>0.329613268375397</v>
+        <v>0.329613208770752</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G731" t="n">
-        <v>0.329613268375397</v>
+        <v>0.329613208770752</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G732" t="n">
-        <v>0.328076541423798</v>
+        <v>0.328076511621475</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G734" t="n">
-        <v>0.324234962463379</v>
+        <v>0.324234902858734</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>0.408499985933304</v>
       </c>
       <c r="G735" t="n">
-        <v>0.313862472772598</v>
+        <v>0.313862442970276</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>0.391999989748001</v>
       </c>
       <c r="G738" t="n">
-        <v>0.301185011863708</v>
+        <v>0.301185071468353</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>0.386500000953674</v>
       </c>
       <c r="G741" t="n">
-        <v>0.29695925116539</v>
+        <v>0.296959221363068</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>0.391000002622604</v>
       </c>
       <c r="G742" t="n">
-        <v>0.300416737794876</v>
+        <v>0.300416707992554</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>0.407499998807907</v>
       </c>
       <c r="G745" t="n">
-        <v>0.313094168901443</v>
+        <v>0.313094139099121</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>0.418999999761581</v>
       </c>
       <c r="G747" t="n">
-        <v>0.321929961442947</v>
+        <v>0.321929901838303</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>0.420500010251999</v>
       </c>
       <c r="G748" t="n">
-        <v>0.323082387447357</v>
+        <v>0.32308241724968</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G749" t="n">
-        <v>0.324234962463379</v>
+        <v>0.324234902858734</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G752" t="n">
-        <v>0.307331681251526</v>
+        <v>0.307331711053848</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>0.404000014066696</v>
       </c>
       <c r="G753" t="n">
-        <v>0.310405015945435</v>
+        <v>0.310405045747757</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>0.399500012397766</v>
       </c>
       <c r="G754" t="n">
-        <v>0.306947559118271</v>
+        <v>0.306947529315948</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>0.409500002861023</v>
       </c>
       <c r="G755" t="n">
-        <v>0.314630776643753</v>
+        <v>0.314630806446075</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>0.402500003576279</v>
       </c>
       <c r="G756" t="n">
-        <v>0.309252500534058</v>
+        <v>0.30925253033638</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G758" t="n">
-        <v>0.307331681251526</v>
+        <v>0.307331711053848</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G759" t="n">
-        <v>0.314246654510498</v>
+        <v>0.31424668431282</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>0.396499991416931</v>
       </c>
       <c r="G761" t="n">
-        <v>0.304642558097839</v>
+        <v>0.304642528295517</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>0.394499987363815</v>
       </c>
       <c r="G762" t="n">
-        <v>0.30310583114624</v>
+        <v>0.303105890750885</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G767" t="n">
-        <v>0.344211488962173</v>
+        <v>0.344211518764496</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G768" t="n">
-        <v>0.345748096704483</v>
+        <v>0.345748156309128</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>0.467999994754791</v>
       </c>
       <c r="G769" t="n">
-        <v>0.359578043222427</v>
+        <v>0.35957807302475</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>0.46450001001358</v>
       </c>
       <c r="G770" t="n">
-        <v>0.356888890266418</v>
+        <v>0.356888949871063</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>0.46900001168251</v>
       </c>
       <c r="G772" t="n">
-        <v>0.360346406698227</v>
+        <v>0.360346376895905</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>0.463499993085861</v>
       </c>
       <c r="G773" t="n">
-        <v>0.356120556592941</v>
+        <v>0.356120616197586</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>0.46900001168251</v>
       </c>
       <c r="G775" t="n">
-        <v>0.360346406698227</v>
+        <v>0.360346376895905</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>0.467500001192093</v>
       </c>
       <c r="G776" t="n">
-        <v>0.35919389128685</v>
+        <v>0.359193950891495</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>0.46450001001358</v>
       </c>
       <c r="G778" t="n">
-        <v>0.356888890266418</v>
+        <v>0.356888949871063</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>0.456999987363815</v>
       </c>
       <c r="G779" t="n">
-        <v>0.351126462221146</v>
+        <v>0.351126432418823</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>0.46900001168251</v>
       </c>
       <c r="G781" t="n">
-        <v>0.360346406698227</v>
+        <v>0.360346376895905</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>0.462999999523163</v>
       </c>
       <c r="G782" t="n">
-        <v>0.355736434459686</v>
+        <v>0.355736404657364</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>0.463499993085861</v>
       </c>
       <c r="G783" t="n">
-        <v>0.356120556592941</v>
+        <v>0.356120616197586</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>0.445499986410141</v>
       </c>
       <c r="G785" t="n">
-        <v>0.342290669679642</v>
+        <v>0.342290639877319</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>0.48199999332428</v>
       </c>
       <c r="G789" t="n">
-        <v>0.370334684848785</v>
+        <v>0.370334714651108</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>0.46450001001358</v>
       </c>
       <c r="G790" t="n">
-        <v>0.356888890266418</v>
+        <v>0.356888949871063</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>0.487500011920929</v>
       </c>
       <c r="G793" t="n">
-        <v>0.374560505151749</v>
+        <v>0.374560475349426</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>0.486999988555908</v>
       </c>
       <c r="G794" t="n">
-        <v>0.374176353216171</v>
+        <v>0.374176323413849</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G795" t="n">
-        <v>0.37648132443428</v>
+        <v>0.376481354236603</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>0.492000013589859</v>
       </c>
       <c r="G796" t="n">
-        <v>0.378018021583557</v>
+        <v>0.378017991781235</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>0.497500002384186</v>
       </c>
       <c r="G798" t="n">
-        <v>0.382243752479553</v>
+        <v>0.382243782281876</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>0.515999972820282</v>
       </c>
       <c r="G804" t="n">
-        <v>0.396457850933075</v>
+        <v>0.396457880735397</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>0.523999989032745</v>
       </c>
       <c r="G807" t="n">
-        <v>0.402604460716248</v>
+        <v>0.402604520320892</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>0.532999992370605</v>
       </c>
       <c r="G809" t="n">
-        <v>0.40951943397522</v>
+        <v>0.409519493579865</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>0.515999972820282</v>
       </c>
       <c r="G810" t="n">
-        <v>0.396457850933075</v>
+        <v>0.396457880735397</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>0.508000016212463</v>
       </c>
       <c r="G813" t="n">
-        <v>0.39031121134758</v>
+        <v>0.390311270952225</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>0.500999987125397</v>
       </c>
       <c r="G815" t="n">
-        <v>0.384932935237885</v>
+        <v>0.384932905435562</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>0.508000016212463</v>
       </c>
       <c r="G818" t="n">
-        <v>0.39031121134758</v>
+        <v>0.390311270952225</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>0.515999972820282</v>
       </c>
       <c r="G819" t="n">
-        <v>0.396457850933075</v>
+        <v>0.396457880735397</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>0.515999972820282</v>
       </c>
       <c r="G820" t="n">
-        <v>0.396457850933075</v>
+        <v>0.396457880735397</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>0.496499985456467</v>
       </c>
       <c r="G822" t="n">
-        <v>0.381475448608398</v>
+        <v>0.381475418806076</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>0.484499990940094</v>
       </c>
       <c r="G825" t="n">
-        <v>0.372255504131317</v>
+        <v>0.372255474328995</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>0.469999998807907</v>
       </c>
       <c r="G826" t="n">
-        <v>0.361114710569382</v>
+        <v>0.361114740371704</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G831" t="n">
-        <v>0.407214432954788</v>
+        <v>0.407214522361755</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G832" t="n">
-        <v>0.407214432954788</v>
+        <v>0.407214522361755</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>0.505999982357025</v>
       </c>
       <c r="G834" t="n">
-        <v>0.388774544000626</v>
+        <v>0.388774573802948</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>0.541000008583069</v>
       </c>
       <c r="G839" t="n">
-        <v>0.415666103363037</v>
+        <v>0.415666043758392</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G840" t="n">
-        <v>0.414897799491882</v>
+        <v>0.414897829294205</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>0.542999982833862</v>
       </c>
       <c r="G841" t="n">
-        <v>0.417202740907669</v>
+        <v>0.417202770709991</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>0.52700001001358</v>
       </c>
       <c r="G842" t="n">
-        <v>0.404909491539001</v>
+        <v>0.404909521341324</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>0.522000014781952</v>
       </c>
       <c r="G843" t="n">
-        <v>0.401067852973938</v>
+        <v>0.40106788277626</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G844" t="n">
-        <v>0.399531155824661</v>
+        <v>0.399531185626984</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G847" t="n">
-        <v>0.399531155824661</v>
+        <v>0.399531185626984</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>0.514999985694885</v>
       </c>
       <c r="G848" t="n">
-        <v>0.39568954706192</v>
+        <v>0.395689517259598</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>0.517000019550323</v>
       </c>
       <c r="G850" t="n">
-        <v>0.397226184606552</v>
+        <v>0.397226214408875</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>0.541000008583069</v>
       </c>
       <c r="G851" t="n">
-        <v>0.415666103363037</v>
+        <v>0.415666043758392</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>0.537999987602234</v>
       </c>
       <c r="G853" t="n">
-        <v>0.413361132144928</v>
+        <v>0.413361102342606</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>0.52700001001358</v>
       </c>
       <c r="G854" t="n">
-        <v>0.404909491539001</v>
+        <v>0.404909521341324</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G855" t="n">
-        <v>0.407214432954788</v>
+        <v>0.407214522361755</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>0.532999992370605</v>
       </c>
       <c r="G857" t="n">
-        <v>0.40951943397522</v>
+        <v>0.409519493579865</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>0.538999974727631</v>
       </c>
       <c r="G862" t="n">
-        <v>0.414129436016083</v>
+        <v>0.414129376411438</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>0.541999995708466</v>
       </c>
       <c r="G863" t="n">
-        <v>0.416434466838837</v>
+        <v>0.416434437036514</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>0.532999992370605</v>
       </c>
       <c r="G864" t="n">
-        <v>0.40951943397522</v>
+        <v>0.409519493579865</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>0.542999982833862</v>
       </c>
       <c r="G865" t="n">
-        <v>0.417202740907669</v>
+        <v>0.417202770709991</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>0.537000000476837</v>
       </c>
       <c r="G870" t="n">
-        <v>0.412592798471451</v>
+        <v>0.412592768669128</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>0.531000018119812</v>
       </c>
       <c r="G874" t="n">
-        <v>0.407982856035233</v>
+        <v>0.40798282623291</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G875" t="n">
-        <v>0.407214432954788</v>
+        <v>0.407214522361755</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>0.522000014781952</v>
       </c>
       <c r="G880" t="n">
-        <v>0.401067852973938</v>
+        <v>0.40106788277626</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>0.515999972820282</v>
       </c>
       <c r="G881" t="n">
-        <v>0.396457850933075</v>
+        <v>0.396457880735397</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>0.522000014781952</v>
       </c>
       <c r="G884" t="n">
-        <v>0.401067852973938</v>
+        <v>0.40106788277626</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G886" t="n">
-        <v>0.407214432954788</v>
+        <v>0.407214522361755</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>0.545000016689301</v>
       </c>
       <c r="G887" t="n">
-        <v>0.418739467859268</v>
+        <v>0.418739438056946</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G889" t="n">
-        <v>0.424117684364319</v>
+        <v>0.424117714166641</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>0.549000024795532</v>
       </c>
       <c r="G890" t="n">
-        <v>0.421812772750854</v>
+        <v>0.421812742948532</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G892" t="n">
-        <v>0.422581076622009</v>
+        <v>0.422581046819687</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>0.545000016689301</v>
       </c>
       <c r="G893" t="n">
-        <v>0.418739467859268</v>
+        <v>0.418739438056946</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>0.541000008583069</v>
       </c>
       <c r="G894" t="n">
-        <v>0.415666103363037</v>
+        <v>0.415666043758392</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>0.541000008583069</v>
       </c>
       <c r="G895" t="n">
-        <v>0.415666103363037</v>
+        <v>0.415666043758392</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>0.545000016689301</v>
       </c>
       <c r="G896" t="n">
-        <v>0.418739467859268</v>
+        <v>0.418739438056946</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G897" t="n">
-        <v>0.430264383554459</v>
+        <v>0.430264353752136</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G898" t="n">
-        <v>0.473290771245956</v>
+        <v>0.473290741443634</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G899" t="n">
-        <v>0.494804054498672</v>
+        <v>0.49480402469635</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G900" t="n">
-        <v>0.494804054498672</v>
+        <v>0.49480402469635</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G901" t="n">
-        <v>0.48404735326767</v>
+        <v>0.484047442674637</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G902" t="n">
-        <v>0.491730690002441</v>
+        <v>0.491730630397797</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>0.642000019550323</v>
       </c>
       <c r="G903" t="n">
-        <v>0.493267327547073</v>
+        <v>0.493267357349396</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G904" t="n">
-        <v>0.505560576915741</v>
+        <v>0.505560636520386</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G906" t="n">
-        <v>0.48865732550621</v>
+        <v>0.488657355308533</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G907" t="n">
-        <v>0.479437410831451</v>
+        <v>0.479437381029129</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G909" t="n">
-        <v>0.482510834932327</v>
+        <v>0.482510715723038</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G910" t="n">
-        <v>0.47021746635437</v>
+        <v>0.470217436552048</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>0.619000017642975</v>
       </c>
       <c r="G911" t="n">
-        <v>0.475595772266388</v>
+        <v>0.47559580206871</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G913" t="n">
-        <v>0.468680858612061</v>
+        <v>0.468680828809738</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G915" t="n">
-        <v>0.465607494115829</v>
+        <v>0.465607464313507</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G916" t="n">
-        <v>0.460997551679611</v>
+        <v>0.460997492074966</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G917" t="n">
-        <v>0.480974137783051</v>
+        <v>0.480974048376083</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G918" t="n">
-        <v>0.453314185142517</v>
+        <v>0.453314214944839</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>0.564999997615814</v>
       </c>
       <c r="G919" t="n">
-        <v>0.434106051921844</v>
+        <v>0.4341059923172</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G920" t="n">
-        <v>0.441789269447327</v>
+        <v>0.441789299249649</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G921" t="n">
-        <v>0.424117684364319</v>
+        <v>0.424117714166641</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G922" t="n">
-        <v>0.44563090801239</v>
+        <v>0.445630967617035</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>0.587000012397766</v>
       </c>
       <c r="G924" t="n">
-        <v>0.451009273529053</v>
+        <v>0.451009213924408</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G925" t="n">
-        <v>0.460997551679611</v>
+        <v>0.460997492074966</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G927" t="n">
-        <v>0.453314185142517</v>
+        <v>0.453314214944839</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>0.591000020503998</v>
       </c>
       <c r="G928" t="n">
-        <v>0.454082578420639</v>
+        <v>0.454082608222961</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G929" t="n">
-        <v>0.457155883312225</v>
+        <v>0.45715594291687</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G930" t="n">
-        <v>0.465607494115829</v>
+        <v>0.465607464313507</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G931" t="n">
-        <v>0.482510834932327</v>
+        <v>0.482510715723038</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G932" t="n">
-        <v>0.48404735326767</v>
+        <v>0.484047442674637</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G935" t="n">
-        <v>0.48404735326767</v>
+        <v>0.484047442674637</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G936" t="n">
-        <v>0.460997551679611</v>
+        <v>0.460997492074966</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G937" t="n">
-        <v>0.451777577400208</v>
+        <v>0.451777547597885</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G939" t="n">
-        <v>0.460997551679611</v>
+        <v>0.460997492074966</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>0.602999985218048</v>
       </c>
       <c r="G941" t="n">
-        <v>0.46330252289772</v>
+        <v>0.463302463293076</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>0.601000010967255</v>
       </c>
       <c r="G942" t="n">
-        <v>0.461765915155411</v>
+        <v>0.461765885353088</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G945" t="n">
-        <v>0.459460854530334</v>
+        <v>0.459460824728012</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G946" t="n">
-        <v>0.460997551679611</v>
+        <v>0.460997492074966</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G947" t="n">
-        <v>0.47021746635437</v>
+        <v>0.470217436552048</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G949" t="n">
-        <v>0.467144191265106</v>
+        <v>0.467144101858139</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G950" t="n">
-        <v>0.457924216985703</v>
+        <v>0.457924246788025</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G953" t="n">
-        <v>0.459460854530334</v>
+        <v>0.459460824728012</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>0.563000023365021</v>
       </c>
       <c r="G955" t="n">
-        <v>0.43256938457489</v>
+        <v>0.432569324970245</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>0.556999981403351</v>
       </c>
       <c r="G957" t="n">
-        <v>0.427959352731705</v>
+        <v>0.427959322929382</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>0.564999997615814</v>
       </c>
       <c r="G958" t="n">
-        <v>0.434106051921844</v>
+        <v>0.4341059923172</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>0.550999999046326</v>
       </c>
       <c r="G962" t="n">
-        <v>0.423349410295486</v>
+        <v>0.423349380493164</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G963" t="n">
-        <v>0.436410993337631</v>
+        <v>0.436411023139954</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>0.561999976634979</v>
       </c>
       <c r="G964" t="n">
-        <v>0.431800991296768</v>
+        <v>0.431801050901413</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G965" t="n">
-        <v>0.441789269447327</v>
+        <v>0.441789299249649</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>0.569000005722046</v>
       </c>
       <c r="G966" t="n">
-        <v>0.437179356813431</v>
+        <v>0.437179327011108</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G968" t="n">
-        <v>0.436410993337631</v>
+        <v>0.436411023139954</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>0.572000026702881</v>
       </c>
       <c r="G969" t="n">
-        <v>0.439484357833862</v>
+        <v>0.43948432803154</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>0.561999976634979</v>
       </c>
       <c r="G970" t="n">
-        <v>0.431800991296768</v>
+        <v>0.431801050901413</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>0.569000005722046</v>
       </c>
       <c r="G971" t="n">
-        <v>0.437179356813431</v>
+        <v>0.437179327011108</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G972" t="n">
-        <v>0.441020995378494</v>
+        <v>0.441020965576172</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G973" t="n">
-        <v>0.441020995378494</v>
+        <v>0.441020965576172</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>0.573000013828278</v>
       </c>
       <c r="G974" t="n">
-        <v>0.440252661705017</v>
+        <v>0.440252631902695</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>0.570999979972839</v>
       </c>
       <c r="G977" t="n">
-        <v>0.438715934753418</v>
+        <v>0.43871596455574</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>0.601000010967255</v>
       </c>
       <c r="G980" t="n">
-        <v>0.461765915155411</v>
+        <v>0.461765885353088</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G981" t="n">
-        <v>0.479437410831451</v>
+        <v>0.479437381029129</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G982" t="n">
-        <v>0.468680858612061</v>
+        <v>0.468680828809738</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G984" t="n">
-        <v>0.485584110021591</v>
+        <v>0.485584050416946</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G987" t="n">
-        <v>0.48404735326767</v>
+        <v>0.484047442674637</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G988" t="n">
-        <v>0.468680858612061</v>
+        <v>0.468680828809738</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>0.592999994754791</v>
       </c>
       <c r="G989" t="n">
-        <v>0.455619186162949</v>
+        <v>0.455619245767593</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G990" t="n">
-        <v>0.457155883312225</v>
+        <v>0.45715594291687</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G992" t="n">
-        <v>0.459460854530334</v>
+        <v>0.459460824728012</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>0.591000020503998</v>
       </c>
       <c r="G994" t="n">
-        <v>0.454082578420639</v>
+        <v>0.454082608222961</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G995" t="n">
-        <v>0.457155883312225</v>
+        <v>0.45715594291687</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>0.577000021934509</v>
       </c>
       <c r="G996" t="n">
-        <v>0.443325936794281</v>
+        <v>0.443325996398926</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G997" t="n">
-        <v>0.436410993337631</v>
+        <v>0.436411023139954</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>0.559000015258789</v>
       </c>
       <c r="G998" t="n">
-        <v>0.429496049880981</v>
+        <v>0.429496020078659</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>0.556999981403351</v>
       </c>
       <c r="G1002" t="n">
-        <v>0.427959352731705</v>
+        <v>0.427959322929382</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>0.546000003814697</v>
       </c>
       <c r="G1003" t="n">
-        <v>0.419507771730423</v>
+        <v>0.419507801532745</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>0.572000026702881</v>
       </c>
       <c r="G1004" t="n">
-        <v>0.439484357833862</v>
+        <v>0.43948432803154</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>0.566999971866608</v>
       </c>
       <c r="G1005" t="n">
-        <v>0.435642629861832</v>
+        <v>0.435642659664154</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G1006" t="n">
-        <v>0.436410993337631</v>
+        <v>0.436411023139954</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G1009" t="n">
-        <v>0.451777577400208</v>
+        <v>0.451777547597885</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1010" t="n">
-        <v>0.44563090801239</v>
+        <v>0.445630967617035</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>0.570999979972839</v>
       </c>
       <c r="G1011" t="n">
-        <v>0.438715934753418</v>
+        <v>0.43871596455574</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>0.569000005722046</v>
       </c>
       <c r="G1012" t="n">
-        <v>0.437179356813431</v>
+        <v>0.437179327011108</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G1013" t="n">
-        <v>0.436410993337631</v>
+        <v>0.436411023139954</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>0.561999976634979</v>
       </c>
       <c r="G1014" t="n">
-        <v>0.431800991296768</v>
+        <v>0.431801050901413</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>0.561999976634979</v>
       </c>
       <c r="G1015" t="n">
-        <v>0.431800991296768</v>
+        <v>0.431801050901413</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>0.578000009059906</v>
       </c>
       <c r="G1016" t="n">
-        <v>0.444094300270081</v>
+        <v>0.444094270467758</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>0.566999971866608</v>
       </c>
       <c r="G1017" t="n">
-        <v>0.435642629861832</v>
+        <v>0.435642659664154</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G1018" t="n">
-        <v>0.42719104886055</v>
+        <v>0.427191019058228</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>0.564999997615814</v>
       </c>
       <c r="G1019" t="n">
-        <v>0.434106051921844</v>
+        <v>0.4341059923172</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>0.561999976634979</v>
       </c>
       <c r="G1020" t="n">
-        <v>0.431800991296768</v>
+        <v>0.431801050901413</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G1023" t="n">
-        <v>0.467144191265106</v>
+        <v>0.467144101858139</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1024" t="n">
-        <v>0.457155883312225</v>
+        <v>0.45715594291687</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>0.577000021934509</v>
       </c>
       <c r="G1026" t="n">
-        <v>0.443325936794281</v>
+        <v>0.443325996398926</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G1027" t="n">
-        <v>0.441020995378494</v>
+        <v>0.441020965576172</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>0.578999996185303</v>
       </c>
       <c r="G1029" t="n">
-        <v>0.444862633943558</v>
+        <v>0.444862574338913</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>0.566999971866608</v>
       </c>
       <c r="G1030" t="n">
-        <v>0.435642629861832</v>
+        <v>0.435642659664154</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>0.556999981403351</v>
       </c>
       <c r="G1031" t="n">
-        <v>0.427959352731705</v>
+        <v>0.427959322929382</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>0.561999976634979</v>
       </c>
       <c r="G1032" t="n">
-        <v>0.431800991296768</v>
+        <v>0.431801050901413</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1033" t="n">
-        <v>0.414897799491882</v>
+        <v>0.414897829294205</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>0.541999995708466</v>
       </c>
       <c r="G1034" t="n">
-        <v>0.416434466838837</v>
+        <v>0.416434437036514</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1035" t="n">
-        <v>0.407214432954788</v>
+        <v>0.407214522361755</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>0.538999974727631</v>
       </c>
       <c r="G1041" t="n">
-        <v>0.414129436016083</v>
+        <v>0.414129376411438</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>0.517000019550323</v>
       </c>
       <c r="G1042" t="n">
-        <v>0.397226184606552</v>
+        <v>0.397226214408875</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G1045" t="n">
-        <v>0.399531155824661</v>
+        <v>0.399531185626984</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>0.523999989032745</v>
       </c>
       <c r="G1048" t="n">
-        <v>0.402604460716248</v>
+        <v>0.402604520320892</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1049" t="n">
-        <v>0.407214432954788</v>
+        <v>0.407214522361755</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>0.52700001001358</v>
       </c>
       <c r="G1050" t="n">
-        <v>0.404909491539001</v>
+        <v>0.404909521341324</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G1051" t="n">
-        <v>0.399531155824661</v>
+        <v>0.399531185626984</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>0.476000010967255</v>
       </c>
       <c r="G1053" t="n">
-        <v>0.365724742412567</v>
+        <v>0.365724712610245</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1054" t="n">
-        <v>0.37648132443428</v>
+        <v>0.376481354236603</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>0.505999982357025</v>
       </c>
       <c r="G1055" t="n">
-        <v>0.388774544000626</v>
+        <v>0.388774573802948</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>0.449000000953674</v>
       </c>
       <c r="G1060" t="n">
-        <v>0.344979852437973</v>
+        <v>0.344979822635651</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G1061" t="n">
-        <v>0.317319989204407</v>
+        <v>0.317319959402084</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>0.391999989748001</v>
       </c>
       <c r="G1062" t="n">
-        <v>0.301185011863708</v>
+        <v>0.301185071468353</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>0.344999998807907</v>
       </c>
       <c r="G1063" t="n">
-        <v>0.265073537826538</v>
+        <v>0.26507356762886</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>0.337999999523163</v>
       </c>
       <c r="G1064" t="n">
-        <v>0.259695291519165</v>
+        <v>0.259695261716843</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>0.349000006914139</v>
       </c>
       <c r="G1065" t="n">
-        <v>0.268146902322769</v>
+        <v>0.268146932125092</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>0.311500012874603</v>
       </c>
       <c r="G1066" t="n">
-        <v>0.23933456838131</v>
+        <v>0.239334538578987</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>0.314999997615814</v>
       </c>
       <c r="G1067" t="n">
-        <v>0.242023676633835</v>
+        <v>0.242023721337318</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>0.319999992847443</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.245865345001221</v>
+        <v>0.245865315198898</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>0.337000012397766</v>
       </c>
       <c r="G1070" t="n">
-        <v>0.258926928043365</v>
+        <v>0.258926957845688</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>0.327499985694885</v>
       </c>
       <c r="G1071" t="n">
-        <v>0.251627832651138</v>
+        <v>0.251627802848816</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>0.360000014305115</v>
       </c>
       <c r="G1073" t="n">
-        <v>0.276598542928696</v>
+        <v>0.276598513126373</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>0.36599999666214</v>
       </c>
       <c r="G1074" t="n">
-        <v>0.281208544969559</v>
+        <v>0.281208485364914</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>0.360000014305115</v>
       </c>
       <c r="G1075" t="n">
-        <v>0.276598542928696</v>
+        <v>0.276598513126373</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>0.350499987602234</v>
       </c>
       <c r="G1076" t="n">
-        <v>0.269299328327179</v>
+        <v>0.269299417734146</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>0.328000009059906</v>
       </c>
       <c r="G1079" t="n">
-        <v>0.252011984586716</v>
+        <v>0.252011954784393</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>0.328000009059906</v>
       </c>
       <c r="G1081" t="n">
-        <v>0.252011984586716</v>
+        <v>0.252011954784393</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>0.319000005722046</v>
       </c>
       <c r="G1082" t="n">
-        <v>0.245097011327744</v>
+        <v>0.245097041130066</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>0.328000009059906</v>
       </c>
       <c r="G1083" t="n">
-        <v>0.252011984586716</v>
+        <v>0.252011954784393</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>0.331499993801117</v>
       </c>
       <c r="G1084" t="n">
-        <v>0.254701107740402</v>
+        <v>0.254701137542725</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>0.337999999523163</v>
       </c>
       <c r="G1085" t="n">
-        <v>0.259695291519165</v>
+        <v>0.259695261716843</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>0.337999999523163</v>
       </c>
       <c r="G1087" t="n">
-        <v>0.259695291519165</v>
+        <v>0.259695261716843</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>0.331000000238419</v>
       </c>
       <c r="G1088" t="n">
-        <v>0.254316985607147</v>
+        <v>0.254316955804825</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>0.340000003576279</v>
       </c>
       <c r="G1089" t="n">
-        <v>0.261231958866119</v>
+        <v>0.261231899261475</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>0.344500005245209</v>
       </c>
       <c r="G1092" t="n">
-        <v>0.264689415693283</v>
+        <v>0.264689445495605</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>0.351999998092651</v>
       </c>
       <c r="G1095" t="n">
-        <v>0.270451903343201</v>
+        <v>0.270451873540878</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>0.354000002145767</v>
       </c>
       <c r="G1096" t="n">
-        <v>0.271988540887833</v>
+        <v>0.27198851108551</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>0.351999998092651</v>
       </c>
       <c r="G1098" t="n">
-        <v>0.270451903343201</v>
+        <v>0.270451873540878</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>0.360500007867813</v>
       </c>
       <c r="G1099" t="n">
-        <v>0.276982724666595</v>
+        <v>0.276982665061951</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>0.361999988555908</v>
       </c>
       <c r="G1100" t="n">
-        <v>0.278135120868683</v>
+        <v>0.278135150671005</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>0.354999989271164</v>
       </c>
       <c r="G1101" t="n">
-        <v>0.272756844758987</v>
+        <v>0.27275687456131</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>0.350499987602234</v>
       </c>
       <c r="G1102" t="n">
-        <v>0.269299328327179</v>
+        <v>0.269299417734146</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>0.349000006914139</v>
       </c>
       <c r="G1105" t="n">
-        <v>0.268146902322769</v>
+        <v>0.268146932125092</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>0.349999994039536</v>
       </c>
       <c r="G1106" t="n">
-        <v>0.268915235996246</v>
+        <v>0.268915206193924</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>0.345999985933304</v>
       </c>
       <c r="G1107" t="n">
-        <v>0.265841871500015</v>
+        <v>0.265841901302338</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>0.344999998807907</v>
       </c>
       <c r="G1111" t="n">
-        <v>0.265073537826538</v>
+        <v>0.26507356762886</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>0.337000012397766</v>
       </c>
       <c r="G1112" t="n">
-        <v>0.258926928043365</v>
+        <v>0.258926957845688</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>0.341500014066696</v>
       </c>
       <c r="G1113" t="n">
-        <v>0.262384414672852</v>
+        <v>0.262384444475174</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>0.341500014066696</v>
       </c>
       <c r="G1114" t="n">
-        <v>0.262384414672852</v>
+        <v>0.262384444475174</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>0.342500001192093</v>
       </c>
       <c r="G1115" t="n">
-        <v>0.263152748346329</v>
+        <v>0.263152778148651</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>0.351999998092651</v>
       </c>
       <c r="G1116" t="n">
-        <v>0.270451903343201</v>
+        <v>0.270451873540878</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>0.349999994039536</v>
       </c>
       <c r="G1117" t="n">
-        <v>0.268915235996246</v>
+        <v>0.268915206193924</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>0.349999994039536</v>
       </c>
       <c r="G1118" t="n">
-        <v>0.268915235996246</v>
+        <v>0.268915206193924</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>0.360000014305115</v>
       </c>
       <c r="G1120" t="n">
-        <v>0.276598542928696</v>
+        <v>0.276598513126373</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>0.360000014305115</v>
       </c>
       <c r="G1121" t="n">
-        <v>0.276598542928696</v>
+        <v>0.276598513126373</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>0.379999995231628</v>
       </c>
       <c r="G1122" t="n">
-        <v>0.291965067386627</v>
+        <v>0.291965126991272</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>0.426499992609024</v>
       </c>
       <c r="G1125" t="n">
-        <v>0.327692419290543</v>
+        <v>0.327692449092865</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>0.393500000238419</v>
       </c>
       <c r="G1129" t="n">
-        <v>0.302337527275085</v>
+        <v>0.302337557077408</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>0.421499997377396</v>
       </c>
       <c r="G1131" t="n">
-        <v>0.323850780725479</v>
+        <v>0.323850750923157</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>0.45550000667572</v>
       </c>
       <c r="G1132" t="n">
-        <v>0.349973946809769</v>
+        <v>0.349973976612091</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>0.412499994039536</v>
       </c>
       <c r="G1136" t="n">
-        <v>0.316935837268829</v>
+        <v>0.316935807466507</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>0.375999987125397</v>
       </c>
       <c r="G1142" t="n">
-        <v>0.288891762495041</v>
+        <v>0.288891792297363</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>0.402500003576279</v>
       </c>
       <c r="G1143" t="n">
-        <v>0.309252500534058</v>
+        <v>0.30925253033638</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>0.397000014781952</v>
       </c>
       <c r="G1144" t="n">
-        <v>0.305026710033417</v>
+        <v>0.305026739835739</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>0.387499988079071</v>
       </c>
       <c r="G1147" t="n">
-        <v>0.297727584838867</v>
+        <v>0.297727555036545</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>0.387499988079071</v>
       </c>
       <c r="G1149" t="n">
-        <v>0.297727584838867</v>
+        <v>0.297727555036545</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>0.394499987363815</v>
       </c>
       <c r="G1151" t="n">
-        <v>0.30310583114624</v>
+        <v>0.303105890750885</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>0.398000001907349</v>
       </c>
       <c r="G1152" t="n">
-        <v>0.305795013904572</v>
+        <v>0.305795043706894</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>0.398000001907349</v>
       </c>
       <c r="G1154" t="n">
-        <v>0.305795013904572</v>
+        <v>0.305795043706894</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G1155" t="n">
-        <v>0.307331681251526</v>
+        <v>0.307331711053848</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G1157" t="n">
-        <v>0.327308267354965</v>
+        <v>0.327308237552643</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>0.40650001168251</v>
       </c>
       <c r="G1159" t="n">
-        <v>0.312325805425644</v>
+        <v>0.312325835227966</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>0.402500003576279</v>
       </c>
       <c r="G1160" t="n">
-        <v>0.309252500534058</v>
+        <v>0.30925253033638</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G1162" t="n">
-        <v>0.331918239593506</v>
+        <v>0.331918209791183</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>0.418500006198883</v>
       </c>
       <c r="G1163" t="n">
-        <v>0.321545779705048</v>
+        <v>0.32154580950737</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>0.407499998807907</v>
       </c>
       <c r="G1164" t="n">
-        <v>0.313094168901443</v>
+        <v>0.313094139099121</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>0.423500001430511</v>
       </c>
       <c r="G1165" t="n">
-        <v>0.325387448072433</v>
+        <v>0.325387418270111</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>0.418999999761581</v>
       </c>
       <c r="G1166" t="n">
-        <v>0.321929961442947</v>
+        <v>0.321929901838303</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G1168" t="n">
-        <v>0.314246654510498</v>
+        <v>0.31424668431282</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>0.420500010251999</v>
       </c>
       <c r="G1171" t="n">
-        <v>0.323082387447357</v>
+        <v>0.32308241724968</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>0.418500006198883</v>
       </c>
       <c r="G1172" t="n">
-        <v>0.321545779705048</v>
+        <v>0.32154580950737</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G1173" t="n">
-        <v>0.317319989204407</v>
+        <v>0.317319959402084</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>0.404000014066696</v>
       </c>
       <c r="G1174" t="n">
-        <v>0.310405015945435</v>
+        <v>0.310405045747757</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>0.404000014066696</v>
       </c>
       <c r="G1178" t="n">
-        <v>0.310405015945435</v>
+        <v>0.310405045747757</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>0.397000014781952</v>
       </c>
       <c r="G1179" t="n">
-        <v>0.305026710033417</v>
+        <v>0.305026739835739</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>0.393500000238419</v>
       </c>
       <c r="G1181" t="n">
-        <v>0.302337527275085</v>
+        <v>0.302337557077408</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>0.380499988794327</v>
       </c>
       <c r="G1188" t="n">
-        <v>0.292349278926849</v>
+        <v>0.292349249124527</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>0.38400000333786</v>
       </c>
       <c r="G1189" t="n">
-        <v>0.295038402080536</v>
+        <v>0.295038431882858</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>0.379999995231628</v>
       </c>
       <c r="G1190" t="n">
-        <v>0.291965067386627</v>
+        <v>0.291965126991272</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>0.374000012874603</v>
       </c>
       <c r="G1192" t="n">
-        <v>0.287355154752731</v>
+        <v>0.287355124950409</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>0.376500010490417</v>
       </c>
       <c r="G1193" t="n">
-        <v>0.289275974035263</v>
+        <v>0.289275944232941</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>0.379000008106232</v>
       </c>
       <c r="G1194" t="n">
-        <v>0.291196793317795</v>
+        <v>0.291196763515472</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>0.369500011205673</v>
       </c>
       <c r="G1196" t="n">
-        <v>0.283897697925568</v>
+        <v>0.283897638320923</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>0.379999995231628</v>
       </c>
       <c r="G1197" t="n">
-        <v>0.291965067386627</v>
+        <v>0.291965126991272</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>0.372999995946884</v>
       </c>
       <c r="G1198" t="n">
-        <v>0.286586791276932</v>
+        <v>0.286586821079254</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>0.370999991893768</v>
       </c>
       <c r="G1199" t="n">
-        <v>0.285050123929977</v>
+        <v>0.2850501537323</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>0.356000006198883</v>
       </c>
       <c r="G1200" t="n">
-        <v>0.273525238037109</v>
+        <v>0.273525208234787</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>0.354999989271164</v>
       </c>
       <c r="G1201" t="n">
-        <v>0.272756844758987</v>
+        <v>0.27275687456131</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>0.354999989271164</v>
       </c>
       <c r="G1202" t="n">
-        <v>0.272756844758987</v>
+        <v>0.27275687456131</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>0.349999994039536</v>
       </c>
       <c r="G1203" t="n">
-        <v>0.268915235996246</v>
+        <v>0.268915206193924</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>0.340499997138977</v>
       </c>
       <c r="G1205" t="n">
-        <v>0.261616080999374</v>
+        <v>0.261616110801697</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>0.344500005245209</v>
       </c>
       <c r="G1206" t="n">
-        <v>0.264689415693283</v>
+        <v>0.264689445495605</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>0.368000000715256</v>
       </c>
       <c r="G1212" t="n">
-        <v>0.282745122909546</v>
+        <v>0.282745152711868</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>0.360000014305115</v>
       </c>
       <c r="G1214" t="n">
-        <v>0.276598542928696</v>
+        <v>0.276598513126373</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>0.349999994039536</v>
       </c>
       <c r="G1215" t="n">
-        <v>0.268915235996246</v>
+        <v>0.268915206193924</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>0.349000006914139</v>
       </c>
       <c r="G1216" t="n">
-        <v>0.268146902322769</v>
+        <v>0.268146932125092</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>0.344500005245209</v>
       </c>
       <c r="G1218" t="n">
-        <v>0.264689415693283</v>
+        <v>0.264689445495605</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>0.337000012397766</v>
       </c>
       <c r="G1219" t="n">
-        <v>0.258926928043365</v>
+        <v>0.258926957845688</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>0.344999998807907</v>
       </c>
       <c r="G1220" t="n">
-        <v>0.265073537826538</v>
+        <v>0.26507356762886</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>0.340000003576279</v>
       </c>
       <c r="G1221" t="n">
-        <v>0.261231958866119</v>
+        <v>0.261231899261475</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>0.333499997854233</v>
       </c>
       <c r="G1225" t="n">
-        <v>0.256237834692001</v>
+        <v>0.256237775087357</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>0.307500004768372</v>
       </c>
       <c r="G1227" t="n">
-        <v>0.236261248588562</v>
+        <v>0.236261233687401</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>0.330000013113022</v>
       </c>
       <c r="G1229" t="n">
-        <v>0.25354865193367</v>
+        <v>0.253548622131348</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>0.34850001335144</v>
       </c>
       <c r="G1230" t="n">
-        <v>0.267762720584869</v>
+        <v>0.267762780189514</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>0.359499990940094</v>
       </c>
       <c r="G1233" t="n">
-        <v>0.276214331388474</v>
+        <v>0.276214301586151</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>0.356000006198883</v>
       </c>
       <c r="G1234" t="n">
-        <v>0.273525238037109</v>
+        <v>0.273525208234787</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>0.36149999499321</v>
       </c>
       <c r="G1235" t="n">
-        <v>0.27775102853775</v>
+        <v>0.277750998735428</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>0.354999989271164</v>
       </c>
       <c r="G1236" t="n">
-        <v>0.272756844758987</v>
+        <v>0.27275687456131</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>0.356000006198883</v>
       </c>
       <c r="G1237" t="n">
-        <v>0.273525238037109</v>
+        <v>0.273525208234787</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>0.383500009775162</v>
       </c>
       <c r="G1239" t="n">
-        <v>0.294654279947281</v>
+        <v>0.294654220342636</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>0.405499994754791</v>
       </c>
       <c r="G1242" t="n">
-        <v>0.311557501554489</v>
+        <v>0.311557471752167</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>0.396499991416931</v>
       </c>
       <c r="G1243" t="n">
-        <v>0.304642558097839</v>
+        <v>0.304642528295517</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>0.392500013113022</v>
       </c>
       <c r="G1245" t="n">
-        <v>0.301569253206253</v>
+        <v>0.301569223403931</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>0.399500012397766</v>
       </c>
       <c r="G1247" t="n">
-        <v>0.306947559118271</v>
+        <v>0.306947529315948</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G1248" t="n">
-        <v>0.319624960422516</v>
+        <v>0.319624930620193</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G1250" t="n">
-        <v>0.330381572246552</v>
+        <v>0.330381542444229</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G1253" t="n">
-        <v>0.344211488962173</v>
+        <v>0.344211518764496</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>0.447499990463257</v>
       </c>
       <c r="G1255" t="n">
-        <v>0.343827307224274</v>
+        <v>0.343827337026596</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1256" t="n">
-        <v>0.345748096704483</v>
+        <v>0.345748156309128</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>0.440499991178513</v>
       </c>
       <c r="G1257" t="n">
-        <v>0.338449001312256</v>
+        <v>0.338449060916901</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>0.440499991178513</v>
       </c>
       <c r="G1258" t="n">
-        <v>0.338449001312256</v>
+        <v>0.338449060916901</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G1264" t="n">
-        <v>0.327308267354965</v>
+        <v>0.327308237552643</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>0.418999999761581</v>
       </c>
       <c r="G1266" t="n">
-        <v>0.321929961442947</v>
+        <v>0.321929901838303</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G1267" t="n">
-        <v>0.324234962463379</v>
+        <v>0.324234902858734</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G1268" t="n">
-        <v>0.324234962463379</v>
+        <v>0.324234902858734</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>0.413500010967255</v>
       </c>
       <c r="G1270" t="n">
-        <v>0.317704141139984</v>
+        <v>0.317704111337662</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G1271" t="n">
-        <v>0.324234962463379</v>
+        <v>0.324234902858734</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G1273" t="n">
-        <v>0.344211488962173</v>
+        <v>0.344211518764496</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G1274" t="n">
-        <v>0.338064879179001</v>
+        <v>0.338064819574356</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>0.438499987125397</v>
       </c>
       <c r="G1275" t="n">
-        <v>0.336912363767624</v>
+        <v>0.336912393569946</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>0.425500005483627</v>
       </c>
       <c r="G1276" t="n">
-        <v>0.326924085617065</v>
+        <v>0.326924055814743</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G1279" t="n">
-        <v>0.328844904899597</v>
+        <v>0.328844875097275</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>0.426499992609024</v>
       </c>
       <c r="G1283" t="n">
-        <v>0.327692419290543</v>
+        <v>0.327692449092865</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>0.416999995708466</v>
       </c>
       <c r="G1284" t="n">
-        <v>0.320393294095993</v>
+        <v>0.320393264293671</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G1285" t="n">
-        <v>0.317319989204407</v>
+        <v>0.317319959402084</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>0.405499994754791</v>
       </c>
       <c r="G1287" t="n">
-        <v>0.311557501554489</v>
+        <v>0.311557471752167</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>0.397000014781952</v>
       </c>
       <c r="G1288" t="n">
-        <v>0.305026710033417</v>
+        <v>0.305026739835739</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G1289" t="n">
-        <v>0.307331681251526</v>
+        <v>0.307331711053848</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>0.407499998807907</v>
       </c>
       <c r="G1291" t="n">
-        <v>0.313094168901443</v>
+        <v>0.313094139099121</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>0.4375</v>
       </c>
       <c r="G1293" t="n">
-        <v>0.336144030094147</v>
+        <v>0.336144000291824</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>0.438499987125397</v>
       </c>
       <c r="G1297" t="n">
-        <v>0.336912363767624</v>
+        <v>0.336912393569946</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>0.452499985694885</v>
       </c>
       <c r="G1299" t="n">
-        <v>0.347668945789337</v>
+        <v>0.347669005393982</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>0.467500001192093</v>
       </c>
       <c r="G1300" t="n">
-        <v>0.35919389128685</v>
+        <v>0.359193950891495</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>0.458000004291534</v>
       </c>
       <c r="G1302" t="n">
-        <v>0.3518947660923</v>
+        <v>0.351894795894623</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>0.46450001001358</v>
       </c>
       <c r="G1308" t="n">
-        <v>0.356888890266418</v>
+        <v>0.356888949871063</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>0.474000006914139</v>
       </c>
       <c r="G1311" t="n">
-        <v>0.36418804526329</v>
+        <v>0.364188075065613</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>0.479000002145767</v>
       </c>
       <c r="G1312" t="n">
-        <v>0.368029713630676</v>
+        <v>0.368029683828354</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>0.460999995470047</v>
       </c>
       <c r="G1317" t="n">
-        <v>0.354199767112732</v>
+        <v>0.35419973731041</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>0.465499997138977</v>
       </c>
       <c r="G1319" t="n">
-        <v>0.35765728354454</v>
+        <v>0.357657253742218</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>0.46399998664856</v>
       </c>
       <c r="G1320" t="n">
-        <v>0.356504738330841</v>
+        <v>0.356504708528519</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>0.453000009059906</v>
       </c>
       <c r="G1323" t="n">
-        <v>0.348053157329559</v>
+        <v>0.348053127527237</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>0.456999987363815</v>
       </c>
       <c r="G1324" t="n">
-        <v>0.351126462221146</v>
+        <v>0.351126432418823</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>0.46450001001358</v>
       </c>
       <c r="G1325" t="n">
-        <v>0.356888890266418</v>
+        <v>0.356888949871063</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>0.45550000667572</v>
       </c>
       <c r="G1327" t="n">
-        <v>0.349973946809769</v>
+        <v>0.349973976612091</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>0.45100000500679</v>
       </c>
       <c r="G1328" t="n">
-        <v>0.346516489982605</v>
+        <v>0.346516460180283</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>0.456000000238419</v>
       </c>
       <c r="G1329" t="n">
-        <v>0.350358128547668</v>
+        <v>0.350358098745346</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>0.450500011444092</v>
       </c>
       <c r="G1330" t="n">
-        <v>0.346132308244705</v>
+        <v>0.346132338047028</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>0.451999992132187</v>
       </c>
       <c r="G1332" t="n">
-        <v>0.347284823656082</v>
+        <v>0.347284764051437</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>0.460999995470047</v>
       </c>
       <c r="G1333" t="n">
-        <v>0.354199767112732</v>
+        <v>0.35419973731041</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>0.472499996423721</v>
       </c>
       <c r="G1335" t="n">
-        <v>0.363035529851913</v>
+        <v>0.363035559654236</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>0.469999998807907</v>
       </c>
       <c r="G1336" t="n">
-        <v>0.361114710569382</v>
+        <v>0.361114740371704</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>0.458000004291534</v>
       </c>
       <c r="G1338" t="n">
-        <v>0.3518947660923</v>
+        <v>0.351894795894623</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>0.46450001001358</v>
       </c>
       <c r="G1339" t="n">
-        <v>0.356888890266418</v>
+        <v>0.356888949871063</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>0.477999985218048</v>
       </c>
       <c r="G1340" t="n">
-        <v>0.367261320352554</v>
+        <v>0.367261350154877</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>0.493499994277954</v>
       </c>
       <c r="G1342" t="n">
-        <v>0.379170477390289</v>
+        <v>0.379170447587967</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>0.493499994277954</v>
       </c>
       <c r="G1344" t="n">
-        <v>0.379170477390289</v>
+        <v>0.379170447587967</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>0.472499996423721</v>
       </c>
       <c r="G1346" t="n">
-        <v>0.363035529851913</v>
+        <v>0.363035559654236</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>0.476000010967255</v>
       </c>
       <c r="G1348" t="n">
-        <v>0.365724742412567</v>
+        <v>0.365724712610245</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>0.477999985218048</v>
       </c>
       <c r="G1349" t="n">
-        <v>0.367261320352554</v>
+        <v>0.367261350154877</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>0.476000010967255</v>
       </c>
       <c r="G1351" t="n">
-        <v>0.365724742412567</v>
+        <v>0.365724712610245</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>0.465499997138977</v>
       </c>
       <c r="G1353" t="n">
-        <v>0.35765728354454</v>
+        <v>0.357657253742218</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>0.477999985218048</v>
       </c>
       <c r="G1360" t="n">
-        <v>0.367261320352554</v>
+        <v>0.367261350154877</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>0.476000010967255</v>
       </c>
       <c r="G1361" t="n">
-        <v>0.365724742412567</v>
+        <v>0.365724712610245</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>0.476000010967255</v>
       </c>
       <c r="G1362" t="n">
-        <v>0.365724742412567</v>
+        <v>0.365724712610245</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>0.48649999499321</v>
       </c>
       <c r="G1365" t="n">
-        <v>0.373792171478271</v>
+        <v>0.373792141675949</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>0.486999988555908</v>
       </c>
       <c r="G1366" t="n">
-        <v>0.374176353216171</v>
+        <v>0.374176323413849</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>0.484499990940094</v>
       </c>
       <c r="G1367" t="n">
-        <v>0.372255504131317</v>
+        <v>0.372255474328995</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>0.476999998092651</v>
       </c>
       <c r="G1370" t="n">
-        <v>0.366492986679077</v>
+        <v>0.3664930164814</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>0.474000006914139</v>
       </c>
       <c r="G1372" t="n">
-        <v>0.36418804526329</v>
+        <v>0.364188075065613</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>0.479000002145767</v>
       </c>
       <c r="G1373" t="n">
-        <v>0.368029713630676</v>
+        <v>0.368029683828354</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>0.48199999332428</v>
       </c>
       <c r="G1374" t="n">
-        <v>0.370334684848785</v>
+        <v>0.370334714651108</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>0.485500007867813</v>
       </c>
       <c r="G1375" t="n">
-        <v>0.373023837804794</v>
+        <v>0.373023808002472</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>0.493999987840652</v>
       </c>
       <c r="G1376" t="n">
-        <v>0.379554599523544</v>
+        <v>0.379554659128189</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>0.501999974250793</v>
       </c>
       <c r="G1378" t="n">
-        <v>0.385701239109039</v>
+        <v>0.385701268911362</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>0.510999977588654</v>
       </c>
       <c r="G1379" t="n">
-        <v>0.392616182565689</v>
+        <v>0.392616242170334</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G1384" t="n">
-        <v>0.42719104886055</v>
+        <v>0.427191019058228</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G1385" t="n">
-        <v>0.430264383554459</v>
+        <v>0.430264353752136</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>0.545000016689301</v>
       </c>
       <c r="G1387" t="n">
-        <v>0.418739467859268</v>
+        <v>0.418739438056946</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>0.545000016689301</v>
       </c>
       <c r="G1390" t="n">
-        <v>0.418739467859268</v>
+        <v>0.418739438056946</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>0.541999995708466</v>
       </c>
       <c r="G1391" t="n">
-        <v>0.416434466838837</v>
+        <v>0.416434437036514</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1392" t="n">
-        <v>0.414897799491882</v>
+        <v>0.414897829294205</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>0.537000000476837</v>
       </c>
       <c r="G1393" t="n">
-        <v>0.412592798471451</v>
+        <v>0.412592768669128</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>0.531000018119812</v>
       </c>
       <c r="G1394" t="n">
-        <v>0.407982856035233</v>
+        <v>0.40798282623291</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>0.532999992370605</v>
       </c>
       <c r="G1395" t="n">
-        <v>0.40951943397522</v>
+        <v>0.409519493579865</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>0.537000000476837</v>
       </c>
       <c r="G1396" t="n">
-        <v>0.412592798471451</v>
+        <v>0.412592768669128</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>0.538999974727631</v>
       </c>
       <c r="G1397" t="n">
-        <v>0.414129436016083</v>
+        <v>0.414129376411438</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>0.541999995708466</v>
       </c>
       <c r="G1398" t="n">
-        <v>0.416434466838837</v>
+        <v>0.416434437036514</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>0.550999999046326</v>
       </c>
       <c r="G1399" t="n">
-        <v>0.423349410295486</v>
+        <v>0.423349380493164</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>0.538999974727631</v>
       </c>
       <c r="G1404" t="n">
-        <v>0.414129436016083</v>
+        <v>0.414129376411438</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>0.523999989032745</v>
       </c>
       <c r="G1405" t="n">
-        <v>0.402604460716248</v>
+        <v>0.402604520320892</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>0.510999977588654</v>
       </c>
       <c r="G1406" t="n">
-        <v>0.392616182565689</v>
+        <v>0.392616242170334</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>0.493499994277954</v>
       </c>
       <c r="G1411" t="n">
-        <v>0.379170477390289</v>
+        <v>0.379170447587967</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>0.497000008821487</v>
       </c>
       <c r="G1413" t="n">
-        <v>0.381859600543976</v>
+        <v>0.381859630346298</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>0.505999982357025</v>
       </c>
       <c r="G1417" t="n">
-        <v>0.388774544000626</v>
+        <v>0.388774573802948</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>0.501999974250793</v>
       </c>
       <c r="G1421" t="n">
-        <v>0.385701239109039</v>
+        <v>0.385701268911362</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>0.497500002384186</v>
       </c>
       <c r="G1422" t="n">
-        <v>0.382243752479553</v>
+        <v>0.382243782281876</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>0.498499989509583</v>
       </c>
       <c r="G1423" t="n">
-        <v>0.383012115955353</v>
+        <v>0.38301208615303</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1424" t="n">
-        <v>0.37648132443428</v>
+        <v>0.376481354236603</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>0.492000013589859</v>
       </c>
       <c r="G1426" t="n">
-        <v>0.378018021583557</v>
+        <v>0.378017991781235</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>0.492500007152557</v>
       </c>
       <c r="G1427" t="n">
-        <v>0.378402173519135</v>
+        <v>0.378402143716812</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1430" t="n">
-        <v>0.37648132443428</v>
+        <v>0.376481354236603</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>0.467500001192093</v>
       </c>
       <c r="G1432" t="n">
-        <v>0.35919389128685</v>
+        <v>0.359193950891495</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>0.451999992132187</v>
       </c>
       <c r="G1434" t="n">
-        <v>0.347284823656082</v>
+        <v>0.347284764051437</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>0.453500002622604</v>
       </c>
       <c r="G1435" t="n">
-        <v>0.348437279462814</v>
+        <v>0.348437309265137</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>0.463499993085861</v>
       </c>
       <c r="G1438" t="n">
-        <v>0.356120556592941</v>
+        <v>0.356120616197586</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G1442" t="n">
-        <v>0.422581076622009</v>
+        <v>0.422581046819687</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>0.545000016689301</v>
       </c>
       <c r="G1443" t="n">
-        <v>0.418739467859268</v>
+        <v>0.418739438056946</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G1445" t="n">
-        <v>0.422581076622009</v>
+        <v>0.422581046819687</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>0.549000024795532</v>
       </c>
       <c r="G1446" t="n">
-        <v>0.421812772750854</v>
+        <v>0.421812742948532</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>0.537000000476837</v>
       </c>
       <c r="G1447" t="n">
-        <v>0.412592798471451</v>
+        <v>0.412592768669128</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>0.521000027656555</v>
       </c>
       <c r="G1449" t="n">
-        <v>0.400299519300461</v>
+        <v>0.400299549102783</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G1451" t="n">
-        <v>0.399531155824661</v>
+        <v>0.399531185626984</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>0.517000019550323</v>
       </c>
       <c r="G1452" t="n">
-        <v>0.397226184606552</v>
+        <v>0.397226214408875</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>0.523999989032745</v>
       </c>
       <c r="G1459" t="n">
-        <v>0.402604460716248</v>
+        <v>0.402604520320892</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>0.500999987125397</v>
       </c>
       <c r="G1460" t="n">
-        <v>0.384932935237885</v>
+        <v>0.384932905435562</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>0.49549999833107</v>
       </c>
       <c r="G1464" t="n">
-        <v>0.380707144737244</v>
+        <v>0.380707085132599</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>0.494500011205673</v>
       </c>
       <c r="G1465" t="n">
-        <v>0.379938751459122</v>
+        <v>0.379938781261444</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>0.504999995231628</v>
       </c>
       <c r="G1468" t="n">
-        <v>0.388006269931793</v>
+        <v>0.388006240129471</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>0.545000016689301</v>
       </c>
       <c r="G1469" t="n">
-        <v>0.418739467859268</v>
+        <v>0.418739438056946</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>0.531000018119812</v>
       </c>
       <c r="G1473" t="n">
-        <v>0.407982856035233</v>
+        <v>0.40798282623291</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>0.521000027656555</v>
       </c>
       <c r="G1476" t="n">
-        <v>0.400299519300461</v>
+        <v>0.400299549102783</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>0.523999989032745</v>
       </c>
       <c r="G1477" t="n">
-        <v>0.402604460716248</v>
+        <v>0.402604520320892</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>0.523999989032745</v>
       </c>
       <c r="G1478" t="n">
-        <v>0.402604460716248</v>
+        <v>0.402604520320892</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>0.538999974727631</v>
       </c>
       <c r="G1479" t="n">
-        <v>0.414129436016083</v>
+        <v>0.414129376411438</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>0.541000008583069</v>
       </c>
       <c r="G1480" t="n">
-        <v>0.415666103363037</v>
+        <v>0.415666043758392</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>0.514999985694885</v>
       </c>
       <c r="G1484" t="n">
-        <v>0.39568954706192</v>
+        <v>0.395689517259598</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>0.514999985694885</v>
       </c>
       <c r="G1487" t="n">
-        <v>0.39568954706192</v>
+        <v>0.395689517259598</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G1488" t="n">
-        <v>0.399531155824661</v>
+        <v>0.399531185626984</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1491" t="n">
-        <v>0.414897799491882</v>
+        <v>0.414897829294205</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>0.515999972820282</v>
       </c>
       <c r="G1495" t="n">
-        <v>0.396457850933075</v>
+        <v>0.396457880735397</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>0.500999987125397</v>
       </c>
       <c r="G1497" t="n">
-        <v>0.384932935237885</v>
+        <v>0.384932905435562</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1500" t="n">
-        <v>0.37648132443428</v>
+        <v>0.376481354236603</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>0.487500011920929</v>
       </c>
       <c r="G1501" t="n">
-        <v>0.374560505151749</v>
+        <v>0.374560475349426</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>0.479499995708466</v>
       </c>
       <c r="G1502" t="n">
-        <v>0.368413835763931</v>
+        <v>0.368413865566254</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>0.460500001907349</v>
       </c>
       <c r="G1503" t="n">
-        <v>0.353815615177155</v>
+        <v>0.353815644979477</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>0.452499985694885</v>
       </c>
       <c r="G1504" t="n">
-        <v>0.347668945789337</v>
+        <v>0.347669005393982</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>0.453000009059906</v>
       </c>
       <c r="G1505" t="n">
-        <v>0.348053157329559</v>
+        <v>0.348053127527237</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>0.46399998664856</v>
       </c>
       <c r="G1506" t="n">
-        <v>0.356504738330841</v>
+        <v>0.356504708528519</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>0.435000002384186</v>
       </c>
       <c r="G1509" t="n">
-        <v>0.334223210811615</v>
+        <v>0.334223181009293</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>0.445499986410141</v>
       </c>
       <c r="G1511" t="n">
-        <v>0.342290669679642</v>
+        <v>0.342290639877319</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G1514" t="n">
-        <v>0.331918239593506</v>
+        <v>0.331918209791183</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G1515" t="n">
-        <v>0.329613268375397</v>
+        <v>0.329613208770752</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>0.425500005483627</v>
       </c>
       <c r="G1516" t="n">
-        <v>0.326924085617065</v>
+        <v>0.326924055814743</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>0.431499987840652</v>
       </c>
       <c r="G1518" t="n">
-        <v>0.331534028053284</v>
+        <v>0.331534057855606</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G1519" t="n">
-        <v>0.319624960422516</v>
+        <v>0.319624930620193</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>0.442999988794327</v>
       </c>
       <c r="G1523" t="n">
-        <v>0.34036985039711</v>
+        <v>0.340369820594788</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G1524" t="n">
-        <v>0.337296515703201</v>
+        <v>0.337296485900879</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>0.442999988794327</v>
       </c>
       <c r="G1527" t="n">
-        <v>0.34036985039711</v>
+        <v>0.340369820594788</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>0.45100000500679</v>
       </c>
       <c r="G1528" t="n">
-        <v>0.346516489982605</v>
+        <v>0.346516460180283</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>0.458000004291534</v>
       </c>
       <c r="G1531" t="n">
-        <v>0.3518947660923</v>
+        <v>0.351894795894623</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>0.456000000238419</v>
       </c>
       <c r="G1533" t="n">
-        <v>0.350358128547668</v>
+        <v>0.350358098745346</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>0.45100000500679</v>
       </c>
       <c r="G1534" t="n">
-        <v>0.346516489982605</v>
+        <v>0.346516460180283</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1536" t="n">
-        <v>0.345748096704483</v>
+        <v>0.345748156309128</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>0.452499985694885</v>
       </c>
       <c r="G1540" t="n">
-        <v>0.347668945789337</v>
+        <v>0.347669005393982</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>0.416999995708466</v>
       </c>
       <c r="G1542" t="n">
-        <v>0.320393294095993</v>
+        <v>0.320393264293671</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>0.420500010251999</v>
       </c>
       <c r="G1543" t="n">
-        <v>0.323082387447357</v>
+        <v>0.32308241724968</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>0.420500010251999</v>
       </c>
       <c r="G1545" t="n">
-        <v>0.323082387447357</v>
+        <v>0.32308241724968</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G1546" t="n">
-        <v>0.330381572246552</v>
+        <v>0.330381542444229</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>0.421499997377396</v>
       </c>
       <c r="G1548" t="n">
-        <v>0.323850780725479</v>
+        <v>0.323850750923157</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G1549" t="n">
-        <v>0.328844904899597</v>
+        <v>0.328844875097275</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G1553" t="n">
-        <v>0.32116162776947</v>
+        <v>0.321161597967148</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G1558" t="n">
-        <v>0.327308267354965</v>
+        <v>0.327308237552643</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G1560" t="n">
-        <v>0.317319989204407</v>
+        <v>0.317319959402084</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G1562" t="n">
-        <v>0.315015017986298</v>
+        <v>0.315014988183975</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>0.412000000476837</v>
       </c>
       <c r="G1564" t="n">
-        <v>0.316551625728607</v>
+        <v>0.31655165553093</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G1567" t="n">
-        <v>0.32116162776947</v>
+        <v>0.321161597967148</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>0.397000014781952</v>
       </c>
       <c r="G1568" t="n">
-        <v>0.305026710033417</v>
+        <v>0.305026739835739</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>0.36149999499321</v>
       </c>
       <c r="G1571" t="n">
-        <v>0.27775102853775</v>
+        <v>0.277750998735428</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>0.36599999666214</v>
       </c>
       <c r="G1573" t="n">
-        <v>0.281208544969559</v>
+        <v>0.281208485364914</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>0.372000008821487</v>
       </c>
       <c r="G1574" t="n">
-        <v>0.285818457603455</v>
+        <v>0.285818487405777</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>0.361000001430511</v>
       </c>
       <c r="G1575" t="n">
-        <v>0.27736684679985</v>
+        <v>0.277366876602173</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>0.38400000333786</v>
       </c>
       <c r="G1576" t="n">
-        <v>0.295038402080536</v>
+        <v>0.295038431882858</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>0.379999995231628</v>
       </c>
       <c r="G1578" t="n">
-        <v>0.291965067386627</v>
+        <v>0.291965126991272</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41449,7 +41449,7 @@
         <v>0.380499988794327</v>
       </c>
       <c r="G1580" t="n">
-        <v>0.292349278926849</v>
+        <v>0.292349249124527</v>
       </c>
       <c r="H1580" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>0.439500004053116</v>
       </c>
       <c r="G1582" t="n">
-        <v>0.337680727243423</v>
+        <v>0.337680697441101</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>0.439500004053116</v>
       </c>
       <c r="G1583" t="n">
-        <v>0.337680727243423</v>
+        <v>0.337680697441101</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>0.453500002622604</v>
       </c>
       <c r="G1584" t="n">
-        <v>0.348437279462814</v>
+        <v>0.348437309265137</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41631,7 +41631,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1587" t="n">
-        <v>0.345748096704483</v>
+        <v>0.345748156309128</v>
       </c>
       <c r="H1587" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>0.444499999284744</v>
       </c>
       <c r="G1590" t="n">
-        <v>0.341522306203842</v>
+        <v>0.341522336006165</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>0.456999987363815</v>
       </c>
       <c r="G1593" t="n">
-        <v>0.351126462221146</v>
+        <v>0.351126432418823</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>0.444000005722046</v>
       </c>
       <c r="G1595" t="n">
-        <v>0.341138184070587</v>
+        <v>0.341138154268265</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>0.460999995470047</v>
       </c>
       <c r="G1596" t="n">
-        <v>0.354199767112732</v>
+        <v>0.35419973731041</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>0.463499993085861</v>
       </c>
       <c r="G1598" t="n">
-        <v>0.356120556592941</v>
+        <v>0.356120616197586</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>0.465000003576279</v>
       </c>
       <c r="G1599" t="n">
-        <v>0.357273131608963</v>
+        <v>0.357273072004318</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>0.465499997138977</v>
       </c>
       <c r="G1600" t="n">
-        <v>0.35765728354454</v>
+        <v>0.357657253742218</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -41995,7 +41995,7 @@
         <v>0.469999998807907</v>
       </c>
       <c r="G1601" t="n">
-        <v>0.361114710569382</v>
+        <v>0.361114740371704</v>
       </c>
       <c r="H1601" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>0.46900001168251</v>
       </c>
       <c r="G1602" t="n">
-        <v>0.360346406698227</v>
+        <v>0.360346376895905</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42047,7 +42047,7 @@
         <v>0.467999994754791</v>
       </c>
       <c r="G1603" t="n">
-        <v>0.359578043222427</v>
+        <v>0.35957807302475</v>
       </c>
       <c r="H1603" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>0.456999987363815</v>
       </c>
       <c r="G1604" t="n">
-        <v>0.351126462221146</v>
+        <v>0.351126432418823</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1605" t="n">
-        <v>0.345748096704483</v>
+        <v>0.345748156309128</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>0.431499987840652</v>
       </c>
       <c r="G1608" t="n">
-        <v>0.331534028053284</v>
+        <v>0.331534057855606</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>0.442999988794327</v>
       </c>
       <c r="G1609" t="n">
-        <v>0.34036985039711</v>
+        <v>0.340369820594788</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42281,7 +42281,7 @@
         <v>0.442999988794327</v>
       </c>
       <c r="G1612" t="n">
-        <v>0.34036985039711</v>
+        <v>0.340369820594788</v>
       </c>
       <c r="H1612" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G1613" t="n">
-        <v>0.330381572246552</v>
+        <v>0.330381542444229</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>0.442999988794327</v>
       </c>
       <c r="G1614" t="n">
-        <v>0.34036985039711</v>
+        <v>0.340369820594788</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>0.42849999666214</v>
       </c>
       <c r="G1615" t="n">
-        <v>0.329229027032852</v>
+        <v>0.329229086637497</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>0.42849999666214</v>
       </c>
       <c r="G1616" t="n">
-        <v>0.329229027032852</v>
+        <v>0.329229086637497</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>0.429500013589859</v>
       </c>
       <c r="G1620" t="n">
-        <v>0.353653162717819</v>
+        <v>0.353653132915497</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G1622" t="n">
-        <v>0.35406482219696</v>
+        <v>0.354064851999283</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42697,7 +42697,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G1628" t="n">
-        <v>0.35406482219696</v>
+        <v>0.354064851999283</v>
       </c>
       <c r="H1628" t="s">
         <v>8</v>
@@ -42723,7 +42723,7 @@
         <v>0.423000007867813</v>
       </c>
       <c r="G1629" t="n">
-        <v>0.348301023244858</v>
+        <v>0.348300963640213</v>
       </c>
       <c r="H1629" t="s">
         <v>8</v>
@@ -43009,7 +43009,7 @@
         <v>0.389499992132187</v>
       </c>
       <c r="G1640" t="n">
-        <v>0.320716857910156</v>
+        <v>0.320716828107834</v>
       </c>
       <c r="H1640" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>0.383500009775162</v>
       </c>
       <c r="G1644" t="n">
-        <v>0.315776407718658</v>
+        <v>0.315776437520981</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43503,7 +43503,7 @@
         <v>0.388999998569489</v>
       </c>
       <c r="G1659" t="n">
-        <v>0.320305198431015</v>
+        <v>0.320305168628693</v>
       </c>
       <c r="H1659" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>0.383500009775162</v>
       </c>
       <c r="G1662" t="n">
-        <v>0.315776407718658</v>
+        <v>0.315776437520981</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43711,7 +43711,7 @@
         <v>0.395000010728836</v>
       </c>
       <c r="G1667" t="n">
-        <v>0.32524561882019</v>
+        <v>0.325245589017868</v>
       </c>
       <c r="H1667" t="s">
         <v>8</v>
@@ -43815,7 +43815,7 @@
         <v>0.39300000667572</v>
       </c>
       <c r="G1671" t="n">
-        <v>0.323598802089691</v>
+        <v>0.323598772287369</v>
       </c>
       <c r="H1671" t="s">
         <v>8</v>
@@ -43997,7 +43997,7 @@
         <v>0.377000004053116</v>
       </c>
       <c r="G1678" t="n">
-        <v>0.310424298048019</v>
+        <v>0.310424327850342</v>
       </c>
       <c r="H1678" t="s">
         <v>8</v>
@@ -44075,7 +44075,7 @@
         <v>0.377000004053116</v>
       </c>
       <c r="G1681" t="n">
-        <v>0.310424298048019</v>
+        <v>0.310424327850342</v>
       </c>
       <c r="H1681" t="s">
         <v>8</v>
@@ -44127,7 +44127,7 @@
         <v>0.382499992847443</v>
       </c>
       <c r="G1683" t="n">
-        <v>0.314952999353409</v>
+        <v>0.314953029155731</v>
       </c>
       <c r="H1683" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>0.377999991178513</v>
       </c>
       <c r="G1684" t="n">
-        <v>0.311247646808624</v>
+        <v>0.311247706413269</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>0.383500009775162</v>
       </c>
       <c r="G1686" t="n">
-        <v>0.315776407718658</v>
+        <v>0.315776437520981</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44309,7 +44309,7 @@
         <v>0.384999990463257</v>
       </c>
       <c r="G1690" t="n">
-        <v>0.317011505365372</v>
+        <v>0.317011535167694</v>
       </c>
       <c r="H1690" t="s">
         <v>8</v>
@@ -44803,7 +44803,7 @@
         <v>0.377000004053116</v>
       </c>
       <c r="G1709" t="n">
-        <v>0.310424298048019</v>
+        <v>0.310424327850342</v>
       </c>
       <c r="H1709" t="s">
         <v>8</v>
@@ -44907,7 +44907,7 @@
         <v>0.375</v>
       </c>
       <c r="G1713" t="n">
-        <v>0.308777451515198</v>
+        <v>0.30877748131752</v>
       </c>
       <c r="H1713" t="s">
         <v>8</v>
@@ -45115,7 +45115,7 @@
         <v>0.374000012874603</v>
       </c>
       <c r="G1721" t="n">
-        <v>0.307954072952271</v>
+        <v>0.307954043149948</v>
       </c>
       <c r="H1721" t="s">
         <v>8</v>
@@ -45167,7 +45167,7 @@
         <v>0.372000008821487</v>
       </c>
       <c r="G1723" t="n">
-        <v>0.306307256221771</v>
+        <v>0.306307286024094</v>
       </c>
       <c r="H1723" t="s">
         <v>8</v>
@@ -45219,7 +45219,7 @@
         <v>0.368999987840652</v>
       </c>
       <c r="G1725" t="n">
-        <v>0.303837031126022</v>
+        <v>0.3038370013237</v>
       </c>
       <c r="H1725" t="s">
         <v>8</v>
@@ -45271,7 +45271,7 @@
         <v>0.368999987840652</v>
       </c>
       <c r="G1727" t="n">
-        <v>0.303837031126022</v>
+        <v>0.3038370013237</v>
       </c>
       <c r="H1727" t="s">
         <v>8</v>
@@ -45297,7 +45297,7 @@
         <v>0.368999987840652</v>
       </c>
       <c r="G1728" t="n">
-        <v>0.303837031126022</v>
+        <v>0.3038370013237</v>
       </c>
       <c r="H1728" t="s">
         <v>8</v>
@@ -45349,7 +45349,7 @@
         <v>0.36599999666214</v>
       </c>
       <c r="G1730" t="n">
-        <v>0.301366806030273</v>
+        <v>0.301366776227951</v>
       </c>
       <c r="H1730" t="s">
         <v>8</v>
@@ -45505,7 +45505,7 @@
         <v>0.375</v>
       </c>
       <c r="G1736" t="n">
-        <v>0.308777451515198</v>
+        <v>0.30877748131752</v>
       </c>
       <c r="H1736" t="s">
         <v>8</v>
@@ -45661,7 +45661,7 @@
         <v>0.395000010728836</v>
       </c>
       <c r="G1742" t="n">
-        <v>0.32524561882019</v>
+        <v>0.325245589017868</v>
       </c>
       <c r="H1742" t="s">
         <v>8</v>
@@ -45687,7 +45687,7 @@
         <v>0.398999989032745</v>
       </c>
       <c r="G1743" t="n">
-        <v>0.328539222478867</v>
+        <v>0.328539192676544</v>
       </c>
       <c r="H1743" t="s">
         <v>8</v>
@@ -45739,7 +45739,7 @@
         <v>0.418500006198883</v>
       </c>
       <c r="G1745" t="n">
-        <v>0.344595670700073</v>
+        <v>0.344595700502396</v>
       </c>
       <c r="H1745" t="s">
         <v>8</v>
@@ -45765,7 +45765,7 @@
         <v>0.414000004529953</v>
       </c>
       <c r="G1746" t="n">
-        <v>0.340890318155289</v>
+        <v>0.340890347957611</v>
       </c>
       <c r="H1746" t="s">
         <v>8</v>
@@ -45869,7 +45869,7 @@
         <v>0.416999995708466</v>
       </c>
       <c r="G1750" t="n">
-        <v>0.343360543251038</v>
+        <v>0.34336057305336</v>
       </c>
       <c r="H1750" t="s">
         <v>8</v>
@@ -45895,7 +45895,7 @@
         <v>0.408499985933304</v>
       </c>
       <c r="G1751" t="n">
-        <v>0.336361557245255</v>
+        <v>0.336361587047577</v>
       </c>
       <c r="H1751" t="s">
         <v>8</v>
@@ -45921,7 +45921,7 @@
         <v>0.412000000476837</v>
       </c>
       <c r="G1752" t="n">
-        <v>0.339243501424789</v>
+        <v>0.339243531227112</v>
       </c>
       <c r="H1752" t="s">
         <v>8</v>
@@ -45973,7 +45973,7 @@
         <v>0.414000004529953</v>
       </c>
       <c r="G1754" t="n">
-        <v>0.340890318155289</v>
+        <v>0.340890347957611</v>
       </c>
       <c r="H1754" t="s">
         <v>8</v>
@@ -46025,7 +46025,7 @@
         <v>0.421499997377396</v>
       </c>
       <c r="G1756" t="n">
-        <v>0.347065895795822</v>
+        <v>0.3470658659935</v>
       </c>
       <c r="H1756" t="s">
         <v>8</v>
@@ -46051,7 +46051,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G1757" t="n">
-        <v>0.34418398141861</v>
+        <v>0.344183951616287</v>
       </c>
       <c r="H1757" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>0.418500006198883</v>
       </c>
       <c r="G1761" t="n">
-        <v>0.344595670700073</v>
+        <v>0.344595700502396</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46285,7 +46285,7 @@
         <v>0.407999992370605</v>
       </c>
       <c r="G1766" t="n">
-        <v>0.335949897766113</v>
+        <v>0.335949867963791</v>
       </c>
       <c r="H1766" t="s">
         <v>8</v>
@@ -46311,7 +46311,7 @@
         <v>0.416999995708466</v>
       </c>
       <c r="G1767" t="n">
-        <v>0.343360543251038</v>
+        <v>0.34336057305336</v>
       </c>
       <c r="H1767" t="s">
         <v>8</v>
@@ -46337,7 +46337,7 @@
         <v>0.417499989271164</v>
       </c>
       <c r="G1768" t="n">
-        <v>0.343772232532501</v>
+        <v>0.343772202730179</v>
       </c>
       <c r="H1768" t="s">
         <v>8</v>
@@ -46363,7 +46363,7 @@
         <v>0.412000000476837</v>
       </c>
       <c r="G1769" t="n">
-        <v>0.339243501424789</v>
+        <v>0.339243531227112</v>
       </c>
       <c r="H1769" t="s">
         <v>8</v>
@@ -46415,7 +46415,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G1771" t="n">
-        <v>0.340066909790039</v>
+        <v>0.340066879987717</v>
       </c>
       <c r="H1771" t="s">
         <v>8</v>
@@ -46467,7 +46467,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G1773" t="n">
-        <v>0.340066909790039</v>
+        <v>0.340066879987717</v>
       </c>
       <c r="H1773" t="s">
         <v>8</v>
@@ -46493,7 +46493,7 @@
         <v>0.413500010967255</v>
       </c>
       <c r="G1774" t="n">
-        <v>0.340478599071503</v>
+        <v>0.340478628873825</v>
       </c>
       <c r="H1774" t="s">
         <v>8</v>
@@ -46753,7 +46753,7 @@
         <v>0.41100001335144</v>
       </c>
       <c r="G1784" t="n">
-        <v>0.33842009305954</v>
+        <v>0.338420122861862</v>
       </c>
       <c r="H1784" t="s">
         <v>8</v>
@@ -46779,7 +46779,7 @@
         <v>0.417499989271164</v>
       </c>
       <c r="G1785" t="n">
-        <v>0.343772232532501</v>
+        <v>0.343772202730179</v>
       </c>
       <c r="H1785" t="s">
         <v>8</v>
@@ -46805,7 +46805,7 @@
         <v>0.414000004529953</v>
       </c>
       <c r="G1786" t="n">
-        <v>0.340890318155289</v>
+        <v>0.340890347957611</v>
       </c>
       <c r="H1786" t="s">
         <v>8</v>
@@ -47143,7 +47143,7 @@
         <v>0.463499993085861</v>
       </c>
       <c r="G1799" t="n">
-        <v>0.38164895772934</v>
+        <v>0.381648987531662</v>
       </c>
       <c r="H1799" t="s">
         <v>8</v>
@@ -47195,7 +47195,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1801" t="n">
-        <v>0.395235151052475</v>
+        <v>0.395235121250153</v>
       </c>
       <c r="H1801" t="s">
         <v>8</v>
@@ -47403,7 +47403,7 @@
         <v>0.495999991893768</v>
       </c>
       <c r="G1809" t="n">
-        <v>0.408409684896469</v>
+        <v>0.408409655094147</v>
       </c>
       <c r="H1809" t="s">
         <v>8</v>
@@ -47533,7 +47533,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1814" t="n">
-        <v>0.395235151052475</v>
+        <v>0.395235121250153</v>
       </c>
       <c r="H1814" t="s">
         <v>8</v>
@@ -47559,7 +47559,7 @@
         <v>0.483000010251999</v>
       </c>
       <c r="G1815" t="n">
-        <v>0.397705405950546</v>
+        <v>0.397705376148224</v>
       </c>
       <c r="H1815" t="s">
         <v>8</v>
@@ -47611,7 +47611,7 @@
         <v>0.483000010251999</v>
       </c>
       <c r="G1817" t="n">
-        <v>0.397705405950546</v>
+        <v>0.397705376148224</v>
       </c>
       <c r="H1817" t="s">
         <v>8</v>
@@ -47741,7 +47741,7 @@
         <v>0.507000029087067</v>
       </c>
       <c r="G1822" t="n">
-        <v>0.417467206716537</v>
+        <v>0.417467176914215</v>
       </c>
       <c r="H1822" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>0.537999987602234</v>
       </c>
       <c r="G1827" t="n">
-        <v>0.442992717027664</v>
+        <v>0.442992746829987</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -47897,7 +47897,7 @@
         <v>0.592999994754791</v>
       </c>
       <c r="G1828" t="n">
-        <v>0.488280147314072</v>
+        <v>0.488280117511749</v>
       </c>
       <c r="H1828" t="s">
         <v>8</v>
@@ -47923,7 +47923,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1829" t="n">
-        <v>0.503924787044525</v>
+        <v>0.50392484664917</v>
       </c>
       <c r="H1829" t="s">
         <v>8</v>
@@ -48001,7 +48001,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1832" t="n">
-        <v>0.522039771080017</v>
+        <v>0.522039711475372</v>
       </c>
       <c r="H1832" t="s">
         <v>8</v>
@@ -48131,7 +48131,7 @@
         <v>0.561999976634979</v>
       </c>
       <c r="G1837" t="n">
-        <v>0.462754517793655</v>
+        <v>0.462754547595978</v>
       </c>
       <c r="H1837" t="s">
         <v>8</v>
@@ -48235,7 +48235,7 @@
         <v>0.598999977111816</v>
       </c>
       <c r="G1841" t="n">
-        <v>0.493220567703247</v>
+        <v>0.493220597505569</v>
       </c>
       <c r="H1841" t="s">
         <v>8</v>
@@ -48261,7 +48261,7 @@
         <v>0.597000002861023</v>
       </c>
       <c r="G1842" t="n">
-        <v>0.491573661565781</v>
+        <v>0.491573691368103</v>
       </c>
       <c r="H1842" t="s">
         <v>8</v>
@@ -48287,7 +48287,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1843" t="n">
-        <v>0.48169282078743</v>
+        <v>0.481692880392075</v>
       </c>
       <c r="H1843" t="s">
         <v>8</v>
@@ -48313,7 +48313,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G1844" t="n">
-        <v>0.467694938182831</v>
+        <v>0.467694967985153</v>
       </c>
       <c r="H1844" t="s">
         <v>8</v>
@@ -48339,7 +48339,7 @@
         <v>0.558000028133392</v>
       </c>
       <c r="G1845" t="n">
-        <v>0.459460914134979</v>
+        <v>0.459460884332657</v>
       </c>
       <c r="H1845" t="s">
         <v>8</v>
@@ -48365,7 +48365,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G1846" t="n">
-        <v>0.461107671260834</v>
+        <v>0.461107641458511</v>
       </c>
       <c r="H1846" t="s">
         <v>8</v>
@@ -48391,7 +48391,7 @@
         <v>0.578999996185303</v>
       </c>
       <c r="G1847" t="n">
-        <v>0.476752400398254</v>
+        <v>0.476752430200577</v>
       </c>
       <c r="H1847" t="s">
         <v>8</v>
@@ -48417,7 +48417,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1848" t="n">
-        <v>0.48169282078743</v>
+        <v>0.481692880392075</v>
       </c>
       <c r="H1848" t="s">
         <v>8</v>
@@ -48443,7 +48443,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G1849" t="n">
-        <v>0.479222625494003</v>
+        <v>0.479222655296326</v>
       </c>
       <c r="H1849" t="s">
         <v>8</v>
@@ -48469,7 +48469,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1850" t="n">
-        <v>0.477575868368149</v>
+        <v>0.477575838565826</v>
       </c>
       <c r="H1850" t="s">
         <v>8</v>
@@ -48495,7 +48495,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1851" t="n">
-        <v>0.477575868368149</v>
+        <v>0.477575838565826</v>
       </c>
       <c r="H1851" t="s">
         <v>8</v>
@@ -48599,7 +48599,7 @@
         <v>0.609000027179718</v>
       </c>
       <c r="G1855" t="n">
-        <v>0.501454591751099</v>
+        <v>0.501454651355743</v>
       </c>
       <c r="H1855" t="s">
         <v>8</v>
@@ -48625,7 +48625,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G1856" t="n">
-        <v>0.498984336853027</v>
+        <v>0.498984396457672</v>
       </c>
       <c r="H1856" t="s">
         <v>8</v>
@@ -48651,7 +48651,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1857" t="n">
-        <v>0.494043916463852</v>
+        <v>0.494043946266174</v>
       </c>
       <c r="H1857" t="s">
         <v>8</v>
@@ -48677,7 +48677,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1858" t="n">
-        <v>0.505571663379669</v>
+        <v>0.505571722984314</v>
       </c>
       <c r="H1858" t="s">
         <v>8</v>
@@ -48703,7 +48703,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G1859" t="n">
-        <v>0.490750372409821</v>
+        <v>0.490750402212143</v>
       </c>
       <c r="H1859" t="s">
         <v>8</v>
@@ -48755,7 +48755,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1861" t="n">
-        <v>0.492397159337997</v>
+        <v>0.492397099733353</v>
       </c>
       <c r="H1861" t="s">
         <v>8</v>
@@ -48781,7 +48781,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1862" t="n">
-        <v>0.482516288757324</v>
+        <v>0.482516258955002</v>
       </c>
       <c r="H1862" t="s">
         <v>8</v>
@@ -48807,7 +48807,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G1863" t="n">
-        <v>0.479222625494003</v>
+        <v>0.479222655296326</v>
       </c>
       <c r="H1863" t="s">
         <v>8</v>
@@ -48859,7 +48859,7 @@
         <v>0.580999970436096</v>
       </c>
       <c r="G1865" t="n">
-        <v>0.478399157524109</v>
+        <v>0.478399127721786</v>
       </c>
       <c r="H1865" t="s">
         <v>8</v>
@@ -48885,7 +48885,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1866" t="n">
-        <v>0.473458766937256</v>
+        <v>0.473458796739578</v>
       </c>
       <c r="H1866" t="s">
         <v>8</v>
@@ -48911,7 +48911,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G1867" t="n">
-        <v>0.467694938182831</v>
+        <v>0.467694967985153</v>
       </c>
       <c r="H1867" t="s">
         <v>8</v>
@@ -48963,7 +48963,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1869" t="n">
-        <v>0.48169282078743</v>
+        <v>0.481692880392075</v>
       </c>
       <c r="H1869" t="s">
         <v>8</v>
@@ -48989,7 +48989,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G1870" t="n">
-        <v>0.490750372409821</v>
+        <v>0.490750402212143</v>
       </c>
       <c r="H1870" t="s">
         <v>8</v>
@@ -49041,7 +49041,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1872" t="n">
-        <v>0.492397159337997</v>
+        <v>0.492397099733353</v>
       </c>
       <c r="H1872" t="s">
         <v>8</v>
@@ -49093,7 +49093,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G1874" t="n">
-        <v>0.479222625494003</v>
+        <v>0.479222655296326</v>
       </c>
       <c r="H1874" t="s">
         <v>8</v>
@@ -49145,7 +49145,7 @@
         <v>0.558000028133392</v>
       </c>
       <c r="G1876" t="n">
-        <v>0.459460914134979</v>
+        <v>0.459460884332657</v>
       </c>
       <c r="H1876" t="s">
         <v>8</v>
@@ -49171,7 +49171,7 @@
         <v>0.564999997615814</v>
       </c>
       <c r="G1877" t="n">
-        <v>0.465224713087082</v>
+        <v>0.465224742889404</v>
       </c>
       <c r="H1877" t="s">
         <v>8</v>
@@ -49223,7 +49223,7 @@
         <v>0.569000005722046</v>
       </c>
       <c r="G1879" t="n">
-        <v>0.46851834654808</v>
+        <v>0.468518376350403</v>
       </c>
       <c r="H1879" t="s">
         <v>8</v>
@@ -49275,7 +49275,7 @@
         <v>0.53600001335144</v>
       </c>
       <c r="G1881" t="n">
-        <v>0.473822295665741</v>
+        <v>0.473822325468063</v>
       </c>
       <c r="H1881" t="s">
         <v>8</v>
@@ -49405,7 +49405,7 @@
         <v>0.499000012874603</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.441114455461502</v>
+        <v>0.441114485263824</v>
       </c>
       <c r="H1886" t="s">
         <v>8</v>
@@ -49457,7 +49457,7 @@
         <v>0.493000000715256</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.435810476541519</v>
+        <v>0.435810446739197</v>
       </c>
       <c r="H1888" t="s">
         <v>8</v>
@@ -49483,7 +49483,7 @@
         <v>0.495999991893768</v>
       </c>
       <c r="G1889" t="n">
-        <v>0.438462466001511</v>
+        <v>0.438462436199188</v>
       </c>
       <c r="H1889" t="s">
         <v>8</v>
@@ -49665,7 +49665,7 @@
         <v>0.503000020980835</v>
       </c>
       <c r="G1896" t="n">
-        <v>0.44465047121048</v>
+        <v>0.444650441408157</v>
       </c>
       <c r="H1896" t="s">
         <v>8</v>
@@ -49717,7 +49717,7 @@
         <v>0.495000004768372</v>
       </c>
       <c r="G1898" t="n">
-        <v>0.437578469514847</v>
+        <v>0.437578439712524</v>
       </c>
       <c r="H1898" t="s">
         <v>8</v>
@@ -49795,7 +49795,7 @@
         <v>0.488000005483627</v>
       </c>
       <c r="G1901" t="n">
-        <v>0.4313904941082</v>
+        <v>0.431390464305878</v>
       </c>
       <c r="H1901" t="s">
         <v>8</v>
@@ -49821,7 +49821,7 @@
         <v>0.492000013589859</v>
       </c>
       <c r="G1902" t="n">
-        <v>0.434926450252533</v>
+        <v>0.434926480054855</v>
       </c>
       <c r="H1902" t="s">
         <v>8</v>
@@ -49925,7 +49925,7 @@
         <v>0.485000014305115</v>
       </c>
       <c r="G1906" t="n">
-        <v>0.428738504648209</v>
+        <v>0.428738474845886</v>
       </c>
       <c r="H1906" t="s">
         <v>8</v>
@@ -49951,7 +49951,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1907" t="n">
-        <v>0.424318492412567</v>
+        <v>0.424318462610245</v>
       </c>
       <c r="H1907" t="s">
         <v>8</v>
@@ -50003,7 +50003,7 @@
         <v>0.49099999666214</v>
       </c>
       <c r="G1909" t="n">
-        <v>0.434042453765869</v>
+        <v>0.434042483568192</v>
       </c>
       <c r="H1909" t="s">
         <v>8</v>
@@ -50081,7 +50081,7 @@
         <v>0.495000004768372</v>
       </c>
       <c r="G1912" t="n">
-        <v>0.437578469514847</v>
+        <v>0.437578439712524</v>
       </c>
       <c r="H1912" t="s">
         <v>8</v>
@@ -50289,7 +50289,7 @@
         <v>0.46849998831749</v>
       </c>
       <c r="G1920" t="n">
-        <v>0.414152503013611</v>
+        <v>0.414152532815933</v>
       </c>
       <c r="H1920" t="s">
         <v>8</v>
@@ -50315,7 +50315,7 @@
         <v>0.47299998998642</v>
       </c>
       <c r="G1921" t="n">
-        <v>0.418130487203598</v>
+        <v>0.41813051700592</v>
       </c>
       <c r="H1921" t="s">
         <v>8</v>
@@ -50419,7 +50419,7 @@
         <v>0.481000006198883</v>
       </c>
       <c r="G1925" t="n">
-        <v>0.425202459096909</v>
+        <v>0.425202488899231</v>
       </c>
       <c r="H1925" t="s">
         <v>8</v>
@@ -50445,7 +50445,7 @@
         <v>0.479499995708466</v>
       </c>
       <c r="G1926" t="n">
-        <v>0.423876523971558</v>
+        <v>0.423876494169235</v>
       </c>
       <c r="H1926" t="s">
         <v>8</v>
@@ -50549,7 +50549,7 @@
         <v>0.481000006198883</v>
       </c>
       <c r="G1930" t="n">
-        <v>0.425202459096909</v>
+        <v>0.425202488899231</v>
       </c>
       <c r="H1930" t="s">
         <v>8</v>
@@ -50575,7 +50575,7 @@
         <v>0.47299998998642</v>
       </c>
       <c r="G1931" t="n">
-        <v>0.418130487203598</v>
+        <v>0.41813051700592</v>
       </c>
       <c r="H1931" t="s">
         <v>8</v>
@@ -50679,7 +50679,7 @@
         <v>0.46849998831749</v>
       </c>
       <c r="G1935" t="n">
-        <v>0.414152503013611</v>
+        <v>0.414152532815933</v>
       </c>
       <c r="H1935" t="s">
         <v>8</v>
@@ -50887,7 +50887,7 @@
         <v>0.461499989032745</v>
       </c>
       <c r="G1943" t="n">
-        <v>0.407964557409286</v>
+        <v>0.407964527606964</v>
       </c>
       <c r="H1943" t="s">
         <v>8</v>
@@ -50965,7 +50965,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1946" t="n">
-        <v>0.424318492412567</v>
+        <v>0.424318462610245</v>
       </c>
       <c r="H1946" t="s">
         <v>8</v>
@@ -50991,7 +50991,7 @@
         <v>0.475499987602234</v>
       </c>
       <c r="G1947" t="n">
-        <v>0.42034050822258</v>
+        <v>0.420340538024902</v>
       </c>
       <c r="H1947" t="s">
         <v>8</v>
@@ -51043,7 +51043,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1949" t="n">
-        <v>0.424318492412567</v>
+        <v>0.424318462610245</v>
       </c>
       <c r="H1949" t="s">
         <v>8</v>
@@ -51095,7 +51095,7 @@
         <v>0.48199999332428</v>
       </c>
       <c r="G1951" t="n">
-        <v>0.426086485385895</v>
+        <v>0.426086515188217</v>
       </c>
       <c r="H1951" t="s">
         <v>8</v>
@@ -51199,7 +51199,7 @@
         <v>0.49099999666214</v>
       </c>
       <c r="G1955" t="n">
-        <v>0.434042453765869</v>
+        <v>0.434042483568192</v>
       </c>
       <c r="H1955" t="s">
         <v>8</v>
@@ -51277,7 +51277,7 @@
         <v>0.488000005483627</v>
       </c>
       <c r="G1958" t="n">
-        <v>0.4313904941082</v>
+        <v>0.431390464305878</v>
       </c>
       <c r="H1958" t="s">
         <v>8</v>
@@ -51303,7 +51303,7 @@
         <v>0.479499995708466</v>
       </c>
       <c r="G1959" t="n">
-        <v>0.423876523971558</v>
+        <v>0.423876494169235</v>
       </c>
       <c r="H1959" t="s">
         <v>8</v>
@@ -51381,7 +51381,7 @@
         <v>0.469999998807907</v>
       </c>
       <c r="G1962" t="n">
-        <v>0.415478527545929</v>
+        <v>0.415478497743607</v>
       </c>
       <c r="H1962" t="s">
         <v>8</v>
@@ -51615,7 +51615,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G1971" t="n">
-        <v>0.396030634641647</v>
+        <v>0.396030604839325</v>
       </c>
       <c r="H1971" t="s">
         <v>8</v>
@@ -51693,7 +51693,7 @@
         <v>0.456499993801117</v>
       </c>
       <c r="G1974" t="n">
-        <v>0.403544574975967</v>
+        <v>0.403544545173645</v>
       </c>
       <c r="H1974" t="s">
         <v>8</v>
@@ -51849,7 +51849,7 @@
         <v>0.444999992847443</v>
       </c>
       <c r="G1980" t="n">
-        <v>0.393378615379333</v>
+        <v>0.393378645181656</v>
       </c>
       <c r="H1980" t="s">
         <v>8</v>
@@ -52005,7 +52005,7 @@
         <v>0.456000000238419</v>
       </c>
       <c r="G1986" t="n">
-        <v>0.403102576732635</v>
+        <v>0.403102546930313</v>
       </c>
       <c r="H1986" t="s">
         <v>8</v>
@@ -52057,7 +52057,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1988" t="n">
-        <v>0.39779856801033</v>
+        <v>0.397798597812653</v>
       </c>
       <c r="H1988" t="s">
         <v>8</v>
@@ -52135,7 +52135,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1991" t="n">
-        <v>0.39779856801033</v>
+        <v>0.397798597812653</v>
       </c>
       <c r="H1991" t="s">
         <v>8</v>
@@ -52291,7 +52291,7 @@
         <v>0.469999998807907</v>
       </c>
       <c r="G1997" t="n">
-        <v>0.415478527545929</v>
+        <v>0.415478497743607</v>
       </c>
       <c r="H1997" t="s">
         <v>8</v>
@@ -52421,7 +52421,7 @@
         <v>0.474999994039536</v>
       </c>
       <c r="G2002" t="n">
-        <v>0.419898509979248</v>
+        <v>0.419898480176926</v>
       </c>
       <c r="H2002" t="s">
         <v>8</v>
@@ -52473,7 +52473,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G2004" t="n">
-        <v>0.424318492412567</v>
+        <v>0.424318462610245</v>
       </c>
       <c r="H2004" t="s">
         <v>8</v>
@@ -52499,7 +52499,7 @@
         <v>0.488000005483627</v>
       </c>
       <c r="G2005" t="n">
-        <v>0.4313904941082</v>
+        <v>0.431390464305878</v>
       </c>
       <c r="H2005" t="s">
         <v>8</v>
@@ -71248,6 +71248,32 @@
         <v>0.535000026226044</v>
       </c>
       <c r="H2726" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2727">
+      <c r="A2727" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2727" t="n">
+        <v>267075</v>
+      </c>
+      <c r="C2727" t="n">
+        <v>0.53600001335144</v>
+      </c>
+      <c r="D2727" t="n">
+        <v>0.526000022888184</v>
+      </c>
+      <c r="E2727" t="n">
+        <v>0.52700001001358</v>
+      </c>
+      <c r="F2727" t="n">
+        <v>0.523999989032745</v>
+      </c>
+      <c r="G2727" t="n">
+        <v>0.523999989032745</v>
+      </c>
+      <c r="H2727" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/IMS.MI.xlsx
+++ b/data/IMS.MI.xlsx
@@ -447,7 +447,7 @@
         <v>0.442499995231628</v>
       </c>
       <c r="G3" t="n">
-        <v>0.327446222305298</v>
+        <v>0.32744625210762</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>0.429300010204315</v>
       </c>
       <c r="G5" t="n">
-        <v>0.317678391933441</v>
+        <v>0.317678362131119</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>0.415300011634827</v>
       </c>
       <c r="G6" t="n">
-        <v>0.307318508625031</v>
+        <v>0.307318478822708</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>0.389800012111664</v>
       </c>
       <c r="G7" t="n">
-        <v>0.288448721170425</v>
+        <v>0.288448691368103</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>0.397799998521805</v>
       </c>
       <c r="G9" t="n">
-        <v>0.294368654489517</v>
+        <v>0.294368624687195</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>0.386000007390976</v>
       </c>
       <c r="G10" t="n">
-        <v>0.285636752843857</v>
+        <v>0.285636723041534</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>0.349000006914139</v>
       </c>
       <c r="G13" t="n">
-        <v>0.258257061243057</v>
+        <v>0.258257031440735</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>0.329199999570847</v>
       </c>
       <c r="G14" t="n">
-        <v>0.243605211377144</v>
+        <v>0.243605226278305</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>0.333000004291534</v>
       </c>
       <c r="G15" t="n">
-        <v>0.246417179703712</v>
+        <v>0.246417164802551</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>0.346500009298325</v>
       </c>
       <c r="G17" t="n">
-        <v>0.256407082080841</v>
+        <v>0.256407052278519</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>0.351099997758865</v>
       </c>
       <c r="G18" t="n">
-        <v>0.259811043739319</v>
+        <v>0.259811013936996</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>0.375</v>
       </c>
       <c r="G24" t="n">
-        <v>0.277496784925461</v>
+        <v>0.277496814727783</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>0.388000011444092</v>
       </c>
       <c r="G25" t="n">
-        <v>0.28711673617363</v>
+        <v>0.287116706371307</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>0.392899990081787</v>
       </c>
       <c r="G26" t="n">
-        <v>0.290742665529251</v>
+        <v>0.290742635726929</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>0.375</v>
       </c>
       <c r="G32" t="n">
-        <v>0.277496784925461</v>
+        <v>0.277496814727783</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>0.375099986791611</v>
       </c>
       <c r="G33" t="n">
-        <v>0.277570784091949</v>
+        <v>0.277570843696594</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>0.402700006961823</v>
       </c>
       <c r="G34" t="n">
-        <v>0.297994583845139</v>
+        <v>0.297994613647461</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G35" t="n">
-        <v>0.310796469449997</v>
+        <v>0.310796439647675</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>0.410199999809265</v>
       </c>
       <c r="G36" t="n">
-        <v>0.303544491529465</v>
+        <v>0.303544521331787</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>0.418500006198883</v>
       </c>
       <c r="G39" t="n">
-        <v>0.309686422348022</v>
+        <v>0.309686452150345</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>0.437000006437302</v>
       </c>
       <c r="G42" t="n">
-        <v>0.323376357555389</v>
+        <v>0.323376297950745</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>0.432500004768372</v>
       </c>
       <c r="G43" t="n">
-        <v>0.320046335458755</v>
+        <v>0.320046305656433</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G45" t="n">
-        <v>0.315236389636993</v>
+        <v>0.315236419439316</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>0.426499992609024</v>
       </c>
       <c r="G46" t="n">
-        <v>0.315606385469437</v>
+        <v>0.315606415271759</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G47" t="n">
-        <v>0.332996159791946</v>
+        <v>0.332996189594269</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>0.444400012493134</v>
       </c>
       <c r="G49" t="n">
-        <v>0.328852236270905</v>
+        <v>0.32885217666626</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>0.446599990129471</v>
       </c>
       <c r="G50" t="n">
-        <v>0.330480188131332</v>
+        <v>0.330480217933655</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>0.42059999704361</v>
       </c>
       <c r="G51" t="n">
-        <v>0.311240434646606</v>
+        <v>0.311240404844284</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>0.405000001192093</v>
       </c>
       <c r="G53" t="n">
-        <v>0.299696564674377</v>
+        <v>0.2996965944767</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>0.401199996471405</v>
       </c>
       <c r="G54" t="n">
-        <v>0.296884596347809</v>
+        <v>0.296884626150131</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G57" t="n">
-        <v>0.295996636152267</v>
+        <v>0.295996606349945</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>0.396899998188019</v>
       </c>
       <c r="G58" t="n">
-        <v>0.293702632188797</v>
+        <v>0.293702602386475</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>0.402700006961823</v>
       </c>
       <c r="G60" t="n">
-        <v>0.297994583845139</v>
+        <v>0.297994613647461</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>0.386999994516373</v>
       </c>
       <c r="G62" t="n">
-        <v>0.286376714706421</v>
+        <v>0.286376744508743</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>0.374000012874603</v>
       </c>
       <c r="G63" t="n">
-        <v>0.276756823062897</v>
+        <v>0.276756882667542</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>0.370999991893768</v>
       </c>
       <c r="G64" t="n">
-        <v>0.27453687787056</v>
+        <v>0.274536848068237</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>0.362899988889694</v>
       </c>
       <c r="G66" t="n">
-        <v>0.268542915582657</v>
+        <v>0.268542885780334</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>0.365500003099442</v>
       </c>
       <c r="G67" t="n">
-        <v>0.270466864109039</v>
+        <v>0.270466893911362</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>0.363000005483627</v>
       </c>
       <c r="G70" t="n">
-        <v>0.268616914749146</v>
+        <v>0.268616884946823</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>0.36379998922348</v>
       </c>
       <c r="G71" t="n">
-        <v>0.269208878278732</v>
+        <v>0.269208908081055</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>0.372000008821487</v>
       </c>
       <c r="G72" t="n">
-        <v>0.275276869535446</v>
+        <v>0.275276839733124</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>0.375</v>
       </c>
       <c r="G73" t="n">
-        <v>0.277496784925461</v>
+        <v>0.277496814727783</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>0.375</v>
       </c>
       <c r="G74" t="n">
-        <v>0.277496784925461</v>
+        <v>0.277496814727783</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>0.39190000295639</v>
       </c>
       <c r="G76" t="n">
-        <v>0.290002673864365</v>
+        <v>0.290002644062042</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>0.405000001192093</v>
       </c>
       <c r="G77" t="n">
-        <v>0.299696564674377</v>
+        <v>0.2996965944767</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G80" t="n">
-        <v>0.318196386098862</v>
+        <v>0.318196356296539</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>0.428299993276596</v>
       </c>
       <c r="G81" t="n">
-        <v>0.316938370466232</v>
+        <v>0.31693834066391</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>0.417499989271164</v>
       </c>
       <c r="G82" t="n">
-        <v>0.308946460485458</v>
+        <v>0.308946430683136</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>0.434300005435944</v>
       </c>
       <c r="G84" t="n">
-        <v>0.321378290653229</v>
+        <v>0.321378320455551</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>0.423900008201599</v>
       </c>
       <c r="G87" t="n">
-        <v>0.313682436943054</v>
+        <v>0.313682407140732</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>0.41499999165535</v>
       </c>
       <c r="G89" t="n">
-        <v>0.30709645152092</v>
+        <v>0.307096481323242</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>0.401199996471405</v>
       </c>
       <c r="G90" t="n">
-        <v>0.296884596347809</v>
+        <v>0.296884626150131</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>0.405000001192093</v>
       </c>
       <c r="G91" t="n">
-        <v>0.299696564674377</v>
+        <v>0.2996965944767</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G92" t="n">
-        <v>0.295996636152267</v>
+        <v>0.295996606349945</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>0.412099987268448</v>
       </c>
       <c r="G94" t="n">
-        <v>0.304950475692749</v>
+        <v>0.304950505495071</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G95" t="n">
-        <v>0.305616497993469</v>
+        <v>0.305616468191147</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>0.412600010633469</v>
       </c>
       <c r="G97" t="n">
-        <v>0.305320501327515</v>
+        <v>0.305320531129837</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>0.399500012397766</v>
       </c>
       <c r="G98" t="n">
-        <v>0.295626640319824</v>
+        <v>0.295626670122147</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>0.416399985551834</v>
       </c>
       <c r="G104" t="n">
-        <v>0.319932252168655</v>
+        <v>0.319932281970978</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G109" t="n">
-        <v>0.307331711053848</v>
+        <v>0.307331740856171</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>0.392500013113022</v>
       </c>
       <c r="G115" t="n">
-        <v>0.301569223403931</v>
+        <v>0.301569193601608</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G120" t="n">
-        <v>0.31424668431282</v>
+        <v>0.314246654510498</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>0.41389998793602</v>
       </c>
       <c r="G121" t="n">
-        <v>0.318011432886124</v>
+        <v>0.318011462688446</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>0.403499990701675</v>
       </c>
       <c r="G124" t="n">
-        <v>0.310020804405212</v>
+        <v>0.310020834207535</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>0.405000001192093</v>
       </c>
       <c r="G126" t="n">
-        <v>0.311173319816589</v>
+        <v>0.311173349618912</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G128" t="n">
-        <v>0.307331711053848</v>
+        <v>0.307331740856171</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G129" t="n">
-        <v>0.307331711053848</v>
+        <v>0.307331740856171</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G130" t="n">
-        <v>0.307331711053848</v>
+        <v>0.307331740856171</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>0.399199992418289</v>
       </c>
       <c r="G132" t="n">
-        <v>0.30671700835228</v>
+        <v>0.306717038154602</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G133" t="n">
-        <v>0.307331711053848</v>
+        <v>0.307331740856171</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>0.397700011730194</v>
       </c>
       <c r="G134" t="n">
-        <v>0.30556458234787</v>
+        <v>0.305564552545547</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G135" t="n">
-        <v>0.307331711053848</v>
+        <v>0.307331740856171</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G136" t="n">
-        <v>0.307331711053848</v>
+        <v>0.307331740856171</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G138" t="n">
-        <v>0.307331711053848</v>
+        <v>0.307331740856171</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>0.399399995803833</v>
       </c>
       <c r="G141" t="n">
-        <v>0.306870639324188</v>
+        <v>0.306870698928833</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>0.395700007677078</v>
       </c>
       <c r="G145" t="n">
-        <v>0.304027885198593</v>
+        <v>0.304027855396271</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>0.390500009059906</v>
       </c>
       <c r="G146" t="n">
-        <v>0.300032585859299</v>
+        <v>0.300032556056976</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>0.405400007963181</v>
       </c>
       <c r="G150" t="n">
-        <v>0.311480641365051</v>
+        <v>0.311480700969696</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>0.388200014829636</v>
       </c>
       <c r="G151" t="n">
-        <v>0.298265397548676</v>
+        <v>0.29826545715332</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>0.385199993848801</v>
       </c>
       <c r="G156" t="n">
-        <v>0.295960396528244</v>
+        <v>0.295960426330566</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>0.387699991464615</v>
       </c>
       <c r="G158" t="n">
-        <v>0.297881275415421</v>
+        <v>0.297881245613098</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>0.387699991464615</v>
       </c>
       <c r="G159" t="n">
-        <v>0.297881275415421</v>
+        <v>0.297881245613098</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>0.391000002622604</v>
       </c>
       <c r="G163" t="n">
-        <v>0.300416707992554</v>
+        <v>0.300416678190231</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>0.390599995851517</v>
       </c>
       <c r="G165" t="n">
-        <v>0.300109386444092</v>
+        <v>0.300109416246414</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>0.388200014829636</v>
       </c>
       <c r="G166" t="n">
-        <v>0.298265397548676</v>
+        <v>0.29826545715332</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>0.388999998569489</v>
       </c>
       <c r="G167" t="n">
-        <v>0.298880040645599</v>
+        <v>0.298880070447922</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>0.397599995136261</v>
       </c>
       <c r="G169" t="n">
-        <v>0.30548769235611</v>
+        <v>0.305487662553787</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>0.394499987363815</v>
       </c>
       <c r="G171" t="n">
-        <v>0.303105890750885</v>
+        <v>0.303105860948563</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>0.395099997520447</v>
       </c>
       <c r="G172" t="n">
-        <v>0.303566843271255</v>
+        <v>0.303566873073578</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G174" t="n">
-        <v>0.307331711053848</v>
+        <v>0.307331740856171</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>0.396800011396408</v>
       </c>
       <c r="G175" t="n">
-        <v>0.304873019456863</v>
+        <v>0.304873049259186</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G176" t="n">
-        <v>0.307331711053848</v>
+        <v>0.307331740856171</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>0.385800004005432</v>
       </c>
       <c r="G180" t="n">
-        <v>0.296421408653259</v>
+        <v>0.296421378850937</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>0.392300009727478</v>
       </c>
       <c r="G181" t="n">
-        <v>0.3014155626297</v>
+        <v>0.301415592432022</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>0.36829999089241</v>
       </c>
       <c r="G183" t="n">
-        <v>0.282975643873215</v>
+        <v>0.282975703477859</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>0.377099990844727</v>
       </c>
       <c r="G185" t="n">
-        <v>0.289736956357956</v>
+        <v>0.289736926555634</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>0.381999999284744</v>
       </c>
       <c r="G187" t="n">
-        <v>0.293501764535904</v>
+        <v>0.293501734733582</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>0.380899995565414</v>
       </c>
       <c r="G188" t="n">
-        <v>0.292656600475311</v>
+        <v>0.292656570672989</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>0.376899987459183</v>
       </c>
       <c r="G190" t="n">
-        <v>0.289583265781403</v>
+        <v>0.289583295583725</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>0.375</v>
       </c>
       <c r="G191" t="n">
-        <v>0.288123488426208</v>
+        <v>0.288123428821564</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>0.370000004768372</v>
       </c>
       <c r="G192" t="n">
-        <v>0.284281820058823</v>
+        <v>0.2842817902565</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>0.374700009822845</v>
       </c>
       <c r="G193" t="n">
-        <v>0.28789296746254</v>
+        <v>0.287892997264862</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>0.381199985742569</v>
       </c>
       <c r="G195" t="n">
-        <v>0.292887061834335</v>
+        <v>0.292887032032013</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>0.381500005722046</v>
       </c>
       <c r="G196" t="n">
-        <v>0.293117612600327</v>
+        <v>0.293117642402649</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>0.379900008440018</v>
       </c>
       <c r="G197" t="n">
-        <v>0.291888266801834</v>
+        <v>0.291888296604156</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>0.372999995946884</v>
       </c>
       <c r="G199" t="n">
-        <v>0.286586821079254</v>
+        <v>0.286586791276932</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>0.381500005722046</v>
       </c>
       <c r="G200" t="n">
-        <v>0.293117612600327</v>
+        <v>0.293117642402649</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>0.379799991846085</v>
       </c>
       <c r="G203" t="n">
-        <v>0.291811436414719</v>
+        <v>0.291811406612396</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>0.388399988412857</v>
       </c>
       <c r="G206" t="n">
-        <v>0.298419088125229</v>
+        <v>0.298419058322906</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>0.388399988412857</v>
       </c>
       <c r="G207" t="n">
-        <v>0.298419088125229</v>
+        <v>0.298419058322906</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>0.388399988412857</v>
       </c>
       <c r="G208" t="n">
-        <v>0.298419088125229</v>
+        <v>0.298419058322906</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>0.383599996566772</v>
       </c>
       <c r="G209" t="n">
-        <v>0.294731110334396</v>
+        <v>0.294731080532074</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>0.374000012874603</v>
       </c>
       <c r="G212" t="n">
-        <v>0.287355124950409</v>
+        <v>0.287355095148087</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>0.380100011825562</v>
       </c>
       <c r="G215" t="n">
-        <v>0.292041927576065</v>
+        <v>0.292041957378387</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>0.373199999332428</v>
       </c>
       <c r="G216" t="n">
-        <v>0.286740452051163</v>
+        <v>0.286740481853485</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>0.370000004768372</v>
       </c>
       <c r="G218" t="n">
-        <v>0.284281820058823</v>
+        <v>0.2842817902565</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>0.363000005483627</v>
       </c>
       <c r="G219" t="n">
-        <v>0.278903543949127</v>
+        <v>0.278903514146805</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>0.351700007915497</v>
       </c>
       <c r="G221" t="n">
-        <v>0.270221412181854</v>
+        <v>0.270221382379532</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>0.354600012302399</v>
       </c>
       <c r="G222" t="n">
-        <v>0.27244958281517</v>
+        <v>0.272449553012848</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>0.356599986553192</v>
       </c>
       <c r="G224" t="n">
-        <v>0.27398619055748</v>
+        <v>0.273986160755157</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>0.358799993991852</v>
       </c>
       <c r="G225" t="n">
-        <v>0.275676518678665</v>
+        <v>0.275676488876343</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>0.352899998426437</v>
       </c>
       <c r="G231" t="n">
-        <v>0.271143347024918</v>
+        <v>0.27114337682724</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>0.349000006914139</v>
       </c>
       <c r="G234" t="n">
-        <v>0.268146932125092</v>
+        <v>0.268146902322769</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>0.34799998998642</v>
       </c>
       <c r="G235" t="n">
-        <v>0.267378568649292</v>
+        <v>0.26737853884697</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>0.345899999141693</v>
       </c>
       <c r="G237" t="n">
-        <v>0.265765070915222</v>
+        <v>0.265765100717545</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>0.348199993371964</v>
       </c>
       <c r="G239" t="n">
-        <v>0.267532199621201</v>
+        <v>0.267532229423523</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>0.363000005483627</v>
       </c>
       <c r="G242" t="n">
-        <v>0.278903543949127</v>
+        <v>0.278903514146805</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>0.368699997663498</v>
       </c>
       <c r="G244" t="n">
-        <v>0.283282965421677</v>
+        <v>0.283282995223999</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>0.364300012588501</v>
       </c>
       <c r="G245" t="n">
-        <v>0.279902309179306</v>
+        <v>0.279902338981628</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>0.362800002098083</v>
       </c>
       <c r="G253" t="n">
-        <v>0.278749853372574</v>
+        <v>0.278749823570251</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>0.363099992275238</v>
       </c>
       <c r="G254" t="n">
-        <v>0.278980314731598</v>
+        <v>0.27898034453392</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>0.362100005149841</v>
       </c>
       <c r="G255" t="n">
-        <v>0.278212040662766</v>
+        <v>0.278212010860443</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>0.377000004053116</v>
       </c>
       <c r="G259" t="n">
-        <v>0.28966012597084</v>
+        <v>0.289660155773163</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>0.383700013160706</v>
       </c>
       <c r="G261" t="n">
-        <v>0.294807970523834</v>
+        <v>0.294807940721512</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>0.377000004053116</v>
       </c>
       <c r="G264" t="n">
-        <v>0.28966012597084</v>
+        <v>0.289660155773163</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>0.375499993562698</v>
       </c>
       <c r="G265" t="n">
-        <v>0.288507580757141</v>
+        <v>0.288507610559464</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>0.370400011539459</v>
       </c>
       <c r="G266" t="n">
-        <v>0.284589141607285</v>
+        <v>0.284589111804962</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>0.378800004720688</v>
       </c>
       <c r="G268" t="n">
-        <v>0.291043102741241</v>
+        <v>0.291043132543564</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>0.379799991846085</v>
       </c>
       <c r="G271" t="n">
-        <v>0.291811436414719</v>
+        <v>0.291811406612396</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>0.381199985742569</v>
       </c>
       <c r="G272" t="n">
-        <v>0.292887061834335</v>
+        <v>0.292887032032013</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>0.383799999952316</v>
       </c>
       <c r="G273" t="n">
-        <v>0.294884741306305</v>
+        <v>0.294884771108627</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>0.372399985790253</v>
       </c>
       <c r="G278" t="n">
-        <v>0.286125808954239</v>
+        <v>0.286125838756561</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>0.370099991559982</v>
       </c>
       <c r="G279" t="n">
-        <v>0.284358650445938</v>
+        <v>0.284358620643616</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>0.360900014638901</v>
       </c>
       <c r="G281" t="n">
-        <v>0.277289986610413</v>
+        <v>0.277290016412735</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>0.359499990940094</v>
       </c>
       <c r="G283" t="n">
-        <v>0.276214301586151</v>
+        <v>0.276214331388474</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>0.356099992990494</v>
       </c>
       <c r="G284" t="n">
-        <v>0.273602038621902</v>
+        <v>0.27360200881958</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>0.351099997758865</v>
       </c>
       <c r="G285" t="n">
-        <v>0.269760370254517</v>
+        <v>0.269760400056839</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>0.353799998760223</v>
       </c>
       <c r="G287" t="n">
-        <v>0.271834909915924</v>
+        <v>0.271834880113602</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>0.36039999127388</v>
       </c>
       <c r="G290" t="n">
-        <v>0.276905834674835</v>
+        <v>0.276905864477158</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>0.364300012588501</v>
       </c>
       <c r="G292" t="n">
-        <v>0.279902309179306</v>
+        <v>0.279902338981628</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>0.367900013923645</v>
       </c>
       <c r="G294" t="n">
-        <v>0.282668322324753</v>
+        <v>0.28266829252243</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>0.365000009536743</v>
       </c>
       <c r="G295" t="n">
-        <v>0.280440181493759</v>
+        <v>0.280440151691437</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>0.363900005817413</v>
       </c>
       <c r="G296" t="n">
-        <v>0.279594987630844</v>
+        <v>0.279595017433167</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>0.361000001430511</v>
       </c>
       <c r="G297" t="n">
-        <v>0.277366876602173</v>
+        <v>0.27736684679985</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>0.36269998550415</v>
       </c>
       <c r="G301" t="n">
-        <v>0.278672963380814</v>
+        <v>0.278672993183136</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>0.363599985837936</v>
       </c>
       <c r="G303" t="n">
-        <v>0.279364466667175</v>
+        <v>0.279364496469498</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>0.373100012540817</v>
       </c>
       <c r="G307" t="n">
-        <v>0.28666365146637</v>
+        <v>0.286663621664047</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>0.366899996995926</v>
       </c>
       <c r="G309" t="n">
-        <v>0.281899988651276</v>
+        <v>0.281899958848953</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>0.369500011205673</v>
       </c>
       <c r="G311" t="n">
-        <v>0.283897638320923</v>
+        <v>0.283897668123245</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>0.36829999089241</v>
       </c>
       <c r="G312" t="n">
-        <v>0.282975643873215</v>
+        <v>0.282975703477859</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>0.371499985456467</v>
       </c>
       <c r="G314" t="n">
-        <v>0.285434246063232</v>
+        <v>0.285434275865555</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>0.395999997854233</v>
       </c>
       <c r="G317" t="n">
-        <v>0.30425837635994</v>
+        <v>0.304258346557617</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>0.405000001192093</v>
       </c>
       <c r="G318" t="n">
-        <v>0.311173319816589</v>
+        <v>0.311173349618912</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>0.418999999761581</v>
       </c>
       <c r="G319" t="n">
-        <v>0.321929901838303</v>
+        <v>0.321929931640625</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>0.423799991607666</v>
       </c>
       <c r="G320" t="n">
-        <v>0.325617909431458</v>
+        <v>0.32561793923378</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>0.43189999461174</v>
       </c>
       <c r="G321" t="n">
-        <v>0.33184140920639</v>
+        <v>0.331841379404068</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>0.404900014400482</v>
       </c>
       <c r="G327" t="n">
-        <v>0.311096549034119</v>
+        <v>0.311096519231796</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G331" t="n">
-        <v>0.307331711053848</v>
+        <v>0.307331740856171</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>0.375999987125397</v>
       </c>
       <c r="G332" t="n">
-        <v>0.288891792297363</v>
+        <v>0.288891762495041</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>0.384200006723404</v>
       </c>
       <c r="G335" t="n">
-        <v>0.295192062854767</v>
+        <v>0.295192092657089</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>0.38629999756813</v>
       </c>
       <c r="G336" t="n">
-        <v>0.296805590391159</v>
+        <v>0.296805560588837</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>0.390500009059906</v>
       </c>
       <c r="G338" t="n">
-        <v>0.300032585859299</v>
+        <v>0.300032556056976</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>0.403800010681152</v>
       </c>
       <c r="G341" t="n">
-        <v>0.310251355171204</v>
+        <v>0.310251325368881</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>0.408100008964539</v>
       </c>
       <c r="G342" t="n">
-        <v>0.313555151224136</v>
+        <v>0.313555181026459</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>0.396800011396408</v>
       </c>
       <c r="G343" t="n">
-        <v>0.304873019456863</v>
+        <v>0.304873049259186</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>0.391499996185303</v>
       </c>
       <c r="G344" t="n">
-        <v>0.300800859928131</v>
+        <v>0.300800889730453</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>0.391499996185303</v>
       </c>
       <c r="G345" t="n">
-        <v>0.300800859928131</v>
+        <v>0.300800889730453</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G350" t="n">
-        <v>0.327308237552643</v>
+        <v>0.327308267354965</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G352" t="n">
-        <v>0.307331711053848</v>
+        <v>0.307331740856171</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>0.406199991703033</v>
       </c>
       <c r="G354" t="n">
-        <v>0.312095314264297</v>
+        <v>0.31209534406662</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>0.408699989318848</v>
       </c>
       <c r="G356" t="n">
-        <v>0.314016133546829</v>
+        <v>0.314016163349152</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G357" t="n">
-        <v>0.315014988183975</v>
+        <v>0.315014958381653</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>0.406399995088577</v>
       </c>
       <c r="G358" t="n">
-        <v>0.312248975038528</v>
+        <v>0.312249004840851</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>0.397599995136261</v>
       </c>
       <c r="G362" t="n">
-        <v>0.30548769235611</v>
+        <v>0.305487662553787</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G363" t="n">
-        <v>0.307331711053848</v>
+        <v>0.307331740856171</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>0.402099996805191</v>
       </c>
       <c r="G364" t="n">
-        <v>0.308945178985596</v>
+        <v>0.308945208787918</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>0.400499999523163</v>
       </c>
       <c r="G367" t="n">
-        <v>0.307715833187103</v>
+        <v>0.307715862989426</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>0.405400007963181</v>
       </c>
       <c r="G369" t="n">
-        <v>0.311480641365051</v>
+        <v>0.311480700969696</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>0.413599997758865</v>
       </c>
       <c r="G371" t="n">
-        <v>0.3177809715271</v>
+        <v>0.317780941724777</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>0.423000007867813</v>
       </c>
       <c r="G375" t="n">
-        <v>0.325003236532211</v>
+        <v>0.325003296136856</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>0.413500010967255</v>
       </c>
       <c r="G377" t="n">
-        <v>0.317704111337662</v>
+        <v>0.317704141139984</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>0.418500006198883</v>
       </c>
       <c r="G378" t="n">
-        <v>0.32154580950737</v>
+        <v>0.321545749902725</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>0.421299993991852</v>
       </c>
       <c r="G381" t="n">
-        <v>0.323697119951248</v>
+        <v>0.323697090148926</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G389" t="n">
-        <v>0.33499151468277</v>
+        <v>0.334991484880447</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>0.441100001335144</v>
       </c>
       <c r="G392" t="n">
-        <v>0.338910013437271</v>
+        <v>0.338909983634949</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>0.440100014209747</v>
       </c>
       <c r="G393" t="n">
-        <v>0.338141739368439</v>
+        <v>0.338141679763794</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>0.442099988460541</v>
       </c>
       <c r="G394" t="n">
-        <v>0.339678347110748</v>
+        <v>0.339678317308426</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>0.456000000238419</v>
       </c>
       <c r="G395" t="n">
-        <v>0.350358098745346</v>
+        <v>0.350358128547668</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>0.451099991798401</v>
       </c>
       <c r="G396" t="n">
-        <v>0.346593290567398</v>
+        <v>0.34659332036972</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G397" t="n">
-        <v>0.344211518764496</v>
+        <v>0.344211488962173</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>0.443399995565414</v>
       </c>
       <c r="G398" t="n">
-        <v>0.34067714214325</v>
+        <v>0.340677171945572</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>0.435499995946884</v>
       </c>
       <c r="G399" t="n">
-        <v>0.334607392549515</v>
+        <v>0.334607362747192</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>0.450500011444092</v>
       </c>
       <c r="G402" t="n">
-        <v>0.346132338047028</v>
+        <v>0.346132308244705</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>0.44200000166893</v>
       </c>
       <c r="G403" t="n">
-        <v>0.339601516723633</v>
+        <v>0.339601546525955</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>0.481499999761581</v>
       </c>
       <c r="G406" t="n">
-        <v>0.369950503110886</v>
+        <v>0.369950532913208</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>0.475600004196167</v>
       </c>
       <c r="G407" t="n">
-        <v>0.36541736125946</v>
+        <v>0.365417391061783</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>0.486900001764297</v>
       </c>
       <c r="G409" t="n">
-        <v>0.374099463224411</v>
+        <v>0.374099522829056</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>0.47979998588562</v>
       </c>
       <c r="G415" t="n">
-        <v>0.3686443567276</v>
+        <v>0.368644386529922</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>0.476700007915497</v>
       </c>
       <c r="G417" t="n">
-        <v>0.366262525320053</v>
+        <v>0.366262555122375</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>0.467500001192093</v>
       </c>
       <c r="G421" t="n">
-        <v>0.359193950891495</v>
+        <v>0.359193921089172</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>0.484200000762939</v>
       </c>
       <c r="G423" t="n">
-        <v>0.372024983167648</v>
+        <v>0.372025042772293</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>0.48879998922348</v>
       </c>
       <c r="G424" t="n">
-        <v>0.375559329986572</v>
+        <v>0.37555930018425</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>0.494899988174438</v>
       </c>
       <c r="G425" t="n">
-        <v>0.380246132612228</v>
+        <v>0.380246102809906</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>0.510999977588654</v>
       </c>
       <c r="G426" t="n">
-        <v>0.392616242170334</v>
+        <v>0.392616212368011</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>0.546000003814697</v>
       </c>
       <c r="G429" t="n">
-        <v>0.419507801532745</v>
+        <v>0.419507771730423</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>0.555000007152557</v>
       </c>
       <c r="G434" t="n">
-        <v>0.426422715187073</v>
+        <v>0.426422744989395</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>0.550999999046326</v>
       </c>
       <c r="G435" t="n">
-        <v>0.423349380493164</v>
+        <v>0.423349410295486</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>0.568499982357025</v>
       </c>
       <c r="G441" t="n">
-        <v>0.436795145273209</v>
+        <v>0.436795175075531</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>0.563499987125397</v>
       </c>
       <c r="G442" t="n">
-        <v>0.43295356631279</v>
+        <v>0.432953536510468</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>0.58950001001358</v>
       </c>
       <c r="G443" t="n">
-        <v>0.452930122613907</v>
+        <v>0.452930092811584</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G444" t="n">
-        <v>0.459460824728012</v>
+        <v>0.459460914134979</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>0.605499982833862</v>
       </c>
       <c r="G445" t="n">
-        <v>0.465223342180252</v>
+        <v>0.46522331237793</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>0.626500010490417</v>
       </c>
       <c r="G447" t="n">
-        <v>0.48135831952095</v>
+        <v>0.481358289718628</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G448" t="n">
-        <v>0.522463798522949</v>
+        <v>0.522463858127594</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>0.671000003814697</v>
       </c>
       <c r="G452" t="n">
-        <v>0.515548825263977</v>
+        <v>0.515548884868622</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>0.637499988079071</v>
       </c>
       <c r="G454" t="n">
-        <v>0.489809900522232</v>
+        <v>0.489809930324554</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>0.625</v>
       </c>
       <c r="G455" t="n">
-        <v>0.480205774307251</v>
+        <v>0.480205804109573</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>0.675499975681305</v>
       </c>
       <c r="G456" t="n">
-        <v>0.519006311893463</v>
+        <v>0.519006371498108</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>0.665499985218048</v>
       </c>
       <c r="G457" t="n">
-        <v>0.511323094367981</v>
+        <v>0.511323153972626</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G458" t="n">
-        <v>0.499413937330246</v>
+        <v>0.499413907527924</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G459" t="n">
-        <v>0.491730630397797</v>
+        <v>0.491730719804764</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>0.625</v>
       </c>
       <c r="G462" t="n">
-        <v>0.480205774307251</v>
+        <v>0.480205804109573</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>0.630999982357025</v>
       </c>
       <c r="G464" t="n">
-        <v>0.484815657138824</v>
+        <v>0.484815686941147</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>0.637499988079071</v>
       </c>
       <c r="G465" t="n">
-        <v>0.489809900522232</v>
+        <v>0.489809930324554</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>0.625</v>
       </c>
       <c r="G466" t="n">
-        <v>0.480205774307251</v>
+        <v>0.480205804109573</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>0.644500017166138</v>
       </c>
       <c r="G467" t="n">
-        <v>0.49518820643425</v>
+        <v>0.495188146829605</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G468" t="n">
-        <v>0.490194082260132</v>
+        <v>0.490194052457809</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G469" t="n">
-        <v>0.491730630397797</v>
+        <v>0.491730719804764</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G470" t="n">
-        <v>0.491730630397797</v>
+        <v>0.491730719804764</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>0.70550000667572</v>
       </c>
       <c r="G472" t="n">
-        <v>0.542056322097778</v>
+        <v>0.542056262493134</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>0.763000011444092</v>
       </c>
       <c r="G474" t="n">
-        <v>0.586235225200653</v>
+        <v>0.586235284805298</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>0.781000018119812</v>
       </c>
       <c r="G475" t="n">
-        <v>0.600065171718597</v>
+        <v>0.600065112113953</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>0.744499981403351</v>
       </c>
       <c r="G477" t="n">
-        <v>0.572021126747131</v>
+        <v>0.572021067142487</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>0.745500028133392</v>
       </c>
       <c r="G478" t="n">
-        <v>0.572789549827576</v>
+        <v>0.572789490222931</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>0.718999981880188</v>
       </c>
       <c r="G479" t="n">
-        <v>0.552428603172302</v>
+        <v>0.552428662776947</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>0.736500024795532</v>
       </c>
       <c r="G483" t="n">
-        <v>0.565874516963959</v>
+        <v>0.565874457359314</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>0.750999987125397</v>
       </c>
       <c r="G484" t="n">
-        <v>0.577015161514282</v>
+        <v>0.577015221118927</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>0.791499972343445</v>
       </c>
       <c r="G487" t="n">
-        <v>0.608132481575012</v>
+        <v>0.608132541179657</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>0.807500004768372</v>
       </c>
       <c r="G489" t="n">
-        <v>0.620425820350647</v>
+        <v>0.620425879955292</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G494" t="n">
-        <v>0.560880362987518</v>
+        <v>0.560880303382874</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>0.778999984264374</v>
       </c>
       <c r="G495" t="n">
-        <v>0.598528444766998</v>
+        <v>0.598528385162354</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>0.750999987125397</v>
       </c>
       <c r="G496" t="n">
-        <v>0.577015161514282</v>
+        <v>0.577015221118927</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>0.778999984264374</v>
       </c>
       <c r="G501" t="n">
-        <v>0.598528444766998</v>
+        <v>0.598528385162354</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>0.782999992370605</v>
       </c>
       <c r="G502" t="n">
-        <v>0.601601719856262</v>
+        <v>0.601601779460907</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>0.750999987125397</v>
       </c>
       <c r="G507" t="n">
-        <v>0.577015161514282</v>
+        <v>0.577015221118927</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>0.737999975681305</v>
       </c>
       <c r="G509" t="n">
-        <v>0.567026972770691</v>
+        <v>0.567026913166046</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>0.707499980926514</v>
       </c>
       <c r="G511" t="n">
-        <v>0.543592929840088</v>
+        <v>0.543592870235443</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>0.735000014305115</v>
       </c>
       <c r="G512" t="n">
-        <v>0.564722001552582</v>
+        <v>0.564721941947937</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>0.75</v>
       </c>
       <c r="G514" t="n">
-        <v>0.576246976852417</v>
+        <v>0.576246857643127</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>0.782999992370605</v>
       </c>
       <c r="G516" t="n">
-        <v>0.601601719856262</v>
+        <v>0.601601779460907</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G519" t="n">
-        <v>0.587003529071808</v>
+        <v>0.587003469467163</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>0.785000026226044</v>
       </c>
       <c r="G525" t="n">
-        <v>0.603138446807861</v>
+        <v>0.603138387203217</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>0.796999990940094</v>
       </c>
       <c r="G526" t="n">
-        <v>0.612358391284943</v>
+        <v>0.612358450889587</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>0.773000001907349</v>
       </c>
       <c r="G528" t="n">
-        <v>0.593918442726135</v>
+        <v>0.59391850233078</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>0.77700001001358</v>
       </c>
       <c r="G529" t="n">
-        <v>0.596991777420044</v>
+        <v>0.596991717815399</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G530" t="n">
-        <v>0.608516752719879</v>
+        <v>0.608516693115234</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>0.767000019550323</v>
       </c>
       <c r="G532" t="n">
-        <v>0.589308440685272</v>
+        <v>0.589308500289917</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>0.750999987125397</v>
       </c>
       <c r="G533" t="n">
-        <v>0.577015161514282</v>
+        <v>0.577015221118927</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>0.75</v>
       </c>
       <c r="G534" t="n">
-        <v>0.576246976852417</v>
+        <v>0.576246857643127</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>0.735000014305115</v>
       </c>
       <c r="G535" t="n">
-        <v>0.564722001552582</v>
+        <v>0.564721941947937</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>0.700999975204468</v>
       </c>
       <c r="G537" t="n">
-        <v>0.538598835468292</v>
+        <v>0.538598716259003</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>0.725000023841858</v>
       </c>
       <c r="G538" t="n">
-        <v>0.55703866481781</v>
+        <v>0.557038724422455</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G539" t="n">
-        <v>0.536293864250183</v>
+        <v>0.536293804645538</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>0.693000018596649</v>
       </c>
       <c r="G544" t="n">
-        <v>0.532452166080475</v>
+        <v>0.53245210647583</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>0.699000000953674</v>
       </c>
       <c r="G545" t="n">
-        <v>0.537062108516693</v>
+        <v>0.537062048912048</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G546" t="n">
-        <v>0.527073800563812</v>
+        <v>0.527073860168457</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G547" t="n">
-        <v>0.522463798522949</v>
+        <v>0.522463858127594</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G548" t="n">
-        <v>0.522463798522949</v>
+        <v>0.522463858127594</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>0.693000018596649</v>
       </c>
       <c r="G549" t="n">
-        <v>0.532452166080475</v>
+        <v>0.53245210647583</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>0.693000018596649</v>
       </c>
       <c r="G552" t="n">
-        <v>0.532452166080475</v>
+        <v>0.53245210647583</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G553" t="n">
-        <v>0.536293864250183</v>
+        <v>0.536293804645538</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G562" t="n">
-        <v>0.519390523433685</v>
+        <v>0.51939058303833</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G564" t="n">
-        <v>0.527073800563812</v>
+        <v>0.527073860168457</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>0.714999973773956</v>
       </c>
       <c r="G568" t="n">
-        <v>0.549355328083038</v>
+        <v>0.549355447292328</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>0.652999997138977</v>
       </c>
       <c r="G569" t="n">
-        <v>0.501718997955322</v>
+        <v>0.501718938350677</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G571" t="n">
-        <v>0.477900743484497</v>
+        <v>0.477900803089142</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>0.625</v>
       </c>
       <c r="G572" t="n">
-        <v>0.480205774307251</v>
+        <v>0.480205804109573</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G574" t="n">
-        <v>0.488657355308533</v>
+        <v>0.488657385110855</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G576" t="n">
-        <v>0.471754193305969</v>
+        <v>0.471754163503647</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G577" t="n">
-        <v>0.491730630397797</v>
+        <v>0.491730719804764</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>0.630999982357025</v>
       </c>
       <c r="G581" t="n">
-        <v>0.484815657138824</v>
+        <v>0.484815686941147</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>0.626999974250793</v>
       </c>
       <c r="G582" t="n">
-        <v>0.481742382049561</v>
+        <v>0.481742411851883</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G583" t="n">
-        <v>0.480974048376083</v>
+        <v>0.480974107980728</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>0.629000008106232</v>
       </c>
       <c r="G584" t="n">
-        <v>0.48327910900116</v>
+        <v>0.483279079198837</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>0.623000025749207</v>
       </c>
       <c r="G585" t="n">
-        <v>0.478669077157974</v>
+        <v>0.478669136762619</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G586" t="n">
-        <v>0.470217436552048</v>
+        <v>0.47021746635437</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>0.609000027179718</v>
       </c>
       <c r="G588" t="n">
-        <v>0.467912554740906</v>
+        <v>0.467912495136261</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>0.60699999332428</v>
       </c>
       <c r="G589" t="n">
-        <v>0.466375827789307</v>
+        <v>0.466375857591629</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G590" t="n">
-        <v>0.470217436552048</v>
+        <v>0.47021746635437</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>0.605000019073486</v>
       </c>
       <c r="G591" t="n">
-        <v>0.464839220046997</v>
+        <v>0.464839190244675</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G592" t="n">
-        <v>0.470217436552048</v>
+        <v>0.47021746635437</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>0.634999990463257</v>
       </c>
       <c r="G595" t="n">
-        <v>0.487889051437378</v>
+        <v>0.4878890812397</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>0.634999990463257</v>
       </c>
       <c r="G596" t="n">
-        <v>0.487889051437378</v>
+        <v>0.4878890812397</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>0.625</v>
       </c>
       <c r="G597" t="n">
-        <v>0.480205774307251</v>
+        <v>0.480205804109573</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G598" t="n">
-        <v>0.491730630397797</v>
+        <v>0.491730719804764</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>0.611000001430511</v>
       </c>
       <c r="G601" t="n">
-        <v>0.469449132680893</v>
+        <v>0.469449162483215</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>0.569000005722046</v>
       </c>
       <c r="G602" t="n">
-        <v>0.437179327011108</v>
+        <v>0.437179356813431</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>0.561999976634979</v>
       </c>
       <c r="G604" t="n">
-        <v>0.431801050901413</v>
+        <v>0.431801021099091</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>0.555000007152557</v>
       </c>
       <c r="G605" t="n">
-        <v>0.426422715187073</v>
+        <v>0.426422744989395</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>0.578000009059906</v>
       </c>
       <c r="G606" t="n">
-        <v>0.444094270467758</v>
+        <v>0.444094300270081</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G608" t="n">
-        <v>0.424117714166641</v>
+        <v>0.424117743968964</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>0.541000008583069</v>
       </c>
       <c r="G611" t="n">
-        <v>0.415666043758392</v>
+        <v>0.415666073560715</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>0.493499994277954</v>
       </c>
       <c r="G614" t="n">
-        <v>0.379170447587967</v>
+        <v>0.379170477390289</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>0.501999974250793</v>
       </c>
       <c r="G616" t="n">
-        <v>0.385701268911362</v>
+        <v>0.385701239109039</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>0.501999974250793</v>
       </c>
       <c r="G618" t="n">
-        <v>0.385701268911362</v>
+        <v>0.385701239109039</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>0.505999982357025</v>
       </c>
       <c r="G619" t="n">
-        <v>0.388774573802948</v>
+        <v>0.388774544000626</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>0.501999974250793</v>
       </c>
       <c r="G623" t="n">
-        <v>0.385701268911362</v>
+        <v>0.385701239109039</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>0.477999985218048</v>
       </c>
       <c r="G625" t="n">
-        <v>0.367261350154877</v>
+        <v>0.367261320352554</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>0.474999994039536</v>
       </c>
       <c r="G626" t="n">
-        <v>0.364956378936768</v>
+        <v>0.364956349134445</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>0.46900001168251</v>
       </c>
       <c r="G630" t="n">
-        <v>0.360346376895905</v>
+        <v>0.360346406698227</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>0.458499997854233</v>
       </c>
       <c r="G631" t="n">
-        <v>0.3522789478302</v>
+        <v>0.352278918027878</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>0.46399998664856</v>
       </c>
       <c r="G632" t="n">
-        <v>0.356504708528519</v>
+        <v>0.356504738330841</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>0.483500003814697</v>
       </c>
       <c r="G633" t="n">
-        <v>0.371487140655518</v>
+        <v>0.371487200260162</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>0.479000002145767</v>
       </c>
       <c r="G634" t="n">
-        <v>0.368029683828354</v>
+        <v>0.368029713630676</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>0.484499990940094</v>
       </c>
       <c r="G635" t="n">
-        <v>0.372255474328995</v>
+        <v>0.37225553393364</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>0.479000002145767</v>
       </c>
       <c r="G638" t="n">
-        <v>0.368029683828354</v>
+        <v>0.368029713630676</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>0.487500011920929</v>
       </c>
       <c r="G641" t="n">
-        <v>0.374560475349426</v>
+        <v>0.374560505151749</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>0.479000002145767</v>
       </c>
       <c r="G642" t="n">
-        <v>0.368029683828354</v>
+        <v>0.368029713630676</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>0.486999988555908</v>
       </c>
       <c r="G643" t="n">
-        <v>0.374176323413849</v>
+        <v>0.374176293611526</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>0.479000002145767</v>
       </c>
       <c r="G645" t="n">
-        <v>0.368029683828354</v>
+        <v>0.368029713630676</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>0.471500009298325</v>
       </c>
       <c r="G646" t="n">
-        <v>0.362267225980759</v>
+        <v>0.362267255783081</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>0.460500001907349</v>
       </c>
       <c r="G647" t="n">
-        <v>0.353815644979477</v>
+        <v>0.353815615177155</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>0.482499986886978</v>
       </c>
       <c r="G651" t="n">
-        <v>0.37071880698204</v>
+        <v>0.370718836784363</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G658" t="n">
-        <v>0.411056160926819</v>
+        <v>0.411056131124496</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>0.49549999833107</v>
       </c>
       <c r="G665" t="n">
-        <v>0.380707085132599</v>
+        <v>0.380707114934921</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>0.486999988555908</v>
       </c>
       <c r="G666" t="n">
-        <v>0.374176323413849</v>
+        <v>0.374176293611526</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>0.472000002861023</v>
       </c>
       <c r="G667" t="n">
-        <v>0.362651407718658</v>
+        <v>0.362651377916336</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>0.467999994754791</v>
       </c>
       <c r="G668" t="n">
-        <v>0.35957807302475</v>
+        <v>0.359578102827072</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G669" t="n">
-        <v>0.353431463241577</v>
+        <v>0.353431403636932</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>0.44650000333786</v>
       </c>
       <c r="G672" t="n">
-        <v>0.343059003353119</v>
+        <v>0.343058973550797</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>0.462000012397766</v>
       </c>
       <c r="G673" t="n">
-        <v>0.354968100786209</v>
+        <v>0.354968130588531</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>0.477999985218048</v>
       </c>
       <c r="G675" t="n">
-        <v>0.367261350154877</v>
+        <v>0.367261320352554</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>0.472000002861023</v>
       </c>
       <c r="G677" t="n">
-        <v>0.362651407718658</v>
+        <v>0.362651377916336</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>0.465000003576279</v>
       </c>
       <c r="G678" t="n">
-        <v>0.357273072004318</v>
+        <v>0.357273101806641</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>0.421499997377396</v>
       </c>
       <c r="G681" t="n">
-        <v>0.323850750923157</v>
+        <v>0.323850780725479</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>0.470999985933304</v>
       </c>
       <c r="G682" t="n">
-        <v>0.361883044242859</v>
+        <v>0.361883074045181</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>0.515999972820282</v>
       </c>
       <c r="G686" t="n">
-        <v>0.396457880735397</v>
+        <v>0.396457850933075</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>0.537000000476837</v>
       </c>
       <c r="G687" t="n">
-        <v>0.412592768669128</v>
+        <v>0.412592828273773</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>0.523000001907349</v>
       </c>
       <c r="G689" t="n">
-        <v>0.401836216449738</v>
+        <v>0.401836156845093</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>0.513000011444092</v>
       </c>
       <c r="G690" t="n">
-        <v>0.394152879714966</v>
+        <v>0.394152939319611</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G691" t="n">
-        <v>0.399531185626984</v>
+        <v>0.399531155824661</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>0.522000014781952</v>
       </c>
       <c r="G694" t="n">
-        <v>0.40106788277626</v>
+        <v>0.401067852973938</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>0.515999972820282</v>
       </c>
       <c r="G695" t="n">
-        <v>0.396457880735397</v>
+        <v>0.396457850933075</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G696" t="n">
-        <v>0.399531185626984</v>
+        <v>0.399531155824661</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>0.51800000667572</v>
       </c>
       <c r="G697" t="n">
-        <v>0.397994548082352</v>
+        <v>0.397994518280029</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>0.513000011444092</v>
       </c>
       <c r="G698" t="n">
-        <v>0.394152879714966</v>
+        <v>0.394152939319611</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>0.501999974250793</v>
       </c>
       <c r="G699" t="n">
-        <v>0.385701268911362</v>
+        <v>0.385701239109039</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>0.474500000476837</v>
       </c>
       <c r="G701" t="n">
-        <v>0.36457222700119</v>
+        <v>0.364572197198868</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G703" t="n">
-        <v>0.345748156309128</v>
+        <v>0.345748126506805</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>0.456000000238419</v>
       </c>
       <c r="G704" t="n">
-        <v>0.350358098745346</v>
+        <v>0.350358128547668</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>0.458499997854233</v>
       </c>
       <c r="G705" t="n">
-        <v>0.3522789478302</v>
+        <v>0.352278918027878</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G706" t="n">
-        <v>0.353431463241577</v>
+        <v>0.353431403636932</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G709" t="n">
-        <v>0.337296485900879</v>
+        <v>0.337296515703201</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G710" t="n">
-        <v>0.329613208770752</v>
+        <v>0.329613268375397</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G711" t="n">
-        <v>0.328076511621475</v>
+        <v>0.328076541423798</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G712" t="n">
-        <v>0.328076511621475</v>
+        <v>0.328076541423798</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>0.431499987840652</v>
       </c>
       <c r="G713" t="n">
-        <v>0.331534057855606</v>
+        <v>0.331534028053284</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G715" t="n">
-        <v>0.31424668431282</v>
+        <v>0.314246654510498</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>0.415499985218048</v>
       </c>
       <c r="G716" t="n">
-        <v>0.319240778684616</v>
+        <v>0.319240808486938</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>0.425500005483627</v>
       </c>
       <c r="G717" t="n">
-        <v>0.326924055814743</v>
+        <v>0.326924085617065</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>0.425500005483627</v>
       </c>
       <c r="G722" t="n">
-        <v>0.326924055814743</v>
+        <v>0.326924085617065</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>0.423000007867813</v>
       </c>
       <c r="G728" t="n">
-        <v>0.325003236532211</v>
+        <v>0.325003296136856</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G729" t="n">
-        <v>0.327308237552643</v>
+        <v>0.327308267354965</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G730" t="n">
-        <v>0.329613208770752</v>
+        <v>0.329613268375397</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G731" t="n">
-        <v>0.329613208770752</v>
+        <v>0.329613268375397</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G732" t="n">
-        <v>0.328076511621475</v>
+        <v>0.328076541423798</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G734" t="n">
-        <v>0.324234902858734</v>
+        <v>0.324234932661057</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>0.408499985933304</v>
       </c>
       <c r="G735" t="n">
-        <v>0.313862442970276</v>
+        <v>0.313862472772598</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>0.391999989748001</v>
       </c>
       <c r="G738" t="n">
-        <v>0.301185071468353</v>
+        <v>0.301185041666031</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>0.390500009059906</v>
       </c>
       <c r="G740" t="n">
-        <v>0.300032585859299</v>
+        <v>0.300032556056976</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>0.386500000953674</v>
       </c>
       <c r="G741" t="n">
-        <v>0.296959221363068</v>
+        <v>0.29695925116539</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>0.391000002622604</v>
       </c>
       <c r="G742" t="n">
-        <v>0.300416707992554</v>
+        <v>0.300416678190231</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>0.400499999523163</v>
       </c>
       <c r="G743" t="n">
-        <v>0.307715833187103</v>
+        <v>0.307715862989426</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>0.418999999761581</v>
       </c>
       <c r="G747" t="n">
-        <v>0.321929901838303</v>
+        <v>0.321929931640625</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>0.420500010251999</v>
       </c>
       <c r="G748" t="n">
-        <v>0.32308241724968</v>
+        <v>0.323082447052002</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G749" t="n">
-        <v>0.324234902858734</v>
+        <v>0.324234932661057</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>0.400999993085861</v>
       </c>
       <c r="G751" t="n">
-        <v>0.308100014925003</v>
+        <v>0.308100044727325</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G752" t="n">
-        <v>0.307331711053848</v>
+        <v>0.307331740856171</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>0.404000014066696</v>
       </c>
       <c r="G753" t="n">
-        <v>0.310405045747757</v>
+        <v>0.310405015945435</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>0.399500012397766</v>
       </c>
       <c r="G754" t="n">
-        <v>0.306947529315948</v>
+        <v>0.306947559118271</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>0.39750000834465</v>
       </c>
       <c r="G757" t="n">
-        <v>0.305410832166672</v>
+        <v>0.305410891771317</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G758" t="n">
-        <v>0.307331711053848</v>
+        <v>0.307331740856171</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G759" t="n">
-        <v>0.31424668431282</v>
+        <v>0.314246654510498</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>0.396499991416931</v>
       </c>
       <c r="G761" t="n">
-        <v>0.304642528295517</v>
+        <v>0.304642558097839</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>0.394499987363815</v>
       </c>
       <c r="G762" t="n">
-        <v>0.303105890750885</v>
+        <v>0.303105860948563</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>0.400999993085861</v>
       </c>
       <c r="G764" t="n">
-        <v>0.308100014925003</v>
+        <v>0.308100044727325</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>0.405000001192093</v>
       </c>
       <c r="G765" t="n">
-        <v>0.311173319816589</v>
+        <v>0.311173349618912</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G767" t="n">
-        <v>0.344211518764496</v>
+        <v>0.344211488962173</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G768" t="n">
-        <v>0.345748156309128</v>
+        <v>0.345748126506805</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>0.467999994754791</v>
       </c>
       <c r="G769" t="n">
-        <v>0.35957807302475</v>
+        <v>0.359578102827072</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>0.46900001168251</v>
       </c>
       <c r="G772" t="n">
-        <v>0.360346376895905</v>
+        <v>0.360346406698227</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>0.46900001168251</v>
       </c>
       <c r="G775" t="n">
-        <v>0.360346376895905</v>
+        <v>0.360346406698227</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>0.467500001192093</v>
       </c>
       <c r="G776" t="n">
-        <v>0.359193950891495</v>
+        <v>0.359193921089172</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>0.456999987363815</v>
       </c>
       <c r="G779" t="n">
-        <v>0.351126432418823</v>
+        <v>0.351126462221146</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G780" t="n">
-        <v>0.353431463241577</v>
+        <v>0.353431403636932</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>0.46900001168251</v>
       </c>
       <c r="G781" t="n">
-        <v>0.360346376895905</v>
+        <v>0.360346406698227</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>0.462999999523163</v>
       </c>
       <c r="G782" t="n">
-        <v>0.355736404657364</v>
+        <v>0.355736434459686</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G784" t="n">
-        <v>0.353431463241577</v>
+        <v>0.353431403636932</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G786" t="n">
-        <v>0.353431463241577</v>
+        <v>0.353431403636932</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>0.48199999332428</v>
       </c>
       <c r="G789" t="n">
-        <v>0.370334714651108</v>
+        <v>0.370334684848785</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>0.474999994039536</v>
       </c>
       <c r="G791" t="n">
-        <v>0.364956378936768</v>
+        <v>0.364956349134445</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>0.487500011920929</v>
       </c>
       <c r="G793" t="n">
-        <v>0.374560475349426</v>
+        <v>0.374560505151749</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>0.486999988555908</v>
       </c>
       <c r="G794" t="n">
-        <v>0.374176323413849</v>
+        <v>0.374176293611526</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>0.499500006437302</v>
       </c>
       <c r="G797" t="n">
-        <v>0.383780419826508</v>
+        <v>0.38378044962883</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>0.490500003099442</v>
       </c>
       <c r="G800" t="n">
-        <v>0.376865446567535</v>
+        <v>0.376865476369858</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>0.49099999666214</v>
       </c>
       <c r="G801" t="n">
-        <v>0.377249628305435</v>
+        <v>0.377249658107758</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>0.523000001907349</v>
       </c>
       <c r="G803" t="n">
-        <v>0.401836216449738</v>
+        <v>0.401836156845093</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>0.515999972820282</v>
       </c>
       <c r="G804" t="n">
-        <v>0.396457880735397</v>
+        <v>0.396457850933075</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>0.524999976158142</v>
       </c>
       <c r="G806" t="n">
-        <v>0.403372824192047</v>
+        <v>0.40337285399437</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>0.528999984264374</v>
       </c>
       <c r="G808" t="n">
-        <v>0.406446129083633</v>
+        <v>0.406446099281311</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>0.515999972820282</v>
       </c>
       <c r="G810" t="n">
-        <v>0.396457880735397</v>
+        <v>0.396457850933075</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>0.515999972820282</v>
       </c>
       <c r="G819" t="n">
-        <v>0.396457880735397</v>
+        <v>0.396457850933075</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>0.515999972820282</v>
       </c>
       <c r="G820" t="n">
-        <v>0.396457880735397</v>
+        <v>0.396457850933075</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>0.513000011444092</v>
       </c>
       <c r="G821" t="n">
-        <v>0.394152879714966</v>
+        <v>0.394152939319611</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>0.496499985456467</v>
       </c>
       <c r="G822" t="n">
-        <v>0.381475418806076</v>
+        <v>0.381475448608398</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>0.484499990940094</v>
       </c>
       <c r="G825" t="n">
-        <v>0.372255474328995</v>
+        <v>0.37225553393364</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>0.523000001907349</v>
       </c>
       <c r="G830" t="n">
-        <v>0.401836216449738</v>
+        <v>0.401836156845093</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G831" t="n">
-        <v>0.407214522361755</v>
+        <v>0.407214492559433</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G832" t="n">
-        <v>0.407214522361755</v>
+        <v>0.407214492559433</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>0.505999982357025</v>
       </c>
       <c r="G834" t="n">
-        <v>0.388774573802948</v>
+        <v>0.388774544000626</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>0.504000008106232</v>
       </c>
       <c r="G836" t="n">
-        <v>0.387237936258316</v>
+        <v>0.387237906455994</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>0.541000008583069</v>
       </c>
       <c r="G839" t="n">
-        <v>0.415666043758392</v>
+        <v>0.415666073560715</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>0.522000014781952</v>
       </c>
       <c r="G843" t="n">
-        <v>0.40106788277626</v>
+        <v>0.401067852973938</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G844" t="n">
-        <v>0.399531185626984</v>
+        <v>0.399531155824661</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G845" t="n">
-        <v>0.411056160926819</v>
+        <v>0.411056131124496</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>0.528999984264374</v>
       </c>
       <c r="G846" t="n">
-        <v>0.406446129083633</v>
+        <v>0.406446099281311</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G847" t="n">
-        <v>0.399531185626984</v>
+        <v>0.399531155824661</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>0.517000019550323</v>
       </c>
       <c r="G850" t="n">
-        <v>0.397226214408875</v>
+        <v>0.397226184606552</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>0.541000008583069</v>
       </c>
       <c r="G851" t="n">
-        <v>0.415666043758392</v>
+        <v>0.415666073560715</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>0.532000005245209</v>
       </c>
       <c r="G852" t="n">
-        <v>0.408751159906387</v>
+        <v>0.408751130104065</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G855" t="n">
-        <v>0.407214522361755</v>
+        <v>0.407214492559433</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>0.523000001907349</v>
       </c>
       <c r="G856" t="n">
-        <v>0.401836216449738</v>
+        <v>0.401836156845093</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>0.533999979496002</v>
       </c>
       <c r="G861" t="n">
-        <v>0.410287797451019</v>
+        <v>0.410287767648697</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>0.538999974727631</v>
       </c>
       <c r="G862" t="n">
-        <v>0.414129376411438</v>
+        <v>0.41412940621376</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>0.532000005245209</v>
       </c>
       <c r="G866" t="n">
-        <v>0.408751159906387</v>
+        <v>0.408751130104065</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G869" t="n">
-        <v>0.411056160926819</v>
+        <v>0.411056131124496</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>0.537000000476837</v>
       </c>
       <c r="G870" t="n">
-        <v>0.412592768669128</v>
+        <v>0.412592828273773</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>0.528999984264374</v>
       </c>
       <c r="G871" t="n">
-        <v>0.406446129083633</v>
+        <v>0.406446099281311</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G873" t="n">
-        <v>0.411056160926819</v>
+        <v>0.411056131124496</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G875" t="n">
-        <v>0.407214522361755</v>
+        <v>0.407214492559433</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>0.523000001907349</v>
       </c>
       <c r="G876" t="n">
-        <v>0.401836216449738</v>
+        <v>0.401836156845093</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>0.522000014781952</v>
       </c>
       <c r="G880" t="n">
-        <v>0.40106788277626</v>
+        <v>0.401067852973938</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>0.515999972820282</v>
       </c>
       <c r="G881" t="n">
-        <v>0.396457880735397</v>
+        <v>0.396457850933075</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>0.532000005245209</v>
       </c>
       <c r="G882" t="n">
-        <v>0.408751159906387</v>
+        <v>0.408751130104065</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>0.528999984264374</v>
       </c>
       <c r="G883" t="n">
-        <v>0.406446129083633</v>
+        <v>0.406446099281311</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>0.522000014781952</v>
       </c>
       <c r="G884" t="n">
-        <v>0.40106788277626</v>
+        <v>0.401067852973938</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>0.51800000667572</v>
       </c>
       <c r="G885" t="n">
-        <v>0.397994548082352</v>
+        <v>0.397994518280029</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G886" t="n">
-        <v>0.407214522361755</v>
+        <v>0.407214492559433</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>0.545000016689301</v>
       </c>
       <c r="G887" t="n">
-        <v>0.418739438056946</v>
+        <v>0.418739408254623</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G889" t="n">
-        <v>0.424117714166641</v>
+        <v>0.424117743968964</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>0.549000024795532</v>
       </c>
       <c r="G890" t="n">
-        <v>0.421812742948532</v>
+        <v>0.421812772750854</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>0.545000016689301</v>
       </c>
       <c r="G893" t="n">
-        <v>0.418739438056946</v>
+        <v>0.418739408254623</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>0.541000008583069</v>
       </c>
       <c r="G894" t="n">
-        <v>0.415666043758392</v>
+        <v>0.415666073560715</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>0.541000008583069</v>
       </c>
       <c r="G895" t="n">
-        <v>0.415666043758392</v>
+        <v>0.415666073560715</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>0.545000016689301</v>
       </c>
       <c r="G896" t="n">
-        <v>0.418739438056946</v>
+        <v>0.418739408254623</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G897" t="n">
-        <v>0.430264353752136</v>
+        <v>0.430264323949814</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G898" t="n">
-        <v>0.473290741443634</v>
+        <v>0.473290801048279</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G901" t="n">
-        <v>0.484047442674637</v>
+        <v>0.484047412872314</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G902" t="n">
-        <v>0.491730630397797</v>
+        <v>0.491730719804764</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G906" t="n">
-        <v>0.488657355308533</v>
+        <v>0.488657385110855</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G907" t="n">
-        <v>0.479437381029129</v>
+        <v>0.479437410831451</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>0.652999997138977</v>
       </c>
       <c r="G908" t="n">
-        <v>0.501718997955322</v>
+        <v>0.501718938350677</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G909" t="n">
-        <v>0.482510715723038</v>
+        <v>0.482510805130005</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G910" t="n">
-        <v>0.470217436552048</v>
+        <v>0.47021746635437</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>0.619000017642975</v>
       </c>
       <c r="G911" t="n">
-        <v>0.47559580206871</v>
+        <v>0.475595772266388</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>0.630999982357025</v>
       </c>
       <c r="G912" t="n">
-        <v>0.484815657138824</v>
+        <v>0.484815686941147</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G914" t="n">
-        <v>0.464070826768875</v>
+        <v>0.464070856571198</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G917" t="n">
-        <v>0.480974048376083</v>
+        <v>0.480974107980728</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G918" t="n">
-        <v>0.453314214944839</v>
+        <v>0.453314185142517</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G921" t="n">
-        <v>0.424117714166641</v>
+        <v>0.424117743968964</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G923" t="n">
-        <v>0.449472606182098</v>
+        <v>0.449472546577454</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>0.598999977111816</v>
       </c>
       <c r="G926" t="n">
-        <v>0.460229188203812</v>
+        <v>0.460229218006134</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G927" t="n">
-        <v>0.453314214944839</v>
+        <v>0.453314185142517</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>0.591000020503998</v>
       </c>
       <c r="G928" t="n">
-        <v>0.454082608222961</v>
+        <v>0.454082578420639</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G931" t="n">
-        <v>0.482510715723038</v>
+        <v>0.482510805130005</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G932" t="n">
-        <v>0.484047442674637</v>
+        <v>0.484047412872314</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G935" t="n">
-        <v>0.484047442674637</v>
+        <v>0.484047412872314</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>0.598999977111816</v>
       </c>
       <c r="G938" t="n">
-        <v>0.460229188203812</v>
+        <v>0.460229218006134</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G940" t="n">
-        <v>0.456387519836426</v>
+        <v>0.456387490034103</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G943" t="n">
-        <v>0.464070826768875</v>
+        <v>0.464070856571198</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>0.598999977111816</v>
       </c>
       <c r="G944" t="n">
-        <v>0.460229188203812</v>
+        <v>0.460229218006134</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G945" t="n">
-        <v>0.459460824728012</v>
+        <v>0.459460914134979</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G947" t="n">
-        <v>0.470217436552048</v>
+        <v>0.47021746635437</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>0.612999975681305</v>
       </c>
       <c r="G948" t="n">
-        <v>0.470985740423203</v>
+        <v>0.470985800027847</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G949" t="n">
-        <v>0.467144101858139</v>
+        <v>0.467144131660461</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G950" t="n">
-        <v>0.457924246788025</v>
+        <v>0.457924276590347</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>0.605000019073486</v>
       </c>
       <c r="G951" t="n">
-        <v>0.464839220046997</v>
+        <v>0.464839190244675</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>0.605000019073486</v>
       </c>
       <c r="G952" t="n">
-        <v>0.464839220046997</v>
+        <v>0.464839190244675</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G953" t="n">
-        <v>0.459460824728012</v>
+        <v>0.459460914134979</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G956" t="n">
-        <v>0.437947660684586</v>
+        <v>0.437947690486908</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G959" t="n">
-        <v>0.433337688446045</v>
+        <v>0.433337718248367</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G961" t="n">
-        <v>0.433337688446045</v>
+        <v>0.433337718248367</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>0.550999999046326</v>
       </c>
       <c r="G962" t="n">
-        <v>0.423349380493164</v>
+        <v>0.423349410295486</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G963" t="n">
-        <v>0.436411023139954</v>
+        <v>0.436410993337631</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>0.561999976634979</v>
       </c>
       <c r="G964" t="n">
-        <v>0.431801050901413</v>
+        <v>0.431801021099091</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>0.569000005722046</v>
       </c>
       <c r="G966" t="n">
-        <v>0.437179327011108</v>
+        <v>0.437179356813431</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G967" t="n">
-        <v>0.433337688446045</v>
+        <v>0.433337718248367</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G968" t="n">
-        <v>0.436411023139954</v>
+        <v>0.436410993337631</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>0.561999976634979</v>
       </c>
       <c r="G970" t="n">
-        <v>0.431801050901413</v>
+        <v>0.431801021099091</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>0.569000005722046</v>
       </c>
       <c r="G971" t="n">
-        <v>0.437179327011108</v>
+        <v>0.437179356813431</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G975" t="n">
-        <v>0.437947660684586</v>
+        <v>0.437947690486908</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G978" t="n">
-        <v>0.442557603120804</v>
+        <v>0.442557573318481</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G979" t="n">
-        <v>0.464070826768875</v>
+        <v>0.464070856571198</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G981" t="n">
-        <v>0.479437381029129</v>
+        <v>0.479437410831451</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>0.612999975681305</v>
       </c>
       <c r="G983" t="n">
-        <v>0.470985740423203</v>
+        <v>0.470985800027847</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G984" t="n">
-        <v>0.485584050416946</v>
+        <v>0.485584110021591</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>0.634999990463257</v>
       </c>
       <c r="G985" t="n">
-        <v>0.487889051437378</v>
+        <v>0.4878890812397</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G986" t="n">
-        <v>0.477900743484497</v>
+        <v>0.477900803089142</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G987" t="n">
-        <v>0.484047442674637</v>
+        <v>0.484047412872314</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>0.592999994754791</v>
       </c>
       <c r="G989" t="n">
-        <v>0.455619245767593</v>
+        <v>0.455619275569916</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G991" t="n">
-        <v>0.456387519836426</v>
+        <v>0.456387490034103</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G992" t="n">
-        <v>0.459460824728012</v>
+        <v>0.459460914134979</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G993" t="n">
-        <v>0.456387519836426</v>
+        <v>0.456387490034103</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>0.591000020503998</v>
       </c>
       <c r="G994" t="n">
-        <v>0.454082608222961</v>
+        <v>0.454082578420639</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>0.577000021934509</v>
       </c>
       <c r="G996" t="n">
-        <v>0.443325996398926</v>
+        <v>0.443326026201248</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G997" t="n">
-        <v>0.436411023139954</v>
+        <v>0.436410993337631</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G999" t="n">
-        <v>0.433337688446045</v>
+        <v>0.433337718248367</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1000" t="n">
-        <v>0.437947660684586</v>
+        <v>0.437947690486908</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>0.546000003814697</v>
       </c>
       <c r="G1003" t="n">
-        <v>0.419507801532745</v>
+        <v>0.419507771730423</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G1006" t="n">
-        <v>0.436411023139954</v>
+        <v>0.436410993337631</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G1007" t="n">
-        <v>0.433337688446045</v>
+        <v>0.433337718248367</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1008" t="n">
-        <v>0.450240910053253</v>
+        <v>0.450240939855576</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>0.569000005722046</v>
       </c>
       <c r="G1012" t="n">
-        <v>0.437179327011108</v>
+        <v>0.437179356813431</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G1013" t="n">
-        <v>0.436411023139954</v>
+        <v>0.436410993337631</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>0.561999976634979</v>
       </c>
       <c r="G1014" t="n">
-        <v>0.431801050901413</v>
+        <v>0.431801021099091</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>0.561999976634979</v>
       </c>
       <c r="G1015" t="n">
-        <v>0.431801050901413</v>
+        <v>0.431801021099091</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>0.578000009059906</v>
       </c>
       <c r="G1016" t="n">
-        <v>0.444094270467758</v>
+        <v>0.444094300270081</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>0.561999976634979</v>
       </c>
       <c r="G1020" t="n">
-        <v>0.431801050901413</v>
+        <v>0.431801021099091</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G1021" t="n">
-        <v>0.456387519836426</v>
+        <v>0.456387490034103</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G1022" t="n">
-        <v>0.464070826768875</v>
+        <v>0.464070856571198</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G1023" t="n">
-        <v>0.467144101858139</v>
+        <v>0.467144131660461</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>0.577000021934509</v>
       </c>
       <c r="G1026" t="n">
-        <v>0.443325996398926</v>
+        <v>0.443326026201248</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1028" t="n">
-        <v>0.449472606182098</v>
+        <v>0.449472546577454</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>0.561999976634979</v>
       </c>
       <c r="G1032" t="n">
-        <v>0.431801050901413</v>
+        <v>0.431801021099091</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1035" t="n">
-        <v>0.407214522361755</v>
+        <v>0.407214492559433</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>0.513000011444092</v>
       </c>
       <c r="G1036" t="n">
-        <v>0.394152879714966</v>
+        <v>0.394152939319611</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>0.524999976158142</v>
       </c>
       <c r="G1040" t="n">
-        <v>0.403372824192047</v>
+        <v>0.40337285399437</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>0.538999974727631</v>
       </c>
       <c r="G1041" t="n">
-        <v>0.414129376411438</v>
+        <v>0.41412940621376</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>0.517000019550323</v>
       </c>
       <c r="G1042" t="n">
-        <v>0.397226214408875</v>
+        <v>0.397226184606552</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>0.51800000667572</v>
       </c>
       <c r="G1043" t="n">
-        <v>0.397994548082352</v>
+        <v>0.397994518280029</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G1045" t="n">
-        <v>0.399531185626984</v>
+        <v>0.399531155824661</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>0.523000001907349</v>
       </c>
       <c r="G1047" t="n">
-        <v>0.401836216449738</v>
+        <v>0.401836156845093</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1049" t="n">
-        <v>0.407214522361755</v>
+        <v>0.407214492559433</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G1051" t="n">
-        <v>0.399531185626984</v>
+        <v>0.399531155824661</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>0.513000011444092</v>
       </c>
       <c r="G1052" t="n">
-        <v>0.394152879714966</v>
+        <v>0.394152939319611</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>0.505999982357025</v>
       </c>
       <c r="G1055" t="n">
-        <v>0.388774573802948</v>
+        <v>0.388774544000626</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>0.485000014305115</v>
       </c>
       <c r="G1056" t="n">
-        <v>0.372639685869217</v>
+        <v>0.372639715671539</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>0.471500009298325</v>
       </c>
       <c r="G1057" t="n">
-        <v>0.362267225980759</v>
+        <v>0.362267255783081</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>0.391999989748001</v>
       </c>
       <c r="G1062" t="n">
-        <v>0.301185071468353</v>
+        <v>0.301185041666031</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>0.337999999523163</v>
       </c>
       <c r="G1064" t="n">
-        <v>0.259695261716843</v>
+        <v>0.259695291519165</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>0.349000006914139</v>
       </c>
       <c r="G1065" t="n">
-        <v>0.268146932125092</v>
+        <v>0.268146902322769</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>0.311500012874603</v>
       </c>
       <c r="G1066" t="n">
-        <v>0.239334538578987</v>
+        <v>0.23933456838131</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>0.314999997615814</v>
       </c>
       <c r="G1067" t="n">
-        <v>0.242023721337318</v>
+        <v>0.242023706436157</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>0.305500000715256</v>
       </c>
       <c r="G1068" t="n">
-        <v>0.234724566340446</v>
+        <v>0.234724581241608</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>0.319999992847443</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.245865315198898</v>
+        <v>0.245865359902382</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>0.347000002861023</v>
       </c>
       <c r="G1072" t="n">
-        <v>0.266610264778137</v>
+        <v>0.266610234975815</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>0.350499987602234</v>
       </c>
       <c r="G1076" t="n">
-        <v>0.269299417734146</v>
+        <v>0.269299358129501</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>0.335999995470047</v>
       </c>
       <c r="G1077" t="n">
-        <v>0.258158624172211</v>
+        <v>0.258158594369888</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>0.328000009059906</v>
       </c>
       <c r="G1079" t="n">
-        <v>0.252011954784393</v>
+        <v>0.252011984586716</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>0.315499991178513</v>
       </c>
       <c r="G1080" t="n">
-        <v>0.242407828569412</v>
+        <v>0.242407843470573</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>0.328000009059906</v>
       </c>
       <c r="G1081" t="n">
-        <v>0.252011954784393</v>
+        <v>0.252011984586716</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>0.319000005722046</v>
       </c>
       <c r="G1082" t="n">
-        <v>0.245097041130066</v>
+        <v>0.245097026228905</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>0.328000009059906</v>
       </c>
       <c r="G1083" t="n">
-        <v>0.252011954784393</v>
+        <v>0.252011984586716</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>0.331499993801117</v>
       </c>
       <c r="G1084" t="n">
-        <v>0.254701137542725</v>
+        <v>0.254701107740402</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>0.337999999523163</v>
       </c>
       <c r="G1085" t="n">
-        <v>0.259695261716843</v>
+        <v>0.259695291519165</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>0.337999999523163</v>
       </c>
       <c r="G1087" t="n">
-        <v>0.259695261716843</v>
+        <v>0.259695291519165</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>0.340000003576279</v>
       </c>
       <c r="G1089" t="n">
-        <v>0.261231899261475</v>
+        <v>0.261231929063797</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>0.34799998998642</v>
       </c>
       <c r="G1090" t="n">
-        <v>0.267378568649292</v>
+        <v>0.26737853884697</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>0.344500005245209</v>
       </c>
       <c r="G1092" t="n">
-        <v>0.264689445495605</v>
+        <v>0.264689415693283</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>0.354000002145767</v>
       </c>
       <c r="G1096" t="n">
-        <v>0.27198851108551</v>
+        <v>0.271988540887833</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>0.354999989271164</v>
       </c>
       <c r="G1101" t="n">
-        <v>0.27275687456131</v>
+        <v>0.272756904363632</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>0.350499987602234</v>
       </c>
       <c r="G1102" t="n">
-        <v>0.269299417734146</v>
+        <v>0.269299358129501</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>0.358500003814697</v>
       </c>
       <c r="G1104" t="n">
-        <v>0.275445997714996</v>
+        <v>0.275446027517319</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>0.349000006914139</v>
       </c>
       <c r="G1105" t="n">
-        <v>0.268146932125092</v>
+        <v>0.268146902322769</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>0.345999985933304</v>
       </c>
       <c r="G1107" t="n">
-        <v>0.265841901302338</v>
+        <v>0.265841871500015</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>0.335999995470047</v>
       </c>
       <c r="G1108" t="n">
-        <v>0.258158624172211</v>
+        <v>0.258158594369888</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>0.423000007867813</v>
       </c>
       <c r="G1124" t="n">
-        <v>0.325003236532211</v>
+        <v>0.325003296136856</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>0.405000001192093</v>
       </c>
       <c r="G1126" t="n">
-        <v>0.311173319816589</v>
+        <v>0.311173349618912</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>0.400499999523163</v>
       </c>
       <c r="G1127" t="n">
-        <v>0.307715833187103</v>
+        <v>0.307715862989426</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>0.39300000667572</v>
       </c>
       <c r="G1130" t="n">
-        <v>0.301953375339508</v>
+        <v>0.301953345537186</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>0.421499997377396</v>
       </c>
       <c r="G1131" t="n">
-        <v>0.323850750923157</v>
+        <v>0.323850780725479</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>0.400499999523163</v>
       </c>
       <c r="G1137" t="n">
-        <v>0.307715833187103</v>
+        <v>0.307715862989426</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>0.405000001192093</v>
       </c>
       <c r="G1138" t="n">
-        <v>0.311173319816589</v>
+        <v>0.311173349618912</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>0.398499995470047</v>
       </c>
       <c r="G1140" t="n">
-        <v>0.306179195642471</v>
+        <v>0.306179225444794</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>0.375999987125397</v>
       </c>
       <c r="G1142" t="n">
-        <v>0.288891792297363</v>
+        <v>0.288891762495041</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>0.397000014781952</v>
       </c>
       <c r="G1144" t="n">
-        <v>0.305026739835739</v>
+        <v>0.305026710033417</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>0.390500009059906</v>
       </c>
       <c r="G1146" t="n">
-        <v>0.300032585859299</v>
+        <v>0.300032556056976</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>0.390500009059906</v>
       </c>
       <c r="G1150" t="n">
-        <v>0.300032585859299</v>
+        <v>0.300032556056976</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>0.394499987363815</v>
       </c>
       <c r="G1151" t="n">
-        <v>0.303105890750885</v>
+        <v>0.303105860948563</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>0.39750000834465</v>
       </c>
       <c r="G1153" t="n">
-        <v>0.305410832166672</v>
+        <v>0.305410891771317</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G1155" t="n">
-        <v>0.307331711053848</v>
+        <v>0.307331740856171</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G1157" t="n">
-        <v>0.327308237552643</v>
+        <v>0.327308267354965</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>0.40650001168251</v>
       </c>
       <c r="G1159" t="n">
-        <v>0.312325835227966</v>
+        <v>0.312325805425644</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>0.418500006198883</v>
       </c>
       <c r="G1163" t="n">
-        <v>0.32154580950737</v>
+        <v>0.321545749902725</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>0.418999999761581</v>
       </c>
       <c r="G1166" t="n">
-        <v>0.321929901838303</v>
+        <v>0.321929931640625</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G1168" t="n">
-        <v>0.31424668431282</v>
+        <v>0.314246654510498</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>0.425000011920929</v>
       </c>
       <c r="G1170" t="n">
-        <v>0.326539903879166</v>
+        <v>0.326539933681488</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>0.420500010251999</v>
       </c>
       <c r="G1171" t="n">
-        <v>0.32308241724968</v>
+        <v>0.323082447052002</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>0.418500006198883</v>
       </c>
       <c r="G1172" t="n">
-        <v>0.32154580950737</v>
+        <v>0.321545749902725</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>0.404000014066696</v>
       </c>
       <c r="G1174" t="n">
-        <v>0.310405045747757</v>
+        <v>0.310405015945435</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>0.404000014066696</v>
       </c>
       <c r="G1178" t="n">
-        <v>0.310405045747757</v>
+        <v>0.310405015945435</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>0.397000014781952</v>
       </c>
       <c r="G1179" t="n">
-        <v>0.305026739835739</v>
+        <v>0.305026710033417</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>0.39300000667572</v>
       </c>
       <c r="G1180" t="n">
-        <v>0.301953375339508</v>
+        <v>0.301953345537186</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>0.390500009059906</v>
       </c>
       <c r="G1182" t="n">
-        <v>0.300032585859299</v>
+        <v>0.300032556056976</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>0.391499996185303</v>
       </c>
       <c r="G1183" t="n">
-        <v>0.300800859928131</v>
+        <v>0.300800889730453</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>0.390500009059906</v>
       </c>
       <c r="G1184" t="n">
-        <v>0.300032585859299</v>
+        <v>0.300032556056976</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>0.375</v>
       </c>
       <c r="G1191" t="n">
-        <v>0.288123488426208</v>
+        <v>0.288123428821564</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>0.374000012874603</v>
       </c>
       <c r="G1192" t="n">
-        <v>0.287355124950409</v>
+        <v>0.287355095148087</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>0.369500011205673</v>
       </c>
       <c r="G1196" t="n">
-        <v>0.283897638320923</v>
+        <v>0.283897668123245</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>0.372999995946884</v>
       </c>
       <c r="G1198" t="n">
-        <v>0.286586821079254</v>
+        <v>0.286586791276932</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>0.356000006198883</v>
       </c>
       <c r="G1200" t="n">
-        <v>0.273525208234787</v>
+        <v>0.273525238037109</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>0.354999989271164</v>
       </c>
       <c r="G1201" t="n">
-        <v>0.27275687456131</v>
+        <v>0.272756904363632</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>0.354999989271164</v>
       </c>
       <c r="G1202" t="n">
-        <v>0.27275687456131</v>
+        <v>0.272756904363632</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>0.344500005245209</v>
       </c>
       <c r="G1206" t="n">
-        <v>0.264689445495605</v>
+        <v>0.264689415693283</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>0.362500011920929</v>
       </c>
       <c r="G1208" t="n">
-        <v>0.278519332408905</v>
+        <v>0.278519362211227</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>0.370000004768372</v>
       </c>
       <c r="G1211" t="n">
-        <v>0.284281820058823</v>
+        <v>0.2842817902565</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>0.349000006914139</v>
       </c>
       <c r="G1216" t="n">
-        <v>0.268146932125092</v>
+        <v>0.268146902322769</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>0.344500005245209</v>
       </c>
       <c r="G1218" t="n">
-        <v>0.264689445495605</v>
+        <v>0.264689415693283</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>0.340000003576279</v>
       </c>
       <c r="G1221" t="n">
-        <v>0.261231899261475</v>
+        <v>0.261231929063797</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>0.332500010728836</v>
       </c>
       <c r="G1222" t="n">
-        <v>0.255469471216202</v>
+        <v>0.255469441413879</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>0.34850001335144</v>
       </c>
       <c r="G1230" t="n">
-        <v>0.267762780189514</v>
+        <v>0.267762750387192</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>0.368999987840652</v>
       </c>
       <c r="G1231" t="n">
-        <v>0.283513486385345</v>
+        <v>0.283513456583023</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>0.370000004768372</v>
       </c>
       <c r="G1232" t="n">
-        <v>0.284281820058823</v>
+        <v>0.2842817902565</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>0.359499990940094</v>
       </c>
       <c r="G1233" t="n">
-        <v>0.276214301586151</v>
+        <v>0.276214331388474</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>0.356000006198883</v>
       </c>
       <c r="G1234" t="n">
-        <v>0.273525208234787</v>
+        <v>0.273525238037109</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>0.354999989271164</v>
       </c>
       <c r="G1236" t="n">
-        <v>0.27275687456131</v>
+        <v>0.272756904363632</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>0.356000006198883</v>
       </c>
       <c r="G1237" t="n">
-        <v>0.273525208234787</v>
+        <v>0.273525238037109</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>0.375</v>
       </c>
       <c r="G1238" t="n">
-        <v>0.288123488426208</v>
+        <v>0.288123428821564</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>0.383500009775162</v>
       </c>
       <c r="G1239" t="n">
-        <v>0.294654220342636</v>
+        <v>0.294654250144958</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>0.388999998569489</v>
       </c>
       <c r="G1240" t="n">
-        <v>0.298880040645599</v>
+        <v>0.298880070447922</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>0.396499991416931</v>
       </c>
       <c r="G1243" t="n">
-        <v>0.304642528295517</v>
+        <v>0.304642558097839</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>0.392500013113022</v>
       </c>
       <c r="G1245" t="n">
-        <v>0.301569223403931</v>
+        <v>0.301569193601608</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>0.398499995470047</v>
       </c>
       <c r="G1246" t="n">
-        <v>0.306179195642471</v>
+        <v>0.306179225444794</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>0.399500012397766</v>
       </c>
       <c r="G1247" t="n">
-        <v>0.306947529315948</v>
+        <v>0.306947559118271</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G1253" t="n">
-        <v>0.344211518764496</v>
+        <v>0.344211488962173</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1256" t="n">
-        <v>0.345748156309128</v>
+        <v>0.345748126506805</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>0.440499991178513</v>
       </c>
       <c r="G1257" t="n">
-        <v>0.338449060916901</v>
+        <v>0.338449031114578</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>0.440499991178513</v>
       </c>
       <c r="G1258" t="n">
-        <v>0.338449060916901</v>
+        <v>0.338449031114578</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G1261" t="n">
-        <v>0.338833183050156</v>
+        <v>0.338833212852478</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>0.423000007867813</v>
       </c>
       <c r="G1263" t="n">
-        <v>0.325003236532211</v>
+        <v>0.325003296136856</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G1264" t="n">
-        <v>0.327308237552643</v>
+        <v>0.327308267354965</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>0.418999999761581</v>
       </c>
       <c r="G1266" t="n">
-        <v>0.321929901838303</v>
+        <v>0.321929931640625</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G1267" t="n">
-        <v>0.324234902858734</v>
+        <v>0.324234932661057</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G1268" t="n">
-        <v>0.324234902858734</v>
+        <v>0.324234932661057</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>0.413500010967255</v>
       </c>
       <c r="G1270" t="n">
-        <v>0.317704111337662</v>
+        <v>0.317704141139984</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G1271" t="n">
-        <v>0.324234902858734</v>
+        <v>0.324234932661057</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G1273" t="n">
-        <v>0.344211518764496</v>
+        <v>0.344211488962173</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G1274" t="n">
-        <v>0.338064819574356</v>
+        <v>0.338064879179001</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>0.438499987125397</v>
       </c>
       <c r="G1275" t="n">
-        <v>0.336912393569946</v>
+        <v>0.336912363767624</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>0.425500005483627</v>
       </c>
       <c r="G1276" t="n">
-        <v>0.326924055814743</v>
+        <v>0.326924085617065</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>0.434500008821487</v>
       </c>
       <c r="G1277" t="n">
-        <v>0.333839058876038</v>
+        <v>0.333839029073715</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>0.430500000715256</v>
       </c>
       <c r="G1278" t="n">
-        <v>0.330765753984451</v>
+        <v>0.330765724182129</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G1279" t="n">
-        <v>0.328844875097275</v>
+        <v>0.32884493470192</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>0.397000014781952</v>
       </c>
       <c r="G1288" t="n">
-        <v>0.305026739835739</v>
+        <v>0.305026710033417</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G1289" t="n">
-        <v>0.307331711053848</v>
+        <v>0.307331740856171</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>0.430500000715256</v>
       </c>
       <c r="G1292" t="n">
-        <v>0.330765753984451</v>
+        <v>0.330765724182129</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>0.438499987125397</v>
       </c>
       <c r="G1297" t="n">
-        <v>0.336912393569946</v>
+        <v>0.336912363767624</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>0.44650000333786</v>
       </c>
       <c r="G1298" t="n">
-        <v>0.343059003353119</v>
+        <v>0.343058973550797</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>0.452499985694885</v>
       </c>
       <c r="G1299" t="n">
-        <v>0.347669005393982</v>
+        <v>0.347668945789337</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>0.467500001192093</v>
       </c>
       <c r="G1300" t="n">
-        <v>0.359193950891495</v>
+        <v>0.359193921089172</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>0.46849998831749</v>
       </c>
       <c r="G1301" t="n">
-        <v>0.35996225476265</v>
+        <v>0.359962224960327</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>0.458000004291534</v>
       </c>
       <c r="G1302" t="n">
-        <v>0.351894795894623</v>
+        <v>0.3518947660923</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G1304" t="n">
-        <v>0.353431463241577</v>
+        <v>0.353431403636932</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>0.474500000476837</v>
       </c>
       <c r="G1305" t="n">
-        <v>0.36457222700119</v>
+        <v>0.364572197198868</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G1309" t="n">
-        <v>0.353431463241577</v>
+        <v>0.353431403636932</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G1310" t="n">
-        <v>0.353431463241577</v>
+        <v>0.353431403636932</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>0.479000002145767</v>
       </c>
       <c r="G1312" t="n">
-        <v>0.368029683828354</v>
+        <v>0.368029713630676</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>0.474999994039536</v>
       </c>
       <c r="G1314" t="n">
-        <v>0.364956378936768</v>
+        <v>0.364956349134445</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>0.46399998664856</v>
       </c>
       <c r="G1320" t="n">
-        <v>0.356504708528519</v>
+        <v>0.356504738330841</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>0.462500005960464</v>
       </c>
       <c r="G1321" t="n">
-        <v>0.355352282524109</v>
+        <v>0.355352252721786</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>0.462000012397766</v>
       </c>
       <c r="G1322" t="n">
-        <v>0.354968100786209</v>
+        <v>0.354968130588531</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>0.453000009059906</v>
       </c>
       <c r="G1323" t="n">
-        <v>0.348053127527237</v>
+        <v>0.348053157329559</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>0.456999987363815</v>
       </c>
       <c r="G1324" t="n">
-        <v>0.351126432418823</v>
+        <v>0.351126462221146</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>0.45100000500679</v>
       </c>
       <c r="G1328" t="n">
-        <v>0.346516460180283</v>
+        <v>0.346516489982605</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>0.456000000238419</v>
       </c>
       <c r="G1329" t="n">
-        <v>0.350358098745346</v>
+        <v>0.350358128547668</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>0.450500011444092</v>
       </c>
       <c r="G1330" t="n">
-        <v>0.346132338047028</v>
+        <v>0.346132308244705</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>0.44200000166893</v>
       </c>
       <c r="G1331" t="n">
-        <v>0.339601516723633</v>
+        <v>0.339601546525955</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>0.451999992132187</v>
       </c>
       <c r="G1332" t="n">
-        <v>0.347284764051437</v>
+        <v>0.34728479385376</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>0.474999994039536</v>
       </c>
       <c r="G1334" t="n">
-        <v>0.364956378936768</v>
+        <v>0.364956349134445</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>0.458000004291534</v>
       </c>
       <c r="G1338" t="n">
-        <v>0.351894795894623</v>
+        <v>0.3518947660923</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>0.477999985218048</v>
       </c>
       <c r="G1340" t="n">
-        <v>0.367261350154877</v>
+        <v>0.367261320352554</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>0.490500003099442</v>
       </c>
       <c r="G1341" t="n">
-        <v>0.376865446567535</v>
+        <v>0.376865476369858</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>0.493499994277954</v>
       </c>
       <c r="G1342" t="n">
-        <v>0.379170447587967</v>
+        <v>0.379170477390289</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>0.493499994277954</v>
       </c>
       <c r="G1344" t="n">
-        <v>0.379170447587967</v>
+        <v>0.379170477390289</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>0.471500009298325</v>
       </c>
       <c r="G1345" t="n">
-        <v>0.362267225980759</v>
+        <v>0.362267255783081</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>0.477999985218048</v>
       </c>
       <c r="G1349" t="n">
-        <v>0.367261350154877</v>
+        <v>0.367261320352554</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>0.474999994039536</v>
       </c>
       <c r="G1352" t="n">
-        <v>0.364956378936768</v>
+        <v>0.364956349134445</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>0.474500000476837</v>
       </c>
       <c r="G1355" t="n">
-        <v>0.36457222700119</v>
+        <v>0.364572197198868</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>0.474500000476837</v>
       </c>
       <c r="G1356" t="n">
-        <v>0.36457222700119</v>
+        <v>0.364572197198868</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>0.477999985218048</v>
       </c>
       <c r="G1360" t="n">
-        <v>0.367261350154877</v>
+        <v>0.367261320352554</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>0.485000014305115</v>
       </c>
       <c r="G1364" t="n">
-        <v>0.372639685869217</v>
+        <v>0.372639715671539</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>0.486999988555908</v>
       </c>
       <c r="G1366" t="n">
-        <v>0.374176323413849</v>
+        <v>0.374176293611526</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>0.484499990940094</v>
       </c>
       <c r="G1367" t="n">
-        <v>0.372255474328995</v>
+        <v>0.37225553393364</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>0.479000002145767</v>
       </c>
       <c r="G1373" t="n">
-        <v>0.368029683828354</v>
+        <v>0.368029713630676</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>0.48199999332428</v>
       </c>
       <c r="G1374" t="n">
-        <v>0.370334714651108</v>
+        <v>0.370334684848785</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>0.485500007867813</v>
       </c>
       <c r="G1375" t="n">
-        <v>0.373023808002472</v>
+        <v>0.373023837804794</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>0.493999987840652</v>
       </c>
       <c r="G1376" t="n">
-        <v>0.379554659128189</v>
+        <v>0.379554629325867</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>0.501999974250793</v>
       </c>
       <c r="G1378" t="n">
-        <v>0.385701268911362</v>
+        <v>0.385701239109039</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>0.510999977588654</v>
       </c>
       <c r="G1379" t="n">
-        <v>0.392616242170334</v>
+        <v>0.392616212368011</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>0.504000008106232</v>
       </c>
       <c r="G1380" t="n">
-        <v>0.387237936258316</v>
+        <v>0.387237906455994</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>0.51800000667572</v>
       </c>
       <c r="G1382" t="n">
-        <v>0.397994548082352</v>
+        <v>0.397994518280029</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G1385" t="n">
-        <v>0.430264353752136</v>
+        <v>0.430264323949814</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>0.554000020027161</v>
       </c>
       <c r="G1386" t="n">
-        <v>0.425654411315918</v>
+        <v>0.42565444111824</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>0.545000016689301</v>
       </c>
       <c r="G1387" t="n">
-        <v>0.418739438056946</v>
+        <v>0.418739408254623</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>0.533999979496002</v>
       </c>
       <c r="G1388" t="n">
-        <v>0.410287797451019</v>
+        <v>0.410287767648697</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G1389" t="n">
-        <v>0.417971074581146</v>
+        <v>0.417971044778824</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>0.545000016689301</v>
       </c>
       <c r="G1390" t="n">
-        <v>0.418739438056946</v>
+        <v>0.418739408254623</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>0.537000000476837</v>
       </c>
       <c r="G1393" t="n">
-        <v>0.412592768669128</v>
+        <v>0.412592828273773</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>0.537000000476837</v>
       </c>
       <c r="G1396" t="n">
-        <v>0.412592768669128</v>
+        <v>0.412592828273773</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>0.538999974727631</v>
       </c>
       <c r="G1397" t="n">
-        <v>0.414129376411438</v>
+        <v>0.41412940621376</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>0.550999999046326</v>
       </c>
       <c r="G1399" t="n">
-        <v>0.423349380493164</v>
+        <v>0.423349410295486</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G1400" t="n">
-        <v>0.417971074581146</v>
+        <v>0.417971044778824</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>0.528999984264374</v>
       </c>
       <c r="G1401" t="n">
-        <v>0.406446129083633</v>
+        <v>0.406446099281311</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>0.528999984264374</v>
       </c>
       <c r="G1402" t="n">
-        <v>0.406446129083633</v>
+        <v>0.406446099281311</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>0.533999979496002</v>
       </c>
       <c r="G1403" t="n">
-        <v>0.410287797451019</v>
+        <v>0.410287767648697</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>0.538999974727631</v>
       </c>
       <c r="G1404" t="n">
-        <v>0.414129376411438</v>
+        <v>0.41412940621376</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>0.510999977588654</v>
       </c>
       <c r="G1406" t="n">
-        <v>0.392616242170334</v>
+        <v>0.392616212368011</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>0.485000014305115</v>
       </c>
       <c r="G1409" t="n">
-        <v>0.372639685869217</v>
+        <v>0.372639715671539</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>0.474500000476837</v>
       </c>
       <c r="G1410" t="n">
-        <v>0.36457222700119</v>
+        <v>0.364572197198868</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>0.493499994277954</v>
       </c>
       <c r="G1411" t="n">
-        <v>0.379170447587967</v>
+        <v>0.379170477390289</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>0.504000008106232</v>
       </c>
       <c r="G1416" t="n">
-        <v>0.387237936258316</v>
+        <v>0.387237906455994</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>0.505999982357025</v>
       </c>
       <c r="G1417" t="n">
-        <v>0.388774573802948</v>
+        <v>0.388774544000626</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>0.504000008106232</v>
       </c>
       <c r="G1419" t="n">
-        <v>0.387237936258316</v>
+        <v>0.387237906455994</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>0.501999974250793</v>
       </c>
       <c r="G1421" t="n">
-        <v>0.385701268911362</v>
+        <v>0.385701239109039</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>0.498499989509583</v>
       </c>
       <c r="G1423" t="n">
-        <v>0.38301208615303</v>
+        <v>0.383012115955353</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>0.491499990224838</v>
       </c>
       <c r="G1425" t="n">
-        <v>0.377633810043335</v>
+        <v>0.377633780241013</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>0.495999991893768</v>
       </c>
       <c r="G1429" t="n">
-        <v>0.381091326475143</v>
+        <v>0.381091296672821</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>0.467500001192093</v>
       </c>
       <c r="G1432" t="n">
-        <v>0.359193950891495</v>
+        <v>0.359193921089172</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>0.451999992132187</v>
       </c>
       <c r="G1434" t="n">
-        <v>0.347284764051437</v>
+        <v>0.34728479385376</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>0.470999985933304</v>
       </c>
       <c r="G1439" t="n">
-        <v>0.361883044242859</v>
+        <v>0.361883074045181</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>0.474500000476837</v>
       </c>
       <c r="G1441" t="n">
-        <v>0.36457222700119</v>
+        <v>0.364572197198868</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>0.545000016689301</v>
       </c>
       <c r="G1443" t="n">
-        <v>0.418739438056946</v>
+        <v>0.418739408254623</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1444" t="n">
-        <v>0.437947660684586</v>
+        <v>0.437947690486908</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>0.549000024795532</v>
       </c>
       <c r="G1446" t="n">
-        <v>0.421812742948532</v>
+        <v>0.421812772750854</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>0.537000000476837</v>
       </c>
       <c r="G1447" t="n">
-        <v>0.412592768669128</v>
+        <v>0.412592828273773</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>0.528999984264374</v>
       </c>
       <c r="G1448" t="n">
-        <v>0.406446129083633</v>
+        <v>0.406446099281311</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>0.521000027656555</v>
       </c>
       <c r="G1449" t="n">
-        <v>0.400299549102783</v>
+        <v>0.400299519300461</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>0.524999976158142</v>
       </c>
       <c r="G1450" t="n">
-        <v>0.403372824192047</v>
+        <v>0.40337285399437</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G1451" t="n">
-        <v>0.399531185626984</v>
+        <v>0.399531155824661</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>0.517000019550323</v>
       </c>
       <c r="G1452" t="n">
-        <v>0.397226214408875</v>
+        <v>0.397226184606552</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>0.513000011444092</v>
       </c>
       <c r="G1456" t="n">
-        <v>0.394152879714966</v>
+        <v>0.394152939319611</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>0.51800000667572</v>
       </c>
       <c r="G1457" t="n">
-        <v>0.397994548082352</v>
+        <v>0.397994518280029</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>0.495999991893768</v>
       </c>
       <c r="G1461" t="n">
-        <v>0.381091326475143</v>
+        <v>0.381091296672821</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>0.49549999833107</v>
       </c>
       <c r="G1464" t="n">
-        <v>0.380707085132599</v>
+        <v>0.380707114934921</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>0.494500011205673</v>
       </c>
       <c r="G1465" t="n">
-        <v>0.379938781261444</v>
+        <v>0.379938811063766</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>0.545000016689301</v>
       </c>
       <c r="G1469" t="n">
-        <v>0.418739438056946</v>
+        <v>0.418739408254623</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>0.532000005245209</v>
       </c>
       <c r="G1471" t="n">
-        <v>0.408751159906387</v>
+        <v>0.408751130104065</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>0.524999976158142</v>
       </c>
       <c r="G1474" t="n">
-        <v>0.403372824192047</v>
+        <v>0.40337285399437</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>0.513000011444092</v>
       </c>
       <c r="G1475" t="n">
-        <v>0.394152879714966</v>
+        <v>0.394152939319611</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>0.521000027656555</v>
       </c>
       <c r="G1476" t="n">
-        <v>0.400299549102783</v>
+        <v>0.400299519300461</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>0.538999974727631</v>
       </c>
       <c r="G1479" t="n">
-        <v>0.414129376411438</v>
+        <v>0.41412940621376</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>0.541000008583069</v>
       </c>
       <c r="G1480" t="n">
-        <v>0.415666043758392</v>
+        <v>0.415666073560715</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>0.523000001907349</v>
       </c>
       <c r="G1482" t="n">
-        <v>0.401836216449738</v>
+        <v>0.401836156845093</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G1488" t="n">
-        <v>0.399531185626984</v>
+        <v>0.399531155824661</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>0.523000001907349</v>
       </c>
       <c r="G1489" t="n">
-        <v>0.401836216449738</v>
+        <v>0.401836156845093</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>0.533999979496002</v>
       </c>
       <c r="G1494" t="n">
-        <v>0.410287797451019</v>
+        <v>0.410287767648697</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>0.515999972820282</v>
       </c>
       <c r="G1495" t="n">
-        <v>0.396457880735397</v>
+        <v>0.396457850933075</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>0.491499990224838</v>
       </c>
       <c r="G1498" t="n">
-        <v>0.377633810043335</v>
+        <v>0.377633780241013</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>0.487500011920929</v>
       </c>
       <c r="G1501" t="n">
-        <v>0.374560475349426</v>
+        <v>0.374560505151749</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>0.479499995708466</v>
       </c>
       <c r="G1502" t="n">
-        <v>0.368413865566254</v>
+        <v>0.368413835763931</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>0.460500001907349</v>
       </c>
       <c r="G1503" t="n">
-        <v>0.353815644979477</v>
+        <v>0.353815615177155</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>0.452499985694885</v>
       </c>
       <c r="G1504" t="n">
-        <v>0.347669005393982</v>
+        <v>0.347668945789337</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>0.453000009059906</v>
       </c>
       <c r="G1505" t="n">
-        <v>0.348053127527237</v>
+        <v>0.348053157329559</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>0.46399998664856</v>
       </c>
       <c r="G1506" t="n">
-        <v>0.356504708528519</v>
+        <v>0.356504738330841</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>0.435000002384186</v>
       </c>
       <c r="G1509" t="n">
-        <v>0.334223181009293</v>
+        <v>0.334223210811615</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>0.444999992847443</v>
       </c>
       <c r="G1510" t="n">
-        <v>0.341906487941742</v>
+        <v>0.341906517744064</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G1512" t="n">
-        <v>0.33499151468277</v>
+        <v>0.334991484880447</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>0.44200000166893</v>
       </c>
       <c r="G1513" t="n">
-        <v>0.339601516723633</v>
+        <v>0.339601546525955</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G1515" t="n">
-        <v>0.329613208770752</v>
+        <v>0.329613268375397</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>0.425500005483627</v>
       </c>
       <c r="G1516" t="n">
-        <v>0.326924055814743</v>
+        <v>0.326924085617065</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G1517" t="n">
-        <v>0.338833183050156</v>
+        <v>0.338833212852478</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>0.431499987840652</v>
       </c>
       <c r="G1518" t="n">
-        <v>0.331534057855606</v>
+        <v>0.331534028053284</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>0.44200000166893</v>
       </c>
       <c r="G1522" t="n">
-        <v>0.339601516723633</v>
+        <v>0.339601546525955</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>0.442999988794327</v>
       </c>
       <c r="G1523" t="n">
-        <v>0.340369820594788</v>
+        <v>0.34036985039711</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G1524" t="n">
-        <v>0.337296485900879</v>
+        <v>0.337296515703201</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>0.442999988794327</v>
       </c>
       <c r="G1527" t="n">
-        <v>0.340369820594788</v>
+        <v>0.34036985039711</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>0.45100000500679</v>
       </c>
       <c r="G1528" t="n">
-        <v>0.346516460180283</v>
+        <v>0.346516489982605</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>0.462000012397766</v>
       </c>
       <c r="G1530" t="n">
-        <v>0.354968100786209</v>
+        <v>0.354968130588531</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>0.458000004291534</v>
       </c>
       <c r="G1531" t="n">
-        <v>0.351894795894623</v>
+        <v>0.3518947660923</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>0.456000000238419</v>
       </c>
       <c r="G1533" t="n">
-        <v>0.350358098745346</v>
+        <v>0.350358128547668</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>0.45100000500679</v>
       </c>
       <c r="G1534" t="n">
-        <v>0.346516460180283</v>
+        <v>0.346516489982605</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1536" t="n">
-        <v>0.345748156309128</v>
+        <v>0.345748126506805</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>0.452499985694885</v>
       </c>
       <c r="G1540" t="n">
-        <v>0.347669005393982</v>
+        <v>0.347668945789337</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>0.420500010251999</v>
       </c>
       <c r="G1543" t="n">
-        <v>0.32308241724968</v>
+        <v>0.323082447052002</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>0.423000007867813</v>
       </c>
       <c r="G1544" t="n">
-        <v>0.325003236532211</v>
+        <v>0.325003296136856</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>0.420500010251999</v>
       </c>
       <c r="G1545" t="n">
-        <v>0.32308241724968</v>
+        <v>0.323082447052002</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>0.423000007867813</v>
       </c>
       <c r="G1547" t="n">
-        <v>0.325003236532211</v>
+        <v>0.325003296136856</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>0.421499997377396</v>
       </c>
       <c r="G1548" t="n">
-        <v>0.323850750923157</v>
+        <v>0.323850780725479</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G1549" t="n">
-        <v>0.328844875097275</v>
+        <v>0.32884493470192</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G1558" t="n">
-        <v>0.327308237552643</v>
+        <v>0.327308267354965</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G1562" t="n">
-        <v>0.315014988183975</v>
+        <v>0.315014958381653</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>0.391499996185303</v>
       </c>
       <c r="G1565" t="n">
-        <v>0.300800859928131</v>
+        <v>0.300800889730453</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>0.400499999523163</v>
       </c>
       <c r="G1566" t="n">
-        <v>0.307715833187103</v>
+        <v>0.307715862989426</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>0.397000014781952</v>
       </c>
       <c r="G1568" t="n">
-        <v>0.305026739835739</v>
+        <v>0.305026710033417</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>0.361000001430511</v>
       </c>
       <c r="G1575" t="n">
-        <v>0.277366876602173</v>
+        <v>0.27736684679985</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41371,7 +41371,7 @@
         <v>0.381999999284744</v>
       </c>
       <c r="G1577" t="n">
-        <v>0.293501764535904</v>
+        <v>0.293501734733582</v>
       </c>
       <c r="H1577" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>0.458499997854233</v>
       </c>
       <c r="G1585" t="n">
-        <v>0.3522789478302</v>
+        <v>0.352278918027878</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41631,7 +41631,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1587" t="n">
-        <v>0.345748156309128</v>
+        <v>0.345748126506805</v>
       </c>
       <c r="H1587" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>0.44650000333786</v>
       </c>
       <c r="G1588" t="n">
-        <v>0.343059003353119</v>
+        <v>0.343058973550797</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>0.434500008821487</v>
       </c>
       <c r="G1589" t="n">
-        <v>0.333839058876038</v>
+        <v>0.333839029073715</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>0.456999987363815</v>
       </c>
       <c r="G1593" t="n">
-        <v>0.351126432418823</v>
+        <v>0.351126462221146</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>0.444999992847443</v>
       </c>
       <c r="G1594" t="n">
-        <v>0.341906487941742</v>
+        <v>0.341906517744064</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>0.465000003576279</v>
       </c>
       <c r="G1599" t="n">
-        <v>0.357273072004318</v>
+        <v>0.357273101806641</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>0.46900001168251</v>
       </c>
       <c r="G1602" t="n">
-        <v>0.360346376895905</v>
+        <v>0.360346406698227</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42047,7 +42047,7 @@
         <v>0.467999994754791</v>
       </c>
       <c r="G1603" t="n">
-        <v>0.35957807302475</v>
+        <v>0.359578102827072</v>
       </c>
       <c r="H1603" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>0.456999987363815</v>
       </c>
       <c r="G1604" t="n">
-        <v>0.351126432418823</v>
+        <v>0.351126462221146</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1605" t="n">
-        <v>0.345748156309128</v>
+        <v>0.345748126506805</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42151,7 +42151,7 @@
         <v>0.435499995946884</v>
       </c>
       <c r="G1607" t="n">
-        <v>0.334607392549515</v>
+        <v>0.334607362747192</v>
       </c>
       <c r="H1607" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>0.431499987840652</v>
       </c>
       <c r="G1608" t="n">
-        <v>0.331534057855606</v>
+        <v>0.331534028053284</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>0.442999988794327</v>
       </c>
       <c r="G1609" t="n">
-        <v>0.340369820594788</v>
+        <v>0.34036985039711</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G1610" t="n">
-        <v>0.338833183050156</v>
+        <v>0.338833212852478</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42255,7 +42255,7 @@
         <v>0.44200000166893</v>
       </c>
       <c r="G1611" t="n">
-        <v>0.339601516723633</v>
+        <v>0.339601546525955</v>
       </c>
       <c r="H1611" t="s">
         <v>8</v>
@@ -42281,7 +42281,7 @@
         <v>0.442999988794327</v>
       </c>
       <c r="G1612" t="n">
-        <v>0.340369820594788</v>
+        <v>0.34036985039711</v>
       </c>
       <c r="H1612" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>0.442999988794327</v>
       </c>
       <c r="G1614" t="n">
-        <v>0.340369820594788</v>
+        <v>0.34036985039711</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>0.42849999666214</v>
       </c>
       <c r="G1615" t="n">
-        <v>0.329229086637497</v>
+        <v>0.329229056835175</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>0.42849999666214</v>
       </c>
       <c r="G1616" t="n">
-        <v>0.329229086637497</v>
+        <v>0.329229056835175</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>0.435499995946884</v>
       </c>
       <c r="G1617" t="n">
-        <v>0.334607392549515</v>
+        <v>0.334607362747192</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>0.435499995946884</v>
       </c>
       <c r="G1618" t="n">
-        <v>0.334607392549515</v>
+        <v>0.334607362747192</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G1622" t="n">
-        <v>0.354064851999283</v>
+        <v>0.35406482219696</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42593,7 +42593,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G1624" t="n">
-        <v>0.347477555274963</v>
+        <v>0.347477585077286</v>
       </c>
       <c r="H1624" t="s">
         <v>8</v>
@@ -42697,7 +42697,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G1628" t="n">
-        <v>0.354064851999283</v>
+        <v>0.35406482219696</v>
       </c>
       <c r="H1628" t="s">
         <v>8</v>
@@ -42723,7 +42723,7 @@
         <v>0.423000007867813</v>
       </c>
       <c r="G1629" t="n">
-        <v>0.348300963640213</v>
+        <v>0.348301023244858</v>
       </c>
       <c r="H1629" t="s">
         <v>8</v>
@@ -42801,7 +42801,7 @@
         <v>0.430999994277954</v>
       </c>
       <c r="G1632" t="n">
-        <v>0.35488823056221</v>
+        <v>0.354888260364532</v>
       </c>
       <c r="H1632" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>0.425500005483627</v>
       </c>
       <c r="G1633" t="n">
-        <v>0.350359499454498</v>
+        <v>0.350359469652176</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42931,7 +42931,7 @@
         <v>0.416500002145767</v>
       </c>
       <c r="G1637" t="n">
-        <v>0.342948853969574</v>
+        <v>0.342948824167252</v>
       </c>
       <c r="H1637" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>0.414499998092651</v>
       </c>
       <c r="G1638" t="n">
-        <v>0.341302007436752</v>
+        <v>0.341302037239075</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>0.405000001192093</v>
       </c>
       <c r="G1639" t="n">
-        <v>0.333479672670364</v>
+        <v>0.333479702472687</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43009,7 +43009,7 @@
         <v>0.389499992132187</v>
       </c>
       <c r="G1640" t="n">
-        <v>0.320716828107834</v>
+        <v>0.320716857910156</v>
       </c>
       <c r="H1640" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>0.383500009775162</v>
       </c>
       <c r="G1644" t="n">
-        <v>0.315776437520981</v>
+        <v>0.315776407718658</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43295,7 +43295,7 @@
         <v>0.379000008106232</v>
       </c>
       <c r="G1651" t="n">
-        <v>0.312071084976196</v>
+        <v>0.312071055173874</v>
       </c>
       <c r="H1651" t="s">
         <v>8</v>
@@ -43373,7 +43373,7 @@
         <v>0.379000008106232</v>
       </c>
       <c r="G1654" t="n">
-        <v>0.312071084976196</v>
+        <v>0.312071055173874</v>
       </c>
       <c r="H1654" t="s">
         <v>8</v>
@@ -43529,7 +43529,7 @@
         <v>0.391999989748001</v>
       </c>
       <c r="G1660" t="n">
-        <v>0.322775393724442</v>
+        <v>0.322775363922119</v>
       </c>
       <c r="H1660" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>0.383500009775162</v>
       </c>
       <c r="G1662" t="n">
-        <v>0.315776437520981</v>
+        <v>0.315776407718658</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43607,7 +43607,7 @@
         <v>0.375499993562698</v>
       </c>
       <c r="G1663" t="n">
-        <v>0.309189140796661</v>
+        <v>0.309189170598984</v>
       </c>
       <c r="H1663" t="s">
         <v>8</v>
@@ -43659,7 +43659,7 @@
         <v>0.389999985694885</v>
       </c>
       <c r="G1665" t="n">
-        <v>0.321128576993942</v>
+        <v>0.32112854719162</v>
       </c>
       <c r="H1665" t="s">
         <v>8</v>
@@ -43711,7 +43711,7 @@
         <v>0.395000010728836</v>
       </c>
       <c r="G1667" t="n">
-        <v>0.325245589017868</v>
+        <v>0.32524561882019</v>
       </c>
       <c r="H1667" t="s">
         <v>8</v>
@@ -43789,7 +43789,7 @@
         <v>0.391999989748001</v>
       </c>
       <c r="G1670" t="n">
-        <v>0.322775393724442</v>
+        <v>0.322775363922119</v>
       </c>
       <c r="H1670" t="s">
         <v>8</v>
@@ -43893,7 +43893,7 @@
         <v>0.382999986410141</v>
       </c>
       <c r="G1674" t="n">
-        <v>0.315364718437195</v>
+        <v>0.315364688634872</v>
       </c>
       <c r="H1674" t="s">
         <v>8</v>
@@ -43997,7 +43997,7 @@
         <v>0.377000004053116</v>
       </c>
       <c r="G1678" t="n">
-        <v>0.310424327850342</v>
+        <v>0.310424298048019</v>
       </c>
       <c r="H1678" t="s">
         <v>8</v>
@@ -44023,7 +44023,7 @@
         <v>0.375499993562698</v>
       </c>
       <c r="G1679" t="n">
-        <v>0.309189140796661</v>
+        <v>0.309189170598984</v>
       </c>
       <c r="H1679" t="s">
         <v>8</v>
@@ -44049,7 +44049,7 @@
         <v>0.375499993562698</v>
       </c>
       <c r="G1680" t="n">
-        <v>0.309189140796661</v>
+        <v>0.309189170598984</v>
       </c>
       <c r="H1680" t="s">
         <v>8</v>
@@ -44075,7 +44075,7 @@
         <v>0.377000004053116</v>
       </c>
       <c r="G1681" t="n">
-        <v>0.310424327850342</v>
+        <v>0.310424298048019</v>
       </c>
       <c r="H1681" t="s">
         <v>8</v>
@@ -44127,7 +44127,7 @@
         <v>0.382499992847443</v>
       </c>
       <c r="G1683" t="n">
-        <v>0.314953029155731</v>
+        <v>0.314952999353409</v>
       </c>
       <c r="H1683" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>0.377999991178513</v>
       </c>
       <c r="G1684" t="n">
-        <v>0.311247706413269</v>
+        <v>0.311247646808624</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>0.383500009775162</v>
       </c>
       <c r="G1686" t="n">
-        <v>0.315776437520981</v>
+        <v>0.315776407718658</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44257,7 +44257,7 @@
         <v>0.389999985694885</v>
       </c>
       <c r="G1688" t="n">
-        <v>0.321128576993942</v>
+        <v>0.32112854719162</v>
       </c>
       <c r="H1688" t="s">
         <v>8</v>
@@ -44309,7 +44309,7 @@
         <v>0.384999990463257</v>
       </c>
       <c r="G1690" t="n">
-        <v>0.317011535167694</v>
+        <v>0.317011505365372</v>
       </c>
       <c r="H1690" t="s">
         <v>8</v>
@@ -44413,7 +44413,7 @@
         <v>0.382999986410141</v>
       </c>
       <c r="G1694" t="n">
-        <v>0.315364718437195</v>
+        <v>0.315364688634872</v>
       </c>
       <c r="H1694" t="s">
         <v>8</v>
@@ -44491,7 +44491,7 @@
         <v>0.379000008106232</v>
       </c>
       <c r="G1697" t="n">
-        <v>0.312071084976196</v>
+        <v>0.312071055173874</v>
       </c>
       <c r="H1697" t="s">
         <v>8</v>
@@ -44569,7 +44569,7 @@
         <v>0.382999986410141</v>
       </c>
       <c r="G1700" t="n">
-        <v>0.315364718437195</v>
+        <v>0.315364688634872</v>
       </c>
       <c r="H1700" t="s">
         <v>8</v>
@@ -44751,7 +44751,7 @@
         <v>0.382999986410141</v>
       </c>
       <c r="G1707" t="n">
-        <v>0.315364718437195</v>
+        <v>0.315364688634872</v>
       </c>
       <c r="H1707" t="s">
         <v>8</v>
@@ -44803,7 +44803,7 @@
         <v>0.377000004053116</v>
       </c>
       <c r="G1709" t="n">
-        <v>0.310424327850342</v>
+        <v>0.310424298048019</v>
       </c>
       <c r="H1709" t="s">
         <v>8</v>
@@ -44829,7 +44829,7 @@
         <v>0.370000004768372</v>
       </c>
       <c r="G1710" t="n">
-        <v>0.304660439491272</v>
+        <v>0.30466040968895</v>
       </c>
       <c r="H1710" t="s">
         <v>8</v>
@@ -44855,7 +44855,7 @@
         <v>0.375499993562698</v>
       </c>
       <c r="G1711" t="n">
-        <v>0.309189140796661</v>
+        <v>0.309189170598984</v>
       </c>
       <c r="H1711" t="s">
         <v>8</v>
@@ -44881,7 +44881,7 @@
         <v>0.375499993562698</v>
       </c>
       <c r="G1712" t="n">
-        <v>0.309189140796661</v>
+        <v>0.309189170598984</v>
       </c>
       <c r="H1712" t="s">
         <v>8</v>
@@ -44907,7 +44907,7 @@
         <v>0.375</v>
       </c>
       <c r="G1713" t="n">
-        <v>0.30877748131752</v>
+        <v>0.308777421712875</v>
       </c>
       <c r="H1713" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>0.370000004768372</v>
       </c>
       <c r="G1718" t="n">
-        <v>0.304660439491272</v>
+        <v>0.30466040968895</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45063,7 +45063,7 @@
         <v>0.370000004768372</v>
       </c>
       <c r="G1719" t="n">
-        <v>0.304660439491272</v>
+        <v>0.30466040968895</v>
       </c>
       <c r="H1719" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>0.375499993562698</v>
       </c>
       <c r="G1720" t="n">
-        <v>0.309189140796661</v>
+        <v>0.309189170598984</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45167,7 +45167,7 @@
         <v>0.372000008821487</v>
       </c>
       <c r="G1723" t="n">
-        <v>0.306307286024094</v>
+        <v>0.306307256221771</v>
       </c>
       <c r="H1723" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>0.366499990224838</v>
       </c>
       <c r="G1724" t="n">
-        <v>0.301778525114059</v>
+        <v>0.301778495311737</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45245,7 +45245,7 @@
         <v>0.370000004768372</v>
       </c>
       <c r="G1726" t="n">
-        <v>0.304660439491272</v>
+        <v>0.30466040968895</v>
       </c>
       <c r="H1726" t="s">
         <v>8</v>
@@ -45401,7 +45401,7 @@
         <v>0.370000004768372</v>
       </c>
       <c r="G1732" t="n">
-        <v>0.304660439491272</v>
+        <v>0.30466040968895</v>
       </c>
       <c r="H1732" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>0.370000004768372</v>
       </c>
       <c r="G1733" t="n">
-        <v>0.304660439491272</v>
+        <v>0.30466040968895</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45479,7 +45479,7 @@
         <v>0.366499990224838</v>
       </c>
       <c r="G1735" t="n">
-        <v>0.301778525114059</v>
+        <v>0.301778495311737</v>
       </c>
       <c r="H1735" t="s">
         <v>8</v>
@@ -45505,7 +45505,7 @@
         <v>0.375</v>
       </c>
       <c r="G1736" t="n">
-        <v>0.30877748131752</v>
+        <v>0.308777421712875</v>
       </c>
       <c r="H1736" t="s">
         <v>8</v>
@@ -45661,7 +45661,7 @@
         <v>0.395000010728836</v>
       </c>
       <c r="G1742" t="n">
-        <v>0.325245589017868</v>
+        <v>0.32524561882019</v>
       </c>
       <c r="H1742" t="s">
         <v>8</v>
@@ -45687,7 +45687,7 @@
         <v>0.398999989032745</v>
       </c>
       <c r="G1743" t="n">
-        <v>0.328539192676544</v>
+        <v>0.328539222478867</v>
       </c>
       <c r="H1743" t="s">
         <v>8</v>
@@ -45713,7 +45713,7 @@
         <v>0.414499998092651</v>
       </c>
       <c r="G1744" t="n">
-        <v>0.341302007436752</v>
+        <v>0.341302037239075</v>
       </c>
       <c r="H1744" t="s">
         <v>8</v>
@@ -45739,7 +45739,7 @@
         <v>0.418500006198883</v>
       </c>
       <c r="G1745" t="n">
-        <v>0.344595700502396</v>
+        <v>0.344595670700073</v>
       </c>
       <c r="H1745" t="s">
         <v>8</v>
@@ -45869,7 +45869,7 @@
         <v>0.416999995708466</v>
       </c>
       <c r="G1750" t="n">
-        <v>0.34336057305336</v>
+        <v>0.343360543251038</v>
       </c>
       <c r="H1750" t="s">
         <v>8</v>
@@ -45895,7 +45895,7 @@
         <v>0.408499985933304</v>
       </c>
       <c r="G1751" t="n">
-        <v>0.336361587047577</v>
+        <v>0.336361557245255</v>
       </c>
       <c r="H1751" t="s">
         <v>8</v>
@@ -45947,7 +45947,7 @@
         <v>0.407000005245209</v>
       </c>
       <c r="G1753" t="n">
-        <v>0.335126459598541</v>
+        <v>0.335126489400864</v>
       </c>
       <c r="H1753" t="s">
         <v>8</v>
@@ -45999,7 +45999,7 @@
         <v>0.435000002384186</v>
       </c>
       <c r="G1755" t="n">
-        <v>0.358181864023209</v>
+        <v>0.358181893825531</v>
       </c>
       <c r="H1755" t="s">
         <v>8</v>
@@ -46051,7 +46051,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G1757" t="n">
-        <v>0.344183951616287</v>
+        <v>0.34418398141861</v>
       </c>
       <c r="H1757" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>0.418500006198883</v>
       </c>
       <c r="G1761" t="n">
-        <v>0.344595700502396</v>
+        <v>0.344595670700073</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46207,7 +46207,7 @@
         <v>0.416500002145767</v>
       </c>
       <c r="G1763" t="n">
-        <v>0.342948853969574</v>
+        <v>0.342948824167252</v>
       </c>
       <c r="H1763" t="s">
         <v>8</v>
@@ -46285,7 +46285,7 @@
         <v>0.407999992370605</v>
       </c>
       <c r="G1766" t="n">
-        <v>0.335949867963791</v>
+        <v>0.335949897766113</v>
       </c>
       <c r="H1766" t="s">
         <v>8</v>
@@ -46311,7 +46311,7 @@
         <v>0.416999995708466</v>
       </c>
       <c r="G1767" t="n">
-        <v>0.34336057305336</v>
+        <v>0.343360543251038</v>
       </c>
       <c r="H1767" t="s">
         <v>8</v>
@@ -46337,7 +46337,7 @@
         <v>0.417499989271164</v>
       </c>
       <c r="G1768" t="n">
-        <v>0.343772202730179</v>
+        <v>0.343772232532501</v>
       </c>
       <c r="H1768" t="s">
         <v>8</v>
@@ -46389,7 +46389,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G1770" t="n">
-        <v>0.33759668469429</v>
+        <v>0.337596714496613</v>
       </c>
       <c r="H1770" t="s">
         <v>8</v>
@@ -46415,7 +46415,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G1771" t="n">
-        <v>0.340066879987717</v>
+        <v>0.340066909790039</v>
       </c>
       <c r="H1771" t="s">
         <v>8</v>
@@ -46467,7 +46467,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G1773" t="n">
-        <v>0.340066879987717</v>
+        <v>0.340066909790039</v>
       </c>
       <c r="H1773" t="s">
         <v>8</v>
@@ -46649,7 +46649,7 @@
         <v>0.395500004291534</v>
       </c>
       <c r="G1780" t="n">
-        <v>0.325657337903976</v>
+        <v>0.325657308101654</v>
       </c>
       <c r="H1780" t="s">
         <v>8</v>
@@ -46701,7 +46701,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G1782" t="n">
-        <v>0.33759668469429</v>
+        <v>0.337596714496613</v>
       </c>
       <c r="H1782" t="s">
         <v>8</v>
@@ -46727,7 +46727,7 @@
         <v>0.407000005245209</v>
       </c>
       <c r="G1783" t="n">
-        <v>0.335126459598541</v>
+        <v>0.335126489400864</v>
       </c>
       <c r="H1783" t="s">
         <v>8</v>
@@ -46779,7 +46779,7 @@
         <v>0.417499989271164</v>
       </c>
       <c r="G1785" t="n">
-        <v>0.343772202730179</v>
+        <v>0.343772232532501</v>
       </c>
       <c r="H1785" t="s">
         <v>8</v>
@@ -46831,7 +46831,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G1787" t="n">
-        <v>0.33759668469429</v>
+        <v>0.337596714496613</v>
       </c>
       <c r="H1787" t="s">
         <v>8</v>
@@ -46857,7 +46857,7 @@
         <v>0.414499998092651</v>
       </c>
       <c r="G1788" t="n">
-        <v>0.341302007436752</v>
+        <v>0.341302037239075</v>
       </c>
       <c r="H1788" t="s">
         <v>8</v>
@@ -46883,7 +46883,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G1789" t="n">
-        <v>0.33759668469429</v>
+        <v>0.337596714496613</v>
       </c>
       <c r="H1789" t="s">
         <v>8</v>
@@ -46935,7 +46935,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G1791" t="n">
-        <v>0.33759668469429</v>
+        <v>0.337596714496613</v>
       </c>
       <c r="H1791" t="s">
         <v>8</v>
@@ -47065,7 +47065,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G1796" t="n">
-        <v>0.359005212783813</v>
+        <v>0.359005242586136</v>
       </c>
       <c r="H1796" t="s">
         <v>8</v>
@@ -47091,7 +47091,7 @@
         <v>0.449499994516373</v>
       </c>
       <c r="G1797" t="n">
-        <v>0.370121270418167</v>
+        <v>0.370121240615845</v>
       </c>
       <c r="H1797" t="s">
         <v>8</v>
@@ -47143,7 +47143,7 @@
         <v>0.463499993085861</v>
       </c>
       <c r="G1799" t="n">
-        <v>0.381648987531662</v>
+        <v>0.38164895772934</v>
       </c>
       <c r="H1799" t="s">
         <v>8</v>
@@ -47195,7 +47195,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1801" t="n">
-        <v>0.395235121250153</v>
+        <v>0.395235151052475</v>
       </c>
       <c r="H1801" t="s">
         <v>8</v>
@@ -47221,7 +47221,7 @@
         <v>0.485500007867813</v>
       </c>
       <c r="G1802" t="n">
-        <v>0.399763882160187</v>
+        <v>0.399763911962509</v>
       </c>
       <c r="H1802" t="s">
         <v>8</v>
@@ -47351,7 +47351,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1807" t="n">
-        <v>0.403469234704971</v>
+        <v>0.403469264507294</v>
       </c>
       <c r="H1807" t="s">
         <v>8</v>
@@ -47533,7 +47533,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1814" t="n">
-        <v>0.395235121250153</v>
+        <v>0.395235151052475</v>
       </c>
       <c r="H1814" t="s">
         <v>8</v>
@@ -47559,7 +47559,7 @@
         <v>0.483000010251999</v>
       </c>
       <c r="G1815" t="n">
-        <v>0.397705376148224</v>
+        <v>0.397705405950546</v>
       </c>
       <c r="H1815" t="s">
         <v>8</v>
@@ -47585,7 +47585,7 @@
         <v>0.490500003099442</v>
       </c>
       <c r="G1816" t="n">
-        <v>0.403880923986435</v>
+        <v>0.403880953788757</v>
       </c>
       <c r="H1816" t="s">
         <v>8</v>
@@ -47611,7 +47611,7 @@
         <v>0.483000010251999</v>
       </c>
       <c r="G1817" t="n">
-        <v>0.397705376148224</v>
+        <v>0.397705405950546</v>
       </c>
       <c r="H1817" t="s">
         <v>8</v>
@@ -47741,7 +47741,7 @@
         <v>0.507000029087067</v>
       </c>
       <c r="G1822" t="n">
-        <v>0.417467176914215</v>
+        <v>0.417467206716537</v>
       </c>
       <c r="H1822" t="s">
         <v>8</v>
@@ -47767,7 +47767,7 @@
         <v>0.526000022888184</v>
       </c>
       <c r="G1823" t="n">
-        <v>0.433111876249313</v>
+        <v>0.433111846446991</v>
       </c>
       <c r="H1823" t="s">
         <v>8</v>
@@ -47793,7 +47793,7 @@
         <v>0.523000001907349</v>
       </c>
       <c r="G1824" t="n">
-        <v>0.430641651153564</v>
+        <v>0.430641621351242</v>
       </c>
       <c r="H1824" t="s">
         <v>8</v>
@@ -47819,7 +47819,7 @@
         <v>0.53600001335144</v>
       </c>
       <c r="G1825" t="n">
-        <v>0.441345930099487</v>
+        <v>0.441345900297165</v>
       </c>
       <c r="H1825" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>0.537999987602234</v>
       </c>
       <c r="G1827" t="n">
-        <v>0.442992746829987</v>
+        <v>0.442992717027664</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -47897,7 +47897,7 @@
         <v>0.592999994754791</v>
       </c>
       <c r="G1828" t="n">
-        <v>0.488280117511749</v>
+        <v>0.488280147314072</v>
       </c>
       <c r="H1828" t="s">
         <v>8</v>
@@ -47923,7 +47923,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1829" t="n">
-        <v>0.50392484664917</v>
+        <v>0.503924787044525</v>
       </c>
       <c r="H1829" t="s">
         <v>8</v>
@@ -47949,7 +47949,7 @@
         <v>0.648999989032745</v>
       </c>
       <c r="G1830" t="n">
-        <v>0.534390866756439</v>
+        <v>0.534390926361084</v>
       </c>
       <c r="H1830" t="s">
         <v>8</v>
@@ -47975,7 +47975,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1831" t="n">
-        <v>0.518746197223663</v>
+        <v>0.518746137619019</v>
       </c>
       <c r="H1831" t="s">
         <v>8</v>
@@ -48001,7 +48001,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1832" t="n">
-        <v>0.522039711475372</v>
+        <v>0.522039771080017</v>
       </c>
       <c r="H1832" t="s">
         <v>8</v>
@@ -48027,7 +48027,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G1833" t="n">
-        <v>0.500631153583527</v>
+        <v>0.500631213188171</v>
       </c>
       <c r="H1833" t="s">
         <v>8</v>
@@ -48105,7 +48105,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1836" t="n">
-        <v>0.485809832811356</v>
+        <v>0.485809862613678</v>
       </c>
       <c r="H1836" t="s">
         <v>8</v>
@@ -48261,7 +48261,7 @@
         <v>0.597000002861023</v>
       </c>
       <c r="G1842" t="n">
-        <v>0.491573691368103</v>
+        <v>0.491573661565781</v>
       </c>
       <c r="H1842" t="s">
         <v>8</v>
@@ -48287,7 +48287,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1843" t="n">
-        <v>0.481692880392075</v>
+        <v>0.48169282078743</v>
       </c>
       <c r="H1843" t="s">
         <v>8</v>
@@ -48339,7 +48339,7 @@
         <v>0.558000028133392</v>
       </c>
       <c r="G1845" t="n">
-        <v>0.459460884332657</v>
+        <v>0.459460914134979</v>
       </c>
       <c r="H1845" t="s">
         <v>8</v>
@@ -48365,7 +48365,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G1846" t="n">
-        <v>0.461107641458511</v>
+        <v>0.461107671260834</v>
       </c>
       <c r="H1846" t="s">
         <v>8</v>
@@ -48391,7 +48391,7 @@
         <v>0.578999996185303</v>
       </c>
       <c r="G1847" t="n">
-        <v>0.476752430200577</v>
+        <v>0.476752400398254</v>
       </c>
       <c r="H1847" t="s">
         <v>8</v>
@@ -48417,7 +48417,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1848" t="n">
-        <v>0.481692880392075</v>
+        <v>0.48169282078743</v>
       </c>
       <c r="H1848" t="s">
         <v>8</v>
@@ -48443,7 +48443,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G1849" t="n">
-        <v>0.479222655296326</v>
+        <v>0.479222625494003</v>
       </c>
       <c r="H1849" t="s">
         <v>8</v>
@@ -48469,7 +48469,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1850" t="n">
-        <v>0.477575838565826</v>
+        <v>0.477575868368149</v>
       </c>
       <c r="H1850" t="s">
         <v>8</v>
@@ -48495,7 +48495,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1851" t="n">
-        <v>0.477575838565826</v>
+        <v>0.477575868368149</v>
       </c>
       <c r="H1851" t="s">
         <v>8</v>
@@ -48521,7 +48521,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1852" t="n">
-        <v>0.485809832811356</v>
+        <v>0.485809862613678</v>
       </c>
       <c r="H1852" t="s">
         <v>8</v>
@@ -48599,7 +48599,7 @@
         <v>0.609000027179718</v>
       </c>
       <c r="G1855" t="n">
-        <v>0.501454651355743</v>
+        <v>0.501454591751099</v>
       </c>
       <c r="H1855" t="s">
         <v>8</v>
@@ -48625,7 +48625,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G1856" t="n">
-        <v>0.498984396457672</v>
+        <v>0.498984336853027</v>
       </c>
       <c r="H1856" t="s">
         <v>8</v>
@@ -48677,7 +48677,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1858" t="n">
-        <v>0.505571722984314</v>
+        <v>0.505571663379669</v>
       </c>
       <c r="H1858" t="s">
         <v>8</v>
@@ -48703,7 +48703,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G1859" t="n">
-        <v>0.490750402212143</v>
+        <v>0.490750372409821</v>
       </c>
       <c r="H1859" t="s">
         <v>8</v>
@@ -48755,7 +48755,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1861" t="n">
-        <v>0.492397099733353</v>
+        <v>0.49239718914032</v>
       </c>
       <c r="H1861" t="s">
         <v>8</v>
@@ -48781,7 +48781,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1862" t="n">
-        <v>0.482516258955002</v>
+        <v>0.482516288757324</v>
       </c>
       <c r="H1862" t="s">
         <v>8</v>
@@ -48807,7 +48807,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G1863" t="n">
-        <v>0.479222655296326</v>
+        <v>0.479222625494003</v>
       </c>
       <c r="H1863" t="s">
         <v>8</v>
@@ -48859,7 +48859,7 @@
         <v>0.580999970436096</v>
       </c>
       <c r="G1865" t="n">
-        <v>0.478399127721786</v>
+        <v>0.478399157524109</v>
       </c>
       <c r="H1865" t="s">
         <v>8</v>
@@ -48937,7 +48937,7 @@
         <v>0.572000026702881</v>
       </c>
       <c r="G1868" t="n">
-        <v>0.470988571643829</v>
+        <v>0.470988601446152</v>
       </c>
       <c r="H1868" t="s">
         <v>8</v>
@@ -48963,7 +48963,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1869" t="n">
-        <v>0.481692880392075</v>
+        <v>0.48169282078743</v>
       </c>
       <c r="H1869" t="s">
         <v>8</v>
@@ -48989,7 +48989,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G1870" t="n">
-        <v>0.490750402212143</v>
+        <v>0.490750372409821</v>
       </c>
       <c r="H1870" t="s">
         <v>8</v>
@@ -49015,7 +49015,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1871" t="n">
-        <v>0.485809832811356</v>
+        <v>0.485809862613678</v>
       </c>
       <c r="H1871" t="s">
         <v>8</v>
@@ -49041,7 +49041,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1872" t="n">
-        <v>0.492397099733353</v>
+        <v>0.49239718914032</v>
       </c>
       <c r="H1872" t="s">
         <v>8</v>
@@ -49093,7 +49093,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G1874" t="n">
-        <v>0.479222655296326</v>
+        <v>0.479222625494003</v>
       </c>
       <c r="H1874" t="s">
         <v>8</v>
@@ -49119,7 +49119,7 @@
         <v>0.570999979972839</v>
       </c>
       <c r="G1875" t="n">
-        <v>0.470165133476257</v>
+        <v>0.47016516327858</v>
       </c>
       <c r="H1875" t="s">
         <v>8</v>
@@ -49145,7 +49145,7 @@
         <v>0.558000028133392</v>
       </c>
       <c r="G1876" t="n">
-        <v>0.459460884332657</v>
+        <v>0.459460914134979</v>
       </c>
       <c r="H1876" t="s">
         <v>8</v>
@@ -49171,7 +49171,7 @@
         <v>0.564999997615814</v>
       </c>
       <c r="G1877" t="n">
-        <v>0.465224742889404</v>
+        <v>0.465224713087082</v>
       </c>
       <c r="H1877" t="s">
         <v>8</v>
@@ -49223,7 +49223,7 @@
         <v>0.569000005722046</v>
       </c>
       <c r="G1879" t="n">
-        <v>0.468518376350403</v>
+        <v>0.46851834654808</v>
       </c>
       <c r="H1879" t="s">
         <v>8</v>
@@ -71262,7 +71262,7 @@
         <v>0.53600001335144</v>
       </c>
       <c r="D2727" t="n">
-        <v>0.526000022888184</v>
+        <v>0.523999989032745</v>
       </c>
       <c r="E2727" t="n">
         <v>0.52700001001358</v>
@@ -71274,6 +71274,32 @@
         <v>0.523999989032745</v>
       </c>
       <c r="H2727" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2728">
+      <c r="A2728" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2728" t="n">
+        <v>86160</v>
+      </c>
+      <c r="C2728" t="n">
+        <v>0.523999989032745</v>
+      </c>
+      <c r="D2728" t="n">
+        <v>0.518999993801117</v>
+      </c>
+      <c r="E2728" t="n">
+        <v>0.519999980926514</v>
+      </c>
+      <c r="F2728" t="n">
+        <v>0.523999989032745</v>
+      </c>
+      <c r="G2728" t="n">
+        <v>0.523999989032745</v>
+      </c>
+      <c r="H2728" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/IMS.MI.xlsx
+++ b/data/IMS.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>0.513000011444092</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>0.526000022888184</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>101804</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>0.531000018119812</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>0.523999989032745</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>0.527999997138977</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/IMS.MI.xlsx
+++ b/data/IMS.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>0.527999997138977</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>0.52700001001358</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>89325</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>0.532999992370605</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>0.521000027656555</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>0.52700001001358</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/IMS.MI.xlsx
+++ b/data/IMS.MI.xlsx
@@ -63311,13 +63311,36 @@
         <v>0.532999992370605</v>
       </c>
       <c r="D2737" t="n">
-        <v>0.521000027656555</v>
+        <v>0.519999980926514</v>
       </c>
       <c r="E2737" t="n">
         <v>0.52700001001358</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>0.519999980926514</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>184498</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>0.528999984264374</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>0.519999980926514</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>0.523999989032745</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/IMS.MI.xlsx
+++ b/data/IMS.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>0.523999989032745</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>0.519999980926514</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>86873</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>0.528999984264374</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>0.519999980926514</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>0.524999976158142</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/IMS.MI.xlsx
+++ b/data/IMS.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>142166</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>0.523000001907349</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>0.518999993801117</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>0.522000014781952</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>0.519999980926514</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IMS.MI.xlsx
+++ b/data/IMS.MI.xlsx
@@ -421,7 +421,7 @@
         <v>0.45100000500679</v>
       </c>
       <c r="G2" t="n">
-        <v>0.333736181259155</v>
+        <v>0.333736211061478</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>0.442499995231628</v>
       </c>
       <c r="G3" t="n">
-        <v>0.32744625210762</v>
+        <v>0.327446222305298</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>0.429300010204315</v>
       </c>
       <c r="G5" t="n">
-        <v>0.317678362131119</v>
+        <v>0.317678391933441</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>0.389800012111664</v>
       </c>
       <c r="G7" t="n">
-        <v>0.288448721170425</v>
+        <v>0.288448691368103</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>0.391000002622604</v>
       </c>
       <c r="G8" t="n">
-        <v>0.289336681365967</v>
+        <v>0.289336711168289</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>0.370000004768372</v>
       </c>
       <c r="G11" t="n">
-        <v>0.273796886205673</v>
+        <v>0.273796856403351</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>0.349999994039536</v>
       </c>
       <c r="G12" t="n">
-        <v>0.258997023105621</v>
+        <v>0.258996993303299</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>0.329199999570847</v>
       </c>
       <c r="G14" t="n">
-        <v>0.243605196475983</v>
+        <v>0.243605211377144</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>0.333000004291534</v>
       </c>
       <c r="G15" t="n">
-        <v>0.246417164802551</v>
+        <v>0.246417179703712</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>0.354999989271164</v>
       </c>
       <c r="G16" t="n">
-        <v>0.262696951627731</v>
+        <v>0.262697011232376</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>0.346500009298325</v>
       </c>
       <c r="G17" t="n">
-        <v>0.256407082080841</v>
+        <v>0.256407111883163</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>0.351099997758865</v>
       </c>
       <c r="G18" t="n">
-        <v>0.259811043739319</v>
+        <v>0.259811013936996</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>0.353399991989136</v>
       </c>
       <c r="G19" t="n">
-        <v>0.261512994766235</v>
+        <v>0.261513024568558</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>0.342999994754791</v>
       </c>
       <c r="G20" t="n">
-        <v>0.253817081451416</v>
+        <v>0.253817051649094</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>0.342000007629395</v>
       </c>
       <c r="G21" t="n">
-        <v>0.253077119588852</v>
+        <v>0.25307708978653</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>0.387699991464615</v>
       </c>
       <c r="G22" t="n">
-        <v>0.286894679069519</v>
+        <v>0.286894738674164</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>0.375</v>
       </c>
       <c r="G24" t="n">
-        <v>0.277496814727783</v>
+        <v>0.277496844530106</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>0.347000002861023</v>
       </c>
       <c r="G28" t="n">
-        <v>0.25677701830864</v>
+        <v>0.256777077913284</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>0.354999989271164</v>
       </c>
       <c r="G29" t="n">
-        <v>0.262696951627731</v>
+        <v>0.262697011232376</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>0.337999999523163</v>
       </c>
       <c r="G30" t="n">
-        <v>0.250117182731628</v>
+        <v>0.250117152929306</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>0.349999994039536</v>
       </c>
       <c r="G31" t="n">
-        <v>0.258997023105621</v>
+        <v>0.258996993303299</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>0.375</v>
       </c>
       <c r="G32" t="n">
-        <v>0.277496814727783</v>
+        <v>0.277496844530106</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>0.402700006961823</v>
       </c>
       <c r="G34" t="n">
-        <v>0.297994613647461</v>
+        <v>0.297994643449783</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G35" t="n">
-        <v>0.310796469449997</v>
+        <v>0.310796439647675</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>0.410199999809265</v>
       </c>
       <c r="G36" t="n">
-        <v>0.303544491529465</v>
+        <v>0.303544521331787</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>0.411300003528595</v>
       </c>
       <c r="G37" t="n">
-        <v>0.304358541965485</v>
+        <v>0.304358512163162</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>0.418500006198883</v>
       </c>
       <c r="G39" t="n">
-        <v>0.309686481952667</v>
+        <v>0.309686452150345</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>0.407599985599518</v>
       </c>
       <c r="G40" t="n">
-        <v>0.30162051320076</v>
+        <v>0.301620543003082</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>0.432500004768372</v>
       </c>
       <c r="G43" t="n">
-        <v>0.320046365261078</v>
+        <v>0.320046335458755</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G45" t="n">
-        <v>0.315236389636993</v>
+        <v>0.315236419439316</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>0.421700000762939</v>
       </c>
       <c r="G52" t="n">
-        <v>0.312054395675659</v>
+        <v>0.312054425477982</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>0.404599994421005</v>
       </c>
       <c r="G55" t="n">
-        <v>0.299400597810745</v>
+        <v>0.299400568008423</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>0.40200001001358</v>
       </c>
       <c r="G56" t="n">
-        <v>0.297476589679718</v>
+        <v>0.297476559877396</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G57" t="n">
-        <v>0.295996606349945</v>
+        <v>0.295996636152267</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>0.396899998188019</v>
       </c>
       <c r="G58" t="n">
-        <v>0.293702632188797</v>
+        <v>0.293702661991119</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>0.402999997138977</v>
       </c>
       <c r="G59" t="n">
-        <v>0.29821652173996</v>
+        <v>0.298216581344604</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>0.402700006961823</v>
       </c>
       <c r="G60" t="n">
-        <v>0.297994613647461</v>
+        <v>0.297994643449783</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>0.387699991464615</v>
       </c>
       <c r="G61" t="n">
-        <v>0.286894679069519</v>
+        <v>0.286894738674164</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>0.374000012874603</v>
       </c>
       <c r="G63" t="n">
-        <v>0.276756823062897</v>
+        <v>0.276756852865219</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>0.370999991893768</v>
       </c>
       <c r="G64" t="n">
-        <v>0.274536818265915</v>
+        <v>0.274536848068237</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>0.368000000715256</v>
       </c>
       <c r="G65" t="n">
-        <v>0.2723169028759</v>
+        <v>0.272316873073578</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>0.365500003099442</v>
       </c>
       <c r="G67" t="n">
-        <v>0.270466923713684</v>
+        <v>0.270466893911362</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>0.362399995326996</v>
       </c>
       <c r="G69" t="n">
-        <v>0.268172919750214</v>
+        <v>0.268172949552536</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>0.363000005483627</v>
       </c>
       <c r="G70" t="n">
-        <v>0.268616914749146</v>
+        <v>0.268616944551468</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>0.36379998922348</v>
       </c>
       <c r="G71" t="n">
-        <v>0.269208908081055</v>
+        <v>0.269208878278732</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>0.372000008821487</v>
       </c>
       <c r="G72" t="n">
-        <v>0.275276869535446</v>
+        <v>0.275276839733124</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>0.375</v>
       </c>
       <c r="G73" t="n">
-        <v>0.277496814727783</v>
+        <v>0.277496844530106</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>0.375</v>
       </c>
       <c r="G74" t="n">
-        <v>0.277496814727783</v>
+        <v>0.277496844530106</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>0.39190000295639</v>
       </c>
       <c r="G76" t="n">
-        <v>0.290002673864365</v>
+        <v>0.290002644062042</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>0.416500002145767</v>
       </c>
       <c r="G78" t="n">
-        <v>0.308206468820572</v>
+        <v>0.308206498622894</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G80" t="n">
-        <v>0.318196356296539</v>
+        <v>0.318196326494217</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>0.428299993276596</v>
       </c>
       <c r="G81" t="n">
-        <v>0.31693834066391</v>
+        <v>0.316938370466232</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>0.434300005435944</v>
       </c>
       <c r="G84" t="n">
-        <v>0.321378350257874</v>
+        <v>0.321378320455551</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>0.431600004434586</v>
       </c>
       <c r="G85" t="n">
-        <v>0.319380342960358</v>
+        <v>0.319380313158035</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>0.419900000095367</v>
       </c>
       <c r="G86" t="n">
-        <v>0.310722440481186</v>
+        <v>0.310722410678864</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>0.423900008201599</v>
       </c>
       <c r="G87" t="n">
-        <v>0.313682407140732</v>
+        <v>0.313682377338409</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>0.423400014638901</v>
       </c>
       <c r="G88" t="n">
-        <v>0.313312441110611</v>
+        <v>0.313312411308289</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>0.41499999165535</v>
       </c>
       <c r="G89" t="n">
-        <v>0.307096481323242</v>
+        <v>0.307096511125565</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G92" t="n">
-        <v>0.295996606349945</v>
+        <v>0.295996636152267</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>0.415699988603592</v>
       </c>
       <c r="G93" t="n">
-        <v>0.307614475488663</v>
+        <v>0.30761444568634</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>0.412099987268448</v>
       </c>
       <c r="G94" t="n">
-        <v>0.304950475692749</v>
+        <v>0.304950505495071</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>0.412600010633469</v>
       </c>
       <c r="G97" t="n">
-        <v>0.305320471525192</v>
+        <v>0.305320531129837</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>0.399500012397766</v>
       </c>
       <c r="G98" t="n">
-        <v>0.295626610517502</v>
+        <v>0.295626640319824</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>0.409200012683868</v>
       </c>
       <c r="G100" t="n">
-        <v>0.314400315284729</v>
+        <v>0.314400345087051</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>0.414400011301041</v>
       </c>
       <c r="G103" t="n">
-        <v>0.318395614624023</v>
+        <v>0.318395644426346</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>0.414000004529953</v>
       </c>
       <c r="G108" t="n">
-        <v>0.318088293075562</v>
+        <v>0.318088322877884</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>0.418799996376038</v>
       </c>
       <c r="G111" t="n">
-        <v>0.321776241064072</v>
+        <v>0.321776270866394</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>0.416999995708466</v>
       </c>
       <c r="G112" t="n">
-        <v>0.320393234491348</v>
+        <v>0.320393264293671</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>0.392500013113022</v>
       </c>
       <c r="G115" t="n">
-        <v>0.301569223403931</v>
+        <v>0.301569253206253</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>0.389999985694885</v>
       </c>
       <c r="G117" t="n">
-        <v>0.299648374319077</v>
+        <v>0.299648344516754</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>0.414799988269806</v>
       </c>
       <c r="G122" t="n">
-        <v>0.318702906370163</v>
+        <v>0.318702936172485</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>0.40599998831749</v>
       </c>
       <c r="G125" t="n">
-        <v>0.311941653490067</v>
+        <v>0.311941683292389</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>0.40599998831749</v>
       </c>
       <c r="G127" t="n">
-        <v>0.311941653490067</v>
+        <v>0.311941683292389</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>0.399899989366531</v>
       </c>
       <c r="G131" t="n">
-        <v>0.307254821062088</v>
+        <v>0.30725485086441</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>0.399199992418289</v>
       </c>
       <c r="G132" t="n">
-        <v>0.30671700835228</v>
+        <v>0.306716978549957</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>0.396899998188019</v>
       </c>
       <c r="G139" t="n">
-        <v>0.304949849843979</v>
+        <v>0.304949879646301</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>0.399399995803833</v>
       </c>
       <c r="G141" t="n">
-        <v>0.306870698928833</v>
+        <v>0.306870669126511</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>0.389999985694885</v>
       </c>
       <c r="G143" t="n">
-        <v>0.299648374319077</v>
+        <v>0.299648344516754</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>0.392800003290176</v>
       </c>
       <c r="G144" t="n">
-        <v>0.301799684762955</v>
+        <v>0.301799714565277</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>0.395700007677078</v>
       </c>
       <c r="G145" t="n">
-        <v>0.304027855396271</v>
+        <v>0.304027885198593</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>0.390500009059906</v>
       </c>
       <c r="G146" t="n">
-        <v>0.300032585859299</v>
+        <v>0.300032556056976</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>0.406800001859665</v>
       </c>
       <c r="G148" t="n">
-        <v>0.312556326389313</v>
+        <v>0.31255629658699</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>0.405400007963181</v>
       </c>
       <c r="G150" t="n">
-        <v>0.311480671167374</v>
+        <v>0.311480700969696</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>0.384700000286102</v>
       </c>
       <c r="G155" t="n">
-        <v>0.295576244592667</v>
+        <v>0.295576214790344</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>0.38740000128746</v>
       </c>
       <c r="G157" t="n">
-        <v>0.297650724649429</v>
+        <v>0.297650694847107</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>0.387699991464615</v>
       </c>
       <c r="G158" t="n">
-        <v>0.297881186008453</v>
+        <v>0.297881245613098</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>0.387699991464615</v>
       </c>
       <c r="G159" t="n">
-        <v>0.297881186008453</v>
+        <v>0.297881245613098</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>0.389999985694885</v>
       </c>
       <c r="G162" t="n">
-        <v>0.299648374319077</v>
+        <v>0.299648344516754</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>0.391000002622604</v>
       </c>
       <c r="G163" t="n">
-        <v>0.300416707992554</v>
+        <v>0.300416767597198</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>0.390599995851517</v>
       </c>
       <c r="G165" t="n">
-        <v>0.300109386444092</v>
+        <v>0.300109416246414</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>0.402900010347366</v>
       </c>
       <c r="G170" t="n">
-        <v>0.309559851884842</v>
+        <v>0.30955982208252</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>0.394499987363815</v>
       </c>
       <c r="G171" t="n">
-        <v>0.303105890750885</v>
+        <v>0.303105860948563</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>0.396800011396408</v>
       </c>
       <c r="G175" t="n">
-        <v>0.304873019456863</v>
+        <v>0.304873049259186</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>0.39070001244545</v>
       </c>
       <c r="G178" t="n">
-        <v>0.30018624663353</v>
+        <v>0.300186216831207</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>0.36829999089241</v>
       </c>
       <c r="G183" t="n">
-        <v>0.282975614070892</v>
+        <v>0.282975643873215</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>0.379999995231628</v>
       </c>
       <c r="G184" t="n">
-        <v>0.291965126991272</v>
+        <v>0.29196509718895</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>0.379999995231628</v>
       </c>
       <c r="G186" t="n">
-        <v>0.291965126991272</v>
+        <v>0.29196509718895</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>0.370000004768372</v>
       </c>
       <c r="G192" t="n">
-        <v>0.284281849861145</v>
+        <v>0.284281820058823</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>0.374700009822845</v>
       </c>
       <c r="G193" t="n">
-        <v>0.28789296746254</v>
+        <v>0.287892997264862</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>0.381199985742569</v>
       </c>
       <c r="G195" t="n">
-        <v>0.292887061834335</v>
+        <v>0.292887091636658</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>0.382999986410141</v>
       </c>
       <c r="G201" t="n">
-        <v>0.294270068407059</v>
+        <v>0.294270098209381</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>0.379999995231628</v>
       </c>
       <c r="G202" t="n">
-        <v>0.291965126991272</v>
+        <v>0.29196509718895</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>0.379799991846085</v>
       </c>
       <c r="G203" t="n">
-        <v>0.291811436414719</v>
+        <v>0.291811406612396</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>0.379999995231628</v>
       </c>
       <c r="G211" t="n">
-        <v>0.291965126991272</v>
+        <v>0.29196509718895</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>0.374000012874603</v>
       </c>
       <c r="G212" t="n">
-        <v>0.287355124950409</v>
+        <v>0.287355154752731</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>0.379999995231628</v>
       </c>
       <c r="G213" t="n">
-        <v>0.291965126991272</v>
+        <v>0.29196509718895</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>0.370000004768372</v>
       </c>
       <c r="G218" t="n">
-        <v>0.284281849861145</v>
+        <v>0.284281820058823</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>0.358700007200241</v>
       </c>
       <c r="G220" t="n">
-        <v>0.275599718093872</v>
+        <v>0.275599658489227</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>0.351700007915497</v>
       </c>
       <c r="G221" t="n">
-        <v>0.270221382379532</v>
+        <v>0.270221412181854</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>0.354600012302399</v>
       </c>
       <c r="G222" t="n">
-        <v>0.272449553012848</v>
+        <v>0.27244958281517</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>0.360000014305115</v>
       </c>
       <c r="G228" t="n">
-        <v>0.276598483324051</v>
+        <v>0.276598513126373</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>0.352699995040894</v>
       </c>
       <c r="G229" t="n">
-        <v>0.270989716053009</v>
+        <v>0.270989686250687</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>0.360000014305115</v>
       </c>
       <c r="G230" t="n">
-        <v>0.276598483324051</v>
+        <v>0.276598513126373</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>0.349000006914139</v>
       </c>
       <c r="G234" t="n">
-        <v>0.268146902322769</v>
+        <v>0.268146872520447</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>0.344399988651276</v>
       </c>
       <c r="G236" t="n">
-        <v>0.264612555503845</v>
+        <v>0.264612585306168</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>0.345899999141693</v>
       </c>
       <c r="G237" t="n">
-        <v>0.265765070915222</v>
+        <v>0.265765100717545</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>0.341500014066696</v>
       </c>
       <c r="G238" t="n">
-        <v>0.262384444475174</v>
+        <v>0.262384474277496</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>0.348199993371964</v>
       </c>
       <c r="G239" t="n">
-        <v>0.267532199621201</v>
+        <v>0.267532229423523</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>0.354699999094009</v>
       </c>
       <c r="G243" t="n">
-        <v>0.272526413202286</v>
+        <v>0.272526353597641</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>0.360599994659424</v>
       </c>
       <c r="G246" t="n">
-        <v>0.277059555053711</v>
+        <v>0.277059525251389</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>0.365099996328354</v>
       </c>
       <c r="G248" t="n">
-        <v>0.280516982078552</v>
+        <v>0.280517041683197</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>0.360000014305115</v>
       </c>
       <c r="G250" t="n">
-        <v>0.276598483324051</v>
+        <v>0.276598513126373</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>0.360599994659424</v>
       </c>
       <c r="G251" t="n">
-        <v>0.277059555053711</v>
+        <v>0.277059525251389</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>0.362800002098083</v>
       </c>
       <c r="G253" t="n">
-        <v>0.278749853372574</v>
+        <v>0.278749823570251</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>0.360000014305115</v>
       </c>
       <c r="G256" t="n">
-        <v>0.276598483324051</v>
+        <v>0.276598513126373</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>0.369700014591217</v>
       </c>
       <c r="G257" t="n">
-        <v>0.284051299095154</v>
+        <v>0.284051328897476</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>0.377999991178513</v>
       </c>
       <c r="G260" t="n">
-        <v>0.290428429841995</v>
+        <v>0.290428459644318</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>0.383700013160706</v>
       </c>
       <c r="G261" t="n">
-        <v>0.294807910919189</v>
+        <v>0.294807940721512</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>0.389999985694885</v>
       </c>
       <c r="G262" t="n">
-        <v>0.299648374319077</v>
+        <v>0.299648344516754</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>0.370400011539459</v>
       </c>
       <c r="G266" t="n">
-        <v>0.284589171409607</v>
+        <v>0.284589141607285</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>0.377999991178513</v>
       </c>
       <c r="G267" t="n">
-        <v>0.290428429841995</v>
+        <v>0.290428459644318</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>0.378800004720688</v>
       </c>
       <c r="G268" t="n">
-        <v>0.291043102741241</v>
+        <v>0.291043132543564</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>0.382499992847443</v>
       </c>
       <c r="G269" t="n">
-        <v>0.293885946273804</v>
+        <v>0.293885916471481</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>0.379799991846085</v>
       </c>
       <c r="G271" t="n">
-        <v>0.291811436414719</v>
+        <v>0.291811406612396</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>0.381199985742569</v>
       </c>
       <c r="G272" t="n">
-        <v>0.292887061834335</v>
+        <v>0.292887091636658</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>0.37729999423027</v>
       </c>
       <c r="G277" t="n">
-        <v>0.289890646934509</v>
+        <v>0.289890617132187</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>0.372399985790253</v>
       </c>
       <c r="G278" t="n">
-        <v>0.286125808954239</v>
+        <v>0.286125779151917</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>0.368000000715256</v>
       </c>
       <c r="G280" t="n">
-        <v>0.282745152711868</v>
+        <v>0.282745122909546</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>0.367000013589859</v>
       </c>
       <c r="G282" t="n">
-        <v>0.281976789236069</v>
+        <v>0.281976819038391</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>0.359499990940094</v>
       </c>
       <c r="G283" t="n">
-        <v>0.276214331388474</v>
+        <v>0.276214301586151</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>0.356099992990494</v>
       </c>
       <c r="G284" t="n">
-        <v>0.27360200881958</v>
+        <v>0.273602038621902</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>0.351099997758865</v>
       </c>
       <c r="G285" t="n">
-        <v>0.269760400056839</v>
+        <v>0.269760370254517</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>0.358000010251999</v>
       </c>
       <c r="G286" t="n">
-        <v>0.275061875581741</v>
+        <v>0.275061845779419</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>0.36039999127388</v>
       </c>
       <c r="G290" t="n">
-        <v>0.276905864477158</v>
+        <v>0.276905834674835</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>0.357699990272522</v>
       </c>
       <c r="G293" t="n">
-        <v>0.27483132481575</v>
+        <v>0.274831354618073</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>0.365000009536743</v>
       </c>
       <c r="G295" t="n">
-        <v>0.280440151691437</v>
+        <v>0.280440181493759</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>0.361000001430511</v>
       </c>
       <c r="G297" t="n">
-        <v>0.277366816997528</v>
+        <v>0.27736684679985</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>0.361999988555908</v>
       </c>
       <c r="G298" t="n">
-        <v>0.278135180473328</v>
+        <v>0.278135150671005</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>0.36599999666214</v>
       </c>
       <c r="G299" t="n">
-        <v>0.281208515167236</v>
+        <v>0.281208485364914</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>0.367000013589859</v>
       </c>
       <c r="G300" t="n">
-        <v>0.281976789236069</v>
+        <v>0.281976819038391</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>0.36269998550415</v>
       </c>
       <c r="G301" t="n">
-        <v>0.278672993183136</v>
+        <v>0.278672963380814</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>0.367799997329712</v>
       </c>
       <c r="G302" t="n">
-        <v>0.28259152173996</v>
+        <v>0.282591491937637</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>0.363999992609024</v>
       </c>
       <c r="G306" t="n">
-        <v>0.279671847820282</v>
+        <v>0.27967181801796</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>0.368000000715256</v>
       </c>
       <c r="G310" t="n">
-        <v>0.282745152711868</v>
+        <v>0.282745122909546</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>0.369500011205673</v>
       </c>
       <c r="G311" t="n">
-        <v>0.283897668123245</v>
+        <v>0.283897697925568</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>0.36829999089241</v>
       </c>
       <c r="G312" t="n">
-        <v>0.282975614070892</v>
+        <v>0.282975643873215</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>0.371300011873245</v>
       </c>
       <c r="G313" t="n">
-        <v>0.285280644893646</v>
+        <v>0.285280615091324</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>0.38400000333786</v>
       </c>
       <c r="G315" t="n">
-        <v>0.295038402080536</v>
+        <v>0.295038431882858</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>0.382999986410141</v>
       </c>
       <c r="G316" t="n">
-        <v>0.294270068407059</v>
+        <v>0.294270098209381</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>0.423799991607666</v>
       </c>
       <c r="G320" t="n">
-        <v>0.32561793923378</v>
+        <v>0.325617909431458</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>0.412499994039536</v>
       </c>
       <c r="G323" t="n">
-        <v>0.316935807466507</v>
+        <v>0.316935777664185</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>0.403200000524521</v>
       </c>
       <c r="G325" t="n">
-        <v>0.309790343046188</v>
+        <v>0.309790313243866</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>0.407499998807907</v>
       </c>
       <c r="G328" t="n">
-        <v>0.313094139099121</v>
+        <v>0.313094168901443</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>0.407400012016296</v>
       </c>
       <c r="G329" t="n">
-        <v>0.313017338514328</v>
+        <v>0.313017308712006</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>0.377999991178513</v>
       </c>
       <c r="G333" t="n">
-        <v>0.290428429841995</v>
+        <v>0.290428459644318</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>0.384200006723404</v>
       </c>
       <c r="G335" t="n">
-        <v>0.295192092657089</v>
+        <v>0.295192062854767</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>0.38629999756813</v>
       </c>
       <c r="G336" t="n">
-        <v>0.296805560588837</v>
+        <v>0.296805530786514</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>0.390500009059906</v>
       </c>
       <c r="G338" t="n">
-        <v>0.300032585859299</v>
+        <v>0.300032556056976</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>0.388000011444092</v>
       </c>
       <c r="G340" t="n">
-        <v>0.298111766576767</v>
+        <v>0.298111736774445</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>0.408100008964539</v>
       </c>
       <c r="G342" t="n">
-        <v>0.313555151224136</v>
+        <v>0.313555181026459</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>0.396800011396408</v>
       </c>
       <c r="G343" t="n">
-        <v>0.304873019456863</v>
+        <v>0.304873049259186</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>0.418900012969971</v>
       </c>
       <c r="G349" t="n">
-        <v>0.32185310125351</v>
+        <v>0.321853131055832</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>0.406199991703033</v>
       </c>
       <c r="G354" t="n">
-        <v>0.312095314264297</v>
+        <v>0.31209534406662</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>0.407499998807907</v>
       </c>
       <c r="G355" t="n">
-        <v>0.313094139099121</v>
+        <v>0.313094168901443</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>0.408699989318848</v>
       </c>
       <c r="G356" t="n">
-        <v>0.314016163349152</v>
+        <v>0.314016133546829</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G357" t="n">
-        <v>0.31501492857933</v>
+        <v>0.315014988183975</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>0.400099992752075</v>
       </c>
       <c r="G361" t="n">
-        <v>0.307408511638641</v>
+        <v>0.307408541440964</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>0.402099996805191</v>
       </c>
       <c r="G364" t="n">
-        <v>0.308945149183273</v>
+        <v>0.308945178985596</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>0.408199995756149</v>
       </c>
       <c r="G365" t="n">
-        <v>0.313632011413574</v>
+        <v>0.313631951808929</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>0.40090000629425</v>
       </c>
       <c r="G366" t="n">
-        <v>0.30802321434021</v>
+        <v>0.308023184537888</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>0.400499999523163</v>
       </c>
       <c r="G367" t="n">
-        <v>0.307715833187103</v>
+        <v>0.307715862989426</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>0.402200013399124</v>
       </c>
       <c r="G368" t="n">
-        <v>0.309021979570389</v>
+        <v>0.309022039175034</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>0.405400007963181</v>
       </c>
       <c r="G369" t="n">
-        <v>0.311480671167374</v>
+        <v>0.311480700969696</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>0.403400003910065</v>
       </c>
       <c r="G370" t="n">
-        <v>0.309944033622742</v>
+        <v>0.309943974018097</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>0.412000000476837</v>
       </c>
       <c r="G372" t="n">
-        <v>0.31655165553093</v>
+        <v>0.316551625728607</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>0.411900013685226</v>
       </c>
       <c r="G373" t="n">
-        <v>0.316474795341492</v>
+        <v>0.316474825143814</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>0.422199994325638</v>
       </c>
       <c r="G374" t="n">
-        <v>0.324388593435287</v>
+        <v>0.324388563632965</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>0.423000007867813</v>
       </c>
       <c r="G375" t="n">
-        <v>0.325003266334534</v>
+        <v>0.325003236532211</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>0.413500010967255</v>
       </c>
       <c r="G377" t="n">
-        <v>0.317704111337662</v>
+        <v>0.317704141139984</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>0.419900000095367</v>
       </c>
       <c r="G380" t="n">
-        <v>0.322621434926987</v>
+        <v>0.322621464729309</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>0.44990000128746</v>
       </c>
       <c r="G386" t="n">
-        <v>0.34567129611969</v>
+        <v>0.345671325922012</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>0.44310000538826</v>
       </c>
       <c r="G387" t="n">
-        <v>0.340446680784225</v>
+        <v>0.340446710586548</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>0.433899998664856</v>
       </c>
       <c r="G388" t="n">
-        <v>0.3333780169487</v>
+        <v>0.333378046751022</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>0.4375</v>
       </c>
       <c r="G390" t="n">
-        <v>0.336144030094147</v>
+        <v>0.336144059896469</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>0.439599990844727</v>
       </c>
       <c r="G391" t="n">
-        <v>0.337757527828217</v>
+        <v>0.337757498025894</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>0.441100001335144</v>
       </c>
       <c r="G392" t="n">
-        <v>0.338909983634949</v>
+        <v>0.338910013437271</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>0.440100014209747</v>
       </c>
       <c r="G393" t="n">
-        <v>0.338141709566116</v>
+        <v>0.338141679763794</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>0.442099988460541</v>
       </c>
       <c r="G394" t="n">
-        <v>0.339678376913071</v>
+        <v>0.339678347110748</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>0.435499995946884</v>
       </c>
       <c r="G399" t="n">
-        <v>0.33460733294487</v>
+        <v>0.334607362747192</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>0.44200000166893</v>
       </c>
       <c r="G403" t="n">
-        <v>0.339601516723633</v>
+        <v>0.33960148692131</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>0.443699985742569</v>
       </c>
       <c r="G404" t="n">
-        <v>0.340907692909241</v>
+        <v>0.340907663106918</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>0.458999991416931</v>
       </c>
       <c r="G405" t="n">
-        <v>0.3526631295681</v>
+        <v>0.352663099765778</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>0.481499999761581</v>
       </c>
       <c r="G406" t="n">
-        <v>0.369950503110886</v>
+        <v>0.369950532913208</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>0.472499996423721</v>
       </c>
       <c r="G408" t="n">
-        <v>0.363035559654236</v>
+        <v>0.363035529851913</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>0.486900001764297</v>
       </c>
       <c r="G409" t="n">
-        <v>0.374099493026733</v>
+        <v>0.374099463224411</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>0.481000006198883</v>
       </c>
       <c r="G411" t="n">
-        <v>0.369566380977631</v>
+        <v>0.369566321372986</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>0.472600013017654</v>
       </c>
       <c r="G414" t="n">
-        <v>0.363112390041351</v>
+        <v>0.363112419843674</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>0.476700007915497</v>
       </c>
       <c r="G417" t="n">
-        <v>0.366262555122375</v>
+        <v>0.366262525320053</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>0.469999998807907</v>
       </c>
       <c r="G418" t="n">
-        <v>0.361114770174026</v>
+        <v>0.361114740371704</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>0.467500001192093</v>
       </c>
       <c r="G421" t="n">
-        <v>0.359193921089172</v>
+        <v>0.35919389128685</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>0.479699999094009</v>
       </c>
       <c r="G422" t="n">
-        <v>0.368567526340485</v>
+        <v>0.368567496538162</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>0.48879998922348</v>
       </c>
       <c r="G424" t="n">
-        <v>0.375559329986572</v>
+        <v>0.37555930018425</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>0.494899988174438</v>
       </c>
       <c r="G425" t="n">
-        <v>0.380246073007584</v>
+        <v>0.380246102809906</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>0.527999997138977</v>
       </c>
       <c r="G427" t="n">
-        <v>0.405677795410156</v>
+        <v>0.405677825212479</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>0.516499996185303</v>
       </c>
       <c r="G430" t="n">
-        <v>0.396842062473297</v>
+        <v>0.396842032670975</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G432" t="n">
-        <v>0.422581046819687</v>
+        <v>0.422581106424332</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>0.555000007152557</v>
       </c>
       <c r="G434" t="n">
-        <v>0.426422715187073</v>
+        <v>0.42642268538475</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>0.550999999046326</v>
       </c>
       <c r="G435" t="n">
-        <v>0.423349440097809</v>
+        <v>0.423349410295486</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G436" t="n">
-        <v>0.422581046819687</v>
+        <v>0.422581106424332</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G439" t="n">
-        <v>0.422581046819687</v>
+        <v>0.422581106424332</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>0.556999981403351</v>
       </c>
       <c r="G440" t="n">
-        <v>0.427959382534027</v>
+        <v>0.427959352731705</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>0.563499987125397</v>
       </c>
       <c r="G442" t="n">
-        <v>0.432953476905823</v>
+        <v>0.4329534471035</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G444" t="n">
-        <v>0.459460854530334</v>
+        <v>0.459460824728012</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>0.605499982833862</v>
       </c>
       <c r="G445" t="n">
-        <v>0.46522331237793</v>
+        <v>0.465223282575607</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>0.609499990940094</v>
       </c>
       <c r="G446" t="n">
-        <v>0.468296647071838</v>
+        <v>0.468296617269516</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>0.626500010490417</v>
       </c>
       <c r="G447" t="n">
-        <v>0.48135831952095</v>
+        <v>0.481358289718628</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G451" t="n">
-        <v>0.507097363471985</v>
+        <v>0.50709730386734</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>0.625</v>
       </c>
       <c r="G455" t="n">
-        <v>0.480205744504929</v>
+        <v>0.480205774307251</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>0.665499985218048</v>
       </c>
       <c r="G457" t="n">
-        <v>0.511323094367981</v>
+        <v>0.511323034763336</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G458" t="n">
-        <v>0.499414026737213</v>
+        <v>0.499414056539536</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G459" t="n">
-        <v>0.491730719804764</v>
+        <v>0.491730690002441</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>0.630500018596649</v>
       </c>
       <c r="G460" t="n">
-        <v>0.484431624412537</v>
+        <v>0.484431535005569</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>0.625</v>
       </c>
       <c r="G462" t="n">
-        <v>0.480205744504929</v>
+        <v>0.480205774307251</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>0.630500018596649</v>
       </c>
       <c r="G463" t="n">
-        <v>0.484431624412537</v>
+        <v>0.484431535005569</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>0.625</v>
       </c>
       <c r="G466" t="n">
-        <v>0.480205744504929</v>
+        <v>0.480205774307251</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>0.644500017166138</v>
       </c>
       <c r="G467" t="n">
-        <v>0.495188176631927</v>
+        <v>0.49518820643425</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G469" t="n">
-        <v>0.491730719804764</v>
+        <v>0.491730690002441</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G470" t="n">
-        <v>0.491730719804764</v>
+        <v>0.491730690002441</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G471" t="n">
-        <v>0.553196966648102</v>
+        <v>0.553197026252747</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>0.70550000667572</v>
       </c>
       <c r="G472" t="n">
-        <v>0.542056202888489</v>
+        <v>0.542056262493134</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>0.781000018119812</v>
       </c>
       <c r="G475" t="n">
-        <v>0.600065171718597</v>
+        <v>0.600065112113953</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G476" t="n">
-        <v>0.582393527030945</v>
+        <v>0.58239358663559</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>0.718999981880188</v>
       </c>
       <c r="G479" t="n">
-        <v>0.552428662776947</v>
+        <v>0.552428603172302</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>0.717499971389771</v>
       </c>
       <c r="G480" t="n">
-        <v>0.551276206970215</v>
+        <v>0.55127626657486</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G482" t="n">
-        <v>0.553196966648102</v>
+        <v>0.553197026252747</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>0.760999977588654</v>
       </c>
       <c r="G486" t="n">
-        <v>0.584698557853699</v>
+        <v>0.584698498249054</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>0.791499972343445</v>
       </c>
       <c r="G487" t="n">
-        <v>0.608132481575012</v>
+        <v>0.608132541179657</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G494" t="n">
-        <v>0.560880303382874</v>
+        <v>0.560880362987518</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>0.778999984264374</v>
       </c>
       <c r="G495" t="n">
-        <v>0.598528444766998</v>
+        <v>0.598528385162354</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>0.778500020503998</v>
       </c>
       <c r="G497" t="n">
-        <v>0.598144352436066</v>
+        <v>0.598144292831421</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>0.806500017642975</v>
       </c>
       <c r="G498" t="n">
-        <v>0.619657516479492</v>
+        <v>0.619657635688782</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>0.778999984264374</v>
       </c>
       <c r="G501" t="n">
-        <v>0.598528444766998</v>
+        <v>0.598528385162354</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>0.763499975204468</v>
       </c>
       <c r="G503" t="n">
-        <v>0.586619317531586</v>
+        <v>0.58661937713623</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>0.764999985694885</v>
       </c>
       <c r="G505" t="n">
-        <v>0.587771892547607</v>
+        <v>0.587771832942963</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>0.760500013828278</v>
       </c>
       <c r="G506" t="n">
-        <v>0.584314405918121</v>
+        <v>0.584314465522766</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>0.751500010490417</v>
       </c>
       <c r="G508" t="n">
-        <v>0.577399373054504</v>
+        <v>0.577399432659149</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>0.737999975681305</v>
       </c>
       <c r="G509" t="n">
-        <v>0.567026853561401</v>
+        <v>0.567026913166046</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>0.747500002384186</v>
       </c>
       <c r="G510" t="n">
-        <v>0.574326038360596</v>
+        <v>0.57432609796524</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>0.732999980449677</v>
       </c>
       <c r="G513" t="n">
-        <v>0.563185334205627</v>
+        <v>0.563185214996338</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G515" t="n">
-        <v>0.582393527030945</v>
+        <v>0.58239358663559</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G517" t="n">
-        <v>0.583930253982544</v>
+        <v>0.583930194377899</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>0.755999982357025</v>
       </c>
       <c r="G518" t="n">
-        <v>0.58085685968399</v>
+        <v>0.580856919288635</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>0.787000000476837</v>
       </c>
       <c r="G520" t="n">
-        <v>0.604675054550171</v>
+        <v>0.604674994945526</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>0.785000026226044</v>
       </c>
       <c r="G525" t="n">
-        <v>0.603138446807861</v>
+        <v>0.603138506412506</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>0.796999990940094</v>
       </c>
       <c r="G526" t="n">
-        <v>0.612358450889587</v>
+        <v>0.612358391284943</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>0.77700001001358</v>
       </c>
       <c r="G529" t="n">
-        <v>0.596991777420044</v>
+        <v>0.596991837024689</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G531" t="n">
-        <v>0.599296748638153</v>
+        <v>0.599296689033508</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>0.767000019550323</v>
       </c>
       <c r="G532" t="n">
-        <v>0.589308500289917</v>
+        <v>0.589308559894562</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>0.721000015735626</v>
       </c>
       <c r="G536" t="n">
-        <v>0.553965389728546</v>
+        <v>0.553965449333191</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>0.725000023841858</v>
       </c>
       <c r="G538" t="n">
-        <v>0.5570387840271</v>
+        <v>0.557038724422455</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G539" t="n">
-        <v>0.536293804645538</v>
+        <v>0.536293745040894</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G546" t="n">
-        <v>0.527073800563812</v>
+        <v>0.527073860168457</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G553" t="n">
-        <v>0.536293804645538</v>
+        <v>0.536293745040894</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G557" t="n">
-        <v>0.517853915691376</v>
+        <v>0.517853856086731</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G558" t="n">
-        <v>0.517853915691376</v>
+        <v>0.517853856086731</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>0.680999994277954</v>
       </c>
       <c r="G561" t="n">
-        <v>0.523232221603394</v>
+        <v>0.523232161998749</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G562" t="n">
-        <v>0.51939058303833</v>
+        <v>0.519390642642975</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>0.683000028133392</v>
       </c>
       <c r="G563" t="n">
-        <v>0.524768888950348</v>
+        <v>0.524768948554993</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G564" t="n">
-        <v>0.527073800563812</v>
+        <v>0.527073860168457</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>0.652999997138977</v>
       </c>
       <c r="G569" t="n">
-        <v>0.501718938350677</v>
+        <v>0.501718997955322</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>0.640999972820282</v>
       </c>
       <c r="G570" t="n">
-        <v>0.492499023675919</v>
+        <v>0.492498993873596</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>0.625</v>
       </c>
       <c r="G572" t="n">
-        <v>0.480205744504929</v>
+        <v>0.480205774307251</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G574" t="n">
-        <v>0.488657414913177</v>
+        <v>0.488657385110855</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G576" t="n">
-        <v>0.471754133701324</v>
+        <v>0.471754103899002</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G577" t="n">
-        <v>0.491730719804764</v>
+        <v>0.491730690002441</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>0.615000009536743</v>
       </c>
       <c r="G578" t="n">
-        <v>0.472522467374802</v>
+        <v>0.472522437572479</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G579" t="n">
-        <v>0.468680799007416</v>
+        <v>0.468680769205093</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G583" t="n">
-        <v>0.480974048376083</v>
+        <v>0.480974018573761</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>0.629000008106232</v>
       </c>
       <c r="G584" t="n">
-        <v>0.483279049396515</v>
+        <v>0.48327910900116</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>0.623000025749207</v>
       </c>
       <c r="G585" t="n">
-        <v>0.478669106960297</v>
+        <v>0.478669077157974</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G586" t="n">
-        <v>0.47021746635437</v>
+        <v>0.470217496156693</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G587" t="n">
-        <v>0.468680799007416</v>
+        <v>0.468680769205093</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>0.609000027179718</v>
       </c>
       <c r="G588" t="n">
-        <v>0.467912495136261</v>
+        <v>0.467912524938583</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G590" t="n">
-        <v>0.47021746635437</v>
+        <v>0.470217496156693</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>0.605000019073486</v>
       </c>
       <c r="G591" t="n">
-        <v>0.46483913064003</v>
+        <v>0.464839190244675</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G592" t="n">
-        <v>0.47021746635437</v>
+        <v>0.470217496156693</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>0.601000010967255</v>
       </c>
       <c r="G593" t="n">
-        <v>0.461765855550766</v>
+        <v>0.461765885353088</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>0.601000010967255</v>
       </c>
       <c r="G594" t="n">
-        <v>0.461765855550766</v>
+        <v>0.461765885353088</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>0.625</v>
       </c>
       <c r="G597" t="n">
-        <v>0.480205744504929</v>
+        <v>0.480205774307251</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G598" t="n">
-        <v>0.491730719804764</v>
+        <v>0.491730690002441</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>0.651000022888184</v>
       </c>
       <c r="G599" t="n">
-        <v>0.500182390213013</v>
+        <v>0.500182330608368</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>0.611000001430511</v>
       </c>
       <c r="G601" t="n">
-        <v>0.469449162483215</v>
+        <v>0.469449192285538</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>0.578999996185303</v>
       </c>
       <c r="G603" t="n">
-        <v>0.444862574338913</v>
+        <v>0.444862604141235</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>0.555000007152557</v>
       </c>
       <c r="G605" t="n">
-        <v>0.426422715187073</v>
+        <v>0.42642268538475</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G607" t="n">
-        <v>0.422581046819687</v>
+        <v>0.422581106424332</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G608" t="n">
-        <v>0.424117684364319</v>
+        <v>0.424117714166641</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G609" t="n">
-        <v>0.422581046819687</v>
+        <v>0.422581106424332</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G610" t="n">
-        <v>0.422581046819687</v>
+        <v>0.422581106424332</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>0.527999997138977</v>
       </c>
       <c r="G612" t="n">
-        <v>0.405677795410156</v>
+        <v>0.405677825212479</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>0.497500002384186</v>
       </c>
       <c r="G615" t="n">
-        <v>0.382243782281876</v>
+        <v>0.382243812084198</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>0.527999997138977</v>
       </c>
       <c r="G617" t="n">
-        <v>0.405677795410156</v>
+        <v>0.405677825212479</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>0.5</v>
       </c>
       <c r="G622" t="n">
-        <v>0.384164601564407</v>
+        <v>0.38416463136673</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>0.477999985218048</v>
       </c>
       <c r="G625" t="n">
-        <v>0.367261350154877</v>
+        <v>0.367261379957199</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>0.469999998807907</v>
       </c>
       <c r="G627" t="n">
-        <v>0.361114770174026</v>
+        <v>0.361114740371704</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>0.469999998807907</v>
       </c>
       <c r="G628" t="n">
-        <v>0.361114770174026</v>
+        <v>0.361114740371704</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>0.469999998807907</v>
       </c>
       <c r="G629" t="n">
-        <v>0.361114770174026</v>
+        <v>0.361114740371704</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>0.458499997854233</v>
       </c>
       <c r="G631" t="n">
-        <v>0.352278977632523</v>
+        <v>0.3522789478302</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>0.483500003814697</v>
       </c>
       <c r="G633" t="n">
-        <v>0.371487140655518</v>
+        <v>0.37148717045784</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>0.484499990940094</v>
       </c>
       <c r="G635" t="n">
-        <v>0.37225553393364</v>
+        <v>0.372255474328995</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>0.469999998807907</v>
       </c>
       <c r="G636" t="n">
-        <v>0.361114770174026</v>
+        <v>0.361114740371704</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>0.476999998092651</v>
       </c>
       <c r="G640" t="n">
-        <v>0.366493076086044</v>
+        <v>0.3664930164814</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>0.486999988555908</v>
       </c>
       <c r="G643" t="n">
-        <v>0.374176323413849</v>
+        <v>0.374176293611526</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>0.476999998092651</v>
       </c>
       <c r="G652" t="n">
-        <v>0.366493076086044</v>
+        <v>0.3664930164814</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>0.460999995470047</v>
       </c>
       <c r="G653" t="n">
-        <v>0.354199767112732</v>
+        <v>0.354199796915054</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>0.458999991416931</v>
       </c>
       <c r="G654" t="n">
-        <v>0.3526631295681</v>
+        <v>0.352663099765778</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G657" t="n">
-        <v>0.422581046819687</v>
+        <v>0.422581106424332</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G658" t="n">
-        <v>0.411056160926819</v>
+        <v>0.411056190729141</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>0.531000018119812</v>
       </c>
       <c r="G660" t="n">
-        <v>0.407982856035233</v>
+        <v>0.40798282623291</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>0.500999987125397</v>
       </c>
       <c r="G661" t="n">
-        <v>0.384932935237885</v>
+        <v>0.384932905435562</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>0.508000016212463</v>
       </c>
       <c r="G662" t="n">
-        <v>0.390311241149902</v>
+        <v>0.39031121134758</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>0.5</v>
       </c>
       <c r="G663" t="n">
-        <v>0.384164601564407</v>
+        <v>0.38416463136673</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>0.492000013589859</v>
       </c>
       <c r="G664" t="n">
-        <v>0.378017991781235</v>
+        <v>0.378018021583557</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>0.486999988555908</v>
       </c>
       <c r="G666" t="n">
-        <v>0.374176323413849</v>
+        <v>0.374176293611526</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G669" t="n">
-        <v>0.353431403636932</v>
+        <v>0.353431463241577</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>0.462000012397766</v>
       </c>
       <c r="G673" t="n">
-        <v>0.354968130588531</v>
+        <v>0.354968100786209</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>0.460999995470047</v>
       </c>
       <c r="G674" t="n">
-        <v>0.354199767112732</v>
+        <v>0.354199796915054</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>0.477999985218048</v>
       </c>
       <c r="G675" t="n">
-        <v>0.367261350154877</v>
+        <v>0.367261379957199</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>0.465000003576279</v>
       </c>
       <c r="G678" t="n">
-        <v>0.357273072004318</v>
+        <v>0.357273101806641</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>0.45550000667572</v>
       </c>
       <c r="G679" t="n">
-        <v>0.349973976612091</v>
+        <v>0.349973946809769</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>0.441500008106232</v>
       </c>
       <c r="G680" t="n">
-        <v>0.339217364788055</v>
+        <v>0.339217334985733</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>0.523000001907349</v>
       </c>
       <c r="G689" t="n">
-        <v>0.401836186647415</v>
+        <v>0.401836156845093</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>0.513000011444092</v>
       </c>
       <c r="G690" t="n">
-        <v>0.394152939319611</v>
+        <v>0.394152909517288</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>0.522000014781952</v>
       </c>
       <c r="G694" t="n">
-        <v>0.401067852973938</v>
+        <v>0.40106788277626</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>0.513000011444092</v>
       </c>
       <c r="G698" t="n">
-        <v>0.394152939319611</v>
+        <v>0.394152909517288</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>0.488999992609024</v>
       </c>
       <c r="G700" t="n">
-        <v>0.375712990760803</v>
+        <v>0.375712960958481</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>0.474500000476837</v>
       </c>
       <c r="G701" t="n">
-        <v>0.364572197198868</v>
+        <v>0.364572256803513</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>0.460999995470047</v>
       </c>
       <c r="G702" t="n">
-        <v>0.354199767112732</v>
+        <v>0.354199796915054</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>0.458499997854233</v>
       </c>
       <c r="G705" t="n">
-        <v>0.352278977632523</v>
+        <v>0.3522789478302</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G706" t="n">
-        <v>0.353431403636932</v>
+        <v>0.353431463241577</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G707" t="n">
-        <v>0.336528211832047</v>
+        <v>0.336528182029724</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>0.437000006437302</v>
       </c>
       <c r="G708" t="n">
-        <v>0.335759878158569</v>
+        <v>0.335759907960892</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G710" t="n">
-        <v>0.329613208770752</v>
+        <v>0.329613268375397</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G711" t="n">
-        <v>0.32807657122612</v>
+        <v>0.328076541423798</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G712" t="n">
-        <v>0.32807657122612</v>
+        <v>0.328076541423798</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>0.431499987840652</v>
       </c>
       <c r="G713" t="n">
-        <v>0.331534028053284</v>
+        <v>0.331534057855606</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>0.415499985218048</v>
       </c>
       <c r="G716" t="n">
-        <v>0.319240778684616</v>
+        <v>0.319240808486938</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>0.425500005483627</v>
       </c>
       <c r="G717" t="n">
-        <v>0.326924085617065</v>
+        <v>0.326924055814743</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>0.407499998807907</v>
       </c>
       <c r="G718" t="n">
-        <v>0.313094139099121</v>
+        <v>0.313094168901443</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G721" t="n">
-        <v>0.322698295116425</v>
+        <v>0.322698265314102</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>0.425500005483627</v>
       </c>
       <c r="G722" t="n">
-        <v>0.326924085617065</v>
+        <v>0.326924055814743</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>0.424499988555908</v>
       </c>
       <c r="G723" t="n">
-        <v>0.326155722141266</v>
+        <v>0.326155751943588</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>0.423000007867813</v>
       </c>
       <c r="G728" t="n">
-        <v>0.325003266334534</v>
+        <v>0.325003236532211</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G730" t="n">
-        <v>0.329613208770752</v>
+        <v>0.329613268375397</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G731" t="n">
-        <v>0.329613208770752</v>
+        <v>0.329613268375397</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G732" t="n">
-        <v>0.32807657122612</v>
+        <v>0.328076541423798</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>0.424499988555908</v>
       </c>
       <c r="G733" t="n">
-        <v>0.326155722141266</v>
+        <v>0.326155751943588</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G734" t="n">
-        <v>0.324234932661057</v>
+        <v>0.324234962463379</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>0.408499985933304</v>
       </c>
       <c r="G735" t="n">
-        <v>0.313862502574921</v>
+        <v>0.313862472772598</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>0.390500009059906</v>
       </c>
       <c r="G740" t="n">
-        <v>0.300032585859299</v>
+        <v>0.300032556056976</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>0.391000002622604</v>
       </c>
       <c r="G742" t="n">
-        <v>0.300416707992554</v>
+        <v>0.300416767597198</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>0.400499999523163</v>
       </c>
       <c r="G743" t="n">
-        <v>0.307715833187103</v>
+        <v>0.307715862989426</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>0.393999993801117</v>
       </c>
       <c r="G744" t="n">
-        <v>0.302721738815308</v>
+        <v>0.302721709012985</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>0.407499998807907</v>
       </c>
       <c r="G745" t="n">
-        <v>0.313094139099121</v>
+        <v>0.313094168901443</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G749" t="n">
-        <v>0.324234932661057</v>
+        <v>0.324234962463379</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>0.404000014066696</v>
       </c>
       <c r="G753" t="n">
-        <v>0.310405015945435</v>
+        <v>0.310404986143112</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>0.399500012397766</v>
       </c>
       <c r="G754" t="n">
-        <v>0.306947499513626</v>
+        <v>0.306947529315948</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>0.39750000834465</v>
       </c>
       <c r="G757" t="n">
-        <v>0.305410891771317</v>
+        <v>0.305410861968994</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>0.394499987363815</v>
       </c>
       <c r="G762" t="n">
-        <v>0.303105890750885</v>
+        <v>0.303105860948563</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>0.417499989271164</v>
       </c>
       <c r="G766" t="n">
-        <v>0.32077744603157</v>
+        <v>0.320777416229248</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>0.465999990701675</v>
       </c>
       <c r="G771" t="n">
-        <v>0.358041405677795</v>
+        <v>0.358041375875473</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>0.469500005245209</v>
       </c>
       <c r="G774" t="n">
-        <v>0.360730558633804</v>
+        <v>0.360730588436127</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>0.467500001192093</v>
       </c>
       <c r="G776" t="n">
-        <v>0.359193921089172</v>
+        <v>0.35919389128685</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>0.467000007629395</v>
       </c>
       <c r="G777" t="n">
-        <v>0.358809739351273</v>
+        <v>0.358809769153595</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>0.456999987363815</v>
       </c>
       <c r="G779" t="n">
-        <v>0.351126462221146</v>
+        <v>0.351126432418823</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G780" t="n">
-        <v>0.353431403636932</v>
+        <v>0.353431463241577</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>0.462999999523163</v>
       </c>
       <c r="G782" t="n">
-        <v>0.355736464262009</v>
+        <v>0.355736434459686</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G784" t="n">
-        <v>0.353431403636932</v>
+        <v>0.353431463241577</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>0.445499986410141</v>
       </c>
       <c r="G785" t="n">
-        <v>0.342290639877319</v>
+        <v>0.342290669679642</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G786" t="n">
-        <v>0.353431403636932</v>
+        <v>0.353431463241577</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>0.483999997377396</v>
       </c>
       <c r="G788" t="n">
-        <v>0.37187135219574</v>
+        <v>0.371871381998062</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>0.48199999332428</v>
       </c>
       <c r="G789" t="n">
-        <v>0.370334655046463</v>
+        <v>0.370334684848785</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>0.486999988555908</v>
       </c>
       <c r="G794" t="n">
-        <v>0.374176323413849</v>
+        <v>0.374176293611526</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>0.492000013589859</v>
       </c>
       <c r="G796" t="n">
-        <v>0.378017991781235</v>
+        <v>0.378018021583557</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>0.497500002384186</v>
       </c>
       <c r="G798" t="n">
-        <v>0.382243782281876</v>
+        <v>0.382243812084198</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>0.489499986171722</v>
       </c>
       <c r="G799" t="n">
-        <v>0.376097142696381</v>
+        <v>0.376097172498703</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>0.5</v>
       </c>
       <c r="G802" t="n">
-        <v>0.384164601564407</v>
+        <v>0.38416463136673</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>0.523000001907349</v>
       </c>
       <c r="G803" t="n">
-        <v>0.401836186647415</v>
+        <v>0.401836156845093</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>0.524999976158142</v>
       </c>
       <c r="G806" t="n">
-        <v>0.40337285399437</v>
+        <v>0.403372824192047</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>0.528999984264374</v>
       </c>
       <c r="G808" t="n">
-        <v>0.406446099281311</v>
+        <v>0.406446129083633</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>0.50900000333786</v>
       </c>
       <c r="G811" t="n">
-        <v>0.39107957482338</v>
+        <v>0.391079545021057</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>0.508000016212463</v>
       </c>
       <c r="G813" t="n">
-        <v>0.390311241149902</v>
+        <v>0.39031121134758</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>0.500999987125397</v>
       </c>
       <c r="G815" t="n">
-        <v>0.384932935237885</v>
+        <v>0.384932905435562</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>0.508000016212463</v>
       </c>
       <c r="G818" t="n">
-        <v>0.390311241149902</v>
+        <v>0.39031121134758</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>0.513000011444092</v>
       </c>
       <c r="G821" t="n">
-        <v>0.394152939319611</v>
+        <v>0.394152909517288</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>0.484499990940094</v>
       </c>
       <c r="G825" t="n">
-        <v>0.37225553393364</v>
+        <v>0.372255474328995</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>0.469999998807907</v>
       </c>
       <c r="G826" t="n">
-        <v>0.361114770174026</v>
+        <v>0.361114740371704</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>0.5</v>
       </c>
       <c r="G829" t="n">
-        <v>0.384164601564407</v>
+        <v>0.38416463136673</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>0.523000001907349</v>
       </c>
       <c r="G830" t="n">
-        <v>0.401836186647415</v>
+        <v>0.401836156845093</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G831" t="n">
-        <v>0.407214432954788</v>
+        <v>0.407214462757111</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G832" t="n">
-        <v>0.407214432954788</v>
+        <v>0.407214462757111</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>0.50900000333786</v>
       </c>
       <c r="G835" t="n">
-        <v>0.39107957482338</v>
+        <v>0.391079545021057</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>0.513999998569489</v>
       </c>
       <c r="G837" t="n">
-        <v>0.394921213388443</v>
+        <v>0.394921243190765</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G840" t="n">
-        <v>0.414897799491882</v>
+        <v>0.41489776968956</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>0.542999982833862</v>
       </c>
       <c r="G841" t="n">
-        <v>0.417202711105347</v>
+        <v>0.417202740907669</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>0.522000014781952</v>
       </c>
       <c r="G843" t="n">
-        <v>0.401067852973938</v>
+        <v>0.40106788277626</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G845" t="n">
-        <v>0.411056160926819</v>
+        <v>0.411056190729141</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>0.528999984264374</v>
       </c>
       <c r="G846" t="n">
-        <v>0.406446099281311</v>
+        <v>0.406446129083633</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>0.527999997138977</v>
       </c>
       <c r="G849" t="n">
-        <v>0.405677795410156</v>
+        <v>0.405677825212479</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G855" t="n">
-        <v>0.407214432954788</v>
+        <v>0.407214462757111</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>0.523000001907349</v>
       </c>
       <c r="G856" t="n">
-        <v>0.401836186647415</v>
+        <v>0.401836156845093</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>0.513999998569489</v>
       </c>
       <c r="G858" t="n">
-        <v>0.394921213388443</v>
+        <v>0.394921243190765</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>0.513999998569489</v>
       </c>
       <c r="G859" t="n">
-        <v>0.394921213388443</v>
+        <v>0.394921243190765</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>0.538999974727631</v>
       </c>
       <c r="G862" t="n">
-        <v>0.41412940621376</v>
+        <v>0.414129436016083</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>0.542999982833862</v>
       </c>
       <c r="G865" t="n">
-        <v>0.417202711105347</v>
+        <v>0.417202740907669</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G869" t="n">
-        <v>0.411056160926819</v>
+        <v>0.411056190729141</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>0.528999984264374</v>
       </c>
       <c r="G871" t="n">
-        <v>0.406446099281311</v>
+        <v>0.406446129083633</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>0.527999997138977</v>
       </c>
       <c r="G872" t="n">
-        <v>0.405677795410156</v>
+        <v>0.405677825212479</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G873" t="n">
-        <v>0.411056160926819</v>
+        <v>0.411056190729141</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>0.531000018119812</v>
       </c>
       <c r="G874" t="n">
-        <v>0.407982856035233</v>
+        <v>0.40798282623291</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G875" t="n">
-        <v>0.407214432954788</v>
+        <v>0.407214462757111</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>0.523000001907349</v>
       </c>
       <c r="G876" t="n">
-        <v>0.401836186647415</v>
+        <v>0.401836156845093</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>0.513999998569489</v>
       </c>
       <c r="G878" t="n">
-        <v>0.394921213388443</v>
+        <v>0.394921243190765</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>0.522000014781952</v>
       </c>
       <c r="G880" t="n">
-        <v>0.401067852973938</v>
+        <v>0.40106788277626</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>0.528999984264374</v>
       </c>
       <c r="G883" t="n">
-        <v>0.406446099281311</v>
+        <v>0.406446129083633</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>0.522000014781952</v>
       </c>
       <c r="G884" t="n">
-        <v>0.401067852973938</v>
+        <v>0.40106788277626</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G886" t="n">
-        <v>0.407214432954788</v>
+        <v>0.407214462757111</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G889" t="n">
-        <v>0.424117684364319</v>
+        <v>0.424117714166641</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>0.549000024795532</v>
       </c>
       <c r="G890" t="n">
-        <v>0.421812772750854</v>
+        <v>0.42181271314621</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G892" t="n">
-        <v>0.422581046819687</v>
+        <v>0.422581106424332</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G897" t="n">
-        <v>0.430264353752136</v>
+        <v>0.430264383554459</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G899" t="n">
-        <v>0.49480402469635</v>
+        <v>0.494803994894028</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G900" t="n">
-        <v>0.49480402469635</v>
+        <v>0.494803994894028</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G901" t="n">
-        <v>0.48404735326767</v>
+        <v>0.484047383069992</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G902" t="n">
-        <v>0.491730719804764</v>
+        <v>0.491730690002441</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G906" t="n">
-        <v>0.488657414913177</v>
+        <v>0.488657385110855</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G907" t="n">
-        <v>0.479437470436096</v>
+        <v>0.479437410831451</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>0.652999997138977</v>
       </c>
       <c r="G908" t="n">
-        <v>0.501718938350677</v>
+        <v>0.501718997955322</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G910" t="n">
-        <v>0.47021746635437</v>
+        <v>0.470217496156693</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>0.619000017642975</v>
       </c>
       <c r="G911" t="n">
-        <v>0.475595742464066</v>
+        <v>0.475595772266388</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G913" t="n">
-        <v>0.468680799007416</v>
+        <v>0.468680769205093</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G914" t="n">
-        <v>0.464070826768875</v>
+        <v>0.464070856571198</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G915" t="n">
-        <v>0.465607553720474</v>
+        <v>0.465607523918152</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G917" t="n">
-        <v>0.480974048376083</v>
+        <v>0.480974018573761</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G918" t="n">
-        <v>0.453314214944839</v>
+        <v>0.453314244747162</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G920" t="n">
-        <v>0.441789239645004</v>
+        <v>0.441789269447327</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G921" t="n">
-        <v>0.424117684364319</v>
+        <v>0.424117714166641</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G922" t="n">
-        <v>0.44563102722168</v>
+        <v>0.445630967617035</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G923" t="n">
-        <v>0.449472576379776</v>
+        <v>0.449472606182098</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>0.587000012397766</v>
       </c>
       <c r="G924" t="n">
-        <v>0.451009303331375</v>
+        <v>0.451009213924408</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>0.598999977111816</v>
       </c>
       <c r="G926" t="n">
-        <v>0.460229247808456</v>
+        <v>0.460229188203812</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G927" t="n">
-        <v>0.453314214944839</v>
+        <v>0.453314244747162</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>0.591000020503998</v>
       </c>
       <c r="G928" t="n">
-        <v>0.454082578420639</v>
+        <v>0.454082548618317</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G929" t="n">
-        <v>0.45715594291687</v>
+        <v>0.457155913114548</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G930" t="n">
-        <v>0.465607553720474</v>
+        <v>0.465607523918152</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G932" t="n">
-        <v>0.48404735326767</v>
+        <v>0.484047383069992</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G935" t="n">
-        <v>0.48404735326767</v>
+        <v>0.484047383069992</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G937" t="n">
-        <v>0.45177760720253</v>
+        <v>0.451777577400208</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>0.598999977111816</v>
       </c>
       <c r="G938" t="n">
-        <v>0.460229247808456</v>
+        <v>0.460229188203812</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G940" t="n">
-        <v>0.456387519836426</v>
+        <v>0.456387549638748</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>0.601000010967255</v>
       </c>
       <c r="G942" t="n">
-        <v>0.461765855550766</v>
+        <v>0.461765885353088</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G943" t="n">
-        <v>0.464070826768875</v>
+        <v>0.464070856571198</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>0.598999977111816</v>
       </c>
       <c r="G944" t="n">
-        <v>0.460229247808456</v>
+        <v>0.460229188203812</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G945" t="n">
-        <v>0.459460854530334</v>
+        <v>0.459460824728012</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G947" t="n">
-        <v>0.47021746635437</v>
+        <v>0.470217496156693</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G949" t="n">
-        <v>0.467144191265106</v>
+        <v>0.467144161462784</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G950" t="n">
-        <v>0.457924246788025</v>
+        <v>0.457924216985703</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>0.605000019073486</v>
       </c>
       <c r="G951" t="n">
-        <v>0.46483913064003</v>
+        <v>0.464839190244675</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>0.605000019073486</v>
       </c>
       <c r="G952" t="n">
-        <v>0.46483913064003</v>
+        <v>0.464839190244675</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G953" t="n">
-        <v>0.459460854530334</v>
+        <v>0.459460824728012</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>0.563000023365021</v>
       </c>
       <c r="G955" t="n">
-        <v>0.43256938457489</v>
+        <v>0.432569324970245</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>0.556999981403351</v>
       </c>
       <c r="G957" t="n">
-        <v>0.427959382534027</v>
+        <v>0.427959352731705</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>0.550999999046326</v>
       </c>
       <c r="G962" t="n">
-        <v>0.423349440097809</v>
+        <v>0.423349410295486</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G963" t="n">
-        <v>0.436410933732986</v>
+        <v>0.436410963535309</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G965" t="n">
-        <v>0.441789239645004</v>
+        <v>0.441789269447327</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G968" t="n">
-        <v>0.436410933732986</v>
+        <v>0.436410963535309</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G972" t="n">
-        <v>0.441020935773849</v>
+        <v>0.441020965576172</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G973" t="n">
-        <v>0.441020935773849</v>
+        <v>0.441020965576172</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G978" t="n">
-        <v>0.442557632923126</v>
+        <v>0.442557603120804</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G979" t="n">
-        <v>0.464070826768875</v>
+        <v>0.464070856571198</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>0.601000010967255</v>
       </c>
       <c r="G980" t="n">
-        <v>0.461765855550766</v>
+        <v>0.461765885353088</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G981" t="n">
-        <v>0.479437470436096</v>
+        <v>0.479437410831451</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G982" t="n">
-        <v>0.468680799007416</v>
+        <v>0.468680769205093</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G984" t="n">
-        <v>0.485584110021591</v>
+        <v>0.485584050416946</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G987" t="n">
-        <v>0.48404735326767</v>
+        <v>0.484047383069992</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G988" t="n">
-        <v>0.468680799007416</v>
+        <v>0.468680769205093</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>0.592999994754791</v>
       </c>
       <c r="G989" t="n">
-        <v>0.455619186162949</v>
+        <v>0.455619245767593</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G990" t="n">
-        <v>0.45715594291687</v>
+        <v>0.457155913114548</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G991" t="n">
-        <v>0.456387519836426</v>
+        <v>0.456387549638748</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G992" t="n">
-        <v>0.459460854530334</v>
+        <v>0.459460824728012</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G993" t="n">
-        <v>0.456387519836426</v>
+        <v>0.456387549638748</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>0.591000020503998</v>
       </c>
       <c r="G994" t="n">
-        <v>0.454082578420639</v>
+        <v>0.454082548618317</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G995" t="n">
-        <v>0.45715594291687</v>
+        <v>0.457155913114548</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G997" t="n">
-        <v>0.436410933732986</v>
+        <v>0.436410963535309</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>0.559000015258789</v>
       </c>
       <c r="G998" t="n">
-        <v>0.429496079683304</v>
+        <v>0.429496049880981</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>0.556999981403351</v>
       </c>
       <c r="G1002" t="n">
-        <v>0.427959382534027</v>
+        <v>0.427959352731705</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G1006" t="n">
-        <v>0.436410933732986</v>
+        <v>0.436410963535309</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1008" t="n">
-        <v>0.450240910053253</v>
+        <v>0.450240939855576</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G1009" t="n">
-        <v>0.45177760720253</v>
+        <v>0.451777577400208</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1010" t="n">
-        <v>0.44563102722168</v>
+        <v>0.445630967617035</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G1013" t="n">
-        <v>0.436410933732986</v>
+        <v>0.436410963535309</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G1021" t="n">
-        <v>0.456387519836426</v>
+        <v>0.456387549638748</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G1022" t="n">
-        <v>0.464070826768875</v>
+        <v>0.464070856571198</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G1023" t="n">
-        <v>0.467144191265106</v>
+        <v>0.467144161462784</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1024" t="n">
-        <v>0.45715594291687</v>
+        <v>0.457155913114548</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G1027" t="n">
-        <v>0.441020935773849</v>
+        <v>0.441020965576172</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1028" t="n">
-        <v>0.449472576379776</v>
+        <v>0.449472606182098</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>0.578999996185303</v>
       </c>
       <c r="G1029" t="n">
-        <v>0.444862574338913</v>
+        <v>0.444862604141235</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>0.556999981403351</v>
       </c>
       <c r="G1031" t="n">
-        <v>0.427959382534027</v>
+        <v>0.427959352731705</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1033" t="n">
-        <v>0.414897799491882</v>
+        <v>0.41489776968956</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1035" t="n">
-        <v>0.407214432954788</v>
+        <v>0.407214462757111</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>0.513000011444092</v>
       </c>
       <c r="G1036" t="n">
-        <v>0.394152939319611</v>
+        <v>0.394152909517288</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>0.488499999046326</v>
       </c>
       <c r="G1037" t="n">
-        <v>0.375328809022903</v>
+        <v>0.375328838825226</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>0.513999998569489</v>
       </c>
       <c r="G1039" t="n">
-        <v>0.394921213388443</v>
+        <v>0.394921243190765</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>0.524999976158142</v>
       </c>
       <c r="G1040" t="n">
-        <v>0.40337285399437</v>
+        <v>0.403372824192047</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>0.538999974727631</v>
       </c>
       <c r="G1041" t="n">
-        <v>0.41412940621376</v>
+        <v>0.414129436016083</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>0.512000024318695</v>
       </c>
       <c r="G1044" t="n">
-        <v>0.393384605646133</v>
+        <v>0.393384575843811</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>0.523000001907349</v>
       </c>
       <c r="G1047" t="n">
-        <v>0.401836186647415</v>
+        <v>0.401836156845093</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1049" t="n">
-        <v>0.407214432954788</v>
+        <v>0.407214462757111</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>0.513000011444092</v>
       </c>
       <c r="G1052" t="n">
-        <v>0.394152939319611</v>
+        <v>0.394152909517288</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>0.485000014305115</v>
       </c>
       <c r="G1056" t="n">
-        <v>0.372639685869217</v>
+        <v>0.372639656066895</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>0.446000009775162</v>
       </c>
       <c r="G1059" t="n">
-        <v>0.342674821615219</v>
+        <v>0.342674851417542</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G1061" t="n">
-        <v>0.317319959402084</v>
+        <v>0.317319929599762</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>0.337999999523163</v>
       </c>
       <c r="G1064" t="n">
-        <v>0.259695291519165</v>
+        <v>0.259695321321487</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>0.349000006914139</v>
       </c>
       <c r="G1065" t="n">
-        <v>0.268146902322769</v>
+        <v>0.268146872520447</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>0.311500012874603</v>
       </c>
       <c r="G1066" t="n">
-        <v>0.239334553480148</v>
+        <v>0.239334538578987</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>0.314999997615814</v>
       </c>
       <c r="G1067" t="n">
-        <v>0.242023676633835</v>
+        <v>0.242023691534996</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>0.305500000715256</v>
       </c>
       <c r="G1068" t="n">
-        <v>0.234724581241608</v>
+        <v>0.234724596142769</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>0.319999992847443</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.245865359902382</v>
+        <v>0.245865345001221</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>0.337000012397766</v>
       </c>
       <c r="G1070" t="n">
-        <v>0.258926957845688</v>
+        <v>0.258926928043365</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>0.347000002861023</v>
       </c>
       <c r="G1072" t="n">
-        <v>0.266610205173492</v>
+        <v>0.266610234975815</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>0.360000014305115</v>
       </c>
       <c r="G1073" t="n">
-        <v>0.276598483324051</v>
+        <v>0.276598513126373</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>0.36599999666214</v>
       </c>
       <c r="G1074" t="n">
-        <v>0.281208515167236</v>
+        <v>0.281208485364914</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>0.360000014305115</v>
       </c>
       <c r="G1075" t="n">
-        <v>0.276598483324051</v>
+        <v>0.276598513126373</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>0.331499993801117</v>
       </c>
       <c r="G1084" t="n">
-        <v>0.254701107740402</v>
+        <v>0.254701137542725</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>0.337999999523163</v>
       </c>
       <c r="G1085" t="n">
-        <v>0.259695291519165</v>
+        <v>0.259695321321487</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>0.337999999523163</v>
       </c>
       <c r="G1087" t="n">
-        <v>0.259695291519165</v>
+        <v>0.259695321321487</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>0.331000000238419</v>
       </c>
       <c r="G1088" t="n">
-        <v>0.254316955804825</v>
+        <v>0.254316985607147</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>0.344500005245209</v>
       </c>
       <c r="G1092" t="n">
-        <v>0.264689445495605</v>
+        <v>0.264689385890961</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>0.360500007867813</v>
       </c>
       <c r="G1099" t="n">
-        <v>0.276982694864273</v>
+        <v>0.276982724666595</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>0.361999988555908</v>
       </c>
       <c r="G1100" t="n">
-        <v>0.278135180473328</v>
+        <v>0.278135150671005</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>0.354999989271164</v>
       </c>
       <c r="G1101" t="n">
-        <v>0.272756844758987</v>
+        <v>0.27275687456131</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>0.358500003814697</v>
       </c>
       <c r="G1104" t="n">
-        <v>0.275446057319641</v>
+        <v>0.275445997714996</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>0.349000006914139</v>
       </c>
       <c r="G1105" t="n">
-        <v>0.268146902322769</v>
+        <v>0.268146872520447</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>0.345999985933304</v>
       </c>
       <c r="G1107" t="n">
-        <v>0.265841901302338</v>
+        <v>0.26584193110466</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>0.336499989032745</v>
       </c>
       <c r="G1109" t="n">
-        <v>0.258542776107788</v>
+        <v>0.258542746305466</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>0.345499992370605</v>
       </c>
       <c r="G1110" t="n">
-        <v>0.265457719564438</v>
+        <v>0.26545774936676</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>0.337000012397766</v>
       </c>
       <c r="G1112" t="n">
-        <v>0.258926957845688</v>
+        <v>0.258926928043365</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>0.341500014066696</v>
       </c>
       <c r="G1113" t="n">
-        <v>0.262384444475174</v>
+        <v>0.262384474277496</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>0.341500014066696</v>
       </c>
       <c r="G1114" t="n">
-        <v>0.262384444475174</v>
+        <v>0.262384474277496</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>0.345499992370605</v>
       </c>
       <c r="G1119" t="n">
-        <v>0.265457719564438</v>
+        <v>0.26545774936676</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>0.360000014305115</v>
       </c>
       <c r="G1120" t="n">
-        <v>0.276598483324051</v>
+        <v>0.276598513126373</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>0.360000014305115</v>
       </c>
       <c r="G1121" t="n">
-        <v>0.276598483324051</v>
+        <v>0.276598513126373</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>0.379999995231628</v>
       </c>
       <c r="G1122" t="n">
-        <v>0.291965126991272</v>
+        <v>0.29196509718895</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>0.381000012159348</v>
       </c>
       <c r="G1123" t="n">
-        <v>0.292733430862427</v>
+        <v>0.292733401060104</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>0.423000007867813</v>
       </c>
       <c r="G1124" t="n">
-        <v>0.325003266334534</v>
+        <v>0.325003236532211</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>0.400499999523163</v>
       </c>
       <c r="G1127" t="n">
-        <v>0.307715833187103</v>
+        <v>0.307715862989426</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>0.389999985694885</v>
       </c>
       <c r="G1128" t="n">
-        <v>0.299648374319077</v>
+        <v>0.299648344516754</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>0.393500000238419</v>
       </c>
       <c r="G1129" t="n">
-        <v>0.302337527275085</v>
+        <v>0.302337497472763</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>0.39300000667572</v>
       </c>
       <c r="G1130" t="n">
-        <v>0.301953375339508</v>
+        <v>0.301953434944153</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>0.45550000667572</v>
       </c>
       <c r="G1132" t="n">
-        <v>0.349973976612091</v>
+        <v>0.349973946809769</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>0.432500004768372</v>
       </c>
       <c r="G1134" t="n">
-        <v>0.332302421331406</v>
+        <v>0.332302391529083</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>0.43299999833107</v>
       </c>
       <c r="G1135" t="n">
-        <v>0.332686543464661</v>
+        <v>0.332686573266983</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>0.412499994039536</v>
       </c>
       <c r="G1136" t="n">
-        <v>0.316935807466507</v>
+        <v>0.316935777664185</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>0.400499999523163</v>
       </c>
       <c r="G1137" t="n">
-        <v>0.307715833187103</v>
+        <v>0.307715862989426</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>0.398499995470047</v>
       </c>
       <c r="G1140" t="n">
-        <v>0.306179225444794</v>
+        <v>0.306179195642471</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>0.388000011444092</v>
       </c>
       <c r="G1141" t="n">
-        <v>0.298111766576767</v>
+        <v>0.298111736774445</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>0.397000014781952</v>
       </c>
       <c r="G1144" t="n">
-        <v>0.305026680231094</v>
+        <v>0.305026710033417</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>0.390500009059906</v>
       </c>
       <c r="G1146" t="n">
-        <v>0.300032585859299</v>
+        <v>0.300032556056976</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>0.389999985694885</v>
       </c>
       <c r="G1148" t="n">
-        <v>0.299648374319077</v>
+        <v>0.299648344516754</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>0.390500009059906</v>
       </c>
       <c r="G1150" t="n">
-        <v>0.300032585859299</v>
+        <v>0.300032556056976</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>0.394499987363815</v>
       </c>
       <c r="G1151" t="n">
-        <v>0.303105890750885</v>
+        <v>0.303105860948563</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>0.39750000834465</v>
       </c>
       <c r="G1153" t="n">
-        <v>0.305410891771317</v>
+        <v>0.305410861968994</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>0.414000004529953</v>
       </c>
       <c r="G1156" t="n">
-        <v>0.318088293075562</v>
+        <v>0.318088322877884</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G1158" t="n">
-        <v>0.322698295116425</v>
+        <v>0.322698265314102</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>0.407499998807907</v>
       </c>
       <c r="G1164" t="n">
-        <v>0.313094139099121</v>
+        <v>0.313094168901443</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>0.41049998998642</v>
       </c>
       <c r="G1167" t="n">
-        <v>0.315399169921875</v>
+        <v>0.315399140119553</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>0.417499989271164</v>
       </c>
       <c r="G1169" t="n">
-        <v>0.32077744603157</v>
+        <v>0.320777416229248</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G1173" t="n">
-        <v>0.317319959402084</v>
+        <v>0.317319929599762</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>0.404000014066696</v>
       </c>
       <c r="G1174" t="n">
-        <v>0.310405015945435</v>
+        <v>0.310404986143112</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>0.40599998831749</v>
       </c>
       <c r="G1175" t="n">
-        <v>0.311941653490067</v>
+        <v>0.311941683292389</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>0.404000014066696</v>
       </c>
       <c r="G1178" t="n">
-        <v>0.310405015945435</v>
+        <v>0.310404986143112</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>0.397000014781952</v>
       </c>
       <c r="G1179" t="n">
-        <v>0.305026680231094</v>
+        <v>0.305026710033417</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>0.39300000667572</v>
       </c>
       <c r="G1180" t="n">
-        <v>0.301953375339508</v>
+        <v>0.301953434944153</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>0.393500000238419</v>
       </c>
       <c r="G1181" t="n">
-        <v>0.302337527275085</v>
+        <v>0.302337497472763</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>0.390500009059906</v>
       </c>
       <c r="G1182" t="n">
-        <v>0.300032585859299</v>
+        <v>0.300032556056976</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>0.390500009059906</v>
       </c>
       <c r="G1184" t="n">
-        <v>0.300032585859299</v>
+        <v>0.300032556056976</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>0.389999985694885</v>
       </c>
       <c r="G1187" t="n">
-        <v>0.299648374319077</v>
+        <v>0.299648344516754</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>0.380499988794327</v>
       </c>
       <c r="G1188" t="n">
-        <v>0.292349278926849</v>
+        <v>0.292349249124527</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>0.38400000333786</v>
       </c>
       <c r="G1189" t="n">
-        <v>0.295038402080536</v>
+        <v>0.295038431882858</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>0.379999995231628</v>
       </c>
       <c r="G1190" t="n">
-        <v>0.291965126991272</v>
+        <v>0.29196509718895</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>0.374000012874603</v>
       </c>
       <c r="G1192" t="n">
-        <v>0.287355124950409</v>
+        <v>0.287355154752731</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>0.379000008106232</v>
       </c>
       <c r="G1194" t="n">
-        <v>0.291196763515472</v>
+        <v>0.291196793317795</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>0.369500011205673</v>
       </c>
       <c r="G1196" t="n">
-        <v>0.283897668123245</v>
+        <v>0.283897697925568</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>0.379999995231628</v>
       </c>
       <c r="G1197" t="n">
-        <v>0.291965126991272</v>
+        <v>0.29196509718895</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>0.370999991893768</v>
       </c>
       <c r="G1199" t="n">
-        <v>0.285050094127655</v>
+        <v>0.285050123929977</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>0.356000006198883</v>
       </c>
       <c r="G1200" t="n">
-        <v>0.273525208234787</v>
+        <v>0.273525238037109</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>0.354999989271164</v>
       </c>
       <c r="G1201" t="n">
-        <v>0.272756844758987</v>
+        <v>0.27275687456131</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>0.354999989271164</v>
       </c>
       <c r="G1202" t="n">
-        <v>0.272756844758987</v>
+        <v>0.27275687456131</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>0.340499997138977</v>
       </c>
       <c r="G1205" t="n">
-        <v>0.261616110801697</v>
+        <v>0.261616080999374</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>0.344500005245209</v>
       </c>
       <c r="G1206" t="n">
-        <v>0.264689445495605</v>
+        <v>0.264689385890961</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>0.351500004529953</v>
       </c>
       <c r="G1207" t="n">
-        <v>0.270067721605301</v>
+        <v>0.270067691802979</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>0.362500011920929</v>
       </c>
       <c r="G1208" t="n">
-        <v>0.27851939201355</v>
+        <v>0.278519362211227</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>0.370000004768372</v>
       </c>
       <c r="G1211" t="n">
-        <v>0.284281849861145</v>
+        <v>0.284281820058823</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>0.368000000715256</v>
       </c>
       <c r="G1212" t="n">
-        <v>0.282745152711868</v>
+        <v>0.282745122909546</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>0.367000013589859</v>
       </c>
       <c r="G1213" t="n">
-        <v>0.281976789236069</v>
+        <v>0.281976819038391</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>0.360000014305115</v>
       </c>
       <c r="G1214" t="n">
-        <v>0.276598483324051</v>
+        <v>0.276598513126373</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>0.349000006914139</v>
       </c>
       <c r="G1216" t="n">
-        <v>0.268146902322769</v>
+        <v>0.268146872520447</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>0.344500005245209</v>
       </c>
       <c r="G1218" t="n">
-        <v>0.264689445495605</v>
+        <v>0.264689385890961</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>0.337000012397766</v>
       </c>
       <c r="G1219" t="n">
-        <v>0.258926957845688</v>
+        <v>0.258926928043365</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>0.333499997854233</v>
       </c>
       <c r="G1225" t="n">
-        <v>0.256237804889679</v>
+        <v>0.256237834692001</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>0.324499994516373</v>
       </c>
       <c r="G1226" t="n">
-        <v>0.249322816729546</v>
+        <v>0.249322831630707</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>0.307500004768372</v>
       </c>
       <c r="G1227" t="n">
-        <v>0.236261233687401</v>
+        <v>0.23626121878624</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>0.330000013113022</v>
       </c>
       <c r="G1229" t="n">
-        <v>0.253548681735992</v>
+        <v>0.25354865193367</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>0.368999987840652</v>
       </c>
       <c r="G1231" t="n">
-        <v>0.283513426780701</v>
+        <v>0.283513456583023</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>0.370000004768372</v>
       </c>
       <c r="G1232" t="n">
-        <v>0.284281849861145</v>
+        <v>0.284281820058823</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>0.359499990940094</v>
       </c>
       <c r="G1233" t="n">
-        <v>0.276214331388474</v>
+        <v>0.276214301586151</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>0.356000006198883</v>
       </c>
       <c r="G1234" t="n">
-        <v>0.273525208234787</v>
+        <v>0.273525238037109</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>0.36149999499321</v>
       </c>
       <c r="G1235" t="n">
-        <v>0.277750998735428</v>
+        <v>0.27775102853775</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>0.354999989271164</v>
       </c>
       <c r="G1236" t="n">
-        <v>0.272756844758987</v>
+        <v>0.27275687456131</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>0.356000006198883</v>
       </c>
       <c r="G1237" t="n">
-        <v>0.273525208234787</v>
+        <v>0.273525238037109</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>0.383500009775162</v>
       </c>
       <c r="G1239" t="n">
-        <v>0.294654250144958</v>
+        <v>0.294654279947281</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>0.392500013113022</v>
       </c>
       <c r="G1245" t="n">
-        <v>0.301569223403931</v>
+        <v>0.301569253206253</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>0.398499995470047</v>
       </c>
       <c r="G1246" t="n">
-        <v>0.306179225444794</v>
+        <v>0.306179195642471</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>0.399500012397766</v>
       </c>
       <c r="G1247" t="n">
-        <v>0.306947499513626</v>
+        <v>0.306947529315948</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G1248" t="n">
-        <v>0.319624990224838</v>
+        <v>0.319624960422516</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G1249" t="n">
-        <v>0.322698295116425</v>
+        <v>0.322698265314102</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>0.43299999833107</v>
       </c>
       <c r="G1251" t="n">
-        <v>0.332686543464661</v>
+        <v>0.332686573266983</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>0.447499990463257</v>
       </c>
       <c r="G1255" t="n">
-        <v>0.343827337026596</v>
+        <v>0.343827366828918</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>0.440499991178513</v>
       </c>
       <c r="G1257" t="n">
-        <v>0.338449031114578</v>
+        <v>0.338449001312256</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>0.440499991178513</v>
       </c>
       <c r="G1258" t="n">
-        <v>0.338449031114578</v>
+        <v>0.338449001312256</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>0.443500012159348</v>
       </c>
       <c r="G1259" t="n">
-        <v>0.340754002332687</v>
+        <v>0.34075403213501</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G1260" t="n">
-        <v>0.336528211832047</v>
+        <v>0.336528182029724</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G1261" t="n">
-        <v>0.338833183050156</v>
+        <v>0.338833212852478</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>0.43299999833107</v>
       </c>
       <c r="G1262" t="n">
-        <v>0.332686543464661</v>
+        <v>0.332686573266983</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>0.423000007867813</v>
       </c>
       <c r="G1263" t="n">
-        <v>0.325003266334534</v>
+        <v>0.325003236532211</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>0.417499989271164</v>
       </c>
       <c r="G1265" t="n">
-        <v>0.32077744603157</v>
+        <v>0.320777416229248</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G1267" t="n">
-        <v>0.324234932661057</v>
+        <v>0.324234962463379</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G1268" t="n">
-        <v>0.324234932661057</v>
+        <v>0.324234962463379</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G1269" t="n">
-        <v>0.322698295116425</v>
+        <v>0.322698265314102</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>0.413500010967255</v>
       </c>
       <c r="G1270" t="n">
-        <v>0.317704111337662</v>
+        <v>0.317704141139984</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G1271" t="n">
-        <v>0.324234932661057</v>
+        <v>0.324234962463379</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G1274" t="n">
-        <v>0.338064849376678</v>
+        <v>0.338064819574356</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>0.438499987125397</v>
       </c>
       <c r="G1275" t="n">
-        <v>0.336912333965302</v>
+        <v>0.336912363767624</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>0.425500005483627</v>
       </c>
       <c r="G1276" t="n">
-        <v>0.326924085617065</v>
+        <v>0.326924055814743</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>0.434500008821487</v>
       </c>
       <c r="G1277" t="n">
-        <v>0.333839058876038</v>
+        <v>0.333839029073715</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>0.430500000715256</v>
       </c>
       <c r="G1278" t="n">
-        <v>0.330765753984451</v>
+        <v>0.330765724182129</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>0.416999995708466</v>
       </c>
       <c r="G1284" t="n">
-        <v>0.320393234491348</v>
+        <v>0.320393264293671</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G1285" t="n">
-        <v>0.317319959402084</v>
+        <v>0.317319929599762</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>0.397000014781952</v>
       </c>
       <c r="G1288" t="n">
-        <v>0.305026680231094</v>
+        <v>0.305026710033417</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>0.393999993801117</v>
       </c>
       <c r="G1290" t="n">
-        <v>0.302721738815308</v>
+        <v>0.302721709012985</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>0.407499998807907</v>
       </c>
       <c r="G1291" t="n">
-        <v>0.313094139099121</v>
+        <v>0.313094168901443</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>0.430500000715256</v>
       </c>
       <c r="G1292" t="n">
-        <v>0.330765753984451</v>
+        <v>0.330765724182129</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>0.4375</v>
       </c>
       <c r="G1293" t="n">
-        <v>0.336144030094147</v>
+        <v>0.336144059896469</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>0.43299999833107</v>
       </c>
       <c r="G1295" t="n">
-        <v>0.332686543464661</v>
+        <v>0.332686573266983</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>0.438499987125397</v>
       </c>
       <c r="G1297" t="n">
-        <v>0.336912333965302</v>
+        <v>0.336912363767624</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>0.467500001192093</v>
       </c>
       <c r="G1300" t="n">
-        <v>0.359193921089172</v>
+        <v>0.35919389128685</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>0.458000004291534</v>
       </c>
       <c r="G1302" t="n">
-        <v>0.351894795894623</v>
+        <v>0.3518947660923</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G1304" t="n">
-        <v>0.353431403636932</v>
+        <v>0.353431463241577</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>0.474500000476837</v>
       </c>
       <c r="G1305" t="n">
-        <v>0.364572197198868</v>
+        <v>0.364572256803513</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>0.467000007629395</v>
       </c>
       <c r="G1306" t="n">
-        <v>0.358809739351273</v>
+        <v>0.358809769153595</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G1309" t="n">
-        <v>0.353431403636932</v>
+        <v>0.353431463241577</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G1310" t="n">
-        <v>0.353431403636932</v>
+        <v>0.353431463241577</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>0.480500012636185</v>
       </c>
       <c r="G1313" t="n">
-        <v>0.369182229042053</v>
+        <v>0.369182169437408</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>0.467000007629395</v>
       </c>
       <c r="G1315" t="n">
-        <v>0.358809739351273</v>
+        <v>0.358809769153595</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>0.460999995470047</v>
       </c>
       <c r="G1317" t="n">
-        <v>0.354199767112732</v>
+        <v>0.354199796915054</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>0.465999990701675</v>
       </c>
       <c r="G1318" t="n">
-        <v>0.358041405677795</v>
+        <v>0.358041375875473</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>0.462000012397766</v>
       </c>
       <c r="G1322" t="n">
-        <v>0.354968130588531</v>
+        <v>0.354968100786209</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>0.456999987363815</v>
       </c>
       <c r="G1324" t="n">
-        <v>0.351126462221146</v>
+        <v>0.351126432418823</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>0.45550000667572</v>
       </c>
       <c r="G1327" t="n">
-        <v>0.349973976612091</v>
+        <v>0.349973946809769</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>0.45100000500679</v>
       </c>
       <c r="G1328" t="n">
-        <v>0.346516489982605</v>
+        <v>0.346516460180283</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>0.44200000166893</v>
       </c>
       <c r="G1331" t="n">
-        <v>0.339601516723633</v>
+        <v>0.33960148692131</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>0.451999992132187</v>
       </c>
       <c r="G1332" t="n">
-        <v>0.34728479385376</v>
+        <v>0.347284823656082</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>0.460999995470047</v>
       </c>
       <c r="G1333" t="n">
-        <v>0.354199767112732</v>
+        <v>0.354199796915054</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>0.472499996423721</v>
       </c>
       <c r="G1335" t="n">
-        <v>0.363035559654236</v>
+        <v>0.363035529851913</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>0.469999998807907</v>
       </c>
       <c r="G1336" t="n">
-        <v>0.361114770174026</v>
+        <v>0.361114740371704</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>0.458000004291534</v>
       </c>
       <c r="G1338" t="n">
-        <v>0.351894795894623</v>
+        <v>0.3518947660923</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>0.477999985218048</v>
       </c>
       <c r="G1340" t="n">
-        <v>0.367261350154877</v>
+        <v>0.367261379957199</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>0.5</v>
       </c>
       <c r="G1343" t="n">
-        <v>0.384164601564407</v>
+        <v>0.38416463136673</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>0.472499996423721</v>
       </c>
       <c r="G1346" t="n">
-        <v>0.363035559654236</v>
+        <v>0.363035529851913</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>0.477999985218048</v>
       </c>
       <c r="G1349" t="n">
-        <v>0.367261350154877</v>
+        <v>0.367261379957199</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>0.47299998998642</v>
       </c>
       <c r="G1350" t="n">
-        <v>0.363419741392136</v>
+        <v>0.363419681787491</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>0.467000007629395</v>
       </c>
       <c r="G1354" t="n">
-        <v>0.358809739351273</v>
+        <v>0.358809769153595</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>0.474500000476837</v>
       </c>
       <c r="G1355" t="n">
-        <v>0.364572197198868</v>
+        <v>0.364572256803513</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>0.474500000476837</v>
       </c>
       <c r="G1356" t="n">
-        <v>0.364572197198868</v>
+        <v>0.364572256803513</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>0.47299998998642</v>
       </c>
       <c r="G1357" t="n">
-        <v>0.363419741392136</v>
+        <v>0.363419681787491</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>0.477999985218048</v>
       </c>
       <c r="G1360" t="n">
-        <v>0.367261350154877</v>
+        <v>0.367261379957199</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>0.483999997377396</v>
       </c>
       <c r="G1363" t="n">
-        <v>0.37187135219574</v>
+        <v>0.371871381998062</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>0.485000014305115</v>
       </c>
       <c r="G1364" t="n">
-        <v>0.372639685869217</v>
+        <v>0.372639656066895</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>0.486999988555908</v>
       </c>
       <c r="G1366" t="n">
-        <v>0.374176323413849</v>
+        <v>0.374176293611526</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>0.484499990940094</v>
       </c>
       <c r="G1367" t="n">
-        <v>0.37225553393364</v>
+        <v>0.372255474328995</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>0.476999998092651</v>
       </c>
       <c r="G1370" t="n">
-        <v>0.366493076086044</v>
+        <v>0.3664930164814</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>0.48199999332428</v>
       </c>
       <c r="G1374" t="n">
-        <v>0.370334655046463</v>
+        <v>0.370334684848785</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>0.485500007867813</v>
       </c>
       <c r="G1375" t="n">
-        <v>0.373023808002472</v>
+        <v>0.373023837804794</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>0.493999987840652</v>
       </c>
       <c r="G1376" t="n">
-        <v>0.379554629325867</v>
+        <v>0.379554599523544</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G1385" t="n">
-        <v>0.430264353752136</v>
+        <v>0.430264383554459</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>0.554000020027161</v>
       </c>
       <c r="G1386" t="n">
-        <v>0.425654381513596</v>
+        <v>0.425654411315918</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G1389" t="n">
-        <v>0.417971134185791</v>
+        <v>0.417971104383469</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1392" t="n">
-        <v>0.414897799491882</v>
+        <v>0.41489776968956</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>0.531000018119812</v>
       </c>
       <c r="G1394" t="n">
-        <v>0.407982856035233</v>
+        <v>0.40798282623291</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>0.538999974727631</v>
       </c>
       <c r="G1397" t="n">
-        <v>0.41412940621376</v>
+        <v>0.414129436016083</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>0.550999999046326</v>
       </c>
       <c r="G1399" t="n">
-        <v>0.423349440097809</v>
+        <v>0.423349410295486</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G1400" t="n">
-        <v>0.417971134185791</v>
+        <v>0.417971104383469</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>0.528999984264374</v>
       </c>
       <c r="G1401" t="n">
-        <v>0.406446099281311</v>
+        <v>0.406446129083633</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>0.528999984264374</v>
       </c>
       <c r="G1402" t="n">
-        <v>0.406446099281311</v>
+        <v>0.406446129083633</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>0.538999974727631</v>
       </c>
       <c r="G1404" t="n">
-        <v>0.41412940621376</v>
+        <v>0.414129436016083</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>0.5</v>
       </c>
       <c r="G1407" t="n">
-        <v>0.384164601564407</v>
+        <v>0.38416463136673</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>0.5</v>
       </c>
       <c r="G1408" t="n">
-        <v>0.384164601564407</v>
+        <v>0.38416463136673</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>0.485000014305115</v>
       </c>
       <c r="G1409" t="n">
-        <v>0.372639685869217</v>
+        <v>0.372639656066895</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>0.474500000476837</v>
       </c>
       <c r="G1410" t="n">
-        <v>0.364572197198868</v>
+        <v>0.364572256803513</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>0.483999997377396</v>
       </c>
       <c r="G1412" t="n">
-        <v>0.37187135219574</v>
+        <v>0.371871381998062</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>0.497000008821487</v>
       </c>
       <c r="G1413" t="n">
-        <v>0.381859630346298</v>
+        <v>0.381859660148621</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>0.5</v>
       </c>
       <c r="G1415" t="n">
-        <v>0.384164601564407</v>
+        <v>0.38416463136673</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>0.497500002384186</v>
       </c>
       <c r="G1422" t="n">
-        <v>0.382243782281876</v>
+        <v>0.382243812084198</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>0.498499989509583</v>
       </c>
       <c r="G1423" t="n">
-        <v>0.383012115955353</v>
+        <v>0.38301208615303</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>0.491499990224838</v>
       </c>
       <c r="G1425" t="n">
-        <v>0.377633810043335</v>
+        <v>0.377633780241013</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>0.492000013589859</v>
       </c>
       <c r="G1426" t="n">
-        <v>0.378017991781235</v>
+        <v>0.378018021583557</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>0.492500007152557</v>
       </c>
       <c r="G1427" t="n">
-        <v>0.378402143716812</v>
+        <v>0.378402173519135</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>0.467500001192093</v>
       </c>
       <c r="G1432" t="n">
-        <v>0.359193921089172</v>
+        <v>0.35919389128685</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>0.443500012159348</v>
       </c>
       <c r="G1433" t="n">
-        <v>0.340754002332687</v>
+        <v>0.34075403213501</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>0.451999992132187</v>
       </c>
       <c r="G1434" t="n">
-        <v>0.34728479385376</v>
+        <v>0.347284823656082</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>0.469500005245209</v>
       </c>
       <c r="G1440" t="n">
-        <v>0.360730558633804</v>
+        <v>0.360730588436127</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>0.474500000476837</v>
       </c>
       <c r="G1441" t="n">
-        <v>0.364572197198868</v>
+        <v>0.364572256803513</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G1442" t="n">
-        <v>0.422581046819687</v>
+        <v>0.422581106424332</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G1445" t="n">
-        <v>0.422581046819687</v>
+        <v>0.422581106424332</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>0.549000024795532</v>
       </c>
       <c r="G1446" t="n">
-        <v>0.421812772750854</v>
+        <v>0.42181271314621</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>0.528999984264374</v>
       </c>
       <c r="G1448" t="n">
-        <v>0.406446099281311</v>
+        <v>0.406446129083633</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>0.524999976158142</v>
       </c>
       <c r="G1450" t="n">
-        <v>0.40337285399437</v>
+        <v>0.403372824192047</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>0.513999998569489</v>
       </c>
       <c r="G1453" t="n">
-        <v>0.394921213388443</v>
+        <v>0.394921243190765</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>0.513000011444092</v>
       </c>
       <c r="G1456" t="n">
-        <v>0.394152939319611</v>
+        <v>0.394152909517288</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>0.513999998569489</v>
       </c>
       <c r="G1458" t="n">
-        <v>0.394921213388443</v>
+        <v>0.394921243190765</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>0.500999987125397</v>
       </c>
       <c r="G1460" t="n">
-        <v>0.384932935237885</v>
+        <v>0.384932905435562</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>0.488499999046326</v>
       </c>
       <c r="G1463" t="n">
-        <v>0.375328809022903</v>
+        <v>0.375328838825226</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>0.494500011205673</v>
       </c>
       <c r="G1465" t="n">
-        <v>0.379938811063766</v>
+        <v>0.379938781261444</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>0.489499986171722</v>
       </c>
       <c r="G1467" t="n">
-        <v>0.376097142696381</v>
+        <v>0.376097172498703</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>0.531000018119812</v>
       </c>
       <c r="G1473" t="n">
-        <v>0.407982856035233</v>
+        <v>0.40798282623291</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>0.524999976158142</v>
       </c>
       <c r="G1474" t="n">
-        <v>0.40337285399437</v>
+        <v>0.403372824192047</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>0.513000011444092</v>
       </c>
       <c r="G1475" t="n">
-        <v>0.394152939319611</v>
+        <v>0.394152909517288</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>0.538999974727631</v>
       </c>
       <c r="G1479" t="n">
-        <v>0.41412940621376</v>
+        <v>0.414129436016083</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>0.523000001907349</v>
       </c>
       <c r="G1482" t="n">
-        <v>0.401836186647415</v>
+        <v>0.401836156845093</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>0.523000001907349</v>
       </c>
       <c r="G1489" t="n">
-        <v>0.401836186647415</v>
+        <v>0.401836156845093</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1491" t="n">
-        <v>0.414897799491882</v>
+        <v>0.41489776968956</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>0.558000028133392</v>
       </c>
       <c r="G1492" t="n">
-        <v>0.428727686405182</v>
+        <v>0.428727716207504</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>0.50900000333786</v>
       </c>
       <c r="G1496" t="n">
-        <v>0.39107957482338</v>
+        <v>0.391079545021057</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>0.500999987125397</v>
       </c>
       <c r="G1497" t="n">
-        <v>0.384932935237885</v>
+        <v>0.384932905435562</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>0.491499990224838</v>
       </c>
       <c r="G1498" t="n">
-        <v>0.377633810043335</v>
+        <v>0.377633780241013</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>0.448500007390976</v>
       </c>
       <c r="G1508" t="n">
-        <v>0.344595670700073</v>
+        <v>0.344595611095428</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>0.445499986410141</v>
       </c>
       <c r="G1511" t="n">
-        <v>0.342290639877319</v>
+        <v>0.342290669679642</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>0.44200000166893</v>
       </c>
       <c r="G1513" t="n">
-        <v>0.339601516723633</v>
+        <v>0.33960148692131</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G1515" t="n">
-        <v>0.329613208770752</v>
+        <v>0.329613268375397</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>0.425500005483627</v>
       </c>
       <c r="G1516" t="n">
-        <v>0.326924085617065</v>
+        <v>0.326924055814743</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G1517" t="n">
-        <v>0.338833183050156</v>
+        <v>0.338833212852478</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>0.431499987840652</v>
       </c>
       <c r="G1518" t="n">
-        <v>0.331534028053284</v>
+        <v>0.331534057855606</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G1519" t="n">
-        <v>0.319624990224838</v>
+        <v>0.319624960422516</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>0.421000003814697</v>
       </c>
       <c r="G1520" t="n">
-        <v>0.323466569185257</v>
+        <v>0.323466598987579</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G1521" t="n">
-        <v>0.336528211832047</v>
+        <v>0.336528182029724</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>0.44200000166893</v>
       </c>
       <c r="G1522" t="n">
-        <v>0.339601516723633</v>
+        <v>0.33960148692131</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>0.45100000500679</v>
       </c>
       <c r="G1528" t="n">
-        <v>0.346516489982605</v>
+        <v>0.346516460180283</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>0.462000012397766</v>
       </c>
       <c r="G1530" t="n">
-        <v>0.354968130588531</v>
+        <v>0.354968100786209</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>0.458000004291534</v>
       </c>
       <c r="G1531" t="n">
-        <v>0.351894795894623</v>
+        <v>0.3518947660923</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>0.448500007390976</v>
       </c>
       <c r="G1532" t="n">
-        <v>0.344595670700073</v>
+        <v>0.344595611095428</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>0.45100000500679</v>
       </c>
       <c r="G1534" t="n">
-        <v>0.346516489982605</v>
+        <v>0.346516460180283</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>0.446000009775162</v>
       </c>
       <c r="G1538" t="n">
-        <v>0.342674821615219</v>
+        <v>0.342674851417542</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>0.443500012159348</v>
       </c>
       <c r="G1539" t="n">
-        <v>0.340754002332687</v>
+        <v>0.34075403213501</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G1541" t="n">
-        <v>0.336528211832047</v>
+        <v>0.336528182029724</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>0.416999995708466</v>
       </c>
       <c r="G1542" t="n">
-        <v>0.320393234491348</v>
+        <v>0.320393264293671</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>0.423000007867813</v>
       </c>
       <c r="G1544" t="n">
-        <v>0.325003266334534</v>
+        <v>0.325003236532211</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>0.423000007867813</v>
       </c>
       <c r="G1547" t="n">
-        <v>0.325003266334534</v>
+        <v>0.325003236532211</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>0.432500004768372</v>
       </c>
       <c r="G1550" t="n">
-        <v>0.332302421331406</v>
+        <v>0.332302391529083</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>0.421000003814697</v>
       </c>
       <c r="G1556" t="n">
-        <v>0.323466569185257</v>
+        <v>0.323466598987579</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>0.40599998831749</v>
       </c>
       <c r="G1557" t="n">
-        <v>0.311941653490067</v>
+        <v>0.311941683292389</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G1560" t="n">
-        <v>0.317319959402084</v>
+        <v>0.317319929599762</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G1561" t="n">
-        <v>0.322698295116425</v>
+        <v>0.322698265314102</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G1562" t="n">
-        <v>0.31501492857933</v>
+        <v>0.315014988183975</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>0.40599998831749</v>
       </c>
       <c r="G1563" t="n">
-        <v>0.311941653490067</v>
+        <v>0.311941683292389</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>0.412000000476837</v>
       </c>
       <c r="G1564" t="n">
-        <v>0.31655165553093</v>
+        <v>0.316551625728607</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>0.400499999523163</v>
       </c>
       <c r="G1566" t="n">
-        <v>0.307715833187103</v>
+        <v>0.307715862989426</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>0.397000014781952</v>
       </c>
       <c r="G1568" t="n">
-        <v>0.305026680231094</v>
+        <v>0.305026710033417</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>0.36149999499321</v>
       </c>
       <c r="G1571" t="n">
-        <v>0.277750998735428</v>
+        <v>0.27775102853775</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>0.363999992609024</v>
       </c>
       <c r="G1572" t="n">
-        <v>0.279671847820282</v>
+        <v>0.27967181801796</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>0.36599999666214</v>
       </c>
       <c r="G1573" t="n">
-        <v>0.281208515167236</v>
+        <v>0.281208485364914</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>0.372000008821487</v>
       </c>
       <c r="G1574" t="n">
-        <v>0.285818487405777</v>
+        <v>0.285818457603455</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>0.361000001430511</v>
       </c>
       <c r="G1575" t="n">
-        <v>0.277366816997528</v>
+        <v>0.27736684679985</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>0.38400000333786</v>
       </c>
       <c r="G1576" t="n">
-        <v>0.295038402080536</v>
+        <v>0.295038431882858</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>0.379999995231628</v>
       </c>
       <c r="G1578" t="n">
-        <v>0.291965126991272</v>
+        <v>0.29196509718895</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>0.393999993801117</v>
       </c>
       <c r="G1579" t="n">
-        <v>0.302721738815308</v>
+        <v>0.302721709012985</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41449,7 +41449,7 @@
         <v>0.380499988794327</v>
       </c>
       <c r="G1580" t="n">
-        <v>0.292349278926849</v>
+        <v>0.292349249124527</v>
       </c>
       <c r="H1580" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>0.40599998831749</v>
       </c>
       <c r="G1581" t="n">
-        <v>0.311941653490067</v>
+        <v>0.311941683292389</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>0.439500004053116</v>
       </c>
       <c r="G1582" t="n">
-        <v>0.337680697441101</v>
+        <v>0.337680727243423</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>0.439500004053116</v>
       </c>
       <c r="G1583" t="n">
-        <v>0.337680697441101</v>
+        <v>0.337680727243423</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>0.458499997854233</v>
       </c>
       <c r="G1585" t="n">
-        <v>0.352278977632523</v>
+        <v>0.3522789478302</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>0.434500008821487</v>
       </c>
       <c r="G1589" t="n">
-        <v>0.333839058876038</v>
+        <v>0.333839029073715</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>0.444499999284744</v>
       </c>
       <c r="G1590" t="n">
-        <v>0.341522365808487</v>
+        <v>0.341522336006165</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>0.456999987363815</v>
       </c>
       <c r="G1593" t="n">
-        <v>0.351126462221146</v>
+        <v>0.351126432418823</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>0.460999995470047</v>
       </c>
       <c r="G1596" t="n">
-        <v>0.354199767112732</v>
+        <v>0.354199796915054</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>0.465000003576279</v>
       </c>
       <c r="G1599" t="n">
-        <v>0.357273072004318</v>
+        <v>0.357273101806641</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -41995,7 +41995,7 @@
         <v>0.469999998807907</v>
       </c>
       <c r="G1601" t="n">
-        <v>0.361114770174026</v>
+        <v>0.361114740371704</v>
       </c>
       <c r="H1601" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>0.456999987363815</v>
       </c>
       <c r="G1604" t="n">
-        <v>0.351126462221146</v>
+        <v>0.351126432418823</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G1606" t="n">
-        <v>0.336528211832047</v>
+        <v>0.336528182029724</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42151,7 +42151,7 @@
         <v>0.435499995946884</v>
       </c>
       <c r="G1607" t="n">
-        <v>0.33460733294487</v>
+        <v>0.334607362747192</v>
       </c>
       <c r="H1607" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>0.431499987840652</v>
       </c>
       <c r="G1608" t="n">
-        <v>0.331534028053284</v>
+        <v>0.331534057855606</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G1610" t="n">
-        <v>0.338833183050156</v>
+        <v>0.338833212852478</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42255,7 +42255,7 @@
         <v>0.44200000166893</v>
       </c>
       <c r="G1611" t="n">
-        <v>0.339601516723633</v>
+        <v>0.33960148692131</v>
       </c>
       <c r="H1611" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>0.42849999666214</v>
       </c>
       <c r="G1615" t="n">
-        <v>0.329229027032852</v>
+        <v>0.329229056835175</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>0.42849999666214</v>
       </c>
       <c r="G1616" t="n">
-        <v>0.329229027032852</v>
+        <v>0.329229056835175</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>0.435499995946884</v>
       </c>
       <c r="G1617" t="n">
-        <v>0.33460733294487</v>
+        <v>0.334607362747192</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>0.435499995946884</v>
       </c>
       <c r="G1618" t="n">
-        <v>0.33460733294487</v>
+        <v>0.334607362747192</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>0.448500007390976</v>
       </c>
       <c r="G1619" t="n">
-        <v>0.344595670700073</v>
+        <v>0.344595611095428</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>0.429500013589859</v>
       </c>
       <c r="G1620" t="n">
-        <v>0.353653132915497</v>
+        <v>0.353653162717819</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42645,7 +42645,7 @@
         <v>0.41499999165535</v>
       </c>
       <c r="G1626" t="n">
-        <v>0.341713726520538</v>
+        <v>0.341713756322861</v>
       </c>
       <c r="H1626" t="s">
         <v>8</v>
@@ -42671,7 +42671,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G1627" t="n">
-        <v>0.34253716468811</v>
+        <v>0.342537134885788</v>
       </c>
       <c r="H1627" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>0.437000006437302</v>
       </c>
       <c r="G1630" t="n">
-        <v>0.359828680753708</v>
+        <v>0.35982871055603</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G1631" t="n">
-        <v>0.353241413831711</v>
+        <v>0.353241443634033</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42801,7 +42801,7 @@
         <v>0.430999994277954</v>
       </c>
       <c r="G1632" t="n">
-        <v>0.35488823056221</v>
+        <v>0.354888200759888</v>
       </c>
       <c r="H1632" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>0.418999999761581</v>
       </c>
       <c r="G1634" t="n">
-        <v>0.345007330179214</v>
+        <v>0.345007359981537</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42879,7 +42879,7 @@
         <v>0.412499994039536</v>
       </c>
       <c r="G1635" t="n">
-        <v>0.339655220508575</v>
+        <v>0.339655190706253</v>
       </c>
       <c r="H1635" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>0.414499998092651</v>
       </c>
       <c r="G1638" t="n">
-        <v>0.341302037239075</v>
+        <v>0.341302007436752</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -43243,7 +43243,7 @@
         <v>0.386000007390976</v>
       </c>
       <c r="G1649" t="n">
-        <v>0.317834973335266</v>
+        <v>0.317834943532944</v>
       </c>
       <c r="H1649" t="s">
         <v>8</v>
@@ -43269,7 +43269,7 @@
         <v>0.388000011444092</v>
       </c>
       <c r="G1650" t="n">
-        <v>0.319481790065765</v>
+        <v>0.319481760263443</v>
       </c>
       <c r="H1650" t="s">
         <v>8</v>
@@ -43295,7 +43295,7 @@
         <v>0.379000008106232</v>
       </c>
       <c r="G1651" t="n">
-        <v>0.312071084976196</v>
+        <v>0.312071114778519</v>
       </c>
       <c r="H1651" t="s">
         <v>8</v>
@@ -43373,7 +43373,7 @@
         <v>0.379000008106232</v>
       </c>
       <c r="G1654" t="n">
-        <v>0.312071084976196</v>
+        <v>0.312071114778519</v>
       </c>
       <c r="H1654" t="s">
         <v>8</v>
@@ -43451,7 +43451,7 @@
         <v>0.386999994516373</v>
       </c>
       <c r="G1657" t="n">
-        <v>0.318658322095871</v>
+        <v>0.318658351898193</v>
       </c>
       <c r="H1657" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>0.386999994516373</v>
       </c>
       <c r="G1658" t="n">
-        <v>0.318658322095871</v>
+        <v>0.318658351898193</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43529,7 +43529,7 @@
         <v>0.391999989748001</v>
       </c>
       <c r="G1660" t="n">
-        <v>0.322775393724442</v>
+        <v>0.322775363922119</v>
       </c>
       <c r="H1660" t="s">
         <v>8</v>
@@ -43555,7 +43555,7 @@
         <v>0.375999987125397</v>
       </c>
       <c r="G1661" t="n">
-        <v>0.309600859880447</v>
+        <v>0.309600830078125</v>
       </c>
       <c r="H1661" t="s">
         <v>8</v>
@@ -43607,7 +43607,7 @@
         <v>0.375499993562698</v>
       </c>
       <c r="G1663" t="n">
-        <v>0.309189170598984</v>
+        <v>0.309189140796661</v>
       </c>
       <c r="H1663" t="s">
         <v>8</v>
@@ -43633,7 +43633,7 @@
         <v>0.386000007390976</v>
       </c>
       <c r="G1664" t="n">
-        <v>0.317834973335266</v>
+        <v>0.317834943532944</v>
       </c>
       <c r="H1664" t="s">
         <v>8</v>
@@ -43659,7 +43659,7 @@
         <v>0.389999985694885</v>
       </c>
       <c r="G1665" t="n">
-        <v>0.32112854719162</v>
+        <v>0.321128517389297</v>
       </c>
       <c r="H1665" t="s">
         <v>8</v>
@@ -43685,7 +43685,7 @@
         <v>0.391000002622604</v>
       </c>
       <c r="G1666" t="n">
-        <v>0.32195195555687</v>
+        <v>0.321951985359192</v>
       </c>
       <c r="H1666" t="s">
         <v>8</v>
@@ -43711,7 +43711,7 @@
         <v>0.395000010728836</v>
       </c>
       <c r="G1667" t="n">
-        <v>0.325245589017868</v>
+        <v>0.32524561882019</v>
       </c>
       <c r="H1667" t="s">
         <v>8</v>
@@ -43789,7 +43789,7 @@
         <v>0.391999989748001</v>
       </c>
       <c r="G1670" t="n">
-        <v>0.322775393724442</v>
+        <v>0.322775363922119</v>
       </c>
       <c r="H1670" t="s">
         <v>8</v>
@@ -43815,7 +43815,7 @@
         <v>0.39300000667572</v>
       </c>
       <c r="G1671" t="n">
-        <v>0.323598802089691</v>
+        <v>0.323598831892014</v>
       </c>
       <c r="H1671" t="s">
         <v>8</v>
@@ -43841,7 +43841,7 @@
         <v>0.388000011444092</v>
       </c>
       <c r="G1672" t="n">
-        <v>0.319481790065765</v>
+        <v>0.319481760263443</v>
       </c>
       <c r="H1672" t="s">
         <v>8</v>
@@ -43893,7 +43893,7 @@
         <v>0.382999986410141</v>
       </c>
       <c r="G1674" t="n">
-        <v>0.315364688634872</v>
+        <v>0.315364718437195</v>
       </c>
       <c r="H1674" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>0.380499988794327</v>
       </c>
       <c r="G1675" t="n">
-        <v>0.313306212425232</v>
+        <v>0.31330618262291</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -44023,7 +44023,7 @@
         <v>0.375499993562698</v>
       </c>
       <c r="G1679" t="n">
-        <v>0.309189170598984</v>
+        <v>0.309189140796661</v>
       </c>
       <c r="H1679" t="s">
         <v>8</v>
@@ -44049,7 +44049,7 @@
         <v>0.375499993562698</v>
       </c>
       <c r="G1680" t="n">
-        <v>0.309189170598984</v>
+        <v>0.309189140796661</v>
       </c>
       <c r="H1680" t="s">
         <v>8</v>
@@ -44257,7 +44257,7 @@
         <v>0.389999985694885</v>
       </c>
       <c r="G1688" t="n">
-        <v>0.32112854719162</v>
+        <v>0.321128517389297</v>
       </c>
       <c r="H1688" t="s">
         <v>8</v>
@@ -44283,7 +44283,7 @@
         <v>0.386000007390976</v>
       </c>
       <c r="G1689" t="n">
-        <v>0.317834973335266</v>
+        <v>0.317834943532944</v>
       </c>
       <c r="H1689" t="s">
         <v>8</v>
@@ -44335,7 +44335,7 @@
         <v>0.385500013828278</v>
       </c>
       <c r="G1691" t="n">
-        <v>0.317423224449158</v>
+        <v>0.31742325425148</v>
       </c>
       <c r="H1691" t="s">
         <v>8</v>
@@ -44387,7 +44387,7 @@
         <v>0.378500014543533</v>
       </c>
       <c r="G1693" t="n">
-        <v>0.311659395694733</v>
+        <v>0.311659425497055</v>
       </c>
       <c r="H1693" t="s">
         <v>8</v>
@@ -44413,7 +44413,7 @@
         <v>0.382999986410141</v>
       </c>
       <c r="G1694" t="n">
-        <v>0.315364688634872</v>
+        <v>0.315364718437195</v>
       </c>
       <c r="H1694" t="s">
         <v>8</v>
@@ -44491,7 +44491,7 @@
         <v>0.379000008106232</v>
       </c>
       <c r="G1697" t="n">
-        <v>0.312071084976196</v>
+        <v>0.312071114778519</v>
       </c>
       <c r="H1697" t="s">
         <v>8</v>
@@ -44543,7 +44543,7 @@
         <v>0.380499988794327</v>
       </c>
       <c r="G1699" t="n">
-        <v>0.313306212425232</v>
+        <v>0.31330618262291</v>
       </c>
       <c r="H1699" t="s">
         <v>8</v>
@@ -44569,7 +44569,7 @@
         <v>0.382999986410141</v>
       </c>
       <c r="G1700" t="n">
-        <v>0.315364688634872</v>
+        <v>0.315364718437195</v>
       </c>
       <c r="H1700" t="s">
         <v>8</v>
@@ -44595,7 +44595,7 @@
         <v>0.386999994516373</v>
       </c>
       <c r="G1701" t="n">
-        <v>0.318658322095871</v>
+        <v>0.318658351898193</v>
       </c>
       <c r="H1701" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>0.38400000333786</v>
       </c>
       <c r="G1702" t="n">
-        <v>0.316188126802444</v>
+        <v>0.316188156604767</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44673,7 +44673,7 @@
         <v>0.38400000333786</v>
       </c>
       <c r="G1704" t="n">
-        <v>0.316188126802444</v>
+        <v>0.316188156604767</v>
       </c>
       <c r="H1704" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>0.386999994516373</v>
       </c>
       <c r="G1706" t="n">
-        <v>0.318658322095871</v>
+        <v>0.318658351898193</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44751,7 +44751,7 @@
         <v>0.382999986410141</v>
       </c>
       <c r="G1707" t="n">
-        <v>0.315364688634872</v>
+        <v>0.315364718437195</v>
       </c>
       <c r="H1707" t="s">
         <v>8</v>
@@ -44777,7 +44777,7 @@
         <v>0.388000011444092</v>
       </c>
       <c r="G1708" t="n">
-        <v>0.319481790065765</v>
+        <v>0.319481760263443</v>
       </c>
       <c r="H1708" t="s">
         <v>8</v>
@@ -44829,7 +44829,7 @@
         <v>0.370000004768372</v>
       </c>
       <c r="G1710" t="n">
-        <v>0.304660439491272</v>
+        <v>0.304660469293594</v>
       </c>
       <c r="H1710" t="s">
         <v>8</v>
@@ -44855,7 +44855,7 @@
         <v>0.375499993562698</v>
       </c>
       <c r="G1711" t="n">
-        <v>0.309189170598984</v>
+        <v>0.309189140796661</v>
       </c>
       <c r="H1711" t="s">
         <v>8</v>
@@ -44881,7 +44881,7 @@
         <v>0.375499993562698</v>
       </c>
       <c r="G1712" t="n">
-        <v>0.309189170598984</v>
+        <v>0.309189140796661</v>
       </c>
       <c r="H1712" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>0.368000000715256</v>
       </c>
       <c r="G1714" t="n">
-        <v>0.303013622760773</v>
+        <v>0.30301359295845</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -45011,7 +45011,7 @@
         <v>0.367500007152557</v>
       </c>
       <c r="G1717" t="n">
-        <v>0.302601933479309</v>
+        <v>0.302601903676987</v>
       </c>
       <c r="H1717" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>0.370000004768372</v>
       </c>
       <c r="G1718" t="n">
-        <v>0.304660439491272</v>
+        <v>0.304660469293594</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45063,7 +45063,7 @@
         <v>0.370000004768372</v>
       </c>
       <c r="G1719" t="n">
-        <v>0.304660439491272</v>
+        <v>0.304660469293594</v>
       </c>
       <c r="H1719" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>0.375499993562698</v>
       </c>
       <c r="G1720" t="n">
-        <v>0.309189170598984</v>
+        <v>0.309189140796661</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45115,7 +45115,7 @@
         <v>0.374000012874603</v>
       </c>
       <c r="G1721" t="n">
-        <v>0.307954072952271</v>
+        <v>0.307954102754593</v>
       </c>
       <c r="H1721" t="s">
         <v>8</v>
@@ -45167,7 +45167,7 @@
         <v>0.372000008821487</v>
       </c>
       <c r="G1723" t="n">
-        <v>0.306307286024094</v>
+        <v>0.306307256221771</v>
       </c>
       <c r="H1723" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>0.366499990224838</v>
       </c>
       <c r="G1724" t="n">
-        <v>0.301778525114059</v>
+        <v>0.301778495311737</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45219,7 +45219,7 @@
         <v>0.368999987840652</v>
       </c>
       <c r="G1725" t="n">
-        <v>0.303836971521378</v>
+        <v>0.3038370013237</v>
       </c>
       <c r="H1725" t="s">
         <v>8</v>
@@ -45245,7 +45245,7 @@
         <v>0.370000004768372</v>
       </c>
       <c r="G1726" t="n">
-        <v>0.304660439491272</v>
+        <v>0.304660469293594</v>
       </c>
       <c r="H1726" t="s">
         <v>8</v>
@@ -45271,7 +45271,7 @@
         <v>0.368999987840652</v>
       </c>
       <c r="G1727" t="n">
-        <v>0.303836971521378</v>
+        <v>0.3038370013237</v>
       </c>
       <c r="H1727" t="s">
         <v>8</v>
@@ -45297,7 +45297,7 @@
         <v>0.368999987840652</v>
       </c>
       <c r="G1728" t="n">
-        <v>0.303836971521378</v>
+        <v>0.3038370013237</v>
       </c>
       <c r="H1728" t="s">
         <v>8</v>
@@ -45323,7 +45323,7 @@
         <v>0.365500003099442</v>
       </c>
       <c r="G1729" t="n">
-        <v>0.300955086946487</v>
+        <v>0.30095511674881</v>
       </c>
       <c r="H1729" t="s">
         <v>8</v>
@@ -45349,7 +45349,7 @@
         <v>0.36599999666214</v>
       </c>
       <c r="G1730" t="n">
-        <v>0.301366806030273</v>
+        <v>0.301366835832596</v>
       </c>
       <c r="H1730" t="s">
         <v>8</v>
@@ -45401,7 +45401,7 @@
         <v>0.370000004768372</v>
       </c>
       <c r="G1732" t="n">
-        <v>0.304660439491272</v>
+        <v>0.304660469293594</v>
       </c>
       <c r="H1732" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>0.370000004768372</v>
       </c>
       <c r="G1733" t="n">
-        <v>0.304660439491272</v>
+        <v>0.304660469293594</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45453,7 +45453,7 @@
         <v>0.368000000715256</v>
       </c>
       <c r="G1734" t="n">
-        <v>0.303013622760773</v>
+        <v>0.30301359295845</v>
       </c>
       <c r="H1734" t="s">
         <v>8</v>
@@ -45479,7 +45479,7 @@
         <v>0.366499990224838</v>
       </c>
       <c r="G1735" t="n">
-        <v>0.301778525114059</v>
+        <v>0.301778495311737</v>
       </c>
       <c r="H1735" t="s">
         <v>8</v>
@@ -45557,7 +45557,7 @@
         <v>0.388000011444092</v>
       </c>
       <c r="G1738" t="n">
-        <v>0.319481790065765</v>
+        <v>0.319481760263443</v>
       </c>
       <c r="H1738" t="s">
         <v>8</v>
@@ -45661,7 +45661,7 @@
         <v>0.395000010728836</v>
       </c>
       <c r="G1742" t="n">
-        <v>0.325245589017868</v>
+        <v>0.32524561882019</v>
       </c>
       <c r="H1742" t="s">
         <v>8</v>
@@ -45713,7 +45713,7 @@
         <v>0.414499998092651</v>
       </c>
       <c r="G1744" t="n">
-        <v>0.341302037239075</v>
+        <v>0.341302007436752</v>
       </c>
       <c r="H1744" t="s">
         <v>8</v>
@@ -45739,7 +45739,7 @@
         <v>0.418500006198883</v>
       </c>
       <c r="G1745" t="n">
-        <v>0.344595700502396</v>
+        <v>0.344595670700073</v>
       </c>
       <c r="H1745" t="s">
         <v>8</v>
@@ -45765,7 +45765,7 @@
         <v>0.414000004529953</v>
       </c>
       <c r="G1746" t="n">
-        <v>0.340890347957611</v>
+        <v>0.340890318155289</v>
       </c>
       <c r="H1746" t="s">
         <v>8</v>
@@ -45791,7 +45791,7 @@
         <v>0.43299999833107</v>
       </c>
       <c r="G1747" t="n">
-        <v>0.356535047292709</v>
+        <v>0.356535077095032</v>
       </c>
       <c r="H1747" t="s">
         <v>8</v>
@@ -45843,7 +45843,7 @@
         <v>0.41499999165535</v>
       </c>
       <c r="G1749" t="n">
-        <v>0.341713726520538</v>
+        <v>0.341713756322861</v>
       </c>
       <c r="H1749" t="s">
         <v>8</v>
@@ -45895,7 +45895,7 @@
         <v>0.408499985933304</v>
       </c>
       <c r="G1751" t="n">
-        <v>0.336361587047577</v>
+        <v>0.336361557245255</v>
       </c>
       <c r="H1751" t="s">
         <v>8</v>
@@ -45921,7 +45921,7 @@
         <v>0.412000000476837</v>
       </c>
       <c r="G1752" t="n">
-        <v>0.339243531227112</v>
+        <v>0.339243501424789</v>
       </c>
       <c r="H1752" t="s">
         <v>8</v>
@@ -45947,7 +45947,7 @@
         <v>0.407000005245209</v>
       </c>
       <c r="G1753" t="n">
-        <v>0.335126489400864</v>
+        <v>0.335126459598541</v>
       </c>
       <c r="H1753" t="s">
         <v>8</v>
@@ -45973,7 +45973,7 @@
         <v>0.414000004529953</v>
       </c>
       <c r="G1754" t="n">
-        <v>0.340890347957611</v>
+        <v>0.340890318155289</v>
       </c>
       <c r="H1754" t="s">
         <v>8</v>
@@ -46051,7 +46051,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G1757" t="n">
-        <v>0.344183951616287</v>
+        <v>0.34418398141861</v>
       </c>
       <c r="H1757" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G1758" t="n">
-        <v>0.336773276329041</v>
+        <v>0.336773306131363</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46103,7 +46103,7 @@
         <v>0.41499999165535</v>
       </c>
       <c r="G1759" t="n">
-        <v>0.341713726520538</v>
+        <v>0.341713756322861</v>
       </c>
       <c r="H1759" t="s">
         <v>8</v>
@@ -46129,7 +46129,7 @@
         <v>0.41949999332428</v>
       </c>
       <c r="G1760" t="n">
-        <v>0.345419079065323</v>
+        <v>0.345419049263</v>
       </c>
       <c r="H1760" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>0.418500006198883</v>
       </c>
       <c r="G1761" t="n">
-        <v>0.344595700502396</v>
+        <v>0.344595670700073</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46285,7 +46285,7 @@
         <v>0.407999992370605</v>
       </c>
       <c r="G1766" t="n">
-        <v>0.335949867963791</v>
+        <v>0.335949897766113</v>
       </c>
       <c r="H1766" t="s">
         <v>8</v>
@@ -46363,7 +46363,7 @@
         <v>0.412000000476837</v>
       </c>
       <c r="G1769" t="n">
-        <v>0.339243531227112</v>
+        <v>0.339243501424789</v>
       </c>
       <c r="H1769" t="s">
         <v>8</v>
@@ -46415,7 +46415,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G1771" t="n">
-        <v>0.340066879987717</v>
+        <v>0.340066909790039</v>
       </c>
       <c r="H1771" t="s">
         <v>8</v>
@@ -46441,7 +46441,7 @@
         <v>0.41499999165535</v>
       </c>
       <c r="G1772" t="n">
-        <v>0.341713726520538</v>
+        <v>0.341713756322861</v>
       </c>
       <c r="H1772" t="s">
         <v>8</v>
@@ -46467,7 +46467,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G1773" t="n">
-        <v>0.340066879987717</v>
+        <v>0.340066909790039</v>
       </c>
       <c r="H1773" t="s">
         <v>8</v>
@@ -46493,7 +46493,7 @@
         <v>0.413500010967255</v>
       </c>
       <c r="G1774" t="n">
-        <v>0.340478599071503</v>
+        <v>0.340478628873825</v>
       </c>
       <c r="H1774" t="s">
         <v>8</v>
@@ -46545,7 +46545,7 @@
         <v>0.412499994039536</v>
       </c>
       <c r="G1776" t="n">
-        <v>0.339655220508575</v>
+        <v>0.339655190706253</v>
       </c>
       <c r="H1776" t="s">
         <v>8</v>
@@ -46571,7 +46571,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G1777" t="n">
-        <v>0.336773276329041</v>
+        <v>0.336773306131363</v>
       </c>
       <c r="H1777" t="s">
         <v>8</v>
@@ -46649,7 +46649,7 @@
         <v>0.395500004291534</v>
       </c>
       <c r="G1780" t="n">
-        <v>0.325657308101654</v>
+        <v>0.325657337903976</v>
       </c>
       <c r="H1780" t="s">
         <v>8</v>
@@ -46727,7 +46727,7 @@
         <v>0.407000005245209</v>
       </c>
       <c r="G1783" t="n">
-        <v>0.335126489400864</v>
+        <v>0.335126459598541</v>
       </c>
       <c r="H1783" t="s">
         <v>8</v>
@@ -46805,7 +46805,7 @@
         <v>0.414000004529953</v>
       </c>
       <c r="G1786" t="n">
-        <v>0.340890347957611</v>
+        <v>0.340890318155289</v>
       </c>
       <c r="H1786" t="s">
         <v>8</v>
@@ -46857,7 +46857,7 @@
         <v>0.414499998092651</v>
       </c>
       <c r="G1788" t="n">
-        <v>0.341302037239075</v>
+        <v>0.341302007436752</v>
       </c>
       <c r="H1788" t="s">
         <v>8</v>
@@ -46961,7 +46961,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G1792" t="n">
-        <v>0.336773276329041</v>
+        <v>0.336773306131363</v>
       </c>
       <c r="H1792" t="s">
         <v>8</v>
@@ -46987,7 +46987,7 @@
         <v>0.41499999165535</v>
       </c>
       <c r="G1793" t="n">
-        <v>0.341713726520538</v>
+        <v>0.341713756322861</v>
       </c>
       <c r="H1793" t="s">
         <v>8</v>
@@ -47039,7 +47039,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G1795" t="n">
-        <v>0.35571163892746</v>
+        <v>0.355711668729782</v>
       </c>
       <c r="H1795" t="s">
         <v>8</v>
@@ -47065,7 +47065,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G1796" t="n">
-        <v>0.359005302190781</v>
+        <v>0.359005272388458</v>
       </c>
       <c r="H1796" t="s">
         <v>8</v>
@@ -47117,7 +47117,7 @@
         <v>0.458999991416931</v>
       </c>
       <c r="G1798" t="n">
-        <v>0.377943634986877</v>
+        <v>0.377943605184555</v>
       </c>
       <c r="H1798" t="s">
         <v>8</v>
@@ -47169,7 +47169,7 @@
         <v>0.474000006914139</v>
       </c>
       <c r="G1800" t="n">
-        <v>0.390294700860977</v>
+        <v>0.3902947306633</v>
       </c>
       <c r="H1800" t="s">
         <v>8</v>
@@ -47195,7 +47195,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1801" t="n">
-        <v>0.395235121250153</v>
+        <v>0.39523509144783</v>
       </c>
       <c r="H1801" t="s">
         <v>8</v>
@@ -47247,7 +47247,7 @@
         <v>0.47299998998642</v>
       </c>
       <c r="G1803" t="n">
-        <v>0.38947132229805</v>
+        <v>0.389471292495728</v>
       </c>
       <c r="H1803" t="s">
         <v>8</v>
@@ -47351,7 +47351,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1807" t="n">
-        <v>0.403469234704971</v>
+        <v>0.403469204902649</v>
       </c>
       <c r="H1807" t="s">
         <v>8</v>
@@ -47533,7 +47533,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1814" t="n">
-        <v>0.395235121250153</v>
+        <v>0.39523509144783</v>
       </c>
       <c r="H1814" t="s">
         <v>8</v>
@@ -47663,7 +47663,7 @@
         <v>0.489499986171722</v>
       </c>
       <c r="G1819" t="n">
-        <v>0.403057515621185</v>
+        <v>0.403057545423508</v>
       </c>
       <c r="H1819" t="s">
         <v>8</v>
@@ -47689,7 +47689,7 @@
         <v>0.479499995708466</v>
       </c>
       <c r="G1820" t="n">
-        <v>0.394823461771011</v>
+        <v>0.394823491573334</v>
       </c>
       <c r="H1820" t="s">
         <v>8</v>
@@ -47741,7 +47741,7 @@
         <v>0.507000029087067</v>
       </c>
       <c r="G1822" t="n">
-        <v>0.417467176914215</v>
+        <v>0.417467147111893</v>
       </c>
       <c r="H1822" t="s">
         <v>8</v>
@@ -47767,7 +47767,7 @@
         <v>0.526000022888184</v>
       </c>
       <c r="G1823" t="n">
-        <v>0.433111846446991</v>
+        <v>0.433111876249313</v>
       </c>
       <c r="H1823" t="s">
         <v>8</v>
@@ -47793,7 +47793,7 @@
         <v>0.523000001907349</v>
       </c>
       <c r="G1824" t="n">
-        <v>0.430641651153564</v>
+        <v>0.430641621351242</v>
       </c>
       <c r="H1824" t="s">
         <v>8</v>
@@ -47897,7 +47897,7 @@
         <v>0.592999994754791</v>
       </c>
       <c r="G1828" t="n">
-        <v>0.488280087709427</v>
+        <v>0.488280147314072</v>
       </c>
       <c r="H1828" t="s">
         <v>8</v>
@@ -47949,7 +47949,7 @@
         <v>0.648999989032745</v>
       </c>
       <c r="G1830" t="n">
-        <v>0.534390807151794</v>
+        <v>0.534390866756439</v>
       </c>
       <c r="H1830" t="s">
         <v>8</v>
@@ -47975,7 +47975,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1831" t="n">
-        <v>0.518746137619019</v>
+        <v>0.518746197223663</v>
       </c>
       <c r="H1831" t="s">
         <v>8</v>
@@ -48105,7 +48105,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1836" t="n">
-        <v>0.485809862613678</v>
+        <v>0.485809892416</v>
       </c>
       <c r="H1836" t="s">
         <v>8</v>
@@ -48131,7 +48131,7 @@
         <v>0.561999976634979</v>
       </c>
       <c r="G1837" t="n">
-        <v>0.462754487991333</v>
+        <v>0.462754458189011</v>
       </c>
       <c r="H1837" t="s">
         <v>8</v>
@@ -48157,7 +48157,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G1838" t="n">
-        <v>0.472635358572006</v>
+        <v>0.472635388374329</v>
       </c>
       <c r="H1838" t="s">
         <v>8</v>
@@ -48209,7 +48209,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G1840" t="n">
-        <v>0.472635358572006</v>
+        <v>0.472635388374329</v>
       </c>
       <c r="H1840" t="s">
         <v>8</v>
@@ -48261,7 +48261,7 @@
         <v>0.597000002861023</v>
       </c>
       <c r="G1842" t="n">
-        <v>0.491573691368103</v>
+        <v>0.491573721170425</v>
       </c>
       <c r="H1842" t="s">
         <v>8</v>
@@ -48287,7 +48287,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1843" t="n">
-        <v>0.48169282078743</v>
+        <v>0.481692880392075</v>
       </c>
       <c r="H1843" t="s">
         <v>8</v>
@@ -48313,7 +48313,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G1844" t="n">
-        <v>0.467694878578186</v>
+        <v>0.467694908380508</v>
       </c>
       <c r="H1844" t="s">
         <v>8</v>
@@ -48391,7 +48391,7 @@
         <v>0.578999996185303</v>
       </c>
       <c r="G1847" t="n">
-        <v>0.476752400398254</v>
+        <v>0.476752430200577</v>
       </c>
       <c r="H1847" t="s">
         <v>8</v>
@@ -48417,7 +48417,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1848" t="n">
-        <v>0.48169282078743</v>
+        <v>0.481692880392075</v>
       </c>
       <c r="H1848" t="s">
         <v>8</v>
@@ -48443,7 +48443,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G1849" t="n">
-        <v>0.479222595691681</v>
+        <v>0.479222625494003</v>
       </c>
       <c r="H1849" t="s">
         <v>8</v>
@@ -48469,7 +48469,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1850" t="n">
-        <v>0.477575898170471</v>
+        <v>0.477575838565826</v>
       </c>
       <c r="H1850" t="s">
         <v>8</v>
@@ -48495,7 +48495,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1851" t="n">
-        <v>0.477575898170471</v>
+        <v>0.477575838565826</v>
       </c>
       <c r="H1851" t="s">
         <v>8</v>
@@ -48521,7 +48521,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1852" t="n">
-        <v>0.485809862613678</v>
+        <v>0.485809892416</v>
       </c>
       <c r="H1852" t="s">
         <v>8</v>
@@ -48599,7 +48599,7 @@
         <v>0.609000027179718</v>
       </c>
       <c r="G1855" t="n">
-        <v>0.501454591751099</v>
+        <v>0.501454651355743</v>
       </c>
       <c r="H1855" t="s">
         <v>8</v>
@@ -48625,7 +48625,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G1856" t="n">
-        <v>0.498984456062317</v>
+        <v>0.498984396457672</v>
       </c>
       <c r="H1856" t="s">
         <v>8</v>
@@ -48651,7 +48651,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1857" t="n">
-        <v>0.494043976068497</v>
+        <v>0.494043916463852</v>
       </c>
       <c r="H1857" t="s">
         <v>8</v>
@@ -48703,7 +48703,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G1859" t="n">
-        <v>0.490750372409821</v>
+        <v>0.490750312805176</v>
       </c>
       <c r="H1859" t="s">
         <v>8</v>
@@ -48729,7 +48729,7 @@
         <v>0.58899998664856</v>
       </c>
       <c r="G1860" t="n">
-        <v>0.484986424446106</v>
+        <v>0.484986454248428</v>
       </c>
       <c r="H1860" t="s">
         <v>8</v>
@@ -48755,7 +48755,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1861" t="n">
-        <v>0.492397129535675</v>
+        <v>0.492397099733353</v>
       </c>
       <c r="H1861" t="s">
         <v>8</v>
@@ -48781,7 +48781,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1862" t="n">
-        <v>0.482516258955002</v>
+        <v>0.482516318559647</v>
       </c>
       <c r="H1862" t="s">
         <v>8</v>
@@ -48807,7 +48807,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G1863" t="n">
-        <v>0.479222595691681</v>
+        <v>0.479222625494003</v>
       </c>
       <c r="H1863" t="s">
         <v>8</v>
@@ -48833,7 +48833,7 @@
         <v>0.58899998664856</v>
       </c>
       <c r="G1864" t="n">
-        <v>0.484986424446106</v>
+        <v>0.484986454248428</v>
       </c>
       <c r="H1864" t="s">
         <v>8</v>
@@ -48859,7 +48859,7 @@
         <v>0.580999970436096</v>
       </c>
       <c r="G1865" t="n">
-        <v>0.478399157524109</v>
+        <v>0.478399187326431</v>
       </c>
       <c r="H1865" t="s">
         <v>8</v>
@@ -48885,7 +48885,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1866" t="n">
-        <v>0.473458737134933</v>
+        <v>0.473458766937256</v>
       </c>
       <c r="H1866" t="s">
         <v>8</v>
@@ -48911,7 +48911,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G1867" t="n">
-        <v>0.467694878578186</v>
+        <v>0.467694908380508</v>
       </c>
       <c r="H1867" t="s">
         <v>8</v>
@@ -48937,7 +48937,7 @@
         <v>0.572000026702881</v>
       </c>
       <c r="G1868" t="n">
-        <v>0.470988541841507</v>
+        <v>0.470988571643829</v>
       </c>
       <c r="H1868" t="s">
         <v>8</v>
@@ -48963,7 +48963,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1869" t="n">
-        <v>0.48169282078743</v>
+        <v>0.481692880392075</v>
       </c>
       <c r="H1869" t="s">
         <v>8</v>
@@ -48989,7 +48989,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G1870" t="n">
-        <v>0.490750372409821</v>
+        <v>0.490750312805176</v>
       </c>
       <c r="H1870" t="s">
         <v>8</v>
@@ -49015,7 +49015,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1871" t="n">
-        <v>0.485809862613678</v>
+        <v>0.485809892416</v>
       </c>
       <c r="H1871" t="s">
         <v>8</v>
@@ -49041,7 +49041,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1872" t="n">
-        <v>0.492397129535675</v>
+        <v>0.492397099733353</v>
       </c>
       <c r="H1872" t="s">
         <v>8</v>
@@ -49067,7 +49067,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G1873" t="n">
-        <v>0.472635358572006</v>
+        <v>0.472635388374329</v>
       </c>
       <c r="H1873" t="s">
         <v>8</v>
@@ -49093,7 +49093,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G1874" t="n">
-        <v>0.479222595691681</v>
+        <v>0.479222625494003</v>
       </c>
       <c r="H1874" t="s">
         <v>8</v>
@@ -49275,7 +49275,7 @@
         <v>0.53600001335144</v>
       </c>
       <c r="G1881" t="n">
-        <v>0.473822325468063</v>
+        <v>0.473822295665741</v>
       </c>
       <c r="H1881" t="s">
         <v>8</v>
@@ -49301,7 +49301,7 @@
         <v>0.51800000667572</v>
       </c>
       <c r="G1882" t="n">
-        <v>0.457910388708115</v>
+        <v>0.457910358905792</v>
       </c>
       <c r="H1882" t="s">
         <v>8</v>
@@ -49327,7 +49327,7 @@
         <v>0.522000014781952</v>
       </c>
       <c r="G1883" t="n">
-        <v>0.461446404457092</v>
+        <v>0.461446434259415</v>
       </c>
       <c r="H1883" t="s">
         <v>8</v>
@@ -49457,7 +49457,7 @@
         <v>0.493000000715256</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.435810476541519</v>
+        <v>0.435810446739197</v>
       </c>
       <c r="H1888" t="s">
         <v>8</v>
@@ -49509,7 +49509,7 @@
         <v>0.483500003814697</v>
       </c>
       <c r="G1890" t="n">
-        <v>0.427412509918213</v>
+        <v>0.427412480115891</v>
       </c>
       <c r="H1890" t="s">
         <v>8</v>
@@ -49561,7 +49561,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1892" t="n">
-        <v>0.433158487081528</v>
+        <v>0.433158457279205</v>
       </c>
       <c r="H1892" t="s">
         <v>8</v>
@@ -49613,7 +49613,7 @@
         <v>0.5</v>
       </c>
       <c r="G1894" t="n">
-        <v>0.441998451948166</v>
+        <v>0.441998422145844</v>
       </c>
       <c r="H1894" t="s">
         <v>8</v>
@@ -49639,7 +49639,7 @@
         <v>0.491499990224838</v>
       </c>
       <c r="G1895" t="n">
-        <v>0.434484422206879</v>
+        <v>0.434484452009201</v>
       </c>
       <c r="H1895" t="s">
         <v>8</v>
@@ -49665,7 +49665,7 @@
         <v>0.503000020980835</v>
       </c>
       <c r="G1896" t="n">
-        <v>0.44465047121048</v>
+        <v>0.444650441408157</v>
       </c>
       <c r="H1896" t="s">
         <v>8</v>
@@ -49717,7 +49717,7 @@
         <v>0.495000004768372</v>
       </c>
       <c r="G1898" t="n">
-        <v>0.437578439712524</v>
+        <v>0.437578469514847</v>
       </c>
       <c r="H1898" t="s">
         <v>8</v>
@@ -49743,7 +49743,7 @@
         <v>0.490500003099442</v>
       </c>
       <c r="G1899" t="n">
-        <v>0.433600455522537</v>
+        <v>0.43360048532486</v>
       </c>
       <c r="H1899" t="s">
         <v>8</v>
@@ -49821,7 +49821,7 @@
         <v>0.492000013589859</v>
       </c>
       <c r="G1902" t="n">
-        <v>0.434926480054855</v>
+        <v>0.434926450252533</v>
       </c>
       <c r="H1902" t="s">
         <v>8</v>
@@ -49899,7 +49899,7 @@
         <v>0.483500003814697</v>
       </c>
       <c r="G1905" t="n">
-        <v>0.427412509918213</v>
+        <v>0.427412480115891</v>
       </c>
       <c r="H1905" t="s">
         <v>8</v>
@@ -49925,7 +49925,7 @@
         <v>0.485000014305115</v>
       </c>
       <c r="G1906" t="n">
-        <v>0.428738474845886</v>
+        <v>0.428738504648209</v>
       </c>
       <c r="H1906" t="s">
         <v>8</v>
@@ -50003,7 +50003,7 @@
         <v>0.49099999666214</v>
       </c>
       <c r="G1909" t="n">
-        <v>0.434042483568192</v>
+        <v>0.434042453765869</v>
       </c>
       <c r="H1909" t="s">
         <v>8</v>
@@ -50029,7 +50029,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1910" t="n">
-        <v>0.433158487081528</v>
+        <v>0.433158457279205</v>
       </c>
       <c r="H1910" t="s">
         <v>8</v>
@@ -50081,7 +50081,7 @@
         <v>0.495000004768372</v>
       </c>
       <c r="G1912" t="n">
-        <v>0.437578439712524</v>
+        <v>0.437578469514847</v>
       </c>
       <c r="H1912" t="s">
         <v>8</v>
@@ -50237,7 +50237,7 @@
         <v>0.465999990701675</v>
       </c>
       <c r="G1918" t="n">
-        <v>0.411942541599274</v>
+        <v>0.411942511796951</v>
       </c>
       <c r="H1918" t="s">
         <v>8</v>
@@ -50315,7 +50315,7 @@
         <v>0.47299998998642</v>
       </c>
       <c r="G1921" t="n">
-        <v>0.41813051700592</v>
+        <v>0.418130487203598</v>
       </c>
       <c r="H1921" t="s">
         <v>8</v>
@@ -50367,7 +50367,7 @@
         <v>0.467999994754791</v>
       </c>
       <c r="G1923" t="n">
-        <v>0.413710504770279</v>
+        <v>0.413710564374924</v>
       </c>
       <c r="H1923" t="s">
         <v>8</v>
@@ -50419,7 +50419,7 @@
         <v>0.481000006198883</v>
       </c>
       <c r="G1925" t="n">
-        <v>0.425202488899231</v>
+        <v>0.425202518701553</v>
       </c>
       <c r="H1925" t="s">
         <v>8</v>
@@ -50445,7 +50445,7 @@
         <v>0.479499995708466</v>
       </c>
       <c r="G1926" t="n">
-        <v>0.423876494169235</v>
+        <v>0.423876523971558</v>
       </c>
       <c r="H1926" t="s">
         <v>8</v>
@@ -50549,7 +50549,7 @@
         <v>0.481000006198883</v>
       </c>
       <c r="G1930" t="n">
-        <v>0.425202488899231</v>
+        <v>0.425202518701553</v>
       </c>
       <c r="H1930" t="s">
         <v>8</v>
@@ -50575,7 +50575,7 @@
         <v>0.47299998998642</v>
       </c>
       <c r="G1931" t="n">
-        <v>0.41813051700592</v>
+        <v>0.418130487203598</v>
       </c>
       <c r="H1931" t="s">
         <v>8</v>
@@ -50601,7 +50601,7 @@
         <v>0.476500004529953</v>
       </c>
       <c r="G1932" t="n">
-        <v>0.421224534511566</v>
+        <v>0.421224504709244</v>
       </c>
       <c r="H1932" t="s">
         <v>8</v>
@@ -50627,7 +50627,7 @@
         <v>0.467500001192093</v>
       </c>
       <c r="G1933" t="n">
-        <v>0.413268536329269</v>
+        <v>0.413268506526947</v>
       </c>
       <c r="H1933" t="s">
         <v>8</v>
@@ -50705,7 +50705,7 @@
         <v>0.462000012397766</v>
       </c>
       <c r="G1936" t="n">
-        <v>0.408406585454941</v>
+        <v>0.408406555652618</v>
       </c>
       <c r="H1936" t="s">
         <v>8</v>
@@ -50783,7 +50783,7 @@
         <v>0.465000003576279</v>
       </c>
       <c r="G1939" t="n">
-        <v>0.41105854511261</v>
+        <v>0.411058574914932</v>
       </c>
       <c r="H1939" t="s">
         <v>8</v>
@@ -50861,7 +50861,7 @@
         <v>0.467999994754791</v>
       </c>
       <c r="G1942" t="n">
-        <v>0.413710504770279</v>
+        <v>0.413710564374924</v>
       </c>
       <c r="H1942" t="s">
         <v>8</v>
@@ -50887,7 +50887,7 @@
         <v>0.461499989032745</v>
       </c>
       <c r="G1943" t="n">
-        <v>0.407964527606964</v>
+        <v>0.407964557409286</v>
       </c>
       <c r="H1943" t="s">
         <v>8</v>
@@ -50913,7 +50913,7 @@
         <v>0.479000002145767</v>
       </c>
       <c r="G1944" t="n">
-        <v>0.423434525728226</v>
+        <v>0.423434495925903</v>
       </c>
       <c r="H1944" t="s">
         <v>8</v>
@@ -50991,7 +50991,7 @@
         <v>0.475499987602234</v>
       </c>
       <c r="G1947" t="n">
-        <v>0.420340478420258</v>
+        <v>0.42034050822258</v>
       </c>
       <c r="H1947" t="s">
         <v>8</v>
@@ -51199,7 +51199,7 @@
         <v>0.49099999666214</v>
       </c>
       <c r="G1955" t="n">
-        <v>0.434042483568192</v>
+        <v>0.434042453765869</v>
       </c>
       <c r="H1955" t="s">
         <v>8</v>
@@ -51251,7 +51251,7 @@
         <v>0.480500012636185</v>
       </c>
       <c r="G1957" t="n">
-        <v>0.424760520458221</v>
+        <v>0.424760490655899</v>
       </c>
       <c r="H1957" t="s">
         <v>8</v>
@@ -51303,7 +51303,7 @@
         <v>0.479499995708466</v>
       </c>
       <c r="G1959" t="n">
-        <v>0.423876494169235</v>
+        <v>0.423876523971558</v>
       </c>
       <c r="H1959" t="s">
         <v>8</v>
@@ -51355,7 +51355,7 @@
         <v>0.47749999165535</v>
       </c>
       <c r="G1961" t="n">
-        <v>0.422108471393585</v>
+        <v>0.422108501195908</v>
       </c>
       <c r="H1961" t="s">
         <v>8</v>
@@ -51381,7 +51381,7 @@
         <v>0.469999998807907</v>
       </c>
       <c r="G1962" t="n">
-        <v>0.415478527545929</v>
+        <v>0.415478557348251</v>
       </c>
       <c r="H1962" t="s">
         <v>8</v>
@@ -51407,7 +51407,7 @@
         <v>0.465999990701675</v>
       </c>
       <c r="G1963" t="n">
-        <v>0.411942541599274</v>
+        <v>0.411942511796951</v>
       </c>
       <c r="H1963" t="s">
         <v>8</v>
@@ -51537,7 +51537,7 @@
         <v>0.467999994754791</v>
       </c>
       <c r="G1968" t="n">
-        <v>0.413710504770279</v>
+        <v>0.413710564374924</v>
       </c>
       <c r="H1968" t="s">
         <v>8</v>
@@ -51667,7 +51667,7 @@
         <v>0.458999991416931</v>
       </c>
       <c r="G1973" t="n">
-        <v>0.405754566192627</v>
+        <v>0.405754595994949</v>
       </c>
       <c r="H1973" t="s">
         <v>8</v>
@@ -51693,7 +51693,7 @@
         <v>0.456499993801117</v>
       </c>
       <c r="G1974" t="n">
-        <v>0.403544574975967</v>
+        <v>0.403544545173645</v>
       </c>
       <c r="H1974" t="s">
         <v>8</v>
@@ -51771,7 +51771,7 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G1977" t="n">
-        <v>0.388958603143692</v>
+        <v>0.388958632946014</v>
       </c>
       <c r="H1977" t="s">
         <v>8</v>
@@ -51875,7 +51875,7 @@
         <v>0.462000012397766</v>
       </c>
       <c r="G1981" t="n">
-        <v>0.408406585454941</v>
+        <v>0.408406555652618</v>
       </c>
       <c r="H1981" t="s">
         <v>8</v>
@@ -51901,7 +51901,7 @@
         <v>0.458999991416931</v>
       </c>
       <c r="G1982" t="n">
-        <v>0.405754566192627</v>
+        <v>0.405754595994949</v>
       </c>
       <c r="H1982" t="s">
         <v>8</v>
@@ -51979,7 +51979,7 @@
         <v>0.465000003576279</v>
       </c>
       <c r="G1985" t="n">
-        <v>0.41105854511261</v>
+        <v>0.411058574914932</v>
       </c>
       <c r="H1985" t="s">
         <v>8</v>
@@ -52005,7 +52005,7 @@
         <v>0.456000000238419</v>
       </c>
       <c r="G1986" t="n">
-        <v>0.403102546930313</v>
+        <v>0.403102576732635</v>
       </c>
       <c r="H1986" t="s">
         <v>8</v>
@@ -52109,7 +52109,7 @@
         <v>0.454499989748001</v>
       </c>
       <c r="G1990" t="n">
-        <v>0.40177658200264</v>
+        <v>0.401776552200317</v>
       </c>
       <c r="H1990" t="s">
         <v>8</v>
@@ -52161,7 +52161,7 @@
         <v>0.465999990701675</v>
       </c>
       <c r="G1992" t="n">
-        <v>0.411942541599274</v>
+        <v>0.411942511796951</v>
       </c>
       <c r="H1992" t="s">
         <v>8</v>
@@ -52213,7 +52213,7 @@
         <v>0.467999994754791</v>
       </c>
       <c r="G1994" t="n">
-        <v>0.413710504770279</v>
+        <v>0.413710564374924</v>
       </c>
       <c r="H1994" t="s">
         <v>8</v>
@@ -52291,7 +52291,7 @@
         <v>0.469999998807907</v>
       </c>
       <c r="G1997" t="n">
-        <v>0.415478527545929</v>
+        <v>0.415478557348251</v>
       </c>
       <c r="H1997" t="s">
         <v>8</v>
@@ -52317,7 +52317,7 @@
         <v>0.467500001192093</v>
       </c>
       <c r="G1998" t="n">
-        <v>0.413268536329269</v>
+        <v>0.413268506526947</v>
       </c>
       <c r="H1998" t="s">
         <v>8</v>
@@ -52343,7 +52343,7 @@
         <v>0.462000012397766</v>
       </c>
       <c r="G1999" t="n">
-        <v>0.408406585454941</v>
+        <v>0.408406555652618</v>
       </c>
       <c r="H1999" t="s">
         <v>8</v>
@@ -52369,7 +52369,7 @@
         <v>0.45550000667572</v>
       </c>
       <c r="G2000" t="n">
-        <v>0.402660578489304</v>
+        <v>0.402660608291626</v>
       </c>
       <c r="H2000" t="s">
         <v>8</v>
@@ -52395,7 +52395,7 @@
         <v>0.476500004529953</v>
       </c>
       <c r="G2001" t="n">
-        <v>0.421224534511566</v>
+        <v>0.421224504709244</v>
       </c>
       <c r="H2001" t="s">
         <v>8</v>
@@ -52525,7 +52525,7 @@
         <v>0.5</v>
       </c>
       <c r="G2006" t="n">
-        <v>0.441998451948166</v>
+        <v>0.441998422145844</v>
       </c>
       <c r="H2006" t="s">
         <v>8</v>
@@ -52551,7 +52551,7 @@
         <v>0.493999987840652</v>
       </c>
       <c r="G2007" t="n">
-        <v>0.436694413423538</v>
+        <v>0.436694473028183</v>
       </c>
       <c r="H2007" t="s">
         <v>8</v>
@@ -52655,7 +52655,7 @@
         <v>0.497500002384186</v>
       </c>
       <c r="G2011" t="n">
-        <v>0.453334271907806</v>
+        <v>0.453334301710129</v>
       </c>
       <c r="H2011" t="s">
         <v>8</v>
@@ -52707,7 +52707,7 @@
         <v>0.497500002384186</v>
       </c>
       <c r="G2013" t="n">
-        <v>0.453334271907806</v>
+        <v>0.453334301710129</v>
       </c>
       <c r="H2013" t="s">
         <v>8</v>
@@ -52759,7 +52759,7 @@
         <v>0.500999987125397</v>
       </c>
       <c r="G2015" t="n">
-        <v>0.456523567438126</v>
+        <v>0.456523537635803</v>
       </c>
       <c r="H2015" t="s">
         <v>8</v>
@@ -52785,7 +52785,7 @@
         <v>0.510999977588654</v>
       </c>
       <c r="G2016" t="n">
-        <v>0.465635776519775</v>
+        <v>0.465635806322098</v>
       </c>
       <c r="H2016" t="s">
         <v>8</v>
@@ -52837,7 +52837,7 @@
         <v>0.513999998569489</v>
       </c>
       <c r="G2018" t="n">
-        <v>0.468369513750076</v>
+        <v>0.468369483947754</v>
       </c>
       <c r="H2018" t="s">
         <v>8</v>
@@ -52863,7 +52863,7 @@
         <v>0.52700001001358</v>
       </c>
       <c r="G2019" t="n">
-        <v>0.480215400457382</v>
+        <v>0.480215430259705</v>
       </c>
       <c r="H2019" t="s">
         <v>8</v>
@@ -52889,7 +52889,7 @@
         <v>0.52700001001358</v>
       </c>
       <c r="G2020" t="n">
-        <v>0.480215400457382</v>
+        <v>0.480215430259705</v>
       </c>
       <c r="H2020" t="s">
         <v>8</v>
@@ -52915,7 +52915,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G2021" t="n">
-        <v>0.482949018478394</v>
+        <v>0.482949078083038</v>
       </c>
       <c r="H2021" t="s">
         <v>8</v>
@@ -52941,7 +52941,7 @@
         <v>0.527999997138977</v>
       </c>
       <c r="G2022" t="n">
-        <v>0.481126666069031</v>
+        <v>0.481126606464386</v>
       </c>
       <c r="H2022" t="s">
         <v>8</v>
@@ -52993,7 +52993,7 @@
         <v>0.52700001001358</v>
       </c>
       <c r="G2024" t="n">
-        <v>0.480215400457382</v>
+        <v>0.480215430259705</v>
       </c>
       <c r="H2024" t="s">
         <v>8</v>
@@ -53019,7 +53019,7 @@
         <v>0.526000022888184</v>
       </c>
       <c r="G2025" t="n">
-        <v>0.479304224252701</v>
+        <v>0.479304194450378</v>
       </c>
       <c r="H2025" t="s">
         <v>8</v>
@@ -53175,7 +53175,7 @@
         <v>0.580999970436096</v>
       </c>
       <c r="G2031" t="n">
-        <v>0.529421508312225</v>
+        <v>0.529421448707581</v>
       </c>
       <c r="H2031" t="s">
         <v>8</v>
@@ -53331,7 +53331,7 @@
         <v>0.565999984741211</v>
       </c>
       <c r="G2037" t="n">
-        <v>0.515753209590912</v>
+        <v>0.515753149986267</v>
       </c>
       <c r="H2037" t="s">
         <v>8</v>
@@ -53357,7 +53357,7 @@
         <v>0.556999981403351</v>
       </c>
       <c r="G2038" t="n">
-        <v>0.507552146911621</v>
+        <v>0.507552087306976</v>
       </c>
       <c r="H2038" t="s">
         <v>8</v>
@@ -53383,7 +53383,7 @@
         <v>0.560999989509583</v>
       </c>
       <c r="G2039" t="n">
-        <v>0.511197090148926</v>
+        <v>0.511197030544281</v>
       </c>
       <c r="H2039" t="s">
         <v>8</v>
@@ -53409,7 +53409,7 @@
         <v>0.564999997615814</v>
       </c>
       <c r="G2040" t="n">
-        <v>0.514841914176941</v>
+        <v>0.514841973781586</v>
       </c>
       <c r="H2040" t="s">
         <v>8</v>
@@ -53435,7 +53435,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2041" t="n">
-        <v>0.519398033618927</v>
+        <v>0.519398093223572</v>
       </c>
       <c r="H2041" t="s">
         <v>8</v>
@@ -53461,7 +53461,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G2042" t="n">
-        <v>0.513930678367615</v>
+        <v>0.51393073797226</v>
       </c>
       <c r="H2042" t="s">
         <v>8</v>
@@ -53539,7 +53539,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G2045" t="n">
-        <v>0.513930678367615</v>
+        <v>0.51393073797226</v>
       </c>
       <c r="H2045" t="s">
         <v>8</v>
@@ -53617,7 +53617,7 @@
         <v>0.560999989509583</v>
       </c>
       <c r="G2048" t="n">
-        <v>0.511197090148926</v>
+        <v>0.511197030544281</v>
       </c>
       <c r="H2048" t="s">
         <v>8</v>
@@ -53643,7 +53643,7 @@
         <v>0.559000015258789</v>
       </c>
       <c r="G2049" t="n">
-        <v>0.509374558925629</v>
+        <v>0.509374618530273</v>
       </c>
       <c r="H2049" t="s">
         <v>8</v>
@@ -53669,7 +53669,7 @@
         <v>0.565999984741211</v>
       </c>
       <c r="G2050" t="n">
-        <v>0.515753209590912</v>
+        <v>0.515753149986267</v>
       </c>
       <c r="H2050" t="s">
         <v>8</v>
@@ -53695,7 +53695,7 @@
         <v>0.578000009059906</v>
       </c>
       <c r="G2051" t="n">
-        <v>0.526687920093536</v>
+        <v>0.526687860488892</v>
       </c>
       <c r="H2051" t="s">
         <v>8</v>
@@ -53747,7 +53747,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G2053" t="n">
-        <v>0.541267454624176</v>
+        <v>0.541267395019531</v>
       </c>
       <c r="H2053" t="s">
         <v>8</v>
@@ -53773,7 +53773,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2054" t="n">
-        <v>0.546734869480133</v>
+        <v>0.546734809875488</v>
       </c>
       <c r="H2054" t="s">
         <v>8</v>
@@ -53799,7 +53799,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2055" t="n">
-        <v>0.546734869480133</v>
+        <v>0.546734809875488</v>
       </c>
       <c r="H2055" t="s">
         <v>8</v>
@@ -53903,7 +53903,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2059" t="n">
-        <v>0.546734869480133</v>
+        <v>0.546734809875488</v>
       </c>
       <c r="H2059" t="s">
         <v>8</v>
@@ -53955,7 +53955,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G2061" t="n">
-        <v>0.564959287643433</v>
+        <v>0.564959347248077</v>
       </c>
       <c r="H2061" t="s">
         <v>8</v>
@@ -54111,7 +54111,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G2067" t="n">
-        <v>0.550379633903503</v>
+        <v>0.550379693508148</v>
       </c>
       <c r="H2067" t="s">
         <v>8</v>
@@ -54241,7 +54241,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2072" t="n">
-        <v>0.546734869480133</v>
+        <v>0.546734809875488</v>
       </c>
       <c r="H2072" t="s">
         <v>8</v>
@@ -54319,7 +54319,7 @@
         <v>0.60699999332428</v>
       </c>
       <c r="G2075" t="n">
-        <v>0.553113341331482</v>
+        <v>0.553113400936127</v>
       </c>
       <c r="H2075" t="s">
         <v>8</v>
@@ -54371,7 +54371,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G2077" t="n">
-        <v>0.564959287643433</v>
+        <v>0.564959347248077</v>
       </c>
       <c r="H2077" t="s">
         <v>8</v>
@@ -54423,7 +54423,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G2079" t="n">
-        <v>0.561314344406128</v>
+        <v>0.561314404010773</v>
       </c>
       <c r="H2079" t="s">
         <v>8</v>
@@ -54501,7 +54501,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G2082" t="n">
-        <v>0.542178750038147</v>
+        <v>0.542178690433502</v>
       </c>
       <c r="H2082" t="s">
         <v>8</v>
@@ -54553,7 +54553,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G2084" t="n">
-        <v>0.550379633903503</v>
+        <v>0.550379693508148</v>
       </c>
       <c r="H2084" t="s">
         <v>8</v>
@@ -54657,7 +54657,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G2088" t="n">
-        <v>0.530332744121552</v>
+        <v>0.530332803726196</v>
       </c>
       <c r="H2088" t="s">
         <v>8</v>
@@ -54813,7 +54813,7 @@
         <v>0.545000016689301</v>
       </c>
       <c r="G2094" t="n">
-        <v>0.496617496013641</v>
+        <v>0.496617466211319</v>
       </c>
       <c r="H2094" t="s">
         <v>8</v>
@@ -54839,7 +54839,7 @@
         <v>0.556999981403351</v>
       </c>
       <c r="G2095" t="n">
-        <v>0.507552146911621</v>
+        <v>0.507552087306976</v>
       </c>
       <c r="H2095" t="s">
         <v>8</v>
@@ -54969,7 +54969,7 @@
         <v>0.542999982833862</v>
       </c>
       <c r="G2100" t="n">
-        <v>0.494794994592667</v>
+        <v>0.494795024394989</v>
       </c>
       <c r="H2100" t="s">
         <v>8</v>
@@ -55021,7 +55021,7 @@
         <v>0.546000003814697</v>
       </c>
       <c r="G2102" t="n">
-        <v>0.497528672218323</v>
+        <v>0.497528731822968</v>
       </c>
       <c r="H2102" t="s">
         <v>8</v>
@@ -55099,7 +55099,7 @@
         <v>0.526000022888184</v>
       </c>
       <c r="G2105" t="n">
-        <v>0.479304224252701</v>
+        <v>0.479304194450378</v>
       </c>
       <c r="H2105" t="s">
         <v>8</v>
@@ -55125,7 +55125,7 @@
         <v>0.531000018119812</v>
       </c>
       <c r="G2106" t="n">
-        <v>0.483860343694687</v>
+        <v>0.483860313892365</v>
       </c>
       <c r="H2106" t="s">
         <v>8</v>
@@ -55151,7 +55151,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G2107" t="n">
-        <v>0.482949018478394</v>
+        <v>0.482949078083038</v>
       </c>
       <c r="H2107" t="s">
         <v>8</v>
@@ -55177,7 +55177,7 @@
         <v>0.526000022888184</v>
       </c>
       <c r="G2108" t="n">
-        <v>0.479304224252701</v>
+        <v>0.479304194450378</v>
       </c>
       <c r="H2108" t="s">
         <v>8</v>
@@ -55203,7 +55203,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G2109" t="n">
-        <v>0.482949018478394</v>
+        <v>0.482949078083038</v>
       </c>
       <c r="H2109" t="s">
         <v>8</v>
@@ -55229,7 +55229,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G2110" t="n">
-        <v>0.487505257129669</v>
+        <v>0.487505227327347</v>
       </c>
       <c r="H2110" t="s">
         <v>8</v>
@@ -55255,7 +55255,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G2111" t="n">
-        <v>0.482949018478394</v>
+        <v>0.482949078083038</v>
       </c>
       <c r="H2111" t="s">
         <v>8</v>
@@ -55281,7 +55281,7 @@
         <v>0.527999997138977</v>
       </c>
       <c r="G2112" t="n">
-        <v>0.481126666069031</v>
+        <v>0.481126606464386</v>
       </c>
       <c r="H2112" t="s">
         <v>8</v>
@@ -55307,7 +55307,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G2113" t="n">
-        <v>0.482949018478394</v>
+        <v>0.482949078083038</v>
       </c>
       <c r="H2113" t="s">
         <v>8</v>
@@ -55333,7 +55333,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G2114" t="n">
-        <v>0.487505257129669</v>
+        <v>0.487505227327347</v>
       </c>
       <c r="H2114" t="s">
         <v>8</v>
@@ -55619,7 +55619,7 @@
         <v>0.578000009059906</v>
       </c>
       <c r="G2125" t="n">
-        <v>0.526687920093536</v>
+        <v>0.526687860488892</v>
       </c>
       <c r="H2125" t="s">
         <v>8</v>
@@ -55645,7 +55645,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G2126" t="n">
-        <v>0.513930678367615</v>
+        <v>0.51393073797226</v>
       </c>
       <c r="H2126" t="s">
         <v>8</v>
@@ -55723,7 +55723,7 @@
         <v>0.531000018119812</v>
       </c>
       <c r="G2129" t="n">
-        <v>0.483860343694687</v>
+        <v>0.483860313892365</v>
       </c>
       <c r="H2129" t="s">
         <v>8</v>
@@ -55749,7 +55749,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G2130" t="n">
-        <v>0.487505257129669</v>
+        <v>0.487505227327347</v>
       </c>
       <c r="H2130" t="s">
         <v>8</v>
@@ -55775,7 +55775,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G2131" t="n">
-        <v>0.482949018478394</v>
+        <v>0.482949078083038</v>
       </c>
       <c r="H2131" t="s">
         <v>8</v>
@@ -55801,7 +55801,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G2132" t="n">
-        <v>0.482949018478394</v>
+        <v>0.482949078083038</v>
       </c>
       <c r="H2132" t="s">
         <v>8</v>
@@ -71678,7 +71678,7 @@
         <v>0.531000018119812</v>
       </c>
       <c r="D2743" t="n">
-        <v>0.522000014781952</v>
+        <v>0.521000027656555</v>
       </c>
       <c r="E2743" t="n">
         <v>0.529999971389771</v>
@@ -71690,6 +71690,32 @@
         <v>0.521000027656555</v>
       </c>
       <c r="H2743" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2744">
+      <c r="A2744" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2744" t="n">
+        <v>71782</v>
+      </c>
+      <c r="C2744" t="n">
+        <v>0.528999984264374</v>
+      </c>
+      <c r="D2744" t="n">
+        <v>0.518999993801117</v>
+      </c>
+      <c r="E2744" t="n">
+        <v>0.528999984264374</v>
+      </c>
+      <c r="F2744" t="n">
+        <v>0.519999980926514</v>
+      </c>
+      <c r="G2744" t="n">
+        <v>0.519999980926514</v>
+      </c>
+      <c r="H2744" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/IMS.MI.xlsx
+++ b/data/IMS.MI.xlsx
@@ -485,7 +485,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G4" t="n">
-        <v>0.321156293153763</v>
+        <v>0.321156352758408</v>
       </c>
       <c r="H4" t="n">
         <v>136639</v>
@@ -543,7 +543,7 @@
         <v>0.415300011634827</v>
       </c>
       <c r="G6" t="n">
-        <v>0.307318478822708</v>
+        <v>0.307318508625031</v>
       </c>
       <c r="H6" t="n">
         <v>199460</v>
@@ -572,7 +572,7 @@
         <v>0.389800012111664</v>
       </c>
       <c r="G7" t="n">
-        <v>0.288448750972748</v>
+        <v>0.288448721170425</v>
       </c>
       <c r="H7" t="n">
         <v>877572</v>
@@ -601,7 +601,7 @@
         <v>0.391000002622604</v>
       </c>
       <c r="G8" t="n">
-        <v>0.289336681365967</v>
+        <v>0.289336651563644</v>
       </c>
       <c r="H8" t="n">
         <v>433410</v>
@@ -630,7 +630,7 @@
         <v>0.397799998521805</v>
       </c>
       <c r="G9" t="n">
-        <v>0.294368654489517</v>
+        <v>0.294368594884872</v>
       </c>
       <c r="H9" t="n">
         <v>1154472</v>
@@ -688,7 +688,7 @@
         <v>0.370000004768372</v>
       </c>
       <c r="G11" t="n">
-        <v>0.273796886205673</v>
+        <v>0.273796856403351</v>
       </c>
       <c r="H11" t="n">
         <v>482282</v>
@@ -746,7 +746,7 @@
         <v>0.349000006914139</v>
       </c>
       <c r="G13" t="n">
-        <v>0.25825709104538</v>
+        <v>0.258257061243057</v>
       </c>
       <c r="H13" t="n">
         <v>657255</v>
@@ -775,7 +775,7 @@
         <v>0.329199999570847</v>
       </c>
       <c r="G14" t="n">
-        <v>0.243605196475983</v>
+        <v>0.243605226278305</v>
       </c>
       <c r="H14" t="n">
         <v>845615</v>
@@ -804,7 +804,7 @@
         <v>0.333000004291534</v>
       </c>
       <c r="G15" t="n">
-        <v>0.246417164802551</v>
+        <v>0.246417194604874</v>
       </c>
       <c r="H15" t="n">
         <v>896826</v>
@@ -833,7 +833,7 @@
         <v>0.354999989271164</v>
       </c>
       <c r="G16" t="n">
-        <v>0.262696951627731</v>
+        <v>0.262696981430054</v>
       </c>
       <c r="H16" t="n">
         <v>574264</v>
@@ -862,7 +862,7 @@
         <v>0.346500009298325</v>
       </c>
       <c r="G17" t="n">
-        <v>0.256407111883163</v>
+        <v>0.256407052278519</v>
       </c>
       <c r="H17" t="n">
         <v>207617</v>
@@ -891,7 +891,7 @@
         <v>0.351099997758865</v>
       </c>
       <c r="G18" t="n">
-        <v>0.259811043739319</v>
+        <v>0.259811013936996</v>
       </c>
       <c r="H18" t="n">
         <v>289577</v>
@@ -949,7 +949,7 @@
         <v>0.342999994754791</v>
       </c>
       <c r="G20" t="n">
-        <v>0.253817111253738</v>
+        <v>0.253817051649094</v>
       </c>
       <c r="H20" t="n">
         <v>123813</v>
@@ -1007,7 +1007,7 @@
         <v>0.387699991464615</v>
       </c>
       <c r="G22" t="n">
-        <v>0.286894708871841</v>
+        <v>0.286894679069519</v>
       </c>
       <c r="H22" t="n">
         <v>1446522</v>
@@ -1094,7 +1094,7 @@
         <v>0.388000011444092</v>
       </c>
       <c r="G25" t="n">
-        <v>0.28711673617363</v>
+        <v>0.287116706371307</v>
       </c>
       <c r="H25" t="n">
         <v>1284870</v>
@@ -1123,7 +1123,7 @@
         <v>0.392899990081787</v>
       </c>
       <c r="G26" t="n">
-        <v>0.290742665529251</v>
+        <v>0.290742635726929</v>
       </c>
       <c r="H26" t="n">
         <v>515445</v>
@@ -1152,7 +1152,7 @@
         <v>0.356499999761581</v>
       </c>
       <c r="G27" t="n">
-        <v>0.263806968927383</v>
+        <v>0.263806998729706</v>
       </c>
       <c r="H27" t="n">
         <v>560505</v>
@@ -1181,7 +1181,7 @@
         <v>0.347000002861023</v>
       </c>
       <c r="G28" t="n">
-        <v>0.256777077913284</v>
+        <v>0.256777048110962</v>
       </c>
       <c r="H28" t="n">
         <v>1141585</v>
@@ -1210,7 +1210,7 @@
         <v>0.354999989271164</v>
       </c>
       <c r="G29" t="n">
-        <v>0.262696951627731</v>
+        <v>0.262696981430054</v>
       </c>
       <c r="H29" t="n">
         <v>987262</v>
@@ -1239,7 +1239,7 @@
         <v>0.337999999523163</v>
       </c>
       <c r="G30" t="n">
-        <v>0.250117123126984</v>
+        <v>0.250117152929306</v>
       </c>
       <c r="H30" t="n">
         <v>845331</v>
@@ -1384,7 +1384,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G35" t="n">
-        <v>0.310796439647675</v>
+        <v>0.310796409845352</v>
       </c>
       <c r="H35" t="n">
         <v>330051</v>
@@ -1500,7 +1500,7 @@
         <v>0.418500006198883</v>
       </c>
       <c r="G39" t="n">
-        <v>0.309686481952667</v>
+        <v>0.309686452150345</v>
       </c>
       <c r="H39" t="n">
         <v>253612</v>
@@ -1587,7 +1587,7 @@
         <v>0.437000006437302</v>
       </c>
       <c r="G42" t="n">
-        <v>0.323376268148422</v>
+        <v>0.323376297950745</v>
       </c>
       <c r="H42" t="n">
         <v>204480</v>
@@ -1616,7 +1616,7 @@
         <v>0.432500004768372</v>
       </c>
       <c r="G43" t="n">
-        <v>0.320046335458755</v>
+        <v>0.320046305656433</v>
       </c>
       <c r="H43" t="n">
         <v>219093</v>
@@ -1674,7 +1674,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G45" t="n">
-        <v>0.315236389636993</v>
+        <v>0.315236419439316</v>
       </c>
       <c r="H45" t="n">
         <v>255696</v>
@@ -1703,7 +1703,7 @@
         <v>0.426499992609024</v>
       </c>
       <c r="G46" t="n">
-        <v>0.315606415271759</v>
+        <v>0.315606385469437</v>
       </c>
       <c r="H46" t="n">
         <v>75248</v>
@@ -1761,7 +1761,7 @@
         <v>0.449000000953674</v>
       </c>
       <c r="G48" t="n">
-        <v>0.332256227731705</v>
+        <v>0.332256197929382</v>
       </c>
       <c r="H48" t="n">
         <v>240329</v>
@@ -1790,7 +1790,7 @@
         <v>0.444400012493134</v>
       </c>
       <c r="G49" t="n">
-        <v>0.328852236270905</v>
+        <v>0.328852206468582</v>
       </c>
       <c r="H49" t="n">
         <v>100779</v>
@@ -1819,7 +1819,7 @@
         <v>0.446599990129471</v>
       </c>
       <c r="G50" t="n">
-        <v>0.330480188131332</v>
+        <v>0.330480217933655</v>
       </c>
       <c r="H50" t="n">
         <v>32677</v>
@@ -1877,7 +1877,7 @@
         <v>0.421700000762939</v>
       </c>
       <c r="G52" t="n">
-        <v>0.312054395675659</v>
+        <v>0.312054425477982</v>
       </c>
       <c r="H52" t="n">
         <v>153460</v>
@@ -1964,7 +1964,7 @@
         <v>0.404599994421005</v>
       </c>
       <c r="G55" t="n">
-        <v>0.299400597810745</v>
+        <v>0.299400568008423</v>
       </c>
       <c r="H55" t="n">
         <v>138129</v>
@@ -2080,7 +2080,7 @@
         <v>0.402999997138977</v>
       </c>
       <c r="G59" t="n">
-        <v>0.29821652173996</v>
+        <v>0.298216611146927</v>
       </c>
       <c r="H59" t="n">
         <v>277234</v>
@@ -2138,7 +2138,7 @@
         <v>0.387699991464615</v>
       </c>
       <c r="G61" t="n">
-        <v>0.286894708871841</v>
+        <v>0.286894679069519</v>
       </c>
       <c r="H61" t="n">
         <v>264789</v>
@@ -2167,7 +2167,7 @@
         <v>0.386999994516373</v>
       </c>
       <c r="G62" t="n">
-        <v>0.286376774311066</v>
+        <v>0.286376744508743</v>
       </c>
       <c r="H62" t="n">
         <v>251390</v>
@@ -2196,7 +2196,7 @@
         <v>0.374000012874603</v>
       </c>
       <c r="G63" t="n">
-        <v>0.276756852865219</v>
+        <v>0.276756793260574</v>
       </c>
       <c r="H63" t="n">
         <v>230800</v>
@@ -2225,7 +2225,7 @@
         <v>0.370999991893768</v>
       </c>
       <c r="G64" t="n">
-        <v>0.274536848068237</v>
+        <v>0.27453687787056</v>
       </c>
       <c r="H64" t="n">
         <v>309537</v>
@@ -2254,7 +2254,7 @@
         <v>0.368000000715256</v>
       </c>
       <c r="G65" t="n">
-        <v>0.272316932678223</v>
+        <v>0.2723169028759</v>
       </c>
       <c r="H65" t="n">
         <v>462580</v>
@@ -2312,7 +2312,7 @@
         <v>0.365500003099442</v>
       </c>
       <c r="G67" t="n">
-        <v>0.270466893911362</v>
+        <v>0.270466923713684</v>
       </c>
       <c r="H67" t="n">
         <v>684193</v>
@@ -2399,7 +2399,7 @@
         <v>0.363000005483627</v>
       </c>
       <c r="G70" t="n">
-        <v>0.268616944551468</v>
+        <v>0.268616914749146</v>
       </c>
       <c r="H70" t="n">
         <v>59990</v>
@@ -2428,7 +2428,7 @@
         <v>0.36379998922348</v>
       </c>
       <c r="G71" t="n">
-        <v>0.269208878278732</v>
+        <v>0.269208908081055</v>
       </c>
       <c r="H71" t="n">
         <v>99070</v>
@@ -2544,7 +2544,7 @@
         <v>0.384999990463257</v>
       </c>
       <c r="G75" t="n">
-        <v>0.28489676117897</v>
+        <v>0.284896731376648</v>
       </c>
       <c r="H75" t="n">
         <v>270841</v>
@@ -2631,7 +2631,7 @@
         <v>0.416500002145767</v>
       </c>
       <c r="G78" t="n">
-        <v>0.308206468820572</v>
+        <v>0.30820643901825</v>
       </c>
       <c r="H78" t="n">
         <v>162052</v>
@@ -2660,7 +2660,7 @@
         <v>0.417800009250641</v>
       </c>
       <c r="G79" t="n">
-        <v>0.309168428182602</v>
+        <v>0.309168457984924</v>
       </c>
       <c r="H79" t="n">
         <v>592614</v>
@@ -2689,7 +2689,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G80" t="n">
-        <v>0.318196356296539</v>
+        <v>0.318196386098862</v>
       </c>
       <c r="H80" t="n">
         <v>196110</v>
@@ -2718,7 +2718,7 @@
         <v>0.428299993276596</v>
       </c>
       <c r="G81" t="n">
-        <v>0.316938370466232</v>
+        <v>0.31693834066391</v>
       </c>
       <c r="H81" t="n">
         <v>307136</v>
@@ -2834,7 +2834,7 @@
         <v>0.431600004434586</v>
       </c>
       <c r="G85" t="n">
-        <v>0.319380342960358</v>
+        <v>0.31938037276268</v>
       </c>
       <c r="H85" t="n">
         <v>324523</v>
@@ -3066,7 +3066,7 @@
         <v>0.415699988603592</v>
       </c>
       <c r="G93" t="n">
-        <v>0.307614505290985</v>
+        <v>0.30761444568634</v>
       </c>
       <c r="H93" t="n">
         <v>129466</v>
@@ -3124,7 +3124,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G95" t="n">
-        <v>0.305616497993469</v>
+        <v>0.305616468191147</v>
       </c>
       <c r="H95" t="n">
         <v>33448</v>
@@ -3182,7 +3182,7 @@
         <v>0.412600010633469</v>
       </c>
       <c r="G97" t="n">
-        <v>0.305320501327515</v>
+        <v>0.305320531129837</v>
       </c>
       <c r="H97" t="n">
         <v>129927</v>
@@ -3240,7 +3240,7 @@
         <v>0.406699985265732</v>
       </c>
       <c r="G99" t="n">
-        <v>0.300954550504684</v>
+        <v>0.300954520702362</v>
       </c>
       <c r="H99" t="n">
         <v>86804</v>
@@ -3298,7 +3298,7 @@
         <v>0.414900004863739</v>
       </c>
       <c r="G101" t="n">
-        <v>0.318779796361923</v>
+        <v>0.318779766559601</v>
       </c>
       <c r="H101" t="n">
         <v>69003</v>
@@ -3327,7 +3327,7 @@
         <v>0.41499999165535</v>
       </c>
       <c r="G102" t="n">
-        <v>0.318856626749039</v>
+        <v>0.318856596946716</v>
       </c>
       <c r="H102" t="n">
         <v>40277</v>
@@ -3385,7 +3385,7 @@
         <v>0.416399985551834</v>
       </c>
       <c r="G104" t="n">
-        <v>0.319932252168655</v>
+        <v>0.319932281970978</v>
       </c>
       <c r="H104" t="n">
         <v>65981</v>
@@ -3414,7 +3414,7 @@
         <v>0.41499999165535</v>
       </c>
       <c r="G105" t="n">
-        <v>0.318856626749039</v>
+        <v>0.318856596946716</v>
       </c>
       <c r="H105" t="n">
         <v>42477</v>
@@ -3443,7 +3443,7 @@
         <v>0.41499999165535</v>
       </c>
       <c r="G106" t="n">
-        <v>0.318856626749039</v>
+        <v>0.318856596946716</v>
       </c>
       <c r="H106" t="n">
         <v>35204</v>
@@ -3472,7 +3472,7 @@
         <v>0.41499999165535</v>
       </c>
       <c r="G107" t="n">
-        <v>0.318856626749039</v>
+        <v>0.318856596946716</v>
       </c>
       <c r="H107" t="n">
         <v>80591</v>
@@ -3530,7 +3530,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G109" t="n">
-        <v>0.307331651449203</v>
+        <v>0.307331681251526</v>
       </c>
       <c r="H109" t="n">
         <v>111759</v>
@@ -3559,7 +3559,7 @@
         <v>0.41499999165535</v>
       </c>
       <c r="G110" t="n">
-        <v>0.318856626749039</v>
+        <v>0.318856596946716</v>
       </c>
       <c r="H110" t="n">
         <v>59591</v>
@@ -3733,7 +3733,7 @@
         <v>0.384999990463257</v>
       </c>
       <c r="G116" t="n">
-        <v>0.295806735754013</v>
+        <v>0.295806705951691</v>
       </c>
       <c r="H116" t="n">
         <v>401743</v>
@@ -3791,7 +3791,7 @@
         <v>0.386000007390976</v>
       </c>
       <c r="G118" t="n">
-        <v>0.296575129032135</v>
+        <v>0.29657506942749</v>
       </c>
       <c r="H118" t="n">
         <v>68644</v>
@@ -4081,7 +4081,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G128" t="n">
-        <v>0.307331651449203</v>
+        <v>0.307331681251526</v>
       </c>
       <c r="H128" t="n">
         <v>33158</v>
@@ -4110,7 +4110,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G129" t="n">
-        <v>0.307331651449203</v>
+        <v>0.307331681251526</v>
       </c>
       <c r="H129" t="n">
         <v>147122</v>
@@ -4139,7 +4139,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G130" t="n">
-        <v>0.307331651449203</v>
+        <v>0.307331681251526</v>
       </c>
       <c r="H130" t="n">
         <v>35313</v>
@@ -4226,7 +4226,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G133" t="n">
-        <v>0.307331651449203</v>
+        <v>0.307331681251526</v>
       </c>
       <c r="H133" t="n">
         <v>199243</v>
@@ -4284,7 +4284,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G135" t="n">
-        <v>0.307331651449203</v>
+        <v>0.307331681251526</v>
       </c>
       <c r="H135" t="n">
         <v>136665</v>
@@ -4313,7 +4313,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G136" t="n">
-        <v>0.307331651449203</v>
+        <v>0.307331681251526</v>
       </c>
       <c r="H136" t="n">
         <v>109601</v>
@@ -4371,7 +4371,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G138" t="n">
-        <v>0.307331651449203</v>
+        <v>0.307331681251526</v>
       </c>
       <c r="H138" t="n">
         <v>126604</v>
@@ -4400,7 +4400,7 @@
         <v>0.396899998188019</v>
       </c>
       <c r="G139" t="n">
-        <v>0.304949879646301</v>
+        <v>0.304949909448624</v>
       </c>
       <c r="H139" t="n">
         <v>252402</v>
@@ -4487,7 +4487,7 @@
         <v>0.387499988079071</v>
       </c>
       <c r="G142" t="n">
-        <v>0.29772761464119</v>
+        <v>0.297727584838867</v>
       </c>
       <c r="H142" t="n">
         <v>506329</v>
@@ -4545,7 +4545,7 @@
         <v>0.392800003290176</v>
       </c>
       <c r="G144" t="n">
-        <v>0.301799714565277</v>
+        <v>0.301799684762955</v>
       </c>
       <c r="H144" t="n">
         <v>21943</v>
@@ -4574,7 +4574,7 @@
         <v>0.395700007677078</v>
       </c>
       <c r="G145" t="n">
-        <v>0.304027855396271</v>
+        <v>0.304027885198593</v>
       </c>
       <c r="H145" t="n">
         <v>23023</v>
@@ -4632,7 +4632,7 @@
         <v>0.407999992370605</v>
       </c>
       <c r="G147" t="n">
-        <v>0.313478291034698</v>
+        <v>0.313478320837021</v>
       </c>
       <c r="H147" t="n">
         <v>174884</v>
@@ -4777,7 +4777,7 @@
         <v>0.389299988746643</v>
       </c>
       <c r="G152" t="n">
-        <v>0.299110561609268</v>
+        <v>0.299110531806946</v>
       </c>
       <c r="H152" t="n">
         <v>107176</v>
@@ -4806,7 +4806,7 @@
         <v>0.397300004959106</v>
       </c>
       <c r="G153" t="n">
-        <v>0.305257230997086</v>
+        <v>0.305257201194763</v>
       </c>
       <c r="H153" t="n">
         <v>32211</v>
@@ -4835,7 +4835,7 @@
         <v>0.397300004959106</v>
       </c>
       <c r="G154" t="n">
-        <v>0.305257230997086</v>
+        <v>0.305257201194763</v>
       </c>
       <c r="H154" t="n">
         <v>125840</v>
@@ -4864,7 +4864,7 @@
         <v>0.384700000286102</v>
       </c>
       <c r="G155" t="n">
-        <v>0.295576184988022</v>
+        <v>0.295576214790344</v>
       </c>
       <c r="H155" t="n">
         <v>84588</v>
@@ -4893,7 +4893,7 @@
         <v>0.385199993848801</v>
       </c>
       <c r="G156" t="n">
-        <v>0.295960396528244</v>
+        <v>0.295960366725922</v>
       </c>
       <c r="H156" t="n">
         <v>31523</v>
@@ -4922,7 +4922,7 @@
         <v>0.38740000128746</v>
       </c>
       <c r="G157" t="n">
-        <v>0.297650724649429</v>
+        <v>0.297650754451752</v>
       </c>
       <c r="H157" t="n">
         <v>8546</v>
@@ -4951,7 +4951,7 @@
         <v>0.387699991464615</v>
       </c>
       <c r="G158" t="n">
-        <v>0.297881186008453</v>
+        <v>0.297881245613098</v>
       </c>
       <c r="H158" t="n">
         <v>56338</v>
@@ -4980,7 +4980,7 @@
         <v>0.387699991464615</v>
       </c>
       <c r="G159" t="n">
-        <v>0.297881186008453</v>
+        <v>0.297881245613098</v>
       </c>
       <c r="H159" t="n">
         <v>100520</v>
@@ -5096,7 +5096,7 @@
         <v>0.391000002622604</v>
       </c>
       <c r="G163" t="n">
-        <v>0.300416707992554</v>
+        <v>0.300416737794876</v>
       </c>
       <c r="H163" t="n">
         <v>27048</v>
@@ -5125,7 +5125,7 @@
         <v>0.384999990463257</v>
       </c>
       <c r="G164" t="n">
-        <v>0.295806735754013</v>
+        <v>0.295806705951691</v>
       </c>
       <c r="H164" t="n">
         <v>18763</v>
@@ -5154,7 +5154,7 @@
         <v>0.390599995851517</v>
       </c>
       <c r="G165" t="n">
-        <v>0.300109386444092</v>
+        <v>0.300109356641769</v>
       </c>
       <c r="H165" t="n">
         <v>64931</v>
@@ -5270,7 +5270,7 @@
         <v>0.397599995136261</v>
       </c>
       <c r="G169" t="n">
-        <v>0.30548769235611</v>
+        <v>0.305487662553787</v>
       </c>
       <c r="H169" t="n">
         <v>47359</v>
@@ -5299,7 +5299,7 @@
         <v>0.402900010347366</v>
       </c>
       <c r="G170" t="n">
-        <v>0.309559851884842</v>
+        <v>0.309559881687164</v>
       </c>
       <c r="H170" t="n">
         <v>421141</v>
@@ -5328,7 +5328,7 @@
         <v>0.394499987363815</v>
       </c>
       <c r="G171" t="n">
-        <v>0.303105860948563</v>
+        <v>0.303105890750885</v>
       </c>
       <c r="H171" t="n">
         <v>99588</v>
@@ -5357,7 +5357,7 @@
         <v>0.395099997520447</v>
       </c>
       <c r="G172" t="n">
-        <v>0.303566873073578</v>
+        <v>0.3035669028759</v>
       </c>
       <c r="H172" t="n">
         <v>110978</v>
@@ -5415,7 +5415,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G174" t="n">
-        <v>0.307331651449203</v>
+        <v>0.307331681251526</v>
       </c>
       <c r="H174" t="n">
         <v>49911</v>
@@ -5444,7 +5444,7 @@
         <v>0.396800011396408</v>
       </c>
       <c r="G175" t="n">
-        <v>0.304873019456863</v>
+        <v>0.304873049259186</v>
       </c>
       <c r="H175" t="n">
         <v>32437</v>
@@ -5473,7 +5473,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G176" t="n">
-        <v>0.307331651449203</v>
+        <v>0.307331681251526</v>
       </c>
       <c r="H176" t="n">
         <v>27461</v>
@@ -5676,7 +5676,7 @@
         <v>0.36829999089241</v>
       </c>
       <c r="G183" t="n">
-        <v>0.282975614070892</v>
+        <v>0.282975643873215</v>
       </c>
       <c r="H183" t="n">
         <v>904350</v>
@@ -5821,7 +5821,7 @@
         <v>0.380899995565414</v>
       </c>
       <c r="G188" t="n">
-        <v>0.292656570672989</v>
+        <v>0.292656600475311</v>
       </c>
       <c r="H188" t="n">
         <v>84648</v>
@@ -5850,7 +5850,7 @@
         <v>0.380699992179871</v>
       </c>
       <c r="G189" t="n">
-        <v>0.29250293970108</v>
+        <v>0.292502909898758</v>
       </c>
       <c r="H189" t="n">
         <v>73863</v>
@@ -5937,7 +5937,7 @@
         <v>0.370000004768372</v>
       </c>
       <c r="G192" t="n">
-        <v>0.284281820058823</v>
+        <v>0.284281849861145</v>
       </c>
       <c r="H192" t="n">
         <v>94136</v>
@@ -5966,7 +5966,7 @@
         <v>0.374700009822845</v>
       </c>
       <c r="G193" t="n">
-        <v>0.287892997264862</v>
+        <v>0.28789296746254</v>
       </c>
       <c r="H193" t="n">
         <v>82455</v>
@@ -6024,7 +6024,7 @@
         <v>0.381199985742569</v>
       </c>
       <c r="G195" t="n">
-        <v>0.292887091636658</v>
+        <v>0.292887061834335</v>
       </c>
       <c r="H195" t="n">
         <v>44416</v>
@@ -6111,7 +6111,7 @@
         <v>0.37720000743866</v>
       </c>
       <c r="G198" t="n">
-        <v>0.289813786745071</v>
+        <v>0.289813756942749</v>
       </c>
       <c r="H198" t="n">
         <v>3058</v>
@@ -6140,7 +6140,7 @@
         <v>0.372999995946884</v>
       </c>
       <c r="G199" t="n">
-        <v>0.286586791276932</v>
+        <v>0.286586850881577</v>
       </c>
       <c r="H199" t="n">
         <v>32621</v>
@@ -6198,7 +6198,7 @@
         <v>0.382999986410141</v>
       </c>
       <c r="G201" t="n">
-        <v>0.294270098209381</v>
+        <v>0.294270068407059</v>
       </c>
       <c r="H201" t="n">
         <v>337594</v>
@@ -6256,7 +6256,7 @@
         <v>0.379799991846085</v>
       </c>
       <c r="G203" t="n">
-        <v>0.291811436414719</v>
+        <v>0.291811406612396</v>
       </c>
       <c r="H203" t="n">
         <v>192330</v>
@@ -6285,7 +6285,7 @@
         <v>0.380800008773804</v>
       </c>
       <c r="G204" t="n">
-        <v>0.292579799890518</v>
+        <v>0.292579770088196</v>
       </c>
       <c r="H204" t="n">
         <v>156396</v>
@@ -6314,7 +6314,7 @@
         <v>0.384900003671646</v>
       </c>
       <c r="G205" t="n">
-        <v>0.295729905366898</v>
+        <v>0.29572993516922</v>
       </c>
       <c r="H205" t="n">
         <v>124130</v>
@@ -6343,7 +6343,7 @@
         <v>0.388399988412857</v>
       </c>
       <c r="G206" t="n">
-        <v>0.298419088125229</v>
+        <v>0.298419058322906</v>
       </c>
       <c r="H206" t="n">
         <v>316047</v>
@@ -6372,7 +6372,7 @@
         <v>0.388399988412857</v>
       </c>
       <c r="G207" t="n">
-        <v>0.298419088125229</v>
+        <v>0.298419058322906</v>
       </c>
       <c r="H207" t="n">
         <v>36787</v>
@@ -6401,7 +6401,7 @@
         <v>0.388399988412857</v>
       </c>
       <c r="G208" t="n">
-        <v>0.298419088125229</v>
+        <v>0.298419058322906</v>
       </c>
       <c r="H208" t="n">
         <v>232394</v>
@@ -6430,7 +6430,7 @@
         <v>0.383599996566772</v>
       </c>
       <c r="G209" t="n">
-        <v>0.294731080532074</v>
+        <v>0.294731050729752</v>
       </c>
       <c r="H209" t="n">
         <v>99376</v>
@@ -6459,7 +6459,7 @@
         <v>0.384999990463257</v>
       </c>
       <c r="G210" t="n">
-        <v>0.295806735754013</v>
+        <v>0.295806705951691</v>
       </c>
       <c r="H210" t="n">
         <v>336050</v>
@@ -6575,7 +6575,7 @@
         <v>0.382400006055832</v>
       </c>
       <c r="G214" t="n">
-        <v>0.293809115886688</v>
+        <v>0.293809086084366</v>
       </c>
       <c r="H214" t="n">
         <v>141041</v>
@@ -6691,7 +6691,7 @@
         <v>0.370000004768372</v>
       </c>
       <c r="G218" t="n">
-        <v>0.284281820058823</v>
+        <v>0.284281849861145</v>
       </c>
       <c r="H218" t="n">
         <v>57832</v>
@@ -6865,7 +6865,7 @@
         <v>0.356599986553192</v>
       </c>
       <c r="G224" t="n">
-        <v>0.27398619055748</v>
+        <v>0.273986220359802</v>
       </c>
       <c r="H224" t="n">
         <v>113864</v>
@@ -7068,7 +7068,7 @@
         <v>0.352899998426437</v>
       </c>
       <c r="G231" t="n">
-        <v>0.271143406629562</v>
+        <v>0.27114337682724</v>
       </c>
       <c r="H231" t="n">
         <v>96101</v>
@@ -7155,7 +7155,7 @@
         <v>0.349000006914139</v>
       </c>
       <c r="G234" t="n">
-        <v>0.268146902322769</v>
+        <v>0.268146872520447</v>
       </c>
       <c r="H234" t="n">
         <v>631160</v>
@@ -7184,7 +7184,7 @@
         <v>0.34799998998642</v>
       </c>
       <c r="G235" t="n">
-        <v>0.267378598451614</v>
+        <v>0.26737853884697</v>
       </c>
       <c r="H235" t="n">
         <v>115347</v>
@@ -7242,7 +7242,7 @@
         <v>0.345899999141693</v>
       </c>
       <c r="G237" t="n">
-        <v>0.2657650411129</v>
+        <v>0.265765100717545</v>
       </c>
       <c r="H237" t="n">
         <v>69294</v>
@@ -7416,7 +7416,7 @@
         <v>0.354699999094009</v>
       </c>
       <c r="G243" t="n">
-        <v>0.272526413202286</v>
+        <v>0.272526353597641</v>
       </c>
       <c r="H243" t="n">
         <v>153986</v>
@@ -7503,7 +7503,7 @@
         <v>0.360599994659424</v>
       </c>
       <c r="G246" t="n">
-        <v>0.277059555053711</v>
+        <v>0.277059525251389</v>
       </c>
       <c r="H246" t="n">
         <v>135695</v>
@@ -7532,7 +7532,7 @@
         <v>0.362399995326996</v>
       </c>
       <c r="G247" t="n">
-        <v>0.278442531824112</v>
+        <v>0.27844250202179</v>
       </c>
       <c r="H247" t="n">
         <v>57911</v>
@@ -7590,7 +7590,7 @@
         <v>0.362399995326996</v>
       </c>
       <c r="G249" t="n">
-        <v>0.278442531824112</v>
+        <v>0.27844250202179</v>
       </c>
       <c r="H249" t="n">
         <v>56247</v>
@@ -7648,7 +7648,7 @@
         <v>0.360599994659424</v>
       </c>
       <c r="G251" t="n">
-        <v>0.277059555053711</v>
+        <v>0.277059525251389</v>
       </c>
       <c r="H251" t="n">
         <v>55864</v>
@@ -7764,7 +7764,7 @@
         <v>0.362100005149841</v>
       </c>
       <c r="G255" t="n">
-        <v>0.278212040662766</v>
+        <v>0.278211981058121</v>
       </c>
       <c r="H255" t="n">
         <v>71245</v>
@@ -7851,7 +7851,7 @@
         <v>0.378500014543533</v>
       </c>
       <c r="G258" t="n">
-        <v>0.290812611579895</v>
+        <v>0.290812581777573</v>
       </c>
       <c r="H258" t="n">
         <v>308237</v>
@@ -7880,7 +7880,7 @@
         <v>0.377000004053116</v>
       </c>
       <c r="G259" t="n">
-        <v>0.289660155773163</v>
+        <v>0.28966012597084</v>
       </c>
       <c r="H259" t="n">
         <v>399052</v>
@@ -7909,7 +7909,7 @@
         <v>0.377999991178513</v>
       </c>
       <c r="G260" t="n">
-        <v>0.290428429841995</v>
+        <v>0.290428400039673</v>
       </c>
       <c r="H260" t="n">
         <v>282205</v>
@@ -8025,7 +8025,7 @@
         <v>0.377000004053116</v>
       </c>
       <c r="G264" t="n">
-        <v>0.289660155773163</v>
+        <v>0.28966012597084</v>
       </c>
       <c r="H264" t="n">
         <v>282378</v>
@@ -8083,7 +8083,7 @@
         <v>0.370400011539459</v>
       </c>
       <c r="G266" t="n">
-        <v>0.284589171409607</v>
+        <v>0.284589141607285</v>
       </c>
       <c r="H266" t="n">
         <v>132520</v>
@@ -8112,7 +8112,7 @@
         <v>0.377999991178513</v>
       </c>
       <c r="G267" t="n">
-        <v>0.290428429841995</v>
+        <v>0.290428400039673</v>
       </c>
       <c r="H267" t="n">
         <v>445095</v>
@@ -8141,7 +8141,7 @@
         <v>0.378800004720688</v>
       </c>
       <c r="G268" t="n">
-        <v>0.291043102741241</v>
+        <v>0.291043072938919</v>
       </c>
       <c r="H268" t="n">
         <v>502074</v>
@@ -8170,7 +8170,7 @@
         <v>0.382499992847443</v>
       </c>
       <c r="G269" t="n">
-        <v>0.293885916471481</v>
+        <v>0.293885946273804</v>
       </c>
       <c r="H269" t="n">
         <v>182954</v>
@@ -8228,7 +8228,7 @@
         <v>0.379799991846085</v>
       </c>
       <c r="G271" t="n">
-        <v>0.291811436414719</v>
+        <v>0.291811406612396</v>
       </c>
       <c r="H271" t="n">
         <v>479418</v>
@@ -8257,7 +8257,7 @@
         <v>0.381199985742569</v>
       </c>
       <c r="G272" t="n">
-        <v>0.292887091636658</v>
+        <v>0.292887061834335</v>
       </c>
       <c r="H272" t="n">
         <v>387615</v>
@@ -8344,7 +8344,7 @@
         <v>0.384999990463257</v>
       </c>
       <c r="G275" t="n">
-        <v>0.295806735754013</v>
+        <v>0.295806705951691</v>
       </c>
       <c r="H275" t="n">
         <v>300298</v>
@@ -8373,7 +8373,7 @@
         <v>0.384900003671646</v>
       </c>
       <c r="G276" t="n">
-        <v>0.295729905366898</v>
+        <v>0.29572993516922</v>
       </c>
       <c r="H276" t="n">
         <v>239257</v>
@@ -8489,7 +8489,7 @@
         <v>0.368000000715256</v>
       </c>
       <c r="G280" t="n">
-        <v>0.282745182514191</v>
+        <v>0.282745122909546</v>
       </c>
       <c r="H280" t="n">
         <v>205102</v>
@@ -8518,7 +8518,7 @@
         <v>0.360900014638901</v>
       </c>
       <c r="G281" t="n">
-        <v>0.277290046215057</v>
+        <v>0.277290016412735</v>
       </c>
       <c r="H281" t="n">
         <v>117501</v>
@@ -8576,7 +8576,7 @@
         <v>0.359499990940094</v>
       </c>
       <c r="G283" t="n">
-        <v>0.276214331388474</v>
+        <v>0.276214361190796</v>
       </c>
       <c r="H283" t="n">
         <v>123038</v>
@@ -8605,7 +8605,7 @@
         <v>0.356099992990494</v>
       </c>
       <c r="G284" t="n">
-        <v>0.273602068424225</v>
+        <v>0.27360200881958</v>
       </c>
       <c r="H284" t="n">
         <v>74655</v>
@@ -8663,7 +8663,7 @@
         <v>0.358000010251999</v>
       </c>
       <c r="G286" t="n">
-        <v>0.275061845779419</v>
+        <v>0.275061875581741</v>
       </c>
       <c r="H286" t="n">
         <v>23496</v>
@@ -8692,7 +8692,7 @@
         <v>0.353799998760223</v>
       </c>
       <c r="G287" t="n">
-        <v>0.271834909915924</v>
+        <v>0.271834850311279</v>
       </c>
       <c r="H287" t="n">
         <v>29000</v>
@@ -8750,7 +8750,7 @@
         <v>0.358200013637543</v>
       </c>
       <c r="G289" t="n">
-        <v>0.275215536355972</v>
+        <v>0.275215566158295</v>
       </c>
       <c r="H289" t="n">
         <v>104065</v>
@@ -8779,7 +8779,7 @@
         <v>0.36039999127388</v>
       </c>
       <c r="G290" t="n">
-        <v>0.276905834674835</v>
+        <v>0.276905864477158</v>
       </c>
       <c r="H290" t="n">
         <v>223343</v>
@@ -8866,7 +8866,7 @@
         <v>0.357699990272522</v>
       </c>
       <c r="G293" t="n">
-        <v>0.27483132481575</v>
+        <v>0.274831384420395</v>
       </c>
       <c r="H293" t="n">
         <v>169100</v>
@@ -8895,7 +8895,7 @@
         <v>0.367900013923645</v>
       </c>
       <c r="G294" t="n">
-        <v>0.282668352127075</v>
+        <v>0.282668322324753</v>
       </c>
       <c r="H294" t="n">
         <v>168356</v>
@@ -8953,7 +8953,7 @@
         <v>0.363900005817413</v>
       </c>
       <c r="G296" t="n">
-        <v>0.279595017433167</v>
+        <v>0.279594987630844</v>
       </c>
       <c r="H296" t="n">
         <v>82937</v>
@@ -8982,7 +8982,7 @@
         <v>0.361000001430511</v>
       </c>
       <c r="G297" t="n">
-        <v>0.277366816997528</v>
+        <v>0.27736684679985</v>
       </c>
       <c r="H297" t="n">
         <v>155279</v>
@@ -9011,7 +9011,7 @@
         <v>0.361999988555908</v>
       </c>
       <c r="G298" t="n">
-        <v>0.278135150671005</v>
+        <v>0.278135180473328</v>
       </c>
       <c r="H298" t="n">
         <v>141640</v>
@@ -9040,7 +9040,7 @@
         <v>0.36599999666214</v>
       </c>
       <c r="G299" t="n">
-        <v>0.281208485364914</v>
+        <v>0.281208515167236</v>
       </c>
       <c r="H299" t="n">
         <v>204598</v>
@@ -9098,7 +9098,7 @@
         <v>0.36269998550415</v>
       </c>
       <c r="G301" t="n">
-        <v>0.278672993183136</v>
+        <v>0.278672963380814</v>
       </c>
       <c r="H301" t="n">
         <v>565039</v>
@@ -9243,7 +9243,7 @@
         <v>0.363999992609024</v>
       </c>
       <c r="G306" t="n">
-        <v>0.279671788215637</v>
+        <v>0.279671847820282</v>
       </c>
       <c r="H306" t="n">
         <v>104629</v>
@@ -9272,7 +9272,7 @@
         <v>0.373100012540817</v>
       </c>
       <c r="G307" t="n">
-        <v>0.286663621664047</v>
+        <v>0.286663681268692</v>
       </c>
       <c r="H307" t="n">
         <v>327704</v>
@@ -9359,7 +9359,7 @@
         <v>0.368000000715256</v>
       </c>
       <c r="G310" t="n">
-        <v>0.282745182514191</v>
+        <v>0.282745122909546</v>
       </c>
       <c r="H310" t="n">
         <v>47229</v>
@@ -9388,7 +9388,7 @@
         <v>0.369500011205673</v>
       </c>
       <c r="G311" t="n">
-        <v>0.283897697925568</v>
+        <v>0.283897668123245</v>
       </c>
       <c r="H311" t="n">
         <v>385846</v>
@@ -9417,7 +9417,7 @@
         <v>0.36829999089241</v>
       </c>
       <c r="G312" t="n">
-        <v>0.282975614070892</v>
+        <v>0.282975643873215</v>
       </c>
       <c r="H312" t="n">
         <v>657695</v>
@@ -9475,7 +9475,7 @@
         <v>0.371499985456467</v>
       </c>
       <c r="G314" t="n">
-        <v>0.285434275865555</v>
+        <v>0.285434305667877</v>
       </c>
       <c r="H314" t="n">
         <v>968385</v>
@@ -9533,7 +9533,7 @@
         <v>0.382999986410141</v>
       </c>
       <c r="G316" t="n">
-        <v>0.294270098209381</v>
+        <v>0.294270068407059</v>
       </c>
       <c r="H316" t="n">
         <v>2465767</v>
@@ -9620,7 +9620,7 @@
         <v>0.418999999761581</v>
       </c>
       <c r="G319" t="n">
-        <v>0.321929961442947</v>
+        <v>0.321929931640625</v>
       </c>
       <c r="H319" t="n">
         <v>2205487</v>
@@ -9678,7 +9678,7 @@
         <v>0.43189999461174</v>
       </c>
       <c r="G321" t="n">
-        <v>0.33184140920639</v>
+        <v>0.331841379404068</v>
       </c>
       <c r="H321" t="n">
         <v>2031714</v>
@@ -9765,7 +9765,7 @@
         <v>0.407999992370605</v>
       </c>
       <c r="G324" t="n">
-        <v>0.313478291034698</v>
+        <v>0.313478320837021</v>
       </c>
       <c r="H324" t="n">
         <v>458689</v>
@@ -9852,7 +9852,7 @@
         <v>0.404900014400482</v>
       </c>
       <c r="G327" t="n">
-        <v>0.311096519231796</v>
+        <v>0.311096489429474</v>
       </c>
       <c r="H327" t="n">
         <v>366751</v>
@@ -9881,7 +9881,7 @@
         <v>0.407499998807907</v>
       </c>
       <c r="G328" t="n">
-        <v>0.313094139099121</v>
+        <v>0.313094109296799</v>
       </c>
       <c r="H328" t="n">
         <v>245052</v>
@@ -9910,7 +9910,7 @@
         <v>0.407400012016296</v>
       </c>
       <c r="G329" t="n">
-        <v>0.313017308712006</v>
+        <v>0.313017338514328</v>
       </c>
       <c r="H329" t="n">
         <v>374594</v>
@@ -9939,7 +9939,7 @@
         <v>0.407999992370605</v>
       </c>
       <c r="G330" t="n">
-        <v>0.313478291034698</v>
+        <v>0.313478320837021</v>
       </c>
       <c r="H330" t="n">
         <v>288587</v>
@@ -9968,7 +9968,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G331" t="n">
-        <v>0.307331651449203</v>
+        <v>0.307331681251526</v>
       </c>
       <c r="H331" t="n">
         <v>786930</v>
@@ -10026,7 +10026,7 @@
         <v>0.377999991178513</v>
       </c>
       <c r="G333" t="n">
-        <v>0.290428429841995</v>
+        <v>0.290428400039673</v>
       </c>
       <c r="H333" t="n">
         <v>367240</v>
@@ -10055,7 +10055,7 @@
         <v>0.381399989128113</v>
       </c>
       <c r="G334" t="n">
-        <v>0.293040722608566</v>
+        <v>0.293040752410889</v>
       </c>
       <c r="H334" t="n">
         <v>423602</v>
@@ -10113,7 +10113,7 @@
         <v>0.38629999756813</v>
       </c>
       <c r="G336" t="n">
-        <v>0.296805560588837</v>
+        <v>0.296805590391159</v>
       </c>
       <c r="H336" t="n">
         <v>233600</v>
@@ -10142,7 +10142,7 @@
         <v>0.387499988079071</v>
       </c>
       <c r="G337" t="n">
-        <v>0.29772761464119</v>
+        <v>0.297727584838867</v>
       </c>
       <c r="H337" t="n">
         <v>70181</v>
@@ -10229,7 +10229,7 @@
         <v>0.388000011444092</v>
       </c>
       <c r="G340" t="n">
-        <v>0.298111766576767</v>
+        <v>0.298111736774445</v>
       </c>
       <c r="H340" t="n">
         <v>365021</v>
@@ -10258,7 +10258,7 @@
         <v>0.403800010681152</v>
       </c>
       <c r="G341" t="n">
-        <v>0.310251325368881</v>
+        <v>0.310251355171204</v>
       </c>
       <c r="H341" t="n">
         <v>450573</v>
@@ -10316,7 +10316,7 @@
         <v>0.396800011396408</v>
       </c>
       <c r="G343" t="n">
-        <v>0.304873019456863</v>
+        <v>0.304873049259186</v>
       </c>
       <c r="H343" t="n">
         <v>912935</v>
@@ -10345,7 +10345,7 @@
         <v>0.391499996185303</v>
       </c>
       <c r="G344" t="n">
-        <v>0.300800859928131</v>
+        <v>0.300800889730453</v>
       </c>
       <c r="H344" t="n">
         <v>289787</v>
@@ -10374,7 +10374,7 @@
         <v>0.391499996185303</v>
       </c>
       <c r="G345" t="n">
-        <v>0.300800859928131</v>
+        <v>0.300800889730453</v>
       </c>
       <c r="H345" t="n">
         <v>211591</v>
@@ -10432,7 +10432,7 @@
         <v>0.40200001001358</v>
       </c>
       <c r="G347" t="n">
-        <v>0.30886834859848</v>
+        <v>0.308868378400803</v>
       </c>
       <c r="H347" t="n">
         <v>1444355</v>
@@ -10519,7 +10519,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G350" t="n">
-        <v>0.327308267354965</v>
+        <v>0.327308237552643</v>
       </c>
       <c r="H350" t="n">
         <v>4076818</v>
@@ -10577,7 +10577,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G352" t="n">
-        <v>0.307331651449203</v>
+        <v>0.307331681251526</v>
       </c>
       <c r="H352" t="n">
         <v>1214448</v>
@@ -10664,7 +10664,7 @@
         <v>0.407499998807907</v>
       </c>
       <c r="G355" t="n">
-        <v>0.313094139099121</v>
+        <v>0.313094109296799</v>
       </c>
       <c r="H355" t="n">
         <v>621148</v>
@@ -10780,7 +10780,7 @@
         <v>0.408600002527237</v>
       </c>
       <c r="G359" t="n">
-        <v>0.313939273357391</v>
+        <v>0.313939332962036</v>
       </c>
       <c r="H359" t="n">
         <v>695103</v>
@@ -10809,7 +10809,7 @@
         <v>0.402999997138977</v>
       </c>
       <c r="G360" t="n">
-        <v>0.309636652469635</v>
+        <v>0.309636682271957</v>
       </c>
       <c r="H360" t="n">
         <v>607461</v>
@@ -10838,7 +10838,7 @@
         <v>0.400099992752075</v>
       </c>
       <c r="G361" t="n">
-        <v>0.307408541440964</v>
+        <v>0.307408511638641</v>
       </c>
       <c r="H361" t="n">
         <v>623997</v>
@@ -10867,7 +10867,7 @@
         <v>0.397599995136261</v>
       </c>
       <c r="G362" t="n">
-        <v>0.30548769235611</v>
+        <v>0.305487662553787</v>
       </c>
       <c r="H362" t="n">
         <v>416430</v>
@@ -10896,7 +10896,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G363" t="n">
-        <v>0.307331651449203</v>
+        <v>0.307331681251526</v>
       </c>
       <c r="H363" t="n">
         <v>459908</v>
@@ -10983,7 +10983,7 @@
         <v>0.40090000629425</v>
       </c>
       <c r="G366" t="n">
-        <v>0.308023184537888</v>
+        <v>0.30802321434021</v>
       </c>
       <c r="H366" t="n">
         <v>380563</v>
@@ -11012,7 +11012,7 @@
         <v>0.400499999523163</v>
       </c>
       <c r="G367" t="n">
-        <v>0.307715833187103</v>
+        <v>0.307715862989426</v>
       </c>
       <c r="H367" t="n">
         <v>136402</v>
@@ -11128,7 +11128,7 @@
         <v>0.413599997758865</v>
       </c>
       <c r="G371" t="n">
-        <v>0.317780941724777</v>
+        <v>0.3177809715271</v>
       </c>
       <c r="H371" t="n">
         <v>407867</v>
@@ -11157,7 +11157,7 @@
         <v>0.412000000476837</v>
       </c>
       <c r="G372" t="n">
-        <v>0.31655165553093</v>
+        <v>0.316551625728607</v>
       </c>
       <c r="H372" t="n">
         <v>261916</v>
@@ -11186,7 +11186,7 @@
         <v>0.411900013685226</v>
       </c>
       <c r="G373" t="n">
-        <v>0.316474795341492</v>
+        <v>0.316474765539169</v>
       </c>
       <c r="H373" t="n">
         <v>253246</v>
@@ -11215,7 +11215,7 @@
         <v>0.422199994325638</v>
       </c>
       <c r="G374" t="n">
-        <v>0.324388563632965</v>
+        <v>0.324388593435287</v>
       </c>
       <c r="H374" t="n">
         <v>1118729</v>
@@ -11273,7 +11273,7 @@
         <v>0.414299994707108</v>
       </c>
       <c r="G376" t="n">
-        <v>0.318318784236908</v>
+        <v>0.318318754434586</v>
       </c>
       <c r="H376" t="n">
         <v>886282</v>
@@ -11302,7 +11302,7 @@
         <v>0.413500010967255</v>
       </c>
       <c r="G377" t="n">
-        <v>0.317704141139984</v>
+        <v>0.317704111337662</v>
       </c>
       <c r="H377" t="n">
         <v>646769</v>
@@ -11331,7 +11331,7 @@
         <v>0.418500006198883</v>
       </c>
       <c r="G378" t="n">
-        <v>0.321545779705048</v>
+        <v>0.321545749902725</v>
       </c>
       <c r="H378" t="n">
         <v>467304</v>
@@ -11447,7 +11447,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G382" t="n">
-        <v>0.333454847335815</v>
+        <v>0.333454877138138</v>
       </c>
       <c r="H382" t="n">
         <v>909487</v>
@@ -11505,7 +11505,7 @@
         <v>0.431800007820129</v>
       </c>
       <c r="G384" t="n">
-        <v>0.331764549016953</v>
+        <v>0.331764578819275</v>
       </c>
       <c r="H384" t="n">
         <v>502424</v>
@@ -11534,7 +11534,7 @@
         <v>0.441900014877319</v>
       </c>
       <c r="G385" t="n">
-        <v>0.33952471613884</v>
+        <v>0.339524686336517</v>
       </c>
       <c r="H385" t="n">
         <v>690454</v>
@@ -11621,7 +11621,7 @@
         <v>0.433899998664856</v>
       </c>
       <c r="G388" t="n">
-        <v>0.333378046751022</v>
+        <v>0.3333780169487</v>
       </c>
       <c r="H388" t="n">
         <v>413640</v>
@@ -11679,7 +11679,7 @@
         <v>0.4375</v>
       </c>
       <c r="G390" t="n">
-        <v>0.336144059896469</v>
+        <v>0.336144030094147</v>
       </c>
       <c r="H390" t="n">
         <v>297502</v>
@@ -11795,7 +11795,7 @@
         <v>0.442099988460541</v>
       </c>
       <c r="G394" t="n">
-        <v>0.339678347110748</v>
+        <v>0.339678317308426</v>
       </c>
       <c r="H394" t="n">
         <v>447700</v>
@@ -11882,7 +11882,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G397" t="n">
-        <v>0.344211518764496</v>
+        <v>0.344211488962173</v>
       </c>
       <c r="H397" t="n">
         <v>444793</v>
@@ -11911,7 +11911,7 @@
         <v>0.443399995565414</v>
       </c>
       <c r="G398" t="n">
-        <v>0.340677201747894</v>
+        <v>0.34067714214325</v>
       </c>
       <c r="H398" t="n">
         <v>373444</v>
@@ -11969,7 +11969,7 @@
         <v>0.440200001001358</v>
       </c>
       <c r="G400" t="n">
-        <v>0.338218539953232</v>
+        <v>0.338218510150909</v>
       </c>
       <c r="H400" t="n">
         <v>2191191</v>
@@ -12027,7 +12027,7 @@
         <v>0.450500011444092</v>
       </c>
       <c r="G402" t="n">
-        <v>0.346132308244705</v>
+        <v>0.346132338047028</v>
       </c>
       <c r="H402" t="n">
         <v>268874</v>
@@ -12085,7 +12085,7 @@
         <v>0.443699985742569</v>
       </c>
       <c r="G404" t="n">
-        <v>0.340907692909241</v>
+        <v>0.340907663106918</v>
       </c>
       <c r="H404" t="n">
         <v>273196</v>
@@ -12114,7 +12114,7 @@
         <v>0.458999991416931</v>
       </c>
       <c r="G405" t="n">
-        <v>0.352663099765778</v>
+        <v>0.352663069963455</v>
       </c>
       <c r="H405" t="n">
         <v>1536809</v>
@@ -12143,7 +12143,7 @@
         <v>0.481499999761581</v>
       </c>
       <c r="G406" t="n">
-        <v>0.369950503110886</v>
+        <v>0.369950473308563</v>
       </c>
       <c r="H406" t="n">
         <v>3256875</v>
@@ -12172,7 +12172,7 @@
         <v>0.475600004196167</v>
       </c>
       <c r="G407" t="n">
-        <v>0.36541736125946</v>
+        <v>0.365417391061783</v>
       </c>
       <c r="H407" t="n">
         <v>1471895</v>
@@ -12201,7 +12201,7 @@
         <v>0.472499996423721</v>
       </c>
       <c r="G408" t="n">
-        <v>0.363035529851913</v>
+        <v>0.363035559654236</v>
       </c>
       <c r="H408" t="n">
         <v>651242</v>
@@ -12230,7 +12230,7 @@
         <v>0.486900001764297</v>
       </c>
       <c r="G409" t="n">
-        <v>0.374099522829056</v>
+        <v>0.374099493026733</v>
       </c>
       <c r="H409" t="n">
         <v>524155</v>
@@ -12346,7 +12346,7 @@
         <v>0.476500004529953</v>
       </c>
       <c r="G413" t="n">
-        <v>0.366108894348145</v>
+        <v>0.366108864545822</v>
       </c>
       <c r="H413" t="n">
         <v>207117</v>
@@ -12375,7 +12375,7 @@
         <v>0.472600013017654</v>
       </c>
       <c r="G414" t="n">
-        <v>0.363112419843674</v>
+        <v>0.363112390041351</v>
       </c>
       <c r="H414" t="n">
         <v>686409</v>
@@ -12404,7 +12404,7 @@
         <v>0.47979998588562</v>
       </c>
       <c r="G415" t="n">
-        <v>0.3686443567276</v>
+        <v>0.368644326925278</v>
       </c>
       <c r="H415" t="n">
         <v>285127</v>
@@ -12433,7 +12433,7 @@
         <v>0.47749999165535</v>
       </c>
       <c r="G416" t="n">
-        <v>0.366877168416977</v>
+        <v>0.366877198219299</v>
       </c>
       <c r="H416" t="n">
         <v>398147</v>
@@ -12462,7 +12462,7 @@
         <v>0.476700007915497</v>
       </c>
       <c r="G417" t="n">
-        <v>0.366262555122375</v>
+        <v>0.366262525320053</v>
       </c>
       <c r="H417" t="n">
         <v>237730</v>
@@ -12491,7 +12491,7 @@
         <v>0.469999998807907</v>
       </c>
       <c r="G418" t="n">
-        <v>0.361114710569382</v>
+        <v>0.361114770174026</v>
       </c>
       <c r="H418" t="n">
         <v>259931</v>
@@ -12520,7 +12520,7 @@
         <v>0.468400001525879</v>
       </c>
       <c r="G419" t="n">
-        <v>0.359885394573212</v>
+        <v>0.359885424375534</v>
       </c>
       <c r="H419" t="n">
         <v>222703</v>
@@ -12549,7 +12549,7 @@
         <v>0.468400001525879</v>
       </c>
       <c r="G420" t="n">
-        <v>0.359885394573212</v>
+        <v>0.359885424375534</v>
       </c>
       <c r="H420" t="n">
         <v>149805</v>
@@ -12636,7 +12636,7 @@
         <v>0.484200000762939</v>
       </c>
       <c r="G423" t="n">
-        <v>0.372024983167648</v>
+        <v>0.372025012969971</v>
       </c>
       <c r="H423" t="n">
         <v>194596</v>
@@ -12694,7 +12694,7 @@
         <v>0.494899988174438</v>
       </c>
       <c r="G425" t="n">
-        <v>0.380246132612228</v>
+        <v>0.380246102809906</v>
       </c>
       <c r="H425" t="n">
         <v>856942</v>
@@ -12752,7 +12752,7 @@
         <v>0.527999997138977</v>
       </c>
       <c r="G427" t="n">
-        <v>0.405677855014801</v>
+        <v>0.405677825212479</v>
       </c>
       <c r="H427" t="n">
         <v>3355365</v>
@@ -12781,7 +12781,7 @@
         <v>0.547999978065491</v>
       </c>
       <c r="G428" t="n">
-        <v>0.421044379472733</v>
+        <v>0.421044409275055</v>
       </c>
       <c r="H428" t="n">
         <v>5904216</v>
@@ -12810,7 +12810,7 @@
         <v>0.546000003814697</v>
       </c>
       <c r="G429" t="n">
-        <v>0.419507771730423</v>
+        <v>0.419507741928101</v>
       </c>
       <c r="H429" t="n">
         <v>2853310</v>
@@ -12839,7 +12839,7 @@
         <v>0.516499996185303</v>
       </c>
       <c r="G430" t="n">
-        <v>0.396842032670975</v>
+        <v>0.396842062473297</v>
       </c>
       <c r="H430" t="n">
         <v>1142932</v>
@@ -12926,7 +12926,7 @@
         <v>0.543500006198883</v>
       </c>
       <c r="G433" t="n">
-        <v>0.417586892843246</v>
+        <v>0.417586952447891</v>
       </c>
       <c r="H433" t="n">
         <v>1375944</v>
@@ -12955,7 +12955,7 @@
         <v>0.555000007152557</v>
       </c>
       <c r="G434" t="n">
-        <v>0.426422744989395</v>
+        <v>0.42642268538475</v>
       </c>
       <c r="H434" t="n">
         <v>1453142</v>
@@ -12984,7 +12984,7 @@
         <v>0.550999999046326</v>
       </c>
       <c r="G435" t="n">
-        <v>0.423349410295486</v>
+        <v>0.423349380493164</v>
       </c>
       <c r="H435" t="n">
         <v>873449</v>
@@ -13042,7 +13042,7 @@
         <v>0.547999978065491</v>
       </c>
       <c r="G437" t="n">
-        <v>0.421044379472733</v>
+        <v>0.421044409275055</v>
       </c>
       <c r="H437" t="n">
         <v>267953</v>
@@ -13071,7 +13071,7 @@
         <v>0.543500006198883</v>
       </c>
       <c r="G438" t="n">
-        <v>0.417586892843246</v>
+        <v>0.417586952447891</v>
       </c>
       <c r="H438" t="n">
         <v>184635</v>
@@ -13158,7 +13158,7 @@
         <v>0.568499982357025</v>
       </c>
       <c r="G441" t="n">
-        <v>0.436795175075531</v>
+        <v>0.436795204877853</v>
       </c>
       <c r="H441" t="n">
         <v>2440736</v>
@@ -13187,7 +13187,7 @@
         <v>0.563499987125397</v>
       </c>
       <c r="G442" t="n">
-        <v>0.432953506708145</v>
+        <v>0.432953476905823</v>
       </c>
       <c r="H442" t="n">
         <v>787757</v>
@@ -13216,7 +13216,7 @@
         <v>0.58950001001358</v>
       </c>
       <c r="G443" t="n">
-        <v>0.452930122613907</v>
+        <v>0.452930092811584</v>
       </c>
       <c r="H443" t="n">
         <v>2357886</v>
@@ -13245,7 +13245,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G444" t="n">
-        <v>0.459460854530334</v>
+        <v>0.459460914134979</v>
       </c>
       <c r="H444" t="n">
         <v>2902956</v>
@@ -13274,7 +13274,7 @@
         <v>0.605499982833862</v>
       </c>
       <c r="G445" t="n">
-        <v>0.465223342180252</v>
+        <v>0.46522331237793</v>
       </c>
       <c r="H445" t="n">
         <v>2721489</v>
@@ -13303,7 +13303,7 @@
         <v>0.609499990940094</v>
       </c>
       <c r="G446" t="n">
-        <v>0.468296647071838</v>
+        <v>0.468296617269516</v>
       </c>
       <c r="H446" t="n">
         <v>2607914</v>
@@ -13361,7 +13361,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G448" t="n">
-        <v>0.522463858127594</v>
+        <v>0.522463917732239</v>
       </c>
       <c r="H448" t="n">
         <v>3477294</v>
@@ -13477,7 +13477,7 @@
         <v>0.671000003814697</v>
       </c>
       <c r="G452" t="n">
-        <v>0.515548884868622</v>
+        <v>0.515548944473267</v>
       </c>
       <c r="H452" t="n">
         <v>1985878</v>
@@ -13535,7 +13535,7 @@
         <v>0.637499988079071</v>
       </c>
       <c r="G454" t="n">
-        <v>0.48980987071991</v>
+        <v>0.489809811115265</v>
       </c>
       <c r="H454" t="n">
         <v>1206247</v>
@@ -13564,7 +13564,7 @@
         <v>0.625</v>
       </c>
       <c r="G455" t="n">
-        <v>0.480205744504929</v>
+        <v>0.480205684900284</v>
       </c>
       <c r="H455" t="n">
         <v>1419629</v>
@@ -13593,7 +13593,7 @@
         <v>0.675499975681305</v>
       </c>
       <c r="G456" t="n">
-        <v>0.519006311893463</v>
+        <v>0.519006371498108</v>
       </c>
       <c r="H456" t="n">
         <v>5995627</v>
@@ -13622,7 +13622,7 @@
         <v>0.665499985218048</v>
       </c>
       <c r="G457" t="n">
-        <v>0.511323094367981</v>
+        <v>0.511323034763336</v>
       </c>
       <c r="H457" t="n">
         <v>1930164</v>
@@ -13651,7 +13651,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G458" t="n">
-        <v>0.499413967132568</v>
+        <v>0.499413907527924</v>
       </c>
       <c r="H458" t="n">
         <v>792662</v>
@@ -13680,7 +13680,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G459" t="n">
-        <v>0.491730660200119</v>
+        <v>0.491730719804764</v>
       </c>
       <c r="H459" t="n">
         <v>2176421</v>
@@ -13709,7 +13709,7 @@
         <v>0.630500018596649</v>
       </c>
       <c r="G460" t="n">
-        <v>0.484431564807892</v>
+        <v>0.484431624412537</v>
       </c>
       <c r="H460" t="n">
         <v>471570</v>
@@ -13738,7 +13738,7 @@
         <v>0.629499971866608</v>
       </c>
       <c r="G461" t="n">
-        <v>0.483663201332092</v>
+        <v>0.483663260936737</v>
       </c>
       <c r="H461" t="n">
         <v>655932</v>
@@ -13767,7 +13767,7 @@
         <v>0.625</v>
       </c>
       <c r="G462" t="n">
-        <v>0.480205744504929</v>
+        <v>0.480205684900284</v>
       </c>
       <c r="H462" t="n">
         <v>797115</v>
@@ -13796,7 +13796,7 @@
         <v>0.630500018596649</v>
       </c>
       <c r="G463" t="n">
-        <v>0.484431564807892</v>
+        <v>0.484431624412537</v>
       </c>
       <c r="H463" t="n">
         <v>1281815</v>
@@ -13825,7 +13825,7 @@
         <v>0.630999982357025</v>
       </c>
       <c r="G464" t="n">
-        <v>0.484815776348114</v>
+        <v>0.484815716743469</v>
       </c>
       <c r="H464" t="n">
         <v>492026</v>
@@ -13854,7 +13854,7 @@
         <v>0.637499988079071</v>
       </c>
       <c r="G465" t="n">
-        <v>0.48980987071991</v>
+        <v>0.489809811115265</v>
       </c>
       <c r="H465" t="n">
         <v>365015</v>
@@ -13883,7 +13883,7 @@
         <v>0.625</v>
       </c>
       <c r="G466" t="n">
-        <v>0.480205744504929</v>
+        <v>0.480205684900284</v>
       </c>
       <c r="H466" t="n">
         <v>314448</v>
@@ -13912,7 +13912,7 @@
         <v>0.644500017166138</v>
       </c>
       <c r="G467" t="n">
-        <v>0.495188236236572</v>
+        <v>0.495188176631927</v>
       </c>
       <c r="H467" t="n">
         <v>1017227</v>
@@ -13941,7 +13941,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G468" t="n">
-        <v>0.490193963050842</v>
+        <v>0.490194022655487</v>
       </c>
       <c r="H468" t="n">
         <v>625767</v>
@@ -13970,7 +13970,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G469" t="n">
-        <v>0.491730660200119</v>
+        <v>0.491730719804764</v>
       </c>
       <c r="H469" t="n">
         <v>617988</v>
@@ -13999,7 +13999,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G470" t="n">
-        <v>0.491730660200119</v>
+        <v>0.491730719804764</v>
       </c>
       <c r="H470" t="n">
         <v>957316</v>
@@ -14057,7 +14057,7 @@
         <v>0.70550000667572</v>
       </c>
       <c r="G472" t="n">
-        <v>0.542056202888489</v>
+        <v>0.542056262493134</v>
       </c>
       <c r="H472" t="n">
         <v>3198240</v>
@@ -14173,7 +14173,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G476" t="n">
-        <v>0.582393527030945</v>
+        <v>0.58239358663559</v>
       </c>
       <c r="H476" t="n">
         <v>2846001</v>
@@ -14231,7 +14231,7 @@
         <v>0.745500028133392</v>
       </c>
       <c r="G478" t="n">
-        <v>0.572789371013641</v>
+        <v>0.572789430618286</v>
       </c>
       <c r="H478" t="n">
         <v>1923656</v>
@@ -14260,7 +14260,7 @@
         <v>0.718999981880188</v>
       </c>
       <c r="G479" t="n">
-        <v>0.552428662776947</v>
+        <v>0.552428722381592</v>
       </c>
       <c r="H479" t="n">
         <v>1597999</v>
@@ -14289,7 +14289,7 @@
         <v>0.717499971389771</v>
       </c>
       <c r="G480" t="n">
-        <v>0.551276206970215</v>
+        <v>0.55127626657486</v>
       </c>
       <c r="H480" t="n">
         <v>2103563</v>
@@ -14318,7 +14318,7 @@
         <v>0.709500014781952</v>
       </c>
       <c r="G481" t="n">
-        <v>0.545129597187042</v>
+        <v>0.545129656791687</v>
       </c>
       <c r="H481" t="n">
         <v>3010065</v>
@@ -14376,7 +14376,7 @@
         <v>0.736500024795532</v>
       </c>
       <c r="G483" t="n">
-        <v>0.565874457359314</v>
+        <v>0.565874516963959</v>
       </c>
       <c r="H483" t="n">
         <v>1180805</v>
@@ -14463,7 +14463,7 @@
         <v>0.760999977588654</v>
       </c>
       <c r="G486" t="n">
-        <v>0.584698498249054</v>
+        <v>0.584698557853699</v>
       </c>
       <c r="H486" t="n">
         <v>1269607</v>
@@ -14550,7 +14550,7 @@
         <v>0.807500004768372</v>
       </c>
       <c r="G489" t="n">
-        <v>0.620425879955292</v>
+        <v>0.620425820350647</v>
       </c>
       <c r="H489" t="n">
         <v>1738954</v>
@@ -14579,7 +14579,7 @@
         <v>0.819500029087067</v>
       </c>
       <c r="G490" t="n">
-        <v>0.629645764827728</v>
+        <v>0.629645824432373</v>
       </c>
       <c r="H490" t="n">
         <v>1071537</v>
@@ -14637,7 +14637,7 @@
         <v>0.791000008583069</v>
       </c>
       <c r="G492" t="n">
-        <v>0.60774838924408</v>
+        <v>0.607748448848724</v>
       </c>
       <c r="H492" t="n">
         <v>1721522</v>
@@ -14666,7 +14666,7 @@
         <v>0.757000029087067</v>
       </c>
       <c r="G493" t="n">
-        <v>0.58162522315979</v>
+        <v>0.581625163555145</v>
       </c>
       <c r="H493" t="n">
         <v>2396861</v>
@@ -14782,7 +14782,7 @@
         <v>0.778500020503998</v>
       </c>
       <c r="G497" t="n">
-        <v>0.598144233226776</v>
+        <v>0.598144352436066</v>
       </c>
       <c r="H497" t="n">
         <v>1934363</v>
@@ -14811,7 +14811,7 @@
         <v>0.806500017642975</v>
       </c>
       <c r="G498" t="n">
-        <v>0.619657576084137</v>
+        <v>0.619657516479492</v>
       </c>
       <c r="H498" t="n">
         <v>1410976</v>
@@ -14927,7 +14927,7 @@
         <v>0.782999992370605</v>
       </c>
       <c r="G502" t="n">
-        <v>0.601601719856262</v>
+        <v>0.601601779460907</v>
       </c>
       <c r="H502" t="n">
         <v>686895</v>
@@ -14956,7 +14956,7 @@
         <v>0.763499975204468</v>
       </c>
       <c r="G503" t="n">
-        <v>0.586619317531586</v>
+        <v>0.586619257926941</v>
       </c>
       <c r="H503" t="n">
         <v>629558</v>
@@ -14985,7 +14985,7 @@
         <v>0.774999976158142</v>
       </c>
       <c r="G504" t="n">
-        <v>0.595455229282379</v>
+        <v>0.595455169677734</v>
       </c>
       <c r="H504" t="n">
         <v>398641</v>
@@ -15014,7 +15014,7 @@
         <v>0.764999985694885</v>
       </c>
       <c r="G505" t="n">
-        <v>0.587771832942963</v>
+        <v>0.587771892547607</v>
       </c>
       <c r="H505" t="n">
         <v>291417</v>
@@ -15043,7 +15043,7 @@
         <v>0.760500013828278</v>
       </c>
       <c r="G506" t="n">
-        <v>0.584314346313477</v>
+        <v>0.584314405918121</v>
       </c>
       <c r="H506" t="n">
         <v>770527</v>
@@ -15130,7 +15130,7 @@
         <v>0.737999975681305</v>
       </c>
       <c r="G509" t="n">
-        <v>0.567026913166046</v>
+        <v>0.567026972770691</v>
       </c>
       <c r="H509" t="n">
         <v>744111</v>
@@ -15188,7 +15188,7 @@
         <v>0.707499980926514</v>
       </c>
       <c r="G511" t="n">
-        <v>0.543592870235443</v>
+        <v>0.543592929840088</v>
       </c>
       <c r="H511" t="n">
         <v>1726266</v>
@@ -15246,7 +15246,7 @@
         <v>0.732999980449677</v>
       </c>
       <c r="G513" t="n">
-        <v>0.563185334205627</v>
+        <v>0.563185274600983</v>
       </c>
       <c r="H513" t="n">
         <v>378186</v>
@@ -15304,7 +15304,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G515" t="n">
-        <v>0.582393527030945</v>
+        <v>0.58239358663559</v>
       </c>
       <c r="H515" t="n">
         <v>912363</v>
@@ -15333,7 +15333,7 @@
         <v>0.782999992370605</v>
       </c>
       <c r="G516" t="n">
-        <v>0.601601719856262</v>
+        <v>0.601601779460907</v>
       </c>
       <c r="H516" t="n">
         <v>878883</v>
@@ -15391,7 +15391,7 @@
         <v>0.755999982357025</v>
       </c>
       <c r="G518" t="n">
-        <v>0.58085685968399</v>
+        <v>0.580856800079346</v>
       </c>
       <c r="H518" t="n">
         <v>526919</v>
@@ -15449,7 +15449,7 @@
         <v>0.787000000476837</v>
       </c>
       <c r="G520" t="n">
-        <v>0.604675054550171</v>
+        <v>0.60467517375946</v>
       </c>
       <c r="H520" t="n">
         <v>1157691</v>
@@ -15478,7 +15478,7 @@
         <v>0.819000005722046</v>
       </c>
       <c r="G521" t="n">
-        <v>0.629261612892151</v>
+        <v>0.629261672496796</v>
       </c>
       <c r="H521" t="n">
         <v>1461439</v>
@@ -15536,7 +15536,7 @@
         <v>0.791000008583069</v>
       </c>
       <c r="G523" t="n">
-        <v>0.60774838924408</v>
+        <v>0.607748448848724</v>
       </c>
       <c r="H523" t="n">
         <v>797771</v>
@@ -15710,7 +15710,7 @@
         <v>0.77700001001358</v>
       </c>
       <c r="G529" t="n">
-        <v>0.596991717815399</v>
+        <v>0.596991777420044</v>
       </c>
       <c r="H529" t="n">
         <v>304526</v>
@@ -15797,7 +15797,7 @@
         <v>0.767000019550323</v>
       </c>
       <c r="G532" t="n">
-        <v>0.589308559894562</v>
+        <v>0.589308500289917</v>
       </c>
       <c r="H532" t="n">
         <v>857549</v>
@@ -15942,7 +15942,7 @@
         <v>0.700999975204468</v>
       </c>
       <c r="G537" t="n">
-        <v>0.538598775863647</v>
+        <v>0.538598716259003</v>
       </c>
       <c r="H537" t="n">
         <v>1837563</v>
@@ -15971,7 +15971,7 @@
         <v>0.725000023841858</v>
       </c>
       <c r="G538" t="n">
-        <v>0.55703866481781</v>
+        <v>0.557038724422455</v>
       </c>
       <c r="H538" t="n">
         <v>575621</v>
@@ -16000,7 +16000,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G539" t="n">
-        <v>0.536293804645538</v>
+        <v>0.536293745040894</v>
       </c>
       <c r="H539" t="n">
         <v>664784</v>
@@ -16029,7 +16029,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G540" t="n">
-        <v>0.524000585079193</v>
+        <v>0.524000465869904</v>
       </c>
       <c r="H540" t="n">
         <v>1040600</v>
@@ -16087,7 +16087,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G542" t="n">
-        <v>0.524000585079193</v>
+        <v>0.524000465869904</v>
       </c>
       <c r="H542" t="n">
         <v>666277</v>
@@ -16116,7 +16116,7 @@
         <v>0.712999999523163</v>
       </c>
       <c r="G543" t="n">
-        <v>0.547818720340729</v>
+        <v>0.547818660736084</v>
       </c>
       <c r="H543" t="n">
         <v>339439</v>
@@ -16232,7 +16232,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G547" t="n">
-        <v>0.522463858127594</v>
+        <v>0.522463917732239</v>
       </c>
       <c r="H547" t="n">
         <v>306515</v>
@@ -16261,7 +16261,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G548" t="n">
-        <v>0.522463858127594</v>
+        <v>0.522463917732239</v>
       </c>
       <c r="H548" t="n">
         <v>170513</v>
@@ -16406,7 +16406,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G553" t="n">
-        <v>0.536293804645538</v>
+        <v>0.536293745040894</v>
       </c>
       <c r="H553" t="n">
         <v>494063</v>
@@ -16435,7 +16435,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G554" t="n">
-        <v>0.520927250385284</v>
+        <v>0.52092719078064</v>
       </c>
       <c r="H554" t="n">
         <v>1172041</v>
@@ -16522,7 +16522,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G557" t="n">
-        <v>0.517853856086731</v>
+        <v>0.517853915691376</v>
       </c>
       <c r="H557" t="n">
         <v>190984</v>
@@ -16551,7 +16551,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G558" t="n">
-        <v>0.517853856086731</v>
+        <v>0.517853915691376</v>
       </c>
       <c r="H558" t="n">
         <v>271346</v>
@@ -16580,7 +16580,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G559" t="n">
-        <v>0.525537252426147</v>
+        <v>0.525537133216858</v>
       </c>
       <c r="H559" t="n">
         <v>293443</v>
@@ -16638,7 +16638,7 @@
         <v>0.680999994277954</v>
       </c>
       <c r="G561" t="n">
-        <v>0.523232281208038</v>
+        <v>0.523232221603394</v>
       </c>
       <c r="H561" t="n">
         <v>294261</v>
@@ -16667,7 +16667,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G562" t="n">
-        <v>0.51939058303833</v>
+        <v>0.519390523433685</v>
       </c>
       <c r="H562" t="n">
         <v>496974</v>
@@ -16754,7 +16754,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G565" t="n">
-        <v>0.524000585079193</v>
+        <v>0.524000465869904</v>
       </c>
       <c r="H565" t="n">
         <v>248564</v>
@@ -16783,7 +16783,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G566" t="n">
-        <v>0.525537252426147</v>
+        <v>0.525537133216858</v>
       </c>
       <c r="H566" t="n">
         <v>384764</v>
@@ -16812,7 +16812,7 @@
         <v>0.757000029087067</v>
       </c>
       <c r="G567" t="n">
-        <v>0.58162522315979</v>
+        <v>0.581625163555145</v>
       </c>
       <c r="H567" t="n">
         <v>1402702</v>
@@ -16899,7 +16899,7 @@
         <v>0.640999972820282</v>
       </c>
       <c r="G570" t="n">
-        <v>0.492498964071274</v>
+        <v>0.492499023675919</v>
       </c>
       <c r="H570" t="n">
         <v>810346</v>
@@ -16957,7 +16957,7 @@
         <v>0.625</v>
       </c>
       <c r="G572" t="n">
-        <v>0.480205744504929</v>
+        <v>0.480205684900284</v>
       </c>
       <c r="H572" t="n">
         <v>400786</v>
@@ -16986,7 +16986,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G573" t="n">
-        <v>0.476364105939865</v>
+        <v>0.476364135742188</v>
       </c>
       <c r="H573" t="n">
         <v>807098</v>
@@ -17015,7 +17015,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G574" t="n">
-        <v>0.488657355308533</v>
+        <v>0.488657414913177</v>
       </c>
       <c r="H574" t="n">
         <v>370134</v>
@@ -17044,7 +17044,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G575" t="n">
-        <v>0.476364105939865</v>
+        <v>0.476364135742188</v>
       </c>
       <c r="H575" t="n">
         <v>567599</v>
@@ -17073,7 +17073,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G576" t="n">
-        <v>0.471754193305969</v>
+        <v>0.471754163503647</v>
       </c>
       <c r="H576" t="n">
         <v>626363</v>
@@ -17102,7 +17102,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G577" t="n">
-        <v>0.491730660200119</v>
+        <v>0.491730719804764</v>
       </c>
       <c r="H577" t="n">
         <v>415872</v>
@@ -17160,7 +17160,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G579" t="n">
-        <v>0.468680858612061</v>
+        <v>0.468680799007416</v>
       </c>
       <c r="H579" t="n">
         <v>303534</v>
@@ -17189,7 +17189,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G580" t="n">
-        <v>0.487120658159256</v>
+        <v>0.487120717763901</v>
       </c>
       <c r="H580" t="n">
         <v>575824</v>
@@ -17218,7 +17218,7 @@
         <v>0.630999982357025</v>
       </c>
       <c r="G581" t="n">
-        <v>0.484815776348114</v>
+        <v>0.484815716743469</v>
       </c>
       <c r="H581" t="n">
         <v>280953</v>
@@ -17247,7 +17247,7 @@
         <v>0.626999974250793</v>
       </c>
       <c r="G582" t="n">
-        <v>0.481742471456528</v>
+        <v>0.481742411851883</v>
       </c>
       <c r="H582" t="n">
         <v>175022</v>
@@ -17305,7 +17305,7 @@
         <v>0.629000008106232</v>
       </c>
       <c r="G584" t="n">
-        <v>0.48327910900116</v>
+        <v>0.483279049396515</v>
       </c>
       <c r="H584" t="n">
         <v>110289</v>
@@ -17334,7 +17334,7 @@
         <v>0.623000025749207</v>
       </c>
       <c r="G585" t="n">
-        <v>0.478669166564941</v>
+        <v>0.478669106960297</v>
       </c>
       <c r="H585" t="n">
         <v>134620</v>
@@ -17363,7 +17363,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G586" t="n">
-        <v>0.470217525959015</v>
+        <v>0.47021746635437</v>
       </c>
       <c r="H586" t="n">
         <v>429416</v>
@@ -17392,7 +17392,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G587" t="n">
-        <v>0.468680858612061</v>
+        <v>0.468680799007416</v>
       </c>
       <c r="H587" t="n">
         <v>511078</v>
@@ -17421,7 +17421,7 @@
         <v>0.609000027179718</v>
       </c>
       <c r="G588" t="n">
-        <v>0.467912584543228</v>
+        <v>0.467912495136261</v>
       </c>
       <c r="H588" t="n">
         <v>258351</v>
@@ -17450,7 +17450,7 @@
         <v>0.60699999332428</v>
       </c>
       <c r="G589" t="n">
-        <v>0.466375797986984</v>
+        <v>0.466375827789307</v>
       </c>
       <c r="H589" t="n">
         <v>484930</v>
@@ -17479,7 +17479,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G590" t="n">
-        <v>0.470217525959015</v>
+        <v>0.47021746635437</v>
       </c>
       <c r="H590" t="n">
         <v>265449</v>
@@ -17508,7 +17508,7 @@
         <v>0.605000019073486</v>
       </c>
       <c r="G591" t="n">
-        <v>0.464839190244675</v>
+        <v>0.464839220046997</v>
       </c>
       <c r="H591" t="n">
         <v>109147</v>
@@ -17537,7 +17537,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G592" t="n">
-        <v>0.470217525959015</v>
+        <v>0.47021746635437</v>
       </c>
       <c r="H592" t="n">
         <v>453837</v>
@@ -17566,7 +17566,7 @@
         <v>0.601000010967255</v>
       </c>
       <c r="G593" t="n">
-        <v>0.461765915155411</v>
+        <v>0.461765885353088</v>
       </c>
       <c r="H593" t="n">
         <v>247749</v>
@@ -17595,7 +17595,7 @@
         <v>0.601000010967255</v>
       </c>
       <c r="G594" t="n">
-        <v>0.461765915155411</v>
+        <v>0.461765885353088</v>
       </c>
       <c r="H594" t="n">
         <v>367678</v>
@@ -17624,7 +17624,7 @@
         <v>0.634999990463257</v>
       </c>
       <c r="G595" t="n">
-        <v>0.487888962030411</v>
+        <v>0.487889021635056</v>
       </c>
       <c r="H595" t="n">
         <v>672923</v>
@@ -17653,7 +17653,7 @@
         <v>0.634999990463257</v>
       </c>
       <c r="G596" t="n">
-        <v>0.487888962030411</v>
+        <v>0.487889021635056</v>
       </c>
       <c r="H596" t="n">
         <v>683406</v>
@@ -17682,7 +17682,7 @@
         <v>0.625</v>
       </c>
       <c r="G597" t="n">
-        <v>0.480205744504929</v>
+        <v>0.480205684900284</v>
       </c>
       <c r="H597" t="n">
         <v>560249</v>
@@ -17711,7 +17711,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G598" t="n">
-        <v>0.491730660200119</v>
+        <v>0.491730719804764</v>
       </c>
       <c r="H598" t="n">
         <v>313393</v>
@@ -17769,7 +17769,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G600" t="n">
-        <v>0.487120658159256</v>
+        <v>0.487120717763901</v>
       </c>
       <c r="H600" t="n">
         <v>708161</v>
@@ -17856,7 +17856,7 @@
         <v>0.578999996185303</v>
       </c>
       <c r="G603" t="n">
-        <v>0.444862574338913</v>
+        <v>0.444862604141235</v>
       </c>
       <c r="H603" t="n">
         <v>479866</v>
@@ -17914,7 +17914,7 @@
         <v>0.555000007152557</v>
       </c>
       <c r="G605" t="n">
-        <v>0.426422744989395</v>
+        <v>0.42642268538475</v>
       </c>
       <c r="H605" t="n">
         <v>455127</v>
@@ -17943,7 +17943,7 @@
         <v>0.578000009059906</v>
       </c>
       <c r="G606" t="n">
-        <v>0.444094300270081</v>
+        <v>0.444094270467758</v>
       </c>
       <c r="H606" t="n">
         <v>586906</v>
@@ -18001,7 +18001,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G608" t="n">
-        <v>0.424117684364319</v>
+        <v>0.424117743968964</v>
       </c>
       <c r="H608" t="n">
         <v>174759</v>
@@ -18088,7 +18088,7 @@
         <v>0.541000008583069</v>
       </c>
       <c r="G611" t="n">
-        <v>0.415666103363037</v>
+        <v>0.415666162967682</v>
       </c>
       <c r="H611" t="n">
         <v>171017</v>
@@ -18117,7 +18117,7 @@
         <v>0.527999997138977</v>
       </c>
       <c r="G612" t="n">
-        <v>0.405677855014801</v>
+        <v>0.405677825212479</v>
       </c>
       <c r="H612" t="n">
         <v>270241</v>
@@ -18146,7 +18146,7 @@
         <v>0.497999995946884</v>
       </c>
       <c r="G613" t="n">
-        <v>0.382627964019775</v>
+        <v>0.382627934217453</v>
       </c>
       <c r="H613" t="n">
         <v>786586</v>
@@ -18175,7 +18175,7 @@
         <v>0.493499994277954</v>
       </c>
       <c r="G614" t="n">
-        <v>0.379170477390289</v>
+        <v>0.379170447587967</v>
       </c>
       <c r="H614" t="n">
         <v>789863</v>
@@ -18233,7 +18233,7 @@
         <v>0.501999974250793</v>
       </c>
       <c r="G616" t="n">
-        <v>0.385701298713684</v>
+        <v>0.385701239109039</v>
       </c>
       <c r="H616" t="n">
         <v>265244</v>
@@ -18262,7 +18262,7 @@
         <v>0.527999997138977</v>
       </c>
       <c r="G617" t="n">
-        <v>0.405677855014801</v>
+        <v>0.405677825212479</v>
       </c>
       <c r="H617" t="n">
         <v>896735</v>
@@ -18291,7 +18291,7 @@
         <v>0.501999974250793</v>
       </c>
       <c r="G618" t="n">
-        <v>0.385701298713684</v>
+        <v>0.385701239109039</v>
       </c>
       <c r="H618" t="n">
         <v>454561</v>
@@ -18320,7 +18320,7 @@
         <v>0.505999982357025</v>
       </c>
       <c r="G619" t="n">
-        <v>0.388774544000626</v>
+        <v>0.388774573802948</v>
       </c>
       <c r="H619" t="n">
         <v>268831</v>
@@ -18349,7 +18349,7 @@
         <v>0.497999995946884</v>
       </c>
       <c r="G620" t="n">
-        <v>0.382627964019775</v>
+        <v>0.382627934217453</v>
       </c>
       <c r="H620" t="n">
         <v>231113</v>
@@ -18436,7 +18436,7 @@
         <v>0.501999974250793</v>
       </c>
       <c r="G623" t="n">
-        <v>0.385701298713684</v>
+        <v>0.385701239109039</v>
       </c>
       <c r="H623" t="n">
         <v>193213</v>
@@ -18494,7 +18494,7 @@
         <v>0.477999985218048</v>
       </c>
       <c r="G625" t="n">
-        <v>0.367261350154877</v>
+        <v>0.367261320352554</v>
       </c>
       <c r="H625" t="n">
         <v>428299</v>
@@ -18552,7 +18552,7 @@
         <v>0.469999998807907</v>
       </c>
       <c r="G627" t="n">
-        <v>0.361114710569382</v>
+        <v>0.361114770174026</v>
       </c>
       <c r="H627" t="n">
         <v>324398</v>
@@ -18581,7 +18581,7 @@
         <v>0.469999998807907</v>
       </c>
       <c r="G628" t="n">
-        <v>0.361114710569382</v>
+        <v>0.361114770174026</v>
       </c>
       <c r="H628" t="n">
         <v>249481</v>
@@ -18610,7 +18610,7 @@
         <v>0.469999998807907</v>
       </c>
       <c r="G629" t="n">
-        <v>0.361114710569382</v>
+        <v>0.361114770174026</v>
       </c>
       <c r="H629" t="n">
         <v>239266</v>
@@ -18668,7 +18668,7 @@
         <v>0.458499997854233</v>
       </c>
       <c r="G631" t="n">
-        <v>0.352278977632523</v>
+        <v>0.3522789478302</v>
       </c>
       <c r="H631" t="n">
         <v>141828</v>
@@ -18697,7 +18697,7 @@
         <v>0.46399998664856</v>
       </c>
       <c r="G632" t="n">
-        <v>0.356504738330841</v>
+        <v>0.356504708528519</v>
       </c>
       <c r="H632" t="n">
         <v>212641</v>
@@ -18726,7 +18726,7 @@
         <v>0.483500003814697</v>
       </c>
       <c r="G633" t="n">
-        <v>0.37148717045784</v>
+        <v>0.371487200260162</v>
       </c>
       <c r="H633" t="n">
         <v>728009</v>
@@ -18755,7 +18755,7 @@
         <v>0.479000002145767</v>
       </c>
       <c r="G634" t="n">
-        <v>0.368029654026031</v>
+        <v>0.368029683828354</v>
       </c>
       <c r="H634" t="n">
         <v>552999</v>
@@ -18784,7 +18784,7 @@
         <v>0.484499990940094</v>
       </c>
       <c r="G635" t="n">
-        <v>0.37225553393364</v>
+        <v>0.372255504131317</v>
       </c>
       <c r="H635" t="n">
         <v>340863</v>
@@ -18813,7 +18813,7 @@
         <v>0.469999998807907</v>
       </c>
       <c r="G636" t="n">
-        <v>0.361114710569382</v>
+        <v>0.361114770174026</v>
       </c>
       <c r="H636" t="n">
         <v>513781</v>
@@ -18871,7 +18871,7 @@
         <v>0.479000002145767</v>
       </c>
       <c r="G638" t="n">
-        <v>0.368029654026031</v>
+        <v>0.368029683828354</v>
       </c>
       <c r="H638" t="n">
         <v>148498</v>
@@ -18900,7 +18900,7 @@
         <v>0.488000005483627</v>
       </c>
       <c r="G639" t="n">
-        <v>0.374944657087326</v>
+        <v>0.374944686889648</v>
       </c>
       <c r="H639" t="n">
         <v>285837</v>
@@ -18929,7 +18929,7 @@
         <v>0.476999998092651</v>
       </c>
       <c r="G640" t="n">
-        <v>0.3664930164814</v>
+        <v>0.366493046283722</v>
       </c>
       <c r="H640" t="n">
         <v>166528</v>
@@ -18958,7 +18958,7 @@
         <v>0.487500011920929</v>
       </c>
       <c r="G641" t="n">
-        <v>0.374560534954071</v>
+        <v>0.374560475349426</v>
       </c>
       <c r="H641" t="n">
         <v>262393</v>
@@ -18987,7 +18987,7 @@
         <v>0.479000002145767</v>
       </c>
       <c r="G642" t="n">
-        <v>0.368029654026031</v>
+        <v>0.368029683828354</v>
       </c>
       <c r="H642" t="n">
         <v>146480</v>
@@ -19045,7 +19045,7 @@
         <v>0.493000000715256</v>
       </c>
       <c r="G644" t="n">
-        <v>0.378786325454712</v>
+        <v>0.37878629565239</v>
       </c>
       <c r="H644" t="n">
         <v>341997</v>
@@ -19074,7 +19074,7 @@
         <v>0.479000002145767</v>
       </c>
       <c r="G645" t="n">
-        <v>0.368029654026031</v>
+        <v>0.368029683828354</v>
       </c>
       <c r="H645" t="n">
         <v>335219</v>
@@ -19132,7 +19132,7 @@
         <v>0.460500001907349</v>
       </c>
       <c r="G647" t="n">
-        <v>0.353815615177155</v>
+        <v>0.353815644979477</v>
       </c>
       <c r="H647" t="n">
         <v>233551</v>
@@ -19161,7 +19161,7 @@
         <v>0.461499989032745</v>
       </c>
       <c r="G648" t="n">
-        <v>0.354583919048309</v>
+        <v>0.354583948850632</v>
       </c>
       <c r="H648" t="n">
         <v>200069</v>
@@ -19277,7 +19277,7 @@
         <v>0.476999998092651</v>
       </c>
       <c r="G652" t="n">
-        <v>0.3664930164814</v>
+        <v>0.366493046283722</v>
       </c>
       <c r="H652" t="n">
         <v>179916</v>
@@ -19306,7 +19306,7 @@
         <v>0.460999995470047</v>
       </c>
       <c r="G653" t="n">
-        <v>0.35419973731041</v>
+        <v>0.354199767112732</v>
       </c>
       <c r="H653" t="n">
         <v>297549</v>
@@ -19335,7 +19335,7 @@
         <v>0.458999991416931</v>
       </c>
       <c r="G654" t="n">
-        <v>0.352663099765778</v>
+        <v>0.352663069963455</v>
       </c>
       <c r="H654" t="n">
         <v>167442</v>
@@ -19393,7 +19393,7 @@
         <v>0.514999985694885</v>
       </c>
       <c r="G656" t="n">
-        <v>0.395689517259598</v>
+        <v>0.39568954706192</v>
       </c>
       <c r="H656" t="n">
         <v>1150425</v>
@@ -19451,7 +19451,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G658" t="n">
-        <v>0.411056131124496</v>
+        <v>0.411056160926819</v>
       </c>
       <c r="H658" t="n">
         <v>748133</v>
@@ -19509,7 +19509,7 @@
         <v>0.531000018119812</v>
       </c>
       <c r="G660" t="n">
-        <v>0.40798282623291</v>
+        <v>0.407982856035233</v>
       </c>
       <c r="H660" t="n">
         <v>307663</v>
@@ -19538,7 +19538,7 @@
         <v>0.500999987125397</v>
       </c>
       <c r="G661" t="n">
-        <v>0.384932965040207</v>
+        <v>0.384932935237885</v>
       </c>
       <c r="H661" t="n">
         <v>705239</v>
@@ -19625,7 +19625,7 @@
         <v>0.492000013589859</v>
       </c>
       <c r="G664" t="n">
-        <v>0.378017991781235</v>
+        <v>0.378017961978912</v>
       </c>
       <c r="H664" t="n">
         <v>230021</v>
@@ -19741,7 +19741,7 @@
         <v>0.467999994754791</v>
       </c>
       <c r="G668" t="n">
-        <v>0.359578043222427</v>
+        <v>0.35957807302475</v>
       </c>
       <c r="H668" t="n">
         <v>174123</v>
@@ -19799,7 +19799,7 @@
         <v>0.455000013113022</v>
       </c>
       <c r="G670" t="n">
-        <v>0.349589794874191</v>
+        <v>0.349589824676514</v>
       </c>
       <c r="H670" t="n">
         <v>256980</v>
@@ -19915,7 +19915,7 @@
         <v>0.460999995470047</v>
       </c>
       <c r="G674" t="n">
-        <v>0.35419973731041</v>
+        <v>0.354199767112732</v>
       </c>
       <c r="H674" t="n">
         <v>97167</v>
@@ -19944,7 +19944,7 @@
         <v>0.477999985218048</v>
       </c>
       <c r="G675" t="n">
-        <v>0.367261350154877</v>
+        <v>0.367261320352554</v>
       </c>
       <c r="H675" t="n">
         <v>289168</v>
@@ -20031,7 +20031,7 @@
         <v>0.465000003576279</v>
       </c>
       <c r="G678" t="n">
-        <v>0.357273101806641</v>
+        <v>0.357273072004318</v>
       </c>
       <c r="H678" t="n">
         <v>104824</v>
@@ -20060,7 +20060,7 @@
         <v>0.45550000667572</v>
       </c>
       <c r="G679" t="n">
-        <v>0.349974006414413</v>
+        <v>0.349973976612091</v>
       </c>
       <c r="H679" t="n">
         <v>212855</v>
@@ -20089,7 +20089,7 @@
         <v>0.441500008106232</v>
       </c>
       <c r="G680" t="n">
-        <v>0.339217334985733</v>
+        <v>0.339217364788055</v>
       </c>
       <c r="H680" t="n">
         <v>343832</v>
@@ -20118,7 +20118,7 @@
         <v>0.421499997377396</v>
       </c>
       <c r="G681" t="n">
-        <v>0.323850780725479</v>
+        <v>0.323850750923157</v>
       </c>
       <c r="H681" t="n">
         <v>724693</v>
@@ -20147,7 +20147,7 @@
         <v>0.470999985933304</v>
       </c>
       <c r="G682" t="n">
-        <v>0.361883014440536</v>
+        <v>0.361883044242859</v>
       </c>
       <c r="H682" t="n">
         <v>1236259</v>
@@ -20176,7 +20176,7 @@
         <v>0.456499993801117</v>
       </c>
       <c r="G683" t="n">
-        <v>0.350742250680923</v>
+        <v>0.350742280483246</v>
       </c>
       <c r="H683" t="n">
         <v>1135892</v>
@@ -20205,7 +20205,7 @@
         <v>0.507000029087067</v>
       </c>
       <c r="G684" t="n">
-        <v>0.389542937278748</v>
+        <v>0.389542907476425</v>
       </c>
       <c r="H684" t="n">
         <v>1589414</v>
@@ -20234,7 +20234,7 @@
         <v>0.526000022888184</v>
       </c>
       <c r="G685" t="n">
-        <v>0.404141157865524</v>
+        <v>0.404141187667847</v>
       </c>
       <c r="H685" t="n">
         <v>2064502</v>
@@ -20263,7 +20263,7 @@
         <v>0.515999972820282</v>
       </c>
       <c r="G686" t="n">
-        <v>0.396457850933075</v>
+        <v>0.396457821130753</v>
       </c>
       <c r="H686" t="n">
         <v>1376351</v>
@@ -20379,7 +20379,7 @@
         <v>0.513000011444092</v>
       </c>
       <c r="G690" t="n">
-        <v>0.394152879714966</v>
+        <v>0.394152909517288</v>
       </c>
       <c r="H690" t="n">
         <v>223583</v>
@@ -20466,7 +20466,7 @@
         <v>0.514999985694885</v>
       </c>
       <c r="G693" t="n">
-        <v>0.395689517259598</v>
+        <v>0.39568954706192</v>
       </c>
       <c r="H693" t="n">
         <v>131952</v>
@@ -20495,7 +20495,7 @@
         <v>0.522000014781952</v>
       </c>
       <c r="G694" t="n">
-        <v>0.401067852973938</v>
+        <v>0.40106788277626</v>
       </c>
       <c r="H694" t="n">
         <v>233957</v>
@@ -20524,7 +20524,7 @@
         <v>0.515999972820282</v>
       </c>
       <c r="G695" t="n">
-        <v>0.396457850933075</v>
+        <v>0.396457821130753</v>
       </c>
       <c r="H695" t="n">
         <v>197138</v>
@@ -20611,7 +20611,7 @@
         <v>0.513000011444092</v>
       </c>
       <c r="G698" t="n">
-        <v>0.394152879714966</v>
+        <v>0.394152909517288</v>
       </c>
       <c r="H698" t="n">
         <v>234451</v>
@@ -20640,7 +20640,7 @@
         <v>0.501999974250793</v>
       </c>
       <c r="G699" t="n">
-        <v>0.385701298713684</v>
+        <v>0.385701239109039</v>
       </c>
       <c r="H699" t="n">
         <v>198124</v>
@@ -20669,7 +20669,7 @@
         <v>0.488999992609024</v>
       </c>
       <c r="G700" t="n">
-        <v>0.375712960958481</v>
+        <v>0.375712990760803</v>
       </c>
       <c r="H700" t="n">
         <v>312921</v>
@@ -20727,7 +20727,7 @@
         <v>0.460999995470047</v>
       </c>
       <c r="G702" t="n">
-        <v>0.35419973731041</v>
+        <v>0.354199767112732</v>
       </c>
       <c r="H702" t="n">
         <v>261656</v>
@@ -20814,7 +20814,7 @@
         <v>0.458499997854233</v>
       </c>
       <c r="G705" t="n">
-        <v>0.352278977632523</v>
+        <v>0.3522789478302</v>
       </c>
       <c r="H705" t="n">
         <v>179603</v>
@@ -20872,7 +20872,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G707" t="n">
-        <v>0.336528211832047</v>
+        <v>0.336528182029724</v>
       </c>
       <c r="H707" t="n">
         <v>382310</v>
@@ -20930,7 +20930,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G709" t="n">
-        <v>0.337296545505524</v>
+        <v>0.337296485900879</v>
       </c>
       <c r="H709" t="n">
         <v>234804</v>
@@ -21046,7 +21046,7 @@
         <v>0.431499987840652</v>
       </c>
       <c r="G713" t="n">
-        <v>0.331534028053284</v>
+        <v>0.331534057855606</v>
       </c>
       <c r="H713" t="n">
         <v>307404</v>
@@ -21191,7 +21191,7 @@
         <v>0.407499998807907</v>
       </c>
       <c r="G718" t="n">
-        <v>0.313094139099121</v>
+        <v>0.313094109296799</v>
       </c>
       <c r="H718" t="n">
         <v>515214</v>
@@ -21220,7 +21220,7 @@
         <v>0.407000005245209</v>
       </c>
       <c r="G719" t="n">
-        <v>0.312709987163544</v>
+        <v>0.312709957361221</v>
       </c>
       <c r="H719" t="n">
         <v>303335</v>
@@ -21278,7 +21278,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G721" t="n">
-        <v>0.322698295116425</v>
+        <v>0.322698265314102</v>
       </c>
       <c r="H721" t="n">
         <v>347349</v>
@@ -21336,7 +21336,7 @@
         <v>0.424499988555908</v>
       </c>
       <c r="G723" t="n">
-        <v>0.326155751943588</v>
+        <v>0.326155722141266</v>
       </c>
       <c r="H723" t="n">
         <v>102043</v>
@@ -21365,7 +21365,7 @@
         <v>0.422500014305115</v>
       </c>
       <c r="G724" t="n">
-        <v>0.324619114398956</v>
+        <v>0.324619084596634</v>
       </c>
       <c r="H724" t="n">
         <v>278767</v>
@@ -21394,7 +21394,7 @@
         <v>0.42399999499321</v>
       </c>
       <c r="G725" t="n">
-        <v>0.325771570205688</v>
+        <v>0.325771600008011</v>
       </c>
       <c r="H725" t="n">
         <v>114286</v>
@@ -21423,7 +21423,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G726" t="n">
-        <v>0.330381572246552</v>
+        <v>0.330381602048874</v>
       </c>
       <c r="H726" t="n">
         <v>139535</v>
@@ -21452,7 +21452,7 @@
         <v>0.429500013589859</v>
       </c>
       <c r="G727" t="n">
-        <v>0.329997420310974</v>
+        <v>0.329997390508652</v>
       </c>
       <c r="H727" t="n">
         <v>72886</v>
@@ -21510,7 +21510,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G729" t="n">
-        <v>0.327308267354965</v>
+        <v>0.327308237552643</v>
       </c>
       <c r="H729" t="n">
         <v>208641</v>
@@ -21626,7 +21626,7 @@
         <v>0.424499988555908</v>
       </c>
       <c r="G733" t="n">
-        <v>0.326155751943588</v>
+        <v>0.326155722141266</v>
       </c>
       <c r="H733" t="n">
         <v>724651</v>
@@ -21655,7 +21655,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G734" t="n">
-        <v>0.324234962463379</v>
+        <v>0.324234932661057</v>
       </c>
       <c r="H734" t="n">
         <v>325336</v>
@@ -21684,7 +21684,7 @@
         <v>0.408499985933304</v>
       </c>
       <c r="G735" t="n">
-        <v>0.313862502574921</v>
+        <v>0.313862472772598</v>
       </c>
       <c r="H735" t="n">
         <v>344044</v>
@@ -21713,7 +21713,7 @@
         <v>0.402999997138977</v>
       </c>
       <c r="G736" t="n">
-        <v>0.309636652469635</v>
+        <v>0.309636682271957</v>
       </c>
       <c r="H736" t="n">
         <v>342140</v>
@@ -21771,7 +21771,7 @@
         <v>0.391999989748001</v>
       </c>
       <c r="G738" t="n">
-        <v>0.301185011863708</v>
+        <v>0.301185041666031</v>
       </c>
       <c r="H738" t="n">
         <v>403644</v>
@@ -21800,7 +21800,7 @@
         <v>0.395500004291534</v>
       </c>
       <c r="G739" t="n">
-        <v>0.30387419462204</v>
+        <v>0.303874224424362</v>
       </c>
       <c r="H739" t="n">
         <v>376873</v>
@@ -21887,7 +21887,7 @@
         <v>0.391000002622604</v>
       </c>
       <c r="G742" t="n">
-        <v>0.300416707992554</v>
+        <v>0.300416737794876</v>
       </c>
       <c r="H742" t="n">
         <v>391531</v>
@@ -21916,7 +21916,7 @@
         <v>0.400499999523163</v>
       </c>
       <c r="G743" t="n">
-        <v>0.307715833187103</v>
+        <v>0.307715862989426</v>
       </c>
       <c r="H743" t="n">
         <v>274193</v>
@@ -21974,7 +21974,7 @@
         <v>0.407499998807907</v>
       </c>
       <c r="G745" t="n">
-        <v>0.313094139099121</v>
+        <v>0.313094109296799</v>
       </c>
       <c r="H745" t="n">
         <v>514024</v>
@@ -22003,7 +22003,7 @@
         <v>0.407000005245209</v>
       </c>
       <c r="G746" t="n">
-        <v>0.312709987163544</v>
+        <v>0.312709957361221</v>
       </c>
       <c r="H746" t="n">
         <v>350463</v>
@@ -22032,7 +22032,7 @@
         <v>0.418999999761581</v>
       </c>
       <c r="G747" t="n">
-        <v>0.321929961442947</v>
+        <v>0.321929931640625</v>
       </c>
       <c r="H747" t="n">
         <v>286820</v>
@@ -22090,7 +22090,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G749" t="n">
-        <v>0.324234962463379</v>
+        <v>0.324234932661057</v>
       </c>
       <c r="H749" t="n">
         <v>251151</v>
@@ -22119,7 +22119,7 @@
         <v>0.407999992370605</v>
       </c>
       <c r="G750" t="n">
-        <v>0.313478291034698</v>
+        <v>0.313478320837021</v>
       </c>
       <c r="H750" t="n">
         <v>251833</v>
@@ -22177,7 +22177,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G752" t="n">
-        <v>0.307331651449203</v>
+        <v>0.307331681251526</v>
       </c>
       <c r="H752" t="n">
         <v>129595</v>
@@ -22206,7 +22206,7 @@
         <v>0.404000014066696</v>
       </c>
       <c r="G753" t="n">
-        <v>0.310405045747757</v>
+        <v>0.310405015945435</v>
       </c>
       <c r="H753" t="n">
         <v>314734</v>
@@ -22264,7 +22264,7 @@
         <v>0.409500002861023</v>
       </c>
       <c r="G755" t="n">
-        <v>0.314630806446075</v>
+        <v>0.314630836248398</v>
       </c>
       <c r="H755" t="n">
         <v>287096</v>
@@ -22322,7 +22322,7 @@
         <v>0.39750000834465</v>
       </c>
       <c r="G757" t="n">
-        <v>0.305410832166672</v>
+        <v>0.305410861968994</v>
       </c>
       <c r="H757" t="n">
         <v>115100</v>
@@ -22351,7 +22351,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G758" t="n">
-        <v>0.307331651449203</v>
+        <v>0.307331681251526</v>
       </c>
       <c r="H758" t="n">
         <v>113770</v>
@@ -22409,7 +22409,7 @@
         <v>0.40149998664856</v>
       </c>
       <c r="G760" t="n">
-        <v>0.30848416686058</v>
+        <v>0.308484226465225</v>
       </c>
       <c r="H760" t="n">
         <v>76300</v>
@@ -22467,7 +22467,7 @@
         <v>0.394499987363815</v>
       </c>
       <c r="G762" t="n">
-        <v>0.303105860948563</v>
+        <v>0.303105890750885</v>
       </c>
       <c r="H762" t="n">
         <v>146968</v>
@@ -22496,7 +22496,7 @@
         <v>0.402999997138977</v>
       </c>
       <c r="G763" t="n">
-        <v>0.309636652469635</v>
+        <v>0.309636682271957</v>
       </c>
       <c r="H763" t="n">
         <v>170392</v>
@@ -22583,7 +22583,7 @@
         <v>0.417499989271164</v>
       </c>
       <c r="G766" t="n">
-        <v>0.32077744603157</v>
+        <v>0.320777416229248</v>
       </c>
       <c r="H766" t="n">
         <v>424605</v>
@@ -22612,7 +22612,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G767" t="n">
-        <v>0.344211518764496</v>
+        <v>0.344211488962173</v>
       </c>
       <c r="H767" t="n">
         <v>469829</v>
@@ -22670,7 +22670,7 @@
         <v>0.467999994754791</v>
       </c>
       <c r="G769" t="n">
-        <v>0.359578043222427</v>
+        <v>0.35957807302475</v>
       </c>
       <c r="H769" t="n">
         <v>451135</v>
@@ -22902,7 +22902,7 @@
         <v>0.467000007629395</v>
       </c>
       <c r="G777" t="n">
-        <v>0.358809739351273</v>
+        <v>0.35880970954895</v>
       </c>
       <c r="H777" t="n">
         <v>104714</v>
@@ -22960,7 +22960,7 @@
         <v>0.456999987363815</v>
       </c>
       <c r="G779" t="n">
-        <v>0.351126462221146</v>
+        <v>0.351126432418823</v>
       </c>
       <c r="H779" t="n">
         <v>59241</v>
@@ -23047,7 +23047,7 @@
         <v>0.462999999523163</v>
       </c>
       <c r="G782" t="n">
-        <v>0.355736434459686</v>
+        <v>0.355736464262009</v>
       </c>
       <c r="H782" t="n">
         <v>103388</v>
@@ -23134,7 +23134,7 @@
         <v>0.445499986410141</v>
       </c>
       <c r="G785" t="n">
-        <v>0.342290639877319</v>
+        <v>0.342290669679642</v>
       </c>
       <c r="H785" t="n">
         <v>202125</v>
@@ -23250,7 +23250,7 @@
         <v>0.48199999332428</v>
       </c>
       <c r="G789" t="n">
-        <v>0.370334655046463</v>
+        <v>0.370334714651108</v>
       </c>
       <c r="H789" t="n">
         <v>89572</v>
@@ -23366,7 +23366,7 @@
         <v>0.487500011920929</v>
       </c>
       <c r="G793" t="n">
-        <v>0.374560534954071</v>
+        <v>0.374560475349426</v>
       </c>
       <c r="H793" t="n">
         <v>146653</v>
@@ -23453,7 +23453,7 @@
         <v>0.492000013589859</v>
       </c>
       <c r="G796" t="n">
-        <v>0.378017991781235</v>
+        <v>0.378017961978912</v>
       </c>
       <c r="H796" t="n">
         <v>46017</v>
@@ -23569,7 +23569,7 @@
         <v>0.490500003099442</v>
       </c>
       <c r="G800" t="n">
-        <v>0.376865476369858</v>
+        <v>0.37686550617218</v>
       </c>
       <c r="H800" t="n">
         <v>189609</v>
@@ -23685,7 +23685,7 @@
         <v>0.515999972820282</v>
       </c>
       <c r="G804" t="n">
-        <v>0.396457850933075</v>
+        <v>0.396457821130753</v>
       </c>
       <c r="H804" t="n">
         <v>741986</v>
@@ -23714,7 +23714,7 @@
         <v>0.518999993801117</v>
       </c>
       <c r="G805" t="n">
-        <v>0.398762881755829</v>
+        <v>0.398762851953506</v>
       </c>
       <c r="H805" t="n">
         <v>618175</v>
@@ -23743,7 +23743,7 @@
         <v>0.524999976158142</v>
       </c>
       <c r="G806" t="n">
-        <v>0.403372824192047</v>
+        <v>0.403372794389725</v>
       </c>
       <c r="H806" t="n">
         <v>300595</v>
@@ -23830,7 +23830,7 @@
         <v>0.532999992370605</v>
       </c>
       <c r="G809" t="n">
-        <v>0.409519463777542</v>
+        <v>0.409519493579865</v>
       </c>
       <c r="H809" t="n">
         <v>420481</v>
@@ -23859,7 +23859,7 @@
         <v>0.515999972820282</v>
       </c>
       <c r="G810" t="n">
-        <v>0.396457850933075</v>
+        <v>0.396457821130753</v>
       </c>
       <c r="H810" t="n">
         <v>351179</v>
@@ -23975,7 +23975,7 @@
         <v>0.493000000715256</v>
       </c>
       <c r="G814" t="n">
-        <v>0.378786325454712</v>
+        <v>0.37878629565239</v>
       </c>
       <c r="H814" t="n">
         <v>221656</v>
@@ -24004,7 +24004,7 @@
         <v>0.500999987125397</v>
       </c>
       <c r="G815" t="n">
-        <v>0.384932965040207</v>
+        <v>0.384932935237885</v>
       </c>
       <c r="H815" t="n">
         <v>212212</v>
@@ -24033,7 +24033,7 @@
         <v>0.497999995946884</v>
       </c>
       <c r="G816" t="n">
-        <v>0.382627964019775</v>
+        <v>0.382627934217453</v>
       </c>
       <c r="H816" t="n">
         <v>191104</v>
@@ -24062,7 +24062,7 @@
         <v>0.497999995946884</v>
       </c>
       <c r="G817" t="n">
-        <v>0.382627964019775</v>
+        <v>0.382627934217453</v>
       </c>
       <c r="H817" t="n">
         <v>241364</v>
@@ -24120,7 +24120,7 @@
         <v>0.515999972820282</v>
       </c>
       <c r="G819" t="n">
-        <v>0.396457850933075</v>
+        <v>0.396457821130753</v>
       </c>
       <c r="H819" t="n">
         <v>316328</v>
@@ -24149,7 +24149,7 @@
         <v>0.515999972820282</v>
       </c>
       <c r="G820" t="n">
-        <v>0.396457850933075</v>
+        <v>0.396457821130753</v>
       </c>
       <c r="H820" t="n">
         <v>328434</v>
@@ -24178,7 +24178,7 @@
         <v>0.513000011444092</v>
       </c>
       <c r="G821" t="n">
-        <v>0.394152879714966</v>
+        <v>0.394152909517288</v>
       </c>
       <c r="H821" t="n">
         <v>101675</v>
@@ -24236,7 +24236,7 @@
         <v>0.493000000715256</v>
       </c>
       <c r="G823" t="n">
-        <v>0.378786325454712</v>
+        <v>0.37878629565239</v>
       </c>
       <c r="H823" t="n">
         <v>520521</v>
@@ -24265,7 +24265,7 @@
         <v>0.488000005483627</v>
       </c>
       <c r="G824" t="n">
-        <v>0.374944657087326</v>
+        <v>0.374944686889648</v>
       </c>
       <c r="H824" t="n">
         <v>478335</v>
@@ -24294,7 +24294,7 @@
         <v>0.484499990940094</v>
       </c>
       <c r="G825" t="n">
-        <v>0.37225553393364</v>
+        <v>0.372255504131317</v>
       </c>
       <c r="H825" t="n">
         <v>113091</v>
@@ -24323,7 +24323,7 @@
         <v>0.469999998807907</v>
       </c>
       <c r="G826" t="n">
-        <v>0.361114710569382</v>
+        <v>0.361114770174026</v>
       </c>
       <c r="H826" t="n">
         <v>592542</v>
@@ -24352,7 +24352,7 @@
         <v>0.47749999165535</v>
       </c>
       <c r="G827" t="n">
-        <v>0.366877168416977</v>
+        <v>0.366877198219299</v>
       </c>
       <c r="H827" t="n">
         <v>265902</v>
@@ -24381,7 +24381,7 @@
         <v>0.488000005483627</v>
       </c>
       <c r="G828" t="n">
-        <v>0.374944657087326</v>
+        <v>0.374944686889648</v>
       </c>
       <c r="H828" t="n">
         <v>134194</v>
@@ -24468,7 +24468,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G831" t="n">
-        <v>0.407214492559433</v>
+        <v>0.407214462757111</v>
       </c>
       <c r="H831" t="n">
         <v>676529</v>
@@ -24497,7 +24497,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G832" t="n">
-        <v>0.407214492559433</v>
+        <v>0.407214462757111</v>
       </c>
       <c r="H832" t="n">
         <v>211428</v>
@@ -24555,7 +24555,7 @@
         <v>0.505999982357025</v>
       </c>
       <c r="G834" t="n">
-        <v>0.388774544000626</v>
+        <v>0.388774573802948</v>
       </c>
       <c r="H834" t="n">
         <v>316836</v>
@@ -24613,7 +24613,7 @@
         <v>0.504000008106232</v>
       </c>
       <c r="G836" t="n">
-        <v>0.387237906455994</v>
+        <v>0.387237936258316</v>
       </c>
       <c r="H836" t="n">
         <v>772178</v>
@@ -24642,7 +24642,7 @@
         <v>0.513999998569489</v>
       </c>
       <c r="G837" t="n">
-        <v>0.394921183586121</v>
+        <v>0.394921213388443</v>
       </c>
       <c r="H837" t="n">
         <v>276903</v>
@@ -24671,7 +24671,7 @@
         <v>0.53600001335144</v>
       </c>
       <c r="G838" t="n">
-        <v>0.411824494600296</v>
+        <v>0.411824464797974</v>
       </c>
       <c r="H838" t="n">
         <v>645486</v>
@@ -24700,7 +24700,7 @@
         <v>0.541000008583069</v>
       </c>
       <c r="G839" t="n">
-        <v>0.415666103363037</v>
+        <v>0.415666162967682</v>
       </c>
       <c r="H839" t="n">
         <v>1478731</v>
@@ -24729,7 +24729,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G840" t="n">
-        <v>0.41489776968956</v>
+        <v>0.414897799491882</v>
       </c>
       <c r="H840" t="n">
         <v>705581</v>
@@ -24758,7 +24758,7 @@
         <v>0.542999982833862</v>
       </c>
       <c r="G841" t="n">
-        <v>0.417202711105347</v>
+        <v>0.417202740907669</v>
       </c>
       <c r="H841" t="n">
         <v>231038</v>
@@ -24816,7 +24816,7 @@
         <v>0.522000014781952</v>
       </c>
       <c r="G843" t="n">
-        <v>0.401067852973938</v>
+        <v>0.40106788277626</v>
       </c>
       <c r="H843" t="n">
         <v>81161</v>
@@ -24874,7 +24874,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G845" t="n">
-        <v>0.411056131124496</v>
+        <v>0.411056160926819</v>
       </c>
       <c r="H845" t="n">
         <v>247309</v>
@@ -24961,7 +24961,7 @@
         <v>0.514999985694885</v>
       </c>
       <c r="G848" t="n">
-        <v>0.395689517259598</v>
+        <v>0.39568954706192</v>
       </c>
       <c r="H848" t="n">
         <v>162782</v>
@@ -24990,7 +24990,7 @@
         <v>0.527999997138977</v>
       </c>
       <c r="G849" t="n">
-        <v>0.405677855014801</v>
+        <v>0.405677825212479</v>
       </c>
       <c r="H849" t="n">
         <v>307539</v>
@@ -25048,7 +25048,7 @@
         <v>0.541000008583069</v>
       </c>
       <c r="G851" t="n">
-        <v>0.415666103363037</v>
+        <v>0.415666162967682</v>
       </c>
       <c r="H851" t="n">
         <v>1167475</v>
@@ -25164,7 +25164,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G855" t="n">
-        <v>0.407214492559433</v>
+        <v>0.407214462757111</v>
       </c>
       <c r="H855" t="n">
         <v>323631</v>
@@ -25222,7 +25222,7 @@
         <v>0.532999992370605</v>
       </c>
       <c r="G857" t="n">
-        <v>0.409519463777542</v>
+        <v>0.409519493579865</v>
       </c>
       <c r="H857" t="n">
         <v>98289</v>
@@ -25251,7 +25251,7 @@
         <v>0.513999998569489</v>
       </c>
       <c r="G858" t="n">
-        <v>0.394921183586121</v>
+        <v>0.394921213388443</v>
       </c>
       <c r="H858" t="n">
         <v>93578</v>
@@ -25280,7 +25280,7 @@
         <v>0.513999998569489</v>
       </c>
       <c r="G859" t="n">
-        <v>0.394921183586121</v>
+        <v>0.394921213388443</v>
       </c>
       <c r="H859" t="n">
         <v>168232</v>
@@ -25338,7 +25338,7 @@
         <v>0.533999979496002</v>
       </c>
       <c r="G861" t="n">
-        <v>0.410287797451019</v>
+        <v>0.410287827253342</v>
       </c>
       <c r="H861" t="n">
         <v>236901</v>
@@ -25367,7 +25367,7 @@
         <v>0.538999974727631</v>
       </c>
       <c r="G862" t="n">
-        <v>0.41412940621376</v>
+        <v>0.414129436016083</v>
       </c>
       <c r="H862" t="n">
         <v>251604</v>
@@ -25425,7 +25425,7 @@
         <v>0.532999992370605</v>
       </c>
       <c r="G864" t="n">
-        <v>0.409519463777542</v>
+        <v>0.409519493579865</v>
       </c>
       <c r="H864" t="n">
         <v>160247</v>
@@ -25454,7 +25454,7 @@
         <v>0.542999982833862</v>
       </c>
       <c r="G865" t="n">
-        <v>0.417202711105347</v>
+        <v>0.417202740907669</v>
       </c>
       <c r="H865" t="n">
         <v>58968</v>
@@ -25512,7 +25512,7 @@
         <v>0.53600001335144</v>
       </c>
       <c r="G867" t="n">
-        <v>0.411824494600296</v>
+        <v>0.411824464797974</v>
       </c>
       <c r="H867" t="n">
         <v>165468</v>
@@ -25541,7 +25541,7 @@
         <v>0.53600001335144</v>
       </c>
       <c r="G868" t="n">
-        <v>0.411824494600296</v>
+        <v>0.411824464797974</v>
       </c>
       <c r="H868" t="n">
         <v>110084</v>
@@ -25570,7 +25570,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G869" t="n">
-        <v>0.411056131124496</v>
+        <v>0.411056160926819</v>
       </c>
       <c r="H869" t="n">
         <v>26107</v>
@@ -25657,7 +25657,7 @@
         <v>0.527999997138977</v>
       </c>
       <c r="G872" t="n">
-        <v>0.405677855014801</v>
+        <v>0.405677825212479</v>
       </c>
       <c r="H872" t="n">
         <v>39874</v>
@@ -25686,7 +25686,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G873" t="n">
-        <v>0.411056131124496</v>
+        <v>0.411056160926819</v>
       </c>
       <c r="H873" t="n">
         <v>164662</v>
@@ -25715,7 +25715,7 @@
         <v>0.531000018119812</v>
       </c>
       <c r="G874" t="n">
-        <v>0.40798282623291</v>
+        <v>0.407982856035233</v>
       </c>
       <c r="H874" t="n">
         <v>64657</v>
@@ -25744,7 +25744,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G875" t="n">
-        <v>0.407214492559433</v>
+        <v>0.407214462757111</v>
       </c>
       <c r="H875" t="n">
         <v>138456</v>
@@ -25802,7 +25802,7 @@
         <v>0.518999993801117</v>
       </c>
       <c r="G877" t="n">
-        <v>0.398762881755829</v>
+        <v>0.398762851953506</v>
       </c>
       <c r="H877" t="n">
         <v>172153</v>
@@ -25831,7 +25831,7 @@
         <v>0.513999998569489</v>
       </c>
       <c r="G878" t="n">
-        <v>0.394921183586121</v>
+        <v>0.394921213388443</v>
       </c>
       <c r="H878" t="n">
         <v>103529</v>
@@ -25889,7 +25889,7 @@
         <v>0.522000014781952</v>
       </c>
       <c r="G880" t="n">
-        <v>0.401067852973938</v>
+        <v>0.40106788277626</v>
       </c>
       <c r="H880" t="n">
         <v>189616</v>
@@ -25918,7 +25918,7 @@
         <v>0.515999972820282</v>
       </c>
       <c r="G881" t="n">
-        <v>0.396457850933075</v>
+        <v>0.396457821130753</v>
       </c>
       <c r="H881" t="n">
         <v>147356</v>
@@ -26005,7 +26005,7 @@
         <v>0.522000014781952</v>
       </c>
       <c r="G884" t="n">
-        <v>0.401067852973938</v>
+        <v>0.40106788277626</v>
       </c>
       <c r="H884" t="n">
         <v>120680</v>
@@ -26063,7 +26063,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G886" t="n">
-        <v>0.407214492559433</v>
+        <v>0.407214462757111</v>
       </c>
       <c r="H886" t="n">
         <v>59228</v>
@@ -26092,7 +26092,7 @@
         <v>0.545000016689301</v>
       </c>
       <c r="G887" t="n">
-        <v>0.418739438056946</v>
+        <v>0.418739467859268</v>
       </c>
       <c r="H887" t="n">
         <v>418294</v>
@@ -26150,7 +26150,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G889" t="n">
-        <v>0.424117684364319</v>
+        <v>0.424117743968964</v>
       </c>
       <c r="H889" t="n">
         <v>244163</v>
@@ -26179,7 +26179,7 @@
         <v>0.549000024795532</v>
       </c>
       <c r="G890" t="n">
-        <v>0.421812772750854</v>
+        <v>0.421812742948532</v>
       </c>
       <c r="H890" t="n">
         <v>70318</v>
@@ -26208,7 +26208,7 @@
         <v>0.547999978065491</v>
       </c>
       <c r="G891" t="n">
-        <v>0.421044379472733</v>
+        <v>0.421044409275055</v>
       </c>
       <c r="H891" t="n">
         <v>321123</v>
@@ -26266,7 +26266,7 @@
         <v>0.545000016689301</v>
       </c>
       <c r="G893" t="n">
-        <v>0.418739438056946</v>
+        <v>0.418739467859268</v>
       </c>
       <c r="H893" t="n">
         <v>162159</v>
@@ -26295,7 +26295,7 @@
         <v>0.541000008583069</v>
       </c>
       <c r="G894" t="n">
-        <v>0.415666103363037</v>
+        <v>0.415666162967682</v>
       </c>
       <c r="H894" t="n">
         <v>157795</v>
@@ -26324,7 +26324,7 @@
         <v>0.541000008583069</v>
       </c>
       <c r="G895" t="n">
-        <v>0.415666103363037</v>
+        <v>0.415666162967682</v>
       </c>
       <c r="H895" t="n">
         <v>164299</v>
@@ -26353,7 +26353,7 @@
         <v>0.545000016689301</v>
       </c>
       <c r="G896" t="n">
-        <v>0.418739438056946</v>
+        <v>0.418739467859268</v>
       </c>
       <c r="H896" t="n">
         <v>179088</v>
@@ -26498,7 +26498,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G901" t="n">
-        <v>0.484047472476959</v>
+        <v>0.484047412872314</v>
       </c>
       <c r="H901" t="n">
         <v>717900</v>
@@ -26527,7 +26527,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G902" t="n">
-        <v>0.491730660200119</v>
+        <v>0.491730719804764</v>
       </c>
       <c r="H902" t="n">
         <v>558327</v>
@@ -26556,7 +26556,7 @@
         <v>0.642000019550323</v>
       </c>
       <c r="G903" t="n">
-        <v>0.493267387151718</v>
+        <v>0.493267416954041</v>
       </c>
       <c r="H903" t="n">
         <v>2542446</v>
@@ -26614,7 +26614,7 @@
         <v>0.658999979496002</v>
       </c>
       <c r="G905" t="n">
-        <v>0.506328940391541</v>
+        <v>0.506328999996185</v>
       </c>
       <c r="H905" t="n">
         <v>603590</v>
@@ -26643,7 +26643,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G906" t="n">
-        <v>0.488657355308533</v>
+        <v>0.488657414913177</v>
       </c>
       <c r="H906" t="n">
         <v>925561</v>
@@ -26730,7 +26730,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G909" t="n">
-        <v>0.48251074552536</v>
+        <v>0.482510805130005</v>
       </c>
       <c r="H909" t="n">
         <v>856870</v>
@@ -26759,7 +26759,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G910" t="n">
-        <v>0.470217525959015</v>
+        <v>0.47021746635437</v>
       </c>
       <c r="H910" t="n">
         <v>646474</v>
@@ -26788,7 +26788,7 @@
         <v>0.619000017642975</v>
       </c>
       <c r="G911" t="n">
-        <v>0.475595831871033</v>
+        <v>0.47559580206871</v>
       </c>
       <c r="H911" t="n">
         <v>213127</v>
@@ -26817,7 +26817,7 @@
         <v>0.630999982357025</v>
       </c>
       <c r="G912" t="n">
-        <v>0.484815776348114</v>
+        <v>0.484815716743469</v>
       </c>
       <c r="H912" t="n">
         <v>503278</v>
@@ -26846,7 +26846,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G913" t="n">
-        <v>0.468680858612061</v>
+        <v>0.468680799007416</v>
       </c>
       <c r="H913" t="n">
         <v>332283</v>
@@ -26875,7 +26875,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G914" t="n">
-        <v>0.464070826768875</v>
+        <v>0.464070796966553</v>
       </c>
       <c r="H914" t="n">
         <v>306237</v>
@@ -26904,7 +26904,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G915" t="n">
-        <v>0.465607523918152</v>
+        <v>0.465607494115829</v>
       </c>
       <c r="H915" t="n">
         <v>168953</v>
@@ -26991,7 +26991,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G918" t="n">
-        <v>0.453314185142517</v>
+        <v>0.453314214944839</v>
       </c>
       <c r="H918" t="n">
         <v>659680</v>
@@ -27020,7 +27020,7 @@
         <v>0.564999997615814</v>
       </c>
       <c r="G919" t="n">
-        <v>0.434106022119522</v>
+        <v>0.434105962514877</v>
       </c>
       <c r="H919" t="n">
         <v>496547</v>
@@ -27049,7 +27049,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G920" t="n">
-        <v>0.441789269447327</v>
+        <v>0.441789239645004</v>
       </c>
       <c r="H920" t="n">
         <v>195067</v>
@@ -27078,7 +27078,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G921" t="n">
-        <v>0.424117684364319</v>
+        <v>0.424117743968964</v>
       </c>
       <c r="H921" t="n">
         <v>245875</v>
@@ -27165,7 +27165,7 @@
         <v>0.587000012397766</v>
       </c>
       <c r="G924" t="n">
-        <v>0.451009273529053</v>
+        <v>0.45100924372673</v>
       </c>
       <c r="H924" t="n">
         <v>192594</v>
@@ -27223,7 +27223,7 @@
         <v>0.598999977111816</v>
       </c>
       <c r="G926" t="n">
-        <v>0.460229188203812</v>
+        <v>0.460229218006134</v>
       </c>
       <c r="H926" t="n">
         <v>582668</v>
@@ -27252,7 +27252,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G927" t="n">
-        <v>0.453314185142517</v>
+        <v>0.453314214944839</v>
       </c>
       <c r="H927" t="n">
         <v>489655</v>
@@ -27281,7 +27281,7 @@
         <v>0.591000020503998</v>
       </c>
       <c r="G928" t="n">
-        <v>0.454082638025284</v>
+        <v>0.454082578420639</v>
       </c>
       <c r="H928" t="n">
         <v>45061</v>
@@ -27310,7 +27310,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G929" t="n">
-        <v>0.457155913114548</v>
+        <v>0.457155883312225</v>
       </c>
       <c r="H929" t="n">
         <v>166347</v>
@@ -27339,7 +27339,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G930" t="n">
-        <v>0.465607523918152</v>
+        <v>0.465607494115829</v>
       </c>
       <c r="H930" t="n">
         <v>252474</v>
@@ -27368,7 +27368,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G931" t="n">
-        <v>0.48251074552536</v>
+        <v>0.482510805130005</v>
       </c>
       <c r="H931" t="n">
         <v>568276</v>
@@ -27397,7 +27397,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G932" t="n">
-        <v>0.484047472476959</v>
+        <v>0.484047412872314</v>
       </c>
       <c r="H932" t="n">
         <v>584324</v>
@@ -27426,7 +27426,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G933" t="n">
-        <v>0.476364105939865</v>
+        <v>0.476364135742188</v>
       </c>
       <c r="H933" t="n">
         <v>1101661</v>
@@ -27455,7 +27455,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G934" t="n">
-        <v>0.476364105939865</v>
+        <v>0.476364135742188</v>
       </c>
       <c r="H934" t="n">
         <v>274594</v>
@@ -27484,7 +27484,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G935" t="n">
-        <v>0.484047472476959</v>
+        <v>0.484047412872314</v>
       </c>
       <c r="H935" t="n">
         <v>253532</v>
@@ -27542,7 +27542,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G937" t="n">
-        <v>0.451777577400208</v>
+        <v>0.45177760720253</v>
       </c>
       <c r="H937" t="n">
         <v>788501</v>
@@ -27571,7 +27571,7 @@
         <v>0.598999977111816</v>
       </c>
       <c r="G938" t="n">
-        <v>0.460229188203812</v>
+        <v>0.460229218006134</v>
       </c>
       <c r="H938" t="n">
         <v>195174</v>
@@ -27629,7 +27629,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G940" t="n">
-        <v>0.456387519836426</v>
+        <v>0.456387490034103</v>
       </c>
       <c r="H940" t="n">
         <v>191014</v>
@@ -27687,7 +27687,7 @@
         <v>0.601000010967255</v>
       </c>
       <c r="G942" t="n">
-        <v>0.461765915155411</v>
+        <v>0.461765885353088</v>
       </c>
       <c r="H942" t="n">
         <v>238130</v>
@@ -27716,7 +27716,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G943" t="n">
-        <v>0.464070826768875</v>
+        <v>0.464070796966553</v>
       </c>
       <c r="H943" t="n">
         <v>214516</v>
@@ -27745,7 +27745,7 @@
         <v>0.598999977111816</v>
       </c>
       <c r="G944" t="n">
-        <v>0.460229188203812</v>
+        <v>0.460229218006134</v>
       </c>
       <c r="H944" t="n">
         <v>412234</v>
@@ -27774,7 +27774,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G945" t="n">
-        <v>0.459460854530334</v>
+        <v>0.459460914134979</v>
       </c>
       <c r="H945" t="n">
         <v>221744</v>
@@ -27832,7 +27832,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G947" t="n">
-        <v>0.470217525959015</v>
+        <v>0.47021746635437</v>
       </c>
       <c r="H947" t="n">
         <v>616889</v>
@@ -27861,7 +27861,7 @@
         <v>0.612999975681305</v>
       </c>
       <c r="G948" t="n">
-        <v>0.47098582983017</v>
+        <v>0.470985740423203</v>
       </c>
       <c r="H948" t="n">
         <v>199113</v>
@@ -27948,7 +27948,7 @@
         <v>0.605000019073486</v>
       </c>
       <c r="G951" t="n">
-        <v>0.464839190244675</v>
+        <v>0.464839220046997</v>
       </c>
       <c r="H951" t="n">
         <v>242874</v>
@@ -27977,7 +27977,7 @@
         <v>0.605000019073486</v>
       </c>
       <c r="G952" t="n">
-        <v>0.464839190244675</v>
+        <v>0.464839220046997</v>
       </c>
       <c r="H952" t="n">
         <v>453599</v>
@@ -28006,7 +28006,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G953" t="n">
-        <v>0.459460854530334</v>
+        <v>0.459460914134979</v>
       </c>
       <c r="H953" t="n">
         <v>153130</v>
@@ -28064,7 +28064,7 @@
         <v>0.563000023365021</v>
       </c>
       <c r="G955" t="n">
-        <v>0.43256938457489</v>
+        <v>0.432569354772568</v>
       </c>
       <c r="H955" t="n">
         <v>490548</v>
@@ -28151,7 +28151,7 @@
         <v>0.564999997615814</v>
       </c>
       <c r="G958" t="n">
-        <v>0.434106022119522</v>
+        <v>0.434105962514877</v>
       </c>
       <c r="H958" t="n">
         <v>166738</v>
@@ -28180,7 +28180,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G959" t="n">
-        <v>0.433337718248367</v>
+        <v>0.433337658643723</v>
       </c>
       <c r="H959" t="n">
         <v>81128</v>
@@ -28209,7 +28209,7 @@
         <v>0.565999984741211</v>
       </c>
       <c r="G960" t="n">
-        <v>0.434874296188354</v>
+        <v>0.434874355792999</v>
       </c>
       <c r="H960" t="n">
         <v>58777</v>
@@ -28238,7 +28238,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G961" t="n">
-        <v>0.433337718248367</v>
+        <v>0.433337658643723</v>
       </c>
       <c r="H961" t="n">
         <v>305827</v>
@@ -28267,7 +28267,7 @@
         <v>0.550999999046326</v>
       </c>
       <c r="G962" t="n">
-        <v>0.423349410295486</v>
+        <v>0.423349380493164</v>
       </c>
       <c r="H962" t="n">
         <v>2075965</v>
@@ -28354,7 +28354,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G965" t="n">
-        <v>0.441789269447327</v>
+        <v>0.441789239645004</v>
       </c>
       <c r="H965" t="n">
         <v>273431</v>
@@ -28412,7 +28412,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G967" t="n">
-        <v>0.433337718248367</v>
+        <v>0.433337658643723</v>
       </c>
       <c r="H967" t="n">
         <v>168580</v>
@@ -28470,7 +28470,7 @@
         <v>0.572000026702881</v>
       </c>
       <c r="G969" t="n">
-        <v>0.439484357833862</v>
+        <v>0.43948432803154</v>
       </c>
       <c r="H969" t="n">
         <v>72543</v>
@@ -28557,7 +28557,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G972" t="n">
-        <v>0.441020995378494</v>
+        <v>0.441020965576172</v>
       </c>
       <c r="H972" t="n">
         <v>121483</v>
@@ -28586,7 +28586,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G973" t="n">
-        <v>0.441020995378494</v>
+        <v>0.441020965576172</v>
       </c>
       <c r="H973" t="n">
         <v>233644</v>
@@ -28615,7 +28615,7 @@
         <v>0.573000013828278</v>
       </c>
       <c r="G974" t="n">
-        <v>0.440252691507339</v>
+        <v>0.440252602100372</v>
       </c>
       <c r="H974" t="n">
         <v>269717</v>
@@ -28673,7 +28673,7 @@
         <v>0.565999984741211</v>
       </c>
       <c r="G976" t="n">
-        <v>0.434874296188354</v>
+        <v>0.434874355792999</v>
       </c>
       <c r="H976" t="n">
         <v>402322</v>
@@ -28702,7 +28702,7 @@
         <v>0.570999979972839</v>
       </c>
       <c r="G977" t="n">
-        <v>0.438715934753418</v>
+        <v>0.43871596455574</v>
       </c>
       <c r="H977" t="n">
         <v>104514</v>
@@ -28731,7 +28731,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G978" t="n">
-        <v>0.442557573318481</v>
+        <v>0.442557632923126</v>
       </c>
       <c r="H978" t="n">
         <v>901348</v>
@@ -28760,7 +28760,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G979" t="n">
-        <v>0.464070826768875</v>
+        <v>0.464070796966553</v>
       </c>
       <c r="H979" t="n">
         <v>782627</v>
@@ -28789,7 +28789,7 @@
         <v>0.601000010967255</v>
       </c>
       <c r="G980" t="n">
-        <v>0.461765915155411</v>
+        <v>0.461765885353088</v>
       </c>
       <c r="H980" t="n">
         <v>509029</v>
@@ -28847,7 +28847,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G982" t="n">
-        <v>0.468680858612061</v>
+        <v>0.468680799007416</v>
       </c>
       <c r="H982" t="n">
         <v>823646</v>
@@ -28876,7 +28876,7 @@
         <v>0.612999975681305</v>
       </c>
       <c r="G983" t="n">
-        <v>0.47098582983017</v>
+        <v>0.470985740423203</v>
       </c>
       <c r="H983" t="n">
         <v>246464</v>
@@ -28934,7 +28934,7 @@
         <v>0.634999990463257</v>
       </c>
       <c r="G985" t="n">
-        <v>0.487888962030411</v>
+        <v>0.487889021635056</v>
       </c>
       <c r="H985" t="n">
         <v>1452096</v>
@@ -28992,7 +28992,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G987" t="n">
-        <v>0.484047472476959</v>
+        <v>0.484047412872314</v>
       </c>
       <c r="H987" t="n">
         <v>572656</v>
@@ -29021,7 +29021,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G988" t="n">
-        <v>0.468680858612061</v>
+        <v>0.468680799007416</v>
       </c>
       <c r="H988" t="n">
         <v>537612</v>
@@ -29050,7 +29050,7 @@
         <v>0.592999994754791</v>
       </c>
       <c r="G989" t="n">
-        <v>0.455619156360626</v>
+        <v>0.455619186162949</v>
       </c>
       <c r="H989" t="n">
         <v>804878</v>
@@ -29079,7 +29079,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G990" t="n">
-        <v>0.457155913114548</v>
+        <v>0.457155883312225</v>
       </c>
       <c r="H990" t="n">
         <v>384886</v>
@@ -29108,7 +29108,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G991" t="n">
-        <v>0.456387519836426</v>
+        <v>0.456387490034103</v>
       </c>
       <c r="H991" t="n">
         <v>221776</v>
@@ -29137,7 +29137,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G992" t="n">
-        <v>0.459460854530334</v>
+        <v>0.459460914134979</v>
       </c>
       <c r="H992" t="n">
         <v>218092</v>
@@ -29166,7 +29166,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G993" t="n">
-        <v>0.456387519836426</v>
+        <v>0.456387490034103</v>
       </c>
       <c r="H993" t="n">
         <v>358194</v>
@@ -29195,7 +29195,7 @@
         <v>0.591000020503998</v>
       </c>
       <c r="G994" t="n">
-        <v>0.454082638025284</v>
+        <v>0.454082578420639</v>
       </c>
       <c r="H994" t="n">
         <v>690412</v>
@@ -29224,7 +29224,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G995" t="n">
-        <v>0.457155913114548</v>
+        <v>0.457155883312225</v>
       </c>
       <c r="H995" t="n">
         <v>694741</v>
@@ -29253,7 +29253,7 @@
         <v>0.577000021934509</v>
       </c>
       <c r="G996" t="n">
-        <v>0.443325966596603</v>
+        <v>0.443325996398926</v>
       </c>
       <c r="H996" t="n">
         <v>1023978</v>
@@ -29340,7 +29340,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G999" t="n">
-        <v>0.433337718248367</v>
+        <v>0.433337658643723</v>
       </c>
       <c r="H999" t="n">
         <v>424221</v>
@@ -29456,7 +29456,7 @@
         <v>0.546000003814697</v>
       </c>
       <c r="G1003" t="n">
-        <v>0.419507771730423</v>
+        <v>0.419507741928101</v>
       </c>
       <c r="H1003" t="n">
         <v>866896</v>
@@ -29485,7 +29485,7 @@
         <v>0.572000026702881</v>
       </c>
       <c r="G1004" t="n">
-        <v>0.439484357833862</v>
+        <v>0.43948432803154</v>
       </c>
       <c r="H1004" t="n">
         <v>824914</v>
@@ -29572,7 +29572,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G1007" t="n">
-        <v>0.433337718248367</v>
+        <v>0.433337658643723</v>
       </c>
       <c r="H1007" t="n">
         <v>390432</v>
@@ -29601,7 +29601,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1008" t="n">
-        <v>0.450240910053253</v>
+        <v>0.450240969657898</v>
       </c>
       <c r="H1008" t="n">
         <v>916326</v>
@@ -29630,7 +29630,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G1009" t="n">
-        <v>0.451777577400208</v>
+        <v>0.45177760720253</v>
       </c>
       <c r="H1009" t="n">
         <v>372288</v>
@@ -29688,7 +29688,7 @@
         <v>0.570999979972839</v>
       </c>
       <c r="G1011" t="n">
-        <v>0.438715934753418</v>
+        <v>0.43871596455574</v>
       </c>
       <c r="H1011" t="n">
         <v>449055</v>
@@ -29833,7 +29833,7 @@
         <v>0.578000009059906</v>
       </c>
       <c r="G1016" t="n">
-        <v>0.444094300270081</v>
+        <v>0.444094270467758</v>
       </c>
       <c r="H1016" t="n">
         <v>387181</v>
@@ -29920,7 +29920,7 @@
         <v>0.564999997615814</v>
       </c>
       <c r="G1019" t="n">
-        <v>0.434106022119522</v>
+        <v>0.434105962514877</v>
       </c>
       <c r="H1019" t="n">
         <v>216207</v>
@@ -29978,7 +29978,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G1021" t="n">
-        <v>0.456387519836426</v>
+        <v>0.456387490034103</v>
       </c>
       <c r="H1021" t="n">
         <v>2260717</v>
@@ -30007,7 +30007,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G1022" t="n">
-        <v>0.464070826768875</v>
+        <v>0.464070796966553</v>
       </c>
       <c r="H1022" t="n">
         <v>2352028</v>
@@ -30065,7 +30065,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1024" t="n">
-        <v>0.457155913114548</v>
+        <v>0.457155883312225</v>
       </c>
       <c r="H1024" t="n">
         <v>914867</v>
@@ -30123,7 +30123,7 @@
         <v>0.577000021934509</v>
       </c>
       <c r="G1026" t="n">
-        <v>0.443325966596603</v>
+        <v>0.443325996398926</v>
       </c>
       <c r="H1026" t="n">
         <v>762183</v>
@@ -30152,7 +30152,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G1027" t="n">
-        <v>0.441020995378494</v>
+        <v>0.441020965576172</v>
       </c>
       <c r="H1027" t="n">
         <v>509745</v>
@@ -30210,7 +30210,7 @@
         <v>0.578999996185303</v>
       </c>
       <c r="G1029" t="n">
-        <v>0.444862574338913</v>
+        <v>0.444862604141235</v>
       </c>
       <c r="H1029" t="n">
         <v>262358</v>
@@ -30326,7 +30326,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1033" t="n">
-        <v>0.41489776968956</v>
+        <v>0.414897799491882</v>
       </c>
       <c r="H1033" t="n">
         <v>581361</v>
@@ -30384,7 +30384,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1035" t="n">
-        <v>0.407214492559433</v>
+        <v>0.407214462757111</v>
       </c>
       <c r="H1035" t="n">
         <v>855969</v>
@@ -30413,7 +30413,7 @@
         <v>0.513000011444092</v>
       </c>
       <c r="G1036" t="n">
-        <v>0.394152879714966</v>
+        <v>0.394152909517288</v>
       </c>
       <c r="H1036" t="n">
         <v>572348</v>
@@ -30442,7 +30442,7 @@
         <v>0.488499999046326</v>
       </c>
       <c r="G1037" t="n">
-        <v>0.375328809022903</v>
+        <v>0.375328779220581</v>
       </c>
       <c r="H1037" t="n">
         <v>885075</v>
@@ -30471,7 +30471,7 @@
         <v>0.503000020980835</v>
       </c>
       <c r="G1038" t="n">
-        <v>0.386469602584839</v>
+        <v>0.386469572782516</v>
       </c>
       <c r="H1038" t="n">
         <v>360514</v>
@@ -30500,7 +30500,7 @@
         <v>0.513999998569489</v>
       </c>
       <c r="G1039" t="n">
-        <v>0.394921183586121</v>
+        <v>0.394921213388443</v>
       </c>
       <c r="H1039" t="n">
         <v>567039</v>
@@ -30529,7 +30529,7 @@
         <v>0.524999976158142</v>
       </c>
       <c r="G1040" t="n">
-        <v>0.403372824192047</v>
+        <v>0.403372794389725</v>
       </c>
       <c r="H1040" t="n">
         <v>295868</v>
@@ -30558,7 +30558,7 @@
         <v>0.538999974727631</v>
       </c>
       <c r="G1041" t="n">
-        <v>0.41412940621376</v>
+        <v>0.414129436016083</v>
       </c>
       <c r="H1041" t="n">
         <v>586951</v>
@@ -30703,7 +30703,7 @@
         <v>0.526000022888184</v>
       </c>
       <c r="G1046" t="n">
-        <v>0.404141157865524</v>
+        <v>0.404141187667847</v>
       </c>
       <c r="H1046" t="n">
         <v>458429</v>
@@ -30790,7 +30790,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1049" t="n">
-        <v>0.407214492559433</v>
+        <v>0.407214462757111</v>
       </c>
       <c r="H1049" t="n">
         <v>207928</v>
@@ -30877,7 +30877,7 @@
         <v>0.513000011444092</v>
       </c>
       <c r="G1052" t="n">
-        <v>0.394152879714966</v>
+        <v>0.394152909517288</v>
       </c>
       <c r="H1052" t="n">
         <v>365776</v>
@@ -30906,7 +30906,7 @@
         <v>0.476000010967255</v>
       </c>
       <c r="G1053" t="n">
-        <v>0.365724712610245</v>
+        <v>0.365724742412567</v>
       </c>
       <c r="H1053" t="n">
         <v>1283464</v>
@@ -30964,7 +30964,7 @@
         <v>0.505999982357025</v>
       </c>
       <c r="G1055" t="n">
-        <v>0.388774544000626</v>
+        <v>0.388774573802948</v>
       </c>
       <c r="H1055" t="n">
         <v>723519</v>
@@ -31051,7 +31051,7 @@
         <v>0.457500010728836</v>
       </c>
       <c r="G1058" t="n">
-        <v>0.351510643959045</v>
+        <v>0.351510614156723</v>
       </c>
       <c r="H1058" t="n">
         <v>775525</v>
@@ -31138,7 +31138,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G1061" t="n">
-        <v>0.317319989204407</v>
+        <v>0.317319959402084</v>
       </c>
       <c r="H1061" t="n">
         <v>558185</v>
@@ -31167,7 +31167,7 @@
         <v>0.391999989748001</v>
       </c>
       <c r="G1062" t="n">
-        <v>0.301185011863708</v>
+        <v>0.301185041666031</v>
       </c>
       <c r="H1062" t="n">
         <v>1337923</v>
@@ -31225,7 +31225,7 @@
         <v>0.337999999523163</v>
       </c>
       <c r="G1064" t="n">
-        <v>0.259695291519165</v>
+        <v>0.259695261716843</v>
       </c>
       <c r="H1064" t="n">
         <v>940784</v>
@@ -31254,7 +31254,7 @@
         <v>0.349000006914139</v>
       </c>
       <c r="G1065" t="n">
-        <v>0.268146902322769</v>
+        <v>0.268146872520447</v>
       </c>
       <c r="H1065" t="n">
         <v>535104</v>
@@ -31283,7 +31283,7 @@
         <v>0.311500012874603</v>
       </c>
       <c r="G1066" t="n">
-        <v>0.239334583282471</v>
+        <v>0.239334553480148</v>
       </c>
       <c r="H1066" t="n">
         <v>812346</v>
@@ -31312,7 +31312,7 @@
         <v>0.314999997615814</v>
       </c>
       <c r="G1067" t="n">
-        <v>0.24202373623848</v>
+        <v>0.242023706436157</v>
       </c>
       <c r="H1067" t="n">
         <v>701200</v>
@@ -31370,7 +31370,7 @@
         <v>0.319999992847443</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.24586533010006</v>
+        <v>0.245865359902382</v>
       </c>
       <c r="H1069" t="n">
         <v>339854</v>
@@ -31399,7 +31399,7 @@
         <v>0.337000012397766</v>
       </c>
       <c r="G1070" t="n">
-        <v>0.258926928043365</v>
+        <v>0.258926957845688</v>
       </c>
       <c r="H1070" t="n">
         <v>190840</v>
@@ -31457,7 +31457,7 @@
         <v>0.347000002861023</v>
       </c>
       <c r="G1072" t="n">
-        <v>0.266610264778137</v>
+        <v>0.266610234975815</v>
       </c>
       <c r="H1072" t="n">
         <v>337708</v>
@@ -31515,7 +31515,7 @@
         <v>0.36599999666214</v>
       </c>
       <c r="G1074" t="n">
-        <v>0.281208485364914</v>
+        <v>0.281208515167236</v>
       </c>
       <c r="H1074" t="n">
         <v>310583</v>
@@ -31573,7 +31573,7 @@
         <v>0.350499987602234</v>
       </c>
       <c r="G1076" t="n">
-        <v>0.269299387931824</v>
+        <v>0.269299358129501</v>
       </c>
       <c r="H1076" t="n">
         <v>210314</v>
@@ -31602,7 +31602,7 @@
         <v>0.335999995470047</v>
       </c>
       <c r="G1077" t="n">
-        <v>0.258158624172211</v>
+        <v>0.258158594369888</v>
       </c>
       <c r="H1077" t="n">
         <v>240206</v>
@@ -31631,7 +31631,7 @@
         <v>0.326999992132187</v>
       </c>
       <c r="G1078" t="n">
-        <v>0.251243650913239</v>
+        <v>0.251243621110916</v>
       </c>
       <c r="H1078" t="n">
         <v>106549</v>
@@ -31689,7 +31689,7 @@
         <v>0.315499991178513</v>
       </c>
       <c r="G1080" t="n">
-        <v>0.242407888174057</v>
+        <v>0.242407858371735</v>
       </c>
       <c r="H1080" t="n">
         <v>359313</v>
@@ -31747,7 +31747,7 @@
         <v>0.319000005722046</v>
       </c>
       <c r="G1082" t="n">
-        <v>0.245096981525421</v>
+        <v>0.245097011327744</v>
       </c>
       <c r="H1082" t="n">
         <v>159502</v>
@@ -31805,7 +31805,7 @@
         <v>0.331499993801117</v>
       </c>
       <c r="G1084" t="n">
-        <v>0.254701137542725</v>
+        <v>0.254701107740402</v>
       </c>
       <c r="H1084" t="n">
         <v>474980</v>
@@ -31834,7 +31834,7 @@
         <v>0.337999999523163</v>
       </c>
       <c r="G1085" t="n">
-        <v>0.259695291519165</v>
+        <v>0.259695261716843</v>
       </c>
       <c r="H1085" t="n">
         <v>305828</v>
@@ -31863,7 +31863,7 @@
         <v>0.340999990701675</v>
       </c>
       <c r="G1086" t="n">
-        <v>0.262000292539597</v>
+        <v>0.262000232934952</v>
       </c>
       <c r="H1086" t="n">
         <v>246813</v>
@@ -31892,7 +31892,7 @@
         <v>0.337999999523163</v>
       </c>
       <c r="G1087" t="n">
-        <v>0.259695291519165</v>
+        <v>0.259695261716843</v>
       </c>
       <c r="H1087" t="n">
         <v>240516</v>
@@ -31950,7 +31950,7 @@
         <v>0.340000003576279</v>
       </c>
       <c r="G1089" t="n">
-        <v>0.261231929063797</v>
+        <v>0.261231958866119</v>
       </c>
       <c r="H1089" t="n">
         <v>174984</v>
@@ -31979,7 +31979,7 @@
         <v>0.34799998998642</v>
       </c>
       <c r="G1090" t="n">
-        <v>0.267378598451614</v>
+        <v>0.26737853884697</v>
       </c>
       <c r="H1090" t="n">
         <v>85920</v>
@@ -32008,7 +32008,7 @@
         <v>0.342000007629395</v>
       </c>
       <c r="G1091" t="n">
-        <v>0.262768626213074</v>
+        <v>0.262768566608429</v>
       </c>
       <c r="H1091" t="n">
         <v>172632</v>
@@ -32037,7 +32037,7 @@
         <v>0.344500005245209</v>
       </c>
       <c r="G1092" t="n">
-        <v>0.264689415693283</v>
+        <v>0.264689445495605</v>
       </c>
       <c r="H1092" t="n">
         <v>504667</v>
@@ -32066,7 +32066,7 @@
         <v>0.342000007629395</v>
       </c>
       <c r="G1093" t="n">
-        <v>0.262768626213074</v>
+        <v>0.262768566608429</v>
       </c>
       <c r="H1093" t="n">
         <v>175638</v>
@@ -32095,7 +32095,7 @@
         <v>0.342000007629395</v>
       </c>
       <c r="G1094" t="n">
-        <v>0.262768626213074</v>
+        <v>0.262768566608429</v>
       </c>
       <c r="H1094" t="n">
         <v>275866</v>
@@ -32182,7 +32182,7 @@
         <v>0.356499999761581</v>
       </c>
       <c r="G1097" t="n">
-        <v>0.273909360170364</v>
+        <v>0.273909330368042</v>
       </c>
       <c r="H1097" t="n">
         <v>281693</v>
@@ -32269,7 +32269,7 @@
         <v>0.361999988555908</v>
       </c>
       <c r="G1100" t="n">
-        <v>0.278135150671005</v>
+        <v>0.278135180473328</v>
       </c>
       <c r="H1100" t="n">
         <v>149347</v>
@@ -32327,7 +32327,7 @@
         <v>0.350499987602234</v>
       </c>
       <c r="G1102" t="n">
-        <v>0.269299387931824</v>
+        <v>0.269299358129501</v>
       </c>
       <c r="H1102" t="n">
         <v>97822</v>
@@ -32356,7 +32356,7 @@
         <v>0.342000007629395</v>
       </c>
       <c r="G1103" t="n">
-        <v>0.262768626213074</v>
+        <v>0.262768566608429</v>
       </c>
       <c r="H1103" t="n">
         <v>200794</v>
@@ -32385,7 +32385,7 @@
         <v>0.358500003814697</v>
       </c>
       <c r="G1104" t="n">
-        <v>0.275446027517319</v>
+        <v>0.275445997714996</v>
       </c>
       <c r="H1104" t="n">
         <v>497581</v>
@@ -32414,7 +32414,7 @@
         <v>0.349000006914139</v>
       </c>
       <c r="G1105" t="n">
-        <v>0.268146902322769</v>
+        <v>0.268146872520447</v>
       </c>
       <c r="H1105" t="n">
         <v>188234</v>
@@ -32501,7 +32501,7 @@
         <v>0.335999995470047</v>
       </c>
       <c r="G1108" t="n">
-        <v>0.258158624172211</v>
+        <v>0.258158594369888</v>
       </c>
       <c r="H1108" t="n">
         <v>213156</v>
@@ -32559,7 +32559,7 @@
         <v>0.345499992370605</v>
       </c>
       <c r="G1110" t="n">
-        <v>0.26545774936676</v>
+        <v>0.265457719564438</v>
       </c>
       <c r="H1110" t="n">
         <v>84381</v>
@@ -32617,7 +32617,7 @@
         <v>0.337000012397766</v>
       </c>
       <c r="G1112" t="n">
-        <v>0.258926928043365</v>
+        <v>0.258926957845688</v>
       </c>
       <c r="H1112" t="n">
         <v>73765</v>
@@ -32820,7 +32820,7 @@
         <v>0.345499992370605</v>
       </c>
       <c r="G1119" t="n">
-        <v>0.26545774936676</v>
+        <v>0.265457719564438</v>
       </c>
       <c r="H1119" t="n">
         <v>175716</v>
@@ -32994,7 +32994,7 @@
         <v>0.426499992609024</v>
       </c>
       <c r="G1125" t="n">
-        <v>0.327692449092865</v>
+        <v>0.327692419290543</v>
       </c>
       <c r="H1125" t="n">
         <v>728674</v>
@@ -33052,7 +33052,7 @@
         <v>0.400499999523163</v>
       </c>
       <c r="G1127" t="n">
-        <v>0.307715833187103</v>
+        <v>0.307715862989426</v>
       </c>
       <c r="H1127" t="n">
         <v>190387</v>
@@ -33110,7 +33110,7 @@
         <v>0.393500000238419</v>
       </c>
       <c r="G1129" t="n">
-        <v>0.302337527275085</v>
+        <v>0.30233758687973</v>
       </c>
       <c r="H1129" t="n">
         <v>423424</v>
@@ -33168,7 +33168,7 @@
         <v>0.421499997377396</v>
       </c>
       <c r="G1131" t="n">
-        <v>0.323850780725479</v>
+        <v>0.323850750923157</v>
       </c>
       <c r="H1131" t="n">
         <v>1692345</v>
@@ -33197,7 +33197,7 @@
         <v>0.45550000667572</v>
       </c>
       <c r="G1132" t="n">
-        <v>0.349974006414413</v>
+        <v>0.349973976612091</v>
       </c>
       <c r="H1132" t="n">
         <v>3674034</v>
@@ -33226,7 +33226,7 @@
         <v>0.455000013113022</v>
       </c>
       <c r="G1133" t="n">
-        <v>0.349589794874191</v>
+        <v>0.349589824676514</v>
       </c>
       <c r="H1133" t="n">
         <v>6074198</v>
@@ -33284,7 +33284,7 @@
         <v>0.43299999833107</v>
       </c>
       <c r="G1135" t="n">
-        <v>0.332686543464661</v>
+        <v>0.332686573266983</v>
       </c>
       <c r="H1135" t="n">
         <v>497355</v>
@@ -33342,7 +33342,7 @@
         <v>0.400499999523163</v>
       </c>
       <c r="G1137" t="n">
-        <v>0.307715833187103</v>
+        <v>0.307715862989426</v>
       </c>
       <c r="H1137" t="n">
         <v>745938</v>
@@ -33400,7 +33400,7 @@
         <v>0.395500004291534</v>
       </c>
       <c r="G1139" t="n">
-        <v>0.30387419462204</v>
+        <v>0.303874224424362</v>
       </c>
       <c r="H1139" t="n">
         <v>257420</v>
@@ -33458,7 +33458,7 @@
         <v>0.388000011444092</v>
       </c>
       <c r="G1141" t="n">
-        <v>0.298111766576767</v>
+        <v>0.298111736774445</v>
       </c>
       <c r="H1141" t="n">
         <v>777351</v>
@@ -33632,7 +33632,7 @@
         <v>0.387499988079071</v>
       </c>
       <c r="G1147" t="n">
-        <v>0.29772761464119</v>
+        <v>0.297727584838867</v>
       </c>
       <c r="H1147" t="n">
         <v>312212</v>
@@ -33690,7 +33690,7 @@
         <v>0.387499988079071</v>
       </c>
       <c r="G1149" t="n">
-        <v>0.29772761464119</v>
+        <v>0.297727584838867</v>
       </c>
       <c r="H1149" t="n">
         <v>377649</v>
@@ -33748,7 +33748,7 @@
         <v>0.394499987363815</v>
       </c>
       <c r="G1151" t="n">
-        <v>0.303105860948563</v>
+        <v>0.303105890750885</v>
       </c>
       <c r="H1151" t="n">
         <v>189730</v>
@@ -33806,7 +33806,7 @@
         <v>0.39750000834465</v>
       </c>
       <c r="G1153" t="n">
-        <v>0.305410832166672</v>
+        <v>0.305410861968994</v>
       </c>
       <c r="H1153" t="n">
         <v>445976</v>
@@ -33864,7 +33864,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G1155" t="n">
-        <v>0.307331651449203</v>
+        <v>0.307331681251526</v>
       </c>
       <c r="H1155" t="n">
         <v>1252599</v>
@@ -33922,7 +33922,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G1157" t="n">
-        <v>0.327308267354965</v>
+        <v>0.327308237552643</v>
       </c>
       <c r="H1157" t="n">
         <v>662608</v>
@@ -33951,7 +33951,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G1158" t="n">
-        <v>0.322698295116425</v>
+        <v>0.322698265314102</v>
       </c>
       <c r="H1158" t="n">
         <v>446962</v>
@@ -33980,7 +33980,7 @@
         <v>0.40650001168251</v>
       </c>
       <c r="G1159" t="n">
-        <v>0.312325775623322</v>
+        <v>0.312325805425644</v>
       </c>
       <c r="H1159" t="n">
         <v>505654</v>
@@ -34038,7 +34038,7 @@
         <v>0.42399999499321</v>
       </c>
       <c r="G1161" t="n">
-        <v>0.325771570205688</v>
+        <v>0.325771600008011</v>
       </c>
       <c r="H1161" t="n">
         <v>2885343</v>
@@ -34067,7 +34067,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G1162" t="n">
-        <v>0.331918209791183</v>
+        <v>0.331918239593506</v>
       </c>
       <c r="H1162" t="n">
         <v>2353979</v>
@@ -34096,7 +34096,7 @@
         <v>0.418500006198883</v>
       </c>
       <c r="G1163" t="n">
-        <v>0.321545779705048</v>
+        <v>0.321545749902725</v>
       </c>
       <c r="H1163" t="n">
         <v>1118913</v>
@@ -34125,7 +34125,7 @@
         <v>0.407499998807907</v>
       </c>
       <c r="G1164" t="n">
-        <v>0.313094139099121</v>
+        <v>0.313094109296799</v>
       </c>
       <c r="H1164" t="n">
         <v>636080</v>
@@ -34183,7 +34183,7 @@
         <v>0.418999999761581</v>
       </c>
       <c r="G1166" t="n">
-        <v>0.321929961442947</v>
+        <v>0.321929931640625</v>
       </c>
       <c r="H1166" t="n">
         <v>771770</v>
@@ -34212,7 +34212,7 @@
         <v>0.41049998998642</v>
       </c>
       <c r="G1167" t="n">
-        <v>0.315399140119553</v>
+        <v>0.31539911031723</v>
       </c>
       <c r="H1167" t="n">
         <v>742911</v>
@@ -34270,7 +34270,7 @@
         <v>0.417499989271164</v>
       </c>
       <c r="G1169" t="n">
-        <v>0.32077744603157</v>
+        <v>0.320777416229248</v>
       </c>
       <c r="H1169" t="n">
         <v>162312</v>
@@ -34357,7 +34357,7 @@
         <v>0.418500006198883</v>
       </c>
       <c r="G1172" t="n">
-        <v>0.321545779705048</v>
+        <v>0.321545749902725</v>
       </c>
       <c r="H1172" t="n">
         <v>222772</v>
@@ -34386,7 +34386,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G1173" t="n">
-        <v>0.317319989204407</v>
+        <v>0.317319959402084</v>
       </c>
       <c r="H1173" t="n">
         <v>136423</v>
@@ -34415,7 +34415,7 @@
         <v>0.404000014066696</v>
       </c>
       <c r="G1174" t="n">
-        <v>0.310405045747757</v>
+        <v>0.310405015945435</v>
       </c>
       <c r="H1174" t="n">
         <v>340373</v>
@@ -34473,7 +34473,7 @@
         <v>0.407999992370605</v>
       </c>
       <c r="G1176" t="n">
-        <v>0.313478291034698</v>
+        <v>0.313478320837021</v>
       </c>
       <c r="H1176" t="n">
         <v>73162</v>
@@ -34502,7 +34502,7 @@
         <v>0.407999992370605</v>
       </c>
       <c r="G1177" t="n">
-        <v>0.313478291034698</v>
+        <v>0.313478320837021</v>
       </c>
       <c r="H1177" t="n">
         <v>171240</v>
@@ -34531,7 +34531,7 @@
         <v>0.404000014066696</v>
       </c>
       <c r="G1178" t="n">
-        <v>0.310405045747757</v>
+        <v>0.310405015945435</v>
       </c>
       <c r="H1178" t="n">
         <v>157300</v>
@@ -34618,7 +34618,7 @@
         <v>0.393500000238419</v>
       </c>
       <c r="G1181" t="n">
-        <v>0.302337527275085</v>
+        <v>0.30233758687973</v>
       </c>
       <c r="H1181" t="n">
         <v>209143</v>
@@ -34676,7 +34676,7 @@
         <v>0.391499996185303</v>
       </c>
       <c r="G1183" t="n">
-        <v>0.300800859928131</v>
+        <v>0.300800889730453</v>
       </c>
       <c r="H1183" t="n">
         <v>73396</v>
@@ -34734,7 +34734,7 @@
         <v>0.386000007390976</v>
       </c>
       <c r="G1185" t="n">
-        <v>0.296575129032135</v>
+        <v>0.29657506942749</v>
       </c>
       <c r="H1185" t="n">
         <v>152328</v>
@@ -34763,7 +34763,7 @@
         <v>0.384999990463257</v>
       </c>
       <c r="G1186" t="n">
-        <v>0.295806735754013</v>
+        <v>0.295806705951691</v>
       </c>
       <c r="H1186" t="n">
         <v>442745</v>
@@ -34821,7 +34821,7 @@
         <v>0.380499988794327</v>
       </c>
       <c r="G1188" t="n">
-        <v>0.292349249124527</v>
+        <v>0.292349278926849</v>
       </c>
       <c r="H1188" t="n">
         <v>387651</v>
@@ -34966,7 +34966,7 @@
         <v>0.376500010490417</v>
       </c>
       <c r="G1193" t="n">
-        <v>0.289275974035263</v>
+        <v>0.289275944232941</v>
       </c>
       <c r="H1193" t="n">
         <v>97667</v>
@@ -34995,7 +34995,7 @@
         <v>0.379000008106232</v>
       </c>
       <c r="G1194" t="n">
-        <v>0.291196763515472</v>
+        <v>0.291196793317795</v>
       </c>
       <c r="H1194" t="n">
         <v>49875</v>
@@ -35024,7 +35024,7 @@
         <v>0.373499989509583</v>
       </c>
       <c r="G1195" t="n">
-        <v>0.286970943212509</v>
+        <v>0.286970973014832</v>
       </c>
       <c r="H1195" t="n">
         <v>100453</v>
@@ -35053,7 +35053,7 @@
         <v>0.369500011205673</v>
       </c>
       <c r="G1196" t="n">
-        <v>0.283897697925568</v>
+        <v>0.283897668123245</v>
       </c>
       <c r="H1196" t="n">
         <v>149719</v>
@@ -35111,7 +35111,7 @@
         <v>0.372999995946884</v>
       </c>
       <c r="G1198" t="n">
-        <v>0.286586791276932</v>
+        <v>0.286586850881577</v>
       </c>
       <c r="H1198" t="n">
         <v>281771</v>
@@ -35314,7 +35314,7 @@
         <v>0.340499997138977</v>
       </c>
       <c r="G1205" t="n">
-        <v>0.261616140604019</v>
+        <v>0.261616110801697</v>
       </c>
       <c r="H1205" t="n">
         <v>132039</v>
@@ -35343,7 +35343,7 @@
         <v>0.344500005245209</v>
       </c>
       <c r="G1206" t="n">
-        <v>0.264689415693283</v>
+        <v>0.264689445495605</v>
       </c>
       <c r="H1206" t="n">
         <v>125582</v>
@@ -35372,7 +35372,7 @@
         <v>0.351500004529953</v>
       </c>
       <c r="G1207" t="n">
-        <v>0.270067751407623</v>
+        <v>0.270067721605301</v>
       </c>
       <c r="H1207" t="n">
         <v>57179</v>
@@ -35401,7 +35401,7 @@
         <v>0.362500011920929</v>
       </c>
       <c r="G1208" t="n">
-        <v>0.278519332408905</v>
+        <v>0.278519362211227</v>
       </c>
       <c r="H1208" t="n">
         <v>292789</v>
@@ -35430,7 +35430,7 @@
         <v>0.356499999761581</v>
       </c>
       <c r="G1209" t="n">
-        <v>0.273909360170364</v>
+        <v>0.273909330368042</v>
       </c>
       <c r="H1209" t="n">
         <v>72200</v>
@@ -35459,7 +35459,7 @@
         <v>0.355500012636185</v>
       </c>
       <c r="G1210" t="n">
-        <v>0.27314105629921</v>
+        <v>0.273141026496887</v>
       </c>
       <c r="H1210" t="n">
         <v>45789</v>
@@ -35488,7 +35488,7 @@
         <v>0.370000004768372</v>
       </c>
       <c r="G1211" t="n">
-        <v>0.284281820058823</v>
+        <v>0.284281849861145</v>
       </c>
       <c r="H1211" t="n">
         <v>133228</v>
@@ -35517,7 +35517,7 @@
         <v>0.368000000715256</v>
       </c>
       <c r="G1212" t="n">
-        <v>0.282745182514191</v>
+        <v>0.282745122909546</v>
       </c>
       <c r="H1212" t="n">
         <v>109764</v>
@@ -35633,7 +35633,7 @@
         <v>0.349000006914139</v>
       </c>
       <c r="G1216" t="n">
-        <v>0.268146902322769</v>
+        <v>0.268146872520447</v>
       </c>
       <c r="H1216" t="n">
         <v>68542</v>
@@ -35662,7 +35662,7 @@
         <v>0.347499996423721</v>
       </c>
       <c r="G1217" t="n">
-        <v>0.266994416713715</v>
+        <v>0.266994386911392</v>
       </c>
       <c r="H1217" t="n">
         <v>180518</v>
@@ -35691,7 +35691,7 @@
         <v>0.344500005245209</v>
       </c>
       <c r="G1218" t="n">
-        <v>0.264689415693283</v>
+        <v>0.264689445495605</v>
       </c>
       <c r="H1218" t="n">
         <v>215334</v>
@@ -35720,7 +35720,7 @@
         <v>0.337000012397766</v>
       </c>
       <c r="G1219" t="n">
-        <v>0.258926928043365</v>
+        <v>0.258926957845688</v>
       </c>
       <c r="H1219" t="n">
         <v>206879</v>
@@ -35778,7 +35778,7 @@
         <v>0.340000003576279</v>
       </c>
       <c r="G1221" t="n">
-        <v>0.261231929063797</v>
+        <v>0.261231958866119</v>
       </c>
       <c r="H1221" t="n">
         <v>170395</v>
@@ -35836,7 +35836,7 @@
         <v>0.329499989748001</v>
       </c>
       <c r="G1223" t="n">
-        <v>0.25316447019577</v>
+        <v>0.253164499998093</v>
       </c>
       <c r="H1223" t="n">
         <v>117915</v>
@@ -35865,7 +35865,7 @@
         <v>0.333999991416931</v>
       </c>
       <c r="G1224" t="n">
-        <v>0.256621986627579</v>
+        <v>0.256621956825256</v>
       </c>
       <c r="H1224" t="n">
         <v>361271</v>
@@ -35923,7 +35923,7 @@
         <v>0.324499994516373</v>
       </c>
       <c r="G1226" t="n">
-        <v>0.249322846531868</v>
+        <v>0.249322816729546</v>
       </c>
       <c r="H1226" t="n">
         <v>177760</v>
@@ -35981,7 +35981,7 @@
         <v>0.310000002384186</v>
       </c>
       <c r="G1228" t="n">
-        <v>0.238182052969933</v>
+        <v>0.238182067871094</v>
       </c>
       <c r="H1228" t="n">
         <v>224862</v>
@@ -36039,7 +36039,7 @@
         <v>0.34850001335144</v>
       </c>
       <c r="G1230" t="n">
-        <v>0.267762780189514</v>
+        <v>0.267762750387192</v>
       </c>
       <c r="H1230" t="n">
         <v>560373</v>
@@ -36068,7 +36068,7 @@
         <v>0.368999987840652</v>
       </c>
       <c r="G1231" t="n">
-        <v>0.283513456583023</v>
+        <v>0.283513486385345</v>
       </c>
       <c r="H1231" t="n">
         <v>490748</v>
@@ -36097,7 +36097,7 @@
         <v>0.370000004768372</v>
       </c>
       <c r="G1232" t="n">
-        <v>0.284281820058823</v>
+        <v>0.284281849861145</v>
       </c>
       <c r="H1232" t="n">
         <v>385267</v>
@@ -36126,7 +36126,7 @@
         <v>0.359499990940094</v>
       </c>
       <c r="G1233" t="n">
-        <v>0.276214331388474</v>
+        <v>0.276214361190796</v>
       </c>
       <c r="H1233" t="n">
         <v>349004</v>
@@ -36300,7 +36300,7 @@
         <v>0.383500009775162</v>
       </c>
       <c r="G1239" t="n">
-        <v>0.294654279947281</v>
+        <v>0.294654250144958</v>
       </c>
       <c r="H1239" t="n">
         <v>603572</v>
@@ -36358,7 +36358,7 @@
         <v>0.407999992370605</v>
       </c>
       <c r="G1241" t="n">
-        <v>0.313478291034698</v>
+        <v>0.313478320837021</v>
       </c>
       <c r="H1241" t="n">
         <v>959845</v>
@@ -36445,7 +36445,7 @@
         <v>0.395500004291534</v>
       </c>
       <c r="G1244" t="n">
-        <v>0.30387419462204</v>
+        <v>0.303874224424362</v>
       </c>
       <c r="H1244" t="n">
         <v>344491</v>
@@ -36561,7 +36561,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G1248" t="n">
-        <v>0.319624960422516</v>
+        <v>0.319624990224838</v>
       </c>
       <c r="H1248" t="n">
         <v>703715</v>
@@ -36590,7 +36590,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G1249" t="n">
-        <v>0.322698295116425</v>
+        <v>0.322698265314102</v>
       </c>
       <c r="H1249" t="n">
         <v>698946</v>
@@ -36619,7 +36619,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G1250" t="n">
-        <v>0.330381572246552</v>
+        <v>0.330381602048874</v>
       </c>
       <c r="H1250" t="n">
         <v>1758008</v>
@@ -36648,7 +36648,7 @@
         <v>0.43299999833107</v>
       </c>
       <c r="G1251" t="n">
-        <v>0.332686543464661</v>
+        <v>0.332686573266983</v>
       </c>
       <c r="H1251" t="n">
         <v>617203</v>
@@ -36677,7 +36677,7 @@
         <v>0.422500014305115</v>
       </c>
       <c r="G1252" t="n">
-        <v>0.324619114398956</v>
+        <v>0.324619084596634</v>
       </c>
       <c r="H1252" t="n">
         <v>434503</v>
@@ -36706,7 +36706,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G1253" t="n">
-        <v>0.344211518764496</v>
+        <v>0.344211488962173</v>
       </c>
       <c r="H1253" t="n">
         <v>674839</v>
@@ -36735,7 +36735,7 @@
         <v>0.457500010728836</v>
       </c>
       <c r="G1254" t="n">
-        <v>0.351510643959045</v>
+        <v>0.351510614156723</v>
       </c>
       <c r="H1254" t="n">
         <v>2042950</v>
@@ -36764,7 +36764,7 @@
         <v>0.447499990463257</v>
       </c>
       <c r="G1255" t="n">
-        <v>0.343827307224274</v>
+        <v>0.343827337026596</v>
       </c>
       <c r="H1255" t="n">
         <v>324880</v>
@@ -36822,7 +36822,7 @@
         <v>0.440499991178513</v>
       </c>
       <c r="G1257" t="n">
-        <v>0.338449001312256</v>
+        <v>0.338449031114578</v>
       </c>
       <c r="H1257" t="n">
         <v>389656</v>
@@ -36851,7 +36851,7 @@
         <v>0.440499991178513</v>
       </c>
       <c r="G1258" t="n">
-        <v>0.338449001312256</v>
+        <v>0.338449031114578</v>
       </c>
       <c r="H1258" t="n">
         <v>301840</v>
@@ -36909,7 +36909,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G1260" t="n">
-        <v>0.336528211832047</v>
+        <v>0.336528182029724</v>
       </c>
       <c r="H1260" t="n">
         <v>283747</v>
@@ -36967,7 +36967,7 @@
         <v>0.43299999833107</v>
       </c>
       <c r="G1262" t="n">
-        <v>0.332686543464661</v>
+        <v>0.332686573266983</v>
       </c>
       <c r="H1262" t="n">
         <v>189982</v>
@@ -37025,7 +37025,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G1264" t="n">
-        <v>0.327308267354965</v>
+        <v>0.327308237552643</v>
       </c>
       <c r="H1264" t="n">
         <v>156531</v>
@@ -37054,7 +37054,7 @@
         <v>0.417499989271164</v>
       </c>
       <c r="G1265" t="n">
-        <v>0.32077744603157</v>
+        <v>0.320777416229248</v>
       </c>
       <c r="H1265" t="n">
         <v>322909</v>
@@ -37083,7 +37083,7 @@
         <v>0.418999999761581</v>
       </c>
       <c r="G1266" t="n">
-        <v>0.321929961442947</v>
+        <v>0.321929931640625</v>
       </c>
       <c r="H1266" t="n">
         <v>94866</v>
@@ -37112,7 +37112,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G1267" t="n">
-        <v>0.324234962463379</v>
+        <v>0.324234932661057</v>
       </c>
       <c r="H1267" t="n">
         <v>152150</v>
@@ -37141,7 +37141,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G1268" t="n">
-        <v>0.324234962463379</v>
+        <v>0.324234932661057</v>
       </c>
       <c r="H1268" t="n">
         <v>132647</v>
@@ -37170,7 +37170,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G1269" t="n">
-        <v>0.322698295116425</v>
+        <v>0.322698265314102</v>
       </c>
       <c r="H1269" t="n">
         <v>139630</v>
@@ -37199,7 +37199,7 @@
         <v>0.413500010967255</v>
       </c>
       <c r="G1270" t="n">
-        <v>0.317704141139984</v>
+        <v>0.317704111337662</v>
       </c>
       <c r="H1270" t="n">
         <v>222853</v>
@@ -37228,7 +37228,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G1271" t="n">
-        <v>0.324234962463379</v>
+        <v>0.324234932661057</v>
       </c>
       <c r="H1271" t="n">
         <v>419507</v>
@@ -37257,7 +37257,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G1272" t="n">
-        <v>0.333454847335815</v>
+        <v>0.333454877138138</v>
       </c>
       <c r="H1272" t="n">
         <v>1179631</v>
@@ -37286,7 +37286,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G1273" t="n">
-        <v>0.344211518764496</v>
+        <v>0.344211488962173</v>
       </c>
       <c r="H1273" t="n">
         <v>658425</v>
@@ -37431,7 +37431,7 @@
         <v>0.430500000715256</v>
       </c>
       <c r="G1278" t="n">
-        <v>0.330765724182129</v>
+        <v>0.330765753984451</v>
       </c>
       <c r="H1278" t="n">
         <v>181343</v>
@@ -37460,7 +37460,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G1279" t="n">
-        <v>0.328844904899597</v>
+        <v>0.328844875097275</v>
       </c>
       <c r="H1279" t="n">
         <v>85899</v>
@@ -37489,7 +37489,7 @@
         <v>0.41499999165535</v>
       </c>
       <c r="G1280" t="n">
-        <v>0.318856626749039</v>
+        <v>0.318856596946716</v>
       </c>
       <c r="H1280" t="n">
         <v>263561</v>
@@ -37518,7 +37518,7 @@
         <v>0.41499999165535</v>
       </c>
       <c r="G1281" t="n">
-        <v>0.318856626749039</v>
+        <v>0.318856596946716</v>
       </c>
       <c r="H1281" t="n">
         <v>138151</v>
@@ -37547,7 +37547,7 @@
         <v>0.42399999499321</v>
       </c>
       <c r="G1282" t="n">
-        <v>0.325771570205688</v>
+        <v>0.325771600008011</v>
       </c>
       <c r="H1282" t="n">
         <v>157010</v>
@@ -37576,7 +37576,7 @@
         <v>0.426499992609024</v>
       </c>
       <c r="G1283" t="n">
-        <v>0.327692449092865</v>
+        <v>0.327692419290543</v>
       </c>
       <c r="H1283" t="n">
         <v>201278</v>
@@ -37634,7 +37634,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G1285" t="n">
-        <v>0.317319989204407</v>
+        <v>0.317319959402084</v>
       </c>
       <c r="H1285" t="n">
         <v>616441</v>
@@ -37663,7 +37663,7 @@
         <v>0.40149998664856</v>
       </c>
       <c r="G1286" t="n">
-        <v>0.30848416686058</v>
+        <v>0.308484226465225</v>
       </c>
       <c r="H1286" t="n">
         <v>673029</v>
@@ -37750,7 +37750,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G1289" t="n">
-        <v>0.307331651449203</v>
+        <v>0.307331681251526</v>
       </c>
       <c r="H1289" t="n">
         <v>636139</v>
@@ -37808,7 +37808,7 @@
         <v>0.407499998807907</v>
       </c>
       <c r="G1291" t="n">
-        <v>0.313094139099121</v>
+        <v>0.313094109296799</v>
       </c>
       <c r="H1291" t="n">
         <v>222603</v>
@@ -37837,7 +37837,7 @@
         <v>0.430500000715256</v>
       </c>
       <c r="G1292" t="n">
-        <v>0.330765724182129</v>
+        <v>0.330765753984451</v>
       </c>
       <c r="H1292" t="n">
         <v>654938</v>
@@ -37866,7 +37866,7 @@
         <v>0.4375</v>
       </c>
       <c r="G1293" t="n">
-        <v>0.336144059896469</v>
+        <v>0.336144030094147</v>
       </c>
       <c r="H1293" t="n">
         <v>830299</v>
@@ -37924,7 +37924,7 @@
         <v>0.43299999833107</v>
       </c>
       <c r="G1295" t="n">
-        <v>0.332686543464661</v>
+        <v>0.332686573266983</v>
       </c>
       <c r="H1295" t="n">
         <v>434361</v>
@@ -38127,7 +38127,7 @@
         <v>0.458000004291534</v>
       </c>
       <c r="G1302" t="n">
-        <v>0.351894795894623</v>
+        <v>0.3518947660923</v>
       </c>
       <c r="H1302" t="n">
         <v>634273</v>
@@ -38156,7 +38156,7 @@
         <v>0.461499989032745</v>
       </c>
       <c r="G1303" t="n">
-        <v>0.354583919048309</v>
+        <v>0.354583948850632</v>
       </c>
       <c r="H1303" t="n">
         <v>498947</v>
@@ -38243,7 +38243,7 @@
         <v>0.467000007629395</v>
       </c>
       <c r="G1306" t="n">
-        <v>0.358809739351273</v>
+        <v>0.35880970954895</v>
       </c>
       <c r="H1306" t="n">
         <v>500494</v>
@@ -38417,7 +38417,7 @@
         <v>0.479000002145767</v>
       </c>
       <c r="G1312" t="n">
-        <v>0.368029654026031</v>
+        <v>0.368029683828354</v>
       </c>
       <c r="H1312" t="n">
         <v>551502</v>
@@ -38504,7 +38504,7 @@
         <v>0.467000007629395</v>
       </c>
       <c r="G1315" t="n">
-        <v>0.358809739351273</v>
+        <v>0.35880970954895</v>
       </c>
       <c r="H1315" t="n">
         <v>186054</v>
@@ -38533,7 +38533,7 @@
         <v>0.456499993801117</v>
       </c>
       <c r="G1316" t="n">
-        <v>0.350742250680923</v>
+        <v>0.350742280483246</v>
       </c>
       <c r="H1316" t="n">
         <v>586599</v>
@@ -38562,7 +38562,7 @@
         <v>0.460999995470047</v>
       </c>
       <c r="G1317" t="n">
-        <v>0.35419973731041</v>
+        <v>0.354199767112732</v>
       </c>
       <c r="H1317" t="n">
         <v>221213</v>
@@ -38649,7 +38649,7 @@
         <v>0.46399998664856</v>
       </c>
       <c r="G1320" t="n">
-        <v>0.356504738330841</v>
+        <v>0.356504708528519</v>
       </c>
       <c r="H1320" t="n">
         <v>165538</v>
@@ -38765,7 +38765,7 @@
         <v>0.456999987363815</v>
       </c>
       <c r="G1324" t="n">
-        <v>0.351126462221146</v>
+        <v>0.351126432418823</v>
       </c>
       <c r="H1324" t="n">
         <v>196561</v>
@@ -38823,7 +38823,7 @@
         <v>0.455000013113022</v>
       </c>
       <c r="G1326" t="n">
-        <v>0.349589794874191</v>
+        <v>0.349589824676514</v>
       </c>
       <c r="H1326" t="n">
         <v>245427</v>
@@ -38852,7 +38852,7 @@
         <v>0.45550000667572</v>
       </c>
       <c r="G1327" t="n">
-        <v>0.349974006414413</v>
+        <v>0.349973976612091</v>
       </c>
       <c r="H1327" t="n">
         <v>337371</v>
@@ -38881,7 +38881,7 @@
         <v>0.45100000500679</v>
       </c>
       <c r="G1328" t="n">
-        <v>0.346516489982605</v>
+        <v>0.346516460180283</v>
       </c>
       <c r="H1328" t="n">
         <v>225436</v>
@@ -38939,7 +38939,7 @@
         <v>0.450500011444092</v>
       </c>
       <c r="G1330" t="n">
-        <v>0.346132308244705</v>
+        <v>0.346132338047028</v>
       </c>
       <c r="H1330" t="n">
         <v>288418</v>
@@ -39026,7 +39026,7 @@
         <v>0.460999995470047</v>
       </c>
       <c r="G1333" t="n">
-        <v>0.35419973731041</v>
+        <v>0.354199767112732</v>
       </c>
       <c r="H1333" t="n">
         <v>598315</v>
@@ -39084,7 +39084,7 @@
         <v>0.472499996423721</v>
       </c>
       <c r="G1335" t="n">
-        <v>0.363035529851913</v>
+        <v>0.363035559654236</v>
       </c>
       <c r="H1335" t="n">
         <v>255911</v>
@@ -39113,7 +39113,7 @@
         <v>0.469999998807907</v>
       </c>
       <c r="G1336" t="n">
-        <v>0.361114710569382</v>
+        <v>0.361114770174026</v>
       </c>
       <c r="H1336" t="n">
         <v>110377</v>
@@ -39142,7 +39142,7 @@
         <v>0.461499989032745</v>
       </c>
       <c r="G1337" t="n">
-        <v>0.354583919048309</v>
+        <v>0.354583948850632</v>
       </c>
       <c r="H1337" t="n">
         <v>193013</v>
@@ -39171,7 +39171,7 @@
         <v>0.458000004291534</v>
       </c>
       <c r="G1338" t="n">
-        <v>0.351894795894623</v>
+        <v>0.3518947660923</v>
       </c>
       <c r="H1338" t="n">
         <v>107286</v>
@@ -39229,7 +39229,7 @@
         <v>0.477999985218048</v>
       </c>
       <c r="G1340" t="n">
-        <v>0.367261350154877</v>
+        <v>0.367261320352554</v>
       </c>
       <c r="H1340" t="n">
         <v>1122989</v>
@@ -39258,7 +39258,7 @@
         <v>0.490500003099442</v>
       </c>
       <c r="G1341" t="n">
-        <v>0.376865476369858</v>
+        <v>0.37686550617218</v>
       </c>
       <c r="H1341" t="n">
         <v>2353291</v>
@@ -39287,7 +39287,7 @@
         <v>0.493499994277954</v>
       </c>
       <c r="G1342" t="n">
-        <v>0.379170477390289</v>
+        <v>0.379170447587967</v>
       </c>
       <c r="H1342" t="n">
         <v>671887</v>
@@ -39345,7 +39345,7 @@
         <v>0.493499994277954</v>
       </c>
       <c r="G1344" t="n">
-        <v>0.379170477390289</v>
+        <v>0.379170447587967</v>
       </c>
       <c r="H1344" t="n">
         <v>420374</v>
@@ -39403,7 +39403,7 @@
         <v>0.472499996423721</v>
       </c>
       <c r="G1346" t="n">
-        <v>0.363035529851913</v>
+        <v>0.363035559654236</v>
       </c>
       <c r="H1346" t="n">
         <v>417183</v>
@@ -39461,7 +39461,7 @@
         <v>0.476000010967255</v>
       </c>
       <c r="G1348" t="n">
-        <v>0.365724712610245</v>
+        <v>0.365724742412567</v>
       </c>
       <c r="H1348" t="n">
         <v>236032</v>
@@ -39490,7 +39490,7 @@
         <v>0.477999985218048</v>
       </c>
       <c r="G1349" t="n">
-        <v>0.367261350154877</v>
+        <v>0.367261320352554</v>
       </c>
       <c r="H1349" t="n">
         <v>93170</v>
@@ -39548,7 +39548,7 @@
         <v>0.476000010967255</v>
       </c>
       <c r="G1351" t="n">
-        <v>0.365724712610245</v>
+        <v>0.365724742412567</v>
       </c>
       <c r="H1351" t="n">
         <v>154112</v>
@@ -39635,7 +39635,7 @@
         <v>0.467000007629395</v>
       </c>
       <c r="G1354" t="n">
-        <v>0.358809739351273</v>
+        <v>0.35880970954895</v>
       </c>
       <c r="H1354" t="n">
         <v>157819</v>
@@ -39809,7 +39809,7 @@
         <v>0.477999985218048</v>
       </c>
       <c r="G1360" t="n">
-        <v>0.367261350154877</v>
+        <v>0.367261320352554</v>
       </c>
       <c r="H1360" t="n">
         <v>208030</v>
@@ -39838,7 +39838,7 @@
         <v>0.476000010967255</v>
       </c>
       <c r="G1361" t="n">
-        <v>0.365724712610245</v>
+        <v>0.365724742412567</v>
       </c>
       <c r="H1361" t="n">
         <v>152141</v>
@@ -39867,7 +39867,7 @@
         <v>0.476000010967255</v>
       </c>
       <c r="G1362" t="n">
-        <v>0.365724712610245</v>
+        <v>0.365724742412567</v>
       </c>
       <c r="H1362" t="n">
         <v>447642</v>
@@ -39954,7 +39954,7 @@
         <v>0.48649999499321</v>
       </c>
       <c r="G1365" t="n">
-        <v>0.373792141675949</v>
+        <v>0.373792171478271</v>
       </c>
       <c r="H1365" t="n">
         <v>261249</v>
@@ -40012,7 +40012,7 @@
         <v>0.484499990940094</v>
       </c>
       <c r="G1367" t="n">
-        <v>0.37225553393364</v>
+        <v>0.372255504131317</v>
       </c>
       <c r="H1367" t="n">
         <v>127705</v>
@@ -40099,7 +40099,7 @@
         <v>0.476999998092651</v>
       </c>
       <c r="G1370" t="n">
-        <v>0.3664930164814</v>
+        <v>0.366493046283722</v>
       </c>
       <c r="H1370" t="n">
         <v>207579</v>
@@ -40128,7 +40128,7 @@
         <v>0.476500004529953</v>
       </c>
       <c r="G1371" t="n">
-        <v>0.366108894348145</v>
+        <v>0.366108864545822</v>
       </c>
       <c r="H1371" t="n">
         <v>86192</v>
@@ -40186,7 +40186,7 @@
         <v>0.479000002145767</v>
       </c>
       <c r="G1373" t="n">
-        <v>0.368029654026031</v>
+        <v>0.368029683828354</v>
       </c>
       <c r="H1373" t="n">
         <v>167090</v>
@@ -40215,7 +40215,7 @@
         <v>0.48199999332428</v>
       </c>
       <c r="G1374" t="n">
-        <v>0.370334655046463</v>
+        <v>0.370334714651108</v>
       </c>
       <c r="H1374" t="n">
         <v>175634</v>
@@ -40273,7 +40273,7 @@
         <v>0.493999987840652</v>
       </c>
       <c r="G1376" t="n">
-        <v>0.379554659128189</v>
+        <v>0.379554599523544</v>
       </c>
       <c r="H1376" t="n">
         <v>792595</v>
@@ -40302,7 +40302,7 @@
         <v>0.503000020980835</v>
       </c>
       <c r="G1377" t="n">
-        <v>0.386469602584839</v>
+        <v>0.386469572782516</v>
       </c>
       <c r="H1377" t="n">
         <v>917325</v>
@@ -40331,7 +40331,7 @@
         <v>0.501999974250793</v>
       </c>
       <c r="G1378" t="n">
-        <v>0.385701298713684</v>
+        <v>0.385701239109039</v>
       </c>
       <c r="H1378" t="n">
         <v>439413</v>
@@ -40389,7 +40389,7 @@
         <v>0.504000008106232</v>
       </c>
       <c r="G1380" t="n">
-        <v>0.387237906455994</v>
+        <v>0.387237936258316</v>
       </c>
       <c r="H1380" t="n">
         <v>429906</v>
@@ -40476,7 +40476,7 @@
         <v>0.547999978065491</v>
       </c>
       <c r="G1383" t="n">
-        <v>0.421044379472733</v>
+        <v>0.421044409275055</v>
       </c>
       <c r="H1383" t="n">
         <v>2587415</v>
@@ -40563,7 +40563,7 @@
         <v>0.554000020027161</v>
       </c>
       <c r="G1386" t="n">
-        <v>0.425654411315918</v>
+        <v>0.425654381513596</v>
       </c>
       <c r="H1386" t="n">
         <v>312064</v>
@@ -40592,7 +40592,7 @@
         <v>0.545000016689301</v>
       </c>
       <c r="G1387" t="n">
-        <v>0.418739438056946</v>
+        <v>0.418739467859268</v>
       </c>
       <c r="H1387" t="n">
         <v>571005</v>
@@ -40621,7 +40621,7 @@
         <v>0.533999979496002</v>
       </c>
       <c r="G1388" t="n">
-        <v>0.410287797451019</v>
+        <v>0.410287827253342</v>
       </c>
       <c r="H1388" t="n">
         <v>693151</v>
@@ -40650,7 +40650,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G1389" t="n">
-        <v>0.417971104383469</v>
+        <v>0.417971134185791</v>
       </c>
       <c r="H1389" t="n">
         <v>799079</v>
@@ -40679,7 +40679,7 @@
         <v>0.545000016689301</v>
       </c>
       <c r="G1390" t="n">
-        <v>0.418739438056946</v>
+        <v>0.418739467859268</v>
       </c>
       <c r="H1390" t="n">
         <v>588569</v>
@@ -40737,7 +40737,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1392" t="n">
-        <v>0.41489776968956</v>
+        <v>0.414897799491882</v>
       </c>
       <c r="H1392" t="n">
         <v>517597</v>
@@ -40795,7 +40795,7 @@
         <v>0.531000018119812</v>
       </c>
       <c r="G1394" t="n">
-        <v>0.40798282623291</v>
+        <v>0.407982856035233</v>
       </c>
       <c r="H1394" t="n">
         <v>364146</v>
@@ -40824,7 +40824,7 @@
         <v>0.532999992370605</v>
       </c>
       <c r="G1395" t="n">
-        <v>0.409519463777542</v>
+        <v>0.409519493579865</v>
       </c>
       <c r="H1395" t="n">
         <v>310765</v>
@@ -40882,7 +40882,7 @@
         <v>0.538999974727631</v>
       </c>
       <c r="G1397" t="n">
-        <v>0.41412940621376</v>
+        <v>0.414129436016083</v>
       </c>
       <c r="H1397" t="n">
         <v>186700</v>
@@ -40940,7 +40940,7 @@
         <v>0.550999999046326</v>
       </c>
       <c r="G1399" t="n">
-        <v>0.423349410295486</v>
+        <v>0.423349380493164</v>
       </c>
       <c r="H1399" t="n">
         <v>442923</v>
@@ -40969,7 +40969,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G1400" t="n">
-        <v>0.417971104383469</v>
+        <v>0.417971134185791</v>
       </c>
       <c r="H1400" t="n">
         <v>181734</v>
@@ -41056,7 +41056,7 @@
         <v>0.533999979496002</v>
       </c>
       <c r="G1403" t="n">
-        <v>0.410287797451019</v>
+        <v>0.410287827253342</v>
       </c>
       <c r="H1403" t="n">
         <v>376604</v>
@@ -41085,7 +41085,7 @@
         <v>0.538999974727631</v>
       </c>
       <c r="G1404" t="n">
-        <v>0.41412940621376</v>
+        <v>0.414129436016083</v>
       </c>
       <c r="H1404" t="n">
         <v>377317</v>
@@ -41288,7 +41288,7 @@
         <v>0.493499994277954</v>
       </c>
       <c r="G1411" t="n">
-        <v>0.379170477390289</v>
+        <v>0.379170447587967</v>
       </c>
       <c r="H1411" t="n">
         <v>403657</v>
@@ -41375,7 +41375,7 @@
         <v>0.503000020980835</v>
       </c>
       <c r="G1414" t="n">
-        <v>0.386469602584839</v>
+        <v>0.386469572782516</v>
       </c>
       <c r="H1414" t="n">
         <v>293157</v>
@@ -41433,7 +41433,7 @@
         <v>0.504000008106232</v>
       </c>
       <c r="G1416" t="n">
-        <v>0.387237906455994</v>
+        <v>0.387237936258316</v>
       </c>
       <c r="H1416" t="n">
         <v>149641</v>
@@ -41462,7 +41462,7 @@
         <v>0.505999982357025</v>
       </c>
       <c r="G1417" t="n">
-        <v>0.388774544000626</v>
+        <v>0.388774573802948</v>
       </c>
       <c r="H1417" t="n">
         <v>274907</v>
@@ -41520,7 +41520,7 @@
         <v>0.504000008106232</v>
       </c>
       <c r="G1419" t="n">
-        <v>0.387237906455994</v>
+        <v>0.387237936258316</v>
       </c>
       <c r="H1419" t="n">
         <v>358942</v>
@@ -41549,7 +41549,7 @@
         <v>0.497999995946884</v>
       </c>
       <c r="G1420" t="n">
-        <v>0.382627964019775</v>
+        <v>0.382627934217453</v>
       </c>
       <c r="H1420" t="n">
         <v>371173</v>
@@ -41578,7 +41578,7 @@
         <v>0.501999974250793</v>
       </c>
       <c r="G1421" t="n">
-        <v>0.385701298713684</v>
+        <v>0.385701239109039</v>
       </c>
       <c r="H1421" t="n">
         <v>316009</v>
@@ -41723,7 +41723,7 @@
         <v>0.492000013589859</v>
       </c>
       <c r="G1426" t="n">
-        <v>0.378017991781235</v>
+        <v>0.378017961978912</v>
       </c>
       <c r="H1426" t="n">
         <v>215745</v>
@@ -41781,7 +41781,7 @@
         <v>0.497999995946884</v>
       </c>
       <c r="G1428" t="n">
-        <v>0.382627964019775</v>
+        <v>0.382627934217453</v>
       </c>
       <c r="H1428" t="n">
         <v>169793</v>
@@ -41810,7 +41810,7 @@
         <v>0.495999991893768</v>
       </c>
       <c r="G1429" t="n">
-        <v>0.381091296672821</v>
+        <v>0.381091266870499</v>
       </c>
       <c r="H1429" t="n">
         <v>221517</v>
@@ -41984,7 +41984,7 @@
         <v>0.453500002622604</v>
       </c>
       <c r="G1435" t="n">
-        <v>0.348437309265137</v>
+        <v>0.348437339067459</v>
       </c>
       <c r="H1435" t="n">
         <v>561083</v>
@@ -42013,7 +42013,7 @@
         <v>0.455000013113022</v>
       </c>
       <c r="G1436" t="n">
-        <v>0.349589794874191</v>
+        <v>0.349589824676514</v>
       </c>
       <c r="H1436" t="n">
         <v>150059</v>
@@ -42042,7 +42042,7 @@
         <v>0.456499993801117</v>
       </c>
       <c r="G1437" t="n">
-        <v>0.350742250680923</v>
+        <v>0.350742280483246</v>
       </c>
       <c r="H1437" t="n">
         <v>308672</v>
@@ -42100,7 +42100,7 @@
         <v>0.470999985933304</v>
       </c>
       <c r="G1439" t="n">
-        <v>0.361883014440536</v>
+        <v>0.361883044242859</v>
       </c>
       <c r="H1439" t="n">
         <v>624571</v>
@@ -42216,7 +42216,7 @@
         <v>0.545000016689301</v>
       </c>
       <c r="G1443" t="n">
-        <v>0.418739438056946</v>
+        <v>0.418739467859268</v>
       </c>
       <c r="H1443" t="n">
         <v>8544072</v>
@@ -42303,7 +42303,7 @@
         <v>0.549000024795532</v>
       </c>
       <c r="G1446" t="n">
-        <v>0.421812772750854</v>
+        <v>0.421812742948532</v>
       </c>
       <c r="H1446" t="n">
         <v>1587777</v>
@@ -42419,7 +42419,7 @@
         <v>0.524999976158142</v>
       </c>
       <c r="G1450" t="n">
-        <v>0.403372824192047</v>
+        <v>0.403372794389725</v>
       </c>
       <c r="H1450" t="n">
         <v>621570</v>
@@ -42506,7 +42506,7 @@
         <v>0.513999998569489</v>
       </c>
       <c r="G1453" t="n">
-        <v>0.394921183586121</v>
+        <v>0.394921213388443</v>
       </c>
       <c r="H1453" t="n">
         <v>324088</v>
@@ -42535,7 +42535,7 @@
         <v>0.507000029087067</v>
       </c>
       <c r="G1454" t="n">
-        <v>0.389542937278748</v>
+        <v>0.389542907476425</v>
       </c>
       <c r="H1454" t="n">
         <v>1115031</v>
@@ -42564,7 +42564,7 @@
         <v>0.499000012874603</v>
       </c>
       <c r="G1455" t="n">
-        <v>0.383396297693253</v>
+        <v>0.38339626789093</v>
       </c>
       <c r="H1455" t="n">
         <v>497718</v>
@@ -42593,7 +42593,7 @@
         <v>0.513000011444092</v>
       </c>
       <c r="G1456" t="n">
-        <v>0.394152879714966</v>
+        <v>0.394152909517288</v>
       </c>
       <c r="H1456" t="n">
         <v>448752</v>
@@ -42651,7 +42651,7 @@
         <v>0.513999998569489</v>
       </c>
       <c r="G1458" t="n">
-        <v>0.394921183586121</v>
+        <v>0.394921213388443</v>
       </c>
       <c r="H1458" t="n">
         <v>157473</v>
@@ -42709,7 +42709,7 @@
         <v>0.500999987125397</v>
       </c>
       <c r="G1460" t="n">
-        <v>0.384932965040207</v>
+        <v>0.384932935237885</v>
       </c>
       <c r="H1460" t="n">
         <v>681074</v>
@@ -42738,7 +42738,7 @@
         <v>0.495999991893768</v>
       </c>
       <c r="G1461" t="n">
-        <v>0.381091296672821</v>
+        <v>0.381091266870499</v>
       </c>
       <c r="H1461" t="n">
         <v>327677</v>
@@ -42767,7 +42767,7 @@
         <v>0.488000005483627</v>
       </c>
       <c r="G1462" t="n">
-        <v>0.374944657087326</v>
+        <v>0.374944686889648</v>
       </c>
       <c r="H1462" t="n">
         <v>474735</v>
@@ -42796,7 +42796,7 @@
         <v>0.488499999046326</v>
       </c>
       <c r="G1463" t="n">
-        <v>0.375328809022903</v>
+        <v>0.375328779220581</v>
       </c>
       <c r="H1463" t="n">
         <v>720591</v>
@@ -42970,7 +42970,7 @@
         <v>0.545000016689301</v>
       </c>
       <c r="G1469" t="n">
-        <v>0.418739438056946</v>
+        <v>0.418739467859268</v>
       </c>
       <c r="H1469" t="n">
         <v>3580885</v>
@@ -42999,7 +42999,7 @@
         <v>0.547999978065491</v>
       </c>
       <c r="G1470" t="n">
-        <v>0.421044379472733</v>
+        <v>0.421044409275055</v>
       </c>
       <c r="H1470" t="n">
         <v>1052105</v>
@@ -43057,7 +43057,7 @@
         <v>0.53600001335144</v>
       </c>
       <c r="G1472" t="n">
-        <v>0.411824494600296</v>
+        <v>0.411824464797974</v>
       </c>
       <c r="H1472" t="n">
         <v>518530</v>
@@ -43086,7 +43086,7 @@
         <v>0.531000018119812</v>
       </c>
       <c r="G1473" t="n">
-        <v>0.40798282623291</v>
+        <v>0.407982856035233</v>
       </c>
       <c r="H1473" t="n">
         <v>339863</v>
@@ -43115,7 +43115,7 @@
         <v>0.524999976158142</v>
       </c>
       <c r="G1474" t="n">
-        <v>0.403372824192047</v>
+        <v>0.403372794389725</v>
       </c>
       <c r="H1474" t="n">
         <v>227709</v>
@@ -43144,7 +43144,7 @@
         <v>0.513000011444092</v>
       </c>
       <c r="G1475" t="n">
-        <v>0.394152879714966</v>
+        <v>0.394152909517288</v>
       </c>
       <c r="H1475" t="n">
         <v>591991</v>
@@ -43260,7 +43260,7 @@
         <v>0.538999974727631</v>
       </c>
       <c r="G1479" t="n">
-        <v>0.41412940621376</v>
+        <v>0.414129436016083</v>
       </c>
       <c r="H1479" t="n">
         <v>690951</v>
@@ -43289,7 +43289,7 @@
         <v>0.541000008583069</v>
       </c>
       <c r="G1480" t="n">
-        <v>0.415666103363037</v>
+        <v>0.415666162967682</v>
       </c>
       <c r="H1480" t="n">
         <v>613061</v>
@@ -43318,7 +43318,7 @@
         <v>0.526000022888184</v>
       </c>
       <c r="G1481" t="n">
-        <v>0.404141157865524</v>
+        <v>0.404141187667847</v>
       </c>
       <c r="H1481" t="n">
         <v>330560</v>
@@ -43376,7 +43376,7 @@
         <v>0.518999993801117</v>
       </c>
       <c r="G1483" t="n">
-        <v>0.398762881755829</v>
+        <v>0.398762851953506</v>
       </c>
       <c r="H1483" t="n">
         <v>431210</v>
@@ -43405,7 +43405,7 @@
         <v>0.514999985694885</v>
       </c>
       <c r="G1484" t="n">
-        <v>0.395689517259598</v>
+        <v>0.39568954706192</v>
       </c>
       <c r="H1484" t="n">
         <v>352539</v>
@@ -43434,7 +43434,7 @@
         <v>0.507000029087067</v>
       </c>
       <c r="G1485" t="n">
-        <v>0.389542937278748</v>
+        <v>0.389542907476425</v>
       </c>
       <c r="H1485" t="n">
         <v>305502</v>
@@ -43492,7 +43492,7 @@
         <v>0.514999985694885</v>
       </c>
       <c r="G1487" t="n">
-        <v>0.395689517259598</v>
+        <v>0.39568954706192</v>
       </c>
       <c r="H1487" t="n">
         <v>208347</v>
@@ -43579,7 +43579,7 @@
         <v>0.526000022888184</v>
       </c>
       <c r="G1490" t="n">
-        <v>0.404141157865524</v>
+        <v>0.404141187667847</v>
       </c>
       <c r="H1490" t="n">
         <v>1397392</v>
@@ -43608,7 +43608,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1491" t="n">
-        <v>0.41489776968956</v>
+        <v>0.414897799491882</v>
       </c>
       <c r="H1491" t="n">
         <v>442383</v>
@@ -43637,7 +43637,7 @@
         <v>0.558000028133392</v>
       </c>
       <c r="G1492" t="n">
-        <v>0.428727716207504</v>
+        <v>0.428727746009827</v>
       </c>
       <c r="H1492" t="n">
         <v>2038664</v>
@@ -43666,7 +43666,7 @@
         <v>0.526000022888184</v>
       </c>
       <c r="G1493" t="n">
-        <v>0.404141157865524</v>
+        <v>0.404141187667847</v>
       </c>
       <c r="H1493" t="n">
         <v>3105393</v>
@@ -43695,7 +43695,7 @@
         <v>0.533999979496002</v>
       </c>
       <c r="G1494" t="n">
-        <v>0.410287797451019</v>
+        <v>0.410287827253342</v>
       </c>
       <c r="H1494" t="n">
         <v>1403748</v>
@@ -43724,7 +43724,7 @@
         <v>0.515999972820282</v>
       </c>
       <c r="G1495" t="n">
-        <v>0.396457850933075</v>
+        <v>0.396457821130753</v>
       </c>
       <c r="H1495" t="n">
         <v>801891</v>
@@ -43782,7 +43782,7 @@
         <v>0.500999987125397</v>
       </c>
       <c r="G1497" t="n">
-        <v>0.384932965040207</v>
+        <v>0.384932935237885</v>
       </c>
       <c r="H1497" t="n">
         <v>610128</v>
@@ -43840,7 +43840,7 @@
         <v>0.497999995946884</v>
       </c>
       <c r="G1499" t="n">
-        <v>0.382627964019775</v>
+        <v>0.382627934217453</v>
       </c>
       <c r="H1499" t="n">
         <v>792105</v>
@@ -43898,7 +43898,7 @@
         <v>0.487500011920929</v>
       </c>
       <c r="G1501" t="n">
-        <v>0.374560534954071</v>
+        <v>0.374560475349426</v>
       </c>
       <c r="H1501" t="n">
         <v>949587</v>
@@ -43927,7 +43927,7 @@
         <v>0.479499995708466</v>
       </c>
       <c r="G1502" t="n">
-        <v>0.368413865566254</v>
+        <v>0.368413835763931</v>
       </c>
       <c r="H1502" t="n">
         <v>786661</v>
@@ -43956,7 +43956,7 @@
         <v>0.460500001907349</v>
       </c>
       <c r="G1503" t="n">
-        <v>0.353815615177155</v>
+        <v>0.353815644979477</v>
       </c>
       <c r="H1503" t="n">
         <v>1328680</v>
@@ -44043,7 +44043,7 @@
         <v>0.46399998664856</v>
       </c>
       <c r="G1506" t="n">
-        <v>0.356504738330841</v>
+        <v>0.356504708528519</v>
       </c>
       <c r="H1506" t="n">
         <v>433459</v>
@@ -44072,7 +44072,7 @@
         <v>0.456499993801117</v>
       </c>
       <c r="G1507" t="n">
-        <v>0.350742250680923</v>
+        <v>0.350742280483246</v>
       </c>
       <c r="H1507" t="n">
         <v>380730</v>
@@ -44101,7 +44101,7 @@
         <v>0.448500007390976</v>
       </c>
       <c r="G1508" t="n">
-        <v>0.344595670700073</v>
+        <v>0.344595640897751</v>
       </c>
       <c r="H1508" t="n">
         <v>904523</v>
@@ -44188,7 +44188,7 @@
         <v>0.445499986410141</v>
       </c>
       <c r="G1511" t="n">
-        <v>0.342290639877319</v>
+        <v>0.342290669679642</v>
       </c>
       <c r="H1511" t="n">
         <v>350971</v>
@@ -44275,7 +44275,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G1514" t="n">
-        <v>0.331918209791183</v>
+        <v>0.331918239593506</v>
       </c>
       <c r="H1514" t="n">
         <v>504577</v>
@@ -44391,7 +44391,7 @@
         <v>0.431499987840652</v>
       </c>
       <c r="G1518" t="n">
-        <v>0.331534028053284</v>
+        <v>0.331534057855606</v>
       </c>
       <c r="H1518" t="n">
         <v>184159</v>
@@ -44420,7 +44420,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G1519" t="n">
-        <v>0.319624960422516</v>
+        <v>0.319624990224838</v>
       </c>
       <c r="H1519" t="n">
         <v>859037</v>
@@ -44478,7 +44478,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G1521" t="n">
-        <v>0.336528211832047</v>
+        <v>0.336528182029724</v>
       </c>
       <c r="H1521" t="n">
         <v>916281</v>
@@ -44536,7 +44536,7 @@
         <v>0.442999988794327</v>
       </c>
       <c r="G1523" t="n">
-        <v>0.340369790792465</v>
+        <v>0.340369820594788</v>
       </c>
       <c r="H1523" t="n">
         <v>573684</v>
@@ -44565,7 +44565,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G1524" t="n">
-        <v>0.337296545505524</v>
+        <v>0.337296485900879</v>
       </c>
       <c r="H1524" t="n">
         <v>248550</v>
@@ -44623,7 +44623,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G1526" t="n">
-        <v>0.333454847335815</v>
+        <v>0.333454877138138</v>
       </c>
       <c r="H1526" t="n">
         <v>244426</v>
@@ -44652,7 +44652,7 @@
         <v>0.442999988794327</v>
       </c>
       <c r="G1527" t="n">
-        <v>0.340369790792465</v>
+        <v>0.340369820594788</v>
       </c>
       <c r="H1527" t="n">
         <v>241342</v>
@@ -44681,7 +44681,7 @@
         <v>0.45100000500679</v>
       </c>
       <c r="G1528" t="n">
-        <v>0.346516489982605</v>
+        <v>0.346516460180283</v>
       </c>
       <c r="H1528" t="n">
         <v>754275</v>
@@ -44768,7 +44768,7 @@
         <v>0.458000004291534</v>
       </c>
       <c r="G1531" t="n">
-        <v>0.351894795894623</v>
+        <v>0.3518947660923</v>
       </c>
       <c r="H1531" t="n">
         <v>446463</v>
@@ -44797,7 +44797,7 @@
         <v>0.448500007390976</v>
       </c>
       <c r="G1532" t="n">
-        <v>0.344595670700073</v>
+        <v>0.344595640897751</v>
       </c>
       <c r="H1532" t="n">
         <v>186297</v>
@@ -44855,7 +44855,7 @@
         <v>0.45100000500679</v>
       </c>
       <c r="G1534" t="n">
-        <v>0.346516489982605</v>
+        <v>0.346516460180283</v>
       </c>
       <c r="H1534" t="n">
         <v>164863</v>
@@ -44884,7 +44884,7 @@
         <v>0.455000013113022</v>
       </c>
       <c r="G1535" t="n">
-        <v>0.349589794874191</v>
+        <v>0.349589824676514</v>
       </c>
       <c r="H1535" t="n">
         <v>104368</v>
@@ -44942,7 +44942,7 @@
         <v>0.455000013113022</v>
       </c>
       <c r="G1537" t="n">
-        <v>0.349589794874191</v>
+        <v>0.349589824676514</v>
       </c>
       <c r="H1537" t="n">
         <v>125332</v>
@@ -45058,7 +45058,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G1541" t="n">
-        <v>0.336528211832047</v>
+        <v>0.336528182029724</v>
       </c>
       <c r="H1541" t="n">
         <v>691794</v>
@@ -45203,7 +45203,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G1546" t="n">
-        <v>0.330381572246552</v>
+        <v>0.330381602048874</v>
       </c>
       <c r="H1546" t="n">
         <v>292695</v>
@@ -45261,7 +45261,7 @@
         <v>0.421499997377396</v>
       </c>
       <c r="G1548" t="n">
-        <v>0.323850780725479</v>
+        <v>0.323850750923157</v>
       </c>
       <c r="H1548" t="n">
         <v>154520</v>
@@ -45290,7 +45290,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G1549" t="n">
-        <v>0.328844904899597</v>
+        <v>0.328844875097275</v>
       </c>
       <c r="H1549" t="n">
         <v>300970</v>
@@ -45348,7 +45348,7 @@
         <v>0.42399999499321</v>
       </c>
       <c r="G1551" t="n">
-        <v>0.325771570205688</v>
+        <v>0.325771600008011</v>
       </c>
       <c r="H1551" t="n">
         <v>194765</v>
@@ -45551,7 +45551,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G1558" t="n">
-        <v>0.327308267354965</v>
+        <v>0.327308237552643</v>
       </c>
       <c r="H1558" t="n">
         <v>411443</v>
@@ -45580,7 +45580,7 @@
         <v>0.42399999499321</v>
       </c>
       <c r="G1559" t="n">
-        <v>0.325771570205688</v>
+        <v>0.325771600008011</v>
       </c>
       <c r="H1559" t="n">
         <v>252017</v>
@@ -45609,7 +45609,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G1560" t="n">
-        <v>0.317319989204407</v>
+        <v>0.317319959402084</v>
       </c>
       <c r="H1560" t="n">
         <v>112376</v>
@@ -45638,7 +45638,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G1561" t="n">
-        <v>0.322698295116425</v>
+        <v>0.322698265314102</v>
       </c>
       <c r="H1561" t="n">
         <v>156375</v>
@@ -45725,7 +45725,7 @@
         <v>0.412000000476837</v>
       </c>
       <c r="G1564" t="n">
-        <v>0.31655165553093</v>
+        <v>0.316551625728607</v>
       </c>
       <c r="H1564" t="n">
         <v>245099</v>
@@ -45754,7 +45754,7 @@
         <v>0.391499996185303</v>
       </c>
       <c r="G1565" t="n">
-        <v>0.300800859928131</v>
+        <v>0.300800889730453</v>
       </c>
       <c r="H1565" t="n">
         <v>1304416</v>
@@ -45783,7 +45783,7 @@
         <v>0.400499999523163</v>
       </c>
       <c r="G1566" t="n">
-        <v>0.307715833187103</v>
+        <v>0.307715862989426</v>
       </c>
       <c r="H1566" t="n">
         <v>320979</v>
@@ -45870,7 +45870,7 @@
         <v>0.386000007390976</v>
       </c>
       <c r="G1569" t="n">
-        <v>0.296575129032135</v>
+        <v>0.29657506942749</v>
       </c>
       <c r="H1569" t="n">
         <v>676848</v>
@@ -45899,7 +45899,7 @@
         <v>0.386000007390976</v>
       </c>
       <c r="G1570" t="n">
-        <v>0.296575129032135</v>
+        <v>0.29657506942749</v>
       </c>
       <c r="H1570" t="n">
         <v>537771</v>
@@ -45957,7 +45957,7 @@
         <v>0.363999992609024</v>
       </c>
       <c r="G1572" t="n">
-        <v>0.279671788215637</v>
+        <v>0.279671847820282</v>
       </c>
       <c r="H1572" t="n">
         <v>1008226</v>
@@ -45986,7 +45986,7 @@
         <v>0.36599999666214</v>
       </c>
       <c r="G1573" t="n">
-        <v>0.281208485364914</v>
+        <v>0.281208515167236</v>
       </c>
       <c r="H1573" t="n">
         <v>809840</v>
@@ -46015,7 +46015,7 @@
         <v>0.372000008821487</v>
       </c>
       <c r="G1574" t="n">
-        <v>0.285818457603455</v>
+        <v>0.285818517208099</v>
       </c>
       <c r="H1574" t="n">
         <v>921065</v>
@@ -46044,7 +46044,7 @@
         <v>0.361000001430511</v>
       </c>
       <c r="G1575" t="n">
-        <v>0.277366816997528</v>
+        <v>0.27736684679985</v>
       </c>
       <c r="H1575" t="n">
         <v>332169</v>
@@ -46189,7 +46189,7 @@
         <v>0.380499988794327</v>
       </c>
       <c r="G1580" t="n">
-        <v>0.292349249124527</v>
+        <v>0.292349278926849</v>
       </c>
       <c r="H1580" t="n">
         <v>276719</v>
@@ -46247,7 +46247,7 @@
         <v>0.439500004053116</v>
       </c>
       <c r="G1582" t="n">
-        <v>0.337680697441101</v>
+        <v>0.337680727243423</v>
       </c>
       <c r="H1582" t="n">
         <v>1748458</v>
@@ -46276,7 +46276,7 @@
         <v>0.439500004053116</v>
       </c>
       <c r="G1583" t="n">
-        <v>0.337680697441101</v>
+        <v>0.337680727243423</v>
       </c>
       <c r="H1583" t="n">
         <v>669580</v>
@@ -46305,7 +46305,7 @@
         <v>0.453500002622604</v>
       </c>
       <c r="G1584" t="n">
-        <v>0.348437309265137</v>
+        <v>0.348437339067459</v>
       </c>
       <c r="H1584" t="n">
         <v>1662749</v>
@@ -46334,7 +46334,7 @@
         <v>0.458499997854233</v>
       </c>
       <c r="G1585" t="n">
-        <v>0.352278977632523</v>
+        <v>0.3522789478302</v>
       </c>
       <c r="H1585" t="n">
         <v>771138</v>
@@ -46566,7 +46566,7 @@
         <v>0.456999987363815</v>
       </c>
       <c r="G1593" t="n">
-        <v>0.351126462221146</v>
+        <v>0.351126432418823</v>
       </c>
       <c r="H1593" t="n">
         <v>962709</v>
@@ -46653,7 +46653,7 @@
         <v>0.460999995470047</v>
       </c>
       <c r="G1596" t="n">
-        <v>0.35419973731041</v>
+        <v>0.354199767112732</v>
       </c>
       <c r="H1596" t="n">
         <v>1082224</v>
@@ -46682,7 +46682,7 @@
         <v>0.461499989032745</v>
       </c>
       <c r="G1597" t="n">
-        <v>0.354583919048309</v>
+        <v>0.354583948850632</v>
       </c>
       <c r="H1597" t="n">
         <v>2019949</v>
@@ -46740,7 +46740,7 @@
         <v>0.465000003576279</v>
       </c>
       <c r="G1599" t="n">
-        <v>0.357273101806641</v>
+        <v>0.357273072004318</v>
       </c>
       <c r="H1599" t="n">
         <v>959895</v>
@@ -46798,7 +46798,7 @@
         <v>0.469999998807907</v>
       </c>
       <c r="G1601" t="n">
-        <v>0.361114710569382</v>
+        <v>0.361114770174026</v>
       </c>
       <c r="H1601" t="n">
         <v>563950</v>
@@ -46856,7 +46856,7 @@
         <v>0.467999994754791</v>
       </c>
       <c r="G1603" t="n">
-        <v>0.359578043222427</v>
+        <v>0.35957807302475</v>
       </c>
       <c r="H1603" t="n">
         <v>866153</v>
@@ -46885,7 +46885,7 @@
         <v>0.456999987363815</v>
       </c>
       <c r="G1604" t="n">
-        <v>0.351126462221146</v>
+        <v>0.351126432418823</v>
       </c>
       <c r="H1604" t="n">
         <v>590891</v>
@@ -46943,7 +46943,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G1606" t="n">
-        <v>0.336528211832047</v>
+        <v>0.336528182029724</v>
       </c>
       <c r="H1606" t="n">
         <v>297337</v>
@@ -47001,7 +47001,7 @@
         <v>0.431499987840652</v>
       </c>
       <c r="G1608" t="n">
-        <v>0.331534028053284</v>
+        <v>0.331534057855606</v>
       </c>
       <c r="H1608" t="n">
         <v>130349</v>
@@ -47030,7 +47030,7 @@
         <v>0.442999988794327</v>
       </c>
       <c r="G1609" t="n">
-        <v>0.340369790792465</v>
+        <v>0.340369820594788</v>
       </c>
       <c r="H1609" t="n">
         <v>325286</v>
@@ -47117,7 +47117,7 @@
         <v>0.442999988794327</v>
       </c>
       <c r="G1612" t="n">
-        <v>0.340369790792465</v>
+        <v>0.340369820594788</v>
       </c>
       <c r="H1612" t="n">
         <v>179870</v>
@@ -47146,7 +47146,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G1613" t="n">
-        <v>0.330381572246552</v>
+        <v>0.330381602048874</v>
       </c>
       <c r="H1613" t="n">
         <v>434003</v>
@@ -47175,7 +47175,7 @@
         <v>0.442999988794327</v>
       </c>
       <c r="G1614" t="n">
-        <v>0.340369790792465</v>
+        <v>0.340369820594788</v>
       </c>
       <c r="H1614" t="n">
         <v>890904</v>
@@ -47204,7 +47204,7 @@
         <v>0.42849999666214</v>
       </c>
       <c r="G1615" t="n">
-        <v>0.329229056835175</v>
+        <v>0.329229027032852</v>
       </c>
       <c r="H1615" t="n">
         <v>475212</v>
@@ -47233,7 +47233,7 @@
         <v>0.42849999666214</v>
       </c>
       <c r="G1616" t="n">
-        <v>0.329229056835175</v>
+        <v>0.329229027032852</v>
       </c>
       <c r="H1616" t="n">
         <v>206760</v>
@@ -47320,7 +47320,7 @@
         <v>0.448500007390976</v>
       </c>
       <c r="G1619" t="n">
-        <v>0.344595670700073</v>
+        <v>0.344595640897751</v>
       </c>
       <c r="H1619" t="n">
         <v>309388</v>
@@ -47349,7 +47349,7 @@
         <v>0.429500013589859</v>
       </c>
       <c r="G1620" t="n">
-        <v>0.353653103113174</v>
+        <v>0.353653132915497</v>
       </c>
       <c r="H1620" t="n">
         <v>196569</v>
@@ -47552,7 +47552,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G1627" t="n">
-        <v>0.342537134885788</v>
+        <v>0.34253716468811</v>
       </c>
       <c r="H1627" t="n">
         <v>91543</v>
@@ -47668,7 +47668,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G1631" t="n">
-        <v>0.353241413831711</v>
+        <v>0.353241384029388</v>
       </c>
       <c r="H1631" t="n">
         <v>113945</v>
@@ -47697,7 +47697,7 @@
         <v>0.430999994277954</v>
       </c>
       <c r="G1632" t="n">
-        <v>0.35488823056221</v>
+        <v>0.354888260364532</v>
       </c>
       <c r="H1632" t="n">
         <v>105648</v>
@@ -47726,7 +47726,7 @@
         <v>0.425500005483627</v>
       </c>
       <c r="G1633" t="n">
-        <v>0.350359529256821</v>
+        <v>0.350359499454498</v>
       </c>
       <c r="H1633" t="n">
         <v>125419</v>
@@ -47755,7 +47755,7 @@
         <v>0.418999999761581</v>
       </c>
       <c r="G1634" t="n">
-        <v>0.345007359981537</v>
+        <v>0.345007330179214</v>
       </c>
       <c r="H1634" t="n">
         <v>336810</v>
@@ -47784,7 +47784,7 @@
         <v>0.412499994039536</v>
       </c>
       <c r="G1635" t="n">
-        <v>0.339655190706253</v>
+        <v>0.339655220508575</v>
       </c>
       <c r="H1635" t="n">
         <v>160967</v>
@@ -47842,7 +47842,7 @@
         <v>0.416500002145767</v>
       </c>
       <c r="G1637" t="n">
-        <v>0.342948853969574</v>
+        <v>0.342948824167252</v>
       </c>
       <c r="H1637" t="n">
         <v>108212</v>
@@ -48132,7 +48132,7 @@
         <v>0.386500000953674</v>
       </c>
       <c r="G1647" t="n">
-        <v>0.31824666261673</v>
+        <v>0.318246632814407</v>
       </c>
       <c r="H1647" t="n">
         <v>131503</v>
@@ -48219,7 +48219,7 @@
         <v>0.388000011444092</v>
       </c>
       <c r="G1650" t="n">
-        <v>0.319481790065765</v>
+        <v>0.319481760263443</v>
       </c>
       <c r="H1650" t="n">
         <v>231717</v>
@@ -48306,7 +48306,7 @@
         <v>0.376500010490417</v>
       </c>
       <c r="G1653" t="n">
-        <v>0.310012608766556</v>
+        <v>0.310012578964233</v>
       </c>
       <c r="H1653" t="n">
         <v>128781</v>
@@ -48422,7 +48422,7 @@
         <v>0.386999994516373</v>
       </c>
       <c r="G1657" t="n">
-        <v>0.318658351898193</v>
+        <v>0.318658322095871</v>
       </c>
       <c r="H1657" t="n">
         <v>113908</v>
@@ -48451,7 +48451,7 @@
         <v>0.386999994516373</v>
       </c>
       <c r="G1658" t="n">
-        <v>0.318658351898193</v>
+        <v>0.318658322095871</v>
       </c>
       <c r="H1658" t="n">
         <v>265917</v>
@@ -48480,7 +48480,7 @@
         <v>0.388999998569489</v>
       </c>
       <c r="G1659" t="n">
-        <v>0.320305198431015</v>
+        <v>0.320305168628693</v>
       </c>
       <c r="H1659" t="n">
         <v>68331</v>
@@ -48509,7 +48509,7 @@
         <v>0.391999989748001</v>
       </c>
       <c r="G1660" t="n">
-        <v>0.322775363922119</v>
+        <v>0.322775393724442</v>
       </c>
       <c r="H1660" t="n">
         <v>62823</v>
@@ -48654,7 +48654,7 @@
         <v>0.389999985694885</v>
       </c>
       <c r="G1665" t="n">
-        <v>0.32112854719162</v>
+        <v>0.321128576993942</v>
       </c>
       <c r="H1665" t="n">
         <v>110148</v>
@@ -48683,7 +48683,7 @@
         <v>0.391000002622604</v>
       </c>
       <c r="G1666" t="n">
-        <v>0.32195195555687</v>
+        <v>0.321951985359192</v>
       </c>
       <c r="H1666" t="n">
         <v>154090</v>
@@ -48741,7 +48741,7 @@
         <v>0.397000014781952</v>
       </c>
       <c r="G1668" t="n">
-        <v>0.326892465353012</v>
+        <v>0.32689243555069</v>
       </c>
       <c r="H1668" t="n">
         <v>132809</v>
@@ -48799,7 +48799,7 @@
         <v>0.391999989748001</v>
       </c>
       <c r="G1670" t="n">
-        <v>0.322775363922119</v>
+        <v>0.322775393724442</v>
       </c>
       <c r="H1670" t="n">
         <v>37842</v>
@@ -48857,7 +48857,7 @@
         <v>0.388000011444092</v>
       </c>
       <c r="G1672" t="n">
-        <v>0.319481790065765</v>
+        <v>0.319481760263443</v>
       </c>
       <c r="H1672" t="n">
         <v>167980</v>
@@ -48944,7 +48944,7 @@
         <v>0.380499988794327</v>
       </c>
       <c r="G1675" t="n">
-        <v>0.31330618262291</v>
+        <v>0.313306212425232</v>
       </c>
       <c r="H1675" t="n">
         <v>176512</v>
@@ -49147,7 +49147,7 @@
         <v>0.376500010490417</v>
       </c>
       <c r="G1682" t="n">
-        <v>0.310012608766556</v>
+        <v>0.310012578964233</v>
       </c>
       <c r="H1682" t="n">
         <v>104564</v>
@@ -49176,7 +49176,7 @@
         <v>0.382499992847443</v>
       </c>
       <c r="G1683" t="n">
-        <v>0.314952999353409</v>
+        <v>0.314953029155731</v>
       </c>
       <c r="H1683" t="n">
         <v>298966</v>
@@ -49321,7 +49321,7 @@
         <v>0.389999985694885</v>
       </c>
       <c r="G1688" t="n">
-        <v>0.32112854719162</v>
+        <v>0.321128576993942</v>
       </c>
       <c r="H1688" t="n">
         <v>323084</v>
@@ -49379,7 +49379,7 @@
         <v>0.384999990463257</v>
       </c>
       <c r="G1690" t="n">
-        <v>0.317011505365372</v>
+        <v>0.317011535167694</v>
       </c>
       <c r="H1690" t="n">
         <v>45696</v>
@@ -49466,7 +49466,7 @@
         <v>0.378500014543533</v>
       </c>
       <c r="G1693" t="n">
-        <v>0.311659395694733</v>
+        <v>0.31165936589241</v>
       </c>
       <c r="H1693" t="n">
         <v>30654</v>
@@ -49640,7 +49640,7 @@
         <v>0.380499988794327</v>
       </c>
       <c r="G1699" t="n">
-        <v>0.31330618262291</v>
+        <v>0.313306212425232</v>
       </c>
       <c r="H1699" t="n">
         <v>164507</v>
@@ -49698,7 +49698,7 @@
         <v>0.386999994516373</v>
       </c>
       <c r="G1701" t="n">
-        <v>0.318658351898193</v>
+        <v>0.318658322095871</v>
       </c>
       <c r="H1701" t="n">
         <v>18198</v>
@@ -49814,7 +49814,7 @@
         <v>0.38850000500679</v>
       </c>
       <c r="G1705" t="n">
-        <v>0.319893449544907</v>
+        <v>0.319893479347229</v>
       </c>
       <c r="H1705" t="n">
         <v>21480</v>
@@ -49843,7 +49843,7 @@
         <v>0.386999994516373</v>
       </c>
       <c r="G1706" t="n">
-        <v>0.318658351898193</v>
+        <v>0.318658322095871</v>
       </c>
       <c r="H1706" t="n">
         <v>4137</v>
@@ -49901,7 +49901,7 @@
         <v>0.388000011444092</v>
       </c>
       <c r="G1708" t="n">
-        <v>0.319481790065765</v>
+        <v>0.319481760263443</v>
       </c>
       <c r="H1708" t="n">
         <v>21455</v>
@@ -49959,7 +49959,7 @@
         <v>0.370000004768372</v>
       </c>
       <c r="G1710" t="n">
-        <v>0.30466040968895</v>
+        <v>0.304660439491272</v>
       </c>
       <c r="H1710" t="n">
         <v>9493</v>
@@ -50075,7 +50075,7 @@
         <v>0.368000000715256</v>
       </c>
       <c r="G1714" t="n">
-        <v>0.303013622760773</v>
+        <v>0.30301359295845</v>
       </c>
       <c r="H1714" t="n">
         <v>43445</v>
@@ -50133,7 +50133,7 @@
         <v>0.376500010490417</v>
       </c>
       <c r="G1716" t="n">
-        <v>0.310012608766556</v>
+        <v>0.310012578964233</v>
       </c>
       <c r="H1716" t="n">
         <v>141283</v>
@@ -50191,7 +50191,7 @@
         <v>0.370000004768372</v>
       </c>
       <c r="G1718" t="n">
-        <v>0.30466040968895</v>
+        <v>0.304660439491272</v>
       </c>
       <c r="H1718" t="n">
         <v>16792</v>
@@ -50220,7 +50220,7 @@
         <v>0.370000004768372</v>
       </c>
       <c r="G1719" t="n">
-        <v>0.30466040968895</v>
+        <v>0.304660439491272</v>
       </c>
       <c r="H1719" t="n">
         <v>31041</v>
@@ -50394,7 +50394,7 @@
         <v>0.368999987840652</v>
       </c>
       <c r="G1725" t="n">
-        <v>0.3038370013237</v>
+        <v>0.303837031126022</v>
       </c>
       <c r="H1725" t="n">
         <v>60987</v>
@@ -50423,7 +50423,7 @@
         <v>0.370000004768372</v>
       </c>
       <c r="G1726" t="n">
-        <v>0.30466040968895</v>
+        <v>0.304660439491272</v>
       </c>
       <c r="H1726" t="n">
         <v>46500</v>
@@ -50452,7 +50452,7 @@
         <v>0.368999987840652</v>
       </c>
       <c r="G1727" t="n">
-        <v>0.3038370013237</v>
+        <v>0.303837031126022</v>
       </c>
       <c r="H1727" t="n">
         <v>31004</v>
@@ -50481,7 +50481,7 @@
         <v>0.368999987840652</v>
       </c>
       <c r="G1728" t="n">
-        <v>0.3038370013237</v>
+        <v>0.303837031126022</v>
       </c>
       <c r="H1728" t="n">
         <v>28531</v>
@@ -50510,7 +50510,7 @@
         <v>0.365500003099442</v>
       </c>
       <c r="G1729" t="n">
-        <v>0.30095511674881</v>
+        <v>0.300955086946487</v>
       </c>
       <c r="H1729" t="n">
         <v>135095</v>
@@ -50568,7 +50568,7 @@
         <v>0.367000013589859</v>
       </c>
       <c r="G1731" t="n">
-        <v>0.302190244197845</v>
+        <v>0.302190214395523</v>
       </c>
       <c r="H1731" t="n">
         <v>67421</v>
@@ -50597,7 +50597,7 @@
         <v>0.370000004768372</v>
       </c>
       <c r="G1732" t="n">
-        <v>0.30466040968895</v>
+        <v>0.304660439491272</v>
       </c>
       <c r="H1732" t="n">
         <v>108643</v>
@@ -50626,7 +50626,7 @@
         <v>0.370000004768372</v>
       </c>
       <c r="G1733" t="n">
-        <v>0.30466040968895</v>
+        <v>0.304660439491272</v>
       </c>
       <c r="H1733" t="n">
         <v>36954</v>
@@ -50655,7 +50655,7 @@
         <v>0.368000000715256</v>
       </c>
       <c r="G1734" t="n">
-        <v>0.303013622760773</v>
+        <v>0.30301359295845</v>
       </c>
       <c r="H1734" t="n">
         <v>50671</v>
@@ -50771,7 +50771,7 @@
         <v>0.388000011444092</v>
       </c>
       <c r="G1738" t="n">
-        <v>0.319481790065765</v>
+        <v>0.319481760263443</v>
       </c>
       <c r="H1738" t="n">
         <v>459268</v>
@@ -50800,7 +50800,7 @@
         <v>0.397000014781952</v>
       </c>
       <c r="G1739" t="n">
-        <v>0.326892465353012</v>
+        <v>0.32689243555069</v>
       </c>
       <c r="H1739" t="n">
         <v>165854</v>
@@ -50829,7 +50829,7 @@
         <v>0.396499991416931</v>
       </c>
       <c r="G1740" t="n">
-        <v>0.326480716466904</v>
+        <v>0.326480686664581</v>
       </c>
       <c r="H1740" t="n">
         <v>178803</v>
@@ -50858,7 +50858,7 @@
         <v>0.396499991416931</v>
       </c>
       <c r="G1741" t="n">
-        <v>0.326480716466904</v>
+        <v>0.326480686664581</v>
       </c>
       <c r="H1741" t="n">
         <v>86528</v>
@@ -51177,7 +51177,7 @@
         <v>0.412000000476837</v>
       </c>
       <c r="G1752" t="n">
-        <v>0.339243531227112</v>
+        <v>0.339243501424789</v>
       </c>
       <c r="H1752" t="n">
         <v>169638</v>
@@ -51206,7 +51206,7 @@
         <v>0.407000005245209</v>
       </c>
       <c r="G1753" t="n">
-        <v>0.335126489400864</v>
+        <v>0.335126459598541</v>
       </c>
       <c r="H1753" t="n">
         <v>247806</v>
@@ -51264,7 +51264,7 @@
         <v>0.435000002384186</v>
       </c>
       <c r="G1755" t="n">
-        <v>0.358181834220886</v>
+        <v>0.358181864023209</v>
       </c>
       <c r="H1755" t="n">
         <v>635657</v>
@@ -51293,7 +51293,7 @@
         <v>0.421499997377396</v>
       </c>
       <c r="G1756" t="n">
-        <v>0.347065836191177</v>
+        <v>0.3470658659935</v>
       </c>
       <c r="H1756" t="n">
         <v>402152</v>
@@ -51409,7 +51409,7 @@
         <v>0.41949999332428</v>
       </c>
       <c r="G1760" t="n">
-        <v>0.345419049263</v>
+        <v>0.345419079065323</v>
       </c>
       <c r="H1760" t="n">
         <v>13236</v>
@@ -51467,7 +51467,7 @@
         <v>0.42399999499321</v>
       </c>
       <c r="G1762" t="n">
-        <v>0.349124372005463</v>
+        <v>0.349124401807785</v>
       </c>
       <c r="H1762" t="n">
         <v>73301</v>
@@ -51496,7 +51496,7 @@
         <v>0.416500002145767</v>
       </c>
       <c r="G1763" t="n">
-        <v>0.342948853969574</v>
+        <v>0.342948824167252</v>
       </c>
       <c r="H1763" t="n">
         <v>285113</v>
@@ -51641,7 +51641,7 @@
         <v>0.417499989271164</v>
       </c>
       <c r="G1768" t="n">
-        <v>0.343772262334824</v>
+        <v>0.343772232532501</v>
       </c>
       <c r="H1768" t="n">
         <v>46000</v>
@@ -51670,7 +51670,7 @@
         <v>0.412000000476837</v>
       </c>
       <c r="G1769" t="n">
-        <v>0.339243531227112</v>
+        <v>0.339243501424789</v>
       </c>
       <c r="H1769" t="n">
         <v>145286</v>
@@ -51699,7 +51699,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G1770" t="n">
-        <v>0.337596714496613</v>
+        <v>0.337596744298935</v>
       </c>
       <c r="H1770" t="n">
         <v>45232</v>
@@ -51728,7 +51728,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G1771" t="n">
-        <v>0.340066909790039</v>
+        <v>0.340066879987717</v>
       </c>
       <c r="H1771" t="n">
         <v>103953</v>
@@ -51786,7 +51786,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G1773" t="n">
-        <v>0.340066909790039</v>
+        <v>0.340066879987717</v>
       </c>
       <c r="H1773" t="n">
         <v>43489</v>
@@ -51815,7 +51815,7 @@
         <v>0.413500010967255</v>
       </c>
       <c r="G1774" t="n">
-        <v>0.340478599071503</v>
+        <v>0.340478628873825</v>
       </c>
       <c r="H1774" t="n">
         <v>22902</v>
@@ -51873,7 +51873,7 @@
         <v>0.412499994039536</v>
       </c>
       <c r="G1776" t="n">
-        <v>0.339655190706253</v>
+        <v>0.339655220508575</v>
       </c>
       <c r="H1776" t="n">
         <v>33908</v>
@@ -51931,7 +51931,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G1778" t="n">
-        <v>0.329362601041794</v>
+        <v>0.329362630844116</v>
       </c>
       <c r="H1778" t="n">
         <v>208738</v>
@@ -51960,7 +51960,7 @@
         <v>0.397000014781952</v>
       </c>
       <c r="G1779" t="n">
-        <v>0.326892465353012</v>
+        <v>0.32689243555069</v>
       </c>
       <c r="H1779" t="n">
         <v>80120</v>
@@ -52018,7 +52018,7 @@
         <v>0.396499991416931</v>
       </c>
       <c r="G1781" t="n">
-        <v>0.326480716466904</v>
+        <v>0.326480686664581</v>
       </c>
       <c r="H1781" t="n">
         <v>99045</v>
@@ -52047,7 +52047,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G1782" t="n">
-        <v>0.337596714496613</v>
+        <v>0.337596744298935</v>
       </c>
       <c r="H1782" t="n">
         <v>184668</v>
@@ -52076,7 +52076,7 @@
         <v>0.407000005245209</v>
       </c>
       <c r="G1783" t="n">
-        <v>0.335126489400864</v>
+        <v>0.335126459598541</v>
       </c>
       <c r="H1783" t="n">
         <v>98882</v>
@@ -52105,7 +52105,7 @@
         <v>0.41100001335144</v>
       </c>
       <c r="G1784" t="n">
-        <v>0.338420122861862</v>
+        <v>0.338420152664185</v>
       </c>
       <c r="H1784" t="n">
         <v>35800</v>
@@ -52134,7 +52134,7 @@
         <v>0.417499989271164</v>
       </c>
       <c r="G1785" t="n">
-        <v>0.343772262334824</v>
+        <v>0.343772232532501</v>
       </c>
       <c r="H1785" t="n">
         <v>101540</v>
@@ -52192,7 +52192,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G1787" t="n">
-        <v>0.337596714496613</v>
+        <v>0.337596744298935</v>
       </c>
       <c r="H1787" t="n">
         <v>62033</v>
@@ -52250,7 +52250,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G1789" t="n">
-        <v>0.337596714496613</v>
+        <v>0.337596744298935</v>
       </c>
       <c r="H1789" t="n">
         <v>141906</v>
@@ -52308,7 +52308,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G1791" t="n">
-        <v>0.337596714496613</v>
+        <v>0.337596744298935</v>
       </c>
       <c r="H1791" t="n">
         <v>181885</v>
@@ -52424,7 +52424,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G1795" t="n">
-        <v>0.35571163892746</v>
+        <v>0.355711668729782</v>
       </c>
       <c r="H1795" t="n">
         <v>603588</v>
@@ -52511,7 +52511,7 @@
         <v>0.458999991416931</v>
       </c>
       <c r="G1798" t="n">
-        <v>0.377943605184555</v>
+        <v>0.377943575382233</v>
       </c>
       <c r="H1798" t="n">
         <v>1277152</v>
@@ -52627,7 +52627,7 @@
         <v>0.485500007867813</v>
       </c>
       <c r="G1802" t="n">
-        <v>0.399763882160187</v>
+        <v>0.399763911962509</v>
       </c>
       <c r="H1802" t="n">
         <v>765228</v>
@@ -52656,7 +52656,7 @@
         <v>0.47299998998642</v>
       </c>
       <c r="G1803" t="n">
-        <v>0.389471262693405</v>
+        <v>0.389471292495728</v>
       </c>
       <c r="H1803" t="n">
         <v>583366</v>
@@ -52772,7 +52772,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1807" t="n">
-        <v>0.403469234704971</v>
+        <v>0.403469204902649</v>
       </c>
       <c r="H1807" t="n">
         <v>462039</v>
@@ -52801,7 +52801,7 @@
         <v>0.497500002384186</v>
       </c>
       <c r="G1808" t="n">
-        <v>0.409644812345505</v>
+        <v>0.409644782543182</v>
       </c>
       <c r="H1808" t="n">
         <v>393036</v>
@@ -52917,7 +52917,7 @@
         <v>0.493499994277954</v>
       </c>
       <c r="G1812" t="n">
-        <v>0.406351119279861</v>
+        <v>0.406351149082184</v>
       </c>
       <c r="H1812" t="n">
         <v>703306</v>
@@ -53120,7 +53120,7 @@
         <v>0.489499986171722</v>
       </c>
       <c r="G1819" t="n">
-        <v>0.403057545423508</v>
+        <v>0.403057515621185</v>
       </c>
       <c r="H1819" t="n">
         <v>659519</v>
@@ -53207,7 +53207,7 @@
         <v>0.507000029087067</v>
       </c>
       <c r="G1822" t="n">
-        <v>0.417467147111893</v>
+        <v>0.417467176914215</v>
       </c>
       <c r="H1822" t="n">
         <v>578557</v>
@@ -53236,7 +53236,7 @@
         <v>0.526000022888184</v>
       </c>
       <c r="G1823" t="n">
-        <v>0.433111876249313</v>
+        <v>0.433111846446991</v>
       </c>
       <c r="H1823" t="n">
         <v>2252434</v>
@@ -53294,7 +53294,7 @@
         <v>0.53600001335144</v>
       </c>
       <c r="G1825" t="n">
-        <v>0.441345989704132</v>
+        <v>0.441345930099487</v>
       </c>
       <c r="H1825" t="n">
         <v>958900</v>
@@ -53323,7 +53323,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G1826" t="n">
-        <v>0.454520463943481</v>
+        <v>0.454520434141159</v>
       </c>
       <c r="H1826" t="n">
         <v>1717611</v>
@@ -53352,7 +53352,7 @@
         <v>0.537999987602234</v>
       </c>
       <c r="G1827" t="n">
-        <v>0.442992717027664</v>
+        <v>0.442992746829987</v>
       </c>
       <c r="H1827" t="n">
         <v>2556404</v>
@@ -53410,7 +53410,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1829" t="n">
-        <v>0.503924906253815</v>
+        <v>0.50392484664917</v>
       </c>
       <c r="H1829" t="n">
         <v>3952439</v>
@@ -53439,7 +53439,7 @@
         <v>0.648999989032745</v>
       </c>
       <c r="G1830" t="n">
-        <v>0.534390866756439</v>
+        <v>0.534390807151794</v>
       </c>
       <c r="H1830" t="n">
         <v>2319403</v>
@@ -53468,7 +53468,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1831" t="n">
-        <v>0.518746197223663</v>
+        <v>0.518746137619019</v>
       </c>
       <c r="H1831" t="n">
         <v>1905714</v>
@@ -53497,7 +53497,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1832" t="n">
-        <v>0.522039771080017</v>
+        <v>0.522039711475372</v>
       </c>
       <c r="H1832" t="n">
         <v>2768663</v>
@@ -53555,7 +53555,7 @@
         <v>0.629000008106232</v>
       </c>
       <c r="G1834" t="n">
-        <v>0.517922818660736</v>
+        <v>0.517922759056091</v>
       </c>
       <c r="H1834" t="n">
         <v>1909845</v>
@@ -53613,7 +53613,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1836" t="n">
-        <v>0.485809803009033</v>
+        <v>0.485809862613678</v>
       </c>
       <c r="H1836" t="n">
         <v>776833</v>
@@ -53671,7 +53671,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G1838" t="n">
-        <v>0.472635358572006</v>
+        <v>0.472635388374329</v>
       </c>
       <c r="H1838" t="n">
         <v>621808</v>
@@ -53729,7 +53729,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G1840" t="n">
-        <v>0.472635358572006</v>
+        <v>0.472635388374329</v>
       </c>
       <c r="H1840" t="n">
         <v>658443</v>
@@ -53787,7 +53787,7 @@
         <v>0.597000002861023</v>
       </c>
       <c r="G1842" t="n">
-        <v>0.491573810577393</v>
+        <v>0.491573750972748</v>
       </c>
       <c r="H1842" t="n">
         <v>825059</v>
@@ -53845,7 +53845,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G1844" t="n">
-        <v>0.467694997787476</v>
+        <v>0.467694967985153</v>
       </c>
       <c r="H1844" t="n">
         <v>469256</v>
@@ -53874,7 +53874,7 @@
         <v>0.558000028133392</v>
       </c>
       <c r="G1845" t="n">
-        <v>0.459460914134979</v>
+        <v>0.459460943937302</v>
       </c>
       <c r="H1845" t="n">
         <v>649329</v>
@@ -53903,7 +53903,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G1846" t="n">
-        <v>0.461107671260834</v>
+        <v>0.461107701063156</v>
       </c>
       <c r="H1846" t="n">
         <v>1119647</v>
@@ -54077,7 +54077,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1852" t="n">
-        <v>0.485809803009033</v>
+        <v>0.485809862613678</v>
       </c>
       <c r="H1852" t="n">
         <v>247487</v>
@@ -54106,7 +54106,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G1853" t="n">
-        <v>0.51545250415802</v>
+        <v>0.515452563762665</v>
       </c>
       <c r="H1853" t="n">
         <v>4291460</v>
@@ -54135,7 +54135,7 @@
         <v>0.612999975681305</v>
       </c>
       <c r="G1854" t="n">
-        <v>0.504748284816742</v>
+        <v>0.504748225212097</v>
       </c>
       <c r="H1854" t="n">
         <v>1642805</v>
@@ -54193,7 +54193,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G1856" t="n">
-        <v>0.498984336853027</v>
+        <v>0.498984396457672</v>
       </c>
       <c r="H1856" t="n">
         <v>384828</v>
@@ -54222,7 +54222,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1857" t="n">
-        <v>0.494043976068497</v>
+        <v>0.494044005870819</v>
       </c>
       <c r="H1857" t="n">
         <v>544168</v>
@@ -54251,7 +54251,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1858" t="n">
-        <v>0.505571722984314</v>
+        <v>0.505571663379669</v>
       </c>
       <c r="H1858" t="n">
         <v>1192967</v>
@@ -54309,7 +54309,7 @@
         <v>0.58899998664856</v>
       </c>
       <c r="G1860" t="n">
-        <v>0.484986484050751</v>
+        <v>0.484986424446106</v>
       </c>
       <c r="H1860" t="n">
         <v>185167</v>
@@ -54338,7 +54338,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1861" t="n">
-        <v>0.492397129535675</v>
+        <v>0.49239718914032</v>
       </c>
       <c r="H1861" t="n">
         <v>266686</v>
@@ -54367,7 +54367,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1862" t="n">
-        <v>0.482516258955002</v>
+        <v>0.482516318559647</v>
       </c>
       <c r="H1862" t="n">
         <v>414253</v>
@@ -54425,7 +54425,7 @@
         <v>0.58899998664856</v>
       </c>
       <c r="G1864" t="n">
-        <v>0.484986484050751</v>
+        <v>0.484986424446106</v>
       </c>
       <c r="H1864" t="n">
         <v>517823</v>
@@ -54483,7 +54483,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1866" t="n">
-        <v>0.473458766937256</v>
+        <v>0.473458737134933</v>
       </c>
       <c r="H1866" t="n">
         <v>569396</v>
@@ -54512,7 +54512,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G1867" t="n">
-        <v>0.467694997787476</v>
+        <v>0.467694967985153</v>
       </c>
       <c r="H1867" t="n">
         <v>297865</v>
@@ -54541,7 +54541,7 @@
         <v>0.572000026702881</v>
       </c>
       <c r="G1868" t="n">
-        <v>0.470988631248474</v>
+        <v>0.470988571643829</v>
       </c>
       <c r="H1868" t="n">
         <v>352772</v>
@@ -54628,7 +54628,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1871" t="n">
-        <v>0.485809803009033</v>
+        <v>0.485809862613678</v>
       </c>
       <c r="H1871" t="n">
         <v>257011</v>
@@ -54657,7 +54657,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1872" t="n">
-        <v>0.492397129535675</v>
+        <v>0.49239718914032</v>
       </c>
       <c r="H1872" t="n">
         <v>481519</v>
@@ -54686,7 +54686,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G1873" t="n">
-        <v>0.472635358572006</v>
+        <v>0.472635388374329</v>
       </c>
       <c r="H1873" t="n">
         <v>520317</v>
@@ -54773,7 +54773,7 @@
         <v>0.558000028133392</v>
       </c>
       <c r="G1876" t="n">
-        <v>0.459460914134979</v>
+        <v>0.459460943937302</v>
       </c>
       <c r="H1876" t="n">
         <v>647895</v>
@@ -54831,7 +54831,7 @@
         <v>0.559000015258789</v>
       </c>
       <c r="G1878" t="n">
-        <v>0.460284292697906</v>
+        <v>0.460284322500229</v>
       </c>
       <c r="H1878" t="n">
         <v>362615</v>
@@ -54860,7 +54860,7 @@
         <v>0.569000005722046</v>
       </c>
       <c r="G1879" t="n">
-        <v>0.46851834654808</v>
+        <v>0.468518376350403</v>
       </c>
       <c r="H1879" t="n">
         <v>457357</v>
@@ -54918,7 +54918,7 @@
         <v>0.53600001335144</v>
       </c>
       <c r="G1881" t="n">
-        <v>0.473822325468063</v>
+        <v>0.473822295665741</v>
       </c>
       <c r="H1881" t="n">
         <v>243623</v>
@@ -54976,7 +54976,7 @@
         <v>0.522000014781952</v>
       </c>
       <c r="G1883" t="n">
-        <v>0.46144637465477</v>
+        <v>0.461446404457092</v>
       </c>
       <c r="H1883" t="n">
         <v>177479</v>
@@ -55005,7 +55005,7 @@
         <v>0.524999976158142</v>
       </c>
       <c r="G1884" t="n">
-        <v>0.464098364114761</v>
+        <v>0.464098334312439</v>
       </c>
       <c r="H1884" t="n">
         <v>252895</v>
@@ -55034,7 +55034,7 @@
         <v>0.513999998569489</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.454374402761459</v>
+        <v>0.454374372959137</v>
       </c>
       <c r="H1885" t="n">
         <v>113498</v>
@@ -55150,7 +55150,7 @@
         <v>0.495999991893768</v>
       </c>
       <c r="G1889" t="n">
-        <v>0.438462466001511</v>
+        <v>0.438462436199188</v>
       </c>
       <c r="H1889" t="n">
         <v>104085</v>
@@ -55179,7 +55179,7 @@
         <v>0.483500003814697</v>
       </c>
       <c r="G1890" t="n">
-        <v>0.427412509918213</v>
+        <v>0.427412480115891</v>
       </c>
       <c r="H1890" t="n">
         <v>976486</v>
@@ -55237,7 +55237,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1892" t="n">
-        <v>0.433158457279205</v>
+        <v>0.433158487081528</v>
       </c>
       <c r="H1892" t="n">
         <v>288125</v>
@@ -55324,7 +55324,7 @@
         <v>0.491499990224838</v>
       </c>
       <c r="G1895" t="n">
-        <v>0.434484452009201</v>
+        <v>0.434484422206879</v>
       </c>
       <c r="H1895" t="n">
         <v>147500</v>
@@ -55440,7 +55440,7 @@
         <v>0.490500003099442</v>
       </c>
       <c r="G1899" t="n">
-        <v>0.43360048532486</v>
+        <v>0.433600455522537</v>
       </c>
       <c r="H1899" t="n">
         <v>283093</v>
@@ -55469,7 +55469,7 @@
         <v>0.487500011920929</v>
       </c>
       <c r="G1900" t="n">
-        <v>0.430948466062546</v>
+        <v>0.430948495864868</v>
       </c>
       <c r="H1900" t="n">
         <v>211964</v>
@@ -55498,7 +55498,7 @@
         <v>0.488000005483627</v>
       </c>
       <c r="G1901" t="n">
-        <v>0.4313904941082</v>
+        <v>0.431390464305878</v>
       </c>
       <c r="H1901" t="n">
         <v>156473</v>
@@ -55614,7 +55614,7 @@
         <v>0.483500003814697</v>
       </c>
       <c r="G1905" t="n">
-        <v>0.427412509918213</v>
+        <v>0.427412480115891</v>
       </c>
       <c r="H1905" t="n">
         <v>220842</v>
@@ -55643,7 +55643,7 @@
         <v>0.485000014305115</v>
       </c>
       <c r="G1906" t="n">
-        <v>0.428738474845886</v>
+        <v>0.428738504648209</v>
       </c>
       <c r="H1906" t="n">
         <v>742245</v>
@@ -55672,7 +55672,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1907" t="n">
-        <v>0.424318492412567</v>
+        <v>0.424318462610245</v>
       </c>
       <c r="H1907" t="n">
         <v>408236</v>
@@ -55701,7 +55701,7 @@
         <v>0.487500011920929</v>
       </c>
       <c r="G1908" t="n">
-        <v>0.430948466062546</v>
+        <v>0.430948495864868</v>
       </c>
       <c r="H1908" t="n">
         <v>150213</v>
@@ -55730,7 +55730,7 @@
         <v>0.49099999666214</v>
       </c>
       <c r="G1909" t="n">
-        <v>0.434042453765869</v>
+        <v>0.434042483568192</v>
       </c>
       <c r="H1909" t="n">
         <v>166903</v>
@@ -55759,7 +55759,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1910" t="n">
-        <v>0.433158457279205</v>
+        <v>0.433158487081528</v>
       </c>
       <c r="H1910" t="n">
         <v>148041</v>
@@ -55846,7 +55846,7 @@
         <v>0.486999988555908</v>
       </c>
       <c r="G1913" t="n">
-        <v>0.430506467819214</v>
+        <v>0.430506438016891</v>
       </c>
       <c r="H1913" t="n">
         <v>479123</v>
@@ -56049,7 +56049,7 @@
         <v>0.46849998831749</v>
       </c>
       <c r="G1920" t="n">
-        <v>0.414152503013611</v>
+        <v>0.414152532815933</v>
       </c>
       <c r="H1920" t="n">
         <v>241945</v>
@@ -56078,7 +56078,7 @@
         <v>0.47299998998642</v>
       </c>
       <c r="G1921" t="n">
-        <v>0.41813051700592</v>
+        <v>0.418130487203598</v>
       </c>
       <c r="H1921" t="n">
         <v>374428</v>
@@ -56107,7 +56107,7 @@
         <v>0.477999985218048</v>
       </c>
       <c r="G1922" t="n">
-        <v>0.422550469636917</v>
+        <v>0.42255049943924</v>
       </c>
       <c r="H1922" t="n">
         <v>225782</v>
@@ -56165,7 +56165,7 @@
         <v>0.477999985218048</v>
       </c>
       <c r="G1924" t="n">
-        <v>0.422550469636917</v>
+        <v>0.42255049943924</v>
       </c>
       <c r="H1924" t="n">
         <v>304823</v>
@@ -56194,7 +56194,7 @@
         <v>0.481000006198883</v>
       </c>
       <c r="G1925" t="n">
-        <v>0.425202488899231</v>
+        <v>0.425202518701553</v>
       </c>
       <c r="H1925" t="n">
         <v>320604</v>
@@ -56281,7 +56281,7 @@
         <v>0.478500008583069</v>
       </c>
       <c r="G1928" t="n">
-        <v>0.422992527484894</v>
+        <v>0.422992497682571</v>
       </c>
       <c r="H1928" t="n">
         <v>476836</v>
@@ -56339,7 +56339,7 @@
         <v>0.481000006198883</v>
       </c>
       <c r="G1930" t="n">
-        <v>0.425202488899231</v>
+        <v>0.425202518701553</v>
       </c>
       <c r="H1930" t="n">
         <v>240437</v>
@@ -56368,7 +56368,7 @@
         <v>0.47299998998642</v>
       </c>
       <c r="G1931" t="n">
-        <v>0.41813051700592</v>
+        <v>0.418130487203598</v>
       </c>
       <c r="H1931" t="n">
         <v>270522</v>
@@ -56455,7 +56455,7 @@
         <v>0.470499992370605</v>
       </c>
       <c r="G1934" t="n">
-        <v>0.415920525789261</v>
+        <v>0.415920495986938</v>
       </c>
       <c r="H1934" t="n">
         <v>102300</v>
@@ -56484,7 +56484,7 @@
         <v>0.46849998831749</v>
       </c>
       <c r="G1935" t="n">
-        <v>0.414152503013611</v>
+        <v>0.414152532815933</v>
       </c>
       <c r="H1935" t="n">
         <v>87538</v>
@@ -56600,7 +56600,7 @@
         <v>0.465000003576279</v>
       </c>
       <c r="G1939" t="n">
-        <v>0.411058515310287</v>
+        <v>0.41105854511261</v>
       </c>
       <c r="H1939" t="n">
         <v>52043</v>
@@ -56629,7 +56629,7 @@
         <v>0.463499993085861</v>
       </c>
       <c r="G1940" t="n">
-        <v>0.409732580184937</v>
+        <v>0.409732550382614</v>
       </c>
       <c r="H1940" t="n">
         <v>67758</v>
@@ -56716,7 +56716,7 @@
         <v>0.461499989032745</v>
       </c>
       <c r="G1943" t="n">
-        <v>0.407964527606964</v>
+        <v>0.407964557409286</v>
       </c>
       <c r="H1943" t="n">
         <v>209838</v>
@@ -56803,7 +56803,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1946" t="n">
-        <v>0.424318492412567</v>
+        <v>0.424318462610245</v>
       </c>
       <c r="H1946" t="n">
         <v>502893</v>
@@ -56832,7 +56832,7 @@
         <v>0.475499987602234</v>
       </c>
       <c r="G1947" t="n">
-        <v>0.42034050822258</v>
+        <v>0.420340478420258</v>
       </c>
       <c r="H1947" t="n">
         <v>192878</v>
@@ -56890,7 +56890,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1949" t="n">
-        <v>0.424318492412567</v>
+        <v>0.424318462610245</v>
       </c>
       <c r="H1949" t="n">
         <v>179559</v>
@@ -56948,7 +56948,7 @@
         <v>0.48199999332428</v>
       </c>
       <c r="G1951" t="n">
-        <v>0.426086485385895</v>
+        <v>0.426086455583572</v>
       </c>
       <c r="H1951" t="n">
         <v>207593</v>
@@ -56977,7 +56977,7 @@
         <v>0.487500011920929</v>
       </c>
       <c r="G1952" t="n">
-        <v>0.430948466062546</v>
+        <v>0.430948495864868</v>
       </c>
       <c r="H1952" t="n">
         <v>136281</v>
@@ -57006,7 +57006,7 @@
         <v>0.484499990940094</v>
       </c>
       <c r="G1953" t="n">
-        <v>0.428296446800232</v>
+        <v>0.428296476602554</v>
       </c>
       <c r="H1953" t="n">
         <v>166626</v>
@@ -57064,7 +57064,7 @@
         <v>0.49099999666214</v>
       </c>
       <c r="G1955" t="n">
-        <v>0.434042453765869</v>
+        <v>0.434042483568192</v>
       </c>
       <c r="H1955" t="n">
         <v>454310</v>
@@ -57151,7 +57151,7 @@
         <v>0.488000005483627</v>
       </c>
       <c r="G1958" t="n">
-        <v>0.4313904941082</v>
+        <v>0.431390464305878</v>
       </c>
       <c r="H1958" t="n">
         <v>525343</v>
@@ -57615,7 +57615,7 @@
         <v>0.456499993801117</v>
       </c>
       <c r="G1974" t="n">
-        <v>0.403544545173645</v>
+        <v>0.403544574975967</v>
       </c>
       <c r="H1974" t="n">
         <v>122727</v>
@@ -57644,7 +57644,7 @@
         <v>0.453000009059906</v>
       </c>
       <c r="G1975" t="n">
-        <v>0.400450557470322</v>
+        <v>0.400450587272644</v>
       </c>
       <c r="H1975" t="n">
         <v>201252</v>
@@ -57760,7 +57760,7 @@
         <v>0.4375</v>
       </c>
       <c r="G1979" t="n">
-        <v>0.386748611927032</v>
+        <v>0.386748641729355</v>
       </c>
       <c r="H1979" t="n">
         <v>106812</v>
@@ -57789,7 +57789,7 @@
         <v>0.444999992847443</v>
       </c>
       <c r="G1980" t="n">
-        <v>0.393378615379333</v>
+        <v>0.393378585577011</v>
       </c>
       <c r="H1980" t="n">
         <v>124352</v>
@@ -57934,7 +57934,7 @@
         <v>0.465000003576279</v>
       </c>
       <c r="G1985" t="n">
-        <v>0.411058515310287</v>
+        <v>0.41105854511261</v>
       </c>
       <c r="H1985" t="n">
         <v>314622</v>
@@ -58079,7 +58079,7 @@
         <v>0.454499989748001</v>
       </c>
       <c r="G1990" t="n">
-        <v>0.40177658200264</v>
+        <v>0.401776552200317</v>
       </c>
       <c r="H1990" t="n">
         <v>1014445</v>
@@ -58369,7 +58369,7 @@
         <v>0.45550000667572</v>
       </c>
       <c r="G2000" t="n">
-        <v>0.402660548686981</v>
+        <v>0.402660578489304</v>
       </c>
       <c r="H2000" t="n">
         <v>132836</v>
@@ -58485,7 +58485,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G2004" t="n">
-        <v>0.424318492412567</v>
+        <v>0.424318462610245</v>
       </c>
       <c r="H2004" t="n">
         <v>395506</v>
@@ -58514,7 +58514,7 @@
         <v>0.488000005483627</v>
       </c>
       <c r="G2005" t="n">
-        <v>0.4313904941082</v>
+        <v>0.431390464305878</v>
       </c>
       <c r="H2005" t="n">
         <v>289841</v>
@@ -58572,7 +58572,7 @@
         <v>0.493999987840652</v>
       </c>
       <c r="G2007" t="n">
-        <v>0.436694443225861</v>
+        <v>0.436694413423538</v>
       </c>
       <c r="H2007" t="n">
         <v>546745</v>
@@ -58601,7 +58601,7 @@
         <v>0.501999974250793</v>
       </c>
       <c r="G2008" t="n">
-        <v>0.443766385316849</v>
+        <v>0.443766415119171</v>
       </c>
       <c r="H2008" t="n">
         <v>741113</v>
@@ -79951,6 +79951,64 @@
         <v>71782</v>
       </c>
       <c r="I2744" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2745">
+      <c r="A2745" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2745" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C2745" t="n">
+        <v>0.519999980926514</v>
+      </c>
+      <c r="D2745" t="n">
+        <v>0.529999971389771</v>
+      </c>
+      <c r="E2745" t="n">
+        <v>0.51800000667572</v>
+      </c>
+      <c r="F2745" t="n">
+        <v>0.51800000667572</v>
+      </c>
+      <c r="G2745" t="n">
+        <v>0.51800000667572</v>
+      </c>
+      <c r="H2745" t="n">
+        <v>123832</v>
+      </c>
+      <c r="I2745" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2746">
+      <c r="A2746" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2746" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2746" t="n">
+        <v>0.51800000667572</v>
+      </c>
+      <c r="D2746" t="n">
+        <v>0.521000027656555</v>
+      </c>
+      <c r="E2746" t="n">
+        <v>0.513999998569489</v>
+      </c>
+      <c r="F2746" t="n">
+        <v>0.517000019550323</v>
+      </c>
+      <c r="G2746" t="n">
+        <v>0.517000019550323</v>
+      </c>
+      <c r="H2746" t="n">
+        <v>76417</v>
+      </c>
+      <c r="I2746" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IMS.MI.xlsx
+++ b/data/IMS.MI.xlsx
@@ -427,7 +427,7 @@
         <v>0.45100000500679</v>
       </c>
       <c r="G2" t="n">
-        <v>0.333736151456833</v>
+        <v>0.333736181259155</v>
       </c>
       <c r="H2" t="n">
         <v>269301</v>
@@ -456,7 +456,7 @@
         <v>0.442499995231628</v>
       </c>
       <c r="G3" t="n">
-        <v>0.32744625210762</v>
+        <v>0.327446281909943</v>
       </c>
       <c r="H3" t="n">
         <v>116529</v>
@@ -485,7 +485,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G4" t="n">
-        <v>0.321156293153763</v>
+        <v>0.321156322956085</v>
       </c>
       <c r="H4" t="n">
         <v>136639</v>
@@ -543,7 +543,7 @@
         <v>0.415300011634827</v>
       </c>
       <c r="G6" t="n">
-        <v>0.307318478822708</v>
+        <v>0.307318449020386</v>
       </c>
       <c r="H6" t="n">
         <v>199460</v>
@@ -572,7 +572,7 @@
         <v>0.389800012111664</v>
       </c>
       <c r="G7" t="n">
-        <v>0.288448691368103</v>
+        <v>0.288448750972748</v>
       </c>
       <c r="H7" t="n">
         <v>877572</v>
@@ -630,7 +630,7 @@
         <v>0.397799998521805</v>
       </c>
       <c r="G9" t="n">
-        <v>0.294368654489517</v>
+        <v>0.294368594884872</v>
       </c>
       <c r="H9" t="n">
         <v>1154472</v>
@@ -717,7 +717,7 @@
         <v>0.349999994039536</v>
       </c>
       <c r="G12" t="n">
-        <v>0.258997023105621</v>
+        <v>0.258997052907944</v>
       </c>
       <c r="H12" t="n">
         <v>608621</v>
@@ -746,7 +746,7 @@
         <v>0.349000006914139</v>
       </c>
       <c r="G13" t="n">
-        <v>0.258257061243057</v>
+        <v>0.258257031440735</v>
       </c>
       <c r="H13" t="n">
         <v>657255</v>
@@ -775,7 +775,7 @@
         <v>0.329199999570847</v>
       </c>
       <c r="G14" t="n">
-        <v>0.243605211377144</v>
+        <v>0.243605196475983</v>
       </c>
       <c r="H14" t="n">
         <v>845615</v>
@@ -804,7 +804,7 @@
         <v>0.333000004291534</v>
       </c>
       <c r="G15" t="n">
-        <v>0.24641714990139</v>
+        <v>0.246417194604874</v>
       </c>
       <c r="H15" t="n">
         <v>896826</v>
@@ -862,7 +862,7 @@
         <v>0.346500009298325</v>
       </c>
       <c r="G17" t="n">
-        <v>0.256407052278519</v>
+        <v>0.256407082080841</v>
       </c>
       <c r="H17" t="n">
         <v>207617</v>
@@ -949,7 +949,7 @@
         <v>0.342999994754791</v>
       </c>
       <c r="G20" t="n">
-        <v>0.253817081451416</v>
+        <v>0.253817111253738</v>
       </c>
       <c r="H20" t="n">
         <v>123813</v>
@@ -978,7 +978,7 @@
         <v>0.342000007629395</v>
       </c>
       <c r="G21" t="n">
-        <v>0.253077119588852</v>
+        <v>0.253077059984207</v>
       </c>
       <c r="H21" t="n">
         <v>129643</v>
@@ -1007,7 +1007,7 @@
         <v>0.387699991464615</v>
       </c>
       <c r="G22" t="n">
-        <v>0.286894708871841</v>
+        <v>0.286894679069519</v>
       </c>
       <c r="H22" t="n">
         <v>1446522</v>
@@ -1065,7 +1065,7 @@
         <v>0.375</v>
       </c>
       <c r="G24" t="n">
-        <v>0.277496814727783</v>
+        <v>0.277496844530106</v>
       </c>
       <c r="H24" t="n">
         <v>1254555</v>
@@ -1094,7 +1094,7 @@
         <v>0.388000011444092</v>
       </c>
       <c r="G25" t="n">
-        <v>0.287116706371307</v>
+        <v>0.28711673617363</v>
       </c>
       <c r="H25" t="n">
         <v>1284870</v>
@@ -1152,7 +1152,7 @@
         <v>0.356499999761581</v>
       </c>
       <c r="G27" t="n">
-        <v>0.263806939125061</v>
+        <v>0.263806968927383</v>
       </c>
       <c r="H27" t="n">
         <v>560505</v>
@@ -1181,7 +1181,7 @@
         <v>0.347000002861023</v>
       </c>
       <c r="G28" t="n">
-        <v>0.256777107715607</v>
+        <v>0.256777077913284</v>
       </c>
       <c r="H28" t="n">
         <v>1141585</v>
@@ -1239,7 +1239,7 @@
         <v>0.337999999523163</v>
       </c>
       <c r="G30" t="n">
-        <v>0.250117123126984</v>
+        <v>0.250117152929306</v>
       </c>
       <c r="H30" t="n">
         <v>845331</v>
@@ -1268,7 +1268,7 @@
         <v>0.349999994039536</v>
       </c>
       <c r="G31" t="n">
-        <v>0.258997023105621</v>
+        <v>0.258997052907944</v>
       </c>
       <c r="H31" t="n">
         <v>219939</v>
@@ -1297,7 +1297,7 @@
         <v>0.375</v>
       </c>
       <c r="G32" t="n">
-        <v>0.277496814727783</v>
+        <v>0.277496844530106</v>
       </c>
       <c r="H32" t="n">
         <v>503860</v>
@@ -1326,7 +1326,7 @@
         <v>0.375099986791611</v>
       </c>
       <c r="G33" t="n">
-        <v>0.277570813894272</v>
+        <v>0.277570843696594</v>
       </c>
       <c r="H33" t="n">
         <v>165124</v>
@@ -1442,7 +1442,7 @@
         <v>0.411300003528595</v>
       </c>
       <c r="G37" t="n">
-        <v>0.304358541965485</v>
+        <v>0.304358512163162</v>
       </c>
       <c r="H37" t="n">
         <v>78198</v>
@@ -1471,7 +1471,7 @@
         <v>0.429899990558624</v>
       </c>
       <c r="G38" t="n">
-        <v>0.318122357130051</v>
+        <v>0.318122327327728</v>
       </c>
       <c r="H38" t="n">
         <v>113069</v>
@@ -1500,7 +1500,7 @@
         <v>0.418500006198883</v>
       </c>
       <c r="G39" t="n">
-        <v>0.309686422348022</v>
+        <v>0.309686452150345</v>
       </c>
       <c r="H39" t="n">
         <v>253612</v>
@@ -1529,7 +1529,7 @@
         <v>0.407599985599518</v>
       </c>
       <c r="G40" t="n">
-        <v>0.301620572805405</v>
+        <v>0.301620543003082</v>
       </c>
       <c r="H40" t="n">
         <v>213766</v>
@@ -1616,7 +1616,7 @@
         <v>0.432500004768372</v>
       </c>
       <c r="G43" t="n">
-        <v>0.320046305656433</v>
+        <v>0.320046365261078</v>
       </c>
       <c r="H43" t="n">
         <v>219093</v>
@@ -1674,7 +1674,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G45" t="n">
-        <v>0.315236419439316</v>
+        <v>0.315236389636993</v>
       </c>
       <c r="H45" t="n">
         <v>255696</v>
@@ -1732,7 +1732,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G47" t="n">
-        <v>0.332996189594269</v>
+        <v>0.332996159791946</v>
       </c>
       <c r="H47" t="n">
         <v>523033</v>
@@ -1819,7 +1819,7 @@
         <v>0.446599990129471</v>
       </c>
       <c r="G50" t="n">
-        <v>0.330480217933655</v>
+        <v>0.330480247735977</v>
       </c>
       <c r="H50" t="n">
         <v>32677</v>
@@ -1848,7 +1848,7 @@
         <v>0.42059999704361</v>
       </c>
       <c r="G51" t="n">
-        <v>0.311240464448929</v>
+        <v>0.311240434646606</v>
       </c>
       <c r="H51" t="n">
         <v>282562</v>
@@ -1877,7 +1877,7 @@
         <v>0.421700000762939</v>
       </c>
       <c r="G52" t="n">
-        <v>0.312054425477982</v>
+        <v>0.312054455280304</v>
       </c>
       <c r="H52" t="n">
         <v>153460</v>
@@ -1906,7 +1906,7 @@
         <v>0.405000001192093</v>
       </c>
       <c r="G53" t="n">
-        <v>0.299696534872055</v>
+        <v>0.299696564674377</v>
       </c>
       <c r="H53" t="n">
         <v>133629</v>
@@ -1993,7 +1993,7 @@
         <v>0.40200001001358</v>
       </c>
       <c r="G56" t="n">
-        <v>0.29747661948204</v>
+        <v>0.297476589679718</v>
       </c>
       <c r="H56" t="n">
         <v>137787</v>
@@ -2022,7 +2022,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G57" t="n">
-        <v>0.295996636152267</v>
+        <v>0.295996606349945</v>
       </c>
       <c r="H57" t="n">
         <v>270619</v>
@@ -2138,7 +2138,7 @@
         <v>0.387699991464615</v>
       </c>
       <c r="G61" t="n">
-        <v>0.286894708871841</v>
+        <v>0.286894679069519</v>
       </c>
       <c r="H61" t="n">
         <v>264789</v>
@@ -2167,7 +2167,7 @@
         <v>0.386999994516373</v>
       </c>
       <c r="G62" t="n">
-        <v>0.286376744508743</v>
+        <v>0.286376714706421</v>
       </c>
       <c r="H62" t="n">
         <v>251390</v>
@@ -2196,7 +2196,7 @@
         <v>0.374000012874603</v>
       </c>
       <c r="G63" t="n">
-        <v>0.276756882667542</v>
+        <v>0.276756852865219</v>
       </c>
       <c r="H63" t="n">
         <v>230800</v>
@@ -2225,7 +2225,7 @@
         <v>0.370999991893768</v>
       </c>
       <c r="G64" t="n">
-        <v>0.27453687787056</v>
+        <v>0.274536818265915</v>
       </c>
       <c r="H64" t="n">
         <v>309537</v>
@@ -2341,7 +2341,7 @@
         <v>0.358200013637543</v>
       </c>
       <c r="G68" t="n">
-        <v>0.26506495475769</v>
+        <v>0.265064924955368</v>
       </c>
       <c r="H68" t="n">
         <v>80404</v>
@@ -2370,7 +2370,7 @@
         <v>0.362399995326996</v>
       </c>
       <c r="G69" t="n">
-        <v>0.268172949552536</v>
+        <v>0.268172919750214</v>
       </c>
       <c r="H69" t="n">
         <v>89071</v>
@@ -2457,7 +2457,7 @@
         <v>0.372000008821487</v>
       </c>
       <c r="G72" t="n">
-        <v>0.275276809930801</v>
+        <v>0.275276839733124</v>
       </c>
       <c r="H72" t="n">
         <v>174786</v>
@@ -2486,7 +2486,7 @@
         <v>0.375</v>
       </c>
       <c r="G73" t="n">
-        <v>0.277496814727783</v>
+        <v>0.277496844530106</v>
       </c>
       <c r="H73" t="n">
         <v>173043</v>
@@ -2515,7 +2515,7 @@
         <v>0.375</v>
       </c>
       <c r="G74" t="n">
-        <v>0.277496814727783</v>
+        <v>0.277496844530106</v>
       </c>
       <c r="H74" t="n">
         <v>152860</v>
@@ -2544,7 +2544,7 @@
         <v>0.384999990463257</v>
       </c>
       <c r="G75" t="n">
-        <v>0.28489676117897</v>
+        <v>0.284896701574326</v>
       </c>
       <c r="H75" t="n">
         <v>270841</v>
@@ -2573,7 +2573,7 @@
         <v>0.39190000295639</v>
       </c>
       <c r="G76" t="n">
-        <v>0.290002673864365</v>
+        <v>0.290002644062042</v>
       </c>
       <c r="H76" t="n">
         <v>252654</v>
@@ -2602,7 +2602,7 @@
         <v>0.405000001192093</v>
       </c>
       <c r="G77" t="n">
-        <v>0.299696534872055</v>
+        <v>0.299696564674377</v>
       </c>
       <c r="H77" t="n">
         <v>328954</v>
@@ -2631,7 +2631,7 @@
         <v>0.416500002145767</v>
       </c>
       <c r="G78" t="n">
-        <v>0.308206498622894</v>
+        <v>0.308206468820572</v>
       </c>
       <c r="H78" t="n">
         <v>162052</v>
@@ -2660,7 +2660,7 @@
         <v>0.417800009250641</v>
       </c>
       <c r="G79" t="n">
-        <v>0.309168487787247</v>
+        <v>0.309168457984924</v>
       </c>
       <c r="H79" t="n">
         <v>592614</v>
@@ -2776,7 +2776,7 @@
         <v>0.424600005149841</v>
       </c>
       <c r="G83" t="n">
-        <v>0.31420037150383</v>
+        <v>0.314200431108475</v>
       </c>
       <c r="H83" t="n">
         <v>250735</v>
@@ -2805,7 +2805,7 @@
         <v>0.434300005435944</v>
       </c>
       <c r="G84" t="n">
-        <v>0.321378350257874</v>
+        <v>0.321378290653229</v>
       </c>
       <c r="H84" t="n">
         <v>355601</v>
@@ -2834,7 +2834,7 @@
         <v>0.431600004434586</v>
       </c>
       <c r="G85" t="n">
-        <v>0.319380313158035</v>
+        <v>0.319380342960358</v>
       </c>
       <c r="H85" t="n">
         <v>324523</v>
@@ -2950,7 +2950,7 @@
         <v>0.41499999165535</v>
       </c>
       <c r="G89" t="n">
-        <v>0.307096481323242</v>
+        <v>0.30709645152092</v>
       </c>
       <c r="H89" t="n">
         <v>184337</v>
@@ -3008,7 +3008,7 @@
         <v>0.405000001192093</v>
       </c>
       <c r="G91" t="n">
-        <v>0.299696534872055</v>
+        <v>0.299696564674377</v>
       </c>
       <c r="H91" t="n">
         <v>75280</v>
@@ -3037,7 +3037,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G92" t="n">
-        <v>0.295996636152267</v>
+        <v>0.295996606349945</v>
       </c>
       <c r="H92" t="n">
         <v>108413</v>
@@ -3066,7 +3066,7 @@
         <v>0.415699988603592</v>
       </c>
       <c r="G93" t="n">
-        <v>0.30761444568634</v>
+        <v>0.307614475488663</v>
       </c>
       <c r="H93" t="n">
         <v>129466</v>
@@ -3095,7 +3095,7 @@
         <v>0.412099987268448</v>
       </c>
       <c r="G94" t="n">
-        <v>0.304950535297394</v>
+        <v>0.304950475692749</v>
       </c>
       <c r="H94" t="n">
         <v>52726</v>
@@ -3153,7 +3153,7 @@
         <v>0.404799997806549</v>
       </c>
       <c r="G96" t="n">
-        <v>0.299548596143723</v>
+        <v>0.2995485663414</v>
       </c>
       <c r="H96" t="n">
         <v>17376</v>
@@ -3182,7 +3182,7 @@
         <v>0.412600010633469</v>
       </c>
       <c r="G97" t="n">
-        <v>0.305320501327515</v>
+        <v>0.305320471525192</v>
       </c>
       <c r="H97" t="n">
         <v>129927</v>
@@ -3240,7 +3240,7 @@
         <v>0.406699985265732</v>
       </c>
       <c r="G99" t="n">
-        <v>0.300954550504684</v>
+        <v>0.30095449090004</v>
       </c>
       <c r="H99" t="n">
         <v>86804</v>
@@ -3269,7 +3269,7 @@
         <v>0.409200012683868</v>
       </c>
       <c r="G100" t="n">
-        <v>0.314400315284729</v>
+        <v>0.314400285482407</v>
       </c>
       <c r="H100" t="n">
         <v>58225</v>
@@ -3356,7 +3356,7 @@
         <v>0.414400011301041</v>
       </c>
       <c r="G103" t="n">
-        <v>0.318395644426346</v>
+        <v>0.318395614624023</v>
       </c>
       <c r="H103" t="n">
         <v>66565</v>
@@ -3385,7 +3385,7 @@
         <v>0.416399985551834</v>
       </c>
       <c r="G104" t="n">
-        <v>0.319932252168655</v>
+        <v>0.3199323117733</v>
       </c>
       <c r="H104" t="n">
         <v>65981</v>
@@ -3501,7 +3501,7 @@
         <v>0.414000004529953</v>
       </c>
       <c r="G108" t="n">
-        <v>0.318088263273239</v>
+        <v>0.318088293075562</v>
       </c>
       <c r="H108" t="n">
         <v>221659</v>
@@ -3530,7 +3530,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G109" t="n">
-        <v>0.307331681251526</v>
+        <v>0.307331711053848</v>
       </c>
       <c r="H109" t="n">
         <v>111759</v>
@@ -3588,7 +3588,7 @@
         <v>0.418799996376038</v>
       </c>
       <c r="G111" t="n">
-        <v>0.321776241064072</v>
+        <v>0.321776270866394</v>
       </c>
       <c r="H111" t="n">
         <v>39838</v>
@@ -3646,7 +3646,7 @@
         <v>0.405499994754791</v>
       </c>
       <c r="G113" t="n">
-        <v>0.311557471752167</v>
+        <v>0.311557501554489</v>
       </c>
       <c r="H113" t="n">
         <v>20324</v>
@@ -3675,7 +3675,7 @@
         <v>0.398000001907349</v>
       </c>
       <c r="G114" t="n">
-        <v>0.305795043706894</v>
+        <v>0.305795013904572</v>
       </c>
       <c r="H114" t="n">
         <v>192474</v>
@@ -3791,7 +3791,7 @@
         <v>0.386000007390976</v>
       </c>
       <c r="G118" t="n">
-        <v>0.29657506942749</v>
+        <v>0.296575099229813</v>
       </c>
       <c r="H118" t="n">
         <v>68644</v>
@@ -3878,7 +3878,7 @@
         <v>0.41389998793602</v>
       </c>
       <c r="G121" t="n">
-        <v>0.318011432886124</v>
+        <v>0.318011462688446</v>
       </c>
       <c r="H121" t="n">
         <v>86534</v>
@@ -3907,7 +3907,7 @@
         <v>0.414799988269806</v>
       </c>
       <c r="G122" t="n">
-        <v>0.318702965974808</v>
+        <v>0.318702936172485</v>
       </c>
       <c r="H122" t="n">
         <v>106745</v>
@@ -3965,7 +3965,7 @@
         <v>0.403499990701675</v>
       </c>
       <c r="G124" t="n">
-        <v>0.310020804405212</v>
+        <v>0.310020834207535</v>
       </c>
       <c r="H124" t="n">
         <v>223601</v>
@@ -3994,7 +3994,7 @@
         <v>0.40599998831749</v>
       </c>
       <c r="G125" t="n">
-        <v>0.311941623687744</v>
+        <v>0.311941653490067</v>
       </c>
       <c r="H125" t="n">
         <v>264439</v>
@@ -4023,7 +4023,7 @@
         <v>0.405000001192093</v>
       </c>
       <c r="G126" t="n">
-        <v>0.311173349618912</v>
+        <v>0.311173319816589</v>
       </c>
       <c r="H126" t="n">
         <v>122243</v>
@@ -4052,7 +4052,7 @@
         <v>0.40599998831749</v>
       </c>
       <c r="G127" t="n">
-        <v>0.311941623687744</v>
+        <v>0.311941653490067</v>
       </c>
       <c r="H127" t="n">
         <v>172806</v>
@@ -4081,7 +4081,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G128" t="n">
-        <v>0.307331681251526</v>
+        <v>0.307331711053848</v>
       </c>
       <c r="H128" t="n">
         <v>33158</v>
@@ -4110,7 +4110,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G129" t="n">
-        <v>0.307331681251526</v>
+        <v>0.307331711053848</v>
       </c>
       <c r="H129" t="n">
         <v>147122</v>
@@ -4139,7 +4139,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G130" t="n">
-        <v>0.307331681251526</v>
+        <v>0.307331711053848</v>
       </c>
       <c r="H130" t="n">
         <v>35313</v>
@@ -4197,7 +4197,7 @@
         <v>0.399199992418289</v>
       </c>
       <c r="G132" t="n">
-        <v>0.30671700835228</v>
+        <v>0.306717038154602</v>
       </c>
       <c r="H132" t="n">
         <v>150465</v>
@@ -4226,7 +4226,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G133" t="n">
-        <v>0.307331681251526</v>
+        <v>0.307331711053848</v>
       </c>
       <c r="H133" t="n">
         <v>199243</v>
@@ -4255,7 +4255,7 @@
         <v>0.397700011730194</v>
       </c>
       <c r="G134" t="n">
-        <v>0.305564552545547</v>
+        <v>0.305564522743225</v>
       </c>
       <c r="H134" t="n">
         <v>200148</v>
@@ -4284,7 +4284,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G135" t="n">
-        <v>0.307331681251526</v>
+        <v>0.307331711053848</v>
       </c>
       <c r="H135" t="n">
         <v>136665</v>
@@ -4313,7 +4313,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G136" t="n">
-        <v>0.307331681251526</v>
+        <v>0.307331711053848</v>
       </c>
       <c r="H136" t="n">
         <v>109601</v>
@@ -4342,7 +4342,7 @@
         <v>0.398000001907349</v>
       </c>
       <c r="G137" t="n">
-        <v>0.305795043706894</v>
+        <v>0.305795013904572</v>
       </c>
       <c r="H137" t="n">
         <v>62518</v>
@@ -4371,7 +4371,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G138" t="n">
-        <v>0.307331681251526</v>
+        <v>0.307331711053848</v>
       </c>
       <c r="H138" t="n">
         <v>126604</v>
@@ -4545,7 +4545,7 @@
         <v>0.392800003290176</v>
       </c>
       <c r="G144" t="n">
-        <v>0.301799744367599</v>
+        <v>0.301799714565277</v>
       </c>
       <c r="H144" t="n">
         <v>21943</v>
@@ -4574,7 +4574,7 @@
         <v>0.395700007677078</v>
       </c>
       <c r="G145" t="n">
-        <v>0.304027885198593</v>
+        <v>0.304027855396271</v>
       </c>
       <c r="H145" t="n">
         <v>23023</v>
@@ -4603,7 +4603,7 @@
         <v>0.390500009059906</v>
       </c>
       <c r="G146" t="n">
-        <v>0.300032585859299</v>
+        <v>0.300032556056976</v>
       </c>
       <c r="H146" t="n">
         <v>20088</v>
@@ -4661,7 +4661,7 @@
         <v>0.406800001859665</v>
       </c>
       <c r="G148" t="n">
-        <v>0.312556326389313</v>
+        <v>0.312556356191635</v>
       </c>
       <c r="H148" t="n">
         <v>111238</v>
@@ -4690,7 +4690,7 @@
         <v>0.400700002908707</v>
       </c>
       <c r="G149" t="n">
-        <v>0.307869523763657</v>
+        <v>0.307869493961334</v>
       </c>
       <c r="H149" t="n">
         <v>122679</v>
@@ -4777,7 +4777,7 @@
         <v>0.389299988746643</v>
       </c>
       <c r="G152" t="n">
-        <v>0.299110561609268</v>
+        <v>0.299110531806946</v>
       </c>
       <c r="H152" t="n">
         <v>107176</v>
@@ -4806,7 +4806,7 @@
         <v>0.397300004959106</v>
       </c>
       <c r="G153" t="n">
-        <v>0.305257230997086</v>
+        <v>0.305257201194763</v>
       </c>
       <c r="H153" t="n">
         <v>32211</v>
@@ -4835,7 +4835,7 @@
         <v>0.397300004959106</v>
       </c>
       <c r="G154" t="n">
-        <v>0.305257230997086</v>
+        <v>0.305257201194763</v>
       </c>
       <c r="H154" t="n">
         <v>125840</v>
@@ -4864,7 +4864,7 @@
         <v>0.384700000286102</v>
       </c>
       <c r="G155" t="n">
-        <v>0.295576274394989</v>
+        <v>0.295576214790344</v>
       </c>
       <c r="H155" t="n">
         <v>84588</v>
@@ -4893,7 +4893,7 @@
         <v>0.385199993848801</v>
       </c>
       <c r="G156" t="n">
-        <v>0.295960366725922</v>
+        <v>0.295960426330566</v>
       </c>
       <c r="H156" t="n">
         <v>31523</v>
@@ -4951,7 +4951,7 @@
         <v>0.387699991464615</v>
       </c>
       <c r="G158" t="n">
-        <v>0.297881275415421</v>
+        <v>0.297881215810776</v>
       </c>
       <c r="H158" t="n">
         <v>56338</v>
@@ -4980,7 +4980,7 @@
         <v>0.387699991464615</v>
       </c>
       <c r="G159" t="n">
-        <v>0.297881275415421</v>
+        <v>0.297881215810776</v>
       </c>
       <c r="H159" t="n">
         <v>100520</v>
@@ -5009,7 +5009,7 @@
         <v>0.382299989461899</v>
       </c>
       <c r="G160" t="n">
-        <v>0.29373225569725</v>
+        <v>0.293732225894928</v>
       </c>
       <c r="H160" t="n">
         <v>67716</v>
@@ -5038,7 +5038,7 @@
         <v>0.388900011777878</v>
       </c>
       <c r="G161" t="n">
-        <v>0.298803210258484</v>
+        <v>0.298803240060806</v>
       </c>
       <c r="H161" t="n">
         <v>86225</v>
@@ -5270,7 +5270,7 @@
         <v>0.397599995136261</v>
       </c>
       <c r="G169" t="n">
-        <v>0.30548769235611</v>
+        <v>0.305487662553787</v>
       </c>
       <c r="H169" t="n">
         <v>47359</v>
@@ -5299,7 +5299,7 @@
         <v>0.402900010347366</v>
       </c>
       <c r="G170" t="n">
-        <v>0.30955982208252</v>
+        <v>0.309559851884842</v>
       </c>
       <c r="H170" t="n">
         <v>421141</v>
@@ -5328,7 +5328,7 @@
         <v>0.394499987363815</v>
       </c>
       <c r="G171" t="n">
-        <v>0.303105890750885</v>
+        <v>0.30310583114624</v>
       </c>
       <c r="H171" t="n">
         <v>99588</v>
@@ -5415,7 +5415,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G174" t="n">
-        <v>0.307331681251526</v>
+        <v>0.307331711053848</v>
       </c>
       <c r="H174" t="n">
         <v>49911</v>
@@ -5444,7 +5444,7 @@
         <v>0.396800011396408</v>
       </c>
       <c r="G175" t="n">
-        <v>0.304873049259186</v>
+        <v>0.304873079061508</v>
       </c>
       <c r="H175" t="n">
         <v>32437</v>
@@ -5473,7 +5473,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G176" t="n">
-        <v>0.307331681251526</v>
+        <v>0.307331711053848</v>
       </c>
       <c r="H176" t="n">
         <v>27461</v>
@@ -5589,7 +5589,7 @@
         <v>0.385800004005432</v>
       </c>
       <c r="G180" t="n">
-        <v>0.296421408653259</v>
+        <v>0.296421349048615</v>
       </c>
       <c r="H180" t="n">
         <v>57078</v>
@@ -5618,7 +5618,7 @@
         <v>0.392300009727478</v>
       </c>
       <c r="G181" t="n">
-        <v>0.3014155626297</v>
+        <v>0.301415592432022</v>
       </c>
       <c r="H181" t="n">
         <v>47493</v>
@@ -5705,7 +5705,7 @@
         <v>0.379999995231628</v>
       </c>
       <c r="G184" t="n">
-        <v>0.29196509718895</v>
+        <v>0.291965067386627</v>
       </c>
       <c r="H184" t="n">
         <v>439065</v>
@@ -5734,7 +5734,7 @@
         <v>0.377099990844727</v>
       </c>
       <c r="G185" t="n">
-        <v>0.289736956357956</v>
+        <v>0.289736926555634</v>
       </c>
       <c r="H185" t="n">
         <v>75662</v>
@@ -5763,7 +5763,7 @@
         <v>0.379999995231628</v>
       </c>
       <c r="G186" t="n">
-        <v>0.29196509718895</v>
+        <v>0.291965067386627</v>
       </c>
       <c r="H186" t="n">
         <v>57765</v>
@@ -5792,7 +5792,7 @@
         <v>0.381999999284744</v>
       </c>
       <c r="G187" t="n">
-        <v>0.293501764535904</v>
+        <v>0.293501734733582</v>
       </c>
       <c r="H187" t="n">
         <v>162509</v>
@@ -5821,7 +5821,7 @@
         <v>0.380899995565414</v>
       </c>
       <c r="G188" t="n">
-        <v>0.292656570672989</v>
+        <v>0.292656600475311</v>
       </c>
       <c r="H188" t="n">
         <v>84648</v>
@@ -5879,7 +5879,7 @@
         <v>0.376899987459183</v>
       </c>
       <c r="G190" t="n">
-        <v>0.28958323597908</v>
+        <v>0.289583265781403</v>
       </c>
       <c r="H190" t="n">
         <v>91226</v>
@@ -5966,7 +5966,7 @@
         <v>0.374700009822845</v>
       </c>
       <c r="G193" t="n">
-        <v>0.28789296746254</v>
+        <v>0.287892997264862</v>
       </c>
       <c r="H193" t="n">
         <v>82455</v>
@@ -6024,7 +6024,7 @@
         <v>0.381199985742569</v>
       </c>
       <c r="G195" t="n">
-        <v>0.292887091636658</v>
+        <v>0.292887061834335</v>
       </c>
       <c r="H195" t="n">
         <v>44416</v>
@@ -6111,7 +6111,7 @@
         <v>0.37720000743866</v>
       </c>
       <c r="G198" t="n">
-        <v>0.289813756942749</v>
+        <v>0.289813786745071</v>
       </c>
       <c r="H198" t="n">
         <v>3058</v>
@@ -6140,7 +6140,7 @@
         <v>0.372999995946884</v>
       </c>
       <c r="G199" t="n">
-        <v>0.286586791276932</v>
+        <v>0.286586821079254</v>
       </c>
       <c r="H199" t="n">
         <v>32621</v>
@@ -6198,7 +6198,7 @@
         <v>0.382999986410141</v>
       </c>
       <c r="G201" t="n">
-        <v>0.294270038604736</v>
+        <v>0.294270098209381</v>
       </c>
       <c r="H201" t="n">
         <v>337594</v>
@@ -6227,7 +6227,7 @@
         <v>0.379999995231628</v>
       </c>
       <c r="G202" t="n">
-        <v>0.29196509718895</v>
+        <v>0.291965067386627</v>
       </c>
       <c r="H202" t="n">
         <v>385031</v>
@@ -6430,7 +6430,7 @@
         <v>0.383599996566772</v>
       </c>
       <c r="G209" t="n">
-        <v>0.294731110334396</v>
+        <v>0.294731080532074</v>
       </c>
       <c r="H209" t="n">
         <v>99376</v>
@@ -6488,7 +6488,7 @@
         <v>0.379999995231628</v>
       </c>
       <c r="G211" t="n">
-        <v>0.29196509718895</v>
+        <v>0.291965067386627</v>
       </c>
       <c r="H211" t="n">
         <v>38312</v>
@@ -6546,7 +6546,7 @@
         <v>0.379999995231628</v>
       </c>
       <c r="G213" t="n">
-        <v>0.29196509718895</v>
+        <v>0.291965067386627</v>
       </c>
       <c r="H213" t="n">
         <v>22302</v>
@@ -6575,7 +6575,7 @@
         <v>0.382400006055832</v>
       </c>
       <c r="G214" t="n">
-        <v>0.293809056282043</v>
+        <v>0.293809115886688</v>
       </c>
       <c r="H214" t="n">
         <v>141041</v>
@@ -6604,7 +6604,7 @@
         <v>0.380100011825562</v>
       </c>
       <c r="G215" t="n">
-        <v>0.292041927576065</v>
+        <v>0.292041957378387</v>
       </c>
       <c r="H215" t="n">
         <v>78352</v>
@@ -6633,7 +6633,7 @@
         <v>0.373199999332428</v>
       </c>
       <c r="G216" t="n">
-        <v>0.286740452051163</v>
+        <v>0.286740481853485</v>
       </c>
       <c r="H216" t="n">
         <v>53185</v>
@@ -6662,7 +6662,7 @@
         <v>0.37049999833107</v>
       </c>
       <c r="G217" t="n">
-        <v>0.2846659719944</v>
+        <v>0.284666001796722</v>
       </c>
       <c r="H217" t="n">
         <v>47039</v>
@@ -6720,7 +6720,7 @@
         <v>0.363000005483627</v>
       </c>
       <c r="G219" t="n">
-        <v>0.278903543949127</v>
+        <v>0.278903514146805</v>
       </c>
       <c r="H219" t="n">
         <v>106149</v>
@@ -6749,7 +6749,7 @@
         <v>0.358700007200241</v>
       </c>
       <c r="G220" t="n">
-        <v>0.27559968829155</v>
+        <v>0.275599718093872</v>
       </c>
       <c r="H220" t="n">
         <v>216541</v>
@@ -6778,7 +6778,7 @@
         <v>0.351700007915497</v>
       </c>
       <c r="G221" t="n">
-        <v>0.270221412181854</v>
+        <v>0.270221382379532</v>
       </c>
       <c r="H221" t="n">
         <v>142567</v>
@@ -6807,7 +6807,7 @@
         <v>0.354600012302399</v>
       </c>
       <c r="G222" t="n">
-        <v>0.27244958281517</v>
+        <v>0.272449553012848</v>
       </c>
       <c r="H222" t="n">
         <v>171926</v>
@@ -6865,7 +6865,7 @@
         <v>0.356599986553192</v>
       </c>
       <c r="G224" t="n">
-        <v>0.27398619055748</v>
+        <v>0.273986130952835</v>
       </c>
       <c r="H224" t="n">
         <v>113864</v>
@@ -6894,7 +6894,7 @@
         <v>0.358799993991852</v>
       </c>
       <c r="G225" t="n">
-        <v>0.275676518678665</v>
+        <v>0.275676488876343</v>
       </c>
       <c r="H225" t="n">
         <v>133727</v>
@@ -6923,7 +6923,7 @@
         <v>0.358599990606308</v>
       </c>
       <c r="G226" t="n">
-        <v>0.275522857904434</v>
+        <v>0.275522828102112</v>
       </c>
       <c r="H226" t="n">
         <v>80224</v>
@@ -6952,7 +6952,7 @@
         <v>0.358599990606308</v>
       </c>
       <c r="G227" t="n">
-        <v>0.275522857904434</v>
+        <v>0.275522828102112</v>
       </c>
       <c r="H227" t="n">
         <v>63509</v>
@@ -7068,7 +7068,7 @@
         <v>0.352899998426437</v>
       </c>
       <c r="G231" t="n">
-        <v>0.271143347024918</v>
+        <v>0.27114337682724</v>
       </c>
       <c r="H231" t="n">
         <v>96101</v>
@@ -7097,7 +7097,7 @@
         <v>0.35699999332428</v>
       </c>
       <c r="G232" t="n">
-        <v>0.274293512105942</v>
+        <v>0.274293571710587</v>
       </c>
       <c r="H232" t="n">
         <v>135147</v>
@@ -7184,7 +7184,7 @@
         <v>0.34799998998642</v>
       </c>
       <c r="G235" t="n">
-        <v>0.267378568649292</v>
+        <v>0.26737853884697</v>
       </c>
       <c r="H235" t="n">
         <v>115347</v>
@@ -7213,7 +7213,7 @@
         <v>0.344399988651276</v>
       </c>
       <c r="G236" t="n">
-        <v>0.264612555503845</v>
+        <v>0.264612585306168</v>
       </c>
       <c r="H236" t="n">
         <v>140440</v>
@@ -7242,7 +7242,7 @@
         <v>0.345899999141693</v>
       </c>
       <c r="G237" t="n">
-        <v>0.265765070915222</v>
+        <v>0.265765100717545</v>
       </c>
       <c r="H237" t="n">
         <v>69294</v>
@@ -7271,7 +7271,7 @@
         <v>0.341500014066696</v>
       </c>
       <c r="G238" t="n">
-        <v>0.262384444475174</v>
+        <v>0.262384414672852</v>
       </c>
       <c r="H238" t="n">
         <v>83468</v>
@@ -7387,7 +7387,7 @@
         <v>0.363000005483627</v>
       </c>
       <c r="G242" t="n">
-        <v>0.278903543949127</v>
+        <v>0.278903514146805</v>
       </c>
       <c r="H242" t="n">
         <v>277659</v>
@@ -7416,7 +7416,7 @@
         <v>0.354699999094009</v>
       </c>
       <c r="G243" t="n">
-        <v>0.272526353597641</v>
+        <v>0.272526383399963</v>
       </c>
       <c r="H243" t="n">
         <v>153986</v>
@@ -7445,7 +7445,7 @@
         <v>0.368699997663498</v>
       </c>
       <c r="G244" t="n">
-        <v>0.283282995223999</v>
+        <v>0.283283025026321</v>
       </c>
       <c r="H244" t="n">
         <v>415238</v>
@@ -7503,7 +7503,7 @@
         <v>0.360599994659424</v>
       </c>
       <c r="G246" t="n">
-        <v>0.277059525251389</v>
+        <v>0.277059555053711</v>
       </c>
       <c r="H246" t="n">
         <v>135695</v>
@@ -7532,7 +7532,7 @@
         <v>0.362399995326996</v>
       </c>
       <c r="G247" t="n">
-        <v>0.278442472219467</v>
+        <v>0.27844250202179</v>
       </c>
       <c r="H247" t="n">
         <v>57911</v>
@@ -7590,7 +7590,7 @@
         <v>0.362399995326996</v>
       </c>
       <c r="G249" t="n">
-        <v>0.278442472219467</v>
+        <v>0.27844250202179</v>
       </c>
       <c r="H249" t="n">
         <v>56247</v>
@@ -7648,7 +7648,7 @@
         <v>0.360599994659424</v>
       </c>
       <c r="G251" t="n">
-        <v>0.277059525251389</v>
+        <v>0.277059555053711</v>
       </c>
       <c r="H251" t="n">
         <v>55864</v>
@@ -7677,7 +7677,7 @@
         <v>0.358599990606308</v>
       </c>
       <c r="G252" t="n">
-        <v>0.275522857904434</v>
+        <v>0.275522828102112</v>
       </c>
       <c r="H252" t="n">
         <v>116963</v>
@@ -7764,7 +7764,7 @@
         <v>0.362100005149841</v>
       </c>
       <c r="G255" t="n">
-        <v>0.278211981058121</v>
+        <v>0.278212010860443</v>
       </c>
       <c r="H255" t="n">
         <v>71245</v>
@@ -7851,7 +7851,7 @@
         <v>0.378500014543533</v>
       </c>
       <c r="G258" t="n">
-        <v>0.290812641382217</v>
+        <v>0.290812611579895</v>
       </c>
       <c r="H258" t="n">
         <v>308237</v>
@@ -7880,7 +7880,7 @@
         <v>0.377000004053116</v>
       </c>
       <c r="G259" t="n">
-        <v>0.289660096168518</v>
+        <v>0.28966012597084</v>
       </c>
       <c r="H259" t="n">
         <v>399052</v>
@@ -7938,7 +7938,7 @@
         <v>0.383700013160706</v>
       </c>
       <c r="G261" t="n">
-        <v>0.294807970523834</v>
+        <v>0.294807940721512</v>
       </c>
       <c r="H261" t="n">
         <v>120257</v>
@@ -8025,7 +8025,7 @@
         <v>0.377000004053116</v>
       </c>
       <c r="G264" t="n">
-        <v>0.289660096168518</v>
+        <v>0.28966012597084</v>
       </c>
       <c r="H264" t="n">
         <v>282378</v>
@@ -8054,7 +8054,7 @@
         <v>0.375499993562698</v>
       </c>
       <c r="G265" t="n">
-        <v>0.288507580757141</v>
+        <v>0.288507610559464</v>
       </c>
       <c r="H265" t="n">
         <v>91700</v>
@@ -8257,7 +8257,7 @@
         <v>0.381199985742569</v>
       </c>
       <c r="G272" t="n">
-        <v>0.292887091636658</v>
+        <v>0.292887061834335</v>
       </c>
       <c r="H272" t="n">
         <v>387615</v>
@@ -8286,7 +8286,7 @@
         <v>0.383799999952316</v>
       </c>
       <c r="G273" t="n">
-        <v>0.294884741306305</v>
+        <v>0.294884771108627</v>
       </c>
       <c r="H273" t="n">
         <v>40526</v>
@@ -8431,7 +8431,7 @@
         <v>0.372399985790253</v>
       </c>
       <c r="G278" t="n">
-        <v>0.286125779151917</v>
+        <v>0.286125808954239</v>
       </c>
       <c r="H278" t="n">
         <v>197429</v>
@@ -8547,7 +8547,7 @@
         <v>0.367000013589859</v>
       </c>
       <c r="G282" t="n">
-        <v>0.281976819038391</v>
+        <v>0.281976848840714</v>
       </c>
       <c r="H282" t="n">
         <v>63920</v>
@@ -8605,7 +8605,7 @@
         <v>0.356099992990494</v>
       </c>
       <c r="G284" t="n">
-        <v>0.273602038621902</v>
+        <v>0.27360200881958</v>
       </c>
       <c r="H284" t="n">
         <v>74655</v>
@@ -8634,7 +8634,7 @@
         <v>0.351099997758865</v>
       </c>
       <c r="G285" t="n">
-        <v>0.269760400056839</v>
+        <v>0.269760429859161</v>
       </c>
       <c r="H285" t="n">
         <v>67853</v>
@@ -8692,7 +8692,7 @@
         <v>0.353799998760223</v>
       </c>
       <c r="G287" t="n">
-        <v>0.271834909915924</v>
+        <v>0.271834880113602</v>
       </c>
       <c r="H287" t="n">
         <v>29000</v>
@@ -8750,7 +8750,7 @@
         <v>0.358200013637543</v>
       </c>
       <c r="G289" t="n">
-        <v>0.275215536355972</v>
+        <v>0.27521550655365</v>
       </c>
       <c r="H289" t="n">
         <v>104065</v>
@@ -8808,7 +8808,7 @@
         <v>0.35699999332428</v>
       </c>
       <c r="G291" t="n">
-        <v>0.274293512105942</v>
+        <v>0.274293571710587</v>
       </c>
       <c r="H291" t="n">
         <v>88831</v>
@@ -8924,7 +8924,7 @@
         <v>0.365000009536743</v>
       </c>
       <c r="G295" t="n">
-        <v>0.280440121889114</v>
+        <v>0.280440151691437</v>
       </c>
       <c r="H295" t="n">
         <v>519734</v>
@@ -8953,7 +8953,7 @@
         <v>0.363900005817413</v>
       </c>
       <c r="G296" t="n">
-        <v>0.279594987630844</v>
+        <v>0.279595017433167</v>
       </c>
       <c r="H296" t="n">
         <v>82937</v>
@@ -9011,7 +9011,7 @@
         <v>0.361999988555908</v>
       </c>
       <c r="G298" t="n">
-        <v>0.278135150671005</v>
+        <v>0.278135120868683</v>
       </c>
       <c r="H298" t="n">
         <v>141640</v>
@@ -9040,7 +9040,7 @@
         <v>0.36599999666214</v>
       </c>
       <c r="G299" t="n">
-        <v>0.281208485364914</v>
+        <v>0.281208544969559</v>
       </c>
       <c r="H299" t="n">
         <v>204598</v>
@@ -9069,7 +9069,7 @@
         <v>0.367000013589859</v>
       </c>
       <c r="G300" t="n">
-        <v>0.281976819038391</v>
+        <v>0.281976848840714</v>
       </c>
       <c r="H300" t="n">
         <v>268721</v>
@@ -9185,7 +9185,7 @@
         <v>0.37169998884201</v>
       </c>
       <c r="G304" t="n">
-        <v>0.285587996244431</v>
+        <v>0.285587966442108</v>
       </c>
       <c r="H304" t="n">
         <v>242038</v>
@@ -9214,7 +9214,7 @@
         <v>0.37049999833107</v>
       </c>
       <c r="G305" t="n">
-        <v>0.2846659719944</v>
+        <v>0.284666001796722</v>
       </c>
       <c r="H305" t="n">
         <v>78957</v>
@@ -9272,7 +9272,7 @@
         <v>0.373100012540817</v>
       </c>
       <c r="G307" t="n">
-        <v>0.28666365146637</v>
+        <v>0.286663621664047</v>
       </c>
       <c r="H307" t="n">
         <v>327704</v>
@@ -9301,7 +9301,7 @@
         <v>0.370200008153915</v>
       </c>
       <c r="G308" t="n">
-        <v>0.284435510635376</v>
+        <v>0.284435480833054</v>
       </c>
       <c r="H308" t="n">
         <v>77640</v>
@@ -9388,7 +9388,7 @@
         <v>0.369500011205673</v>
       </c>
       <c r="G311" t="n">
-        <v>0.283897668123245</v>
+        <v>0.283897697925568</v>
       </c>
       <c r="H311" t="n">
         <v>385846</v>
@@ -9446,7 +9446,7 @@
         <v>0.371300011873245</v>
       </c>
       <c r="G313" t="n">
-        <v>0.285280644893646</v>
+        <v>0.285280615091324</v>
       </c>
       <c r="H313" t="n">
         <v>185974</v>
@@ -9475,7 +9475,7 @@
         <v>0.371499985456467</v>
       </c>
       <c r="G314" t="n">
-        <v>0.285434275865555</v>
+        <v>0.285434305667877</v>
       </c>
       <c r="H314" t="n">
         <v>968385</v>
@@ -9504,7 +9504,7 @@
         <v>0.38400000333786</v>
       </c>
       <c r="G315" t="n">
-        <v>0.295038461685181</v>
+        <v>0.295038431882858</v>
       </c>
       <c r="H315" t="n">
         <v>718113</v>
@@ -9533,7 +9533,7 @@
         <v>0.382999986410141</v>
       </c>
       <c r="G316" t="n">
-        <v>0.294270038604736</v>
+        <v>0.294270098209381</v>
       </c>
       <c r="H316" t="n">
         <v>2465767</v>
@@ -9591,7 +9591,7 @@
         <v>0.405000001192093</v>
       </c>
       <c r="G318" t="n">
-        <v>0.311173349618912</v>
+        <v>0.311173319816589</v>
       </c>
       <c r="H318" t="n">
         <v>1167342</v>
@@ -9649,7 +9649,7 @@
         <v>0.423799991607666</v>
       </c>
       <c r="G320" t="n">
-        <v>0.325617879629135</v>
+        <v>0.32561793923378</v>
       </c>
       <c r="H320" t="n">
         <v>1505627</v>
@@ -9736,7 +9736,7 @@
         <v>0.412499994039536</v>
       </c>
       <c r="G323" t="n">
-        <v>0.316935777664185</v>
+        <v>0.316935807466507</v>
       </c>
       <c r="H323" t="n">
         <v>292888</v>
@@ -9823,7 +9823,7 @@
         <v>0.402500003576279</v>
       </c>
       <c r="G326" t="n">
-        <v>0.30925253033638</v>
+        <v>0.309252500534058</v>
       </c>
       <c r="H326" t="n">
         <v>176977</v>
@@ -9852,7 +9852,7 @@
         <v>0.404900014400482</v>
       </c>
       <c r="G327" t="n">
-        <v>0.311096489429474</v>
+        <v>0.311096549034119</v>
       </c>
       <c r="H327" t="n">
         <v>366751</v>
@@ -9968,7 +9968,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G331" t="n">
-        <v>0.307331681251526</v>
+        <v>0.307331711053848</v>
       </c>
       <c r="H331" t="n">
         <v>786930</v>
@@ -9997,7 +9997,7 @@
         <v>0.375999987125397</v>
       </c>
       <c r="G332" t="n">
-        <v>0.288891792297363</v>
+        <v>0.288891762495041</v>
       </c>
       <c r="H332" t="n">
         <v>1226633</v>
@@ -10113,7 +10113,7 @@
         <v>0.38629999756813</v>
       </c>
       <c r="G336" t="n">
-        <v>0.296805620193481</v>
+        <v>0.296805590391159</v>
       </c>
       <c r="H336" t="n">
         <v>233600</v>
@@ -10171,7 +10171,7 @@
         <v>0.390500009059906</v>
       </c>
       <c r="G338" t="n">
-        <v>0.300032585859299</v>
+        <v>0.300032556056976</v>
       </c>
       <c r="H338" t="n">
         <v>436560</v>
@@ -10200,7 +10200,7 @@
         <v>0.386900007724762</v>
       </c>
       <c r="G339" t="n">
-        <v>0.297266572713852</v>
+        <v>0.297266602516174</v>
       </c>
       <c r="H339" t="n">
         <v>577932</v>
@@ -10258,7 +10258,7 @@
         <v>0.403800010681152</v>
       </c>
       <c r="G341" t="n">
-        <v>0.310251355171204</v>
+        <v>0.310251325368881</v>
       </c>
       <c r="H341" t="n">
         <v>450573</v>
@@ -10287,7 +10287,7 @@
         <v>0.408100008964539</v>
       </c>
       <c r="G342" t="n">
-        <v>0.313555151224136</v>
+        <v>0.313555181026459</v>
       </c>
       <c r="H342" t="n">
         <v>868203</v>
@@ -10316,7 +10316,7 @@
         <v>0.396800011396408</v>
       </c>
       <c r="G343" t="n">
-        <v>0.304873049259186</v>
+        <v>0.304873079061508</v>
       </c>
       <c r="H343" t="n">
         <v>912935</v>
@@ -10461,7 +10461,7 @@
         <v>0.390100002288818</v>
       </c>
       <c r="G348" t="n">
-        <v>0.299725234508514</v>
+        <v>0.299725204706192</v>
       </c>
       <c r="H348" t="n">
         <v>938447</v>
@@ -10519,7 +10519,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G350" t="n">
-        <v>0.327308237552643</v>
+        <v>0.327308267354965</v>
       </c>
       <c r="H350" t="n">
         <v>4076818</v>
@@ -10577,7 +10577,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G352" t="n">
-        <v>0.307331681251526</v>
+        <v>0.307331711053848</v>
       </c>
       <c r="H352" t="n">
         <v>1214448</v>
@@ -10606,7 +10606,7 @@
         <v>0.402500003576279</v>
       </c>
       <c r="G353" t="n">
-        <v>0.30925253033638</v>
+        <v>0.309252500534058</v>
       </c>
       <c r="H353" t="n">
         <v>829852</v>
@@ -10635,7 +10635,7 @@
         <v>0.406199991703033</v>
       </c>
       <c r="G354" t="n">
-        <v>0.31209534406662</v>
+        <v>0.312095314264297</v>
       </c>
       <c r="H354" t="n">
         <v>404219</v>
@@ -10751,7 +10751,7 @@
         <v>0.406399995088577</v>
       </c>
       <c r="G358" t="n">
-        <v>0.312248975038528</v>
+        <v>0.312249004840851</v>
       </c>
       <c r="H358" t="n">
         <v>577929</v>
@@ -10780,7 +10780,7 @@
         <v>0.408600002527237</v>
       </c>
       <c r="G359" t="n">
-        <v>0.313939332962036</v>
+        <v>0.313939303159714</v>
       </c>
       <c r="H359" t="n">
         <v>695103</v>
@@ -10867,7 +10867,7 @@
         <v>0.397599995136261</v>
       </c>
       <c r="G362" t="n">
-        <v>0.30548769235611</v>
+        <v>0.305487662553787</v>
       </c>
       <c r="H362" t="n">
         <v>416430</v>
@@ -10896,7 +10896,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G363" t="n">
-        <v>0.307331681251526</v>
+        <v>0.307331711053848</v>
       </c>
       <c r="H363" t="n">
         <v>459908</v>
@@ -10983,7 +10983,7 @@
         <v>0.40090000629425</v>
       </c>
       <c r="G366" t="n">
-        <v>0.308023154735565</v>
+        <v>0.308023184537888</v>
       </c>
       <c r="H366" t="n">
         <v>380563</v>
@@ -11099,7 +11099,7 @@
         <v>0.403400003910065</v>
       </c>
       <c r="G370" t="n">
-        <v>0.309944003820419</v>
+        <v>0.309943974018097</v>
       </c>
       <c r="H370" t="n">
         <v>180098</v>
@@ -11157,7 +11157,7 @@
         <v>0.412000000476837</v>
       </c>
       <c r="G372" t="n">
-        <v>0.316551625728607</v>
+        <v>0.31655165553093</v>
       </c>
       <c r="H372" t="n">
         <v>261916</v>
@@ -11215,7 +11215,7 @@
         <v>0.422199994325638</v>
       </c>
       <c r="G374" t="n">
-        <v>0.324388593435287</v>
+        <v>0.32438862323761</v>
       </c>
       <c r="H374" t="n">
         <v>1118729</v>
@@ -11273,7 +11273,7 @@
         <v>0.414299994707108</v>
       </c>
       <c r="G376" t="n">
-        <v>0.318318754434586</v>
+        <v>0.318318784236908</v>
       </c>
       <c r="H376" t="n">
         <v>886282</v>
@@ -11302,7 +11302,7 @@
         <v>0.413500010967255</v>
       </c>
       <c r="G377" t="n">
-        <v>0.317704141139984</v>
+        <v>0.317704170942307</v>
       </c>
       <c r="H377" t="n">
         <v>646769</v>
@@ -11331,7 +11331,7 @@
         <v>0.418500006198883</v>
       </c>
       <c r="G378" t="n">
-        <v>0.32154580950737</v>
+        <v>0.321545749902725</v>
       </c>
       <c r="H378" t="n">
         <v>467304</v>
@@ -11360,7 +11360,7 @@
         <v>0.417100012302399</v>
       </c>
       <c r="G379" t="n">
-        <v>0.320470094680786</v>
+        <v>0.320470124483109</v>
       </c>
       <c r="H379" t="n">
         <v>339473</v>
@@ -11476,7 +11476,7 @@
         <v>0.426099985837936</v>
       </c>
       <c r="G383" t="n">
-        <v>0.327385097742081</v>
+        <v>0.327385038137436</v>
       </c>
       <c r="H383" t="n">
         <v>1943633</v>
@@ -11534,7 +11534,7 @@
         <v>0.441900014877319</v>
       </c>
       <c r="G385" t="n">
-        <v>0.339524656534195</v>
+        <v>0.339524686336517</v>
       </c>
       <c r="H385" t="n">
         <v>690454</v>
@@ -11708,7 +11708,7 @@
         <v>0.439599990844727</v>
       </c>
       <c r="G391" t="n">
-        <v>0.337757527828217</v>
+        <v>0.337757498025894</v>
       </c>
       <c r="H391" t="n">
         <v>301832</v>
@@ -11766,7 +11766,7 @@
         <v>0.440100014209747</v>
       </c>
       <c r="G393" t="n">
-        <v>0.338141739368439</v>
+        <v>0.338141679763794</v>
       </c>
       <c r="H393" t="n">
         <v>287602</v>
@@ -11824,7 +11824,7 @@
         <v>0.456000000238419</v>
       </c>
       <c r="G395" t="n">
-        <v>0.350358098745346</v>
+        <v>0.350358158349991</v>
       </c>
       <c r="H395" t="n">
         <v>1534207</v>
@@ -11882,7 +11882,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G397" t="n">
-        <v>0.344211518764496</v>
+        <v>0.344211488962173</v>
       </c>
       <c r="H397" t="n">
         <v>444793</v>
@@ -11911,7 +11911,7 @@
         <v>0.443399995565414</v>
       </c>
       <c r="G398" t="n">
-        <v>0.34067714214325</v>
+        <v>0.340677171945572</v>
       </c>
       <c r="H398" t="n">
         <v>373444</v>
@@ -11998,7 +11998,7 @@
         <v>0.451499998569489</v>
       </c>
       <c r="G401" t="n">
-        <v>0.346900671720505</v>
+        <v>0.346900641918182</v>
       </c>
       <c r="H401" t="n">
         <v>897799</v>
@@ -12027,7 +12027,7 @@
         <v>0.450500011444092</v>
       </c>
       <c r="G402" t="n">
-        <v>0.346132278442383</v>
+        <v>0.346132308244705</v>
       </c>
       <c r="H402" t="n">
         <v>268874</v>
@@ -12056,7 +12056,7 @@
         <v>0.44200000166893</v>
       </c>
       <c r="G403" t="n">
-        <v>0.339601516723633</v>
+        <v>0.339601546525955</v>
       </c>
       <c r="H403" t="n">
         <v>713524</v>
@@ -12114,7 +12114,7 @@
         <v>0.458999991416931</v>
       </c>
       <c r="G405" t="n">
-        <v>0.352663099765778</v>
+        <v>0.352663069963455</v>
       </c>
       <c r="H405" t="n">
         <v>1536809</v>
@@ -12143,7 +12143,7 @@
         <v>0.481499999761581</v>
       </c>
       <c r="G406" t="n">
-        <v>0.369950503110886</v>
+        <v>0.369950532913208</v>
       </c>
       <c r="H406" t="n">
         <v>3256875</v>
@@ -12201,7 +12201,7 @@
         <v>0.472499996423721</v>
       </c>
       <c r="G408" t="n">
-        <v>0.363035559654236</v>
+        <v>0.363035529851913</v>
       </c>
       <c r="H408" t="n">
         <v>651242</v>
@@ -12230,7 +12230,7 @@
         <v>0.486900001764297</v>
       </c>
       <c r="G409" t="n">
-        <v>0.374099493026733</v>
+        <v>0.374099522829056</v>
       </c>
       <c r="H409" t="n">
         <v>524155</v>
@@ -12404,7 +12404,7 @@
         <v>0.47979998588562</v>
       </c>
       <c r="G415" t="n">
-        <v>0.368644326925278</v>
+        <v>0.3686443567276</v>
       </c>
       <c r="H415" t="n">
         <v>285127</v>
@@ -12433,7 +12433,7 @@
         <v>0.47749999165535</v>
       </c>
       <c r="G416" t="n">
-        <v>0.366877228021622</v>
+        <v>0.366877198219299</v>
       </c>
       <c r="H416" t="n">
         <v>398147</v>
@@ -12520,7 +12520,7 @@
         <v>0.468400001525879</v>
       </c>
       <c r="G419" t="n">
-        <v>0.359885364770889</v>
+        <v>0.359885394573212</v>
       </c>
       <c r="H419" t="n">
         <v>222703</v>
@@ -12549,7 +12549,7 @@
         <v>0.468400001525879</v>
       </c>
       <c r="G420" t="n">
-        <v>0.359885364770889</v>
+        <v>0.359885394573212</v>
       </c>
       <c r="H420" t="n">
         <v>149805</v>
@@ -12578,7 +12578,7 @@
         <v>0.467500001192093</v>
       </c>
       <c r="G421" t="n">
-        <v>0.359193950891495</v>
+        <v>0.35919389128685</v>
       </c>
       <c r="H421" t="n">
         <v>252312</v>
@@ -12607,7 +12607,7 @@
         <v>0.479699999094009</v>
       </c>
       <c r="G422" t="n">
-        <v>0.368567526340485</v>
+        <v>0.368567496538162</v>
       </c>
       <c r="H422" t="n">
         <v>376085</v>
@@ -12636,7 +12636,7 @@
         <v>0.484200000762939</v>
       </c>
       <c r="G423" t="n">
-        <v>0.372025012969971</v>
+        <v>0.372025042772293</v>
       </c>
       <c r="H423" t="n">
         <v>194596</v>
@@ -12723,7 +12723,7 @@
         <v>0.510999977588654</v>
       </c>
       <c r="G426" t="n">
-        <v>0.392616242170334</v>
+        <v>0.392616182565689</v>
       </c>
       <c r="H426" t="n">
         <v>2496160</v>
@@ -12752,7 +12752,7 @@
         <v>0.527999997138977</v>
       </c>
       <c r="G427" t="n">
-        <v>0.405677795410156</v>
+        <v>0.405677855014801</v>
       </c>
       <c r="H427" t="n">
         <v>3355365</v>
@@ -12810,7 +12810,7 @@
         <v>0.546000003814697</v>
       </c>
       <c r="G429" t="n">
-        <v>0.419507801532745</v>
+        <v>0.419507741928101</v>
       </c>
       <c r="H429" t="n">
         <v>2853310</v>
@@ -12839,7 +12839,7 @@
         <v>0.516499996185303</v>
       </c>
       <c r="G430" t="n">
-        <v>0.396842062473297</v>
+        <v>0.396842032670975</v>
       </c>
       <c r="H430" t="n">
         <v>1142932</v>
@@ -12868,7 +12868,7 @@
         <v>0.537999987602234</v>
       </c>
       <c r="G431" t="n">
-        <v>0.413361102342606</v>
+        <v>0.413361132144928</v>
       </c>
       <c r="H431" t="n">
         <v>2605273</v>
@@ -12897,7 +12897,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G432" t="n">
-        <v>0.422581046819687</v>
+        <v>0.422581076622009</v>
       </c>
       <c r="H432" t="n">
         <v>994448</v>
@@ -12926,7 +12926,7 @@
         <v>0.543500006198883</v>
       </c>
       <c r="G433" t="n">
-        <v>0.417586922645569</v>
+        <v>0.417586892843246</v>
       </c>
       <c r="H433" t="n">
         <v>1375944</v>
@@ -12955,7 +12955,7 @@
         <v>0.555000007152557</v>
       </c>
       <c r="G434" t="n">
-        <v>0.426422715187073</v>
+        <v>0.426422744989395</v>
       </c>
       <c r="H434" t="n">
         <v>1453142</v>
@@ -12984,7 +12984,7 @@
         <v>0.550999999046326</v>
       </c>
       <c r="G435" t="n">
-        <v>0.423349440097809</v>
+        <v>0.423349410295486</v>
       </c>
       <c r="H435" t="n">
         <v>873449</v>
@@ -13013,7 +13013,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G436" t="n">
-        <v>0.422581046819687</v>
+        <v>0.422581076622009</v>
       </c>
       <c r="H436" t="n">
         <v>337178</v>
@@ -13071,7 +13071,7 @@
         <v>0.543500006198883</v>
       </c>
       <c r="G438" t="n">
-        <v>0.417586922645569</v>
+        <v>0.417586892843246</v>
       </c>
       <c r="H438" t="n">
         <v>184635</v>
@@ -13100,7 +13100,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G439" t="n">
-        <v>0.422581046819687</v>
+        <v>0.422581076622009</v>
       </c>
       <c r="H439" t="n">
         <v>425997</v>
@@ -13129,7 +13129,7 @@
         <v>0.556999981403351</v>
       </c>
       <c r="G440" t="n">
-        <v>0.427959352731705</v>
+        <v>0.427959322929382</v>
       </c>
       <c r="H440" t="n">
         <v>2218199</v>
@@ -13158,7 +13158,7 @@
         <v>0.568499982357025</v>
       </c>
       <c r="G441" t="n">
-        <v>0.436795145273209</v>
+        <v>0.436795175075531</v>
       </c>
       <c r="H441" t="n">
         <v>2440736</v>
@@ -13187,7 +13187,7 @@
         <v>0.563499987125397</v>
       </c>
       <c r="G442" t="n">
-        <v>0.43295356631279</v>
+        <v>0.432953476905823</v>
       </c>
       <c r="H442" t="n">
         <v>787757</v>
@@ -13216,7 +13216,7 @@
         <v>0.58950001001358</v>
       </c>
       <c r="G443" t="n">
-        <v>0.452930092811584</v>
+        <v>0.452930063009262</v>
       </c>
       <c r="H443" t="n">
         <v>2357886</v>
@@ -13332,7 +13332,7 @@
         <v>0.626500010490417</v>
       </c>
       <c r="G447" t="n">
-        <v>0.48135831952095</v>
+        <v>0.481358289718628</v>
       </c>
       <c r="H447" t="n">
         <v>1771102</v>
@@ -13361,7 +13361,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G448" t="n">
-        <v>0.522463858127594</v>
+        <v>0.522463917732239</v>
       </c>
       <c r="H448" t="n">
         <v>3477294</v>
@@ -13390,7 +13390,7 @@
         <v>0.670499980449677</v>
       </c>
       <c r="G449" t="n">
-        <v>0.515164732933044</v>
+        <v>0.5151646733284</v>
       </c>
       <c r="H449" t="n">
         <v>3190686</v>
@@ -13419,7 +13419,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G450" t="n">
-        <v>0.505560576915741</v>
+        <v>0.505560636520386</v>
       </c>
       <c r="H450" t="n">
         <v>1135116</v>
@@ -13448,7 +13448,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G451" t="n">
-        <v>0.507097244262695</v>
+        <v>0.50709730386734</v>
       </c>
       <c r="H451" t="n">
         <v>1742431</v>
@@ -13477,7 +13477,7 @@
         <v>0.671000003814697</v>
       </c>
       <c r="G452" t="n">
-        <v>0.515548825263977</v>
+        <v>0.515548884868622</v>
       </c>
       <c r="H452" t="n">
         <v>1985878</v>
@@ -13506,7 +13506,7 @@
         <v>0.654999971389771</v>
       </c>
       <c r="G453" t="n">
-        <v>0.503255605697632</v>
+        <v>0.503255665302277</v>
       </c>
       <c r="H453" t="n">
         <v>624801</v>
@@ -13535,7 +13535,7 @@
         <v>0.637499988079071</v>
       </c>
       <c r="G454" t="n">
-        <v>0.489809960126877</v>
+        <v>0.48980987071991</v>
       </c>
       <c r="H454" t="n">
         <v>1206247</v>
@@ -13564,7 +13564,7 @@
         <v>0.625</v>
       </c>
       <c r="G455" t="n">
-        <v>0.480205714702606</v>
+        <v>0.480205684900284</v>
       </c>
       <c r="H455" t="n">
         <v>1419629</v>
@@ -13651,7 +13651,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G458" t="n">
-        <v>0.499413937330246</v>
+        <v>0.499413967132568</v>
       </c>
       <c r="H458" t="n">
         <v>792662</v>
@@ -13680,7 +13680,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G459" t="n">
-        <v>0.491730630397797</v>
+        <v>0.491730719804764</v>
       </c>
       <c r="H459" t="n">
         <v>2176421</v>
@@ -13738,7 +13738,7 @@
         <v>0.629499971866608</v>
       </c>
       <c r="G461" t="n">
-        <v>0.483663231134415</v>
+        <v>0.48366317152977</v>
       </c>
       <c r="H461" t="n">
         <v>655932</v>
@@ -13767,7 +13767,7 @@
         <v>0.625</v>
       </c>
       <c r="G462" t="n">
-        <v>0.480205714702606</v>
+        <v>0.480205684900284</v>
       </c>
       <c r="H462" t="n">
         <v>797115</v>
@@ -13854,7 +13854,7 @@
         <v>0.637499988079071</v>
       </c>
       <c r="G465" t="n">
-        <v>0.489809960126877</v>
+        <v>0.48980987071991</v>
       </c>
       <c r="H465" t="n">
         <v>365015</v>
@@ -13883,7 +13883,7 @@
         <v>0.625</v>
       </c>
       <c r="G466" t="n">
-        <v>0.480205714702606</v>
+        <v>0.480205684900284</v>
       </c>
       <c r="H466" t="n">
         <v>314448</v>
@@ -13912,7 +13912,7 @@
         <v>0.644500017166138</v>
       </c>
       <c r="G467" t="n">
-        <v>0.49518820643425</v>
+        <v>0.495188146829605</v>
       </c>
       <c r="H467" t="n">
         <v>1017227</v>
@@ -13941,7 +13941,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G468" t="n">
-        <v>0.490194082260132</v>
+        <v>0.490193992853165</v>
       </c>
       <c r="H468" t="n">
         <v>625767</v>
@@ -13970,7 +13970,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G469" t="n">
-        <v>0.491730630397797</v>
+        <v>0.491730719804764</v>
       </c>
       <c r="H469" t="n">
         <v>617988</v>
@@ -13999,7 +13999,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G470" t="n">
-        <v>0.491730630397797</v>
+        <v>0.491730719804764</v>
       </c>
       <c r="H470" t="n">
         <v>957316</v>
@@ -14057,7 +14057,7 @@
         <v>0.70550000667572</v>
       </c>
       <c r="G472" t="n">
-        <v>0.542056322097778</v>
+        <v>0.542056202888489</v>
       </c>
       <c r="H472" t="n">
         <v>3198240</v>
@@ -14144,7 +14144,7 @@
         <v>0.781000018119812</v>
       </c>
       <c r="G475" t="n">
-        <v>0.600065171718597</v>
+        <v>0.600065112113953</v>
       </c>
       <c r="H475" t="n">
         <v>2922756</v>
@@ -14173,7 +14173,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G476" t="n">
-        <v>0.5823934674263</v>
+        <v>0.58239358663559</v>
       </c>
       <c r="H476" t="n">
         <v>2846001</v>
@@ -14202,7 +14202,7 @@
         <v>0.744499981403351</v>
       </c>
       <c r="G477" t="n">
-        <v>0.572021126747131</v>
+        <v>0.572021067142487</v>
       </c>
       <c r="H477" t="n">
         <v>2189782</v>
@@ -14289,7 +14289,7 @@
         <v>0.717499971389771</v>
       </c>
       <c r="G480" t="n">
-        <v>0.551276206970215</v>
+        <v>0.55127614736557</v>
       </c>
       <c r="H480" t="n">
         <v>2103563</v>
@@ -14318,7 +14318,7 @@
         <v>0.709500014781952</v>
       </c>
       <c r="G481" t="n">
-        <v>0.545129597187042</v>
+        <v>0.545129537582397</v>
       </c>
       <c r="H481" t="n">
         <v>3010065</v>
@@ -14376,7 +14376,7 @@
         <v>0.736500024795532</v>
       </c>
       <c r="G483" t="n">
-        <v>0.565874457359314</v>
+        <v>0.565874397754669</v>
       </c>
       <c r="H483" t="n">
         <v>1180805</v>
@@ -14405,7 +14405,7 @@
         <v>0.750999987125397</v>
       </c>
       <c r="G484" t="n">
-        <v>0.577015161514282</v>
+        <v>0.577015221118927</v>
       </c>
       <c r="H484" t="n">
         <v>1937631</v>
@@ -14521,7 +14521,7 @@
         <v>0.809499979019165</v>
       </c>
       <c r="G488" t="n">
-        <v>0.621962487697601</v>
+        <v>0.621962428092957</v>
       </c>
       <c r="H488" t="n">
         <v>2987472</v>
@@ -14550,7 +14550,7 @@
         <v>0.807500004768372</v>
       </c>
       <c r="G489" t="n">
-        <v>0.620425879955292</v>
+        <v>0.620425820350647</v>
       </c>
       <c r="H489" t="n">
         <v>1738954</v>
@@ -14579,7 +14579,7 @@
         <v>0.819500029087067</v>
       </c>
       <c r="G490" t="n">
-        <v>0.629645884037018</v>
+        <v>0.629645824432373</v>
       </c>
       <c r="H490" t="n">
         <v>1071537</v>
@@ -14666,7 +14666,7 @@
         <v>0.757000029087067</v>
       </c>
       <c r="G493" t="n">
-        <v>0.581625282764435</v>
+        <v>0.58162522315979</v>
       </c>
       <c r="H493" t="n">
         <v>2396861</v>
@@ -14695,7 +14695,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G494" t="n">
-        <v>0.560880243778229</v>
+        <v>0.560880303382874</v>
       </c>
       <c r="H494" t="n">
         <v>1301066</v>
@@ -14753,7 +14753,7 @@
         <v>0.750999987125397</v>
       </c>
       <c r="G496" t="n">
-        <v>0.577015161514282</v>
+        <v>0.577015221118927</v>
       </c>
       <c r="H496" t="n">
         <v>931319</v>
@@ -14811,7 +14811,7 @@
         <v>0.806500017642975</v>
       </c>
       <c r="G498" t="n">
-        <v>0.619657576084137</v>
+        <v>0.619657516479492</v>
       </c>
       <c r="H498" t="n">
         <v>1410976</v>
@@ -15072,7 +15072,7 @@
         <v>0.750999987125397</v>
       </c>
       <c r="G507" t="n">
-        <v>0.577015161514282</v>
+        <v>0.577015221118927</v>
       </c>
       <c r="H507" t="n">
         <v>749146</v>
@@ -15130,7 +15130,7 @@
         <v>0.737999975681305</v>
       </c>
       <c r="G509" t="n">
-        <v>0.567026913166046</v>
+        <v>0.567026972770691</v>
       </c>
       <c r="H509" t="n">
         <v>744111</v>
@@ -15217,7 +15217,7 @@
         <v>0.735000014305115</v>
       </c>
       <c r="G512" t="n">
-        <v>0.564722001552582</v>
+        <v>0.564721941947937</v>
       </c>
       <c r="H512" t="n">
         <v>1031254</v>
@@ -15246,7 +15246,7 @@
         <v>0.732999980449677</v>
       </c>
       <c r="G513" t="n">
-        <v>0.563185334205627</v>
+        <v>0.563185274600983</v>
       </c>
       <c r="H513" t="n">
         <v>378186</v>
@@ -15304,7 +15304,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G515" t="n">
-        <v>0.5823934674263</v>
+        <v>0.58239358663559</v>
       </c>
       <c r="H515" t="n">
         <v>912363</v>
@@ -15362,7 +15362,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G517" t="n">
-        <v>0.583930194377899</v>
+        <v>0.583930134773254</v>
       </c>
       <c r="H517" t="n">
         <v>1370057</v>
@@ -15420,7 +15420,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G519" t="n">
-        <v>0.587003529071808</v>
+        <v>0.587003469467163</v>
       </c>
       <c r="H519" t="n">
         <v>606635</v>
@@ -15449,7 +15449,7 @@
         <v>0.787000000476837</v>
       </c>
       <c r="G520" t="n">
-        <v>0.604675114154816</v>
+        <v>0.604675054550171</v>
       </c>
       <c r="H520" t="n">
         <v>1157691</v>
@@ -15478,7 +15478,7 @@
         <v>0.819000005722046</v>
       </c>
       <c r="G521" t="n">
-        <v>0.629261553287506</v>
+        <v>0.629261612892151</v>
       </c>
       <c r="H521" t="n">
         <v>1461439</v>
@@ -15507,7 +15507,7 @@
         <v>0.805000007152557</v>
       </c>
       <c r="G522" t="n">
-        <v>0.61850506067276</v>
+        <v>0.618505001068115</v>
       </c>
       <c r="H522" t="n">
         <v>1651802</v>
@@ -15652,7 +15652,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G527" t="n">
-        <v>0.611590087413788</v>
+        <v>0.611590027809143</v>
       </c>
       <c r="H527" t="n">
         <v>476964</v>
@@ -15681,7 +15681,7 @@
         <v>0.773000001907349</v>
       </c>
       <c r="G528" t="n">
-        <v>0.59391850233078</v>
+        <v>0.593918561935425</v>
       </c>
       <c r="H528" t="n">
         <v>651505</v>
@@ -15710,7 +15710,7 @@
         <v>0.77700001001358</v>
       </c>
       <c r="G529" t="n">
-        <v>0.596991777420044</v>
+        <v>0.596991717815399</v>
       </c>
       <c r="H529" t="n">
         <v>304526</v>
@@ -15797,7 +15797,7 @@
         <v>0.767000019550323</v>
       </c>
       <c r="G532" t="n">
-        <v>0.589308500289917</v>
+        <v>0.589308559894562</v>
       </c>
       <c r="H532" t="n">
         <v>857549</v>
@@ -15826,7 +15826,7 @@
         <v>0.750999987125397</v>
       </c>
       <c r="G533" t="n">
-        <v>0.577015161514282</v>
+        <v>0.577015221118927</v>
       </c>
       <c r="H533" t="n">
         <v>957201</v>
@@ -15884,7 +15884,7 @@
         <v>0.735000014305115</v>
       </c>
       <c r="G535" t="n">
-        <v>0.564722001552582</v>
+        <v>0.564721941947937</v>
       </c>
       <c r="H535" t="n">
         <v>661843</v>
@@ -15913,7 +15913,7 @@
         <v>0.721000015735626</v>
       </c>
       <c r="G536" t="n">
-        <v>0.553965330123901</v>
+        <v>0.553965389728546</v>
       </c>
       <c r="H536" t="n">
         <v>1092957</v>
@@ -15942,7 +15942,7 @@
         <v>0.700999975204468</v>
       </c>
       <c r="G537" t="n">
-        <v>0.538598716259003</v>
+        <v>0.538598656654358</v>
       </c>
       <c r="H537" t="n">
         <v>1837563</v>
@@ -15971,7 +15971,7 @@
         <v>0.725000023841858</v>
       </c>
       <c r="G538" t="n">
-        <v>0.55703866481781</v>
+        <v>0.557038724422455</v>
       </c>
       <c r="H538" t="n">
         <v>575621</v>
@@ -16029,7 +16029,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G540" t="n">
-        <v>0.524000465869904</v>
+        <v>0.524000525474548</v>
       </c>
       <c r="H540" t="n">
         <v>1040600</v>
@@ -16058,7 +16058,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G541" t="n">
-        <v>0.537830412387848</v>
+        <v>0.537830471992493</v>
       </c>
       <c r="H541" t="n">
         <v>573646</v>
@@ -16087,7 +16087,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G542" t="n">
-        <v>0.524000465869904</v>
+        <v>0.524000525474548</v>
       </c>
       <c r="H542" t="n">
         <v>666277</v>
@@ -16116,7 +16116,7 @@
         <v>0.712999999523163</v>
       </c>
       <c r="G543" t="n">
-        <v>0.547818660736084</v>
+        <v>0.547818720340729</v>
       </c>
       <c r="H543" t="n">
         <v>339439</v>
@@ -16145,7 +16145,7 @@
         <v>0.693000018596649</v>
       </c>
       <c r="G544" t="n">
-        <v>0.53245210647583</v>
+        <v>0.532452166080475</v>
       </c>
       <c r="H544" t="n">
         <v>519204</v>
@@ -16203,7 +16203,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G546" t="n">
-        <v>0.527073800563812</v>
+        <v>0.527073919773102</v>
       </c>
       <c r="H546" t="n">
         <v>491772</v>
@@ -16232,7 +16232,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G547" t="n">
-        <v>0.522463858127594</v>
+        <v>0.522463917732239</v>
       </c>
       <c r="H547" t="n">
         <v>306515</v>
@@ -16261,7 +16261,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G548" t="n">
-        <v>0.522463858127594</v>
+        <v>0.522463917732239</v>
       </c>
       <c r="H548" t="n">
         <v>170513</v>
@@ -16290,7 +16290,7 @@
         <v>0.693000018596649</v>
       </c>
       <c r="G549" t="n">
-        <v>0.53245210647583</v>
+        <v>0.532452166080475</v>
       </c>
       <c r="H549" t="n">
         <v>879246</v>
@@ -16319,7 +16319,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G550" t="n">
-        <v>0.537830412387848</v>
+        <v>0.537830471992493</v>
       </c>
       <c r="H550" t="n">
         <v>523508</v>
@@ -16348,7 +16348,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G551" t="n">
-        <v>0.537830412387848</v>
+        <v>0.537830471992493</v>
       </c>
       <c r="H551" t="n">
         <v>148628</v>
@@ -16377,7 +16377,7 @@
         <v>0.693000018596649</v>
       </c>
       <c r="G552" t="n">
-        <v>0.53245210647583</v>
+        <v>0.532452166080475</v>
       </c>
       <c r="H552" t="n">
         <v>439975</v>
@@ -16464,7 +16464,7 @@
         <v>0.654999971389771</v>
       </c>
       <c r="G555" t="n">
-        <v>0.503255605697632</v>
+        <v>0.503255665302277</v>
       </c>
       <c r="H555" t="n">
         <v>506200</v>
@@ -16493,7 +16493,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G556" t="n">
-        <v>0.505560576915741</v>
+        <v>0.505560636520386</v>
       </c>
       <c r="H556" t="n">
         <v>345792</v>
@@ -16609,7 +16609,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G560" t="n">
-        <v>0.530147075653076</v>
+        <v>0.530147135257721</v>
       </c>
       <c r="H560" t="n">
         <v>124108</v>
@@ -16667,7 +16667,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G562" t="n">
-        <v>0.519390523433685</v>
+        <v>0.51939058303833</v>
       </c>
       <c r="H562" t="n">
         <v>496974</v>
@@ -16696,7 +16696,7 @@
         <v>0.683000028133392</v>
       </c>
       <c r="G563" t="n">
-        <v>0.524768888950348</v>
+        <v>0.524768829345703</v>
       </c>
       <c r="H563" t="n">
         <v>404459</v>
@@ -16725,7 +16725,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G564" t="n">
-        <v>0.527073800563812</v>
+        <v>0.527073919773102</v>
       </c>
       <c r="H564" t="n">
         <v>395488</v>
@@ -16754,7 +16754,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G565" t="n">
-        <v>0.524000465869904</v>
+        <v>0.524000525474548</v>
       </c>
       <c r="H565" t="n">
         <v>248564</v>
@@ -16812,7 +16812,7 @@
         <v>0.757000029087067</v>
       </c>
       <c r="G567" t="n">
-        <v>0.581625282764435</v>
+        <v>0.58162522315979</v>
       </c>
       <c r="H567" t="n">
         <v>1402702</v>
@@ -16870,7 +16870,7 @@
         <v>0.652999997138977</v>
       </c>
       <c r="G569" t="n">
-        <v>0.501718938350677</v>
+        <v>0.501718997955322</v>
       </c>
       <c r="H569" t="n">
         <v>1883764</v>
@@ -16899,7 +16899,7 @@
         <v>0.640999972820282</v>
       </c>
       <c r="G570" t="n">
-        <v>0.492498964071274</v>
+        <v>0.492499023675919</v>
       </c>
       <c r="H570" t="n">
         <v>810346</v>
@@ -16957,7 +16957,7 @@
         <v>0.625</v>
       </c>
       <c r="G572" t="n">
-        <v>0.480205714702606</v>
+        <v>0.480205684900284</v>
       </c>
       <c r="H572" t="n">
         <v>400786</v>
@@ -17073,7 +17073,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G576" t="n">
-        <v>0.471754193305969</v>
+        <v>0.471754163503647</v>
       </c>
       <c r="H576" t="n">
         <v>626363</v>
@@ -17102,7 +17102,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G577" t="n">
-        <v>0.491730630397797</v>
+        <v>0.491730719804764</v>
       </c>
       <c r="H577" t="n">
         <v>415872</v>
@@ -17131,7 +17131,7 @@
         <v>0.615000009536743</v>
       </c>
       <c r="G578" t="n">
-        <v>0.472522467374802</v>
+        <v>0.472522497177124</v>
       </c>
       <c r="H578" t="n">
         <v>993314</v>
@@ -17160,7 +17160,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G579" t="n">
-        <v>0.468680828809738</v>
+        <v>0.468680888414383</v>
       </c>
       <c r="H579" t="n">
         <v>303534</v>
@@ -17247,7 +17247,7 @@
         <v>0.626999974250793</v>
       </c>
       <c r="G582" t="n">
-        <v>0.481742382049561</v>
+        <v>0.481742411851883</v>
       </c>
       <c r="H582" t="n">
         <v>175022</v>
@@ -17276,7 +17276,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G583" t="n">
-        <v>0.480974048376083</v>
+        <v>0.480974137783051</v>
       </c>
       <c r="H583" t="n">
         <v>726387</v>
@@ -17305,7 +17305,7 @@
         <v>0.629000008106232</v>
       </c>
       <c r="G584" t="n">
-        <v>0.48327898979187</v>
+        <v>0.483279019594193</v>
       </c>
       <c r="H584" t="n">
         <v>110289</v>
@@ -17334,7 +17334,7 @@
         <v>0.623000025749207</v>
       </c>
       <c r="G585" t="n">
-        <v>0.478669077157974</v>
+        <v>0.478669136762619</v>
       </c>
       <c r="H585" t="n">
         <v>134620</v>
@@ -17363,7 +17363,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G586" t="n">
-        <v>0.470217436552048</v>
+        <v>0.47021746635437</v>
       </c>
       <c r="H586" t="n">
         <v>429416</v>
@@ -17392,7 +17392,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G587" t="n">
-        <v>0.468680828809738</v>
+        <v>0.468680888414383</v>
       </c>
       <c r="H587" t="n">
         <v>511078</v>
@@ -17450,7 +17450,7 @@
         <v>0.60699999332428</v>
       </c>
       <c r="G589" t="n">
-        <v>0.466375827789307</v>
+        <v>0.466375797986984</v>
       </c>
       <c r="H589" t="n">
         <v>484930</v>
@@ -17479,7 +17479,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G590" t="n">
-        <v>0.470217436552048</v>
+        <v>0.47021746635437</v>
       </c>
       <c r="H590" t="n">
         <v>265449</v>
@@ -17508,7 +17508,7 @@
         <v>0.605000019073486</v>
       </c>
       <c r="G591" t="n">
-        <v>0.464839190244675</v>
+        <v>0.464839220046997</v>
       </c>
       <c r="H591" t="n">
         <v>109147</v>
@@ -17537,7 +17537,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G592" t="n">
-        <v>0.470217436552048</v>
+        <v>0.47021746635437</v>
       </c>
       <c r="H592" t="n">
         <v>453837</v>
@@ -17566,7 +17566,7 @@
         <v>0.601000010967255</v>
       </c>
       <c r="G593" t="n">
-        <v>0.461765855550766</v>
+        <v>0.461765885353088</v>
       </c>
       <c r="H593" t="n">
         <v>247749</v>
@@ -17595,7 +17595,7 @@
         <v>0.601000010967255</v>
       </c>
       <c r="G594" t="n">
-        <v>0.461765855550766</v>
+        <v>0.461765885353088</v>
       </c>
       <c r="H594" t="n">
         <v>367678</v>
@@ -17624,7 +17624,7 @@
         <v>0.634999990463257</v>
       </c>
       <c r="G595" t="n">
-        <v>0.487889051437378</v>
+        <v>0.4878890812397</v>
       </c>
       <c r="H595" t="n">
         <v>672923</v>
@@ -17653,7 +17653,7 @@
         <v>0.634999990463257</v>
       </c>
       <c r="G596" t="n">
-        <v>0.487889051437378</v>
+        <v>0.4878890812397</v>
       </c>
       <c r="H596" t="n">
         <v>683406</v>
@@ -17682,7 +17682,7 @@
         <v>0.625</v>
       </c>
       <c r="G597" t="n">
-        <v>0.480205714702606</v>
+        <v>0.480205684900284</v>
       </c>
       <c r="H597" t="n">
         <v>560249</v>
@@ -17711,7 +17711,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G598" t="n">
-        <v>0.491730630397797</v>
+        <v>0.491730719804764</v>
       </c>
       <c r="H598" t="n">
         <v>313393</v>
@@ -17885,7 +17885,7 @@
         <v>0.561999976634979</v>
       </c>
       <c r="G604" t="n">
-        <v>0.431800991296768</v>
+        <v>0.431800961494446</v>
       </c>
       <c r="H604" t="n">
         <v>386280</v>
@@ -17914,7 +17914,7 @@
         <v>0.555000007152557</v>
       </c>
       <c r="G605" t="n">
-        <v>0.426422715187073</v>
+        <v>0.426422744989395</v>
       </c>
       <c r="H605" t="n">
         <v>455127</v>
@@ -17972,7 +17972,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G607" t="n">
-        <v>0.422581046819687</v>
+        <v>0.422581076622009</v>
       </c>
       <c r="H607" t="n">
         <v>367522</v>
@@ -18001,7 +18001,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G608" t="n">
-        <v>0.424117684364319</v>
+        <v>0.424117714166641</v>
       </c>
       <c r="H608" t="n">
         <v>174759</v>
@@ -18030,7 +18030,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G609" t="n">
-        <v>0.422581046819687</v>
+        <v>0.422581076622009</v>
       </c>
       <c r="H609" t="n">
         <v>93758</v>
@@ -18059,7 +18059,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G610" t="n">
-        <v>0.422581046819687</v>
+        <v>0.422581076622009</v>
       </c>
       <c r="H610" t="n">
         <v>181297</v>
@@ -18088,7 +18088,7 @@
         <v>0.541000008583069</v>
       </c>
       <c r="G611" t="n">
-        <v>0.415666103363037</v>
+        <v>0.415666133165359</v>
       </c>
       <c r="H611" t="n">
         <v>171017</v>
@@ -18117,7 +18117,7 @@
         <v>0.527999997138977</v>
       </c>
       <c r="G612" t="n">
-        <v>0.405677795410156</v>
+        <v>0.405677855014801</v>
       </c>
       <c r="H612" t="n">
         <v>270241</v>
@@ -18146,7 +18146,7 @@
         <v>0.497999995946884</v>
       </c>
       <c r="G613" t="n">
-        <v>0.382627993822098</v>
+        <v>0.382627964019775</v>
       </c>
       <c r="H613" t="n">
         <v>786586</v>
@@ -18175,7 +18175,7 @@
         <v>0.493499994277954</v>
       </c>
       <c r="G614" t="n">
-        <v>0.379170447587967</v>
+        <v>0.379170477390289</v>
       </c>
       <c r="H614" t="n">
         <v>789863</v>
@@ -18233,7 +18233,7 @@
         <v>0.501999974250793</v>
       </c>
       <c r="G616" t="n">
-        <v>0.385701268911362</v>
+        <v>0.385701239109039</v>
       </c>
       <c r="H616" t="n">
         <v>265244</v>
@@ -18262,7 +18262,7 @@
         <v>0.527999997138977</v>
       </c>
       <c r="G617" t="n">
-        <v>0.405677795410156</v>
+        <v>0.405677855014801</v>
       </c>
       <c r="H617" t="n">
         <v>896735</v>
@@ -18291,7 +18291,7 @@
         <v>0.501999974250793</v>
       </c>
       <c r="G618" t="n">
-        <v>0.385701268911362</v>
+        <v>0.385701239109039</v>
       </c>
       <c r="H618" t="n">
         <v>454561</v>
@@ -18320,7 +18320,7 @@
         <v>0.505999982357025</v>
       </c>
       <c r="G619" t="n">
-        <v>0.388774573802948</v>
+        <v>0.388774544000626</v>
       </c>
       <c r="H619" t="n">
         <v>268831</v>
@@ -18349,7 +18349,7 @@
         <v>0.497999995946884</v>
       </c>
       <c r="G620" t="n">
-        <v>0.382627993822098</v>
+        <v>0.382627964019775</v>
       </c>
       <c r="H620" t="n">
         <v>231113</v>
@@ -18436,7 +18436,7 @@
         <v>0.501999974250793</v>
       </c>
       <c r="G623" t="n">
-        <v>0.385701268911362</v>
+        <v>0.385701239109039</v>
       </c>
       <c r="H623" t="n">
         <v>193213</v>
@@ -18465,7 +18465,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G624" t="n">
-        <v>0.376481354236603</v>
+        <v>0.37648132443428</v>
       </c>
       <c r="H624" t="n">
         <v>343746</v>
@@ -18494,7 +18494,7 @@
         <v>0.477999985218048</v>
       </c>
       <c r="G625" t="n">
-        <v>0.367261379957199</v>
+        <v>0.367261320352554</v>
       </c>
       <c r="H625" t="n">
         <v>428299</v>
@@ -18639,7 +18639,7 @@
         <v>0.46900001168251</v>
       </c>
       <c r="G630" t="n">
-        <v>0.360346406698227</v>
+        <v>0.360346436500549</v>
       </c>
       <c r="H630" t="n">
         <v>57708</v>
@@ -18726,7 +18726,7 @@
         <v>0.483500003814697</v>
       </c>
       <c r="G633" t="n">
-        <v>0.371487140655518</v>
+        <v>0.371487200260162</v>
       </c>
       <c r="H633" t="n">
         <v>728009</v>
@@ -18755,7 +18755,7 @@
         <v>0.479000002145767</v>
       </c>
       <c r="G634" t="n">
-        <v>0.368029683828354</v>
+        <v>0.368029713630676</v>
       </c>
       <c r="H634" t="n">
         <v>552999</v>
@@ -18842,7 +18842,7 @@
         <v>0.475499987602234</v>
       </c>
       <c r="G637" t="n">
-        <v>0.365340560674667</v>
+        <v>0.365340530872345</v>
       </c>
       <c r="H637" t="n">
         <v>283820</v>
@@ -18871,7 +18871,7 @@
         <v>0.479000002145767</v>
       </c>
       <c r="G638" t="n">
-        <v>0.368029683828354</v>
+        <v>0.368029713630676</v>
       </c>
       <c r="H638" t="n">
         <v>148498</v>
@@ -18900,7 +18900,7 @@
         <v>0.488000005483627</v>
       </c>
       <c r="G639" t="n">
-        <v>0.374944657087326</v>
+        <v>0.374944627285004</v>
       </c>
       <c r="H639" t="n">
         <v>285837</v>
@@ -18958,7 +18958,7 @@
         <v>0.487500011920929</v>
       </c>
       <c r="G641" t="n">
-        <v>0.374560475349426</v>
+        <v>0.374560505151749</v>
       </c>
       <c r="H641" t="n">
         <v>262393</v>
@@ -18987,7 +18987,7 @@
         <v>0.479000002145767</v>
       </c>
       <c r="G642" t="n">
-        <v>0.368029683828354</v>
+        <v>0.368029713630676</v>
       </c>
       <c r="H642" t="n">
         <v>146480</v>
@@ -19074,7 +19074,7 @@
         <v>0.479000002145767</v>
       </c>
       <c r="G645" t="n">
-        <v>0.368029683828354</v>
+        <v>0.368029713630676</v>
       </c>
       <c r="H645" t="n">
         <v>335219</v>
@@ -19248,7 +19248,7 @@
         <v>0.482499986886978</v>
       </c>
       <c r="G651" t="n">
-        <v>0.37071880698204</v>
+        <v>0.370718866586685</v>
       </c>
       <c r="H651" t="n">
         <v>599958</v>
@@ -19335,7 +19335,7 @@
         <v>0.458999991416931</v>
       </c>
       <c r="G654" t="n">
-        <v>0.352663099765778</v>
+        <v>0.352663069963455</v>
       </c>
       <c r="H654" t="n">
         <v>167442</v>
@@ -19422,7 +19422,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G657" t="n">
-        <v>0.422581046819687</v>
+        <v>0.422581076622009</v>
       </c>
       <c r="H657" t="n">
         <v>1988486</v>
@@ -19451,7 +19451,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G658" t="n">
-        <v>0.411056190729141</v>
+        <v>0.411056131124496</v>
       </c>
       <c r="H658" t="n">
         <v>748133</v>
@@ -19480,7 +19480,7 @@
         <v>0.537999987602234</v>
       </c>
       <c r="G659" t="n">
-        <v>0.413361102342606</v>
+        <v>0.413361132144928</v>
       </c>
       <c r="H659" t="n">
         <v>289639</v>
@@ -19538,7 +19538,7 @@
         <v>0.500999987125397</v>
       </c>
       <c r="G661" t="n">
-        <v>0.384932905435562</v>
+        <v>0.384932935237885</v>
       </c>
       <c r="H661" t="n">
         <v>705239</v>
@@ -19567,7 +19567,7 @@
         <v>0.508000016212463</v>
       </c>
       <c r="G662" t="n">
-        <v>0.390311270952225</v>
+        <v>0.390311241149902</v>
       </c>
       <c r="H662" t="n">
         <v>161920</v>
@@ -19654,7 +19654,7 @@
         <v>0.49549999833107</v>
       </c>
       <c r="G665" t="n">
-        <v>0.380707114934921</v>
+        <v>0.380707144737244</v>
       </c>
       <c r="H665" t="n">
         <v>87542</v>
@@ -19712,7 +19712,7 @@
         <v>0.472000002861023</v>
       </c>
       <c r="G667" t="n">
-        <v>0.362651407718658</v>
+        <v>0.362651377916336</v>
       </c>
       <c r="H667" t="n">
         <v>219387</v>
@@ -19770,7 +19770,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G669" t="n">
-        <v>0.353431463241577</v>
+        <v>0.353431433439255</v>
       </c>
       <c r="H669" t="n">
         <v>160106</v>
@@ -19828,7 +19828,7 @@
         <v>0.449000000953674</v>
       </c>
       <c r="G671" t="n">
-        <v>0.344979852437973</v>
+        <v>0.344979822635651</v>
       </c>
       <c r="H671" t="n">
         <v>92649</v>
@@ -19886,7 +19886,7 @@
         <v>0.462000012397766</v>
       </c>
       <c r="G673" t="n">
-        <v>0.354968100786209</v>
+        <v>0.354968130588531</v>
       </c>
       <c r="H673" t="n">
         <v>244664</v>
@@ -19944,7 +19944,7 @@
         <v>0.477999985218048</v>
       </c>
       <c r="G675" t="n">
-        <v>0.367261379957199</v>
+        <v>0.367261320352554</v>
       </c>
       <c r="H675" t="n">
         <v>289168</v>
@@ -19973,7 +19973,7 @@
         <v>0.474000006914139</v>
       </c>
       <c r="G676" t="n">
-        <v>0.364188075065613</v>
+        <v>0.36418804526329</v>
       </c>
       <c r="H676" t="n">
         <v>199647</v>
@@ -20002,7 +20002,7 @@
         <v>0.472000002861023</v>
       </c>
       <c r="G677" t="n">
-        <v>0.362651407718658</v>
+        <v>0.362651377916336</v>
       </c>
       <c r="H677" t="n">
         <v>149291</v>
@@ -20031,7 +20031,7 @@
         <v>0.465000003576279</v>
       </c>
       <c r="G678" t="n">
-        <v>0.357273042201996</v>
+        <v>0.357273101806641</v>
       </c>
       <c r="H678" t="n">
         <v>104824</v>
@@ -20089,7 +20089,7 @@
         <v>0.441500008106232</v>
       </c>
       <c r="G680" t="n">
-        <v>0.339217364788055</v>
+        <v>0.339217334985733</v>
       </c>
       <c r="H680" t="n">
         <v>343832</v>
@@ -20118,7 +20118,7 @@
         <v>0.421499997377396</v>
       </c>
       <c r="G681" t="n">
-        <v>0.323850750923157</v>
+        <v>0.323850780725479</v>
       </c>
       <c r="H681" t="n">
         <v>724693</v>
@@ -20234,7 +20234,7 @@
         <v>0.526000022888184</v>
       </c>
       <c r="G685" t="n">
-        <v>0.404141157865524</v>
+        <v>0.404141187667847</v>
       </c>
       <c r="H685" t="n">
         <v>2064502</v>
@@ -20350,7 +20350,7 @@
         <v>0.523000001907349</v>
       </c>
       <c r="G689" t="n">
-        <v>0.401836216449738</v>
+        <v>0.401836186647415</v>
       </c>
       <c r="H689" t="n">
         <v>415530</v>
@@ -20408,7 +20408,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G691" t="n">
-        <v>0.399531185626984</v>
+        <v>0.399531155824661</v>
       </c>
       <c r="H691" t="n">
         <v>406693</v>
@@ -20553,7 +20553,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G696" t="n">
-        <v>0.399531185626984</v>
+        <v>0.399531155824661</v>
       </c>
       <c r="H696" t="n">
         <v>201598</v>
@@ -20640,7 +20640,7 @@
         <v>0.501999974250793</v>
       </c>
       <c r="G699" t="n">
-        <v>0.385701268911362</v>
+        <v>0.385701239109039</v>
       </c>
       <c r="H699" t="n">
         <v>198124</v>
@@ -20669,7 +20669,7 @@
         <v>0.488999992609024</v>
       </c>
       <c r="G700" t="n">
-        <v>0.375712960958481</v>
+        <v>0.375712990760803</v>
       </c>
       <c r="H700" t="n">
         <v>312921</v>
@@ -20698,7 +20698,7 @@
         <v>0.474500000476837</v>
       </c>
       <c r="G701" t="n">
-        <v>0.36457222700119</v>
+        <v>0.364572197198868</v>
       </c>
       <c r="H701" t="n">
         <v>335266</v>
@@ -20756,7 +20756,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G703" t="n">
-        <v>0.345748156309128</v>
+        <v>0.345748126506805</v>
       </c>
       <c r="H703" t="n">
         <v>491413</v>
@@ -20785,7 +20785,7 @@
         <v>0.456000000238419</v>
       </c>
       <c r="G704" t="n">
-        <v>0.350358098745346</v>
+        <v>0.350358158349991</v>
       </c>
       <c r="H704" t="n">
         <v>221121</v>
@@ -20843,7 +20843,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G706" t="n">
-        <v>0.353431463241577</v>
+        <v>0.353431433439255</v>
       </c>
       <c r="H706" t="n">
         <v>149990</v>
@@ -20901,7 +20901,7 @@
         <v>0.437000006437302</v>
       </c>
       <c r="G708" t="n">
-        <v>0.335759907960892</v>
+        <v>0.335759878158569</v>
       </c>
       <c r="H708" t="n">
         <v>107169</v>
@@ -20930,7 +20930,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G709" t="n">
-        <v>0.337296515703201</v>
+        <v>0.337296545505524</v>
       </c>
       <c r="H709" t="n">
         <v>234804</v>
@@ -20959,7 +20959,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G710" t="n">
-        <v>0.329613238573074</v>
+        <v>0.329613268375397</v>
       </c>
       <c r="H710" t="n">
         <v>223066</v>
@@ -21046,7 +21046,7 @@
         <v>0.431499987840652</v>
       </c>
       <c r="G713" t="n">
-        <v>0.331534057855606</v>
+        <v>0.331534028053284</v>
       </c>
       <c r="H713" t="n">
         <v>307404</v>
@@ -21133,7 +21133,7 @@
         <v>0.415499985218048</v>
       </c>
       <c r="G716" t="n">
-        <v>0.319240778684616</v>
+        <v>0.319240808486938</v>
       </c>
       <c r="H716" t="n">
         <v>424195</v>
@@ -21162,7 +21162,7 @@
         <v>0.425500005483627</v>
       </c>
       <c r="G717" t="n">
-        <v>0.326924085617065</v>
+        <v>0.326924115419388</v>
       </c>
       <c r="H717" t="n">
         <v>358227</v>
@@ -21307,7 +21307,7 @@
         <v>0.425500005483627</v>
       </c>
       <c r="G722" t="n">
-        <v>0.326924085617065</v>
+        <v>0.326924115419388</v>
       </c>
       <c r="H722" t="n">
         <v>316862</v>
@@ -21510,7 +21510,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G729" t="n">
-        <v>0.327308237552643</v>
+        <v>0.327308267354965</v>
       </c>
       <c r="H729" t="n">
         <v>208641</v>
@@ -21539,7 +21539,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G730" t="n">
-        <v>0.329613238573074</v>
+        <v>0.329613268375397</v>
       </c>
       <c r="H730" t="n">
         <v>432947</v>
@@ -21568,7 +21568,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G731" t="n">
-        <v>0.329613238573074</v>
+        <v>0.329613268375397</v>
       </c>
       <c r="H731" t="n">
         <v>137721</v>
@@ -21655,7 +21655,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G734" t="n">
-        <v>0.324234932661057</v>
+        <v>0.324234962463379</v>
       </c>
       <c r="H734" t="n">
         <v>325336</v>
@@ -21771,7 +21771,7 @@
         <v>0.391999989748001</v>
       </c>
       <c r="G738" t="n">
-        <v>0.301185041666031</v>
+        <v>0.301185011863708</v>
       </c>
       <c r="H738" t="n">
         <v>403644</v>
@@ -21829,7 +21829,7 @@
         <v>0.390500009059906</v>
       </c>
       <c r="G740" t="n">
-        <v>0.300032585859299</v>
+        <v>0.300032556056976</v>
       </c>
       <c r="H740" t="n">
         <v>241360</v>
@@ -21858,7 +21858,7 @@
         <v>0.386500000953674</v>
       </c>
       <c r="G741" t="n">
-        <v>0.29695925116539</v>
+        <v>0.296959280967712</v>
       </c>
       <c r="H741" t="n">
         <v>323948</v>
@@ -22061,7 +22061,7 @@
         <v>0.420500010251999</v>
       </c>
       <c r="G748" t="n">
-        <v>0.323082447052002</v>
+        <v>0.32308241724968</v>
       </c>
       <c r="H748" t="n">
         <v>251745</v>
@@ -22090,7 +22090,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G749" t="n">
-        <v>0.324234932661057</v>
+        <v>0.324234962463379</v>
       </c>
       <c r="H749" t="n">
         <v>251151</v>
@@ -22148,7 +22148,7 @@
         <v>0.400999993085861</v>
       </c>
       <c r="G751" t="n">
-        <v>0.308100014925003</v>
+        <v>0.308100044727325</v>
       </c>
       <c r="H751" t="n">
         <v>202896</v>
@@ -22177,7 +22177,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G752" t="n">
-        <v>0.307331681251526</v>
+        <v>0.307331711053848</v>
       </c>
       <c r="H752" t="n">
         <v>129595</v>
@@ -22235,7 +22235,7 @@
         <v>0.399500012397766</v>
       </c>
       <c r="G754" t="n">
-        <v>0.306947529315948</v>
+        <v>0.306947559118271</v>
       </c>
       <c r="H754" t="n">
         <v>401419</v>
@@ -22264,7 +22264,7 @@
         <v>0.409500002861023</v>
       </c>
       <c r="G755" t="n">
-        <v>0.314630776643753</v>
+        <v>0.314630806446075</v>
       </c>
       <c r="H755" t="n">
         <v>287096</v>
@@ -22293,7 +22293,7 @@
         <v>0.402500003576279</v>
       </c>
       <c r="G756" t="n">
-        <v>0.30925253033638</v>
+        <v>0.309252500534058</v>
       </c>
       <c r="H756" t="n">
         <v>76449</v>
@@ -22322,7 +22322,7 @@
         <v>0.39750000834465</v>
       </c>
       <c r="G757" t="n">
-        <v>0.305410832166672</v>
+        <v>0.305410861968994</v>
       </c>
       <c r="H757" t="n">
         <v>115100</v>
@@ -22351,7 +22351,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G758" t="n">
-        <v>0.307331681251526</v>
+        <v>0.307331711053848</v>
       </c>
       <c r="H758" t="n">
         <v>113770</v>
@@ -22438,7 +22438,7 @@
         <v>0.396499991416931</v>
       </c>
       <c r="G761" t="n">
-        <v>0.304642498493195</v>
+        <v>0.304642558097839</v>
       </c>
       <c r="H761" t="n">
         <v>131300</v>
@@ -22467,7 +22467,7 @@
         <v>0.394499987363815</v>
       </c>
       <c r="G762" t="n">
-        <v>0.303105890750885</v>
+        <v>0.30310583114624</v>
       </c>
       <c r="H762" t="n">
         <v>146968</v>
@@ -22525,7 +22525,7 @@
         <v>0.400999993085861</v>
       </c>
       <c r="G764" t="n">
-        <v>0.308100014925003</v>
+        <v>0.308100044727325</v>
       </c>
       <c r="H764" t="n">
         <v>349318</v>
@@ -22554,7 +22554,7 @@
         <v>0.405000001192093</v>
       </c>
       <c r="G765" t="n">
-        <v>0.311173349618912</v>
+        <v>0.311173319816589</v>
       </c>
       <c r="H765" t="n">
         <v>718374</v>
@@ -22612,7 +22612,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G767" t="n">
-        <v>0.344211518764496</v>
+        <v>0.344211488962173</v>
       </c>
       <c r="H767" t="n">
         <v>469829</v>
@@ -22641,7 +22641,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G768" t="n">
-        <v>0.345748156309128</v>
+        <v>0.345748126506805</v>
       </c>
       <c r="H768" t="n">
         <v>479201</v>
@@ -22728,7 +22728,7 @@
         <v>0.465999990701675</v>
       </c>
       <c r="G771" t="n">
-        <v>0.358041435480118</v>
+        <v>0.358041405677795</v>
       </c>
       <c r="H771" t="n">
         <v>281269</v>
@@ -22757,7 +22757,7 @@
         <v>0.46900001168251</v>
       </c>
       <c r="G772" t="n">
-        <v>0.360346406698227</v>
+        <v>0.360346436500549</v>
       </c>
       <c r="H772" t="n">
         <v>115767</v>
@@ -22786,7 +22786,7 @@
         <v>0.463499993085861</v>
       </c>
       <c r="G773" t="n">
-        <v>0.356120616197586</v>
+        <v>0.356120556592941</v>
       </c>
       <c r="H773" t="n">
         <v>419176</v>
@@ -22815,7 +22815,7 @@
         <v>0.469500005245209</v>
       </c>
       <c r="G774" t="n">
-        <v>0.360730558633804</v>
+        <v>0.360730588436127</v>
       </c>
       <c r="H774" t="n">
         <v>336791</v>
@@ -22844,7 +22844,7 @@
         <v>0.46900001168251</v>
       </c>
       <c r="G775" t="n">
-        <v>0.360346406698227</v>
+        <v>0.360346436500549</v>
       </c>
       <c r="H775" t="n">
         <v>28576</v>
@@ -22873,7 +22873,7 @@
         <v>0.467500001192093</v>
       </c>
       <c r="G776" t="n">
-        <v>0.359193950891495</v>
+        <v>0.35919389128685</v>
       </c>
       <c r="H776" t="n">
         <v>287740</v>
@@ -22989,7 +22989,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G780" t="n">
-        <v>0.353431463241577</v>
+        <v>0.353431433439255</v>
       </c>
       <c r="H780" t="n">
         <v>99529</v>
@@ -23018,7 +23018,7 @@
         <v>0.46900001168251</v>
       </c>
       <c r="G781" t="n">
-        <v>0.360346406698227</v>
+        <v>0.360346436500549</v>
       </c>
       <c r="H781" t="n">
         <v>166707</v>
@@ -23047,7 +23047,7 @@
         <v>0.462999999523163</v>
       </c>
       <c r="G782" t="n">
-        <v>0.355736404657364</v>
+        <v>0.355736434459686</v>
       </c>
       <c r="H782" t="n">
         <v>103388</v>
@@ -23076,7 +23076,7 @@
         <v>0.463499993085861</v>
       </c>
       <c r="G783" t="n">
-        <v>0.356120616197586</v>
+        <v>0.356120556592941</v>
       </c>
       <c r="H783" t="n">
         <v>143503</v>
@@ -23105,7 +23105,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G784" t="n">
-        <v>0.353431463241577</v>
+        <v>0.353431433439255</v>
       </c>
       <c r="H784" t="n">
         <v>27296</v>
@@ -23163,7 +23163,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G786" t="n">
-        <v>0.353431463241577</v>
+        <v>0.353431433439255</v>
       </c>
       <c r="H786" t="n">
         <v>382158</v>
@@ -23366,7 +23366,7 @@
         <v>0.487500011920929</v>
       </c>
       <c r="G793" t="n">
-        <v>0.374560475349426</v>
+        <v>0.374560505151749</v>
       </c>
       <c r="H793" t="n">
         <v>146653</v>
@@ -23424,7 +23424,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G795" t="n">
-        <v>0.376481354236603</v>
+        <v>0.37648132443428</v>
       </c>
       <c r="H795" t="n">
         <v>85302</v>
@@ -23482,7 +23482,7 @@
         <v>0.499500006437302</v>
       </c>
       <c r="G797" t="n">
-        <v>0.383780419826508</v>
+        <v>0.38378044962883</v>
       </c>
       <c r="H797" t="n">
         <v>169843</v>
@@ -23569,7 +23569,7 @@
         <v>0.490500003099442</v>
       </c>
       <c r="G800" t="n">
-        <v>0.376865476369858</v>
+        <v>0.376865446567535</v>
       </c>
       <c r="H800" t="n">
         <v>189609</v>
@@ -23656,7 +23656,7 @@
         <v>0.523000001907349</v>
       </c>
       <c r="G803" t="n">
-        <v>0.401836216449738</v>
+        <v>0.401836186647415</v>
       </c>
       <c r="H803" t="n">
         <v>888677</v>
@@ -23801,7 +23801,7 @@
         <v>0.528999984264374</v>
       </c>
       <c r="G808" t="n">
-        <v>0.406446129083633</v>
+        <v>0.406446099281311</v>
       </c>
       <c r="H808" t="n">
         <v>777349</v>
@@ -23830,7 +23830,7 @@
         <v>0.532999992370605</v>
       </c>
       <c r="G809" t="n">
-        <v>0.409519493579865</v>
+        <v>0.40951943397522</v>
       </c>
       <c r="H809" t="n">
         <v>420481</v>
@@ -23946,7 +23946,7 @@
         <v>0.508000016212463</v>
       </c>
       <c r="G813" t="n">
-        <v>0.390311270952225</v>
+        <v>0.390311241149902</v>
       </c>
       <c r="H813" t="n">
         <v>130813</v>
@@ -24004,7 +24004,7 @@
         <v>0.500999987125397</v>
       </c>
       <c r="G815" t="n">
-        <v>0.384932905435562</v>
+        <v>0.384932935237885</v>
       </c>
       <c r="H815" t="n">
         <v>212212</v>
@@ -24033,7 +24033,7 @@
         <v>0.497999995946884</v>
       </c>
       <c r="G816" t="n">
-        <v>0.382627993822098</v>
+        <v>0.382627964019775</v>
       </c>
       <c r="H816" t="n">
         <v>191104</v>
@@ -24062,7 +24062,7 @@
         <v>0.497999995946884</v>
       </c>
       <c r="G817" t="n">
-        <v>0.382627993822098</v>
+        <v>0.382627964019775</v>
       </c>
       <c r="H817" t="n">
         <v>241364</v>
@@ -24091,7 +24091,7 @@
         <v>0.508000016212463</v>
       </c>
       <c r="G818" t="n">
-        <v>0.390311270952225</v>
+        <v>0.390311241149902</v>
       </c>
       <c r="H818" t="n">
         <v>237275</v>
@@ -24265,7 +24265,7 @@
         <v>0.488000005483627</v>
       </c>
       <c r="G824" t="n">
-        <v>0.374944657087326</v>
+        <v>0.374944627285004</v>
       </c>
       <c r="H824" t="n">
         <v>478335</v>
@@ -24352,7 +24352,7 @@
         <v>0.47749999165535</v>
       </c>
       <c r="G827" t="n">
-        <v>0.366877228021622</v>
+        <v>0.366877198219299</v>
       </c>
       <c r="H827" t="n">
         <v>265902</v>
@@ -24381,7 +24381,7 @@
         <v>0.488000005483627</v>
       </c>
       <c r="G828" t="n">
-        <v>0.374944657087326</v>
+        <v>0.374944627285004</v>
       </c>
       <c r="H828" t="n">
         <v>134194</v>
@@ -24439,7 +24439,7 @@
         <v>0.523000001907349</v>
       </c>
       <c r="G830" t="n">
-        <v>0.401836216449738</v>
+        <v>0.401836186647415</v>
       </c>
       <c r="H830" t="n">
         <v>1112558</v>
@@ -24468,7 +24468,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G831" t="n">
-        <v>0.407214462757111</v>
+        <v>0.407214432954788</v>
       </c>
       <c r="H831" t="n">
         <v>676529</v>
@@ -24497,7 +24497,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G832" t="n">
-        <v>0.407214462757111</v>
+        <v>0.407214432954788</v>
       </c>
       <c r="H832" t="n">
         <v>211428</v>
@@ -24555,7 +24555,7 @@
         <v>0.505999982357025</v>
       </c>
       <c r="G834" t="n">
-        <v>0.388774573802948</v>
+        <v>0.388774544000626</v>
       </c>
       <c r="H834" t="n">
         <v>316836</v>
@@ -24613,7 +24613,7 @@
         <v>0.504000008106232</v>
       </c>
       <c r="G836" t="n">
-        <v>0.387237966060638</v>
+        <v>0.387237906455994</v>
       </c>
       <c r="H836" t="n">
         <v>772178</v>
@@ -24642,7 +24642,7 @@
         <v>0.513999998569489</v>
       </c>
       <c r="G837" t="n">
-        <v>0.394921183586121</v>
+        <v>0.394921243190765</v>
       </c>
       <c r="H837" t="n">
         <v>276903</v>
@@ -24671,7 +24671,7 @@
         <v>0.53600001335144</v>
       </c>
       <c r="G838" t="n">
-        <v>0.411824464797974</v>
+        <v>0.411824494600296</v>
       </c>
       <c r="H838" t="n">
         <v>645486</v>
@@ -24700,7 +24700,7 @@
         <v>0.541000008583069</v>
       </c>
       <c r="G839" t="n">
-        <v>0.415666103363037</v>
+        <v>0.415666133165359</v>
       </c>
       <c r="H839" t="n">
         <v>1478731</v>
@@ -24758,7 +24758,7 @@
         <v>0.542999982833862</v>
       </c>
       <c r="G841" t="n">
-        <v>0.417202770709991</v>
+        <v>0.417202711105347</v>
       </c>
       <c r="H841" t="n">
         <v>231038</v>
@@ -24845,7 +24845,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G844" t="n">
-        <v>0.399531185626984</v>
+        <v>0.399531155824661</v>
       </c>
       <c r="H844" t="n">
         <v>421448</v>
@@ -24874,7 +24874,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G845" t="n">
-        <v>0.411056190729141</v>
+        <v>0.411056131124496</v>
       </c>
       <c r="H845" t="n">
         <v>247309</v>
@@ -24903,7 +24903,7 @@
         <v>0.528999984264374</v>
       </c>
       <c r="G846" t="n">
-        <v>0.406446129083633</v>
+        <v>0.406446099281311</v>
       </c>
       <c r="H846" t="n">
         <v>49635</v>
@@ -24932,7 +24932,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G847" t="n">
-        <v>0.399531185626984</v>
+        <v>0.399531155824661</v>
       </c>
       <c r="H847" t="n">
         <v>246653</v>
@@ -24990,7 +24990,7 @@
         <v>0.527999997138977</v>
       </c>
       <c r="G849" t="n">
-        <v>0.405677795410156</v>
+        <v>0.405677855014801</v>
       </c>
       <c r="H849" t="n">
         <v>307539</v>
@@ -25019,7 +25019,7 @@
         <v>0.517000019550323</v>
       </c>
       <c r="G850" t="n">
-        <v>0.397226214408875</v>
+        <v>0.397226184606552</v>
       </c>
       <c r="H850" t="n">
         <v>238987</v>
@@ -25048,7 +25048,7 @@
         <v>0.541000008583069</v>
       </c>
       <c r="G851" t="n">
-        <v>0.415666103363037</v>
+        <v>0.415666133165359</v>
       </c>
       <c r="H851" t="n">
         <v>1167475</v>
@@ -25106,7 +25106,7 @@
         <v>0.537999987602234</v>
       </c>
       <c r="G853" t="n">
-        <v>0.413361102342606</v>
+        <v>0.413361132144928</v>
       </c>
       <c r="H853" t="n">
         <v>219969</v>
@@ -25164,7 +25164,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G855" t="n">
-        <v>0.407214462757111</v>
+        <v>0.407214432954788</v>
       </c>
       <c r="H855" t="n">
         <v>323631</v>
@@ -25193,7 +25193,7 @@
         <v>0.523000001907349</v>
       </c>
       <c r="G856" t="n">
-        <v>0.401836216449738</v>
+        <v>0.401836186647415</v>
       </c>
       <c r="H856" t="n">
         <v>243089</v>
@@ -25222,7 +25222,7 @@
         <v>0.532999992370605</v>
       </c>
       <c r="G857" t="n">
-        <v>0.409519493579865</v>
+        <v>0.40951943397522</v>
       </c>
       <c r="H857" t="n">
         <v>98289</v>
@@ -25251,7 +25251,7 @@
         <v>0.513999998569489</v>
       </c>
       <c r="G858" t="n">
-        <v>0.394921183586121</v>
+        <v>0.394921243190765</v>
       </c>
       <c r="H858" t="n">
         <v>93578</v>
@@ -25280,7 +25280,7 @@
         <v>0.513999998569489</v>
       </c>
       <c r="G859" t="n">
-        <v>0.394921183586121</v>
+        <v>0.394921243190765</v>
       </c>
       <c r="H859" t="n">
         <v>168232</v>
@@ -25338,7 +25338,7 @@
         <v>0.533999979496002</v>
       </c>
       <c r="G861" t="n">
-        <v>0.410287797451019</v>
+        <v>0.410287767648697</v>
       </c>
       <c r="H861" t="n">
         <v>236901</v>
@@ -25396,7 +25396,7 @@
         <v>0.541999995708466</v>
       </c>
       <c r="G863" t="n">
-        <v>0.416434437036514</v>
+        <v>0.416434466838837</v>
       </c>
       <c r="H863" t="n">
         <v>412329</v>
@@ -25425,7 +25425,7 @@
         <v>0.532999992370605</v>
       </c>
       <c r="G864" t="n">
-        <v>0.409519493579865</v>
+        <v>0.40951943397522</v>
       </c>
       <c r="H864" t="n">
         <v>160247</v>
@@ -25454,7 +25454,7 @@
         <v>0.542999982833862</v>
       </c>
       <c r="G865" t="n">
-        <v>0.417202770709991</v>
+        <v>0.417202711105347</v>
       </c>
       <c r="H865" t="n">
         <v>58968</v>
@@ -25512,7 +25512,7 @@
         <v>0.53600001335144</v>
       </c>
       <c r="G867" t="n">
-        <v>0.411824464797974</v>
+        <v>0.411824494600296</v>
       </c>
       <c r="H867" t="n">
         <v>165468</v>
@@ -25541,7 +25541,7 @@
         <v>0.53600001335144</v>
       </c>
       <c r="G868" t="n">
-        <v>0.411824464797974</v>
+        <v>0.411824494600296</v>
       </c>
       <c r="H868" t="n">
         <v>110084</v>
@@ -25570,7 +25570,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G869" t="n">
-        <v>0.411056190729141</v>
+        <v>0.411056131124496</v>
       </c>
       <c r="H869" t="n">
         <v>26107</v>
@@ -25628,7 +25628,7 @@
         <v>0.528999984264374</v>
       </c>
       <c r="G871" t="n">
-        <v>0.406446129083633</v>
+        <v>0.406446099281311</v>
       </c>
       <c r="H871" t="n">
         <v>78639</v>
@@ -25657,7 +25657,7 @@
         <v>0.527999997138977</v>
       </c>
       <c r="G872" t="n">
-        <v>0.405677795410156</v>
+        <v>0.405677855014801</v>
       </c>
       <c r="H872" t="n">
         <v>39874</v>
@@ -25686,7 +25686,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G873" t="n">
-        <v>0.411056190729141</v>
+        <v>0.411056131124496</v>
       </c>
       <c r="H873" t="n">
         <v>164662</v>
@@ -25744,7 +25744,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G875" t="n">
-        <v>0.407214462757111</v>
+        <v>0.407214432954788</v>
       </c>
       <c r="H875" t="n">
         <v>138456</v>
@@ -25773,7 +25773,7 @@
         <v>0.523000001907349</v>
       </c>
       <c r="G876" t="n">
-        <v>0.401836216449738</v>
+        <v>0.401836186647415</v>
       </c>
       <c r="H876" t="n">
         <v>154240</v>
@@ -25831,7 +25831,7 @@
         <v>0.513999998569489</v>
       </c>
       <c r="G878" t="n">
-        <v>0.394921183586121</v>
+        <v>0.394921243190765</v>
       </c>
       <c r="H878" t="n">
         <v>103529</v>
@@ -25976,7 +25976,7 @@
         <v>0.528999984264374</v>
       </c>
       <c r="G883" t="n">
-        <v>0.406446129083633</v>
+        <v>0.406446099281311</v>
       </c>
       <c r="H883" t="n">
         <v>108395</v>
@@ -26063,7 +26063,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G886" t="n">
-        <v>0.407214462757111</v>
+        <v>0.407214432954788</v>
       </c>
       <c r="H886" t="n">
         <v>59228</v>
@@ -26092,7 +26092,7 @@
         <v>0.545000016689301</v>
       </c>
       <c r="G887" t="n">
-        <v>0.418739467859268</v>
+        <v>0.418739438056946</v>
       </c>
       <c r="H887" t="n">
         <v>418294</v>
@@ -26150,7 +26150,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G889" t="n">
-        <v>0.424117684364319</v>
+        <v>0.424117714166641</v>
       </c>
       <c r="H889" t="n">
         <v>244163</v>
@@ -26179,7 +26179,7 @@
         <v>0.549000024795532</v>
       </c>
       <c r="G890" t="n">
-        <v>0.421812742948532</v>
+        <v>0.421812772750854</v>
       </c>
       <c r="H890" t="n">
         <v>70318</v>
@@ -26237,7 +26237,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G892" t="n">
-        <v>0.422581046819687</v>
+        <v>0.422581076622009</v>
       </c>
       <c r="H892" t="n">
         <v>109119</v>
@@ -26266,7 +26266,7 @@
         <v>0.545000016689301</v>
       </c>
       <c r="G893" t="n">
-        <v>0.418739467859268</v>
+        <v>0.418739438056946</v>
       </c>
       <c r="H893" t="n">
         <v>162159</v>
@@ -26295,7 +26295,7 @@
         <v>0.541000008583069</v>
       </c>
       <c r="G894" t="n">
-        <v>0.415666103363037</v>
+        <v>0.415666133165359</v>
       </c>
       <c r="H894" t="n">
         <v>157795</v>
@@ -26324,7 +26324,7 @@
         <v>0.541000008583069</v>
       </c>
       <c r="G895" t="n">
-        <v>0.415666103363037</v>
+        <v>0.415666133165359</v>
       </c>
       <c r="H895" t="n">
         <v>164299</v>
@@ -26353,7 +26353,7 @@
         <v>0.545000016689301</v>
       </c>
       <c r="G896" t="n">
-        <v>0.418739467859268</v>
+        <v>0.418739438056946</v>
       </c>
       <c r="H896" t="n">
         <v>179088</v>
@@ -26411,7 +26411,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G898" t="n">
-        <v>0.473290741443634</v>
+        <v>0.473290771245956</v>
       </c>
       <c r="H898" t="n">
         <v>4692510</v>
@@ -26498,7 +26498,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G901" t="n">
-        <v>0.484047383069992</v>
+        <v>0.48404735326767</v>
       </c>
       <c r="H901" t="n">
         <v>717900</v>
@@ -26527,7 +26527,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G902" t="n">
-        <v>0.491730630397797</v>
+        <v>0.491730719804764</v>
       </c>
       <c r="H902" t="n">
         <v>558327</v>
@@ -26585,7 +26585,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G904" t="n">
-        <v>0.505560576915741</v>
+        <v>0.505560636520386</v>
       </c>
       <c r="H904" t="n">
         <v>1336429</v>
@@ -26614,7 +26614,7 @@
         <v>0.658999979496002</v>
       </c>
       <c r="G905" t="n">
-        <v>0.506328940391541</v>
+        <v>0.506328999996185</v>
       </c>
       <c r="H905" t="n">
         <v>603590</v>
@@ -26672,7 +26672,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G907" t="n">
-        <v>0.479437381029129</v>
+        <v>0.479437410831451</v>
       </c>
       <c r="H907" t="n">
         <v>547040</v>
@@ -26701,7 +26701,7 @@
         <v>0.652999997138977</v>
       </c>
       <c r="G908" t="n">
-        <v>0.501718938350677</v>
+        <v>0.501718997955322</v>
       </c>
       <c r="H908" t="n">
         <v>815143</v>
@@ -26730,7 +26730,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G909" t="n">
-        <v>0.482510775327682</v>
+        <v>0.482510805130005</v>
       </c>
       <c r="H909" t="n">
         <v>856870</v>
@@ -26759,7 +26759,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G910" t="n">
-        <v>0.470217436552048</v>
+        <v>0.47021746635437</v>
       </c>
       <c r="H910" t="n">
         <v>646474</v>
@@ -26788,7 +26788,7 @@
         <v>0.619000017642975</v>
       </c>
       <c r="G911" t="n">
-        <v>0.475595742464066</v>
+        <v>0.475595772266388</v>
       </c>
       <c r="H911" t="n">
         <v>213127</v>
@@ -26846,7 +26846,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G913" t="n">
-        <v>0.468680828809738</v>
+        <v>0.468680888414383</v>
       </c>
       <c r="H913" t="n">
         <v>332283</v>
@@ -26875,7 +26875,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G914" t="n">
-        <v>0.464070856571198</v>
+        <v>0.464070826768875</v>
       </c>
       <c r="H914" t="n">
         <v>306237</v>
@@ -26904,7 +26904,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G915" t="n">
-        <v>0.465607523918152</v>
+        <v>0.465607494115829</v>
       </c>
       <c r="H915" t="n">
         <v>168953</v>
@@ -26962,7 +26962,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G917" t="n">
-        <v>0.480974048376083</v>
+        <v>0.480974137783051</v>
       </c>
       <c r="H917" t="n">
         <v>354079</v>
@@ -26991,7 +26991,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G918" t="n">
-        <v>0.453314214944839</v>
+        <v>0.453314185142517</v>
       </c>
       <c r="H918" t="n">
         <v>659680</v>
@@ -27020,7 +27020,7 @@
         <v>0.564999997615814</v>
       </c>
       <c r="G919" t="n">
-        <v>0.4341059923172</v>
+        <v>0.434106051921844</v>
       </c>
       <c r="H919" t="n">
         <v>496547</v>
@@ -27049,7 +27049,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G920" t="n">
-        <v>0.441789299249649</v>
+        <v>0.441789269447327</v>
       </c>
       <c r="H920" t="n">
         <v>195067</v>
@@ -27078,7 +27078,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G921" t="n">
-        <v>0.424117684364319</v>
+        <v>0.424117714166641</v>
       </c>
       <c r="H921" t="n">
         <v>245875</v>
@@ -27107,7 +27107,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G922" t="n">
-        <v>0.445630997419357</v>
+        <v>0.44563090801239</v>
       </c>
       <c r="H922" t="n">
         <v>323452</v>
@@ -27136,7 +27136,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G923" t="n">
-        <v>0.449472606182098</v>
+        <v>0.449472576379776</v>
       </c>
       <c r="H923" t="n">
         <v>186439</v>
@@ -27252,7 +27252,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G927" t="n">
-        <v>0.453314214944839</v>
+        <v>0.453314185142517</v>
       </c>
       <c r="H927" t="n">
         <v>489655</v>
@@ -27281,7 +27281,7 @@
         <v>0.591000020503998</v>
       </c>
       <c r="G928" t="n">
-        <v>0.454082608222961</v>
+        <v>0.454082578420639</v>
       </c>
       <c r="H928" t="n">
         <v>45061</v>
@@ -27339,7 +27339,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G930" t="n">
-        <v>0.465607523918152</v>
+        <v>0.465607494115829</v>
       </c>
       <c r="H930" t="n">
         <v>252474</v>
@@ -27368,7 +27368,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G931" t="n">
-        <v>0.482510775327682</v>
+        <v>0.482510805130005</v>
       </c>
       <c r="H931" t="n">
         <v>568276</v>
@@ -27397,7 +27397,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G932" t="n">
-        <v>0.484047383069992</v>
+        <v>0.48404735326767</v>
       </c>
       <c r="H932" t="n">
         <v>584324</v>
@@ -27484,7 +27484,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G935" t="n">
-        <v>0.484047383069992</v>
+        <v>0.48404735326767</v>
       </c>
       <c r="H935" t="n">
         <v>253532</v>
@@ -27687,7 +27687,7 @@
         <v>0.601000010967255</v>
       </c>
       <c r="G942" t="n">
-        <v>0.461765855550766</v>
+        <v>0.461765885353088</v>
       </c>
       <c r="H942" t="n">
         <v>238130</v>
@@ -27716,7 +27716,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G943" t="n">
-        <v>0.464070856571198</v>
+        <v>0.464070826768875</v>
       </c>
       <c r="H943" t="n">
         <v>214516</v>
@@ -27832,7 +27832,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G947" t="n">
-        <v>0.470217436552048</v>
+        <v>0.47021746635437</v>
       </c>
       <c r="H947" t="n">
         <v>616889</v>
@@ -27890,7 +27890,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G949" t="n">
-        <v>0.467144161462784</v>
+        <v>0.467144191265106</v>
       </c>
       <c r="H949" t="n">
         <v>268968</v>
@@ -27948,7 +27948,7 @@
         <v>0.605000019073486</v>
       </c>
       <c r="G951" t="n">
-        <v>0.464839190244675</v>
+        <v>0.464839220046997</v>
       </c>
       <c r="H951" t="n">
         <v>242874</v>
@@ -27977,7 +27977,7 @@
         <v>0.605000019073486</v>
       </c>
       <c r="G952" t="n">
-        <v>0.464839190244675</v>
+        <v>0.464839220046997</v>
       </c>
       <c r="H952" t="n">
         <v>453599</v>
@@ -28064,7 +28064,7 @@
         <v>0.563000023365021</v>
       </c>
       <c r="G955" t="n">
-        <v>0.432569354772568</v>
+        <v>0.43256938457489</v>
       </c>
       <c r="H955" t="n">
         <v>490548</v>
@@ -28122,7 +28122,7 @@
         <v>0.556999981403351</v>
       </c>
       <c r="G957" t="n">
-        <v>0.427959352731705</v>
+        <v>0.427959322929382</v>
       </c>
       <c r="H957" t="n">
         <v>320311</v>
@@ -28151,7 +28151,7 @@
         <v>0.564999997615814</v>
       </c>
       <c r="G958" t="n">
-        <v>0.4341059923172</v>
+        <v>0.434106051921844</v>
       </c>
       <c r="H958" t="n">
         <v>166738</v>
@@ -28209,7 +28209,7 @@
         <v>0.565999984741211</v>
       </c>
       <c r="G960" t="n">
-        <v>0.434874355792999</v>
+        <v>0.434874296188354</v>
       </c>
       <c r="H960" t="n">
         <v>58777</v>
@@ -28267,7 +28267,7 @@
         <v>0.550999999046326</v>
       </c>
       <c r="G962" t="n">
-        <v>0.423349440097809</v>
+        <v>0.423349410295486</v>
       </c>
       <c r="H962" t="n">
         <v>2075965</v>
@@ -28325,7 +28325,7 @@
         <v>0.561999976634979</v>
       </c>
       <c r="G964" t="n">
-        <v>0.431800991296768</v>
+        <v>0.431800961494446</v>
       </c>
       <c r="H964" t="n">
         <v>395710</v>
@@ -28354,7 +28354,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G965" t="n">
-        <v>0.441789299249649</v>
+        <v>0.441789269447327</v>
       </c>
       <c r="H965" t="n">
         <v>273431</v>
@@ -28499,7 +28499,7 @@
         <v>0.561999976634979</v>
       </c>
       <c r="G970" t="n">
-        <v>0.431800991296768</v>
+        <v>0.431800961494446</v>
       </c>
       <c r="H970" t="n">
         <v>104001</v>
@@ -28557,7 +28557,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G972" t="n">
-        <v>0.441020965576172</v>
+        <v>0.441020995378494</v>
       </c>
       <c r="H972" t="n">
         <v>121483</v>
@@ -28586,7 +28586,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G973" t="n">
-        <v>0.441020965576172</v>
+        <v>0.441020995378494</v>
       </c>
       <c r="H973" t="n">
         <v>233644</v>
@@ -28615,7 +28615,7 @@
         <v>0.573000013828278</v>
       </c>
       <c r="G974" t="n">
-        <v>0.440252661705017</v>
+        <v>0.440252631902695</v>
       </c>
       <c r="H974" t="n">
         <v>269717</v>
@@ -28673,7 +28673,7 @@
         <v>0.565999984741211</v>
       </c>
       <c r="G976" t="n">
-        <v>0.434874355792999</v>
+        <v>0.434874296188354</v>
       </c>
       <c r="H976" t="n">
         <v>402322</v>
@@ -28760,7 +28760,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G979" t="n">
-        <v>0.464070856571198</v>
+        <v>0.464070826768875</v>
       </c>
       <c r="H979" t="n">
         <v>782627</v>
@@ -28789,7 +28789,7 @@
         <v>0.601000010967255</v>
       </c>
       <c r="G980" t="n">
-        <v>0.461765855550766</v>
+        <v>0.461765885353088</v>
       </c>
       <c r="H980" t="n">
         <v>509029</v>
@@ -28818,7 +28818,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G981" t="n">
-        <v>0.479437381029129</v>
+        <v>0.479437410831451</v>
       </c>
       <c r="H981" t="n">
         <v>867574</v>
@@ -28847,7 +28847,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G982" t="n">
-        <v>0.468680828809738</v>
+        <v>0.468680888414383</v>
       </c>
       <c r="H982" t="n">
         <v>823646</v>
@@ -28934,7 +28934,7 @@
         <v>0.634999990463257</v>
       </c>
       <c r="G985" t="n">
-        <v>0.487889051437378</v>
+        <v>0.4878890812397</v>
       </c>
       <c r="H985" t="n">
         <v>1452096</v>
@@ -28992,7 +28992,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G987" t="n">
-        <v>0.484047383069992</v>
+        <v>0.48404735326767</v>
       </c>
       <c r="H987" t="n">
         <v>572656</v>
@@ -29021,7 +29021,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G988" t="n">
-        <v>0.468680828809738</v>
+        <v>0.468680888414383</v>
       </c>
       <c r="H988" t="n">
         <v>537612</v>
@@ -29050,7 +29050,7 @@
         <v>0.592999994754791</v>
       </c>
       <c r="G989" t="n">
-        <v>0.455619275569916</v>
+        <v>0.455619186162949</v>
       </c>
       <c r="H989" t="n">
         <v>804878</v>
@@ -29195,7 +29195,7 @@
         <v>0.591000020503998</v>
       </c>
       <c r="G994" t="n">
-        <v>0.454082608222961</v>
+        <v>0.454082578420639</v>
       </c>
       <c r="H994" t="n">
         <v>690412</v>
@@ -29311,7 +29311,7 @@
         <v>0.559000015258789</v>
       </c>
       <c r="G998" t="n">
-        <v>0.429496079683304</v>
+        <v>0.429496049880981</v>
       </c>
       <c r="H998" t="n">
         <v>343888</v>
@@ -29427,7 +29427,7 @@
         <v>0.556999981403351</v>
       </c>
       <c r="G1002" t="n">
-        <v>0.427959352731705</v>
+        <v>0.427959322929382</v>
       </c>
       <c r="H1002" t="n">
         <v>542461</v>
@@ -29456,7 +29456,7 @@
         <v>0.546000003814697</v>
       </c>
       <c r="G1003" t="n">
-        <v>0.419507801532745</v>
+        <v>0.419507741928101</v>
       </c>
       <c r="H1003" t="n">
         <v>866896</v>
@@ -29514,7 +29514,7 @@
         <v>0.566999971866608</v>
       </c>
       <c r="G1005" t="n">
-        <v>0.435642659664154</v>
+        <v>0.435642629861832</v>
       </c>
       <c r="H1005" t="n">
         <v>403723</v>
@@ -29659,7 +29659,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1010" t="n">
-        <v>0.445630997419357</v>
+        <v>0.44563090801239</v>
       </c>
       <c r="H1010" t="n">
         <v>212526</v>
@@ -29775,7 +29775,7 @@
         <v>0.561999976634979</v>
       </c>
       <c r="G1014" t="n">
-        <v>0.431800991296768</v>
+        <v>0.431800961494446</v>
       </c>
       <c r="H1014" t="n">
         <v>159672</v>
@@ -29804,7 +29804,7 @@
         <v>0.561999976634979</v>
       </c>
       <c r="G1015" t="n">
-        <v>0.431800991296768</v>
+        <v>0.431800961494446</v>
       </c>
       <c r="H1015" t="n">
         <v>354384</v>
@@ -29862,7 +29862,7 @@
         <v>0.566999971866608</v>
       </c>
       <c r="G1017" t="n">
-        <v>0.435642659664154</v>
+        <v>0.435642629861832</v>
       </c>
       <c r="H1017" t="n">
         <v>202506</v>
@@ -29920,7 +29920,7 @@
         <v>0.564999997615814</v>
       </c>
       <c r="G1019" t="n">
-        <v>0.4341059923172</v>
+        <v>0.434106051921844</v>
       </c>
       <c r="H1019" t="n">
         <v>216207</v>
@@ -29949,7 +29949,7 @@
         <v>0.561999976634979</v>
       </c>
       <c r="G1020" t="n">
-        <v>0.431800991296768</v>
+        <v>0.431800961494446</v>
       </c>
       <c r="H1020" t="n">
         <v>141720</v>
@@ -30007,7 +30007,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G1022" t="n">
-        <v>0.464070856571198</v>
+        <v>0.464070826768875</v>
       </c>
       <c r="H1022" t="n">
         <v>2352028</v>
@@ -30036,7 +30036,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G1023" t="n">
-        <v>0.467144161462784</v>
+        <v>0.467144191265106</v>
       </c>
       <c r="H1023" t="n">
         <v>1163154</v>
@@ -30152,7 +30152,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G1027" t="n">
-        <v>0.441020965576172</v>
+        <v>0.441020995378494</v>
       </c>
       <c r="H1027" t="n">
         <v>509745</v>
@@ -30181,7 +30181,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1028" t="n">
-        <v>0.449472606182098</v>
+        <v>0.449472576379776</v>
       </c>
       <c r="H1028" t="n">
         <v>554067</v>
@@ -30239,7 +30239,7 @@
         <v>0.566999971866608</v>
       </c>
       <c r="G1030" t="n">
-        <v>0.435642659664154</v>
+        <v>0.435642629861832</v>
       </c>
       <c r="H1030" t="n">
         <v>378490</v>
@@ -30268,7 +30268,7 @@
         <v>0.556999981403351</v>
       </c>
       <c r="G1031" t="n">
-        <v>0.427959352731705</v>
+        <v>0.427959322929382</v>
       </c>
       <c r="H1031" t="n">
         <v>603780</v>
@@ -30297,7 +30297,7 @@
         <v>0.561999976634979</v>
       </c>
       <c r="G1032" t="n">
-        <v>0.431800991296768</v>
+        <v>0.431800961494446</v>
       </c>
       <c r="H1032" t="n">
         <v>356286</v>
@@ -30355,7 +30355,7 @@
         <v>0.541999995708466</v>
       </c>
       <c r="G1034" t="n">
-        <v>0.416434437036514</v>
+        <v>0.416434466838837</v>
       </c>
       <c r="H1034" t="n">
         <v>665489</v>
@@ -30384,7 +30384,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1035" t="n">
-        <v>0.407214462757111</v>
+        <v>0.407214432954788</v>
       </c>
       <c r="H1035" t="n">
         <v>855969</v>
@@ -30442,7 +30442,7 @@
         <v>0.488499999046326</v>
       </c>
       <c r="G1037" t="n">
-        <v>0.375328838825226</v>
+        <v>0.375328809022903</v>
       </c>
       <c r="H1037" t="n">
         <v>885075</v>
@@ -30500,7 +30500,7 @@
         <v>0.513999998569489</v>
       </c>
       <c r="G1039" t="n">
-        <v>0.394921183586121</v>
+        <v>0.394921243190765</v>
       </c>
       <c r="H1039" t="n">
         <v>567039</v>
@@ -30587,7 +30587,7 @@
         <v>0.517000019550323</v>
       </c>
       <c r="G1042" t="n">
-        <v>0.397226214408875</v>
+        <v>0.397226184606552</v>
       </c>
       <c r="H1042" t="n">
         <v>356939</v>
@@ -30645,7 +30645,7 @@
         <v>0.512000024318695</v>
       </c>
       <c r="G1044" t="n">
-        <v>0.393384546041489</v>
+        <v>0.393384575843811</v>
       </c>
       <c r="H1044" t="n">
         <v>296706</v>
@@ -30674,7 +30674,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G1045" t="n">
-        <v>0.399531185626984</v>
+        <v>0.399531155824661</v>
       </c>
       <c r="H1045" t="n">
         <v>428216</v>
@@ -30703,7 +30703,7 @@
         <v>0.526000022888184</v>
       </c>
       <c r="G1046" t="n">
-        <v>0.404141157865524</v>
+        <v>0.404141187667847</v>
       </c>
       <c r="H1046" t="n">
         <v>458429</v>
@@ -30732,7 +30732,7 @@
         <v>0.523000001907349</v>
       </c>
       <c r="G1047" t="n">
-        <v>0.401836216449738</v>
+        <v>0.401836186647415</v>
       </c>
       <c r="H1047" t="n">
         <v>212371</v>
@@ -30790,7 +30790,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1049" t="n">
-        <v>0.407214462757111</v>
+        <v>0.407214432954788</v>
       </c>
       <c r="H1049" t="n">
         <v>207928</v>
@@ -30848,7 +30848,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G1051" t="n">
-        <v>0.399531185626984</v>
+        <v>0.399531155824661</v>
       </c>
       <c r="H1051" t="n">
         <v>472303</v>
@@ -30935,7 +30935,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1054" t="n">
-        <v>0.376481354236603</v>
+        <v>0.37648132443428</v>
       </c>
       <c r="H1054" t="n">
         <v>445853</v>
@@ -30964,7 +30964,7 @@
         <v>0.505999982357025</v>
       </c>
       <c r="G1055" t="n">
-        <v>0.388774573802948</v>
+        <v>0.388774544000626</v>
       </c>
       <c r="H1055" t="n">
         <v>723519</v>
@@ -30993,7 +30993,7 @@
         <v>0.485000014305115</v>
       </c>
       <c r="G1056" t="n">
-        <v>0.372639685869217</v>
+        <v>0.372639715671539</v>
       </c>
       <c r="H1056" t="n">
         <v>377231</v>
@@ -31051,7 +31051,7 @@
         <v>0.457500010728836</v>
       </c>
       <c r="G1058" t="n">
-        <v>0.351510614156723</v>
+        <v>0.351510643959045</v>
       </c>
       <c r="H1058" t="n">
         <v>775525</v>
@@ -31109,7 +31109,7 @@
         <v>0.449000000953674</v>
       </c>
       <c r="G1060" t="n">
-        <v>0.344979852437973</v>
+        <v>0.344979822635651</v>
       </c>
       <c r="H1060" t="n">
         <v>611983</v>
@@ -31138,7 +31138,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G1061" t="n">
-        <v>0.317319959402084</v>
+        <v>0.317319989204407</v>
       </c>
       <c r="H1061" t="n">
         <v>558185</v>
@@ -31167,7 +31167,7 @@
         <v>0.391999989748001</v>
       </c>
       <c r="G1062" t="n">
-        <v>0.301185041666031</v>
+        <v>0.301185011863708</v>
       </c>
       <c r="H1062" t="n">
         <v>1337923</v>
@@ -31196,7 +31196,7 @@
         <v>0.344999998807907</v>
       </c>
       <c r="G1063" t="n">
-        <v>0.265073537826538</v>
+        <v>0.26507356762886</v>
       </c>
       <c r="H1063" t="n">
         <v>995909</v>
@@ -31225,7 +31225,7 @@
         <v>0.337999999523163</v>
       </c>
       <c r="G1064" t="n">
-        <v>0.259695261716843</v>
+        <v>0.259695291519165</v>
       </c>
       <c r="H1064" t="n">
         <v>940784</v>
@@ -31283,7 +31283,7 @@
         <v>0.311500012874603</v>
       </c>
       <c r="G1066" t="n">
-        <v>0.239334538578987</v>
+        <v>0.23933456838131</v>
       </c>
       <c r="H1066" t="n">
         <v>812346</v>
@@ -31312,7 +31312,7 @@
         <v>0.314999997615814</v>
       </c>
       <c r="G1067" t="n">
-        <v>0.242023691534996</v>
+        <v>0.242023676633835</v>
       </c>
       <c r="H1067" t="n">
         <v>701200</v>
@@ -31370,7 +31370,7 @@
         <v>0.319999992847443</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.245865315198898</v>
+        <v>0.245865359902382</v>
       </c>
       <c r="H1069" t="n">
         <v>339854</v>
@@ -31428,7 +31428,7 @@
         <v>0.327499985694885</v>
       </c>
       <c r="G1071" t="n">
-        <v>0.251627802848816</v>
+        <v>0.251627832651138</v>
       </c>
       <c r="H1071" t="n">
         <v>345277</v>
@@ -31515,7 +31515,7 @@
         <v>0.36599999666214</v>
       </c>
       <c r="G1074" t="n">
-        <v>0.281208485364914</v>
+        <v>0.281208544969559</v>
       </c>
       <c r="H1074" t="n">
         <v>310583</v>
@@ -31573,7 +31573,7 @@
         <v>0.350499987602234</v>
       </c>
       <c r="G1076" t="n">
-        <v>0.269299358129501</v>
+        <v>0.269299328327179</v>
       </c>
       <c r="H1076" t="n">
         <v>210314</v>
@@ -31747,7 +31747,7 @@
         <v>0.319000005722046</v>
       </c>
       <c r="G1082" t="n">
-        <v>0.245097041130066</v>
+        <v>0.245096996426582</v>
       </c>
       <c r="H1082" t="n">
         <v>159502</v>
@@ -31805,7 +31805,7 @@
         <v>0.331499993801117</v>
       </c>
       <c r="G1084" t="n">
-        <v>0.254701137542725</v>
+        <v>0.254701107740402</v>
       </c>
       <c r="H1084" t="n">
         <v>474980</v>
@@ -31834,7 +31834,7 @@
         <v>0.337999999523163</v>
       </c>
       <c r="G1085" t="n">
-        <v>0.259695261716843</v>
+        <v>0.259695291519165</v>
       </c>
       <c r="H1085" t="n">
         <v>305828</v>
@@ -31863,7 +31863,7 @@
         <v>0.340999990701675</v>
       </c>
       <c r="G1086" t="n">
-        <v>0.262000232934952</v>
+        <v>0.262000262737274</v>
       </c>
       <c r="H1086" t="n">
         <v>246813</v>
@@ -31892,7 +31892,7 @@
         <v>0.337999999523163</v>
       </c>
       <c r="G1087" t="n">
-        <v>0.259695261716843</v>
+        <v>0.259695291519165</v>
       </c>
       <c r="H1087" t="n">
         <v>240516</v>
@@ -31950,7 +31950,7 @@
         <v>0.340000003576279</v>
       </c>
       <c r="G1089" t="n">
-        <v>0.261231929063797</v>
+        <v>0.261231958866119</v>
       </c>
       <c r="H1089" t="n">
         <v>174984</v>
@@ -31979,7 +31979,7 @@
         <v>0.34799998998642</v>
       </c>
       <c r="G1090" t="n">
-        <v>0.267378568649292</v>
+        <v>0.26737853884697</v>
       </c>
       <c r="H1090" t="n">
         <v>85920</v>
@@ -32153,7 +32153,7 @@
         <v>0.354000002145767</v>
       </c>
       <c r="G1096" t="n">
-        <v>0.271988540887833</v>
+        <v>0.271988570690155</v>
       </c>
       <c r="H1096" t="n">
         <v>364858</v>
@@ -32182,7 +32182,7 @@
         <v>0.356499999761581</v>
       </c>
       <c r="G1097" t="n">
-        <v>0.273909330368042</v>
+        <v>0.273909360170364</v>
       </c>
       <c r="H1097" t="n">
         <v>281693</v>
@@ -32240,7 +32240,7 @@
         <v>0.360500007867813</v>
       </c>
       <c r="G1099" t="n">
-        <v>0.276982665061951</v>
+        <v>0.276982694864273</v>
       </c>
       <c r="H1099" t="n">
         <v>753760</v>
@@ -32269,7 +32269,7 @@
         <v>0.361999988555908</v>
       </c>
       <c r="G1100" t="n">
-        <v>0.278135150671005</v>
+        <v>0.278135120868683</v>
       </c>
       <c r="H1100" t="n">
         <v>149347</v>
@@ -32327,7 +32327,7 @@
         <v>0.350499987602234</v>
       </c>
       <c r="G1102" t="n">
-        <v>0.269299358129501</v>
+        <v>0.269299328327179</v>
       </c>
       <c r="H1102" t="n">
         <v>97822</v>
@@ -32385,7 +32385,7 @@
         <v>0.358500003814697</v>
       </c>
       <c r="G1104" t="n">
-        <v>0.275445997714996</v>
+        <v>0.275446027517319</v>
       </c>
       <c r="H1104" t="n">
         <v>497581</v>
@@ -32443,7 +32443,7 @@
         <v>0.349999994039536</v>
       </c>
       <c r="G1106" t="n">
-        <v>0.268915206193924</v>
+        <v>0.268915235996246</v>
       </c>
       <c r="H1106" t="n">
         <v>68428</v>
@@ -32530,7 +32530,7 @@
         <v>0.336499989032745</v>
       </c>
       <c r="G1109" t="n">
-        <v>0.258542776107788</v>
+        <v>0.25854280591011</v>
       </c>
       <c r="H1109" t="n">
         <v>164664</v>
@@ -32588,7 +32588,7 @@
         <v>0.344999998807907</v>
       </c>
       <c r="G1111" t="n">
-        <v>0.265073537826538</v>
+        <v>0.26507356762886</v>
       </c>
       <c r="H1111" t="n">
         <v>109553</v>
@@ -32646,7 +32646,7 @@
         <v>0.341500014066696</v>
       </c>
       <c r="G1113" t="n">
-        <v>0.262384444475174</v>
+        <v>0.262384414672852</v>
       </c>
       <c r="H1113" t="n">
         <v>181536</v>
@@ -32675,7 +32675,7 @@
         <v>0.341500014066696</v>
       </c>
       <c r="G1114" t="n">
-        <v>0.262384444475174</v>
+        <v>0.262384414672852</v>
       </c>
       <c r="H1114" t="n">
         <v>99469</v>
@@ -32704,7 +32704,7 @@
         <v>0.342500001192093</v>
       </c>
       <c r="G1115" t="n">
-        <v>0.263152748346329</v>
+        <v>0.263152778148651</v>
       </c>
       <c r="H1115" t="n">
         <v>498955</v>
@@ -32762,7 +32762,7 @@
         <v>0.349999994039536</v>
       </c>
       <c r="G1117" t="n">
-        <v>0.268915206193924</v>
+        <v>0.268915235996246</v>
       </c>
       <c r="H1117" t="n">
         <v>497200</v>
@@ -32791,7 +32791,7 @@
         <v>0.349999994039536</v>
       </c>
       <c r="G1118" t="n">
-        <v>0.268915206193924</v>
+        <v>0.268915235996246</v>
       </c>
       <c r="H1118" t="n">
         <v>271041</v>
@@ -32907,7 +32907,7 @@
         <v>0.379999995231628</v>
       </c>
       <c r="G1122" t="n">
-        <v>0.29196509718895</v>
+        <v>0.291965067386627</v>
       </c>
       <c r="H1122" t="n">
         <v>1026613</v>
@@ -32994,7 +32994,7 @@
         <v>0.426499992609024</v>
       </c>
       <c r="G1125" t="n">
-        <v>0.32769238948822</v>
+        <v>0.327692419290543</v>
       </c>
       <c r="H1125" t="n">
         <v>728674</v>
@@ -33023,7 +33023,7 @@
         <v>0.405000001192093</v>
       </c>
       <c r="G1126" t="n">
-        <v>0.311173349618912</v>
+        <v>0.311173319816589</v>
       </c>
       <c r="H1126" t="n">
         <v>1073289</v>
@@ -33110,7 +33110,7 @@
         <v>0.393500000238419</v>
       </c>
       <c r="G1129" t="n">
-        <v>0.302337557077408</v>
+        <v>0.302337527275085</v>
       </c>
       <c r="H1129" t="n">
         <v>423424</v>
@@ -33168,7 +33168,7 @@
         <v>0.421499997377396</v>
       </c>
       <c r="G1131" t="n">
-        <v>0.323850750923157</v>
+        <v>0.323850780725479</v>
       </c>
       <c r="H1131" t="n">
         <v>1692345</v>
@@ -33255,7 +33255,7 @@
         <v>0.432500004768372</v>
       </c>
       <c r="G1134" t="n">
-        <v>0.332302361726761</v>
+        <v>0.332302391529083</v>
       </c>
       <c r="H1134" t="n">
         <v>1837051</v>
@@ -33313,7 +33313,7 @@
         <v>0.412499994039536</v>
       </c>
       <c r="G1136" t="n">
-        <v>0.316935777664185</v>
+        <v>0.316935807466507</v>
       </c>
       <c r="H1136" t="n">
         <v>1314565</v>
@@ -33371,7 +33371,7 @@
         <v>0.405000001192093</v>
       </c>
       <c r="G1138" t="n">
-        <v>0.311173349618912</v>
+        <v>0.311173319816589</v>
       </c>
       <c r="H1138" t="n">
         <v>653182</v>
@@ -33487,7 +33487,7 @@
         <v>0.375999987125397</v>
       </c>
       <c r="G1142" t="n">
-        <v>0.288891792297363</v>
+        <v>0.288891762495041</v>
       </c>
       <c r="H1142" t="n">
         <v>503641</v>
@@ -33516,7 +33516,7 @@
         <v>0.402500003576279</v>
       </c>
       <c r="G1143" t="n">
-        <v>0.30925253033638</v>
+        <v>0.309252500534058</v>
       </c>
       <c r="H1143" t="n">
         <v>1132374</v>
@@ -33603,7 +33603,7 @@
         <v>0.390500009059906</v>
       </c>
       <c r="G1146" t="n">
-        <v>0.300032585859299</v>
+        <v>0.300032556056976</v>
       </c>
       <c r="H1146" t="n">
         <v>454417</v>
@@ -33719,7 +33719,7 @@
         <v>0.390500009059906</v>
       </c>
       <c r="G1150" t="n">
-        <v>0.300032585859299</v>
+        <v>0.300032556056976</v>
       </c>
       <c r="H1150" t="n">
         <v>350508</v>
@@ -33748,7 +33748,7 @@
         <v>0.394499987363815</v>
       </c>
       <c r="G1151" t="n">
-        <v>0.303105890750885</v>
+        <v>0.30310583114624</v>
       </c>
       <c r="H1151" t="n">
         <v>189730</v>
@@ -33777,7 +33777,7 @@
         <v>0.398000001907349</v>
       </c>
       <c r="G1152" t="n">
-        <v>0.305795043706894</v>
+        <v>0.305795013904572</v>
       </c>
       <c r="H1152" t="n">
         <v>372963</v>
@@ -33806,7 +33806,7 @@
         <v>0.39750000834465</v>
       </c>
       <c r="G1153" t="n">
-        <v>0.305410832166672</v>
+        <v>0.305410861968994</v>
       </c>
       <c r="H1153" t="n">
         <v>445976</v>
@@ -33835,7 +33835,7 @@
         <v>0.398000001907349</v>
       </c>
       <c r="G1154" t="n">
-        <v>0.305795043706894</v>
+        <v>0.305795013904572</v>
       </c>
       <c r="H1154" t="n">
         <v>556841</v>
@@ -33864,7 +33864,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G1155" t="n">
-        <v>0.307331681251526</v>
+        <v>0.307331711053848</v>
       </c>
       <c r="H1155" t="n">
         <v>1252599</v>
@@ -33893,7 +33893,7 @@
         <v>0.414000004529953</v>
       </c>
       <c r="G1156" t="n">
-        <v>0.318088263273239</v>
+        <v>0.318088293075562</v>
       </c>
       <c r="H1156" t="n">
         <v>2122523</v>
@@ -33922,7 +33922,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G1157" t="n">
-        <v>0.327308237552643</v>
+        <v>0.327308267354965</v>
       </c>
       <c r="H1157" t="n">
         <v>662608</v>
@@ -33980,7 +33980,7 @@
         <v>0.40650001168251</v>
       </c>
       <c r="G1159" t="n">
-        <v>0.312325835227966</v>
+        <v>0.312325805425644</v>
       </c>
       <c r="H1159" t="n">
         <v>505654</v>
@@ -34009,7 +34009,7 @@
         <v>0.402500003576279</v>
       </c>
       <c r="G1160" t="n">
-        <v>0.30925253033638</v>
+        <v>0.309252500534058</v>
       </c>
       <c r="H1160" t="n">
         <v>315526</v>
@@ -34096,7 +34096,7 @@
         <v>0.418500006198883</v>
       </c>
       <c r="G1163" t="n">
-        <v>0.32154580950737</v>
+        <v>0.321545749902725</v>
       </c>
       <c r="H1163" t="n">
         <v>1118913</v>
@@ -34299,7 +34299,7 @@
         <v>0.425000011920929</v>
       </c>
       <c r="G1170" t="n">
-        <v>0.326539933681488</v>
+        <v>0.326539903879166</v>
       </c>
       <c r="H1170" t="n">
         <v>321799</v>
@@ -34328,7 +34328,7 @@
         <v>0.420500010251999</v>
       </c>
       <c r="G1171" t="n">
-        <v>0.323082447052002</v>
+        <v>0.32308241724968</v>
       </c>
       <c r="H1171" t="n">
         <v>413447</v>
@@ -34357,7 +34357,7 @@
         <v>0.418500006198883</v>
       </c>
       <c r="G1172" t="n">
-        <v>0.32154580950737</v>
+        <v>0.321545749902725</v>
       </c>
       <c r="H1172" t="n">
         <v>222772</v>
@@ -34386,7 +34386,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G1173" t="n">
-        <v>0.317319959402084</v>
+        <v>0.317319989204407</v>
       </c>
       <c r="H1173" t="n">
         <v>136423</v>
@@ -34444,7 +34444,7 @@
         <v>0.40599998831749</v>
       </c>
       <c r="G1175" t="n">
-        <v>0.311941623687744</v>
+        <v>0.311941653490067</v>
       </c>
       <c r="H1175" t="n">
         <v>110560</v>
@@ -34618,7 +34618,7 @@
         <v>0.393500000238419</v>
       </c>
       <c r="G1181" t="n">
-        <v>0.302337557077408</v>
+        <v>0.302337527275085</v>
       </c>
       <c r="H1181" t="n">
         <v>209143</v>
@@ -34647,7 +34647,7 @@
         <v>0.390500009059906</v>
       </c>
       <c r="G1182" t="n">
-        <v>0.300032585859299</v>
+        <v>0.300032556056976</v>
       </c>
       <c r="H1182" t="n">
         <v>500499</v>
@@ -34705,7 +34705,7 @@
         <v>0.390500009059906</v>
       </c>
       <c r="G1184" t="n">
-        <v>0.300032585859299</v>
+        <v>0.300032556056976</v>
       </c>
       <c r="H1184" t="n">
         <v>150711</v>
@@ -34734,7 +34734,7 @@
         <v>0.386000007390976</v>
       </c>
       <c r="G1185" t="n">
-        <v>0.29657506942749</v>
+        <v>0.296575099229813</v>
       </c>
       <c r="H1185" t="n">
         <v>152328</v>
@@ -34850,7 +34850,7 @@
         <v>0.38400000333786</v>
       </c>
       <c r="G1189" t="n">
-        <v>0.295038461685181</v>
+        <v>0.295038431882858</v>
       </c>
       <c r="H1189" t="n">
         <v>146287</v>
@@ -34879,7 +34879,7 @@
         <v>0.379999995231628</v>
       </c>
       <c r="G1190" t="n">
-        <v>0.29196509718895</v>
+        <v>0.291965067386627</v>
       </c>
       <c r="H1190" t="n">
         <v>168766</v>
@@ -34995,7 +34995,7 @@
         <v>0.379000008106232</v>
       </c>
       <c r="G1194" t="n">
-        <v>0.29119673371315</v>
+        <v>0.291196793317795</v>
       </c>
       <c r="H1194" t="n">
         <v>49875</v>
@@ -35053,7 +35053,7 @@
         <v>0.369500011205673</v>
       </c>
       <c r="G1196" t="n">
-        <v>0.283897668123245</v>
+        <v>0.283897697925568</v>
       </c>
       <c r="H1196" t="n">
         <v>149719</v>
@@ -35082,7 +35082,7 @@
         <v>0.379999995231628</v>
       </c>
       <c r="G1197" t="n">
-        <v>0.29196509718895</v>
+        <v>0.291965067386627</v>
       </c>
       <c r="H1197" t="n">
         <v>74046</v>
@@ -35111,7 +35111,7 @@
         <v>0.372999995946884</v>
       </c>
       <c r="G1198" t="n">
-        <v>0.286586791276932</v>
+        <v>0.286586821079254</v>
       </c>
       <c r="H1198" t="n">
         <v>281771</v>
@@ -35169,7 +35169,7 @@
         <v>0.356000006198883</v>
       </c>
       <c r="G1200" t="n">
-        <v>0.273525208234787</v>
+        <v>0.273525238037109</v>
       </c>
       <c r="H1200" t="n">
         <v>365229</v>
@@ -35256,7 +35256,7 @@
         <v>0.349999994039536</v>
       </c>
       <c r="G1203" t="n">
-        <v>0.268915206193924</v>
+        <v>0.268915235996246</v>
       </c>
       <c r="H1203" t="n">
         <v>342085</v>
@@ -35372,7 +35372,7 @@
         <v>0.351500004529953</v>
       </c>
       <c r="G1207" t="n">
-        <v>0.270067721605301</v>
+        <v>0.270067751407623</v>
       </c>
       <c r="H1207" t="n">
         <v>57179</v>
@@ -35401,7 +35401,7 @@
         <v>0.362500011920929</v>
       </c>
       <c r="G1208" t="n">
-        <v>0.278519332408905</v>
+        <v>0.278519362211227</v>
       </c>
       <c r="H1208" t="n">
         <v>292789</v>
@@ -35430,7 +35430,7 @@
         <v>0.356499999761581</v>
       </c>
       <c r="G1209" t="n">
-        <v>0.273909330368042</v>
+        <v>0.273909360170364</v>
       </c>
       <c r="H1209" t="n">
         <v>72200</v>
@@ -35459,7 +35459,7 @@
         <v>0.355500012636185</v>
       </c>
       <c r="G1210" t="n">
-        <v>0.27314105629921</v>
+        <v>0.273141026496887</v>
       </c>
       <c r="H1210" t="n">
         <v>45789</v>
@@ -35546,7 +35546,7 @@
         <v>0.367000013589859</v>
       </c>
       <c r="G1213" t="n">
-        <v>0.281976819038391</v>
+        <v>0.281976848840714</v>
       </c>
       <c r="H1213" t="n">
         <v>115261</v>
@@ -35604,7 +35604,7 @@
         <v>0.349999994039536</v>
       </c>
       <c r="G1215" t="n">
-        <v>0.268915206193924</v>
+        <v>0.268915235996246</v>
       </c>
       <c r="H1215" t="n">
         <v>102432</v>
@@ -35749,7 +35749,7 @@
         <v>0.344999998807907</v>
       </c>
       <c r="G1220" t="n">
-        <v>0.265073537826538</v>
+        <v>0.26507356762886</v>
       </c>
       <c r="H1220" t="n">
         <v>228492</v>
@@ -35778,7 +35778,7 @@
         <v>0.340000003576279</v>
       </c>
       <c r="G1221" t="n">
-        <v>0.261231929063797</v>
+        <v>0.261231958866119</v>
       </c>
       <c r="H1221" t="n">
         <v>170395</v>
@@ -35807,7 +35807,7 @@
         <v>0.332500010728836</v>
       </c>
       <c r="G1222" t="n">
-        <v>0.255469471216202</v>
+        <v>0.255469441413879</v>
       </c>
       <c r="H1222" t="n">
         <v>125246</v>
@@ -35836,7 +35836,7 @@
         <v>0.329499989748001</v>
       </c>
       <c r="G1223" t="n">
-        <v>0.25316447019577</v>
+        <v>0.253164499998093</v>
       </c>
       <c r="H1223" t="n">
         <v>117915</v>
@@ -35923,7 +35923,7 @@
         <v>0.324499994516373</v>
       </c>
       <c r="G1226" t="n">
-        <v>0.249322801828384</v>
+        <v>0.249322831630707</v>
       </c>
       <c r="H1226" t="n">
         <v>177760</v>
@@ -35952,7 +35952,7 @@
         <v>0.307500004768372</v>
       </c>
       <c r="G1227" t="n">
-        <v>0.236261233687401</v>
+        <v>0.236261248588562</v>
       </c>
       <c r="H1227" t="n">
         <v>367021</v>
@@ -36010,7 +36010,7 @@
         <v>0.330000013113022</v>
       </c>
       <c r="G1229" t="n">
-        <v>0.253548622131348</v>
+        <v>0.25354865193367</v>
       </c>
       <c r="H1229" t="n">
         <v>451154</v>
@@ -36039,7 +36039,7 @@
         <v>0.34850001335144</v>
       </c>
       <c r="G1230" t="n">
-        <v>0.267762750387192</v>
+        <v>0.267762720584869</v>
       </c>
       <c r="H1230" t="n">
         <v>560373</v>
@@ -36068,7 +36068,7 @@
         <v>0.368999987840652</v>
       </c>
       <c r="G1231" t="n">
-        <v>0.283513456583023</v>
+        <v>0.283513486385345</v>
       </c>
       <c r="H1231" t="n">
         <v>490748</v>
@@ -36155,7 +36155,7 @@
         <v>0.356000006198883</v>
       </c>
       <c r="G1234" t="n">
-        <v>0.273525208234787</v>
+        <v>0.273525238037109</v>
       </c>
       <c r="H1234" t="n">
         <v>259949</v>
@@ -36242,7 +36242,7 @@
         <v>0.356000006198883</v>
       </c>
       <c r="G1237" t="n">
-        <v>0.273525208234787</v>
+        <v>0.273525238037109</v>
       </c>
       <c r="H1237" t="n">
         <v>174278</v>
@@ -36300,7 +36300,7 @@
         <v>0.383500009775162</v>
       </c>
       <c r="G1239" t="n">
-        <v>0.294654250144958</v>
+        <v>0.294654279947281</v>
       </c>
       <c r="H1239" t="n">
         <v>603572</v>
@@ -36387,7 +36387,7 @@
         <v>0.405499994754791</v>
       </c>
       <c r="G1242" t="n">
-        <v>0.311557471752167</v>
+        <v>0.311557501554489</v>
       </c>
       <c r="H1242" t="n">
         <v>489392</v>
@@ -36416,7 +36416,7 @@
         <v>0.396499991416931</v>
       </c>
       <c r="G1243" t="n">
-        <v>0.304642498493195</v>
+        <v>0.304642558097839</v>
       </c>
       <c r="H1243" t="n">
         <v>383182</v>
@@ -36532,7 +36532,7 @@
         <v>0.399500012397766</v>
       </c>
       <c r="G1247" t="n">
-        <v>0.306947529315948</v>
+        <v>0.306947559118271</v>
       </c>
       <c r="H1247" t="n">
         <v>726928</v>
@@ -36706,7 +36706,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G1253" t="n">
-        <v>0.344211518764496</v>
+        <v>0.344211488962173</v>
       </c>
       <c r="H1253" t="n">
         <v>674839</v>
@@ -36735,7 +36735,7 @@
         <v>0.457500010728836</v>
       </c>
       <c r="G1254" t="n">
-        <v>0.351510614156723</v>
+        <v>0.351510643959045</v>
       </c>
       <c r="H1254" t="n">
         <v>2042950</v>
@@ -36793,7 +36793,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1256" t="n">
-        <v>0.345748156309128</v>
+        <v>0.345748126506805</v>
       </c>
       <c r="H1256" t="n">
         <v>211309</v>
@@ -36938,7 +36938,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G1261" t="n">
-        <v>0.338833212852478</v>
+        <v>0.338833183050156</v>
       </c>
       <c r="H1261" t="n">
         <v>80114</v>
@@ -37025,7 +37025,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G1264" t="n">
-        <v>0.327308237552643</v>
+        <v>0.327308267354965</v>
       </c>
       <c r="H1264" t="n">
         <v>156531</v>
@@ -37112,7 +37112,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G1267" t="n">
-        <v>0.324234932661057</v>
+        <v>0.324234962463379</v>
       </c>
       <c r="H1267" t="n">
         <v>152150</v>
@@ -37141,7 +37141,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G1268" t="n">
-        <v>0.324234932661057</v>
+        <v>0.324234962463379</v>
       </c>
       <c r="H1268" t="n">
         <v>132647</v>
@@ -37199,7 +37199,7 @@
         <v>0.413500010967255</v>
       </c>
       <c r="G1270" t="n">
-        <v>0.317704141139984</v>
+        <v>0.317704170942307</v>
       </c>
       <c r="H1270" t="n">
         <v>222853</v>
@@ -37228,7 +37228,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G1271" t="n">
-        <v>0.324234932661057</v>
+        <v>0.324234962463379</v>
       </c>
       <c r="H1271" t="n">
         <v>419507</v>
@@ -37286,7 +37286,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G1273" t="n">
-        <v>0.344211518764496</v>
+        <v>0.344211488962173</v>
       </c>
       <c r="H1273" t="n">
         <v>658425</v>
@@ -37315,7 +37315,7 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G1274" t="n">
-        <v>0.338064819574356</v>
+        <v>0.338064879179001</v>
       </c>
       <c r="H1274" t="n">
         <v>205820</v>
@@ -37344,7 +37344,7 @@
         <v>0.438499987125397</v>
       </c>
       <c r="G1275" t="n">
-        <v>0.336912333965302</v>
+        <v>0.336912363767624</v>
       </c>
       <c r="H1275" t="n">
         <v>222585</v>
@@ -37373,7 +37373,7 @@
         <v>0.425500005483627</v>
       </c>
       <c r="G1276" t="n">
-        <v>0.326924085617065</v>
+        <v>0.326924115419388</v>
       </c>
       <c r="H1276" t="n">
         <v>651575</v>
@@ -37402,7 +37402,7 @@
         <v>0.434500008821487</v>
       </c>
       <c r="G1277" t="n">
-        <v>0.333839058876038</v>
+        <v>0.333839029073715</v>
       </c>
       <c r="H1277" t="n">
         <v>772991</v>
@@ -37460,7 +37460,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G1279" t="n">
-        <v>0.328844875097275</v>
+        <v>0.32884493470192</v>
       </c>
       <c r="H1279" t="n">
         <v>85899</v>
@@ -37576,7 +37576,7 @@
         <v>0.426499992609024</v>
       </c>
       <c r="G1283" t="n">
-        <v>0.32769238948822</v>
+        <v>0.327692419290543</v>
       </c>
       <c r="H1283" t="n">
         <v>201278</v>
@@ -37634,7 +37634,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G1285" t="n">
-        <v>0.317319959402084</v>
+        <v>0.317319989204407</v>
       </c>
       <c r="H1285" t="n">
         <v>616441</v>
@@ -37692,7 +37692,7 @@
         <v>0.405499994754791</v>
       </c>
       <c r="G1287" t="n">
-        <v>0.311557471752167</v>
+        <v>0.311557501554489</v>
       </c>
       <c r="H1287" t="n">
         <v>207951</v>
@@ -37750,7 +37750,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G1289" t="n">
-        <v>0.307331681251526</v>
+        <v>0.307331711053848</v>
       </c>
       <c r="H1289" t="n">
         <v>636139</v>
@@ -37895,7 +37895,7 @@
         <v>0.442499995231628</v>
       </c>
       <c r="G1294" t="n">
-        <v>0.33998566865921</v>
+        <v>0.339985728263855</v>
       </c>
       <c r="H1294" t="n">
         <v>453481</v>
@@ -37953,7 +37953,7 @@
         <v>0.442499995231628</v>
       </c>
       <c r="G1296" t="n">
-        <v>0.33998566865921</v>
+        <v>0.339985728263855</v>
       </c>
       <c r="H1296" t="n">
         <v>645967</v>
@@ -37982,7 +37982,7 @@
         <v>0.438499987125397</v>
       </c>
       <c r="G1297" t="n">
-        <v>0.336912333965302</v>
+        <v>0.336912363767624</v>
       </c>
       <c r="H1297" t="n">
         <v>538759</v>
@@ -38069,7 +38069,7 @@
         <v>0.467500001192093</v>
       </c>
       <c r="G1300" t="n">
-        <v>0.359193950891495</v>
+        <v>0.35919389128685</v>
       </c>
       <c r="H1300" t="n">
         <v>954233</v>
@@ -38127,7 +38127,7 @@
         <v>0.458000004291534</v>
       </c>
       <c r="G1302" t="n">
-        <v>0.351894795894623</v>
+        <v>0.3518947660923</v>
       </c>
       <c r="H1302" t="n">
         <v>634273</v>
@@ -38185,7 +38185,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G1304" t="n">
-        <v>0.353431463241577</v>
+        <v>0.353431433439255</v>
       </c>
       <c r="H1304" t="n">
         <v>538303</v>
@@ -38214,7 +38214,7 @@
         <v>0.474500000476837</v>
       </c>
       <c r="G1305" t="n">
-        <v>0.36457222700119</v>
+        <v>0.364572197198868</v>
       </c>
       <c r="H1305" t="n">
         <v>720968</v>
@@ -38330,7 +38330,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G1309" t="n">
-        <v>0.353431463241577</v>
+        <v>0.353431433439255</v>
       </c>
       <c r="H1309" t="n">
         <v>264309</v>
@@ -38359,7 +38359,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G1310" t="n">
-        <v>0.353431463241577</v>
+        <v>0.353431433439255</v>
       </c>
       <c r="H1310" t="n">
         <v>248356</v>
@@ -38388,7 +38388,7 @@
         <v>0.474000006914139</v>
       </c>
       <c r="G1311" t="n">
-        <v>0.364188075065613</v>
+        <v>0.36418804526329</v>
       </c>
       <c r="H1311" t="n">
         <v>684426</v>
@@ -38417,7 +38417,7 @@
         <v>0.479000002145767</v>
       </c>
       <c r="G1312" t="n">
-        <v>0.368029683828354</v>
+        <v>0.368029713630676</v>
       </c>
       <c r="H1312" t="n">
         <v>551502</v>
@@ -38591,7 +38591,7 @@
         <v>0.465999990701675</v>
       </c>
       <c r="G1318" t="n">
-        <v>0.358041435480118</v>
+        <v>0.358041405677795</v>
       </c>
       <c r="H1318" t="n">
         <v>109101</v>
@@ -38707,7 +38707,7 @@
         <v>0.462000012397766</v>
       </c>
       <c r="G1322" t="n">
-        <v>0.354968100786209</v>
+        <v>0.354968130588531</v>
       </c>
       <c r="H1322" t="n">
         <v>239416</v>
@@ -38736,7 +38736,7 @@
         <v>0.453000009059906</v>
       </c>
       <c r="G1323" t="n">
-        <v>0.348053127527237</v>
+        <v>0.348053157329559</v>
       </c>
       <c r="H1323" t="n">
         <v>759977</v>
@@ -38910,7 +38910,7 @@
         <v>0.456000000238419</v>
       </c>
       <c r="G1329" t="n">
-        <v>0.350358098745346</v>
+        <v>0.350358158349991</v>
       </c>
       <c r="H1329" t="n">
         <v>64317</v>
@@ -38939,7 +38939,7 @@
         <v>0.450500011444092</v>
       </c>
       <c r="G1330" t="n">
-        <v>0.346132278442383</v>
+        <v>0.346132308244705</v>
       </c>
       <c r="H1330" t="n">
         <v>288418</v>
@@ -38968,7 +38968,7 @@
         <v>0.44200000166893</v>
       </c>
       <c r="G1331" t="n">
-        <v>0.339601516723633</v>
+        <v>0.339601546525955</v>
       </c>
       <c r="H1331" t="n">
         <v>233906</v>
@@ -38997,7 +38997,7 @@
         <v>0.451999992132187</v>
       </c>
       <c r="G1332" t="n">
-        <v>0.34728479385376</v>
+        <v>0.347284823656082</v>
       </c>
       <c r="H1332" t="n">
         <v>518740</v>
@@ -39084,7 +39084,7 @@
         <v>0.472499996423721</v>
       </c>
       <c r="G1335" t="n">
-        <v>0.363035559654236</v>
+        <v>0.363035529851913</v>
       </c>
       <c r="H1335" t="n">
         <v>255911</v>
@@ -39171,7 +39171,7 @@
         <v>0.458000004291534</v>
       </c>
       <c r="G1338" t="n">
-        <v>0.351894795894623</v>
+        <v>0.3518947660923</v>
       </c>
       <c r="H1338" t="n">
         <v>107286</v>
@@ -39229,7 +39229,7 @@
         <v>0.477999985218048</v>
       </c>
       <c r="G1340" t="n">
-        <v>0.367261379957199</v>
+        <v>0.367261320352554</v>
       </c>
       <c r="H1340" t="n">
         <v>1122989</v>
@@ -39258,7 +39258,7 @@
         <v>0.490500003099442</v>
       </c>
       <c r="G1341" t="n">
-        <v>0.376865476369858</v>
+        <v>0.376865446567535</v>
       </c>
       <c r="H1341" t="n">
         <v>2353291</v>
@@ -39287,7 +39287,7 @@
         <v>0.493499994277954</v>
       </c>
       <c r="G1342" t="n">
-        <v>0.379170447587967</v>
+        <v>0.379170477390289</v>
       </c>
       <c r="H1342" t="n">
         <v>671887</v>
@@ -39345,7 +39345,7 @@
         <v>0.493499994277954</v>
       </c>
       <c r="G1344" t="n">
-        <v>0.379170447587967</v>
+        <v>0.379170477390289</v>
       </c>
       <c r="H1344" t="n">
         <v>420374</v>
@@ -39403,7 +39403,7 @@
         <v>0.472499996423721</v>
       </c>
       <c r="G1346" t="n">
-        <v>0.363035559654236</v>
+        <v>0.363035529851913</v>
       </c>
       <c r="H1346" t="n">
         <v>417183</v>
@@ -39490,7 +39490,7 @@
         <v>0.477999985218048</v>
       </c>
       <c r="G1349" t="n">
-        <v>0.367261379957199</v>
+        <v>0.367261320352554</v>
       </c>
       <c r="H1349" t="n">
         <v>93170</v>
@@ -39664,7 +39664,7 @@
         <v>0.474500000476837</v>
       </c>
       <c r="G1355" t="n">
-        <v>0.36457222700119</v>
+        <v>0.364572197198868</v>
       </c>
       <c r="H1355" t="n">
         <v>203582</v>
@@ -39693,7 +39693,7 @@
         <v>0.474500000476837</v>
       </c>
       <c r="G1356" t="n">
-        <v>0.36457222700119</v>
+        <v>0.364572197198868</v>
       </c>
       <c r="H1356" t="n">
         <v>85584</v>
@@ -39809,7 +39809,7 @@
         <v>0.477999985218048</v>
       </c>
       <c r="G1360" t="n">
-        <v>0.367261379957199</v>
+        <v>0.367261320352554</v>
       </c>
       <c r="H1360" t="n">
         <v>208030</v>
@@ -39925,7 +39925,7 @@
         <v>0.485000014305115</v>
       </c>
       <c r="G1364" t="n">
-        <v>0.372639685869217</v>
+        <v>0.372639715671539</v>
       </c>
       <c r="H1364" t="n">
         <v>314630</v>
@@ -39954,7 +39954,7 @@
         <v>0.48649999499321</v>
       </c>
       <c r="G1365" t="n">
-        <v>0.373792171478271</v>
+        <v>0.373792141675949</v>
       </c>
       <c r="H1365" t="n">
         <v>261249</v>
@@ -40070,7 +40070,7 @@
         <v>0.475499987602234</v>
       </c>
       <c r="G1369" t="n">
-        <v>0.365340560674667</v>
+        <v>0.365340530872345</v>
       </c>
       <c r="H1369" t="n">
         <v>180910</v>
@@ -40157,7 +40157,7 @@
         <v>0.474000006914139</v>
       </c>
       <c r="G1372" t="n">
-        <v>0.364188075065613</v>
+        <v>0.36418804526329</v>
       </c>
       <c r="H1372" t="n">
         <v>99465</v>
@@ -40186,7 +40186,7 @@
         <v>0.479000002145767</v>
       </c>
       <c r="G1373" t="n">
-        <v>0.368029683828354</v>
+        <v>0.368029713630676</v>
       </c>
       <c r="H1373" t="n">
         <v>167090</v>
@@ -40244,7 +40244,7 @@
         <v>0.485500007867813</v>
       </c>
       <c r="G1375" t="n">
-        <v>0.373023808002472</v>
+        <v>0.373023837804794</v>
       </c>
       <c r="H1375" t="n">
         <v>122760</v>
@@ -40273,7 +40273,7 @@
         <v>0.493999987840652</v>
       </c>
       <c r="G1376" t="n">
-        <v>0.379554629325867</v>
+        <v>0.379554599523544</v>
       </c>
       <c r="H1376" t="n">
         <v>792595</v>
@@ -40331,7 +40331,7 @@
         <v>0.501999974250793</v>
       </c>
       <c r="G1378" t="n">
-        <v>0.385701268911362</v>
+        <v>0.385701239109039</v>
       </c>
       <c r="H1378" t="n">
         <v>439413</v>
@@ -40360,7 +40360,7 @@
         <v>0.510999977588654</v>
       </c>
       <c r="G1379" t="n">
-        <v>0.392616242170334</v>
+        <v>0.392616182565689</v>
       </c>
       <c r="H1379" t="n">
         <v>376087</v>
@@ -40389,7 +40389,7 @@
         <v>0.504000008106232</v>
       </c>
       <c r="G1380" t="n">
-        <v>0.387237966060638</v>
+        <v>0.387237906455994</v>
       </c>
       <c r="H1380" t="n">
         <v>429906</v>
@@ -40563,7 +40563,7 @@
         <v>0.554000020027161</v>
       </c>
       <c r="G1386" t="n">
-        <v>0.42565444111824</v>
+        <v>0.425654411315918</v>
       </c>
       <c r="H1386" t="n">
         <v>312064</v>
@@ -40592,7 +40592,7 @@
         <v>0.545000016689301</v>
       </c>
       <c r="G1387" t="n">
-        <v>0.418739467859268</v>
+        <v>0.418739438056946</v>
       </c>
       <c r="H1387" t="n">
         <v>571005</v>
@@ -40621,7 +40621,7 @@
         <v>0.533999979496002</v>
       </c>
       <c r="G1388" t="n">
-        <v>0.410287797451019</v>
+        <v>0.410287767648697</v>
       </c>
       <c r="H1388" t="n">
         <v>693151</v>
@@ -40650,7 +40650,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G1389" t="n">
-        <v>0.417971104383469</v>
+        <v>0.417971074581146</v>
       </c>
       <c r="H1389" t="n">
         <v>799079</v>
@@ -40679,7 +40679,7 @@
         <v>0.545000016689301</v>
       </c>
       <c r="G1390" t="n">
-        <v>0.418739467859268</v>
+        <v>0.418739438056946</v>
       </c>
       <c r="H1390" t="n">
         <v>588569</v>
@@ -40708,7 +40708,7 @@
         <v>0.541999995708466</v>
       </c>
       <c r="G1391" t="n">
-        <v>0.416434437036514</v>
+        <v>0.416434466838837</v>
       </c>
       <c r="H1391" t="n">
         <v>1196998</v>
@@ -40824,7 +40824,7 @@
         <v>0.532999992370605</v>
       </c>
       <c r="G1395" t="n">
-        <v>0.409519493579865</v>
+        <v>0.40951943397522</v>
       </c>
       <c r="H1395" t="n">
         <v>310765</v>
@@ -40911,7 +40911,7 @@
         <v>0.541999995708466</v>
       </c>
       <c r="G1398" t="n">
-        <v>0.416434437036514</v>
+        <v>0.416434466838837</v>
       </c>
       <c r="H1398" t="n">
         <v>419110</v>
@@ -40940,7 +40940,7 @@
         <v>0.550999999046326</v>
       </c>
       <c r="G1399" t="n">
-        <v>0.423349440097809</v>
+        <v>0.423349410295486</v>
       </c>
       <c r="H1399" t="n">
         <v>442923</v>
@@ -40969,7 +40969,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G1400" t="n">
-        <v>0.417971104383469</v>
+        <v>0.417971074581146</v>
       </c>
       <c r="H1400" t="n">
         <v>181734</v>
@@ -40998,7 +40998,7 @@
         <v>0.528999984264374</v>
       </c>
       <c r="G1401" t="n">
-        <v>0.406446129083633</v>
+        <v>0.406446099281311</v>
       </c>
       <c r="H1401" t="n">
         <v>369579</v>
@@ -41027,7 +41027,7 @@
         <v>0.528999984264374</v>
       </c>
       <c r="G1402" t="n">
-        <v>0.406446129083633</v>
+        <v>0.406446099281311</v>
       </c>
       <c r="H1402" t="n">
         <v>776792</v>
@@ -41056,7 +41056,7 @@
         <v>0.533999979496002</v>
       </c>
       <c r="G1403" t="n">
-        <v>0.410287797451019</v>
+        <v>0.410287767648697</v>
       </c>
       <c r="H1403" t="n">
         <v>376604</v>
@@ -41143,7 +41143,7 @@
         <v>0.510999977588654</v>
       </c>
       <c r="G1406" t="n">
-        <v>0.392616242170334</v>
+        <v>0.392616182565689</v>
       </c>
       <c r="H1406" t="n">
         <v>1301061</v>
@@ -41230,7 +41230,7 @@
         <v>0.485000014305115</v>
       </c>
       <c r="G1409" t="n">
-        <v>0.372639685869217</v>
+        <v>0.372639715671539</v>
       </c>
       <c r="H1409" t="n">
         <v>655810</v>
@@ -41259,7 +41259,7 @@
         <v>0.474500000476837</v>
       </c>
       <c r="G1410" t="n">
-        <v>0.36457222700119</v>
+        <v>0.364572197198868</v>
       </c>
       <c r="H1410" t="n">
         <v>739946</v>
@@ -41288,7 +41288,7 @@
         <v>0.493499994277954</v>
       </c>
       <c r="G1411" t="n">
-        <v>0.379170447587967</v>
+        <v>0.379170477390289</v>
       </c>
       <c r="H1411" t="n">
         <v>403657</v>
@@ -41433,7 +41433,7 @@
         <v>0.504000008106232</v>
       </c>
       <c r="G1416" t="n">
-        <v>0.387237966060638</v>
+        <v>0.387237906455994</v>
       </c>
       <c r="H1416" t="n">
         <v>149641</v>
@@ -41462,7 +41462,7 @@
         <v>0.505999982357025</v>
       </c>
       <c r="G1417" t="n">
-        <v>0.388774573802948</v>
+        <v>0.388774544000626</v>
       </c>
       <c r="H1417" t="n">
         <v>274907</v>
@@ -41520,7 +41520,7 @@
         <v>0.504000008106232</v>
       </c>
       <c r="G1419" t="n">
-        <v>0.387237966060638</v>
+        <v>0.387237906455994</v>
       </c>
       <c r="H1419" t="n">
         <v>358942</v>
@@ -41549,7 +41549,7 @@
         <v>0.497999995946884</v>
       </c>
       <c r="G1420" t="n">
-        <v>0.382627993822098</v>
+        <v>0.382627964019775</v>
       </c>
       <c r="H1420" t="n">
         <v>371173</v>
@@ -41578,7 +41578,7 @@
         <v>0.501999974250793</v>
       </c>
       <c r="G1421" t="n">
-        <v>0.385701268911362</v>
+        <v>0.385701239109039</v>
       </c>
       <c r="H1421" t="n">
         <v>316009</v>
@@ -41636,7 +41636,7 @@
         <v>0.498499989509583</v>
       </c>
       <c r="G1423" t="n">
-        <v>0.383012115955353</v>
+        <v>0.383012145757675</v>
       </c>
       <c r="H1423" t="n">
         <v>385727</v>
@@ -41665,7 +41665,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1424" t="n">
-        <v>0.376481354236603</v>
+        <v>0.37648132443428</v>
       </c>
       <c r="H1424" t="n">
         <v>119471</v>
@@ -41694,7 +41694,7 @@
         <v>0.491499990224838</v>
       </c>
       <c r="G1425" t="n">
-        <v>0.377633780241013</v>
+        <v>0.377633810043335</v>
       </c>
       <c r="H1425" t="n">
         <v>238157</v>
@@ -41752,7 +41752,7 @@
         <v>0.492500007152557</v>
       </c>
       <c r="G1427" t="n">
-        <v>0.378402173519135</v>
+        <v>0.378402143716812</v>
       </c>
       <c r="H1427" t="n">
         <v>201644</v>
@@ -41781,7 +41781,7 @@
         <v>0.497999995946884</v>
       </c>
       <c r="G1428" t="n">
-        <v>0.382627993822098</v>
+        <v>0.382627964019775</v>
       </c>
       <c r="H1428" t="n">
         <v>169793</v>
@@ -41810,7 +41810,7 @@
         <v>0.495999991893768</v>
       </c>
       <c r="G1429" t="n">
-        <v>0.381091296672821</v>
+        <v>0.381091326475143</v>
       </c>
       <c r="H1429" t="n">
         <v>221517</v>
@@ -41839,7 +41839,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1430" t="n">
-        <v>0.376481354236603</v>
+        <v>0.37648132443428</v>
       </c>
       <c r="H1430" t="n">
         <v>48516</v>
@@ -41868,7 +41868,7 @@
         <v>0.495000004768372</v>
       </c>
       <c r="G1431" t="n">
-        <v>0.380322992801666</v>
+        <v>0.380322962999344</v>
       </c>
       <c r="H1431" t="n">
         <v>478406</v>
@@ -41897,7 +41897,7 @@
         <v>0.467500001192093</v>
       </c>
       <c r="G1432" t="n">
-        <v>0.359193950891495</v>
+        <v>0.35919389128685</v>
       </c>
       <c r="H1432" t="n">
         <v>2537340</v>
@@ -41955,7 +41955,7 @@
         <v>0.451999992132187</v>
       </c>
       <c r="G1434" t="n">
-        <v>0.34728479385376</v>
+        <v>0.347284823656082</v>
       </c>
       <c r="H1434" t="n">
         <v>785696</v>
@@ -42071,7 +42071,7 @@
         <v>0.463499993085861</v>
       </c>
       <c r="G1438" t="n">
-        <v>0.356120616197586</v>
+        <v>0.356120556592941</v>
       </c>
       <c r="H1438" t="n">
         <v>647629</v>
@@ -42129,7 +42129,7 @@
         <v>0.469500005245209</v>
       </c>
       <c r="G1440" t="n">
-        <v>0.360730558633804</v>
+        <v>0.360730588436127</v>
       </c>
       <c r="H1440" t="n">
         <v>360412</v>
@@ -42158,7 +42158,7 @@
         <v>0.474500000476837</v>
       </c>
       <c r="G1441" t="n">
-        <v>0.36457222700119</v>
+        <v>0.364572197198868</v>
       </c>
       <c r="H1441" t="n">
         <v>375277</v>
@@ -42187,7 +42187,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G1442" t="n">
-        <v>0.422581046819687</v>
+        <v>0.422581076622009</v>
       </c>
       <c r="H1442" t="n">
         <v>10499570</v>
@@ -42216,7 +42216,7 @@
         <v>0.545000016689301</v>
       </c>
       <c r="G1443" t="n">
-        <v>0.418739467859268</v>
+        <v>0.418739438056946</v>
       </c>
       <c r="H1443" t="n">
         <v>8544072</v>
@@ -42274,7 +42274,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G1445" t="n">
-        <v>0.422581046819687</v>
+        <v>0.422581076622009</v>
       </c>
       <c r="H1445" t="n">
         <v>3065828</v>
@@ -42303,7 +42303,7 @@
         <v>0.549000024795532</v>
       </c>
       <c r="G1446" t="n">
-        <v>0.421812742948532</v>
+        <v>0.421812772750854</v>
       </c>
       <c r="H1446" t="n">
         <v>1587777</v>
@@ -42361,7 +42361,7 @@
         <v>0.528999984264374</v>
       </c>
       <c r="G1448" t="n">
-        <v>0.406446129083633</v>
+        <v>0.406446099281311</v>
       </c>
       <c r="H1448" t="n">
         <v>1547488</v>
@@ -42390,7 +42390,7 @@
         <v>0.521000027656555</v>
       </c>
       <c r="G1449" t="n">
-        <v>0.400299549102783</v>
+        <v>0.400299519300461</v>
       </c>
       <c r="H1449" t="n">
         <v>795437</v>
@@ -42448,7 +42448,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G1451" t="n">
-        <v>0.399531185626984</v>
+        <v>0.399531155824661</v>
       </c>
       <c r="H1451" t="n">
         <v>804234</v>
@@ -42477,7 +42477,7 @@
         <v>0.517000019550323</v>
       </c>
       <c r="G1452" t="n">
-        <v>0.397226214408875</v>
+        <v>0.397226184606552</v>
       </c>
       <c r="H1452" t="n">
         <v>603908</v>
@@ -42506,7 +42506,7 @@
         <v>0.513999998569489</v>
       </c>
       <c r="G1453" t="n">
-        <v>0.394921183586121</v>
+        <v>0.394921243190765</v>
       </c>
       <c r="H1453" t="n">
         <v>324088</v>
@@ -42651,7 +42651,7 @@
         <v>0.513999998569489</v>
       </c>
       <c r="G1458" t="n">
-        <v>0.394921183586121</v>
+        <v>0.394921243190765</v>
       </c>
       <c r="H1458" t="n">
         <v>157473</v>
@@ -42709,7 +42709,7 @@
         <v>0.500999987125397</v>
       </c>
       <c r="G1460" t="n">
-        <v>0.384932905435562</v>
+        <v>0.384932935237885</v>
       </c>
       <c r="H1460" t="n">
         <v>681074</v>
@@ -42738,7 +42738,7 @@
         <v>0.495999991893768</v>
       </c>
       <c r="G1461" t="n">
-        <v>0.381091296672821</v>
+        <v>0.381091326475143</v>
       </c>
       <c r="H1461" t="n">
         <v>327677</v>
@@ -42767,7 +42767,7 @@
         <v>0.488000005483627</v>
       </c>
       <c r="G1462" t="n">
-        <v>0.374944657087326</v>
+        <v>0.374944627285004</v>
       </c>
       <c r="H1462" t="n">
         <v>474735</v>
@@ -42796,7 +42796,7 @@
         <v>0.488499999046326</v>
       </c>
       <c r="G1463" t="n">
-        <v>0.375328838825226</v>
+        <v>0.375328809022903</v>
       </c>
       <c r="H1463" t="n">
         <v>720591</v>
@@ -42825,7 +42825,7 @@
         <v>0.49549999833107</v>
       </c>
       <c r="G1464" t="n">
-        <v>0.380707114934921</v>
+        <v>0.380707144737244</v>
       </c>
       <c r="H1464" t="n">
         <v>226218</v>
@@ -42941,7 +42941,7 @@
         <v>0.504999995231628</v>
       </c>
       <c r="G1468" t="n">
-        <v>0.388006240129471</v>
+        <v>0.388006269931793</v>
       </c>
       <c r="H1468" t="n">
         <v>633941</v>
@@ -42970,7 +42970,7 @@
         <v>0.545000016689301</v>
       </c>
       <c r="G1469" t="n">
-        <v>0.418739467859268</v>
+        <v>0.418739438056946</v>
       </c>
       <c r="H1469" t="n">
         <v>3580885</v>
@@ -43057,7 +43057,7 @@
         <v>0.53600001335144</v>
       </c>
       <c r="G1472" t="n">
-        <v>0.411824464797974</v>
+        <v>0.411824494600296</v>
       </c>
       <c r="H1472" t="n">
         <v>518530</v>
@@ -43173,7 +43173,7 @@
         <v>0.521000027656555</v>
       </c>
       <c r="G1476" t="n">
-        <v>0.400299549102783</v>
+        <v>0.400299519300461</v>
       </c>
       <c r="H1476" t="n">
         <v>413917</v>
@@ -43289,7 +43289,7 @@
         <v>0.541000008583069</v>
       </c>
       <c r="G1480" t="n">
-        <v>0.415666103363037</v>
+        <v>0.415666133165359</v>
       </c>
       <c r="H1480" t="n">
         <v>613061</v>
@@ -43318,7 +43318,7 @@
         <v>0.526000022888184</v>
       </c>
       <c r="G1481" t="n">
-        <v>0.404141157865524</v>
+        <v>0.404141187667847</v>
       </c>
       <c r="H1481" t="n">
         <v>330560</v>
@@ -43347,7 +43347,7 @@
         <v>0.523000001907349</v>
       </c>
       <c r="G1482" t="n">
-        <v>0.401836216449738</v>
+        <v>0.401836186647415</v>
       </c>
       <c r="H1482" t="n">
         <v>444124</v>
@@ -43521,7 +43521,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G1488" t="n">
-        <v>0.399531185626984</v>
+        <v>0.399531155824661</v>
       </c>
       <c r="H1488" t="n">
         <v>403223</v>
@@ -43550,7 +43550,7 @@
         <v>0.523000001907349</v>
       </c>
       <c r="G1489" t="n">
-        <v>0.401836216449738</v>
+        <v>0.401836186647415</v>
       </c>
       <c r="H1489" t="n">
         <v>326523</v>
@@ -43579,7 +43579,7 @@
         <v>0.526000022888184</v>
       </c>
       <c r="G1490" t="n">
-        <v>0.404141157865524</v>
+        <v>0.404141187667847</v>
       </c>
       <c r="H1490" t="n">
         <v>1397392</v>
@@ -43666,7 +43666,7 @@
         <v>0.526000022888184</v>
       </c>
       <c r="G1493" t="n">
-        <v>0.404141157865524</v>
+        <v>0.404141187667847</v>
       </c>
       <c r="H1493" t="n">
         <v>3105393</v>
@@ -43695,7 +43695,7 @@
         <v>0.533999979496002</v>
       </c>
       <c r="G1494" t="n">
-        <v>0.410287797451019</v>
+        <v>0.410287767648697</v>
       </c>
       <c r="H1494" t="n">
         <v>1403748</v>
@@ -43782,7 +43782,7 @@
         <v>0.500999987125397</v>
       </c>
       <c r="G1497" t="n">
-        <v>0.384932905435562</v>
+        <v>0.384932935237885</v>
       </c>
       <c r="H1497" t="n">
         <v>610128</v>
@@ -43811,7 +43811,7 @@
         <v>0.491499990224838</v>
       </c>
       <c r="G1498" t="n">
-        <v>0.377633780241013</v>
+        <v>0.377633810043335</v>
       </c>
       <c r="H1498" t="n">
         <v>751082</v>
@@ -43840,7 +43840,7 @@
         <v>0.497999995946884</v>
       </c>
       <c r="G1499" t="n">
-        <v>0.382627993822098</v>
+        <v>0.382627964019775</v>
       </c>
       <c r="H1499" t="n">
         <v>792105</v>
@@ -43869,7 +43869,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1500" t="n">
-        <v>0.376481354236603</v>
+        <v>0.37648132443428</v>
       </c>
       <c r="H1500" t="n">
         <v>616271</v>
@@ -43898,7 +43898,7 @@
         <v>0.487500011920929</v>
       </c>
       <c r="G1501" t="n">
-        <v>0.374560475349426</v>
+        <v>0.374560505151749</v>
       </c>
       <c r="H1501" t="n">
         <v>949587</v>
@@ -43927,7 +43927,7 @@
         <v>0.479499995708466</v>
       </c>
       <c r="G1502" t="n">
-        <v>0.368413895368576</v>
+        <v>0.368413835763931</v>
       </c>
       <c r="H1502" t="n">
         <v>786661</v>
@@ -44014,7 +44014,7 @@
         <v>0.453000009059906</v>
       </c>
       <c r="G1505" t="n">
-        <v>0.348053127527237</v>
+        <v>0.348053157329559</v>
       </c>
       <c r="H1505" t="n">
         <v>894000</v>
@@ -44159,7 +44159,7 @@
         <v>0.444999992847443</v>
       </c>
       <c r="G1510" t="n">
-        <v>0.341906547546387</v>
+        <v>0.341906487941742</v>
       </c>
       <c r="H1510" t="n">
         <v>1550377</v>
@@ -44246,7 +44246,7 @@
         <v>0.44200000166893</v>
       </c>
       <c r="G1513" t="n">
-        <v>0.339601516723633</v>
+        <v>0.339601546525955</v>
       </c>
       <c r="H1513" t="n">
         <v>356572</v>
@@ -44304,7 +44304,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G1515" t="n">
-        <v>0.329613238573074</v>
+        <v>0.329613268375397</v>
       </c>
       <c r="H1515" t="n">
         <v>555351</v>
@@ -44333,7 +44333,7 @@
         <v>0.425500005483627</v>
       </c>
       <c r="G1516" t="n">
-        <v>0.326924085617065</v>
+        <v>0.326924115419388</v>
       </c>
       <c r="H1516" t="n">
         <v>331911</v>
@@ -44362,7 +44362,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G1517" t="n">
-        <v>0.338833212852478</v>
+        <v>0.338833183050156</v>
       </c>
       <c r="H1517" t="n">
         <v>625622</v>
@@ -44391,7 +44391,7 @@
         <v>0.431499987840652</v>
       </c>
       <c r="G1518" t="n">
-        <v>0.331534057855606</v>
+        <v>0.331534028053284</v>
       </c>
       <c r="H1518" t="n">
         <v>184159</v>
@@ -44449,7 +44449,7 @@
         <v>0.421000003814697</v>
       </c>
       <c r="G1520" t="n">
-        <v>0.323466598987579</v>
+        <v>0.323466569185257</v>
       </c>
       <c r="H1520" t="n">
         <v>297294</v>
@@ -44507,7 +44507,7 @@
         <v>0.44200000166893</v>
       </c>
       <c r="G1522" t="n">
-        <v>0.339601516723633</v>
+        <v>0.339601546525955</v>
       </c>
       <c r="H1522" t="n">
         <v>217434</v>
@@ -44565,7 +44565,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G1524" t="n">
-        <v>0.337296515703201</v>
+        <v>0.337296545505524</v>
       </c>
       <c r="H1524" t="n">
         <v>248550</v>
@@ -44594,7 +44594,7 @@
         <v>0.430999994277954</v>
       </c>
       <c r="G1525" t="n">
-        <v>0.331149905920029</v>
+        <v>0.331149876117706</v>
       </c>
       <c r="H1525" t="n">
         <v>143956</v>
@@ -44739,7 +44739,7 @@
         <v>0.462000012397766</v>
       </c>
       <c r="G1530" t="n">
-        <v>0.354968100786209</v>
+        <v>0.354968130588531</v>
       </c>
       <c r="H1530" t="n">
         <v>543816</v>
@@ -44768,7 +44768,7 @@
         <v>0.458000004291534</v>
       </c>
       <c r="G1531" t="n">
-        <v>0.351894795894623</v>
+        <v>0.3518947660923</v>
       </c>
       <c r="H1531" t="n">
         <v>446463</v>
@@ -44826,7 +44826,7 @@
         <v>0.456000000238419</v>
       </c>
       <c r="G1533" t="n">
-        <v>0.350358098745346</v>
+        <v>0.350358158349991</v>
       </c>
       <c r="H1533" t="n">
         <v>173653</v>
@@ -44913,7 +44913,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1536" t="n">
-        <v>0.345748156309128</v>
+        <v>0.345748126506805</v>
       </c>
       <c r="H1536" t="n">
         <v>153683</v>
@@ -45116,7 +45116,7 @@
         <v>0.420500010251999</v>
       </c>
       <c r="G1543" t="n">
-        <v>0.323082447052002</v>
+        <v>0.32308241724968</v>
       </c>
       <c r="H1543" t="n">
         <v>677742</v>
@@ -45174,7 +45174,7 @@
         <v>0.420500010251999</v>
       </c>
       <c r="G1545" t="n">
-        <v>0.323082447052002</v>
+        <v>0.32308241724968</v>
       </c>
       <c r="H1545" t="n">
         <v>213454</v>
@@ -45261,7 +45261,7 @@
         <v>0.421499997377396</v>
       </c>
       <c r="G1548" t="n">
-        <v>0.323850750923157</v>
+        <v>0.323850780725479</v>
       </c>
       <c r="H1548" t="n">
         <v>154520</v>
@@ -45290,7 +45290,7 @@
         <v>0.428000003099442</v>
       </c>
       <c r="G1549" t="n">
-        <v>0.328844875097275</v>
+        <v>0.32884493470192</v>
       </c>
       <c r="H1549" t="n">
         <v>300970</v>
@@ -45319,7 +45319,7 @@
         <v>0.432500004768372</v>
       </c>
       <c r="G1550" t="n">
-        <v>0.332302361726761</v>
+        <v>0.332302391529083</v>
       </c>
       <c r="H1550" t="n">
         <v>187127</v>
@@ -45435,7 +45435,7 @@
         <v>0.430999994277954</v>
       </c>
       <c r="G1554" t="n">
-        <v>0.331149905920029</v>
+        <v>0.331149876117706</v>
       </c>
       <c r="H1554" t="n">
         <v>239976</v>
@@ -45464,7 +45464,7 @@
         <v>0.430999994277954</v>
       </c>
       <c r="G1555" t="n">
-        <v>0.331149905920029</v>
+        <v>0.331149876117706</v>
       </c>
       <c r="H1555" t="n">
         <v>232435</v>
@@ -45493,7 +45493,7 @@
         <v>0.421000003814697</v>
       </c>
       <c r="G1556" t="n">
-        <v>0.323466598987579</v>
+        <v>0.323466569185257</v>
       </c>
       <c r="H1556" t="n">
         <v>236203</v>
@@ -45522,7 +45522,7 @@
         <v>0.40599998831749</v>
       </c>
       <c r="G1557" t="n">
-        <v>0.311941623687744</v>
+        <v>0.311941653490067</v>
       </c>
       <c r="H1557" t="n">
         <v>560928</v>
@@ -45551,7 +45551,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G1558" t="n">
-        <v>0.327308237552643</v>
+        <v>0.327308267354965</v>
       </c>
       <c r="H1558" t="n">
         <v>411443</v>
@@ -45609,7 +45609,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G1560" t="n">
-        <v>0.317319959402084</v>
+        <v>0.317319989204407</v>
       </c>
       <c r="H1560" t="n">
         <v>112376</v>
@@ -45696,7 +45696,7 @@
         <v>0.40599998831749</v>
       </c>
       <c r="G1563" t="n">
-        <v>0.311941623687744</v>
+        <v>0.311941653490067</v>
       </c>
       <c r="H1563" t="n">
         <v>426484</v>
@@ -45725,7 +45725,7 @@
         <v>0.412000000476837</v>
       </c>
       <c r="G1564" t="n">
-        <v>0.316551625728607</v>
+        <v>0.31655165553093</v>
       </c>
       <c r="H1564" t="n">
         <v>245099</v>
@@ -45870,7 +45870,7 @@
         <v>0.386000007390976</v>
       </c>
       <c r="G1569" t="n">
-        <v>0.29657506942749</v>
+        <v>0.296575099229813</v>
       </c>
       <c r="H1569" t="n">
         <v>676848</v>
@@ -45899,7 +45899,7 @@
         <v>0.386000007390976</v>
       </c>
       <c r="G1570" t="n">
-        <v>0.29657506942749</v>
+        <v>0.296575099229813</v>
       </c>
       <c r="H1570" t="n">
         <v>537771</v>
@@ -45986,7 +45986,7 @@
         <v>0.36599999666214</v>
       </c>
       <c r="G1573" t="n">
-        <v>0.281208485364914</v>
+        <v>0.281208544969559</v>
       </c>
       <c r="H1573" t="n">
         <v>809840</v>
@@ -46073,7 +46073,7 @@
         <v>0.38400000333786</v>
       </c>
       <c r="G1576" t="n">
-        <v>0.295038461685181</v>
+        <v>0.295038431882858</v>
       </c>
       <c r="H1576" t="n">
         <v>465210</v>
@@ -46102,7 +46102,7 @@
         <v>0.381999999284744</v>
       </c>
       <c r="G1577" t="n">
-        <v>0.293501764535904</v>
+        <v>0.293501734733582</v>
       </c>
       <c r="H1577" t="n">
         <v>150066</v>
@@ -46131,7 +46131,7 @@
         <v>0.379999995231628</v>
       </c>
       <c r="G1578" t="n">
-        <v>0.29196509718895</v>
+        <v>0.291965067386627</v>
       </c>
       <c r="H1578" t="n">
         <v>116948</v>
@@ -46218,7 +46218,7 @@
         <v>0.40599998831749</v>
       </c>
       <c r="G1581" t="n">
-        <v>0.311941623687744</v>
+        <v>0.311941653490067</v>
       </c>
       <c r="H1581" t="n">
         <v>1601217</v>
@@ -46392,7 +46392,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1587" t="n">
-        <v>0.345748156309128</v>
+        <v>0.345748126506805</v>
       </c>
       <c r="H1587" t="n">
         <v>379279</v>
@@ -46450,7 +46450,7 @@
         <v>0.434500008821487</v>
       </c>
       <c r="G1589" t="n">
-        <v>0.333839058876038</v>
+        <v>0.333839029073715</v>
       </c>
       <c r="H1589" t="n">
         <v>1414754</v>
@@ -46508,7 +46508,7 @@
         <v>0.442499995231628</v>
       </c>
       <c r="G1591" t="n">
-        <v>0.33998566865921</v>
+        <v>0.339985728263855</v>
       </c>
       <c r="H1591" t="n">
         <v>810523</v>
@@ -46537,7 +46537,7 @@
         <v>0.442499995231628</v>
       </c>
       <c r="G1592" t="n">
-        <v>0.33998566865921</v>
+        <v>0.339985728263855</v>
       </c>
       <c r="H1592" t="n">
         <v>216499</v>
@@ -46595,7 +46595,7 @@
         <v>0.444999992847443</v>
       </c>
       <c r="G1594" t="n">
-        <v>0.341906547546387</v>
+        <v>0.341906487941742</v>
       </c>
       <c r="H1594" t="n">
         <v>447565</v>
@@ -46711,7 +46711,7 @@
         <v>0.463499993085861</v>
       </c>
       <c r="G1598" t="n">
-        <v>0.356120616197586</v>
+        <v>0.356120556592941</v>
       </c>
       <c r="H1598" t="n">
         <v>304751</v>
@@ -46740,7 +46740,7 @@
         <v>0.465000003576279</v>
       </c>
       <c r="G1599" t="n">
-        <v>0.357273042201996</v>
+        <v>0.357273101806641</v>
       </c>
       <c r="H1599" t="n">
         <v>959895</v>
@@ -46827,7 +46827,7 @@
         <v>0.46900001168251</v>
       </c>
       <c r="G1602" t="n">
-        <v>0.360346406698227</v>
+        <v>0.360346436500549</v>
       </c>
       <c r="H1602" t="n">
         <v>509038</v>
@@ -46914,7 +46914,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1605" t="n">
-        <v>0.345748156309128</v>
+        <v>0.345748126506805</v>
       </c>
       <c r="H1605" t="n">
         <v>296945</v>
@@ -47001,7 +47001,7 @@
         <v>0.431499987840652</v>
       </c>
       <c r="G1608" t="n">
-        <v>0.331534057855606</v>
+        <v>0.331534028053284</v>
       </c>
       <c r="H1608" t="n">
         <v>130349</v>
@@ -47059,7 +47059,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G1610" t="n">
-        <v>0.338833212852478</v>
+        <v>0.338833183050156</v>
       </c>
       <c r="H1610" t="n">
         <v>237094</v>
@@ -47088,7 +47088,7 @@
         <v>0.44200000166893</v>
       </c>
       <c r="G1611" t="n">
-        <v>0.339601516723633</v>
+        <v>0.339601546525955</v>
       </c>
       <c r="H1611" t="n">
         <v>210502</v>
@@ -47378,7 +47378,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G1621" t="n">
-        <v>0.351594567298889</v>
+        <v>0.351594597101212</v>
       </c>
       <c r="H1621" t="n">
         <v>170521</v>
@@ -47407,7 +47407,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G1622" t="n">
-        <v>0.354064851999283</v>
+        <v>0.35406482219696</v>
       </c>
       <c r="H1622" t="n">
         <v>125247</v>
@@ -47465,7 +47465,7 @@
         <v>0.421999990940094</v>
       </c>
       <c r="G1624" t="n">
-        <v>0.347477555274963</v>
+        <v>0.347477585077286</v>
       </c>
       <c r="H1624" t="n">
         <v>233138</v>
@@ -47581,7 +47581,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G1628" t="n">
-        <v>0.354064851999283</v>
+        <v>0.35406482219696</v>
       </c>
       <c r="H1628" t="n">
         <v>312370</v>
@@ -47610,7 +47610,7 @@
         <v>0.423000007867813</v>
       </c>
       <c r="G1629" t="n">
-        <v>0.348300993442535</v>
+        <v>0.348301023244858</v>
       </c>
       <c r="H1629" t="n">
         <v>66544</v>
@@ -47639,7 +47639,7 @@
         <v>0.437000006437302</v>
       </c>
       <c r="G1630" t="n">
-        <v>0.359828680753708</v>
+        <v>0.35982871055603</v>
       </c>
       <c r="H1630" t="n">
         <v>165663</v>
@@ -47726,7 +47726,7 @@
         <v>0.425500005483627</v>
       </c>
       <c r="G1633" t="n">
-        <v>0.350359499454498</v>
+        <v>0.350359469652176</v>
       </c>
       <c r="H1633" t="n">
         <v>125419</v>
@@ -47842,7 +47842,7 @@
         <v>0.416500002145767</v>
       </c>
       <c r="G1637" t="n">
-        <v>0.342948853969574</v>
+        <v>0.342948824167252</v>
       </c>
       <c r="H1637" t="n">
         <v>108212</v>
@@ -47900,7 +47900,7 @@
         <v>0.405000001192093</v>
       </c>
       <c r="G1639" t="n">
-        <v>0.333479672670364</v>
+        <v>0.333479702472687</v>
       </c>
       <c r="H1639" t="n">
         <v>433862</v>
@@ -48045,7 +48045,7 @@
         <v>0.383500009775162</v>
       </c>
       <c r="G1644" t="n">
-        <v>0.315776437520981</v>
+        <v>0.315776407718658</v>
       </c>
       <c r="H1644" t="n">
         <v>145234</v>
@@ -48103,7 +48103,7 @@
         <v>0.379999995231628</v>
       </c>
       <c r="G1646" t="n">
-        <v>0.312894493341446</v>
+        <v>0.312894523143768</v>
       </c>
       <c r="H1646" t="n">
         <v>81077</v>
@@ -48161,7 +48161,7 @@
         <v>0.379999995231628</v>
       </c>
       <c r="G1648" t="n">
-        <v>0.312894493341446</v>
+        <v>0.312894523143768</v>
       </c>
       <c r="H1648" t="n">
         <v>78332</v>
@@ -48248,7 +48248,7 @@
         <v>0.379000008106232</v>
       </c>
       <c r="G1651" t="n">
-        <v>0.312071084976196</v>
+        <v>0.312071055173874</v>
       </c>
       <c r="H1651" t="n">
         <v>252848</v>
@@ -48335,7 +48335,7 @@
         <v>0.379000008106232</v>
       </c>
       <c r="G1654" t="n">
-        <v>0.312071084976196</v>
+        <v>0.312071055173874</v>
       </c>
       <c r="H1654" t="n">
         <v>112300</v>
@@ -48364,7 +48364,7 @@
         <v>0.381999999284744</v>
       </c>
       <c r="G1655" t="n">
-        <v>0.314541310071945</v>
+        <v>0.314541280269623</v>
       </c>
       <c r="H1655" t="n">
         <v>81447</v>
@@ -48393,7 +48393,7 @@
         <v>0.379999995231628</v>
       </c>
       <c r="G1656" t="n">
-        <v>0.312894493341446</v>
+        <v>0.312894523143768</v>
       </c>
       <c r="H1656" t="n">
         <v>78461</v>
@@ -48509,7 +48509,7 @@
         <v>0.391999989748001</v>
       </c>
       <c r="G1660" t="n">
-        <v>0.322775393724442</v>
+        <v>0.322775363922119</v>
       </c>
       <c r="H1660" t="n">
         <v>62823</v>
@@ -48538,7 +48538,7 @@
         <v>0.375999987125397</v>
       </c>
       <c r="G1661" t="n">
-        <v>0.30960088968277</v>
+        <v>0.309600859880447</v>
       </c>
       <c r="H1661" t="n">
         <v>77009</v>
@@ -48567,7 +48567,7 @@
         <v>0.383500009775162</v>
       </c>
       <c r="G1662" t="n">
-        <v>0.315776437520981</v>
+        <v>0.315776407718658</v>
       </c>
       <c r="H1662" t="n">
         <v>112230</v>
@@ -48596,7 +48596,7 @@
         <v>0.375499993562698</v>
       </c>
       <c r="G1663" t="n">
-        <v>0.309189140796661</v>
+        <v>0.309189170598984</v>
       </c>
       <c r="H1663" t="n">
         <v>81159</v>
@@ -48683,7 +48683,7 @@
         <v>0.391000002622604</v>
       </c>
       <c r="G1666" t="n">
-        <v>0.321951985359192</v>
+        <v>0.32195195555687</v>
       </c>
       <c r="H1666" t="n">
         <v>154090</v>
@@ -48712,7 +48712,7 @@
         <v>0.395000010728836</v>
       </c>
       <c r="G1667" t="n">
-        <v>0.325245589017868</v>
+        <v>0.32524561882019</v>
       </c>
       <c r="H1667" t="n">
         <v>78349</v>
@@ -48799,7 +48799,7 @@
         <v>0.391999989748001</v>
       </c>
       <c r="G1670" t="n">
-        <v>0.322775393724442</v>
+        <v>0.322775363922119</v>
       </c>
       <c r="H1670" t="n">
         <v>37842</v>
@@ -48886,7 +48886,7 @@
         <v>0.379999995231628</v>
       </c>
       <c r="G1673" t="n">
-        <v>0.312894493341446</v>
+        <v>0.312894523143768</v>
       </c>
       <c r="H1673" t="n">
         <v>209173</v>
@@ -48915,7 +48915,7 @@
         <v>0.382999986410141</v>
       </c>
       <c r="G1674" t="n">
-        <v>0.315364718437195</v>
+        <v>0.315364688634872</v>
       </c>
       <c r="H1674" t="n">
         <v>62062</v>
@@ -48973,7 +48973,7 @@
         <v>0.379999995231628</v>
       </c>
       <c r="G1676" t="n">
-        <v>0.312894493341446</v>
+        <v>0.312894523143768</v>
       </c>
       <c r="H1676" t="n">
         <v>272596</v>
@@ -49002,7 +49002,7 @@
         <v>0.379999995231628</v>
       </c>
       <c r="G1677" t="n">
-        <v>0.312894493341446</v>
+        <v>0.312894523143768</v>
       </c>
       <c r="H1677" t="n">
         <v>97607</v>
@@ -49060,7 +49060,7 @@
         <v>0.375499993562698</v>
       </c>
       <c r="G1679" t="n">
-        <v>0.309189140796661</v>
+        <v>0.309189170598984</v>
       </c>
       <c r="H1679" t="n">
         <v>319058</v>
@@ -49089,7 +49089,7 @@
         <v>0.375499993562698</v>
       </c>
       <c r="G1680" t="n">
-        <v>0.309189140796661</v>
+        <v>0.309189170598984</v>
       </c>
       <c r="H1680" t="n">
         <v>325064</v>
@@ -49176,7 +49176,7 @@
         <v>0.382499992847443</v>
       </c>
       <c r="G1683" t="n">
-        <v>0.314953029155731</v>
+        <v>0.314952999353409</v>
       </c>
       <c r="H1683" t="n">
         <v>298966</v>
@@ -49205,7 +49205,7 @@
         <v>0.377999991178513</v>
       </c>
       <c r="G1684" t="n">
-        <v>0.311247676610947</v>
+        <v>0.311247646808624</v>
       </c>
       <c r="H1684" t="n">
         <v>257059</v>
@@ -49263,7 +49263,7 @@
         <v>0.383500009775162</v>
       </c>
       <c r="G1686" t="n">
-        <v>0.315776437520981</v>
+        <v>0.315776407718658</v>
       </c>
       <c r="H1686" t="n">
         <v>186000</v>
@@ -49292,7 +49292,7 @@
         <v>0.381999999284744</v>
       </c>
       <c r="G1687" t="n">
-        <v>0.314541310071945</v>
+        <v>0.314541280269623</v>
       </c>
       <c r="H1687" t="n">
         <v>175543</v>
@@ -49379,7 +49379,7 @@
         <v>0.384999990463257</v>
       </c>
       <c r="G1690" t="n">
-        <v>0.317011535167694</v>
+        <v>0.317011505365372</v>
       </c>
       <c r="H1690" t="n">
         <v>45696</v>
@@ -49495,7 +49495,7 @@
         <v>0.382999986410141</v>
       </c>
       <c r="G1694" t="n">
-        <v>0.315364718437195</v>
+        <v>0.315364688634872</v>
       </c>
       <c r="H1694" t="n">
         <v>41860</v>
@@ -49553,7 +49553,7 @@
         <v>0.381999999284744</v>
       </c>
       <c r="G1696" t="n">
-        <v>0.314541310071945</v>
+        <v>0.314541280269623</v>
       </c>
       <c r="H1696" t="n">
         <v>95383</v>
@@ -49582,7 +49582,7 @@
         <v>0.379000008106232</v>
       </c>
       <c r="G1697" t="n">
-        <v>0.312071084976196</v>
+        <v>0.312071055173874</v>
       </c>
       <c r="H1697" t="n">
         <v>59890</v>
@@ -49669,7 +49669,7 @@
         <v>0.382999986410141</v>
       </c>
       <c r="G1700" t="n">
-        <v>0.315364718437195</v>
+        <v>0.315364688634872</v>
       </c>
       <c r="H1700" t="n">
         <v>75608</v>
@@ -49727,7 +49727,7 @@
         <v>0.38400000333786</v>
       </c>
       <c r="G1702" t="n">
-        <v>0.316188156604767</v>
+        <v>0.316188126802444</v>
       </c>
       <c r="H1702" t="n">
         <v>83696</v>
@@ -49785,7 +49785,7 @@
         <v>0.38400000333786</v>
       </c>
       <c r="G1704" t="n">
-        <v>0.316188156604767</v>
+        <v>0.316188126802444</v>
       </c>
       <c r="H1704" t="n">
         <v>143495</v>
@@ -49872,7 +49872,7 @@
         <v>0.382999986410141</v>
       </c>
       <c r="G1707" t="n">
-        <v>0.315364718437195</v>
+        <v>0.315364688634872</v>
       </c>
       <c r="H1707" t="n">
         <v>48600</v>
@@ -49988,7 +49988,7 @@
         <v>0.375499993562698</v>
       </c>
       <c r="G1711" t="n">
-        <v>0.309189140796661</v>
+        <v>0.309189170598984</v>
       </c>
       <c r="H1711" t="n">
         <v>31154</v>
@@ -50017,7 +50017,7 @@
         <v>0.375499993562698</v>
       </c>
       <c r="G1712" t="n">
-        <v>0.309189140796661</v>
+        <v>0.309189170598984</v>
       </c>
       <c r="H1712" t="n">
         <v>18723</v>
@@ -50046,7 +50046,7 @@
         <v>0.375</v>
       </c>
       <c r="G1713" t="n">
-        <v>0.30877748131752</v>
+        <v>0.308777421712875</v>
       </c>
       <c r="H1713" t="n">
         <v>81764</v>
@@ -50249,7 +50249,7 @@
         <v>0.375499993562698</v>
       </c>
       <c r="G1720" t="n">
-        <v>0.309189140796661</v>
+        <v>0.309189170598984</v>
       </c>
       <c r="H1720" t="n">
         <v>55721</v>
@@ -50278,7 +50278,7 @@
         <v>0.374000012874603</v>
       </c>
       <c r="G1721" t="n">
-        <v>0.307954072952271</v>
+        <v>0.307954043149948</v>
       </c>
       <c r="H1721" t="n">
         <v>14419</v>
@@ -50394,7 +50394,7 @@
         <v>0.368999987840652</v>
       </c>
       <c r="G1725" t="n">
-        <v>0.303837031126022</v>
+        <v>0.3038370013237</v>
       </c>
       <c r="H1725" t="n">
         <v>60987</v>
@@ -50452,7 +50452,7 @@
         <v>0.368999987840652</v>
       </c>
       <c r="G1727" t="n">
-        <v>0.303837031126022</v>
+        <v>0.3038370013237</v>
       </c>
       <c r="H1727" t="n">
         <v>31004</v>
@@ -50481,7 +50481,7 @@
         <v>0.368999987840652</v>
       </c>
       <c r="G1728" t="n">
-        <v>0.303837031126022</v>
+        <v>0.3038370013237</v>
       </c>
       <c r="H1728" t="n">
         <v>28531</v>
@@ -50539,7 +50539,7 @@
         <v>0.36599999666214</v>
       </c>
       <c r="G1730" t="n">
-        <v>0.301366806030273</v>
+        <v>0.301366776227951</v>
       </c>
       <c r="H1730" t="n">
         <v>147345</v>
@@ -50713,7 +50713,7 @@
         <v>0.375</v>
       </c>
       <c r="G1736" t="n">
-        <v>0.30877748131752</v>
+        <v>0.308777421712875</v>
       </c>
       <c r="H1736" t="n">
         <v>55960</v>
@@ -50887,7 +50887,7 @@
         <v>0.395000010728836</v>
       </c>
       <c r="G1742" t="n">
-        <v>0.325245589017868</v>
+        <v>0.32524561882019</v>
       </c>
       <c r="H1742" t="n">
         <v>35966</v>
@@ -50916,7 +50916,7 @@
         <v>0.398999989032745</v>
       </c>
       <c r="G1743" t="n">
-        <v>0.328539192676544</v>
+        <v>0.328539222478867</v>
       </c>
       <c r="H1743" t="n">
         <v>296612</v>
@@ -51148,7 +51148,7 @@
         <v>0.408499985933304</v>
       </c>
       <c r="G1751" t="n">
-        <v>0.336361587047577</v>
+        <v>0.336361557245255</v>
       </c>
       <c r="H1751" t="n">
         <v>132918</v>
@@ -51206,7 +51206,7 @@
         <v>0.407000005245209</v>
       </c>
       <c r="G1753" t="n">
-        <v>0.335126459598541</v>
+        <v>0.335126489400864</v>
       </c>
       <c r="H1753" t="n">
         <v>247806</v>
@@ -51264,7 +51264,7 @@
         <v>0.435000002384186</v>
       </c>
       <c r="G1755" t="n">
-        <v>0.358181834220886</v>
+        <v>0.358181893825531</v>
       </c>
       <c r="H1755" t="n">
         <v>635657</v>
@@ -51322,7 +51322,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G1757" t="n">
-        <v>0.344183951616287</v>
+        <v>0.34418398141861</v>
       </c>
       <c r="H1757" t="n">
         <v>55905</v>
@@ -51351,7 +51351,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G1758" t="n">
-        <v>0.336773276329041</v>
+        <v>0.336773306131363</v>
       </c>
       <c r="H1758" t="n">
         <v>567680</v>
@@ -51496,7 +51496,7 @@
         <v>0.416500002145767</v>
       </c>
       <c r="G1763" t="n">
-        <v>0.342948853969574</v>
+        <v>0.342948824167252</v>
       </c>
       <c r="H1763" t="n">
         <v>285113</v>
@@ -51583,7 +51583,7 @@
         <v>0.407999992370605</v>
       </c>
       <c r="G1766" t="n">
-        <v>0.335949867963791</v>
+        <v>0.335949897766113</v>
       </c>
       <c r="H1766" t="n">
         <v>173577</v>
@@ -51641,7 +51641,7 @@
         <v>0.417499989271164</v>
       </c>
       <c r="G1768" t="n">
-        <v>0.343772202730179</v>
+        <v>0.343772232532501</v>
       </c>
       <c r="H1768" t="n">
         <v>46000</v>
@@ -51699,7 +51699,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G1770" t="n">
-        <v>0.33759668469429</v>
+        <v>0.337596714496613</v>
       </c>
       <c r="H1770" t="n">
         <v>45232</v>
@@ -51844,7 +51844,7 @@
         <v>0.403499990701675</v>
       </c>
       <c r="G1775" t="n">
-        <v>0.332244515419006</v>
+        <v>0.332244545221329</v>
       </c>
       <c r="H1775" t="n">
         <v>152685</v>
@@ -51902,7 +51902,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G1777" t="n">
-        <v>0.336773276329041</v>
+        <v>0.336773306131363</v>
       </c>
       <c r="H1777" t="n">
         <v>8318</v>
@@ -52047,7 +52047,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G1782" t="n">
-        <v>0.33759668469429</v>
+        <v>0.337596714496613</v>
       </c>
       <c r="H1782" t="n">
         <v>184668</v>
@@ -52076,7 +52076,7 @@
         <v>0.407000005245209</v>
       </c>
       <c r="G1783" t="n">
-        <v>0.335126459598541</v>
+        <v>0.335126489400864</v>
       </c>
       <c r="H1783" t="n">
         <v>98882</v>
@@ -52134,7 +52134,7 @@
         <v>0.417499989271164</v>
       </c>
       <c r="G1785" t="n">
-        <v>0.343772202730179</v>
+        <v>0.343772232532501</v>
       </c>
       <c r="H1785" t="n">
         <v>101540</v>
@@ -52192,7 +52192,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G1787" t="n">
-        <v>0.33759668469429</v>
+        <v>0.337596714496613</v>
       </c>
       <c r="H1787" t="n">
         <v>62033</v>
@@ -52250,7 +52250,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G1789" t="n">
-        <v>0.33759668469429</v>
+        <v>0.337596714496613</v>
       </c>
       <c r="H1789" t="n">
         <v>141906</v>
@@ -52308,7 +52308,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G1791" t="n">
-        <v>0.33759668469429</v>
+        <v>0.337596714496613</v>
       </c>
       <c r="H1791" t="n">
         <v>181885</v>
@@ -52337,7 +52337,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G1792" t="n">
-        <v>0.336773276329041</v>
+        <v>0.336773306131363</v>
       </c>
       <c r="H1792" t="n">
         <v>137492</v>
@@ -52453,7 +52453,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G1796" t="n">
-        <v>0.359005212783813</v>
+        <v>0.359005242586136</v>
       </c>
       <c r="H1796" t="n">
         <v>2169503</v>
@@ -52540,7 +52540,7 @@
         <v>0.463499993085861</v>
       </c>
       <c r="G1799" t="n">
-        <v>0.381648987531662</v>
+        <v>0.38164895772934</v>
       </c>
       <c r="H1799" t="n">
         <v>647457</v>
@@ -52627,7 +52627,7 @@
         <v>0.485500007867813</v>
       </c>
       <c r="G1802" t="n">
-        <v>0.399763882160187</v>
+        <v>0.399763911962509</v>
       </c>
       <c r="H1802" t="n">
         <v>765228</v>
@@ -52656,7 +52656,7 @@
         <v>0.47299998998642</v>
       </c>
       <c r="G1803" t="n">
-        <v>0.389471292495728</v>
+        <v>0.38947132229805</v>
       </c>
       <c r="H1803" t="n">
         <v>583366</v>
@@ -52685,7 +52685,7 @@
         <v>0.488000005483627</v>
       </c>
       <c r="G1804" t="n">
-        <v>0.401822447776794</v>
+        <v>0.401822417974472</v>
       </c>
       <c r="H1804" t="n">
         <v>1085002</v>
@@ -52772,7 +52772,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G1807" t="n">
-        <v>0.403469234704971</v>
+        <v>0.403469264507294</v>
       </c>
       <c r="H1807" t="n">
         <v>462039</v>
@@ -52830,7 +52830,7 @@
         <v>0.495999991893768</v>
       </c>
       <c r="G1809" t="n">
-        <v>0.408409684896469</v>
+        <v>0.408409655094147</v>
       </c>
       <c r="H1809" t="n">
         <v>111073</v>
@@ -52859,7 +52859,7 @@
         <v>0.493000000715256</v>
       </c>
       <c r="G1810" t="n">
-        <v>0.40593945980072</v>
+        <v>0.405939429998398</v>
       </c>
       <c r="H1810" t="n">
         <v>482414</v>
@@ -52888,7 +52888,7 @@
         <v>0.493000000715256</v>
       </c>
       <c r="G1811" t="n">
-        <v>0.40593945980072</v>
+        <v>0.405939429998398</v>
       </c>
       <c r="H1811" t="n">
         <v>516711</v>
@@ -53004,7 +53004,7 @@
         <v>0.483000010251999</v>
       </c>
       <c r="G1815" t="n">
-        <v>0.397705376148224</v>
+        <v>0.397705405950546</v>
       </c>
       <c r="H1815" t="n">
         <v>462612</v>
@@ -53033,7 +53033,7 @@
         <v>0.490500003099442</v>
       </c>
       <c r="G1816" t="n">
-        <v>0.403880923986435</v>
+        <v>0.403880953788757</v>
       </c>
       <c r="H1816" t="n">
         <v>390012</v>
@@ -53062,7 +53062,7 @@
         <v>0.483000010251999</v>
       </c>
       <c r="G1817" t="n">
-        <v>0.397705376148224</v>
+        <v>0.397705405950546</v>
       </c>
       <c r="H1817" t="n">
         <v>579159</v>
@@ -53149,7 +53149,7 @@
         <v>0.479499995708466</v>
       </c>
       <c r="G1820" t="n">
-        <v>0.394823491573334</v>
+        <v>0.394823461771011</v>
       </c>
       <c r="H1820" t="n">
         <v>682797</v>
@@ -53207,7 +53207,7 @@
         <v>0.507000029087067</v>
       </c>
       <c r="G1822" t="n">
-        <v>0.417467176914215</v>
+        <v>0.417467206716537</v>
       </c>
       <c r="H1822" t="n">
         <v>578557</v>
@@ -53236,7 +53236,7 @@
         <v>0.526000022888184</v>
       </c>
       <c r="G1823" t="n">
-        <v>0.433111876249313</v>
+        <v>0.433111846446991</v>
       </c>
       <c r="H1823" t="n">
         <v>2252434</v>
@@ -53265,7 +53265,7 @@
         <v>0.523000001907349</v>
       </c>
       <c r="G1824" t="n">
-        <v>0.430641651153564</v>
+        <v>0.430641621351242</v>
       </c>
       <c r="H1824" t="n">
         <v>1003953</v>
@@ -53323,7 +53323,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G1826" t="n">
-        <v>0.454520404338837</v>
+        <v>0.454520434141159</v>
       </c>
       <c r="H1826" t="n">
         <v>1717611</v>
@@ -53381,7 +53381,7 @@
         <v>0.592999994754791</v>
       </c>
       <c r="G1828" t="n">
-        <v>0.488280177116394</v>
+        <v>0.488280147314072</v>
       </c>
       <c r="H1828" t="n">
         <v>3495608</v>
@@ -53439,7 +53439,7 @@
         <v>0.648999989032745</v>
       </c>
       <c r="G1830" t="n">
-        <v>0.534390866756439</v>
+        <v>0.534390926361084</v>
       </c>
       <c r="H1830" t="n">
         <v>2319403</v>
@@ -53497,7 +53497,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1832" t="n">
-        <v>0.522039711475372</v>
+        <v>0.522039771080017</v>
       </c>
       <c r="H1832" t="n">
         <v>2768663</v>
@@ -53613,7 +53613,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1836" t="n">
-        <v>0.485809832811356</v>
+        <v>0.485809862613678</v>
       </c>
       <c r="H1836" t="n">
         <v>776833</v>
@@ -53758,7 +53758,7 @@
         <v>0.598999977111816</v>
       </c>
       <c r="G1841" t="n">
-        <v>0.493220567703247</v>
+        <v>0.493220597505569</v>
       </c>
       <c r="H1841" t="n">
         <v>1904674</v>
@@ -53787,7 +53787,7 @@
         <v>0.597000002861023</v>
       </c>
       <c r="G1842" t="n">
-        <v>0.491573691368103</v>
+        <v>0.491573661565781</v>
       </c>
       <c r="H1842" t="n">
         <v>825059</v>
@@ -53932,7 +53932,7 @@
         <v>0.578999996185303</v>
       </c>
       <c r="G1847" t="n">
-        <v>0.476752430200577</v>
+        <v>0.476752400398254</v>
       </c>
       <c r="H1847" t="n">
         <v>530149</v>
@@ -53990,7 +53990,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G1849" t="n">
-        <v>0.479222655296326</v>
+        <v>0.479222625494003</v>
       </c>
       <c r="H1849" t="n">
         <v>282957</v>
@@ -54019,7 +54019,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1850" t="n">
-        <v>0.477575838565826</v>
+        <v>0.477575868368149</v>
       </c>
       <c r="H1850" t="n">
         <v>156316</v>
@@ -54048,7 +54048,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1851" t="n">
-        <v>0.477575838565826</v>
+        <v>0.477575868368149</v>
       </c>
       <c r="H1851" t="n">
         <v>1518646</v>
@@ -54077,7 +54077,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1852" t="n">
-        <v>0.485809832811356</v>
+        <v>0.485809862613678</v>
       </c>
       <c r="H1852" t="n">
         <v>247487</v>
@@ -54164,7 +54164,7 @@
         <v>0.609000027179718</v>
       </c>
       <c r="G1855" t="n">
-        <v>0.501454651355743</v>
+        <v>0.501454591751099</v>
       </c>
       <c r="H1855" t="n">
         <v>466043</v>
@@ -54193,7 +54193,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G1856" t="n">
-        <v>0.498984396457672</v>
+        <v>0.498984336853027</v>
       </c>
       <c r="H1856" t="n">
         <v>384828</v>
@@ -54280,7 +54280,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G1859" t="n">
-        <v>0.490750342607498</v>
+        <v>0.490750372409821</v>
       </c>
       <c r="H1859" t="n">
         <v>533019</v>
@@ -54338,7 +54338,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1861" t="n">
-        <v>0.492397159337997</v>
+        <v>0.49239718914032</v>
       </c>
       <c r="H1861" t="n">
         <v>266686</v>
@@ -54367,7 +54367,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1862" t="n">
-        <v>0.482516258955002</v>
+        <v>0.482516288757324</v>
       </c>
       <c r="H1862" t="n">
         <v>414253</v>
@@ -54396,7 +54396,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G1863" t="n">
-        <v>0.479222655296326</v>
+        <v>0.479222625494003</v>
       </c>
       <c r="H1863" t="n">
         <v>392940</v>
@@ -54454,7 +54454,7 @@
         <v>0.580999970436096</v>
       </c>
       <c r="G1865" t="n">
-        <v>0.478399127721786</v>
+        <v>0.478399157524109</v>
       </c>
       <c r="H1865" t="n">
         <v>635783</v>
@@ -54541,7 +54541,7 @@
         <v>0.572000026702881</v>
       </c>
       <c r="G1868" t="n">
-        <v>0.470988571643829</v>
+        <v>0.470988601446152</v>
       </c>
       <c r="H1868" t="n">
         <v>352772</v>
@@ -54599,7 +54599,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G1870" t="n">
-        <v>0.490750342607498</v>
+        <v>0.490750372409821</v>
       </c>
       <c r="H1870" t="n">
         <v>238389</v>
@@ -54628,7 +54628,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1871" t="n">
-        <v>0.485809832811356</v>
+        <v>0.485809862613678</v>
       </c>
       <c r="H1871" t="n">
         <v>257011</v>
@@ -54657,7 +54657,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1872" t="n">
-        <v>0.492397159337997</v>
+        <v>0.49239718914032</v>
       </c>
       <c r="H1872" t="n">
         <v>481519</v>
@@ -54715,7 +54715,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G1874" t="n">
-        <v>0.479222655296326</v>
+        <v>0.479222625494003</v>
       </c>
       <c r="H1874" t="n">
         <v>506422</v>
@@ -54744,7 +54744,7 @@
         <v>0.570999979972839</v>
       </c>
       <c r="G1875" t="n">
-        <v>0.470165193080902</v>
+        <v>0.47016516327858</v>
       </c>
       <c r="H1875" t="n">
         <v>320961</v>
@@ -54802,7 +54802,7 @@
         <v>0.564999997615814</v>
       </c>
       <c r="G1877" t="n">
-        <v>0.46522468328476</v>
+        <v>0.465224713087082</v>
       </c>
       <c r="H1877" t="n">
         <v>329202</v>
@@ -54860,7 +54860,7 @@
         <v>0.569000005722046</v>
       </c>
       <c r="G1879" t="n">
-        <v>0.468518316745758</v>
+        <v>0.46851834654808</v>
       </c>
       <c r="H1879" t="n">
         <v>457357</v>
@@ -54918,7 +54918,7 @@
         <v>0.53600001335144</v>
       </c>
       <c r="G1881" t="n">
-        <v>0.473822295665741</v>
+        <v>0.473822325468063</v>
       </c>
       <c r="H1881" t="n">
         <v>243623</v>
@@ -55063,7 +55063,7 @@
         <v>0.499000012874603</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.441114455461502</v>
+        <v>0.441114485263824</v>
       </c>
       <c r="H1886" t="n">
         <v>401308</v>
@@ -55121,7 +55121,7 @@
         <v>0.493000000715256</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.435810476541519</v>
+        <v>0.435810446739197</v>
       </c>
       <c r="H1888" t="n">
         <v>211129</v>
@@ -55150,7 +55150,7 @@
         <v>0.495999991893768</v>
       </c>
       <c r="G1889" t="n">
-        <v>0.438462466001511</v>
+        <v>0.438462436199188</v>
       </c>
       <c r="H1889" t="n">
         <v>104085</v>
@@ -55353,7 +55353,7 @@
         <v>0.503000020980835</v>
       </c>
       <c r="G1896" t="n">
-        <v>0.44465047121048</v>
+        <v>0.444650441408157</v>
       </c>
       <c r="H1896" t="n">
         <v>137077</v>
@@ -55411,7 +55411,7 @@
         <v>0.495000004768372</v>
       </c>
       <c r="G1898" t="n">
-        <v>0.437578469514847</v>
+        <v>0.437578439712524</v>
       </c>
       <c r="H1898" t="n">
         <v>75639</v>
@@ -55498,7 +55498,7 @@
         <v>0.488000005483627</v>
       </c>
       <c r="G1901" t="n">
-        <v>0.4313904941082</v>
+        <v>0.431390464305878</v>
       </c>
       <c r="H1901" t="n">
         <v>156473</v>
@@ -55527,7 +55527,7 @@
         <v>0.492000013589859</v>
       </c>
       <c r="G1902" t="n">
-        <v>0.434926450252533</v>
+        <v>0.434926480054855</v>
       </c>
       <c r="H1902" t="n">
         <v>227078</v>
@@ -55643,7 +55643,7 @@
         <v>0.485000014305115</v>
       </c>
       <c r="G1906" t="n">
-        <v>0.428738504648209</v>
+        <v>0.428738474845886</v>
       </c>
       <c r="H1906" t="n">
         <v>742245</v>
@@ -55672,7 +55672,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1907" t="n">
-        <v>0.424318492412567</v>
+        <v>0.424318462610245</v>
       </c>
       <c r="H1907" t="n">
         <v>408236</v>
@@ -55730,7 +55730,7 @@
         <v>0.49099999666214</v>
       </c>
       <c r="G1909" t="n">
-        <v>0.434042453765869</v>
+        <v>0.434042483568192</v>
       </c>
       <c r="H1909" t="n">
         <v>166903</v>
@@ -55817,7 +55817,7 @@
         <v>0.495000004768372</v>
       </c>
       <c r="G1912" t="n">
-        <v>0.437578469514847</v>
+        <v>0.437578439712524</v>
       </c>
       <c r="H1912" t="n">
         <v>1576478</v>
@@ -56049,7 +56049,7 @@
         <v>0.46849998831749</v>
       </c>
       <c r="G1920" t="n">
-        <v>0.414152503013611</v>
+        <v>0.414152532815933</v>
       </c>
       <c r="H1920" t="n">
         <v>241945</v>
@@ -56078,7 +56078,7 @@
         <v>0.47299998998642</v>
       </c>
       <c r="G1921" t="n">
-        <v>0.418130487203598</v>
+        <v>0.41813051700592</v>
       </c>
       <c r="H1921" t="n">
         <v>374428</v>
@@ -56194,7 +56194,7 @@
         <v>0.481000006198883</v>
       </c>
       <c r="G1925" t="n">
-        <v>0.425202459096909</v>
+        <v>0.425202488899231</v>
       </c>
       <c r="H1925" t="n">
         <v>320604</v>
@@ -56223,7 +56223,7 @@
         <v>0.479499995708466</v>
       </c>
       <c r="G1926" t="n">
-        <v>0.423876523971558</v>
+        <v>0.423876494169235</v>
       </c>
       <c r="H1926" t="n">
         <v>119608</v>
@@ -56339,7 +56339,7 @@
         <v>0.481000006198883</v>
       </c>
       <c r="G1930" t="n">
-        <v>0.425202459096909</v>
+        <v>0.425202488899231</v>
       </c>
       <c r="H1930" t="n">
         <v>240437</v>
@@ -56368,7 +56368,7 @@
         <v>0.47299998998642</v>
       </c>
       <c r="G1931" t="n">
-        <v>0.418130487203598</v>
+        <v>0.41813051700592</v>
       </c>
       <c r="H1931" t="n">
         <v>270522</v>
@@ -56484,7 +56484,7 @@
         <v>0.46849998831749</v>
       </c>
       <c r="G1935" t="n">
-        <v>0.414152503013611</v>
+        <v>0.414152532815933</v>
       </c>
       <c r="H1935" t="n">
         <v>87538</v>
@@ -56716,7 +56716,7 @@
         <v>0.461499989032745</v>
       </c>
       <c r="G1943" t="n">
-        <v>0.407964557409286</v>
+        <v>0.407964527606964</v>
       </c>
       <c r="H1943" t="n">
         <v>209838</v>
@@ -56803,7 +56803,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1946" t="n">
-        <v>0.424318492412567</v>
+        <v>0.424318462610245</v>
       </c>
       <c r="H1946" t="n">
         <v>502893</v>
@@ -56832,7 +56832,7 @@
         <v>0.475499987602234</v>
       </c>
       <c r="G1947" t="n">
-        <v>0.42034050822258</v>
+        <v>0.420340538024902</v>
       </c>
       <c r="H1947" t="n">
         <v>192878</v>
@@ -56890,7 +56890,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1949" t="n">
-        <v>0.424318492412567</v>
+        <v>0.424318462610245</v>
       </c>
       <c r="H1949" t="n">
         <v>179559</v>
@@ -56948,7 +56948,7 @@
         <v>0.48199999332428</v>
       </c>
       <c r="G1951" t="n">
-        <v>0.426086485385895</v>
+        <v>0.426086515188217</v>
       </c>
       <c r="H1951" t="n">
         <v>207593</v>
@@ -57064,7 +57064,7 @@
         <v>0.49099999666214</v>
       </c>
       <c r="G1955" t="n">
-        <v>0.434042453765869</v>
+        <v>0.434042483568192</v>
       </c>
       <c r="H1955" t="n">
         <v>454310</v>
@@ -57151,7 +57151,7 @@
         <v>0.488000005483627</v>
       </c>
       <c r="G1958" t="n">
-        <v>0.4313904941082</v>
+        <v>0.431390464305878</v>
       </c>
       <c r="H1958" t="n">
         <v>525343</v>
@@ -57180,7 +57180,7 @@
         <v>0.479499995708466</v>
       </c>
       <c r="G1959" t="n">
-        <v>0.423876523971558</v>
+        <v>0.423876494169235</v>
       </c>
       <c r="H1959" t="n">
         <v>274068</v>
@@ -57267,7 +57267,7 @@
         <v>0.469999998807907</v>
       </c>
       <c r="G1962" t="n">
-        <v>0.415478527545929</v>
+        <v>0.415478497743607</v>
       </c>
       <c r="H1962" t="n">
         <v>350501</v>
@@ -57528,7 +57528,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G1971" t="n">
-        <v>0.396030634641647</v>
+        <v>0.396030604839325</v>
       </c>
       <c r="H1971" t="n">
         <v>1096924</v>
@@ -57615,7 +57615,7 @@
         <v>0.456499993801117</v>
       </c>
       <c r="G1974" t="n">
-        <v>0.403544574975967</v>
+        <v>0.403544545173645</v>
       </c>
       <c r="H1974" t="n">
         <v>122727</v>
@@ -57789,7 +57789,7 @@
         <v>0.444999992847443</v>
       </c>
       <c r="G1980" t="n">
-        <v>0.393378615379333</v>
+        <v>0.393378645181656</v>
       </c>
       <c r="H1980" t="n">
         <v>124352</v>
@@ -57963,7 +57963,7 @@
         <v>0.456000000238419</v>
       </c>
       <c r="G1986" t="n">
-        <v>0.403102576732635</v>
+        <v>0.403102546930313</v>
       </c>
       <c r="H1986" t="n">
         <v>215250</v>
@@ -58021,7 +58021,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1988" t="n">
-        <v>0.39779856801033</v>
+        <v>0.397798597812653</v>
       </c>
       <c r="H1988" t="n">
         <v>350072</v>
@@ -58108,7 +58108,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1991" t="n">
-        <v>0.39779856801033</v>
+        <v>0.397798597812653</v>
       </c>
       <c r="H1991" t="n">
         <v>362590</v>
@@ -58282,7 +58282,7 @@
         <v>0.469999998807907</v>
       </c>
       <c r="G1997" t="n">
-        <v>0.415478527545929</v>
+        <v>0.415478497743607</v>
       </c>
       <c r="H1997" t="n">
         <v>143450</v>
@@ -58427,7 +58427,7 @@
         <v>0.474999994039536</v>
       </c>
       <c r="G2002" t="n">
-        <v>0.419898509979248</v>
+        <v>0.419898480176926</v>
       </c>
       <c r="H2002" t="n">
         <v>834020</v>
@@ -58485,7 +58485,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G2004" t="n">
-        <v>0.424318492412567</v>
+        <v>0.424318462610245</v>
       </c>
       <c r="H2004" t="n">
         <v>395506</v>
@@ -58514,7 +58514,7 @@
         <v>0.488000005483627</v>
       </c>
       <c r="G2005" t="n">
-        <v>0.4313904941082</v>
+        <v>0.431390464305878</v>
       </c>
       <c r="H2005" t="n">
         <v>289841</v>
@@ -80096,6 +80096,35 @@
         <v>250273</v>
       </c>
       <c r="I2749" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2750">
+      <c r="A2750" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2750" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2750" t="n">
+        <v>0.515999972820282</v>
+      </c>
+      <c r="D2750" t="n">
+        <v>0.515999972820282</v>
+      </c>
+      <c r="E2750" t="n">
+        <v>0.510999977588654</v>
+      </c>
+      <c r="F2750" t="n">
+        <v>0.514999985694885</v>
+      </c>
+      <c r="G2750" t="n">
+        <v>0.514999985694885</v>
+      </c>
+      <c r="H2750" t="n">
+        <v>52304</v>
+      </c>
+      <c r="I2750" t="s">
         <v>9</v>
       </c>
     </row>
